--- a/PCE06D.xlsx
+++ b/PCE06D.xlsx
@@ -478,129 +478,153 @@
     <t>23</t>
   </si>
   <si>
+    <t>20088631</t>
+  </si>
+  <si>
+    <t>CLS UP WHT LMN SLT95</t>
+  </si>
+  <si>
+    <t>20029646</t>
+  </si>
+  <si>
+    <t>CLOSE UP ICY WHT 160</t>
+  </si>
+  <si>
+    <t>20125623</t>
+  </si>
+  <si>
+    <t>CLS UP FR MLTVTMN160</t>
+  </si>
+  <si>
+    <t>20040702</t>
+  </si>
+  <si>
+    <t>PEPSODENT FRSH/CL190</t>
+  </si>
+  <si>
+    <t>20047217</t>
+  </si>
+  <si>
+    <t>PEPSODENT WHITE 225G</t>
+  </si>
+  <si>
+    <t>20087525</t>
+  </si>
+  <si>
+    <t>PPSODENT PG WHITE2'S</t>
+  </si>
+  <si>
+    <t>PT,(E-2B)</t>
+  </si>
+  <si>
+    <t>20118537</t>
+  </si>
+  <si>
+    <t>PSODENT WHT 120+30G</t>
+  </si>
+  <si>
+    <t>20041266</t>
+  </si>
+  <si>
+    <t>PEPSODENT ACT COM190</t>
+  </si>
+  <si>
+    <t>10004714</t>
+  </si>
+  <si>
+    <t>PEPSODENT WHITE 120G</t>
+  </si>
+  <si>
+    <t>10004048</t>
+  </si>
+  <si>
+    <t>PEPSODENT WHITE 72G</t>
+  </si>
+  <si>
+    <t>20092076</t>
+  </si>
+  <si>
+    <t>PSODENT PG CHARC 160</t>
+  </si>
+  <si>
+    <t>10025411</t>
+  </si>
+  <si>
+    <t>PEPSODENT ACT+WHT190</t>
+  </si>
+  <si>
+    <t>20136643</t>
+  </si>
+  <si>
+    <t>PSODENT PG STRG 190G</t>
+  </si>
+  <si>
+    <t>10025410</t>
+  </si>
+  <si>
+    <t>PEPSODENT ACT+WHT75</t>
+  </si>
+  <si>
+    <t>20017141</t>
+  </si>
+  <si>
+    <t>PPSODENT PG C.FRS160</t>
+  </si>
+  <si>
+    <t>20108708</t>
+  </si>
+  <si>
+    <t>PEPSODENT COMP8 150G</t>
+  </si>
+  <si>
+    <t>20048211</t>
+  </si>
+  <si>
+    <t>SYSTEMA PG MNT/B 190</t>
+  </si>
+  <si>
+    <t>20108465</t>
+  </si>
+  <si>
+    <t>DARLIE PG FRS.CLN150</t>
+  </si>
+  <si>
+    <t>20141837</t>
+  </si>
+  <si>
+    <t>PEPSODENT PG FIFA95</t>
+  </si>
+  <si>
+    <t>20035686</t>
+  </si>
+  <si>
+    <t>PEPSODENT SSTV EX100</t>
+  </si>
+  <si>
+    <t>20038203</t>
+  </si>
+  <si>
+    <t>ENZIM PG 40 PLS 124G</t>
+  </si>
+  <si>
+    <t>10003163</t>
+  </si>
+  <si>
+    <t>ENZIM PG MINT 124G</t>
+  </si>
+  <si>
+    <t>20042026</t>
+  </si>
+  <si>
+    <t>LSTERINE GRN.TEA 100</t>
+  </si>
+  <si>
     <t>20017349</t>
   </si>
   <si>
     <t>LSTERINE CL.MINT 100</t>
   </si>
   <si>
-    <t>20042026</t>
-  </si>
-  <si>
-    <t>LSTERINE GRN.TEA 100</t>
-  </si>
-  <si>
-    <t>20088631</t>
-  </si>
-  <si>
-    <t>CLS UP WHT LMN SLT95</t>
-  </si>
-  <si>
-    <t>20029646</t>
-  </si>
-  <si>
-    <t>CLOSE UP ICY WHT 160</t>
-  </si>
-  <si>
-    <t>20125623</t>
-  </si>
-  <si>
-    <t>CLS UP FR MLTVTMN160</t>
-  </si>
-  <si>
-    <t>20040702</t>
-  </si>
-  <si>
-    <t>PEPSODENT FRSH/CL190</t>
-  </si>
-  <si>
-    <t>20047217</t>
-  </si>
-  <si>
-    <t>PEPSODENT WHITE 225G</t>
-  </si>
-  <si>
-    <t>20087525</t>
-  </si>
-  <si>
-    <t>PPSODENT PG WHITE2'S</t>
-  </si>
-  <si>
-    <t>PT,(E-2B)</t>
-  </si>
-  <si>
-    <t>20118537</t>
-  </si>
-  <si>
-    <t>PSODENT WHT 120+30G</t>
-  </si>
-  <si>
-    <t>20041266</t>
-  </si>
-  <si>
-    <t>PEPSODENT ACT COM190</t>
-  </si>
-  <si>
-    <t>10004714</t>
-  </si>
-  <si>
-    <t>PEPSODENT WHITE 120G</t>
-  </si>
-  <si>
-    <t>10004048</t>
-  </si>
-  <si>
-    <t>PEPSODENT WHITE 72G</t>
-  </si>
-  <si>
-    <t>20092076</t>
-  </si>
-  <si>
-    <t>PSODENT PG CHARC 160</t>
-  </si>
-  <si>
-    <t>10025411</t>
-  </si>
-  <si>
-    <t>PEPSODENT ACT+WHT190</t>
-  </si>
-  <si>
-    <t>20136643</t>
-  </si>
-  <si>
-    <t>PSODENT PG STRG 190G</t>
-  </si>
-  <si>
-    <t>10025410</t>
-  </si>
-  <si>
-    <t>PEPSODENT ACT+WHT75</t>
-  </si>
-  <si>
-    <t>20017141</t>
-  </si>
-  <si>
-    <t>PPSODENT PG C.FRS160</t>
-  </si>
-  <si>
-    <t>20108708</t>
-  </si>
-  <si>
-    <t>PEPSODENT COMP8 150G</t>
-  </si>
-  <si>
-    <t>20048211</t>
-  </si>
-  <si>
-    <t>SYSTEMA PG MNT/B 190</t>
-  </si>
-  <si>
-    <t>20108465</t>
-  </si>
-  <si>
-    <t>DARLIE PG FRS.CLN150</t>
-  </si>
-  <si>
     <t>10012742</t>
   </si>
   <si>
@@ -655,30 +679,6 @@
     <t>CLOSE UP TRAVEL KIT</t>
   </si>
   <si>
-    <t>10003163</t>
-  </si>
-  <si>
-    <t>ENZIM PG MINT 124G</t>
-  </si>
-  <si>
-    <t>20038203</t>
-  </si>
-  <si>
-    <t>ENZIM PG 40 PLS 124G</t>
-  </si>
-  <si>
-    <t>20035686</t>
-  </si>
-  <si>
-    <t>PEPSODENT SSTV EX100</t>
-  </si>
-  <si>
-    <t>20141837</t>
-  </si>
-  <si>
-    <t>PEPSODENT PG FIFA95</t>
-  </si>
-  <si>
     <t>20024922</t>
   </si>
   <si>
@@ -3745,7 +3745,7 @@
     <t>20108294</t>
   </si>
   <si>
-    <t>ROMANO EDT ATTDE 100</t>
+    <t>ROMANO EDP ATTDE 100</t>
   </si>
   <si>
     <t>20125158</t>
@@ -6005,7 +6005,7 @@
         <v>4</v>
       </c>
       <c r="F63" s="1" t="s">
-        <v>5</v>
+        <v>13</v>
       </c>
     </row>
     <row r="64" spans="1:6" x14ac:dyDescent="0.25">
@@ -6025,7 +6025,7 @@
         <v>8</v>
       </c>
       <c r="F64" s="1" t="s">
-        <v>5</v>
+        <v>123</v>
       </c>
     </row>
     <row r="65" spans="1:6" x14ac:dyDescent="0.25">
@@ -6105,15 +6105,15 @@
         <v>19</v>
       </c>
       <c r="F68" s="1" t="s">
-        <v>123</v>
+        <v>167</v>
       </c>
     </row>
     <row r="69" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A69" s="1" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="B69" s="1" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="C69" s="1" t="s">
         <v>3</v>
@@ -6130,10 +6130,10 @@
     </row>
     <row r="70" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A70" s="1" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="B70" s="1" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="C70" s="1" t="s">
         <v>3</v>
@@ -6145,7 +6145,7 @@
         <v>25</v>
       </c>
       <c r="F70" s="1" t="s">
-        <v>171</v>
+        <v>123</v>
       </c>
     </row>
     <row r="71" spans="1:6" x14ac:dyDescent="0.25">
@@ -6165,7 +6165,7 @@
         <v>28</v>
       </c>
       <c r="F71" s="1" t="s">
-        <v>13</v>
+        <v>123</v>
       </c>
     </row>
     <row r="72" spans="1:6" x14ac:dyDescent="0.25">
@@ -6205,7 +6205,7 @@
         <v>35</v>
       </c>
       <c r="F73" s="1" t="s">
-        <v>123</v>
+        <v>13</v>
       </c>
     </row>
     <row r="74" spans="1:6" x14ac:dyDescent="0.25">
@@ -6285,7 +6285,7 @@
         <v>96</v>
       </c>
       <c r="F77" s="1" t="s">
-        <v>13</v>
+        <v>123</v>
       </c>
     </row>
     <row r="78" spans="1:6" x14ac:dyDescent="0.25">
@@ -6305,7 +6305,7 @@
         <v>99</v>
       </c>
       <c r="F78" s="1" t="s">
-        <v>123</v>
+        <v>13</v>
       </c>
     </row>
     <row r="79" spans="1:6" x14ac:dyDescent="0.25">
@@ -6325,7 +6325,7 @@
         <v>136</v>
       </c>
       <c r="F79" s="1" t="s">
-        <v>123</v>
+        <v>5</v>
       </c>
     </row>
     <row r="80" spans="1:6" x14ac:dyDescent="0.25">
@@ -6345,7 +6345,7 @@
         <v>139</v>
       </c>
       <c r="F80" s="1" t="s">
-        <v>13</v>
+        <v>5</v>
       </c>
     </row>
     <row r="81" spans="1:6" x14ac:dyDescent="0.25">
@@ -6365,7 +6365,7 @@
         <v>142</v>
       </c>
       <c r="F81" s="1" t="s">
-        <v>5</v>
+        <v>120</v>
       </c>
     </row>
     <row r="82" spans="1:6" x14ac:dyDescent="0.25">
@@ -6385,7 +6385,7 @@
         <v>145</v>
       </c>
       <c r="F82" s="1" t="s">
-        <v>5</v>
+        <v>123</v>
       </c>
     </row>
     <row r="83" spans="1:6" x14ac:dyDescent="0.25">
@@ -6399,10 +6399,10 @@
         <v>3</v>
       </c>
       <c r="D83" s="1" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="E83" s="1" t="s">
-        <v>4</v>
+        <v>148</v>
       </c>
       <c r="F83" s="1" t="s">
         <v>5</v>
@@ -6419,10 +6419,10 @@
         <v>3</v>
       </c>
       <c r="D84" s="1" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="E84" s="1" t="s">
-        <v>8</v>
+        <v>151</v>
       </c>
       <c r="F84" s="1" t="s">
         <v>5</v>
@@ -6442,7 +6442,7 @@
         <v>19</v>
       </c>
       <c r="E85" s="1" t="s">
-        <v>45</v>
+        <v>4</v>
       </c>
       <c r="F85" s="1" t="s">
         <v>5</v>
@@ -6462,10 +6462,10 @@
         <v>19</v>
       </c>
       <c r="E86" s="1" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="F86" s="1" t="s">
-        <v>29</v>
+        <v>5</v>
       </c>
     </row>
     <row r="87" spans="1:6" x14ac:dyDescent="0.25">
@@ -6482,7 +6482,7 @@
         <v>19</v>
       </c>
       <c r="E87" s="1" t="s">
-        <v>16</v>
+        <v>45</v>
       </c>
       <c r="F87" s="1" t="s">
         <v>5</v>
@@ -6502,10 +6502,10 @@
         <v>19</v>
       </c>
       <c r="E88" s="1" t="s">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="F88" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="89" spans="1:6" x14ac:dyDescent="0.25">
@@ -6522,10 +6522,10 @@
         <v>19</v>
       </c>
       <c r="E89" s="1" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="F89" s="1" t="s">
-        <v>13</v>
+        <v>5</v>
       </c>
     </row>
     <row r="90" spans="1:6" x14ac:dyDescent="0.25">
@@ -6542,10 +6542,10 @@
         <v>19</v>
       </c>
       <c r="E90" s="1" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="F90" s="1" t="s">
-        <v>9</v>
+        <v>29</v>
       </c>
     </row>
     <row r="91" spans="1:6" x14ac:dyDescent="0.25">
@@ -6562,10 +6562,10 @@
         <v>19</v>
       </c>
       <c r="E91" s="1" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="F91" s="1" t="s">
-        <v>13</v>
+        <v>5</v>
       </c>
     </row>
     <row r="92" spans="1:6" x14ac:dyDescent="0.25">
@@ -6582,10 +6582,10 @@
         <v>19</v>
       </c>
       <c r="E92" s="1" t="s">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="F92" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="93" spans="1:6" x14ac:dyDescent="0.25">
@@ -6602,10 +6602,10 @@
         <v>19</v>
       </c>
       <c r="E93" s="1" t="s">
-        <v>35</v>
+        <v>28</v>
       </c>
       <c r="F93" s="1" t="s">
-        <v>5</v>
+        <v>13</v>
       </c>
     </row>
     <row r="94" spans="1:6" x14ac:dyDescent="0.25">
@@ -6622,10 +6622,10 @@
         <v>19</v>
       </c>
       <c r="E94" s="1" t="s">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="F94" s="1" t="s">
-        <v>123</v>
+        <v>9</v>
       </c>
     </row>
     <row r="95" spans="1:6" x14ac:dyDescent="0.25">
@@ -6642,10 +6642,10 @@
         <v>19</v>
       </c>
       <c r="E95" s="1" t="s">
-        <v>90</v>
+        <v>35</v>
       </c>
       <c r="F95" s="1" t="s">
-        <v>120</v>
+        <v>13</v>
       </c>
     </row>
     <row r="96" spans="1:6" x14ac:dyDescent="0.25">
@@ -6685,7 +6685,7 @@
         <v>8</v>
       </c>
       <c r="F97" s="1" t="s">
-        <v>171</v>
+        <v>167</v>
       </c>
     </row>
     <row r="98" spans="1:6" x14ac:dyDescent="0.25">
@@ -6705,7 +6705,7 @@
         <v>45</v>
       </c>
       <c r="F98" s="1" t="s">
-        <v>171</v>
+        <v>167</v>
       </c>
     </row>
     <row r="99" spans="1:6" x14ac:dyDescent="0.25">
@@ -6725,7 +6725,7 @@
         <v>12</v>
       </c>
       <c r="F99" s="1" t="s">
-        <v>171</v>
+        <v>167</v>
       </c>
     </row>
     <row r="100" spans="1:6" x14ac:dyDescent="0.25">
@@ -6782,7 +6782,7 @@
         <v>22</v>
       </c>
       <c r="E102" s="1" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="F102" s="1" t="s">
         <v>13</v>
@@ -6802,7 +6802,7 @@
         <v>22</v>
       </c>
       <c r="E103" s="1" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="F103" s="1" t="s">
         <v>64</v>
@@ -6822,7 +6822,7 @@
         <v>22</v>
       </c>
       <c r="E104" s="1" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="F104" s="1" t="s">
         <v>64</v>
@@ -6842,7 +6842,7 @@
         <v>22</v>
       </c>
       <c r="E105" s="1" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="F105" s="1" t="s">
         <v>5</v>
@@ -6862,7 +6862,7 @@
         <v>22</v>
       </c>
       <c r="E106" s="1" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="F106" s="1" t="s">
         <v>29</v>
@@ -9762,7 +9762,7 @@
         <v>136</v>
       </c>
       <c r="E251" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F251" s="1" t="s">
         <v>9</v>
@@ -9782,7 +9782,7 @@
         <v>136</v>
       </c>
       <c r="E252" s="1" t="s">
-        <v>45</v>
+        <v>8</v>
       </c>
       <c r="F252" s="1" t="s">
         <v>9</v>
@@ -9802,7 +9802,7 @@
         <v>136</v>
       </c>
       <c r="E253" s="1" t="s">
-        <v>12</v>
+        <v>45</v>
       </c>
       <c r="F253" s="1" t="s">
         <v>5</v>
@@ -9822,7 +9822,7 @@
         <v>136</v>
       </c>
       <c r="E254" s="1" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="F254" s="1" t="s">
         <v>13</v>
@@ -9842,7 +9842,7 @@
         <v>136</v>
       </c>
       <c r="E255" s="1" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="F255" s="1" t="s">
         <v>120</v>
@@ -9862,7 +9862,7 @@
         <v>136</v>
       </c>
       <c r="E256" s="1" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="F256" s="1" t="s">
         <v>13</v>
@@ -9882,7 +9882,7 @@
         <v>136</v>
       </c>
       <c r="E257" s="1" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="F257" s="1" t="s">
         <v>13</v>
@@ -9902,7 +9902,7 @@
         <v>136</v>
       </c>
       <c r="E258" s="1" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="F258" s="1" t="s">
         <v>13</v>
@@ -9922,7 +9922,7 @@
         <v>136</v>
       </c>
       <c r="E259" s="1" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="F259" s="1" t="s">
         <v>13</v>
@@ -13205,7 +13205,7 @@
         <v>16</v>
       </c>
       <c r="F423" s="1" t="s">
-        <v>171</v>
+        <v>167</v>
       </c>
     </row>
     <row r="424" spans="1:6" x14ac:dyDescent="0.25">
@@ -13225,7 +13225,7 @@
         <v>19</v>
       </c>
       <c r="F424" s="1" t="s">
-        <v>171</v>
+        <v>167</v>
       </c>
     </row>
     <row r="425" spans="1:6" x14ac:dyDescent="0.25">
@@ -13705,7 +13705,7 @@
         <v>22</v>
       </c>
       <c r="F448" s="1" t="s">
-        <v>171</v>
+        <v>167</v>
       </c>
     </row>
     <row r="449" spans="1:6" x14ac:dyDescent="0.25">

--- a/PCE06D.xlsx
+++ b/PCE06D.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4152" uniqueCount="1445">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4146" uniqueCount="1443">
   <si>
     <t/>
   </si>
@@ -1628,12 +1628,6 @@
   </si>
   <si>
     <t>DETTOL BW FRESH 370G</t>
-  </si>
-  <si>
-    <t>20102722</t>
-  </si>
-  <si>
-    <t>DETTOL BW HONEY 370G</t>
   </si>
   <si>
     <t>20115145</t>
@@ -4738,7 +4732,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F692"/>
+  <dimension ref="A1:F691"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
@@ -9802,10 +9796,10 @@
         <v>136</v>
       </c>
       <c r="E253" s="1" t="s">
-        <v>45</v>
+        <v>12</v>
       </c>
       <c r="F253" s="1" t="s">
-        <v>5</v>
+        <v>13</v>
       </c>
     </row>
     <row r="254" spans="1:6" x14ac:dyDescent="0.25">
@@ -9822,10 +9816,10 @@
         <v>136</v>
       </c>
       <c r="E254" s="1" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="F254" s="1" t="s">
-        <v>13</v>
+        <v>120</v>
       </c>
     </row>
     <row r="255" spans="1:6" x14ac:dyDescent="0.25">
@@ -9842,10 +9836,10 @@
         <v>136</v>
       </c>
       <c r="E255" s="1" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="F255" s="1" t="s">
-        <v>120</v>
+        <v>13</v>
       </c>
     </row>
     <row r="256" spans="1:6" x14ac:dyDescent="0.25">
@@ -9862,7 +9856,7 @@
         <v>136</v>
       </c>
       <c r="E256" s="1" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="F256" s="1" t="s">
         <v>13</v>
@@ -9882,7 +9876,7 @@
         <v>136</v>
       </c>
       <c r="E257" s="1" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="F257" s="1" t="s">
         <v>13</v>
@@ -9902,7 +9896,7 @@
         <v>136</v>
       </c>
       <c r="E258" s="1" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="F258" s="1" t="s">
         <v>13</v>
@@ -9919,13 +9913,13 @@
         <v>3</v>
       </c>
       <c r="D259" s="1" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="E259" s="1" t="s">
-        <v>28</v>
+        <v>4</v>
       </c>
       <c r="F259" s="1" t="s">
-        <v>13</v>
+        <v>29</v>
       </c>
     </row>
     <row r="260" spans="1:6" x14ac:dyDescent="0.25">
@@ -9942,7 +9936,7 @@
         <v>139</v>
       </c>
       <c r="E260" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F260" s="1" t="s">
         <v>29</v>
@@ -9962,7 +9956,7 @@
         <v>139</v>
       </c>
       <c r="E261" s="1" t="s">
-        <v>8</v>
+        <v>45</v>
       </c>
       <c r="F261" s="1" t="s">
         <v>29</v>
@@ -9982,7 +9976,7 @@
         <v>139</v>
       </c>
       <c r="E262" s="1" t="s">
-        <v>45</v>
+        <v>12</v>
       </c>
       <c r="F262" s="1" t="s">
         <v>29</v>
@@ -10002,7 +9996,7 @@
         <v>139</v>
       </c>
       <c r="E263" s="1" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="F263" s="1" t="s">
         <v>29</v>
@@ -10022,10 +10016,10 @@
         <v>139</v>
       </c>
       <c r="E264" s="1" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="F264" s="1" t="s">
-        <v>29</v>
+        <v>9</v>
       </c>
     </row>
     <row r="265" spans="1:6" x14ac:dyDescent="0.25">
@@ -10042,7 +10036,7 @@
         <v>139</v>
       </c>
       <c r="E265" s="1" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="F265" s="1" t="s">
         <v>9</v>
@@ -10062,10 +10056,10 @@
         <v>139</v>
       </c>
       <c r="E266" s="1" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="F266" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="267" spans="1:6" x14ac:dyDescent="0.25">
@@ -10082,10 +10076,10 @@
         <v>139</v>
       </c>
       <c r="E267" s="1" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="F267" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="268" spans="1:6" x14ac:dyDescent="0.25">
@@ -10093,7 +10087,7 @@
         <v>569</v>
       </c>
       <c r="B268" s="1" t="s">
-        <v>570</v>
+        <v>568</v>
       </c>
       <c r="C268" s="1" t="s">
         <v>3</v>
@@ -10102,7 +10096,7 @@
         <v>139</v>
       </c>
       <c r="E268" s="1" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="F268" s="1" t="s">
         <v>9</v>
@@ -10110,22 +10104,22 @@
     </row>
     <row r="269" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A269" s="1" t="s">
+        <v>570</v>
+      </c>
+      <c r="B269" s="1" t="s">
         <v>571</v>
       </c>
-      <c r="B269" s="1" t="s">
-        <v>570</v>
-      </c>
       <c r="C269" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D269" s="1" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="E269" s="1" t="s">
-        <v>32</v>
+        <v>4</v>
       </c>
       <c r="F269" s="1" t="s">
-        <v>9</v>
+        <v>29</v>
       </c>
     </row>
     <row r="270" spans="1:6" x14ac:dyDescent="0.25">
@@ -10142,7 +10136,7 @@
         <v>142</v>
       </c>
       <c r="E270" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F270" s="1" t="s">
         <v>29</v>
@@ -10162,7 +10156,7 @@
         <v>142</v>
       </c>
       <c r="E271" s="1" t="s">
-        <v>8</v>
+        <v>45</v>
       </c>
       <c r="F271" s="1" t="s">
         <v>29</v>
@@ -10182,7 +10176,7 @@
         <v>142</v>
       </c>
       <c r="E272" s="1" t="s">
-        <v>45</v>
+        <v>12</v>
       </c>
       <c r="F272" s="1" t="s">
         <v>29</v>
@@ -10202,7 +10196,7 @@
         <v>142</v>
       </c>
       <c r="E273" s="1" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="F273" s="1" t="s">
         <v>29</v>
@@ -10222,7 +10216,7 @@
         <v>142</v>
       </c>
       <c r="E274" s="1" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="F274" s="1" t="s">
         <v>29</v>
@@ -10242,7 +10236,7 @@
         <v>142</v>
       </c>
       <c r="E275" s="1" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="F275" s="1" t="s">
         <v>29</v>
@@ -10262,7 +10256,7 @@
         <v>142</v>
       </c>
       <c r="E276" s="1" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="F276" s="1" t="s">
         <v>29</v>
@@ -10282,10 +10276,10 @@
         <v>142</v>
       </c>
       <c r="E277" s="1" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="F277" s="1" t="s">
-        <v>29</v>
+        <v>5</v>
       </c>
     </row>
     <row r="278" spans="1:6" x14ac:dyDescent="0.25">
@@ -10302,7 +10296,7 @@
         <v>142</v>
       </c>
       <c r="E278" s="1" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="F278" s="1" t="s">
         <v>5</v>
@@ -10319,13 +10313,13 @@
         <v>3</v>
       </c>
       <c r="D279" s="1" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="E279" s="1" t="s">
-        <v>32</v>
+        <v>4</v>
       </c>
       <c r="F279" s="1" t="s">
-        <v>5</v>
+        <v>13</v>
       </c>
     </row>
     <row r="280" spans="1:6" x14ac:dyDescent="0.25">
@@ -10342,7 +10336,7 @@
         <v>145</v>
       </c>
       <c r="E280" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F280" s="1" t="s">
         <v>13</v>
@@ -10362,7 +10356,7 @@
         <v>145</v>
       </c>
       <c r="E281" s="1" t="s">
-        <v>8</v>
+        <v>45</v>
       </c>
       <c r="F281" s="1" t="s">
         <v>13</v>
@@ -10382,7 +10376,7 @@
         <v>145</v>
       </c>
       <c r="E282" s="1" t="s">
-        <v>45</v>
+        <v>12</v>
       </c>
       <c r="F282" s="1" t="s">
         <v>13</v>
@@ -10402,10 +10396,10 @@
         <v>145</v>
       </c>
       <c r="E283" s="1" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="F283" s="1" t="s">
-        <v>13</v>
+        <v>120</v>
       </c>
     </row>
     <row r="284" spans="1:6" x14ac:dyDescent="0.25">
@@ -10422,7 +10416,7 @@
         <v>145</v>
       </c>
       <c r="E284" s="1" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="F284" s="1" t="s">
         <v>120</v>
@@ -10442,10 +10436,10 @@
         <v>145</v>
       </c>
       <c r="E285" s="1" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="F285" s="1" t="s">
-        <v>120</v>
+        <v>5</v>
       </c>
     </row>
     <row r="286" spans="1:6" x14ac:dyDescent="0.25">
@@ -10462,7 +10456,7 @@
         <v>145</v>
       </c>
       <c r="E286" s="1" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="F286" s="1" t="s">
         <v>5</v>
@@ -10482,7 +10476,7 @@
         <v>145</v>
       </c>
       <c r="E287" s="1" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="F287" s="1" t="s">
         <v>5</v>
@@ -10502,7 +10496,7 @@
         <v>145</v>
       </c>
       <c r="E288" s="1" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="F288" s="1" t="s">
         <v>5</v>
@@ -10519,13 +10513,13 @@
         <v>3</v>
       </c>
       <c r="D289" s="1" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="E289" s="1" t="s">
-        <v>32</v>
+        <v>4</v>
       </c>
       <c r="F289" s="1" t="s">
-        <v>5</v>
+        <v>123</v>
       </c>
     </row>
     <row r="290" spans="1:6" x14ac:dyDescent="0.25">
@@ -10542,7 +10536,7 @@
         <v>148</v>
       </c>
       <c r="E290" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F290" s="1" t="s">
         <v>123</v>
@@ -10562,10 +10556,10 @@
         <v>148</v>
       </c>
       <c r="E291" s="1" t="s">
-        <v>8</v>
+        <v>45</v>
       </c>
       <c r="F291" s="1" t="s">
-        <v>123</v>
+        <v>29</v>
       </c>
     </row>
     <row r="292" spans="1:6" x14ac:dyDescent="0.25">
@@ -10582,10 +10576,10 @@
         <v>148</v>
       </c>
       <c r="E292" s="1" t="s">
-        <v>45</v>
+        <v>12</v>
       </c>
       <c r="F292" s="1" t="s">
-        <v>29</v>
+        <v>5</v>
       </c>
     </row>
     <row r="293" spans="1:6" x14ac:dyDescent="0.25">
@@ -10602,7 +10596,7 @@
         <v>148</v>
       </c>
       <c r="E293" s="1" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="F293" s="1" t="s">
         <v>5</v>
@@ -10622,7 +10616,7 @@
         <v>148</v>
       </c>
       <c r="E294" s="1" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="F294" s="1" t="s">
         <v>5</v>
@@ -10642,7 +10636,7 @@
         <v>148</v>
       </c>
       <c r="E295" s="1" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="F295" s="1" t="s">
         <v>5</v>
@@ -10662,7 +10656,7 @@
         <v>148</v>
       </c>
       <c r="E296" s="1" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="F296" s="1" t="s">
         <v>5</v>
@@ -10682,7 +10676,7 @@
         <v>148</v>
       </c>
       <c r="E297" s="1" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="F297" s="1" t="s">
         <v>5</v>
@@ -10702,7 +10696,7 @@
         <v>148</v>
       </c>
       <c r="E298" s="1" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="F298" s="1" t="s">
         <v>5</v>
@@ -10719,10 +10713,10 @@
         <v>3</v>
       </c>
       <c r="D299" s="1" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="E299" s="1" t="s">
-        <v>32</v>
+        <v>4</v>
       </c>
       <c r="F299" s="1" t="s">
         <v>5</v>
@@ -10742,7 +10736,7 @@
         <v>151</v>
       </c>
       <c r="E300" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F300" s="1" t="s">
         <v>5</v>
@@ -10762,7 +10756,7 @@
         <v>151</v>
       </c>
       <c r="E301" s="1" t="s">
-        <v>8</v>
+        <v>45</v>
       </c>
       <c r="F301" s="1" t="s">
         <v>5</v>
@@ -10782,7 +10776,7 @@
         <v>151</v>
       </c>
       <c r="E302" s="1" t="s">
-        <v>45</v>
+        <v>12</v>
       </c>
       <c r="F302" s="1" t="s">
         <v>5</v>
@@ -10802,7 +10796,7 @@
         <v>151</v>
       </c>
       <c r="E303" s="1" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="F303" s="1" t="s">
         <v>5</v>
@@ -10822,7 +10816,7 @@
         <v>151</v>
       </c>
       <c r="E304" s="1" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="F304" s="1" t="s">
         <v>5</v>
@@ -10842,7 +10836,7 @@
         <v>151</v>
       </c>
       <c r="E305" s="1" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="F305" s="1" t="s">
         <v>5</v>
@@ -10862,18 +10856,18 @@
         <v>151</v>
       </c>
       <c r="E306" s="1" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="F306" s="1" t="s">
-        <v>5</v>
+        <v>646</v>
       </c>
     </row>
     <row r="307" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A307" s="1" t="s">
-        <v>646</v>
+        <v>647</v>
       </c>
       <c r="B307" s="1" t="s">
-        <v>647</v>
+        <v>648</v>
       </c>
       <c r="C307" s="1" t="s">
         <v>3</v>
@@ -10882,10 +10876,10 @@
         <v>151</v>
       </c>
       <c r="E307" s="1" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="F307" s="1" t="s">
-        <v>648</v>
+        <v>646</v>
       </c>
     </row>
     <row r="308" spans="1:6" x14ac:dyDescent="0.25">
@@ -10902,10 +10896,10 @@
         <v>151</v>
       </c>
       <c r="E308" s="1" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="F308" s="1" t="s">
-        <v>648</v>
+        <v>5</v>
       </c>
     </row>
     <row r="309" spans="1:6" x14ac:dyDescent="0.25">
@@ -10922,7 +10916,7 @@
         <v>151</v>
       </c>
       <c r="E309" s="1" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="F309" s="1" t="s">
         <v>5</v>
@@ -10942,10 +10936,10 @@
         <v>151</v>
       </c>
       <c r="E310" s="1" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="F310" s="1" t="s">
-        <v>5</v>
+        <v>29</v>
       </c>
     </row>
     <row r="311" spans="1:6" x14ac:dyDescent="0.25">
@@ -10962,7 +10956,7 @@
         <v>151</v>
       </c>
       <c r="E311" s="1" t="s">
-        <v>38</v>
+        <v>90</v>
       </c>
       <c r="F311" s="1" t="s">
         <v>29</v>
@@ -10982,10 +10976,10 @@
         <v>151</v>
       </c>
       <c r="E312" s="1" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="F312" s="1" t="s">
-        <v>29</v>
+        <v>5</v>
       </c>
     </row>
     <row r="313" spans="1:6" x14ac:dyDescent="0.25">
@@ -10999,10 +10993,10 @@
         <v>3</v>
       </c>
       <c r="D313" s="1" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="E313" s="1" t="s">
-        <v>93</v>
+        <v>4</v>
       </c>
       <c r="F313" s="1" t="s">
         <v>5</v>
@@ -11022,7 +11016,7 @@
         <v>154</v>
       </c>
       <c r="E314" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F314" s="1" t="s">
         <v>5</v>
@@ -11042,10 +11036,10 @@
         <v>154</v>
       </c>
       <c r="E315" s="1" t="s">
-        <v>8</v>
+        <v>45</v>
       </c>
       <c r="F315" s="1" t="s">
-        <v>5</v>
+        <v>64</v>
       </c>
     </row>
     <row r="316" spans="1:6" x14ac:dyDescent="0.25">
@@ -11062,10 +11056,10 @@
         <v>154</v>
       </c>
       <c r="E316" s="1" t="s">
-        <v>45</v>
+        <v>12</v>
       </c>
       <c r="F316" s="1" t="s">
-        <v>64</v>
+        <v>5</v>
       </c>
     </row>
     <row r="317" spans="1:6" x14ac:dyDescent="0.25">
@@ -11082,7 +11076,7 @@
         <v>154</v>
       </c>
       <c r="E317" s="1" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="F317" s="1" t="s">
         <v>5</v>
@@ -11102,7 +11096,7 @@
         <v>154</v>
       </c>
       <c r="E318" s="1" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="F318" s="1" t="s">
         <v>5</v>
@@ -11122,7 +11116,7 @@
         <v>154</v>
       </c>
       <c r="E319" s="1" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="F319" s="1" t="s">
         <v>5</v>
@@ -11142,7 +11136,7 @@
         <v>154</v>
       </c>
       <c r="E320" s="1" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="F320" s="1" t="s">
         <v>5</v>
@@ -11162,7 +11156,7 @@
         <v>154</v>
       </c>
       <c r="E321" s="1" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="F321" s="1" t="s">
         <v>5</v>
@@ -11182,7 +11176,7 @@
         <v>154</v>
       </c>
       <c r="E322" s="1" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="F322" s="1" t="s">
         <v>5</v>
@@ -11202,10 +11196,10 @@
         <v>154</v>
       </c>
       <c r="E323" s="1" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="F323" s="1" t="s">
-        <v>5</v>
+        <v>13</v>
       </c>
     </row>
     <row r="324" spans="1:6" x14ac:dyDescent="0.25">
@@ -11222,10 +11216,10 @@
         <v>154</v>
       </c>
       <c r="E324" s="1" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="F324" s="1" t="s">
-        <v>13</v>
+        <v>5</v>
       </c>
     </row>
     <row r="325" spans="1:6" x14ac:dyDescent="0.25">
@@ -11242,10 +11236,10 @@
         <v>154</v>
       </c>
       <c r="E325" s="1" t="s">
-        <v>38</v>
+        <v>90</v>
       </c>
       <c r="F325" s="1" t="s">
-        <v>5</v>
+        <v>29</v>
       </c>
     </row>
     <row r="326" spans="1:6" x14ac:dyDescent="0.25">
@@ -11262,7 +11256,7 @@
         <v>154</v>
       </c>
       <c r="E326" s="1" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="F326" s="1" t="s">
         <v>29</v>
@@ -11282,10 +11276,10 @@
         <v>154</v>
       </c>
       <c r="E327" s="1" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="F327" s="1" t="s">
-        <v>29</v>
+        <v>232</v>
       </c>
     </row>
     <row r="328" spans="1:6" x14ac:dyDescent="0.25">
@@ -11302,10 +11296,10 @@
         <v>154</v>
       </c>
       <c r="E328" s="1" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="F328" s="1" t="s">
-        <v>232</v>
+        <v>5</v>
       </c>
     </row>
     <row r="329" spans="1:6" x14ac:dyDescent="0.25">
@@ -11322,7 +11316,7 @@
         <v>154</v>
       </c>
       <c r="E329" s="1" t="s">
-        <v>99</v>
+        <v>136</v>
       </c>
       <c r="F329" s="1" t="s">
         <v>5</v>
@@ -11342,7 +11336,7 @@
         <v>154</v>
       </c>
       <c r="E330" s="1" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="F330" s="1" t="s">
         <v>5</v>
@@ -11359,30 +11353,30 @@
         <v>3</v>
       </c>
       <c r="D331" s="1" t="s">
-        <v>154</v>
+        <v>697</v>
       </c>
       <c r="E331" s="1" t="s">
-        <v>139</v>
+        <v>4</v>
       </c>
       <c r="F331" s="1" t="s">
-        <v>5</v>
+        <v>13</v>
       </c>
     </row>
     <row r="332" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A332" s="1" t="s">
+        <v>698</v>
+      </c>
+      <c r="B332" s="1" t="s">
+        <v>699</v>
+      </c>
+      <c r="C332" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D332" s="1" t="s">
         <v>697</v>
       </c>
-      <c r="B332" s="1" t="s">
-        <v>698</v>
-      </c>
-      <c r="C332" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D332" s="1" t="s">
-        <v>699</v>
-      </c>
       <c r="E332" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F332" s="1" t="s">
         <v>13</v>
@@ -11399,10 +11393,10 @@
         <v>3</v>
       </c>
       <c r="D333" s="1" t="s">
-        <v>699</v>
+        <v>697</v>
       </c>
       <c r="E333" s="1" t="s">
-        <v>8</v>
+        <v>45</v>
       </c>
       <c r="F333" s="1" t="s">
         <v>13</v>
@@ -11419,10 +11413,10 @@
         <v>3</v>
       </c>
       <c r="D334" s="1" t="s">
-        <v>699</v>
+        <v>697</v>
       </c>
       <c r="E334" s="1" t="s">
-        <v>45</v>
+        <v>12</v>
       </c>
       <c r="F334" s="1" t="s">
         <v>13</v>
@@ -11439,10 +11433,10 @@
         <v>3</v>
       </c>
       <c r="D335" s="1" t="s">
-        <v>699</v>
+        <v>697</v>
       </c>
       <c r="E335" s="1" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="F335" s="1" t="s">
         <v>13</v>
@@ -11459,13 +11453,13 @@
         <v>3</v>
       </c>
       <c r="D336" s="1" t="s">
-        <v>699</v>
+        <v>697</v>
       </c>
       <c r="E336" s="1" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="F336" s="1" t="s">
-        <v>13</v>
+        <v>29</v>
       </c>
     </row>
     <row r="337" spans="1:6" x14ac:dyDescent="0.25">
@@ -11479,10 +11473,10 @@
         <v>3</v>
       </c>
       <c r="D337" s="1" t="s">
-        <v>699</v>
+        <v>697</v>
       </c>
       <c r="E337" s="1" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="F337" s="1" t="s">
         <v>29</v>
@@ -11499,13 +11493,13 @@
         <v>3</v>
       </c>
       <c r="D338" s="1" t="s">
-        <v>699</v>
+        <v>697</v>
       </c>
       <c r="E338" s="1" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="F338" s="1" t="s">
-        <v>29</v>
+        <v>5</v>
       </c>
     </row>
     <row r="339" spans="1:6" x14ac:dyDescent="0.25">
@@ -11519,10 +11513,10 @@
         <v>3</v>
       </c>
       <c r="D339" s="1" t="s">
-        <v>699</v>
+        <v>697</v>
       </c>
       <c r="E339" s="1" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="F339" s="1" t="s">
         <v>5</v>
@@ -11539,10 +11533,10 @@
         <v>3</v>
       </c>
       <c r="D340" s="1" t="s">
-        <v>699</v>
+        <v>697</v>
       </c>
       <c r="E340" s="1" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="F340" s="1" t="s">
         <v>5</v>
@@ -11559,10 +11553,10 @@
         <v>3</v>
       </c>
       <c r="D341" s="1" t="s">
-        <v>699</v>
+        <v>697</v>
       </c>
       <c r="E341" s="1" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="F341" s="1" t="s">
         <v>5</v>
@@ -11579,10 +11573,10 @@
         <v>3</v>
       </c>
       <c r="D342" s="1" t="s">
-        <v>699</v>
+        <v>697</v>
       </c>
       <c r="E342" s="1" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="F342" s="1" t="s">
         <v>5</v>
@@ -11599,13 +11593,13 @@
         <v>3</v>
       </c>
       <c r="D343" s="1" t="s">
-        <v>699</v>
+        <v>697</v>
       </c>
       <c r="E343" s="1" t="s">
-        <v>38</v>
+        <v>90</v>
       </c>
       <c r="F343" s="1" t="s">
-        <v>5</v>
+        <v>13</v>
       </c>
     </row>
     <row r="344" spans="1:6" x14ac:dyDescent="0.25">
@@ -11619,10 +11613,10 @@
         <v>3</v>
       </c>
       <c r="D344" s="1" t="s">
-        <v>699</v>
+        <v>724</v>
       </c>
       <c r="E344" s="1" t="s">
-        <v>90</v>
+        <v>4</v>
       </c>
       <c r="F344" s="1" t="s">
         <v>13</v>
@@ -11630,19 +11624,19 @@
     </row>
     <row r="345" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A345" s="1" t="s">
+        <v>725</v>
+      </c>
+      <c r="B345" s="1" t="s">
+        <v>726</v>
+      </c>
+      <c r="C345" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D345" s="1" t="s">
         <v>724</v>
       </c>
-      <c r="B345" s="1" t="s">
-        <v>725</v>
-      </c>
-      <c r="C345" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D345" s="1" t="s">
-        <v>726</v>
-      </c>
       <c r="E345" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F345" s="1" t="s">
         <v>13</v>
@@ -11659,13 +11653,13 @@
         <v>3</v>
       </c>
       <c r="D346" s="1" t="s">
-        <v>726</v>
+        <v>724</v>
       </c>
       <c r="E346" s="1" t="s">
-        <v>8</v>
+        <v>45</v>
       </c>
       <c r="F346" s="1" t="s">
-        <v>13</v>
+        <v>29</v>
       </c>
     </row>
     <row r="347" spans="1:6" x14ac:dyDescent="0.25">
@@ -11679,13 +11673,13 @@
         <v>3</v>
       </c>
       <c r="D347" s="1" t="s">
-        <v>726</v>
+        <v>724</v>
       </c>
       <c r="E347" s="1" t="s">
-        <v>45</v>
+        <v>12</v>
       </c>
       <c r="F347" s="1" t="s">
-        <v>29</v>
+        <v>64</v>
       </c>
     </row>
     <row r="348" spans="1:6" x14ac:dyDescent="0.25">
@@ -11699,10 +11693,10 @@
         <v>3</v>
       </c>
       <c r="D348" s="1" t="s">
-        <v>726</v>
+        <v>724</v>
       </c>
       <c r="E348" s="1" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="F348" s="1" t="s">
         <v>64</v>
@@ -11719,13 +11713,13 @@
         <v>3</v>
       </c>
       <c r="D349" s="1" t="s">
-        <v>726</v>
+        <v>724</v>
       </c>
       <c r="E349" s="1" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="F349" s="1" t="s">
-        <v>64</v>
+        <v>5</v>
       </c>
     </row>
     <row r="350" spans="1:6" x14ac:dyDescent="0.25">
@@ -11739,13 +11733,13 @@
         <v>3</v>
       </c>
       <c r="D350" s="1" t="s">
-        <v>726</v>
+        <v>724</v>
       </c>
       <c r="E350" s="1" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="F350" s="1" t="s">
-        <v>5</v>
+        <v>64</v>
       </c>
     </row>
     <row r="351" spans="1:6" x14ac:dyDescent="0.25">
@@ -11759,13 +11753,13 @@
         <v>3</v>
       </c>
       <c r="D351" s="1" t="s">
-        <v>726</v>
+        <v>724</v>
       </c>
       <c r="E351" s="1" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="F351" s="1" t="s">
-        <v>64</v>
+        <v>29</v>
       </c>
     </row>
     <row r="352" spans="1:6" x14ac:dyDescent="0.25">
@@ -11779,13 +11773,13 @@
         <v>3</v>
       </c>
       <c r="D352" s="1" t="s">
-        <v>726</v>
+        <v>724</v>
       </c>
       <c r="E352" s="1" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="F352" s="1" t="s">
-        <v>29</v>
+        <v>5</v>
       </c>
     </row>
     <row r="353" spans="1:6" x14ac:dyDescent="0.25">
@@ -11799,13 +11793,13 @@
         <v>3</v>
       </c>
       <c r="D353" s="1" t="s">
-        <v>726</v>
+        <v>724</v>
       </c>
       <c r="E353" s="1" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="F353" s="1" t="s">
-        <v>5</v>
+        <v>29</v>
       </c>
     </row>
     <row r="354" spans="1:6" x14ac:dyDescent="0.25">
@@ -11819,13 +11813,13 @@
         <v>3</v>
       </c>
       <c r="D354" s="1" t="s">
-        <v>726</v>
+        <v>724</v>
       </c>
       <c r="E354" s="1" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="F354" s="1" t="s">
-        <v>29</v>
+        <v>5</v>
       </c>
     </row>
     <row r="355" spans="1:6" x14ac:dyDescent="0.25">
@@ -11839,10 +11833,10 @@
         <v>3</v>
       </c>
       <c r="D355" s="1" t="s">
-        <v>726</v>
+        <v>724</v>
       </c>
       <c r="E355" s="1" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="F355" s="1" t="s">
         <v>5</v>
@@ -11859,13 +11853,13 @@
         <v>3</v>
       </c>
       <c r="D356" s="1" t="s">
-        <v>726</v>
+        <v>724</v>
       </c>
       <c r="E356" s="1" t="s">
-        <v>38</v>
+        <v>90</v>
       </c>
       <c r="F356" s="1" t="s">
-        <v>5</v>
+        <v>13</v>
       </c>
     </row>
     <row r="357" spans="1:6" x14ac:dyDescent="0.25">
@@ -11879,10 +11873,10 @@
         <v>3</v>
       </c>
       <c r="D357" s="1" t="s">
-        <v>726</v>
+        <v>724</v>
       </c>
       <c r="E357" s="1" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="F357" s="1" t="s">
         <v>13</v>
@@ -11899,30 +11893,30 @@
         <v>3</v>
       </c>
       <c r="D358" s="1" t="s">
-        <v>726</v>
+        <v>753</v>
       </c>
       <c r="E358" s="1" t="s">
-        <v>93</v>
+        <v>4</v>
       </c>
       <c r="F358" s="1" t="s">
-        <v>13</v>
+        <v>5</v>
       </c>
     </row>
     <row r="359" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A359" s="1" t="s">
+        <v>754</v>
+      </c>
+      <c r="B359" s="1" t="s">
+        <v>755</v>
+      </c>
+      <c r="C359" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D359" s="1" t="s">
         <v>753</v>
       </c>
-      <c r="B359" s="1" t="s">
-        <v>754</v>
-      </c>
-      <c r="C359" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D359" s="1" t="s">
-        <v>755</v>
-      </c>
       <c r="E359" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F359" s="1" t="s">
         <v>5</v>
@@ -11939,10 +11933,10 @@
         <v>3</v>
       </c>
       <c r="D360" s="1" t="s">
-        <v>755</v>
+        <v>753</v>
       </c>
       <c r="E360" s="1" t="s">
-        <v>8</v>
+        <v>45</v>
       </c>
       <c r="F360" s="1" t="s">
         <v>5</v>
@@ -11959,10 +11953,10 @@
         <v>3</v>
       </c>
       <c r="D361" s="1" t="s">
-        <v>755</v>
+        <v>753</v>
       </c>
       <c r="E361" s="1" t="s">
-        <v>45</v>
+        <v>12</v>
       </c>
       <c r="F361" s="1" t="s">
         <v>5</v>
@@ -11979,13 +11973,13 @@
         <v>3</v>
       </c>
       <c r="D362" s="1" t="s">
-        <v>755</v>
+        <v>753</v>
       </c>
       <c r="E362" s="1" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="F362" s="1" t="s">
-        <v>5</v>
+        <v>29</v>
       </c>
     </row>
     <row r="363" spans="1:6" x14ac:dyDescent="0.25">
@@ -11999,13 +11993,13 @@
         <v>3</v>
       </c>
       <c r="D363" s="1" t="s">
-        <v>755</v>
+        <v>753</v>
       </c>
       <c r="E363" s="1" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="F363" s="1" t="s">
-        <v>29</v>
+        <v>5</v>
       </c>
     </row>
     <row r="364" spans="1:6" x14ac:dyDescent="0.25">
@@ -12019,10 +12013,10 @@
         <v>3</v>
       </c>
       <c r="D364" s="1" t="s">
-        <v>755</v>
+        <v>753</v>
       </c>
       <c r="E364" s="1" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="F364" s="1" t="s">
         <v>5</v>
@@ -12039,13 +12033,13 @@
         <v>3</v>
       </c>
       <c r="D365" s="1" t="s">
-        <v>755</v>
+        <v>753</v>
       </c>
       <c r="E365" s="1" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="F365" s="1" t="s">
-        <v>5</v>
+        <v>29</v>
       </c>
     </row>
     <row r="366" spans="1:6" x14ac:dyDescent="0.25">
@@ -12059,10 +12053,10 @@
         <v>3</v>
       </c>
       <c r="D366" s="1" t="s">
-        <v>755</v>
+        <v>753</v>
       </c>
       <c r="E366" s="1" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="F366" s="1" t="s">
         <v>29</v>
@@ -12079,10 +12073,10 @@
         <v>3</v>
       </c>
       <c r="D367" s="1" t="s">
-        <v>755</v>
+        <v>753</v>
       </c>
       <c r="E367" s="1" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="F367" s="1" t="s">
         <v>29</v>
@@ -12099,10 +12093,10 @@
         <v>3</v>
       </c>
       <c r="D368" s="1" t="s">
-        <v>755</v>
+        <v>753</v>
       </c>
       <c r="E368" s="1" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="F368" s="1" t="s">
         <v>29</v>
@@ -12119,13 +12113,13 @@
         <v>3</v>
       </c>
       <c r="D369" s="1" t="s">
-        <v>755</v>
+        <v>753</v>
       </c>
       <c r="E369" s="1" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="F369" s="1" t="s">
-        <v>29</v>
+        <v>9</v>
       </c>
     </row>
     <row r="370" spans="1:6" x14ac:dyDescent="0.25">
@@ -12139,13 +12133,13 @@
         <v>3</v>
       </c>
       <c r="D370" s="1" t="s">
-        <v>755</v>
+        <v>753</v>
       </c>
       <c r="E370" s="1" t="s">
-        <v>38</v>
+        <v>90</v>
       </c>
       <c r="F370" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="371" spans="1:6" x14ac:dyDescent="0.25">
@@ -12159,10 +12153,10 @@
         <v>3</v>
       </c>
       <c r="D371" s="1" t="s">
-        <v>755</v>
+        <v>753</v>
       </c>
       <c r="E371" s="1" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="F371" s="1" t="s">
         <v>5</v>
@@ -12179,10 +12173,10 @@
         <v>3</v>
       </c>
       <c r="D372" s="1" t="s">
-        <v>755</v>
+        <v>753</v>
       </c>
       <c r="E372" s="1" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="F372" s="1" t="s">
         <v>5</v>
@@ -12199,10 +12193,10 @@
         <v>3</v>
       </c>
       <c r="D373" s="1" t="s">
-        <v>755</v>
+        <v>753</v>
       </c>
       <c r="E373" s="1" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="F373" s="1" t="s">
         <v>5</v>
@@ -12219,13 +12213,13 @@
         <v>3</v>
       </c>
       <c r="D374" s="1" t="s">
-        <v>755</v>
+        <v>753</v>
       </c>
       <c r="E374" s="1" t="s">
-        <v>99</v>
+        <v>136</v>
       </c>
       <c r="F374" s="1" t="s">
-        <v>5</v>
+        <v>29</v>
       </c>
     </row>
     <row r="375" spans="1:6" x14ac:dyDescent="0.25">
@@ -12239,10 +12233,10 @@
         <v>3</v>
       </c>
       <c r="D375" s="1" t="s">
-        <v>755</v>
+        <v>753</v>
       </c>
       <c r="E375" s="1" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="F375" s="1" t="s">
         <v>29</v>
@@ -12259,10 +12253,10 @@
         <v>3</v>
       </c>
       <c r="D376" s="1" t="s">
-        <v>755</v>
+        <v>753</v>
       </c>
       <c r="E376" s="1" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="F376" s="1" t="s">
         <v>29</v>
@@ -12279,10 +12273,10 @@
         <v>3</v>
       </c>
       <c r="D377" s="1" t="s">
-        <v>755</v>
+        <v>792</v>
       </c>
       <c r="E377" s="1" t="s">
-        <v>142</v>
+        <v>4</v>
       </c>
       <c r="F377" s="1" t="s">
         <v>29</v>
@@ -12290,22 +12284,22 @@
     </row>
     <row r="378" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A378" s="1" t="s">
+        <v>793</v>
+      </c>
+      <c r="B378" s="1" t="s">
+        <v>794</v>
+      </c>
+      <c r="C378" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D378" s="1" t="s">
         <v>792</v>
       </c>
-      <c r="B378" s="1" t="s">
-        <v>793</v>
-      </c>
-      <c r="C378" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D378" s="1" t="s">
-        <v>794</v>
-      </c>
       <c r="E378" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F378" s="1" t="s">
-        <v>29</v>
+        <v>5</v>
       </c>
     </row>
     <row r="379" spans="1:6" x14ac:dyDescent="0.25">
@@ -12319,10 +12313,10 @@
         <v>3</v>
       </c>
       <c r="D379" s="1" t="s">
-        <v>794</v>
+        <v>792</v>
       </c>
       <c r="E379" s="1" t="s">
-        <v>8</v>
+        <v>45</v>
       </c>
       <c r="F379" s="1" t="s">
         <v>5</v>
@@ -12339,10 +12333,10 @@
         <v>3</v>
       </c>
       <c r="D380" s="1" t="s">
-        <v>794</v>
+        <v>792</v>
       </c>
       <c r="E380" s="1" t="s">
-        <v>45</v>
+        <v>12</v>
       </c>
       <c r="F380" s="1" t="s">
         <v>5</v>
@@ -12359,10 +12353,10 @@
         <v>3</v>
       </c>
       <c r="D381" s="1" t="s">
-        <v>794</v>
+        <v>792</v>
       </c>
       <c r="E381" s="1" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="F381" s="1" t="s">
         <v>5</v>
@@ -12379,10 +12373,10 @@
         <v>3</v>
       </c>
       <c r="D382" s="1" t="s">
-        <v>794</v>
+        <v>792</v>
       </c>
       <c r="E382" s="1" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="F382" s="1" t="s">
         <v>5</v>
@@ -12399,13 +12393,13 @@
         <v>3</v>
       </c>
       <c r="D383" s="1" t="s">
-        <v>794</v>
+        <v>792</v>
       </c>
       <c r="E383" s="1" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="F383" s="1" t="s">
-        <v>5</v>
+        <v>29</v>
       </c>
     </row>
     <row r="384" spans="1:6" x14ac:dyDescent="0.25">
@@ -12419,13 +12413,13 @@
         <v>3</v>
       </c>
       <c r="D384" s="1" t="s">
-        <v>794</v>
+        <v>792</v>
       </c>
       <c r="E384" s="1" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="F384" s="1" t="s">
-        <v>29</v>
+        <v>5</v>
       </c>
     </row>
     <row r="385" spans="1:6" x14ac:dyDescent="0.25">
@@ -12439,10 +12433,10 @@
         <v>3</v>
       </c>
       <c r="D385" s="1" t="s">
-        <v>794</v>
+        <v>792</v>
       </c>
       <c r="E385" s="1" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="F385" s="1" t="s">
         <v>5</v>
@@ -12459,10 +12453,10 @@
         <v>3</v>
       </c>
       <c r="D386" s="1" t="s">
-        <v>794</v>
+        <v>792</v>
       </c>
       <c r="E386" s="1" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="F386" s="1" t="s">
         <v>5</v>
@@ -12479,10 +12473,10 @@
         <v>3</v>
       </c>
       <c r="D387" s="1" t="s">
-        <v>794</v>
+        <v>792</v>
       </c>
       <c r="E387" s="1" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="F387" s="1" t="s">
         <v>5</v>
@@ -12499,13 +12493,13 @@
         <v>3</v>
       </c>
       <c r="D388" s="1" t="s">
-        <v>794</v>
+        <v>792</v>
       </c>
       <c r="E388" s="1" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="F388" s="1" t="s">
-        <v>5</v>
+        <v>29</v>
       </c>
     </row>
     <row r="389" spans="1:6" x14ac:dyDescent="0.25">
@@ -12519,10 +12513,10 @@
         <v>3</v>
       </c>
       <c r="D389" s="1" t="s">
-        <v>794</v>
+        <v>792</v>
       </c>
       <c r="E389" s="1" t="s">
-        <v>38</v>
+        <v>90</v>
       </c>
       <c r="F389" s="1" t="s">
         <v>29</v>
@@ -12539,10 +12533,10 @@
         <v>3</v>
       </c>
       <c r="D390" s="1" t="s">
-        <v>794</v>
+        <v>792</v>
       </c>
       <c r="E390" s="1" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="F390" s="1" t="s">
         <v>29</v>
@@ -12559,10 +12553,10 @@
         <v>3</v>
       </c>
       <c r="D391" s="1" t="s">
-        <v>794</v>
+        <v>792</v>
       </c>
       <c r="E391" s="1" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="F391" s="1" t="s">
         <v>29</v>
@@ -12579,13 +12573,13 @@
         <v>3</v>
       </c>
       <c r="D392" s="1" t="s">
-        <v>794</v>
+        <v>792</v>
       </c>
       <c r="E392" s="1" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="F392" s="1" t="s">
-        <v>29</v>
+        <v>5</v>
       </c>
     </row>
     <row r="393" spans="1:6" x14ac:dyDescent="0.25">
@@ -12599,10 +12593,10 @@
         <v>3</v>
       </c>
       <c r="D393" s="1" t="s">
-        <v>794</v>
+        <v>792</v>
       </c>
       <c r="E393" s="1" t="s">
-        <v>99</v>
+        <v>136</v>
       </c>
       <c r="F393" s="1" t="s">
         <v>5</v>
@@ -12619,13 +12613,13 @@
         <v>3</v>
       </c>
       <c r="D394" s="1" t="s">
-        <v>794</v>
+        <v>792</v>
       </c>
       <c r="E394" s="1" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="F394" s="1" t="s">
-        <v>5</v>
+        <v>29</v>
       </c>
     </row>
     <row r="395" spans="1:6" x14ac:dyDescent="0.25">
@@ -12639,13 +12633,13 @@
         <v>3</v>
       </c>
       <c r="D395" s="1" t="s">
-        <v>794</v>
+        <v>792</v>
       </c>
       <c r="E395" s="1" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="F395" s="1" t="s">
-        <v>29</v>
+        <v>9</v>
       </c>
     </row>
     <row r="396" spans="1:6" x14ac:dyDescent="0.25">
@@ -12659,10 +12653,10 @@
         <v>3</v>
       </c>
       <c r="D396" s="1" t="s">
-        <v>794</v>
+        <v>792</v>
       </c>
       <c r="E396" s="1" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="F396" s="1" t="s">
         <v>9</v>
@@ -12679,33 +12673,33 @@
         <v>3</v>
       </c>
       <c r="D397" s="1" t="s">
-        <v>794</v>
+        <v>833</v>
       </c>
       <c r="E397" s="1" t="s">
-        <v>145</v>
+        <v>4</v>
       </c>
       <c r="F397" s="1" t="s">
-        <v>9</v>
+        <v>29</v>
       </c>
     </row>
     <row r="398" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A398" s="1" t="s">
+        <v>834</v>
+      </c>
+      <c r="B398" s="1" t="s">
+        <v>835</v>
+      </c>
+      <c r="C398" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D398" s="1" t="s">
         <v>833</v>
       </c>
-      <c r="B398" s="1" t="s">
-        <v>834</v>
-      </c>
-      <c r="C398" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D398" s="1" t="s">
-        <v>835</v>
-      </c>
       <c r="E398" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F398" s="1" t="s">
-        <v>29</v>
+        <v>64</v>
       </c>
     </row>
     <row r="399" spans="1:6" x14ac:dyDescent="0.25">
@@ -12719,10 +12713,10 @@
         <v>3</v>
       </c>
       <c r="D399" s="1" t="s">
-        <v>835</v>
+        <v>833</v>
       </c>
       <c r="E399" s="1" t="s">
-        <v>8</v>
+        <v>45</v>
       </c>
       <c r="F399" s="1" t="s">
         <v>64</v>
@@ -12739,10 +12733,10 @@
         <v>3</v>
       </c>
       <c r="D400" s="1" t="s">
-        <v>835</v>
+        <v>833</v>
       </c>
       <c r="E400" s="1" t="s">
-        <v>45</v>
+        <v>12</v>
       </c>
       <c r="F400" s="1" t="s">
         <v>64</v>
@@ -12759,10 +12753,10 @@
         <v>3</v>
       </c>
       <c r="D401" s="1" t="s">
-        <v>835</v>
+        <v>833</v>
       </c>
       <c r="E401" s="1" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="F401" s="1" t="s">
         <v>64</v>
@@ -12779,13 +12773,13 @@
         <v>3</v>
       </c>
       <c r="D402" s="1" t="s">
-        <v>835</v>
+        <v>833</v>
       </c>
       <c r="E402" s="1" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="F402" s="1" t="s">
-        <v>64</v>
+        <v>5</v>
       </c>
     </row>
     <row r="403" spans="1:6" x14ac:dyDescent="0.25">
@@ -12799,10 +12793,10 @@
         <v>3</v>
       </c>
       <c r="D403" s="1" t="s">
-        <v>835</v>
+        <v>833</v>
       </c>
       <c r="E403" s="1" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="F403" s="1" t="s">
         <v>5</v>
@@ -12819,13 +12813,13 @@
         <v>3</v>
       </c>
       <c r="D404" s="1" t="s">
-        <v>835</v>
+        <v>833</v>
       </c>
       <c r="E404" s="1" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="F404" s="1" t="s">
-        <v>5</v>
+        <v>13</v>
       </c>
     </row>
     <row r="405" spans="1:6" x14ac:dyDescent="0.25">
@@ -12839,10 +12833,10 @@
         <v>3</v>
       </c>
       <c r="D405" s="1" t="s">
-        <v>835</v>
+        <v>833</v>
       </c>
       <c r="E405" s="1" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="F405" s="1" t="s">
         <v>13</v>
@@ -12859,10 +12853,10 @@
         <v>3</v>
       </c>
       <c r="D406" s="1" t="s">
-        <v>835</v>
+        <v>833</v>
       </c>
       <c r="E406" s="1" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="F406" s="1" t="s">
         <v>13</v>
@@ -12879,10 +12873,10 @@
         <v>3</v>
       </c>
       <c r="D407" s="1" t="s">
-        <v>835</v>
+        <v>833</v>
       </c>
       <c r="E407" s="1" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="F407" s="1" t="s">
         <v>13</v>
@@ -12899,10 +12893,10 @@
         <v>3</v>
       </c>
       <c r="D408" s="1" t="s">
-        <v>835</v>
+        <v>833</v>
       </c>
       <c r="E408" s="1" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="F408" s="1" t="s">
         <v>13</v>
@@ -12919,10 +12913,10 @@
         <v>3</v>
       </c>
       <c r="D409" s="1" t="s">
-        <v>835</v>
+        <v>833</v>
       </c>
       <c r="E409" s="1" t="s">
-        <v>38</v>
+        <v>90</v>
       </c>
       <c r="F409" s="1" t="s">
         <v>13</v>
@@ -12939,10 +12933,10 @@
         <v>3</v>
       </c>
       <c r="D410" s="1" t="s">
-        <v>835</v>
+        <v>833</v>
       </c>
       <c r="E410" s="1" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="F410" s="1" t="s">
         <v>13</v>
@@ -12959,10 +12953,10 @@
         <v>3</v>
       </c>
       <c r="D411" s="1" t="s">
-        <v>835</v>
+        <v>833</v>
       </c>
       <c r="E411" s="1" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="F411" s="1" t="s">
         <v>13</v>
@@ -12979,10 +12973,10 @@
         <v>3</v>
       </c>
       <c r="D412" s="1" t="s">
-        <v>835</v>
+        <v>833</v>
       </c>
       <c r="E412" s="1" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="F412" s="1" t="s">
         <v>13</v>
@@ -12999,10 +12993,10 @@
         <v>3</v>
       </c>
       <c r="D413" s="1" t="s">
-        <v>835</v>
+        <v>833</v>
       </c>
       <c r="E413" s="1" t="s">
-        <v>99</v>
+        <v>136</v>
       </c>
       <c r="F413" s="1" t="s">
         <v>13</v>
@@ -13019,13 +13013,13 @@
         <v>3</v>
       </c>
       <c r="D414" s="1" t="s">
-        <v>835</v>
+        <v>833</v>
       </c>
       <c r="E414" s="1" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="F414" s="1" t="s">
-        <v>13</v>
+        <v>5</v>
       </c>
     </row>
     <row r="415" spans="1:6" x14ac:dyDescent="0.25">
@@ -13039,13 +13033,13 @@
         <v>3</v>
       </c>
       <c r="D415" s="1" t="s">
-        <v>835</v>
+        <v>833</v>
       </c>
       <c r="E415" s="1" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="F415" s="1" t="s">
-        <v>5</v>
+        <v>29</v>
       </c>
     </row>
     <row r="416" spans="1:6" x14ac:dyDescent="0.25">
@@ -13059,10 +13053,10 @@
         <v>3</v>
       </c>
       <c r="D416" s="1" t="s">
-        <v>835</v>
+        <v>833</v>
       </c>
       <c r="E416" s="1" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="F416" s="1" t="s">
         <v>29</v>
@@ -13079,13 +13073,13 @@
         <v>3</v>
       </c>
       <c r="D417" s="1" t="s">
-        <v>835</v>
+        <v>833</v>
       </c>
       <c r="E417" s="1" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="F417" s="1" t="s">
-        <v>29</v>
+        <v>5</v>
       </c>
     </row>
     <row r="418" spans="1:6" x14ac:dyDescent="0.25">
@@ -13099,33 +13093,33 @@
         <v>3</v>
       </c>
       <c r="D418" s="1" t="s">
-        <v>835</v>
+        <v>876</v>
       </c>
       <c r="E418" s="1" t="s">
-        <v>148</v>
+        <v>4</v>
       </c>
       <c r="F418" s="1" t="s">
-        <v>5</v>
+        <v>120</v>
       </c>
     </row>
     <row r="419" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A419" s="1" t="s">
+        <v>877</v>
+      </c>
+      <c r="B419" s="1" t="s">
+        <v>878</v>
+      </c>
+      <c r="C419" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D419" s="1" t="s">
         <v>876</v>
       </c>
-      <c r="B419" s="1" t="s">
-        <v>877</v>
-      </c>
-      <c r="C419" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D419" s="1" t="s">
-        <v>878</v>
-      </c>
       <c r="E419" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F419" s="1" t="s">
-        <v>120</v>
+        <v>64</v>
       </c>
     </row>
     <row r="420" spans="1:6" x14ac:dyDescent="0.25">
@@ -13139,13 +13133,13 @@
         <v>3</v>
       </c>
       <c r="D420" s="1" t="s">
-        <v>878</v>
+        <v>876</v>
       </c>
       <c r="E420" s="1" t="s">
-        <v>8</v>
+        <v>45</v>
       </c>
       <c r="F420" s="1" t="s">
-        <v>64</v>
+        <v>232</v>
       </c>
     </row>
     <row r="421" spans="1:6" x14ac:dyDescent="0.25">
@@ -13159,13 +13153,13 @@
         <v>3</v>
       </c>
       <c r="D421" s="1" t="s">
-        <v>878</v>
+        <v>876</v>
       </c>
       <c r="E421" s="1" t="s">
-        <v>45</v>
+        <v>12</v>
       </c>
       <c r="F421" s="1" t="s">
-        <v>232</v>
+        <v>64</v>
       </c>
     </row>
     <row r="422" spans="1:6" x14ac:dyDescent="0.25">
@@ -13179,13 +13173,13 @@
         <v>3</v>
       </c>
       <c r="D422" s="1" t="s">
-        <v>878</v>
+        <v>876</v>
       </c>
       <c r="E422" s="1" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="F422" s="1" t="s">
-        <v>64</v>
+        <v>167</v>
       </c>
     </row>
     <row r="423" spans="1:6" x14ac:dyDescent="0.25">
@@ -13199,10 +13193,10 @@
         <v>3</v>
       </c>
       <c r="D423" s="1" t="s">
-        <v>878</v>
+        <v>876</v>
       </c>
       <c r="E423" s="1" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="F423" s="1" t="s">
         <v>167</v>
@@ -13219,13 +13213,13 @@
         <v>3</v>
       </c>
       <c r="D424" s="1" t="s">
-        <v>878</v>
+        <v>876</v>
       </c>
       <c r="E424" s="1" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="F424" s="1" t="s">
-        <v>167</v>
+        <v>64</v>
       </c>
     </row>
     <row r="425" spans="1:6" x14ac:dyDescent="0.25">
@@ -13239,30 +13233,30 @@
         <v>3</v>
       </c>
       <c r="D425" s="1" t="s">
-        <v>878</v>
+        <v>891</v>
       </c>
       <c r="E425" s="1" t="s">
-        <v>22</v>
+        <v>4</v>
       </c>
       <c r="F425" s="1" t="s">
-        <v>64</v>
+        <v>5</v>
       </c>
     </row>
     <row r="426" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A426" s="1" t="s">
+        <v>892</v>
+      </c>
+      <c r="B426" s="1" t="s">
+        <v>893</v>
+      </c>
+      <c r="C426" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D426" s="1" t="s">
         <v>891</v>
       </c>
-      <c r="B426" s="1" t="s">
-        <v>892</v>
-      </c>
-      <c r="C426" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D426" s="1" t="s">
-        <v>893</v>
-      </c>
       <c r="E426" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F426" s="1" t="s">
         <v>5</v>
@@ -13279,33 +13273,33 @@
         <v>3</v>
       </c>
       <c r="D427" s="1" t="s">
-        <v>893</v>
+        <v>891</v>
       </c>
       <c r="E427" s="1" t="s">
-        <v>8</v>
+        <v>45</v>
       </c>
       <c r="F427" s="1" t="s">
-        <v>5</v>
+        <v>896</v>
       </c>
     </row>
     <row r="428" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A428" s="1" t="s">
-        <v>896</v>
+        <v>897</v>
       </c>
       <c r="B428" s="1" t="s">
-        <v>897</v>
+        <v>898</v>
       </c>
       <c r="C428" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D428" s="1" t="s">
-        <v>893</v>
+        <v>891</v>
       </c>
       <c r="E428" s="1" t="s">
-        <v>45</v>
+        <v>12</v>
       </c>
       <c r="F428" s="1" t="s">
-        <v>898</v>
+        <v>9</v>
       </c>
     </row>
     <row r="429" spans="1:6" x14ac:dyDescent="0.25">
@@ -13319,13 +13313,13 @@
         <v>3</v>
       </c>
       <c r="D429" s="1" t="s">
-        <v>893</v>
+        <v>891</v>
       </c>
       <c r="E429" s="1" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="F429" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="430" spans="1:6" x14ac:dyDescent="0.25">
@@ -13339,10 +13333,10 @@
         <v>3</v>
       </c>
       <c r="D430" s="1" t="s">
-        <v>893</v>
+        <v>891</v>
       </c>
       <c r="E430" s="1" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="F430" s="1" t="s">
         <v>5</v>
@@ -13359,13 +13353,13 @@
         <v>3</v>
       </c>
       <c r="D431" s="1" t="s">
-        <v>893</v>
+        <v>891</v>
       </c>
       <c r="E431" s="1" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="F431" s="1" t="s">
-        <v>5</v>
+        <v>64</v>
       </c>
     </row>
     <row r="432" spans="1:6" x14ac:dyDescent="0.25">
@@ -13379,13 +13373,13 @@
         <v>3</v>
       </c>
       <c r="D432" s="1" t="s">
-        <v>893</v>
+        <v>891</v>
       </c>
       <c r="E432" s="1" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="F432" s="1" t="s">
-        <v>64</v>
+        <v>13</v>
       </c>
     </row>
     <row r="433" spans="1:6" x14ac:dyDescent="0.25">
@@ -13399,13 +13393,13 @@
         <v>3</v>
       </c>
       <c r="D433" s="1" t="s">
-        <v>893</v>
+        <v>891</v>
       </c>
       <c r="E433" s="1" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="F433" s="1" t="s">
-        <v>13</v>
+        <v>5</v>
       </c>
     </row>
     <row r="434" spans="1:6" x14ac:dyDescent="0.25">
@@ -13419,10 +13413,10 @@
         <v>3</v>
       </c>
       <c r="D434" s="1" t="s">
-        <v>893</v>
+        <v>891</v>
       </c>
       <c r="E434" s="1" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="F434" s="1" t="s">
         <v>5</v>
@@ -13439,13 +13433,13 @@
         <v>3</v>
       </c>
       <c r="D435" s="1" t="s">
-        <v>893</v>
+        <v>891</v>
       </c>
       <c r="E435" s="1" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="F435" s="1" t="s">
-        <v>5</v>
+        <v>13</v>
       </c>
     </row>
     <row r="436" spans="1:6" x14ac:dyDescent="0.25">
@@ -13459,13 +13453,13 @@
         <v>3</v>
       </c>
       <c r="D436" s="1" t="s">
-        <v>893</v>
+        <v>891</v>
       </c>
       <c r="E436" s="1" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="F436" s="1" t="s">
-        <v>13</v>
+        <v>64</v>
       </c>
     </row>
     <row r="437" spans="1:6" x14ac:dyDescent="0.25">
@@ -13479,13 +13473,13 @@
         <v>3</v>
       </c>
       <c r="D437" s="1" t="s">
-        <v>893</v>
+        <v>891</v>
       </c>
       <c r="E437" s="1" t="s">
-        <v>38</v>
+        <v>90</v>
       </c>
       <c r="F437" s="1" t="s">
-        <v>64</v>
+        <v>5</v>
       </c>
     </row>
     <row r="438" spans="1:6" x14ac:dyDescent="0.25">
@@ -13499,10 +13493,10 @@
         <v>3</v>
       </c>
       <c r="D438" s="1" t="s">
-        <v>893</v>
+        <v>891</v>
       </c>
       <c r="E438" s="1" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="F438" s="1" t="s">
         <v>5</v>
@@ -13519,10 +13513,10 @@
         <v>3</v>
       </c>
       <c r="D439" s="1" t="s">
-        <v>893</v>
+        <v>891</v>
       </c>
       <c r="E439" s="1" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="F439" s="1" t="s">
         <v>5</v>
@@ -13539,10 +13533,10 @@
         <v>3</v>
       </c>
       <c r="D440" s="1" t="s">
-        <v>893</v>
+        <v>891</v>
       </c>
       <c r="E440" s="1" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="F440" s="1" t="s">
         <v>5</v>
@@ -13559,10 +13553,10 @@
         <v>3</v>
       </c>
       <c r="D441" s="1" t="s">
-        <v>893</v>
+        <v>925</v>
       </c>
       <c r="E441" s="1" t="s">
-        <v>99</v>
+        <v>4</v>
       </c>
       <c r="F441" s="1" t="s">
         <v>5</v>
@@ -13570,19 +13564,19 @@
     </row>
     <row r="442" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A442" s="1" t="s">
+        <v>926</v>
+      </c>
+      <c r="B442" s="1" t="s">
+        <v>927</v>
+      </c>
+      <c r="C442" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D442" s="1" t="s">
         <v>925</v>
       </c>
-      <c r="B442" s="1" t="s">
-        <v>926</v>
-      </c>
-      <c r="C442" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D442" s="1" t="s">
-        <v>927</v>
-      </c>
       <c r="E442" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F442" s="1" t="s">
         <v>5</v>
@@ -13599,10 +13593,10 @@
         <v>3</v>
       </c>
       <c r="D443" s="1" t="s">
-        <v>927</v>
+        <v>925</v>
       </c>
       <c r="E443" s="1" t="s">
-        <v>8</v>
+        <v>45</v>
       </c>
       <c r="F443" s="1" t="s">
         <v>5</v>
@@ -13619,10 +13613,10 @@
         <v>3</v>
       </c>
       <c r="D444" s="1" t="s">
-        <v>927</v>
+        <v>925</v>
       </c>
       <c r="E444" s="1" t="s">
-        <v>45</v>
+        <v>12</v>
       </c>
       <c r="F444" s="1" t="s">
         <v>5</v>
@@ -13639,13 +13633,13 @@
         <v>3</v>
       </c>
       <c r="D445" s="1" t="s">
-        <v>927</v>
+        <v>925</v>
       </c>
       <c r="E445" s="1" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="F445" s="1" t="s">
-        <v>5</v>
+        <v>29</v>
       </c>
     </row>
     <row r="446" spans="1:6" x14ac:dyDescent="0.25">
@@ -13659,13 +13653,13 @@
         <v>3</v>
       </c>
       <c r="D446" s="1" t="s">
-        <v>927</v>
+        <v>925</v>
       </c>
       <c r="E446" s="1" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="F446" s="1" t="s">
-        <v>29</v>
+        <v>64</v>
       </c>
     </row>
     <row r="447" spans="1:6" x14ac:dyDescent="0.25">
@@ -13679,13 +13673,13 @@
         <v>3</v>
       </c>
       <c r="D447" s="1" t="s">
-        <v>927</v>
+        <v>925</v>
       </c>
       <c r="E447" s="1" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="F447" s="1" t="s">
-        <v>64</v>
+        <v>167</v>
       </c>
     </row>
     <row r="448" spans="1:6" x14ac:dyDescent="0.25">
@@ -13699,13 +13693,13 @@
         <v>3</v>
       </c>
       <c r="D448" s="1" t="s">
-        <v>927</v>
+        <v>925</v>
       </c>
       <c r="E448" s="1" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="F448" s="1" t="s">
-        <v>167</v>
+        <v>13</v>
       </c>
     </row>
     <row r="449" spans="1:6" x14ac:dyDescent="0.25">
@@ -13719,13 +13713,13 @@
         <v>3</v>
       </c>
       <c r="D449" s="1" t="s">
-        <v>927</v>
+        <v>925</v>
       </c>
       <c r="E449" s="1" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="F449" s="1" t="s">
-        <v>13</v>
+        <v>5</v>
       </c>
     </row>
     <row r="450" spans="1:6" x14ac:dyDescent="0.25">
@@ -13739,13 +13733,13 @@
         <v>3</v>
       </c>
       <c r="D450" s="1" t="s">
-        <v>927</v>
+        <v>925</v>
       </c>
       <c r="E450" s="1" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="F450" s="1" t="s">
-        <v>5</v>
+        <v>29</v>
       </c>
     </row>
     <row r="451" spans="1:6" x14ac:dyDescent="0.25">
@@ -13759,10 +13753,10 @@
         <v>3</v>
       </c>
       <c r="D451" s="1" t="s">
-        <v>927</v>
+        <v>925</v>
       </c>
       <c r="E451" s="1" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="F451" s="1" t="s">
         <v>29</v>
@@ -13779,10 +13773,10 @@
         <v>3</v>
       </c>
       <c r="D452" s="1" t="s">
-        <v>927</v>
+        <v>925</v>
       </c>
       <c r="E452" s="1" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="F452" s="1" t="s">
         <v>29</v>
@@ -13799,13 +13793,13 @@
         <v>3</v>
       </c>
       <c r="D453" s="1" t="s">
-        <v>927</v>
+        <v>925</v>
       </c>
       <c r="E453" s="1" t="s">
-        <v>38</v>
+        <v>90</v>
       </c>
       <c r="F453" s="1" t="s">
-        <v>29</v>
+        <v>9</v>
       </c>
     </row>
     <row r="454" spans="1:6" x14ac:dyDescent="0.25">
@@ -13819,13 +13813,13 @@
         <v>3</v>
       </c>
       <c r="D454" s="1" t="s">
-        <v>927</v>
+        <v>925</v>
       </c>
       <c r="E454" s="1" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="F454" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="455" spans="1:6" x14ac:dyDescent="0.25">
@@ -13839,30 +13833,30 @@
         <v>3</v>
       </c>
       <c r="D455" s="1" t="s">
-        <v>927</v>
+        <v>954</v>
       </c>
       <c r="E455" s="1" t="s">
-        <v>93</v>
+        <v>4</v>
       </c>
       <c r="F455" s="1" t="s">
-        <v>5</v>
+        <v>64</v>
       </c>
     </row>
     <row r="456" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A456" s="1" t="s">
+        <v>955</v>
+      </c>
+      <c r="B456" s="1" t="s">
+        <v>956</v>
+      </c>
+      <c r="C456" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D456" s="1" t="s">
         <v>954</v>
       </c>
-      <c r="B456" s="1" t="s">
-        <v>955</v>
-      </c>
-      <c r="C456" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D456" s="1" t="s">
-        <v>956</v>
-      </c>
       <c r="E456" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F456" s="1" t="s">
         <v>64</v>
@@ -13879,10 +13873,10 @@
         <v>3</v>
       </c>
       <c r="D457" s="1" t="s">
-        <v>956</v>
+        <v>954</v>
       </c>
       <c r="E457" s="1" t="s">
-        <v>8</v>
+        <v>45</v>
       </c>
       <c r="F457" s="1" t="s">
         <v>64</v>
@@ -13899,13 +13893,13 @@
         <v>3</v>
       </c>
       <c r="D458" s="1" t="s">
-        <v>956</v>
+        <v>954</v>
       </c>
       <c r="E458" s="1" t="s">
-        <v>45</v>
+        <v>12</v>
       </c>
       <c r="F458" s="1" t="s">
-        <v>64</v>
+        <v>5</v>
       </c>
     </row>
     <row r="459" spans="1:6" x14ac:dyDescent="0.25">
@@ -13919,10 +13913,10 @@
         <v>3</v>
       </c>
       <c r="D459" s="1" t="s">
-        <v>956</v>
+        <v>954</v>
       </c>
       <c r="E459" s="1" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="F459" s="1" t="s">
         <v>5</v>
@@ -13939,13 +13933,13 @@
         <v>3</v>
       </c>
       <c r="D460" s="1" t="s">
-        <v>956</v>
+        <v>954</v>
       </c>
       <c r="E460" s="1" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="F460" s="1" t="s">
-        <v>5</v>
+        <v>64</v>
       </c>
     </row>
     <row r="461" spans="1:6" x14ac:dyDescent="0.25">
@@ -13959,13 +13953,13 @@
         <v>3</v>
       </c>
       <c r="D461" s="1" t="s">
-        <v>956</v>
+        <v>954</v>
       </c>
       <c r="E461" s="1" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="F461" s="1" t="s">
-        <v>64</v>
+        <v>120</v>
       </c>
     </row>
     <row r="462" spans="1:6" x14ac:dyDescent="0.25">
@@ -13979,10 +13973,10 @@
         <v>3</v>
       </c>
       <c r="D462" s="1" t="s">
-        <v>956</v>
+        <v>954</v>
       </c>
       <c r="E462" s="1" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="F462" s="1" t="s">
         <v>120</v>
@@ -13999,13 +13993,13 @@
         <v>3</v>
       </c>
       <c r="D463" s="1" t="s">
-        <v>956</v>
+        <v>954</v>
       </c>
       <c r="E463" s="1" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="F463" s="1" t="s">
-        <v>120</v>
+        <v>13</v>
       </c>
     </row>
     <row r="464" spans="1:6" x14ac:dyDescent="0.25">
@@ -14019,10 +14013,10 @@
         <v>3</v>
       </c>
       <c r="D464" s="1" t="s">
-        <v>956</v>
+        <v>954</v>
       </c>
       <c r="E464" s="1" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="F464" s="1" t="s">
         <v>13</v>
@@ -14039,13 +14033,13 @@
         <v>3</v>
       </c>
       <c r="D465" s="1" t="s">
-        <v>956</v>
+        <v>954</v>
       </c>
       <c r="E465" s="1" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="F465" s="1" t="s">
-        <v>13</v>
+        <v>64</v>
       </c>
     </row>
     <row r="466" spans="1:6" x14ac:dyDescent="0.25">
@@ -14059,10 +14053,10 @@
         <v>3</v>
       </c>
       <c r="D466" s="1" t="s">
-        <v>956</v>
+        <v>954</v>
       </c>
       <c r="E466" s="1" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="F466" s="1" t="s">
         <v>64</v>
@@ -14079,13 +14073,13 @@
         <v>3</v>
       </c>
       <c r="D467" s="1" t="s">
-        <v>956</v>
+        <v>954</v>
       </c>
       <c r="E467" s="1" t="s">
-        <v>38</v>
+        <v>90</v>
       </c>
       <c r="F467" s="1" t="s">
-        <v>64</v>
+        <v>5</v>
       </c>
     </row>
     <row r="468" spans="1:6" x14ac:dyDescent="0.25">
@@ -14099,10 +14093,10 @@
         <v>3</v>
       </c>
       <c r="D468" s="1" t="s">
-        <v>956</v>
+        <v>954</v>
       </c>
       <c r="E468" s="1" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="F468" s="1" t="s">
         <v>5</v>
@@ -14119,10 +14113,10 @@
         <v>3</v>
       </c>
       <c r="D469" s="1" t="s">
-        <v>956</v>
+        <v>954</v>
       </c>
       <c r="E469" s="1" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="F469" s="1" t="s">
         <v>5</v>
@@ -14139,33 +14133,33 @@
         <v>3</v>
       </c>
       <c r="D470" s="1" t="s">
-        <v>956</v>
+        <v>985</v>
       </c>
       <c r="E470" s="1" t="s">
-        <v>96</v>
+        <v>4</v>
       </c>
       <c r="F470" s="1" t="s">
-        <v>5</v>
+        <v>64</v>
       </c>
     </row>
     <row r="471" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A471" s="1" t="s">
+        <v>986</v>
+      </c>
+      <c r="B471" s="1" t="s">
+        <v>987</v>
+      </c>
+      <c r="C471" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D471" s="1" t="s">
         <v>985</v>
       </c>
-      <c r="B471" s="1" t="s">
-        <v>986</v>
-      </c>
-      <c r="C471" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D471" s="1" t="s">
-        <v>987</v>
-      </c>
       <c r="E471" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F471" s="1" t="s">
-        <v>64</v>
+        <v>5</v>
       </c>
     </row>
     <row r="472" spans="1:6" x14ac:dyDescent="0.25">
@@ -14179,33 +14173,33 @@
         <v>3</v>
       </c>
       <c r="D472" s="1" t="s">
-        <v>987</v>
+        <v>985</v>
       </c>
       <c r="E472" s="1" t="s">
-        <v>8</v>
+        <v>45</v>
       </c>
       <c r="F472" s="1" t="s">
-        <v>5</v>
+        <v>990</v>
       </c>
     </row>
     <row r="473" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A473" s="1" t="s">
+        <v>991</v>
+      </c>
+      <c r="B473" s="1" t="s">
+        <v>992</v>
+      </c>
+      <c r="C473" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D473" s="1" t="s">
+        <v>985</v>
+      </c>
+      <c r="E473" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="F473" s="1" t="s">
         <v>990</v>
-      </c>
-      <c r="B473" s="1" t="s">
-        <v>991</v>
-      </c>
-      <c r="C473" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D473" s="1" t="s">
-        <v>987</v>
-      </c>
-      <c r="E473" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="F473" s="1" t="s">
-        <v>992</v>
       </c>
     </row>
     <row r="474" spans="1:6" x14ac:dyDescent="0.25">
@@ -14219,13 +14213,13 @@
         <v>3</v>
       </c>
       <c r="D474" s="1" t="s">
-        <v>987</v>
+        <v>985</v>
       </c>
       <c r="E474" s="1" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="F474" s="1" t="s">
-        <v>992</v>
+        <v>5</v>
       </c>
     </row>
     <row r="475" spans="1:6" x14ac:dyDescent="0.25">
@@ -14239,10 +14233,10 @@
         <v>3</v>
       </c>
       <c r="D475" s="1" t="s">
-        <v>987</v>
+        <v>985</v>
       </c>
       <c r="E475" s="1" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="F475" s="1" t="s">
         <v>5</v>
@@ -14259,10 +14253,10 @@
         <v>3</v>
       </c>
       <c r="D476" s="1" t="s">
-        <v>987</v>
+        <v>985</v>
       </c>
       <c r="E476" s="1" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="F476" s="1" t="s">
         <v>5</v>
@@ -14279,10 +14273,10 @@
         <v>3</v>
       </c>
       <c r="D477" s="1" t="s">
-        <v>987</v>
+        <v>985</v>
       </c>
       <c r="E477" s="1" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="F477" s="1" t="s">
         <v>5</v>
@@ -14299,10 +14293,10 @@
         <v>3</v>
       </c>
       <c r="D478" s="1" t="s">
-        <v>987</v>
+        <v>985</v>
       </c>
       <c r="E478" s="1" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="F478" s="1" t="s">
         <v>5</v>
@@ -14319,10 +14313,10 @@
         <v>3</v>
       </c>
       <c r="D479" s="1" t="s">
-        <v>987</v>
+        <v>985</v>
       </c>
       <c r="E479" s="1" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="F479" s="1" t="s">
         <v>5</v>
@@ -14339,10 +14333,10 @@
         <v>3</v>
       </c>
       <c r="D480" s="1" t="s">
-        <v>987</v>
+        <v>985</v>
       </c>
       <c r="E480" s="1" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="F480" s="1" t="s">
         <v>5</v>
@@ -14359,10 +14353,10 @@
         <v>3</v>
       </c>
       <c r="D481" s="1" t="s">
-        <v>987</v>
+        <v>985</v>
       </c>
       <c r="E481" s="1" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="F481" s="1" t="s">
         <v>5</v>
@@ -14379,10 +14373,10 @@
         <v>3</v>
       </c>
       <c r="D482" s="1" t="s">
-        <v>987</v>
+        <v>985</v>
       </c>
       <c r="E482" s="1" t="s">
-        <v>38</v>
+        <v>90</v>
       </c>
       <c r="F482" s="1" t="s">
         <v>5</v>
@@ -14399,10 +14393,10 @@
         <v>3</v>
       </c>
       <c r="D483" s="1" t="s">
-        <v>987</v>
+        <v>985</v>
       </c>
       <c r="E483" s="1" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="F483" s="1" t="s">
         <v>5</v>
@@ -14419,10 +14413,10 @@
         <v>3</v>
       </c>
       <c r="D484" s="1" t="s">
-        <v>987</v>
+        <v>985</v>
       </c>
       <c r="E484" s="1" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="F484" s="1" t="s">
         <v>5</v>
@@ -14439,10 +14433,10 @@
         <v>3</v>
       </c>
       <c r="D485" s="1" t="s">
-        <v>987</v>
+        <v>985</v>
       </c>
       <c r="E485" s="1" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="F485" s="1" t="s">
         <v>5</v>
@@ -14459,33 +14453,33 @@
         <v>3</v>
       </c>
       <c r="D486" s="1" t="s">
-        <v>987</v>
+        <v>1019</v>
       </c>
       <c r="E486" s="1" t="s">
-        <v>99</v>
+        <v>4</v>
       </c>
       <c r="F486" s="1" t="s">
-        <v>5</v>
+        <v>13</v>
       </c>
     </row>
     <row r="487" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A487" s="1" t="s">
+        <v>1020</v>
+      </c>
+      <c r="B487" s="1" t="s">
+        <v>1021</v>
+      </c>
+      <c r="C487" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D487" s="1" t="s">
         <v>1019</v>
       </c>
-      <c r="B487" s="1" t="s">
-        <v>1020</v>
-      </c>
-      <c r="C487" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D487" s="1" t="s">
-        <v>1021</v>
-      </c>
       <c r="E487" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F487" s="1" t="s">
-        <v>13</v>
+        <v>5</v>
       </c>
     </row>
     <row r="488" spans="1:6" x14ac:dyDescent="0.25">
@@ -14499,10 +14493,10 @@
         <v>3</v>
       </c>
       <c r="D488" s="1" t="s">
-        <v>1021</v>
+        <v>1019</v>
       </c>
       <c r="E488" s="1" t="s">
-        <v>8</v>
+        <v>45</v>
       </c>
       <c r="F488" s="1" t="s">
         <v>5</v>
@@ -14519,10 +14513,10 @@
         <v>3</v>
       </c>
       <c r="D489" s="1" t="s">
-        <v>1021</v>
+        <v>1019</v>
       </c>
       <c r="E489" s="1" t="s">
-        <v>45</v>
+        <v>12</v>
       </c>
       <c r="F489" s="1" t="s">
         <v>5</v>
@@ -14539,13 +14533,13 @@
         <v>3</v>
       </c>
       <c r="D490" s="1" t="s">
-        <v>1021</v>
+        <v>1019</v>
       </c>
       <c r="E490" s="1" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="F490" s="1" t="s">
-        <v>5</v>
+        <v>120</v>
       </c>
     </row>
     <row r="491" spans="1:6" x14ac:dyDescent="0.25">
@@ -14559,10 +14553,10 @@
         <v>3</v>
       </c>
       <c r="D491" s="1" t="s">
-        <v>1021</v>
+        <v>1019</v>
       </c>
       <c r="E491" s="1" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="F491" s="1" t="s">
         <v>120</v>
@@ -14579,13 +14573,13 @@
         <v>3</v>
       </c>
       <c r="D492" s="1" t="s">
-        <v>1021</v>
+        <v>1019</v>
       </c>
       <c r="E492" s="1" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="F492" s="1" t="s">
-        <v>120</v>
+        <v>5</v>
       </c>
     </row>
     <row r="493" spans="1:6" x14ac:dyDescent="0.25">
@@ -14599,10 +14593,10 @@
         <v>3</v>
       </c>
       <c r="D493" s="1" t="s">
-        <v>1021</v>
+        <v>1019</v>
       </c>
       <c r="E493" s="1" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="F493" s="1" t="s">
         <v>5</v>
@@ -14619,10 +14613,10 @@
         <v>3</v>
       </c>
       <c r="D494" s="1" t="s">
-        <v>1021</v>
+        <v>1019</v>
       </c>
       <c r="E494" s="1" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="F494" s="1" t="s">
         <v>5</v>
@@ -14639,33 +14633,33 @@
         <v>3</v>
       </c>
       <c r="D495" s="1" t="s">
-        <v>1021</v>
+        <v>1019</v>
       </c>
       <c r="E495" s="1" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="F495" s="1" t="s">
-        <v>5</v>
+        <v>1038</v>
       </c>
     </row>
     <row r="496" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A496" s="1" t="s">
-        <v>1038</v>
+        <v>1039</v>
       </c>
       <c r="B496" s="1" t="s">
-        <v>1039</v>
+        <v>1040</v>
       </c>
       <c r="C496" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D496" s="1" t="s">
-        <v>1021</v>
+        <v>1019</v>
       </c>
       <c r="E496" s="1" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="F496" s="1" t="s">
-        <v>1040</v>
+        <v>5</v>
       </c>
     </row>
     <row r="497" spans="1:6" x14ac:dyDescent="0.25">
@@ -14679,10 +14673,10 @@
         <v>3</v>
       </c>
       <c r="D497" s="1" t="s">
-        <v>1021</v>
+        <v>1019</v>
       </c>
       <c r="E497" s="1" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="F497" s="1" t="s">
         <v>5</v>
@@ -14699,10 +14693,10 @@
         <v>3</v>
       </c>
       <c r="D498" s="1" t="s">
-        <v>1021</v>
+        <v>1019</v>
       </c>
       <c r="E498" s="1" t="s">
-        <v>38</v>
+        <v>90</v>
       </c>
       <c r="F498" s="1" t="s">
         <v>5</v>
@@ -14719,10 +14713,10 @@
         <v>3</v>
       </c>
       <c r="D499" s="1" t="s">
-        <v>1021</v>
+        <v>1019</v>
       </c>
       <c r="E499" s="1" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="F499" s="1" t="s">
         <v>5</v>
@@ -14739,10 +14733,10 @@
         <v>3</v>
       </c>
       <c r="D500" s="1" t="s">
-        <v>1021</v>
+        <v>1019</v>
       </c>
       <c r="E500" s="1" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="F500" s="1" t="s">
         <v>5</v>
@@ -14759,10 +14753,10 @@
         <v>3</v>
       </c>
       <c r="D501" s="1" t="s">
-        <v>1021</v>
+        <v>1019</v>
       </c>
       <c r="E501" s="1" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="F501" s="1" t="s">
         <v>5</v>
@@ -14779,13 +14773,13 @@
         <v>3</v>
       </c>
       <c r="D502" s="1" t="s">
-        <v>1021</v>
+        <v>1019</v>
       </c>
       <c r="E502" s="1" t="s">
-        <v>99</v>
+        <v>136</v>
       </c>
       <c r="F502" s="1" t="s">
-        <v>5</v>
+        <v>13</v>
       </c>
     </row>
     <row r="503" spans="1:6" x14ac:dyDescent="0.25">
@@ -14799,10 +14793,10 @@
         <v>3</v>
       </c>
       <c r="D503" s="1" t="s">
-        <v>1021</v>
+        <v>1019</v>
       </c>
       <c r="E503" s="1" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="F503" s="1" t="s">
         <v>13</v>
@@ -14819,30 +14813,30 @@
         <v>3</v>
       </c>
       <c r="D504" s="1" t="s">
-        <v>1021</v>
+        <v>1057</v>
       </c>
       <c r="E504" s="1" t="s">
-        <v>139</v>
+        <v>4</v>
       </c>
       <c r="F504" s="1" t="s">
-        <v>13</v>
+        <v>5</v>
       </c>
     </row>
     <row r="505" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A505" s="1" t="s">
+        <v>1058</v>
+      </c>
+      <c r="B505" s="1" t="s">
+        <v>1059</v>
+      </c>
+      <c r="C505" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D505" s="1" t="s">
         <v>1057</v>
       </c>
-      <c r="B505" s="1" t="s">
-        <v>1058</v>
-      </c>
-      <c r="C505" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D505" s="1" t="s">
-        <v>1059</v>
-      </c>
       <c r="E505" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F505" s="1" t="s">
         <v>5</v>
@@ -14859,10 +14853,10 @@
         <v>3</v>
       </c>
       <c r="D506" s="1" t="s">
-        <v>1059</v>
+        <v>1057</v>
       </c>
       <c r="E506" s="1" t="s">
-        <v>8</v>
+        <v>45</v>
       </c>
       <c r="F506" s="1" t="s">
         <v>5</v>
@@ -14879,10 +14873,10 @@
         <v>3</v>
       </c>
       <c r="D507" s="1" t="s">
-        <v>1059</v>
+        <v>1057</v>
       </c>
       <c r="E507" s="1" t="s">
-        <v>45</v>
+        <v>12</v>
       </c>
       <c r="F507" s="1" t="s">
         <v>5</v>
@@ -14899,10 +14893,10 @@
         <v>3</v>
       </c>
       <c r="D508" s="1" t="s">
-        <v>1059</v>
+        <v>1057</v>
       </c>
       <c r="E508" s="1" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="F508" s="1" t="s">
         <v>5</v>
@@ -14919,10 +14913,10 @@
         <v>3</v>
       </c>
       <c r="D509" s="1" t="s">
-        <v>1059</v>
+        <v>1057</v>
       </c>
       <c r="E509" s="1" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="F509" s="1" t="s">
         <v>5</v>
@@ -14939,10 +14933,10 @@
         <v>3</v>
       </c>
       <c r="D510" s="1" t="s">
-        <v>1059</v>
+        <v>1057</v>
       </c>
       <c r="E510" s="1" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="F510" s="1" t="s">
         <v>5</v>
@@ -14959,10 +14953,10 @@
         <v>3</v>
       </c>
       <c r="D511" s="1" t="s">
-        <v>1059</v>
+        <v>1057</v>
       </c>
       <c r="E511" s="1" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="F511" s="1" t="s">
         <v>5</v>
@@ -14979,10 +14973,10 @@
         <v>3</v>
       </c>
       <c r="D512" s="1" t="s">
-        <v>1059</v>
+        <v>1057</v>
       </c>
       <c r="E512" s="1" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="F512" s="1" t="s">
         <v>5</v>
@@ -14999,10 +14993,10 @@
         <v>3</v>
       </c>
       <c r="D513" s="1" t="s">
-        <v>1059</v>
+        <v>1057</v>
       </c>
       <c r="E513" s="1" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="F513" s="1" t="s">
         <v>5</v>
@@ -15019,10 +15013,10 @@
         <v>3</v>
       </c>
       <c r="D514" s="1" t="s">
-        <v>1059</v>
+        <v>1057</v>
       </c>
       <c r="E514" s="1" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="F514" s="1" t="s">
         <v>5</v>
@@ -15039,10 +15033,10 @@
         <v>3</v>
       </c>
       <c r="D515" s="1" t="s">
-        <v>1059</v>
+        <v>1057</v>
       </c>
       <c r="E515" s="1" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="F515" s="1" t="s">
         <v>5</v>
@@ -15059,10 +15053,10 @@
         <v>3</v>
       </c>
       <c r="D516" s="1" t="s">
-        <v>1059</v>
+        <v>1057</v>
       </c>
       <c r="E516" s="1" t="s">
-        <v>38</v>
+        <v>90</v>
       </c>
       <c r="F516" s="1" t="s">
         <v>5</v>
@@ -15079,10 +15073,10 @@
         <v>3</v>
       </c>
       <c r="D517" s="1" t="s">
-        <v>1059</v>
+        <v>1057</v>
       </c>
       <c r="E517" s="1" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="F517" s="1" t="s">
         <v>5</v>
@@ -15099,10 +15093,10 @@
         <v>3</v>
       </c>
       <c r="D518" s="1" t="s">
-        <v>1059</v>
+        <v>1057</v>
       </c>
       <c r="E518" s="1" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="F518" s="1" t="s">
         <v>5</v>
@@ -15119,33 +15113,33 @@
         <v>3</v>
       </c>
       <c r="D519" s="1" t="s">
-        <v>1059</v>
+        <v>1088</v>
       </c>
       <c r="E519" s="1" t="s">
-        <v>96</v>
+        <v>4</v>
       </c>
       <c r="F519" s="1" t="s">
-        <v>5</v>
+        <v>64</v>
       </c>
     </row>
     <row r="520" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A520" s="1" t="s">
+        <v>1089</v>
+      </c>
+      <c r="B520" s="1" t="s">
+        <v>1090</v>
+      </c>
+      <c r="C520" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D520" s="1" t="s">
         <v>1088</v>
-      </c>
-      <c r="B520" s="1" t="s">
-        <v>1089</v>
-      </c>
-      <c r="C520" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D520" s="1" t="s">
-        <v>1090</v>
       </c>
       <c r="E520" s="1" t="s">
         <v>4</v>
       </c>
       <c r="F520" s="1" t="s">
-        <v>64</v>
+        <v>5</v>
       </c>
     </row>
     <row r="521" spans="1:6" x14ac:dyDescent="0.25">
@@ -15159,7 +15153,7 @@
         <v>3</v>
       </c>
       <c r="D521" s="1" t="s">
-        <v>1090</v>
+        <v>1088</v>
       </c>
       <c r="E521" s="1" t="s">
         <v>4</v>
@@ -15179,13 +15173,13 @@
         <v>3</v>
       </c>
       <c r="D522" s="1" t="s">
-        <v>1090</v>
+        <v>1088</v>
       </c>
       <c r="E522" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F522" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="523" spans="1:6" x14ac:dyDescent="0.25">
@@ -15199,13 +15193,13 @@
         <v>3</v>
       </c>
       <c r="D523" s="1" t="s">
-        <v>1090</v>
+        <v>1088</v>
       </c>
       <c r="E523" s="1" t="s">
         <v>8</v>
       </c>
       <c r="F523" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="524" spans="1:6" x14ac:dyDescent="0.25">
@@ -15219,7 +15213,7 @@
         <v>3</v>
       </c>
       <c r="D524" s="1" t="s">
-        <v>1090</v>
+        <v>1088</v>
       </c>
       <c r="E524" s="1" t="s">
         <v>8</v>
@@ -15239,10 +15233,10 @@
         <v>3</v>
       </c>
       <c r="D525" s="1" t="s">
-        <v>1090</v>
+        <v>1088</v>
       </c>
       <c r="E525" s="1" t="s">
-        <v>8</v>
+        <v>45</v>
       </c>
       <c r="F525" s="1" t="s">
         <v>5</v>
@@ -15259,7 +15253,7 @@
         <v>3</v>
       </c>
       <c r="D526" s="1" t="s">
-        <v>1090</v>
+        <v>1088</v>
       </c>
       <c r="E526" s="1" t="s">
         <v>45</v>
@@ -15279,7 +15273,7 @@
         <v>3</v>
       </c>
       <c r="D527" s="1" t="s">
-        <v>1090</v>
+        <v>1088</v>
       </c>
       <c r="E527" s="1" t="s">
         <v>45</v>
@@ -15299,10 +15293,10 @@
         <v>3</v>
       </c>
       <c r="D528" s="1" t="s">
-        <v>1090</v>
+        <v>1088</v>
       </c>
       <c r="E528" s="1" t="s">
-        <v>45</v>
+        <v>12</v>
       </c>
       <c r="F528" s="1" t="s">
         <v>5</v>
@@ -15319,7 +15313,7 @@
         <v>3</v>
       </c>
       <c r="D529" s="1" t="s">
-        <v>1090</v>
+        <v>1088</v>
       </c>
       <c r="E529" s="1" t="s">
         <v>12</v>
@@ -15339,7 +15333,7 @@
         <v>3</v>
       </c>
       <c r="D530" s="1" t="s">
-        <v>1090</v>
+        <v>1088</v>
       </c>
       <c r="E530" s="1" t="s">
         <v>12</v>
@@ -15359,10 +15353,10 @@
         <v>3</v>
       </c>
       <c r="D531" s="1" t="s">
-        <v>1090</v>
+        <v>1088</v>
       </c>
       <c r="E531" s="1" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="F531" s="1" t="s">
         <v>5</v>
@@ -15379,7 +15373,7 @@
         <v>3</v>
       </c>
       <c r="D532" s="1" t="s">
-        <v>1090</v>
+        <v>1088</v>
       </c>
       <c r="E532" s="1" t="s">
         <v>16</v>
@@ -15399,7 +15393,7 @@
         <v>3</v>
       </c>
       <c r="D533" s="1" t="s">
-        <v>1090</v>
+        <v>1088</v>
       </c>
       <c r="E533" s="1" t="s">
         <v>16</v>
@@ -15419,13 +15413,13 @@
         <v>3</v>
       </c>
       <c r="D534" s="1" t="s">
-        <v>1090</v>
+        <v>1088</v>
       </c>
       <c r="E534" s="1" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="F534" s="1" t="s">
-        <v>5</v>
+        <v>64</v>
       </c>
     </row>
     <row r="535" spans="1:6" x14ac:dyDescent="0.25">
@@ -15439,13 +15433,13 @@
         <v>3</v>
       </c>
       <c r="D535" s="1" t="s">
-        <v>1090</v>
+        <v>1088</v>
       </c>
       <c r="E535" s="1" t="s">
         <v>19</v>
       </c>
       <c r="F535" s="1" t="s">
-        <v>64</v>
+        <v>5</v>
       </c>
     </row>
     <row r="536" spans="1:6" x14ac:dyDescent="0.25">
@@ -15459,7 +15453,7 @@
         <v>3</v>
       </c>
       <c r="D536" s="1" t="s">
-        <v>1090</v>
+        <v>1088</v>
       </c>
       <c r="E536" s="1" t="s">
         <v>19</v>
@@ -15479,13 +15473,13 @@
         <v>3</v>
       </c>
       <c r="D537" s="1" t="s">
-        <v>1090</v>
+        <v>1088</v>
       </c>
       <c r="E537" s="1" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="F537" s="1" t="s">
-        <v>5</v>
+        <v>64</v>
       </c>
     </row>
     <row r="538" spans="1:6" x14ac:dyDescent="0.25">
@@ -15499,7 +15493,7 @@
         <v>3</v>
       </c>
       <c r="D538" s="1" t="s">
-        <v>1090</v>
+        <v>1088</v>
       </c>
       <c r="E538" s="1" t="s">
         <v>22</v>
@@ -15519,13 +15513,13 @@
         <v>3</v>
       </c>
       <c r="D539" s="1" t="s">
-        <v>1090</v>
+        <v>1088</v>
       </c>
       <c r="E539" s="1" t="s">
         <v>22</v>
       </c>
       <c r="F539" s="1" t="s">
-        <v>64</v>
+        <v>5</v>
       </c>
     </row>
     <row r="540" spans="1:6" x14ac:dyDescent="0.25">
@@ -15539,13 +15533,13 @@
         <v>3</v>
       </c>
       <c r="D540" s="1" t="s">
-        <v>1090</v>
+        <v>1088</v>
       </c>
       <c r="E540" s="1" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="F540" s="1" t="s">
-        <v>5</v>
+        <v>64</v>
       </c>
     </row>
     <row r="541" spans="1:6" x14ac:dyDescent="0.25">
@@ -15559,13 +15553,13 @@
         <v>3</v>
       </c>
       <c r="D541" s="1" t="s">
-        <v>1090</v>
+        <v>1088</v>
       </c>
       <c r="E541" s="1" t="s">
         <v>25</v>
       </c>
       <c r="F541" s="1" t="s">
-        <v>64</v>
+        <v>13</v>
       </c>
     </row>
     <row r="542" spans="1:6" x14ac:dyDescent="0.25">
@@ -15579,13 +15573,13 @@
         <v>3</v>
       </c>
       <c r="D542" s="1" t="s">
-        <v>1090</v>
+        <v>1088</v>
       </c>
       <c r="E542" s="1" t="s">
         <v>25</v>
       </c>
       <c r="F542" s="1" t="s">
-        <v>13</v>
+        <v>5</v>
       </c>
     </row>
     <row r="543" spans="1:6" x14ac:dyDescent="0.25">
@@ -15599,13 +15593,13 @@
         <v>3</v>
       </c>
       <c r="D543" s="1" t="s">
-        <v>1090</v>
+        <v>1088</v>
       </c>
       <c r="E543" s="1" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="F543" s="1" t="s">
-        <v>5</v>
+        <v>13</v>
       </c>
     </row>
     <row r="544" spans="1:6" x14ac:dyDescent="0.25">
@@ -15619,13 +15613,13 @@
         <v>3</v>
       </c>
       <c r="D544" s="1" t="s">
-        <v>1090</v>
+        <v>1088</v>
       </c>
       <c r="E544" s="1" t="s">
         <v>28</v>
       </c>
       <c r="F544" s="1" t="s">
-        <v>13</v>
+        <v>5</v>
       </c>
     </row>
     <row r="545" spans="1:6" x14ac:dyDescent="0.25">
@@ -15639,13 +15633,13 @@
         <v>3</v>
       </c>
       <c r="D545" s="1" t="s">
-        <v>1090</v>
+        <v>1088</v>
       </c>
       <c r="E545" s="1" t="s">
         <v>28</v>
       </c>
       <c r="F545" s="1" t="s">
-        <v>5</v>
+        <v>120</v>
       </c>
     </row>
     <row r="546" spans="1:6" x14ac:dyDescent="0.25">
@@ -15659,13 +15653,13 @@
         <v>3</v>
       </c>
       <c r="D546" s="1" t="s">
-        <v>1090</v>
+        <v>1088</v>
       </c>
       <c r="E546" s="1" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="F546" s="1" t="s">
-        <v>120</v>
+        <v>9</v>
       </c>
     </row>
     <row r="547" spans="1:6" x14ac:dyDescent="0.25">
@@ -15679,13 +15673,13 @@
         <v>3</v>
       </c>
       <c r="D547" s="1" t="s">
-        <v>1090</v>
+        <v>1088</v>
       </c>
       <c r="E547" s="1" t="s">
         <v>32</v>
       </c>
       <c r="F547" s="1" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
     </row>
     <row r="548" spans="1:6" x14ac:dyDescent="0.25">
@@ -15699,13 +15693,13 @@
         <v>3</v>
       </c>
       <c r="D548" s="1" t="s">
-        <v>1090</v>
+        <v>1088</v>
       </c>
       <c r="E548" s="1" t="s">
         <v>32</v>
       </c>
       <c r="F548" s="1" t="s">
-        <v>13</v>
+        <v>120</v>
       </c>
     </row>
     <row r="549" spans="1:6" x14ac:dyDescent="0.25">
@@ -15719,13 +15713,13 @@
         <v>3</v>
       </c>
       <c r="D549" s="1" t="s">
-        <v>1090</v>
+        <v>1088</v>
       </c>
       <c r="E549" s="1" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="F549" s="1" t="s">
-        <v>120</v>
+        <v>5</v>
       </c>
     </row>
     <row r="550" spans="1:6" x14ac:dyDescent="0.25">
@@ -15739,7 +15733,7 @@
         <v>3</v>
       </c>
       <c r="D550" s="1" t="s">
-        <v>1090</v>
+        <v>1088</v>
       </c>
       <c r="E550" s="1" t="s">
         <v>35</v>
@@ -15759,13 +15753,13 @@
         <v>3</v>
       </c>
       <c r="D551" s="1" t="s">
-        <v>1090</v>
+        <v>1088</v>
       </c>
       <c r="E551" s="1" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="F551" s="1" t="s">
-        <v>5</v>
+        <v>64</v>
       </c>
     </row>
     <row r="552" spans="1:6" x14ac:dyDescent="0.25">
@@ -15779,13 +15773,13 @@
         <v>3</v>
       </c>
       <c r="D552" s="1" t="s">
-        <v>1090</v>
+        <v>1088</v>
       </c>
       <c r="E552" s="1" t="s">
-        <v>38</v>
+        <v>90</v>
       </c>
       <c r="F552" s="1" t="s">
-        <v>64</v>
+        <v>5</v>
       </c>
     </row>
     <row r="553" spans="1:6" x14ac:dyDescent="0.25">
@@ -15799,10 +15793,10 @@
         <v>3</v>
       </c>
       <c r="D553" s="1" t="s">
-        <v>1090</v>
+        <v>1088</v>
       </c>
       <c r="E553" s="1" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="F553" s="1" t="s">
         <v>5</v>
@@ -15819,10 +15813,10 @@
         <v>3</v>
       </c>
       <c r="D554" s="1" t="s">
-        <v>1090</v>
+        <v>1088</v>
       </c>
       <c r="E554" s="1" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="F554" s="1" t="s">
         <v>5</v>
@@ -15839,10 +15833,10 @@
         <v>3</v>
       </c>
       <c r="D555" s="1" t="s">
-        <v>1090</v>
+        <v>1161</v>
       </c>
       <c r="E555" s="1" t="s">
-        <v>96</v>
+        <v>4</v>
       </c>
       <c r="F555" s="1" t="s">
         <v>5</v>
@@ -15850,22 +15844,22 @@
     </row>
     <row r="556" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A556" s="1" t="s">
+        <v>1162</v>
+      </c>
+      <c r="B556" s="1" t="s">
+        <v>1163</v>
+      </c>
+      <c r="C556" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D556" s="1" t="s">
         <v>1161</v>
       </c>
-      <c r="B556" s="1" t="s">
-        <v>1162</v>
-      </c>
-      <c r="C556" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D556" s="1" t="s">
-        <v>1163</v>
-      </c>
       <c r="E556" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F556" s="1" t="s">
-        <v>5</v>
+        <v>64</v>
       </c>
     </row>
     <row r="557" spans="1:6" x14ac:dyDescent="0.25">
@@ -15879,13 +15873,13 @@
         <v>3</v>
       </c>
       <c r="D557" s="1" t="s">
-        <v>1163</v>
+        <v>1161</v>
       </c>
       <c r="E557" s="1" t="s">
-        <v>8</v>
+        <v>45</v>
       </c>
       <c r="F557" s="1" t="s">
-        <v>64</v>
+        <v>5</v>
       </c>
     </row>
     <row r="558" spans="1:6" x14ac:dyDescent="0.25">
@@ -15899,10 +15893,10 @@
         <v>3</v>
       </c>
       <c r="D558" s="1" t="s">
-        <v>1163</v>
+        <v>1161</v>
       </c>
       <c r="E558" s="1" t="s">
-        <v>45</v>
+        <v>12</v>
       </c>
       <c r="F558" s="1" t="s">
         <v>5</v>
@@ -15919,10 +15913,10 @@
         <v>3</v>
       </c>
       <c r="D559" s="1" t="s">
-        <v>1163</v>
+        <v>1161</v>
       </c>
       <c r="E559" s="1" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="F559" s="1" t="s">
         <v>5</v>
@@ -15939,13 +15933,13 @@
         <v>3</v>
       </c>
       <c r="D560" s="1" t="s">
-        <v>1163</v>
+        <v>1161</v>
       </c>
       <c r="E560" s="1" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="F560" s="1" t="s">
-        <v>5</v>
+        <v>13</v>
       </c>
     </row>
     <row r="561" spans="1:6" x14ac:dyDescent="0.25">
@@ -15959,10 +15953,10 @@
         <v>3</v>
       </c>
       <c r="D561" s="1" t="s">
-        <v>1163</v>
+        <v>1161</v>
       </c>
       <c r="E561" s="1" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="F561" s="1" t="s">
         <v>13</v>
@@ -15979,13 +15973,13 @@
         <v>3</v>
       </c>
       <c r="D562" s="1" t="s">
-        <v>1163</v>
+        <v>1161</v>
       </c>
       <c r="E562" s="1" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="F562" s="1" t="s">
-        <v>13</v>
+        <v>5</v>
       </c>
     </row>
     <row r="563" spans="1:6" x14ac:dyDescent="0.25">
@@ -15999,13 +15993,13 @@
         <v>3</v>
       </c>
       <c r="D563" s="1" t="s">
-        <v>1163</v>
+        <v>1161</v>
       </c>
       <c r="E563" s="1" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="F563" s="1" t="s">
-        <v>5</v>
+        <v>64</v>
       </c>
     </row>
     <row r="564" spans="1:6" x14ac:dyDescent="0.25">
@@ -16019,10 +16013,10 @@
         <v>3</v>
       </c>
       <c r="D564" s="1" t="s">
-        <v>1163</v>
+        <v>1161</v>
       </c>
       <c r="E564" s="1" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="F564" s="1" t="s">
         <v>64</v>
@@ -16039,13 +16033,13 @@
         <v>3</v>
       </c>
       <c r="D565" s="1" t="s">
-        <v>1163</v>
+        <v>1161</v>
       </c>
       <c r="E565" s="1" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="F565" s="1" t="s">
-        <v>64</v>
+        <v>5</v>
       </c>
     </row>
     <row r="566" spans="1:6" x14ac:dyDescent="0.25">
@@ -16059,10 +16053,10 @@
         <v>3</v>
       </c>
       <c r="D566" s="1" t="s">
-        <v>1163</v>
+        <v>1161</v>
       </c>
       <c r="E566" s="1" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="F566" s="1" t="s">
         <v>5</v>
@@ -16079,10 +16073,10 @@
         <v>3</v>
       </c>
       <c r="D567" s="1" t="s">
-        <v>1163</v>
+        <v>1161</v>
       </c>
       <c r="E567" s="1" t="s">
-        <v>38</v>
+        <v>90</v>
       </c>
       <c r="F567" s="1" t="s">
         <v>5</v>
@@ -16099,13 +16093,13 @@
         <v>3</v>
       </c>
       <c r="D568" s="1" t="s">
-        <v>1163</v>
+        <v>1161</v>
       </c>
       <c r="E568" s="1" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="F568" s="1" t="s">
-        <v>5</v>
+        <v>64</v>
       </c>
     </row>
     <row r="569" spans="1:6" x14ac:dyDescent="0.25">
@@ -16119,10 +16113,10 @@
         <v>3</v>
       </c>
       <c r="D569" s="1" t="s">
-        <v>1163</v>
+        <v>1190</v>
       </c>
       <c r="E569" s="1" t="s">
-        <v>93</v>
+        <v>4</v>
       </c>
       <c r="F569" s="1" t="s">
         <v>64</v>
@@ -16130,19 +16124,19 @@
     </row>
     <row r="570" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A570" s="1" t="s">
+        <v>1191</v>
+      </c>
+      <c r="B570" s="1" t="s">
+        <v>1192</v>
+      </c>
+      <c r="C570" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D570" s="1" t="s">
         <v>1190</v>
       </c>
-      <c r="B570" s="1" t="s">
-        <v>1191</v>
-      </c>
-      <c r="C570" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D570" s="1" t="s">
-        <v>1192</v>
-      </c>
       <c r="E570" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F570" s="1" t="s">
         <v>64</v>
@@ -16159,13 +16153,13 @@
         <v>3</v>
       </c>
       <c r="D571" s="1" t="s">
-        <v>1192</v>
+        <v>1190</v>
       </c>
       <c r="E571" s="1" t="s">
-        <v>8</v>
+        <v>45</v>
       </c>
       <c r="F571" s="1" t="s">
-        <v>64</v>
+        <v>5</v>
       </c>
     </row>
     <row r="572" spans="1:6" x14ac:dyDescent="0.25">
@@ -16179,13 +16173,13 @@
         <v>3</v>
       </c>
       <c r="D572" s="1" t="s">
-        <v>1192</v>
+        <v>1190</v>
       </c>
       <c r="E572" s="1" t="s">
-        <v>45</v>
+        <v>12</v>
       </c>
       <c r="F572" s="1" t="s">
-        <v>5</v>
+        <v>64</v>
       </c>
     </row>
     <row r="573" spans="1:6" x14ac:dyDescent="0.25">
@@ -16199,10 +16193,10 @@
         <v>3</v>
       </c>
       <c r="D573" s="1" t="s">
-        <v>1192</v>
+        <v>1190</v>
       </c>
       <c r="E573" s="1" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="F573" s="1" t="s">
         <v>64</v>
@@ -16219,10 +16213,10 @@
         <v>3</v>
       </c>
       <c r="D574" s="1" t="s">
-        <v>1192</v>
+        <v>1190</v>
       </c>
       <c r="E574" s="1" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="F574" s="1" t="s">
         <v>64</v>
@@ -16239,13 +16233,13 @@
         <v>3</v>
       </c>
       <c r="D575" s="1" t="s">
-        <v>1192</v>
+        <v>1190</v>
       </c>
       <c r="E575" s="1" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="F575" s="1" t="s">
-        <v>64</v>
+        <v>5</v>
       </c>
     </row>
     <row r="576" spans="1:6" x14ac:dyDescent="0.25">
@@ -16259,10 +16253,10 @@
         <v>3</v>
       </c>
       <c r="D576" s="1" t="s">
-        <v>1192</v>
+        <v>1190</v>
       </c>
       <c r="E576" s="1" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="F576" s="1" t="s">
         <v>5</v>
@@ -16279,10 +16273,10 @@
         <v>3</v>
       </c>
       <c r="D577" s="1" t="s">
-        <v>1192</v>
+        <v>1190</v>
       </c>
       <c r="E577" s="1" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="F577" s="1" t="s">
         <v>5</v>
@@ -16299,10 +16293,10 @@
         <v>3</v>
       </c>
       <c r="D578" s="1" t="s">
-        <v>1192</v>
+        <v>1190</v>
       </c>
       <c r="E578" s="1" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="F578" s="1" t="s">
         <v>5</v>
@@ -16319,10 +16313,10 @@
         <v>3</v>
       </c>
       <c r="D579" s="1" t="s">
-        <v>1192</v>
+        <v>1190</v>
       </c>
       <c r="E579" s="1" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="F579" s="1" t="s">
         <v>5</v>
@@ -16339,10 +16333,10 @@
         <v>3</v>
       </c>
       <c r="D580" s="1" t="s">
-        <v>1192</v>
+        <v>1190</v>
       </c>
       <c r="E580" s="1" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="F580" s="1" t="s">
         <v>5</v>
@@ -16359,10 +16353,10 @@
         <v>3</v>
       </c>
       <c r="D581" s="1" t="s">
-        <v>1192</v>
+        <v>1190</v>
       </c>
       <c r="E581" s="1" t="s">
-        <v>38</v>
+        <v>90</v>
       </c>
       <c r="F581" s="1" t="s">
         <v>5</v>
@@ -16379,10 +16373,10 @@
         <v>3</v>
       </c>
       <c r="D582" s="1" t="s">
-        <v>1192</v>
+        <v>1190</v>
       </c>
       <c r="E582" s="1" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="F582" s="1" t="s">
         <v>5</v>
@@ -16399,10 +16393,10 @@
         <v>3</v>
       </c>
       <c r="D583" s="1" t="s">
-        <v>1192</v>
+        <v>1219</v>
       </c>
       <c r="E583" s="1" t="s">
-        <v>93</v>
+        <v>4</v>
       </c>
       <c r="F583" s="1" t="s">
         <v>5</v>
@@ -16410,22 +16404,22 @@
     </row>
     <row r="584" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A584" s="1" t="s">
+        <v>1220</v>
+      </c>
+      <c r="B584" s="1" t="s">
+        <v>1221</v>
+      </c>
+      <c r="C584" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D584" s="1" t="s">
         <v>1219</v>
       </c>
-      <c r="B584" s="1" t="s">
-        <v>1220</v>
-      </c>
-      <c r="C584" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D584" s="1" t="s">
-        <v>1221</v>
-      </c>
       <c r="E584" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F584" s="1" t="s">
-        <v>5</v>
+        <v>64</v>
       </c>
     </row>
     <row r="585" spans="1:6" x14ac:dyDescent="0.25">
@@ -16439,13 +16433,13 @@
         <v>3</v>
       </c>
       <c r="D585" s="1" t="s">
-        <v>1221</v>
+        <v>1219</v>
       </c>
       <c r="E585" s="1" t="s">
-        <v>8</v>
+        <v>45</v>
       </c>
       <c r="F585" s="1" t="s">
-        <v>64</v>
+        <v>5</v>
       </c>
     </row>
     <row r="586" spans="1:6" x14ac:dyDescent="0.25">
@@ -16459,10 +16453,10 @@
         <v>3</v>
       </c>
       <c r="D586" s="1" t="s">
-        <v>1221</v>
+        <v>1219</v>
       </c>
       <c r="E586" s="1" t="s">
-        <v>45</v>
+        <v>12</v>
       </c>
       <c r="F586" s="1" t="s">
         <v>5</v>
@@ -16479,33 +16473,33 @@
         <v>3</v>
       </c>
       <c r="D587" s="1" t="s">
-        <v>1221</v>
+        <v>1219</v>
       </c>
       <c r="E587" s="1" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="F587" s="1" t="s">
-        <v>5</v>
+        <v>1228</v>
       </c>
     </row>
     <row r="588" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A588" s="1" t="s">
+        <v>1229</v>
+      </c>
+      <c r="B588" s="1" t="s">
+        <v>1230</v>
+      </c>
+      <c r="C588" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D588" s="1" t="s">
+        <v>1219</v>
+      </c>
+      <c r="E588" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="F588" s="1" t="s">
         <v>1228</v>
-      </c>
-      <c r="B588" s="1" t="s">
-        <v>1229</v>
-      </c>
-      <c r="C588" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D588" s="1" t="s">
-        <v>1221</v>
-      </c>
-      <c r="E588" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="F588" s="1" t="s">
-        <v>1230</v>
       </c>
     </row>
     <row r="589" spans="1:6" x14ac:dyDescent="0.25">
@@ -16519,13 +16513,13 @@
         <v>3</v>
       </c>
       <c r="D589" s="1" t="s">
-        <v>1221</v>
+        <v>1219</v>
       </c>
       <c r="E589" s="1" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="F589" s="1" t="s">
-        <v>1230</v>
+        <v>5</v>
       </c>
     </row>
     <row r="590" spans="1:6" x14ac:dyDescent="0.25">
@@ -16539,10 +16533,10 @@
         <v>3</v>
       </c>
       <c r="D590" s="1" t="s">
-        <v>1221</v>
+        <v>1219</v>
       </c>
       <c r="E590" s="1" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="F590" s="1" t="s">
         <v>5</v>
@@ -16559,10 +16553,10 @@
         <v>3</v>
       </c>
       <c r="D591" s="1" t="s">
-        <v>1221</v>
+        <v>1219</v>
       </c>
       <c r="E591" s="1" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="F591" s="1" t="s">
         <v>5</v>
@@ -16579,10 +16573,10 @@
         <v>3</v>
       </c>
       <c r="D592" s="1" t="s">
-        <v>1221</v>
+        <v>1219</v>
       </c>
       <c r="E592" s="1" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="F592" s="1" t="s">
         <v>5</v>
@@ -16599,13 +16593,13 @@
         <v>3</v>
       </c>
       <c r="D593" s="1" t="s">
-        <v>1221</v>
+        <v>1219</v>
       </c>
       <c r="E593" s="1" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="F593" s="1" t="s">
-        <v>5</v>
+        <v>29</v>
       </c>
     </row>
     <row r="594" spans="1:6" x14ac:dyDescent="0.25">
@@ -16619,13 +16613,13 @@
         <v>3</v>
       </c>
       <c r="D594" s="1" t="s">
-        <v>1221</v>
+        <v>1219</v>
       </c>
       <c r="E594" s="1" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="F594" s="1" t="s">
-        <v>29</v>
+        <v>5</v>
       </c>
     </row>
     <row r="595" spans="1:6" x14ac:dyDescent="0.25">
@@ -16639,10 +16633,10 @@
         <v>3</v>
       </c>
       <c r="D595" s="1" t="s">
-        <v>1221</v>
+        <v>1219</v>
       </c>
       <c r="E595" s="1" t="s">
-        <v>38</v>
+        <v>90</v>
       </c>
       <c r="F595" s="1" t="s">
         <v>5</v>
@@ -16659,10 +16653,10 @@
         <v>3</v>
       </c>
       <c r="D596" s="1" t="s">
-        <v>1221</v>
+        <v>1219</v>
       </c>
       <c r="E596" s="1" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="F596" s="1" t="s">
         <v>5</v>
@@ -16679,10 +16673,10 @@
         <v>3</v>
       </c>
       <c r="D597" s="1" t="s">
-        <v>1221</v>
+        <v>1219</v>
       </c>
       <c r="E597" s="1" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="F597" s="1" t="s">
         <v>5</v>
@@ -16699,10 +16693,10 @@
         <v>3</v>
       </c>
       <c r="D598" s="1" t="s">
-        <v>1221</v>
+        <v>1219</v>
       </c>
       <c r="E598" s="1" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="F598" s="1" t="s">
         <v>5</v>
@@ -16719,30 +16713,30 @@
         <v>3</v>
       </c>
       <c r="D599" s="1" t="s">
-        <v>1221</v>
+        <v>1253</v>
       </c>
       <c r="E599" s="1" t="s">
-        <v>99</v>
+        <v>4</v>
       </c>
       <c r="F599" s="1" t="s">
-        <v>5</v>
+        <v>29</v>
       </c>
     </row>
     <row r="600" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A600" s="1" t="s">
+        <v>1254</v>
+      </c>
+      <c r="B600" s="1" t="s">
+        <v>1255</v>
+      </c>
+      <c r="C600" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D600" s="1" t="s">
         <v>1253</v>
       </c>
-      <c r="B600" s="1" t="s">
-        <v>1254</v>
-      </c>
-      <c r="C600" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D600" s="1" t="s">
-        <v>1255</v>
-      </c>
       <c r="E600" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F600" s="1" t="s">
         <v>29</v>
@@ -16759,10 +16753,10 @@
         <v>3</v>
       </c>
       <c r="D601" s="1" t="s">
-        <v>1255</v>
+        <v>1253</v>
       </c>
       <c r="E601" s="1" t="s">
-        <v>8</v>
+        <v>45</v>
       </c>
       <c r="F601" s="1" t="s">
         <v>29</v>
@@ -16779,13 +16773,13 @@
         <v>3</v>
       </c>
       <c r="D602" s="1" t="s">
-        <v>1255</v>
+        <v>1253</v>
       </c>
       <c r="E602" s="1" t="s">
-        <v>45</v>
+        <v>12</v>
       </c>
       <c r="F602" s="1" t="s">
-        <v>29</v>
+        <v>120</v>
       </c>
     </row>
     <row r="603" spans="1:6" x14ac:dyDescent="0.25">
@@ -16799,13 +16793,13 @@
         <v>3</v>
       </c>
       <c r="D603" s="1" t="s">
-        <v>1255</v>
+        <v>1253</v>
       </c>
       <c r="E603" s="1" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="F603" s="1" t="s">
-        <v>120</v>
+        <v>5</v>
       </c>
     </row>
     <row r="604" spans="1:6" x14ac:dyDescent="0.25">
@@ -16819,10 +16813,10 @@
         <v>3</v>
       </c>
       <c r="D604" s="1" t="s">
-        <v>1255</v>
+        <v>1253</v>
       </c>
       <c r="E604" s="1" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="F604" s="1" t="s">
         <v>5</v>
@@ -16839,10 +16833,10 @@
         <v>3</v>
       </c>
       <c r="D605" s="1" t="s">
-        <v>1255</v>
+        <v>1253</v>
       </c>
       <c r="E605" s="1" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="F605" s="1" t="s">
         <v>5</v>
@@ -16859,10 +16853,10 @@
         <v>3</v>
       </c>
       <c r="D606" s="1" t="s">
-        <v>1255</v>
+        <v>1253</v>
       </c>
       <c r="E606" s="1" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="F606" s="1" t="s">
         <v>5</v>
@@ -16879,10 +16873,10 @@
         <v>3</v>
       </c>
       <c r="D607" s="1" t="s">
-        <v>1255</v>
+        <v>1253</v>
       </c>
       <c r="E607" s="1" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="F607" s="1" t="s">
         <v>5</v>
@@ -16899,10 +16893,10 @@
         <v>3</v>
       </c>
       <c r="D608" s="1" t="s">
-        <v>1255</v>
+        <v>1253</v>
       </c>
       <c r="E608" s="1" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="F608" s="1" t="s">
         <v>5</v>
@@ -16919,10 +16913,10 @@
         <v>3</v>
       </c>
       <c r="D609" s="1" t="s">
-        <v>1255</v>
+        <v>1253</v>
       </c>
       <c r="E609" s="1" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="F609" s="1" t="s">
         <v>5</v>
@@ -16939,10 +16933,10 @@
         <v>3</v>
       </c>
       <c r="D610" s="1" t="s">
-        <v>1255</v>
+        <v>1253</v>
       </c>
       <c r="E610" s="1" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="F610" s="1" t="s">
         <v>5</v>
@@ -16959,10 +16953,10 @@
         <v>3</v>
       </c>
       <c r="D611" s="1" t="s">
-        <v>1255</v>
+        <v>1253</v>
       </c>
       <c r="E611" s="1" t="s">
-        <v>38</v>
+        <v>90</v>
       </c>
       <c r="F611" s="1" t="s">
         <v>5</v>
@@ -16979,10 +16973,10 @@
         <v>3</v>
       </c>
       <c r="D612" s="1" t="s">
-        <v>1255</v>
+        <v>1253</v>
       </c>
       <c r="E612" s="1" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="F612" s="1" t="s">
         <v>5</v>
@@ -16999,13 +16993,13 @@
         <v>3</v>
       </c>
       <c r="D613" s="1" t="s">
-        <v>1255</v>
+        <v>1253</v>
       </c>
       <c r="E613" s="1" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="F613" s="1" t="s">
-        <v>5</v>
+        <v>29</v>
       </c>
     </row>
     <row r="614" spans="1:6" x14ac:dyDescent="0.25">
@@ -17019,13 +17013,13 @@
         <v>3</v>
       </c>
       <c r="D614" s="1" t="s">
-        <v>1255</v>
+        <v>1253</v>
       </c>
       <c r="E614" s="1" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="F614" s="1" t="s">
-        <v>29</v>
+        <v>5</v>
       </c>
     </row>
     <row r="615" spans="1:6" x14ac:dyDescent="0.25">
@@ -17039,10 +17033,10 @@
         <v>3</v>
       </c>
       <c r="D615" s="1" t="s">
-        <v>1255</v>
+        <v>1253</v>
       </c>
       <c r="E615" s="1" t="s">
-        <v>99</v>
+        <v>136</v>
       </c>
       <c r="F615" s="1" t="s">
         <v>5</v>
@@ -17059,33 +17053,33 @@
         <v>3</v>
       </c>
       <c r="D616" s="1" t="s">
-        <v>1255</v>
+        <v>1288</v>
       </c>
       <c r="E616" s="1" t="s">
-        <v>136</v>
+        <v>4</v>
       </c>
       <c r="F616" s="1" t="s">
-        <v>5</v>
+        <v>64</v>
       </c>
     </row>
     <row r="617" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A617" s="1" t="s">
+        <v>1289</v>
+      </c>
+      <c r="B617" s="1" t="s">
+        <v>1290</v>
+      </c>
+      <c r="C617" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D617" s="1" t="s">
         <v>1288</v>
       </c>
-      <c r="B617" s="1" t="s">
-        <v>1289</v>
-      </c>
-      <c r="C617" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D617" s="1" t="s">
-        <v>1290</v>
-      </c>
       <c r="E617" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F617" s="1" t="s">
-        <v>64</v>
+        <v>29</v>
       </c>
     </row>
     <row r="618" spans="1:6" x14ac:dyDescent="0.25">
@@ -17099,13 +17093,13 @@
         <v>3</v>
       </c>
       <c r="D618" s="1" t="s">
-        <v>1290</v>
+        <v>1288</v>
       </c>
       <c r="E618" s="1" t="s">
-        <v>8</v>
+        <v>45</v>
       </c>
       <c r="F618" s="1" t="s">
-        <v>29</v>
+        <v>5</v>
       </c>
     </row>
     <row r="619" spans="1:6" x14ac:dyDescent="0.25">
@@ -17119,10 +17113,10 @@
         <v>3</v>
       </c>
       <c r="D619" s="1" t="s">
-        <v>1290</v>
+        <v>1288</v>
       </c>
       <c r="E619" s="1" t="s">
-        <v>45</v>
+        <v>12</v>
       </c>
       <c r="F619" s="1" t="s">
         <v>5</v>
@@ -17139,10 +17133,10 @@
         <v>3</v>
       </c>
       <c r="D620" s="1" t="s">
-        <v>1290</v>
+        <v>1288</v>
       </c>
       <c r="E620" s="1" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="F620" s="1" t="s">
         <v>5</v>
@@ -17159,13 +17153,13 @@
         <v>3</v>
       </c>
       <c r="D621" s="1" t="s">
-        <v>1290</v>
+        <v>1288</v>
       </c>
       <c r="E621" s="1" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="F621" s="1" t="s">
-        <v>5</v>
+        <v>29</v>
       </c>
     </row>
     <row r="622" spans="1:6" x14ac:dyDescent="0.25">
@@ -17179,10 +17173,10 @@
         <v>3</v>
       </c>
       <c r="D622" s="1" t="s">
-        <v>1290</v>
+        <v>1288</v>
       </c>
       <c r="E622" s="1" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="F622" s="1" t="s">
         <v>29</v>
@@ -17199,13 +17193,13 @@
         <v>3</v>
       </c>
       <c r="D623" s="1" t="s">
-        <v>1290</v>
+        <v>1288</v>
       </c>
       <c r="E623" s="1" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="F623" s="1" t="s">
-        <v>29</v>
+        <v>5</v>
       </c>
     </row>
     <row r="624" spans="1:6" x14ac:dyDescent="0.25">
@@ -17219,10 +17213,10 @@
         <v>3</v>
       </c>
       <c r="D624" s="1" t="s">
-        <v>1290</v>
+        <v>1288</v>
       </c>
       <c r="E624" s="1" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="F624" s="1" t="s">
         <v>5</v>
@@ -17239,13 +17233,13 @@
         <v>3</v>
       </c>
       <c r="D625" s="1" t="s">
-        <v>1290</v>
+        <v>1288</v>
       </c>
       <c r="E625" s="1" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="F625" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="626" spans="1:6" x14ac:dyDescent="0.25">
@@ -17259,13 +17253,13 @@
         <v>3</v>
       </c>
       <c r="D626" s="1" t="s">
-        <v>1290</v>
+        <v>1288</v>
       </c>
       <c r="E626" s="1" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="F626" s="1" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
     </row>
     <row r="627" spans="1:6" x14ac:dyDescent="0.25">
@@ -17279,13 +17273,13 @@
         <v>3</v>
       </c>
       <c r="D627" s="1" t="s">
-        <v>1290</v>
+        <v>1288</v>
       </c>
       <c r="E627" s="1" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="F627" s="1" t="s">
-        <v>13</v>
+        <v>29</v>
       </c>
     </row>
     <row r="628" spans="1:6" x14ac:dyDescent="0.25">
@@ -17299,10 +17293,10 @@
         <v>3</v>
       </c>
       <c r="D628" s="1" t="s">
-        <v>1290</v>
+        <v>1288</v>
       </c>
       <c r="E628" s="1" t="s">
-        <v>38</v>
+        <v>90</v>
       </c>
       <c r="F628" s="1" t="s">
         <v>29</v>
@@ -17319,10 +17313,10 @@
         <v>3</v>
       </c>
       <c r="D629" s="1" t="s">
-        <v>1290</v>
+        <v>1288</v>
       </c>
       <c r="E629" s="1" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="F629" s="1" t="s">
         <v>29</v>
@@ -17339,10 +17333,10 @@
         <v>3</v>
       </c>
       <c r="D630" s="1" t="s">
-        <v>1290</v>
+        <v>1288</v>
       </c>
       <c r="E630" s="1" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="F630" s="1" t="s">
         <v>29</v>
@@ -17359,13 +17353,13 @@
         <v>3</v>
       </c>
       <c r="D631" s="1" t="s">
-        <v>1290</v>
+        <v>1288</v>
       </c>
       <c r="E631" s="1" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="F631" s="1" t="s">
-        <v>29</v>
+        <v>5</v>
       </c>
     </row>
     <row r="632" spans="1:6" x14ac:dyDescent="0.25">
@@ -17379,13 +17373,13 @@
         <v>3</v>
       </c>
       <c r="D632" s="1" t="s">
-        <v>1290</v>
+        <v>1288</v>
       </c>
       <c r="E632" s="1" t="s">
-        <v>99</v>
+        <v>136</v>
       </c>
       <c r="F632" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="633" spans="1:6" x14ac:dyDescent="0.25">
@@ -17399,13 +17393,13 @@
         <v>3</v>
       </c>
       <c r="D633" s="1" t="s">
-        <v>1290</v>
+        <v>1288</v>
       </c>
       <c r="E633" s="1" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="F633" s="1" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
     </row>
     <row r="634" spans="1:6" x14ac:dyDescent="0.25">
@@ -17419,33 +17413,33 @@
         <v>3</v>
       </c>
       <c r="D634" s="1" t="s">
-        <v>1290</v>
+        <v>1325</v>
       </c>
       <c r="E634" s="1" t="s">
-        <v>139</v>
+        <v>4</v>
       </c>
       <c r="F634" s="1" t="s">
-        <v>13</v>
+        <v>29</v>
       </c>
     </row>
     <row r="635" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A635" s="1" t="s">
+        <v>1326</v>
+      </c>
+      <c r="B635" s="1" t="s">
+        <v>1327</v>
+      </c>
+      <c r="C635" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D635" s="1" t="s">
         <v>1325</v>
       </c>
-      <c r="B635" s="1" t="s">
-        <v>1326</v>
-      </c>
-      <c r="C635" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D635" s="1" t="s">
-        <v>1327</v>
-      </c>
       <c r="E635" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F635" s="1" t="s">
-        <v>29</v>
+        <v>5</v>
       </c>
     </row>
     <row r="636" spans="1:6" x14ac:dyDescent="0.25">
@@ -17459,10 +17453,10 @@
         <v>3</v>
       </c>
       <c r="D636" s="1" t="s">
-        <v>1327</v>
+        <v>1325</v>
       </c>
       <c r="E636" s="1" t="s">
-        <v>8</v>
+        <v>45</v>
       </c>
       <c r="F636" s="1" t="s">
         <v>5</v>
@@ -17473,16 +17467,16 @@
         <v>1330</v>
       </c>
       <c r="B637" s="1" t="s">
-        <v>1331</v>
+        <v>1329</v>
       </c>
       <c r="C637" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D637" s="1" t="s">
-        <v>1327</v>
+        <v>1325</v>
       </c>
       <c r="E637" s="1" t="s">
-        <v>45</v>
+        <v>12</v>
       </c>
       <c r="F637" s="1" t="s">
         <v>5</v>
@@ -17490,22 +17484,22 @@
     </row>
     <row r="638" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A638" s="1" t="s">
+        <v>1331</v>
+      </c>
+      <c r="B638" s="1" t="s">
         <v>1332</v>
       </c>
-      <c r="B638" s="1" t="s">
-        <v>1331</v>
-      </c>
       <c r="C638" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D638" s="1" t="s">
-        <v>1327</v>
+        <v>1325</v>
       </c>
       <c r="E638" s="1" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="F638" s="1" t="s">
-        <v>5</v>
+        <v>64</v>
       </c>
     </row>
     <row r="639" spans="1:6" x14ac:dyDescent="0.25">
@@ -17519,10 +17513,10 @@
         <v>3</v>
       </c>
       <c r="D639" s="1" t="s">
-        <v>1327</v>
+        <v>1325</v>
       </c>
       <c r="E639" s="1" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="F639" s="1" t="s">
         <v>64</v>
@@ -17539,13 +17533,13 @@
         <v>3</v>
       </c>
       <c r="D640" s="1" t="s">
-        <v>1327</v>
+        <v>1325</v>
       </c>
       <c r="E640" s="1" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="F640" s="1" t="s">
-        <v>64</v>
+        <v>13</v>
       </c>
     </row>
     <row r="641" spans="1:6" x14ac:dyDescent="0.25">
@@ -17559,10 +17553,10 @@
         <v>3</v>
       </c>
       <c r="D641" s="1" t="s">
-        <v>1327</v>
+        <v>1325</v>
       </c>
       <c r="E641" s="1" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="F641" s="1" t="s">
         <v>13</v>
@@ -17579,10 +17573,10 @@
         <v>3</v>
       </c>
       <c r="D642" s="1" t="s">
-        <v>1327</v>
+        <v>1325</v>
       </c>
       <c r="E642" s="1" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="F642" s="1" t="s">
         <v>13</v>
@@ -17599,10 +17593,10 @@
         <v>3</v>
       </c>
       <c r="D643" s="1" t="s">
-        <v>1327</v>
+        <v>1325</v>
       </c>
       <c r="E643" s="1" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="F643" s="1" t="s">
         <v>13</v>
@@ -17619,10 +17613,10 @@
         <v>3</v>
       </c>
       <c r="D644" s="1" t="s">
-        <v>1327</v>
+        <v>1325</v>
       </c>
       <c r="E644" s="1" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="F644" s="1" t="s">
         <v>13</v>
@@ -17639,10 +17633,10 @@
         <v>3</v>
       </c>
       <c r="D645" s="1" t="s">
-        <v>1327</v>
+        <v>1325</v>
       </c>
       <c r="E645" s="1" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="F645" s="1" t="s">
         <v>13</v>
@@ -17659,13 +17653,13 @@
         <v>3</v>
       </c>
       <c r="D646" s="1" t="s">
-        <v>1327</v>
+        <v>1325</v>
       </c>
       <c r="E646" s="1" t="s">
-        <v>38</v>
+        <v>90</v>
       </c>
       <c r="F646" s="1" t="s">
-        <v>13</v>
+        <v>120</v>
       </c>
     </row>
     <row r="647" spans="1:6" x14ac:dyDescent="0.25">
@@ -17679,10 +17673,10 @@
         <v>3</v>
       </c>
       <c r="D647" s="1" t="s">
-        <v>1327</v>
+        <v>1325</v>
       </c>
       <c r="E647" s="1" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="F647" s="1" t="s">
         <v>120</v>
@@ -17699,13 +17693,13 @@
         <v>3</v>
       </c>
       <c r="D648" s="1" t="s">
-        <v>1327</v>
+        <v>1325</v>
       </c>
       <c r="E648" s="1" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="F648" s="1" t="s">
-        <v>120</v>
+        <v>9</v>
       </c>
     </row>
     <row r="649" spans="1:6" x14ac:dyDescent="0.25">
@@ -17719,10 +17713,10 @@
         <v>3</v>
       </c>
       <c r="D649" s="1" t="s">
-        <v>1327</v>
+        <v>1325</v>
       </c>
       <c r="E649" s="1" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="F649" s="1" t="s">
         <v>9</v>
@@ -17739,10 +17733,10 @@
         <v>3</v>
       </c>
       <c r="D650" s="1" t="s">
-        <v>1327</v>
+        <v>1325</v>
       </c>
       <c r="E650" s="1" t="s">
-        <v>99</v>
+        <v>136</v>
       </c>
       <c r="F650" s="1" t="s">
         <v>9</v>
@@ -17759,10 +17753,10 @@
         <v>3</v>
       </c>
       <c r="D651" s="1" t="s">
-        <v>1327</v>
+        <v>1325</v>
       </c>
       <c r="E651" s="1" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="F651" s="1" t="s">
         <v>9</v>
@@ -17779,10 +17773,10 @@
         <v>3</v>
       </c>
       <c r="D652" s="1" t="s">
-        <v>1327</v>
+        <v>1361</v>
       </c>
       <c r="E652" s="1" t="s">
-        <v>139</v>
+        <v>4</v>
       </c>
       <c r="F652" s="1" t="s">
         <v>9</v>
@@ -17790,19 +17784,19 @@
     </row>
     <row r="653" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A653" s="1" t="s">
+        <v>1362</v>
+      </c>
+      <c r="B653" s="1" t="s">
+        <v>1363</v>
+      </c>
+      <c r="C653" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D653" s="1" t="s">
         <v>1361</v>
       </c>
-      <c r="B653" s="1" t="s">
-        <v>1362</v>
-      </c>
-      <c r="C653" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D653" s="1" t="s">
-        <v>1363</v>
-      </c>
       <c r="E653" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F653" s="1" t="s">
         <v>9</v>
@@ -17819,10 +17813,10 @@
         <v>3</v>
       </c>
       <c r="D654" s="1" t="s">
-        <v>1363</v>
+        <v>1361</v>
       </c>
       <c r="E654" s="1" t="s">
-        <v>8</v>
+        <v>45</v>
       </c>
       <c r="F654" s="1" t="s">
         <v>9</v>
@@ -17839,10 +17833,10 @@
         <v>3</v>
       </c>
       <c r="D655" s="1" t="s">
-        <v>1363</v>
+        <v>1361</v>
       </c>
       <c r="E655" s="1" t="s">
-        <v>45</v>
+        <v>12</v>
       </c>
       <c r="F655" s="1" t="s">
         <v>9</v>
@@ -17859,13 +17853,13 @@
         <v>3</v>
       </c>
       <c r="D656" s="1" t="s">
-        <v>1363</v>
+        <v>1361</v>
       </c>
       <c r="E656" s="1" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="F656" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="657" spans="1:6" x14ac:dyDescent="0.25">
@@ -17879,13 +17873,13 @@
         <v>3</v>
       </c>
       <c r="D657" s="1" t="s">
-        <v>1363</v>
+        <v>1361</v>
       </c>
       <c r="E657" s="1" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="F657" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="658" spans="1:6" x14ac:dyDescent="0.25">
@@ -17899,13 +17893,13 @@
         <v>3</v>
       </c>
       <c r="D658" s="1" t="s">
-        <v>1363</v>
+        <v>1361</v>
       </c>
       <c r="E658" s="1" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="F658" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="659" spans="1:6" x14ac:dyDescent="0.25">
@@ -17919,13 +17913,13 @@
         <v>3</v>
       </c>
       <c r="D659" s="1" t="s">
-        <v>1363</v>
+        <v>1361</v>
       </c>
       <c r="E659" s="1" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="F659" s="1" t="s">
-        <v>5</v>
+        <v>13</v>
       </c>
     </row>
     <row r="660" spans="1:6" x14ac:dyDescent="0.25">
@@ -17939,13 +17933,13 @@
         <v>3</v>
       </c>
       <c r="D660" s="1" t="s">
-        <v>1363</v>
+        <v>1361</v>
       </c>
       <c r="E660" s="1" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="F660" s="1" t="s">
-        <v>13</v>
+        <v>5</v>
       </c>
     </row>
     <row r="661" spans="1:6" x14ac:dyDescent="0.25">
@@ -17959,13 +17953,13 @@
         <v>3</v>
       </c>
       <c r="D661" s="1" t="s">
-        <v>1363</v>
+        <v>1361</v>
       </c>
       <c r="E661" s="1" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="F661" s="1" t="s">
-        <v>5</v>
+        <v>13</v>
       </c>
     </row>
     <row r="662" spans="1:6" x14ac:dyDescent="0.25">
@@ -17979,10 +17973,10 @@
         <v>3</v>
       </c>
       <c r="D662" s="1" t="s">
-        <v>1363</v>
+        <v>1361</v>
       </c>
       <c r="E662" s="1" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="F662" s="1" t="s">
         <v>13</v>
@@ -17999,10 +17993,10 @@
         <v>3</v>
       </c>
       <c r="D663" s="1" t="s">
-        <v>1363</v>
+        <v>1361</v>
       </c>
       <c r="E663" s="1" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="F663" s="1" t="s">
         <v>13</v>
@@ -18019,10 +18013,10 @@
         <v>3</v>
       </c>
       <c r="D664" s="1" t="s">
-        <v>1363</v>
+        <v>1361</v>
       </c>
       <c r="E664" s="1" t="s">
-        <v>38</v>
+        <v>90</v>
       </c>
       <c r="F664" s="1" t="s">
         <v>13</v>
@@ -18039,33 +18033,33 @@
         <v>3</v>
       </c>
       <c r="D665" s="1" t="s">
-        <v>1363</v>
+        <v>1388</v>
       </c>
       <c r="E665" s="1" t="s">
-        <v>90</v>
+        <v>4</v>
       </c>
       <c r="F665" s="1" t="s">
-        <v>13</v>
+        <v>1389</v>
       </c>
     </row>
     <row r="666" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A666" s="1" t="s">
+        <v>1390</v>
+      </c>
+      <c r="B666" s="1" t="s">
+        <v>1391</v>
+      </c>
+      <c r="C666" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D666" s="1" t="s">
         <v>1388</v>
       </c>
-      <c r="B666" s="1" t="s">
+      <c r="E666" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="F666" s="1" t="s">
         <v>1389</v>
-      </c>
-      <c r="C666" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D666" s="1" t="s">
-        <v>1390</v>
-      </c>
-      <c r="E666" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F666" s="1" t="s">
-        <v>1391</v>
       </c>
     </row>
     <row r="667" spans="1:6" x14ac:dyDescent="0.25">
@@ -18079,13 +18073,13 @@
         <v>3</v>
       </c>
       <c r="D667" s="1" t="s">
-        <v>1390</v>
+        <v>1388</v>
       </c>
       <c r="E667" s="1" t="s">
-        <v>8</v>
+        <v>45</v>
       </c>
       <c r="F667" s="1" t="s">
-        <v>1391</v>
+        <v>1389</v>
       </c>
     </row>
     <row r="668" spans="1:6" x14ac:dyDescent="0.25">
@@ -18099,13 +18093,13 @@
         <v>3</v>
       </c>
       <c r="D668" s="1" t="s">
-        <v>1390</v>
+        <v>1388</v>
       </c>
       <c r="E668" s="1" t="s">
-        <v>45</v>
+        <v>12</v>
       </c>
       <c r="F668" s="1" t="s">
-        <v>1391</v>
+        <v>1389</v>
       </c>
     </row>
     <row r="669" spans="1:6" x14ac:dyDescent="0.25">
@@ -18119,13 +18113,13 @@
         <v>3</v>
       </c>
       <c r="D669" s="1" t="s">
-        <v>1390</v>
+        <v>1388</v>
       </c>
       <c r="E669" s="1" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="F669" s="1" t="s">
-        <v>1391</v>
+        <v>1389</v>
       </c>
     </row>
     <row r="670" spans="1:6" x14ac:dyDescent="0.25">
@@ -18139,13 +18133,13 @@
         <v>3</v>
       </c>
       <c r="D670" s="1" t="s">
-        <v>1390</v>
+        <v>1388</v>
       </c>
       <c r="E670" s="1" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="F670" s="1" t="s">
-        <v>1391</v>
+        <v>1389</v>
       </c>
     </row>
     <row r="671" spans="1:6" x14ac:dyDescent="0.25">
@@ -18159,13 +18153,13 @@
         <v>3</v>
       </c>
       <c r="D671" s="1" t="s">
-        <v>1390</v>
+        <v>1388</v>
       </c>
       <c r="E671" s="1" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="F671" s="1" t="s">
-        <v>1391</v>
+        <v>1389</v>
       </c>
     </row>
     <row r="672" spans="1:6" x14ac:dyDescent="0.25">
@@ -18179,13 +18173,13 @@
         <v>3</v>
       </c>
       <c r="D672" s="1" t="s">
-        <v>1390</v>
+        <v>1388</v>
       </c>
       <c r="E672" s="1" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="F672" s="1" t="s">
-        <v>1391</v>
+        <v>232</v>
       </c>
     </row>
     <row r="673" spans="1:6" x14ac:dyDescent="0.25">
@@ -18199,13 +18193,13 @@
         <v>3</v>
       </c>
       <c r="D673" s="1" t="s">
-        <v>1390</v>
+        <v>1388</v>
       </c>
       <c r="E673" s="1" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="F673" s="1" t="s">
-        <v>232</v>
+        <v>5</v>
       </c>
     </row>
     <row r="674" spans="1:6" x14ac:dyDescent="0.25">
@@ -18219,13 +18213,13 @@
         <v>3</v>
       </c>
       <c r="D674" s="1" t="s">
-        <v>1390</v>
+        <v>1388</v>
       </c>
       <c r="E674" s="1" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="F674" s="1" t="s">
-        <v>5</v>
+        <v>1389</v>
       </c>
     </row>
     <row r="675" spans="1:6" x14ac:dyDescent="0.25">
@@ -18239,13 +18233,13 @@
         <v>3</v>
       </c>
       <c r="D675" s="1" t="s">
-        <v>1390</v>
+        <v>1388</v>
       </c>
       <c r="E675" s="1" t="s">
         <v>32</v>
       </c>
       <c r="F675" s="1" t="s">
-        <v>1391</v>
+        <v>1389</v>
       </c>
     </row>
     <row r="676" spans="1:6" x14ac:dyDescent="0.25">
@@ -18259,13 +18253,13 @@
         <v>3</v>
       </c>
       <c r="D676" s="1" t="s">
-        <v>1390</v>
+        <v>1388</v>
       </c>
       <c r="E676" s="1" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="F676" s="1" t="s">
-        <v>1391</v>
+        <v>1389</v>
       </c>
     </row>
     <row r="677" spans="1:6" x14ac:dyDescent="0.25">
@@ -18279,13 +18273,13 @@
         <v>3</v>
       </c>
       <c r="D677" s="1" t="s">
-        <v>1390</v>
+        <v>1388</v>
       </c>
       <c r="E677" s="1" t="s">
         <v>35</v>
       </c>
       <c r="F677" s="1" t="s">
-        <v>1391</v>
+        <v>1389</v>
       </c>
     </row>
     <row r="678" spans="1:6" x14ac:dyDescent="0.25">
@@ -18299,13 +18293,13 @@
         <v>3</v>
       </c>
       <c r="D678" s="1" t="s">
-        <v>1390</v>
+        <v>1388</v>
       </c>
       <c r="E678" s="1" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="F678" s="1" t="s">
-        <v>1391</v>
+        <v>232</v>
       </c>
     </row>
     <row r="679" spans="1:6" x14ac:dyDescent="0.25">
@@ -18319,13 +18313,13 @@
         <v>3</v>
       </c>
       <c r="D679" s="1" t="s">
-        <v>1390</v>
+        <v>1388</v>
       </c>
       <c r="E679" s="1" t="s">
-        <v>38</v>
+        <v>90</v>
       </c>
       <c r="F679" s="1" t="s">
-        <v>232</v>
+        <v>1389</v>
       </c>
     </row>
     <row r="680" spans="1:6" x14ac:dyDescent="0.25">
@@ -18339,30 +18333,30 @@
         <v>3</v>
       </c>
       <c r="D680" s="1" t="s">
-        <v>1390</v>
+        <v>1420</v>
       </c>
       <c r="E680" s="1" t="s">
-        <v>90</v>
+        <v>4</v>
       </c>
       <c r="F680" s="1" t="s">
-        <v>1391</v>
+        <v>5</v>
       </c>
     </row>
     <row r="681" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A681" s="1" t="s">
+        <v>1421</v>
+      </c>
+      <c r="B681" s="1" t="s">
+        <v>1422</v>
+      </c>
+      <c r="C681" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D681" s="1" t="s">
         <v>1420</v>
       </c>
-      <c r="B681" s="1" t="s">
-        <v>1421</v>
-      </c>
-      <c r="C681" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D681" s="1" t="s">
-        <v>1422</v>
-      </c>
       <c r="E681" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F681" s="1" t="s">
         <v>5</v>
@@ -18379,10 +18373,10 @@
         <v>3</v>
       </c>
       <c r="D682" s="1" t="s">
-        <v>1422</v>
+        <v>1420</v>
       </c>
       <c r="E682" s="1" t="s">
-        <v>8</v>
+        <v>45</v>
       </c>
       <c r="F682" s="1" t="s">
         <v>5</v>
@@ -18399,13 +18393,13 @@
         <v>3</v>
       </c>
       <c r="D683" s="1" t="s">
-        <v>1422</v>
+        <v>1420</v>
       </c>
       <c r="E683" s="1" t="s">
-        <v>45</v>
+        <v>12</v>
       </c>
       <c r="F683" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="684" spans="1:6" x14ac:dyDescent="0.25">
@@ -18419,10 +18413,10 @@
         <v>3</v>
       </c>
       <c r="D684" s="1" t="s">
-        <v>1422</v>
+        <v>1420</v>
       </c>
       <c r="E684" s="1" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="F684" s="1" t="s">
         <v>9</v>
@@ -18439,13 +18433,13 @@
         <v>3</v>
       </c>
       <c r="D685" s="1" t="s">
-        <v>1422</v>
+        <v>1420</v>
       </c>
       <c r="E685" s="1" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="F685" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="686" spans="1:6" x14ac:dyDescent="0.25">
@@ -18459,13 +18453,13 @@
         <v>3</v>
       </c>
       <c r="D686" s="1" t="s">
-        <v>1422</v>
+        <v>1420</v>
       </c>
       <c r="E686" s="1" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="F686" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="687" spans="1:6" x14ac:dyDescent="0.25">
@@ -18479,13 +18473,13 @@
         <v>3</v>
       </c>
       <c r="D687" s="1" t="s">
-        <v>1422</v>
+        <v>1420</v>
       </c>
       <c r="E687" s="1" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="F687" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="688" spans="1:6" x14ac:dyDescent="0.25">
@@ -18499,10 +18493,10 @@
         <v>3</v>
       </c>
       <c r="D688" s="1" t="s">
-        <v>1422</v>
+        <v>1420</v>
       </c>
       <c r="E688" s="1" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="F688" s="1" t="s">
         <v>5</v>
@@ -18519,13 +18513,13 @@
         <v>3</v>
       </c>
       <c r="D689" s="1" t="s">
-        <v>1422</v>
+        <v>1420</v>
       </c>
       <c r="E689" s="1" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="F689" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="690" spans="1:6" x14ac:dyDescent="0.25">
@@ -18539,10 +18533,10 @@
         <v>3</v>
       </c>
       <c r="D690" s="1" t="s">
-        <v>1422</v>
+        <v>1420</v>
       </c>
       <c r="E690" s="1" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="F690" s="1" t="s">
         <v>9</v>
@@ -18559,32 +18553,12 @@
         <v>3</v>
       </c>
       <c r="D691" s="1" t="s">
-        <v>1422</v>
+        <v>1420</v>
       </c>
       <c r="E691" s="1" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="F691" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="692" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A692" s="1" t="s">
-        <v>1443</v>
-      </c>
-      <c r="B692" s="1" t="s">
-        <v>1444</v>
-      </c>
-      <c r="C692" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D692" s="1" t="s">
-        <v>1422</v>
-      </c>
-      <c r="E692" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="F692" s="1" t="s">
         <v>9</v>
       </c>
     </row>

--- a/PCE06D.xlsx
+++ b/PCE06D.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4164" uniqueCount="1450">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4182" uniqueCount="1457">
   <si>
     <t/>
   </si>
@@ -2647,15 +2647,21 @@
     <t>POSH DEO HJB R.GRN50</t>
   </si>
   <si>
+    <t>20098912</t>
+  </si>
+  <si>
+    <t>WRDH PB MCLR WTR 100</t>
+  </si>
+  <si>
+    <t>29</t>
+  </si>
+  <si>
     <t>20140349</t>
   </si>
   <si>
     <t>IDM RND COTTON 60'S</t>
   </si>
   <si>
-    <t>29</t>
-  </si>
-  <si>
     <t>10006957</t>
   </si>
   <si>
@@ -2692,15 +2698,24 @@
     <t>SLCTION RND KPS 80'S</t>
   </si>
   <si>
+    <t>20142123</t>
+  </si>
+  <si>
+    <t>BDL FW PAPAYA 100G</t>
+  </si>
+  <si>
+    <t>30</t>
+  </si>
+  <si>
+    <t>TG,(E-3B)</t>
+  </si>
+  <si>
     <t>20139602</t>
   </si>
   <si>
     <t>AZZURA DB FC WSH 100</t>
   </si>
   <si>
-    <t>30</t>
-  </si>
-  <si>
     <t>20138098</t>
   </si>
   <si>
@@ -2764,1603 +2779,1609 @@
     <t>GLOW&amp;LOVELY DRM.GL50</t>
   </si>
   <si>
+    <t>20093587</t>
+  </si>
+  <si>
+    <t>SENKA PRFCT WHIP 50</t>
+  </si>
+  <si>
+    <t>20135695</t>
+  </si>
+  <si>
+    <t>C&amp;C VITAMIN C FW 100</t>
+  </si>
+  <si>
+    <t>20008420</t>
+  </si>
+  <si>
+    <t>CLEAN&amp;CLEAR FAC100ML</t>
+  </si>
+  <si>
+    <t>20000765</t>
+  </si>
+  <si>
+    <t>CLEAN&amp;CLEAR FAC 50</t>
+  </si>
+  <si>
+    <t>20138028</t>
+  </si>
+  <si>
+    <t>G2G FW MILK AMINO 80</t>
+  </si>
+  <si>
+    <t>31</t>
+  </si>
+  <si>
+    <t>20139173</t>
+  </si>
+  <si>
+    <t>G2G FW P.VITA C 80G</t>
+  </si>
+  <si>
+    <t>20136004</t>
+  </si>
+  <si>
+    <t>GLAD2 CLNSR CNTELA70</t>
+  </si>
+  <si>
+    <t>20134060</t>
+  </si>
+  <si>
+    <t>GLAD2 CLNSR BLBRRY70</t>
+  </si>
+  <si>
+    <t>20140352</t>
+  </si>
+  <si>
+    <t>G2G FW DEEP PC 70ML</t>
+  </si>
+  <si>
+    <t>20141939</t>
+  </si>
+  <si>
+    <t>G2G SERUM FW NIACI70</t>
+  </si>
+  <si>
+    <t>10012397</t>
+  </si>
+  <si>
+    <t>NVEA SB FF PEARL 100</t>
+  </si>
+  <si>
+    <t>20067449</t>
+  </si>
+  <si>
+    <t>GLW&amp;LOVELY DRM.GL100</t>
+  </si>
+  <si>
+    <t>20110117</t>
+  </si>
+  <si>
+    <t>G&amp;L FC.FOAM VIT.C100</t>
+  </si>
+  <si>
+    <t>20130082</t>
+  </si>
+  <si>
+    <t>EMINA BS FACE WSH100</t>
+  </si>
+  <si>
+    <t>20134238</t>
+  </si>
+  <si>
+    <t>POISE FF OIL.CTRL100</t>
+  </si>
+  <si>
+    <t>20092317</t>
+  </si>
+  <si>
+    <t>POISE FAC.FM WHT 100</t>
+  </si>
+  <si>
+    <t>20127065</t>
+  </si>
+  <si>
+    <t>POISE FF ANT.ACNE100</t>
+  </si>
+  <si>
+    <t>20021810</t>
+  </si>
+  <si>
+    <t>ACNES CREAMY WASH100</t>
+  </si>
+  <si>
+    <t>20056357</t>
+  </si>
+  <si>
+    <t>ACNES FW CMP.WHT 100</t>
+  </si>
+  <si>
+    <t>20141979</t>
+  </si>
+  <si>
+    <t>GARNIER SKR GLOW 100</t>
+  </si>
+  <si>
+    <t>32</t>
+  </si>
+  <si>
+    <t>20141978</t>
+  </si>
+  <si>
+    <t>GARNIER VITC LWPH100</t>
+  </si>
+  <si>
+    <t>20136511</t>
+  </si>
+  <si>
+    <t>GRNR SRM CLNSR 100</t>
+  </si>
+  <si>
+    <t>20052782</t>
+  </si>
+  <si>
+    <t>GRNIER SKR GLW HY100</t>
+  </si>
+  <si>
+    <t>20025002</t>
+  </si>
+  <si>
+    <t>GRNIER BC FW VT.C100</t>
+  </si>
+  <si>
+    <t>20040194</t>
+  </si>
+  <si>
+    <t>GRNR BC FWS.VT.C100</t>
+  </si>
+  <si>
+    <t>20137610</t>
+  </si>
+  <si>
+    <t>PONDS HYDRA.MRCL 90G</t>
+  </si>
+  <si>
+    <t>20137608</t>
+  </si>
+  <si>
+    <t>PONDS BRGHT MRCL 90G</t>
+  </si>
+  <si>
+    <t>20067202</t>
+  </si>
+  <si>
+    <t>PONDS PW PR.CHR100G</t>
+  </si>
+  <si>
+    <t>20067210</t>
+  </si>
+  <si>
+    <t>PONDS PW NSRCNL 100G</t>
+  </si>
+  <si>
+    <t>20090023</t>
+  </si>
+  <si>
+    <t>WRDH BRGH MUG CLY100</t>
+  </si>
+  <si>
+    <t>20090022</t>
+  </si>
+  <si>
+    <t>WRDH BRG NOW ENZM100</t>
+  </si>
+  <si>
+    <t>20106672</t>
+  </si>
+  <si>
+    <t>WRDH LG FAC.FOAM 100</t>
+  </si>
+  <si>
+    <t>20071676</t>
+  </si>
+  <si>
+    <t>WRDH C/S CLRFY FW100</t>
+  </si>
+  <si>
+    <t>20078833</t>
+  </si>
+  <si>
+    <t>WRDAH C.WSH C-DEF100</t>
+  </si>
+  <si>
+    <t>20115358</t>
+  </si>
+  <si>
+    <t>HMLYA P.NEEM MASK100</t>
+  </si>
+  <si>
+    <t>33</t>
+  </si>
+  <si>
+    <t>20140296</t>
+  </si>
+  <si>
+    <t>D/A STCK ACNE.CR 20</t>
+  </si>
+  <si>
+    <t>20139950</t>
+  </si>
+  <si>
+    <t>HMLY TURMERIC CSM 30</t>
+  </si>
+  <si>
+    <t>20139313</t>
+  </si>
+  <si>
+    <t>HMLY PRFY N/C SM 30</t>
+  </si>
+  <si>
+    <t>20133290</t>
+  </si>
+  <si>
+    <t>GLAD2 MUGWORT ACID25</t>
+  </si>
+  <si>
+    <t>20139050</t>
+  </si>
+  <si>
+    <t>EMINA WTR UV GEL25ML</t>
+  </si>
+  <si>
+    <t>20139605</t>
+  </si>
+  <si>
+    <t>AZZURA SS SPF 50 30G</t>
+  </si>
+  <si>
+    <t>20139439</t>
+  </si>
+  <si>
+    <t>SCORA B.ME UP SS 30G</t>
+  </si>
+  <si>
+    <t>20135594</t>
+  </si>
+  <si>
+    <t>CARASUN SS UV.SUNS30</t>
+  </si>
+  <si>
+    <t>20133672</t>
+  </si>
+  <si>
+    <t>HNSUI COL.SUNS.SPF50</t>
+  </si>
+  <si>
+    <t>20139352</t>
+  </si>
+  <si>
+    <t>HNSUI SS LGHT.PRO 30</t>
+  </si>
+  <si>
+    <t>20130191</t>
+  </si>
+  <si>
+    <t>HNSUI COL.SUNSCRN 30</t>
+  </si>
+  <si>
+    <t>20134797</t>
+  </si>
+  <si>
+    <t>WRDH UV ACN/CL SUN35</t>
+  </si>
+  <si>
+    <t>20110001</t>
+  </si>
+  <si>
+    <t>WARDAH UV GRD GEL40</t>
+  </si>
+  <si>
+    <t>20131253</t>
+  </si>
+  <si>
+    <t>WARDAH UV AIRY SRM25</t>
+  </si>
+  <si>
+    <t>20138742</t>
+  </si>
+  <si>
+    <t>S/AYU T.UP SNSCRN 30</t>
+  </si>
+  <si>
+    <t>20072834</t>
+  </si>
+  <si>
+    <t>PONDS AM PLMB DAY 10</t>
+  </si>
+  <si>
+    <t>34</t>
+  </si>
+  <si>
+    <t>20140080</t>
+  </si>
+  <si>
+    <t>GRNR NCNAMIDE DTC 30</t>
+  </si>
+  <si>
+    <t>20140081</t>
+  </si>
+  <si>
+    <t>GRNR SALICYLC DTC 30</t>
+  </si>
+  <si>
+    <t>20140079</t>
+  </si>
+  <si>
+    <t>GRNIER VIT.C DTC 30</t>
+  </si>
+  <si>
+    <t>20139845</t>
+  </si>
+  <si>
+    <t>PONDS BIOME NIAR 15G</t>
+  </si>
+  <si>
+    <t>20139846</t>
+  </si>
+  <si>
+    <t>PONDS BIOME CERA 15G</t>
+  </si>
+  <si>
+    <t>20139604</t>
+  </si>
+  <si>
+    <t>AZZURA DB DAY CRM 30</t>
+  </si>
+  <si>
+    <t>20127466</t>
+  </si>
+  <si>
+    <t>IMPLRA SPF40 SS 50ML</t>
+  </si>
+  <si>
+    <t>20136433</t>
+  </si>
+  <si>
+    <t>PIGEON SUNSCREN 30ML</t>
+  </si>
+  <si>
+    <t>20134326</t>
+  </si>
+  <si>
+    <t>SCRLT ULT SUNSCRN 30</t>
+  </si>
+  <si>
+    <t>RT,(E-7.5B)</t>
+  </si>
+  <si>
+    <t>20137670</t>
+  </si>
+  <si>
+    <t>GRNR SPR UV COOL.WTR</t>
+  </si>
+  <si>
+    <t>20129129</t>
+  </si>
+  <si>
+    <t>AZARINE CALM MA SS40</t>
+  </si>
+  <si>
+    <t>20129130</t>
+  </si>
+  <si>
+    <t>AZARINE HYD SS.GEL30</t>
+  </si>
+  <si>
+    <t>20137412</t>
+  </si>
+  <si>
+    <t>SHNZUI BS SUNSCRN 30</t>
+  </si>
+  <si>
+    <t>20123451</t>
+  </si>
+  <si>
+    <t>EMINA SUN BT 30PA 20</t>
+  </si>
+  <si>
+    <t>20096136</t>
+  </si>
+  <si>
+    <t>EMINA SUN BT 30PA 50</t>
+  </si>
+  <si>
+    <t>20138347</t>
+  </si>
+  <si>
+    <t>G&amp;G SUNSSCREN 15G</t>
+  </si>
+  <si>
+    <t>20126525</t>
+  </si>
+  <si>
+    <t>G&amp;L ULTMTE UV VT.C20</t>
+  </si>
+  <si>
+    <t>20137409</t>
+  </si>
+  <si>
+    <t>SHNZUI BR.SRM MS.30G</t>
+  </si>
+  <si>
+    <t>35</t>
+  </si>
+  <si>
+    <t>20133739</t>
+  </si>
+  <si>
+    <t>T/O HYALUCERA MOIS50</t>
+  </si>
+  <si>
+    <t>20138027</t>
+  </si>
+  <si>
+    <t>WRDAH SYM MS.GEL 30G</t>
+  </si>
+  <si>
+    <t>20135184</t>
+  </si>
+  <si>
+    <t>HANASUI MOIST GEL 30</t>
+  </si>
+  <si>
+    <t>20137606</t>
+  </si>
+  <si>
+    <t>EMINA BRIGHT GLW 30G</t>
+  </si>
+  <si>
+    <t>20137609</t>
+  </si>
+  <si>
+    <t>EMINA BARRIER GEL 30</t>
+  </si>
+  <si>
+    <t>20133297</t>
+  </si>
+  <si>
+    <t>GLAD2 SOOTHNG GEL55G</t>
+  </si>
+  <si>
+    <t>20132715</t>
+  </si>
+  <si>
+    <t>GLAD2 MOIST BLBRRY30</t>
+  </si>
+  <si>
+    <t>20133309</t>
+  </si>
+  <si>
+    <t>GLAD2 POMEGRANATE 30</t>
+  </si>
+  <si>
+    <t>20135851</t>
+  </si>
+  <si>
+    <t>GLAD2 MOIST PEACH30</t>
+  </si>
+  <si>
+    <t>20134565</t>
+  </si>
+  <si>
+    <t>GLAD2 MOIST YUJA DRK</t>
+  </si>
+  <si>
+    <t>20139172</t>
+  </si>
+  <si>
+    <t>G2G VITA C MOIST 30G</t>
+  </si>
+  <si>
+    <t>20137696</t>
+  </si>
+  <si>
+    <t>GINZA TXA BR.MOIS 30</t>
+  </si>
+  <si>
+    <t>20138306</t>
+  </si>
+  <si>
+    <t>SCORA NIACINAMD HYDR</t>
+  </si>
+  <si>
+    <t>20138684</t>
+  </si>
+  <si>
+    <t>SCORA D-PANTNL MOIST</t>
+  </si>
+  <si>
+    <t>20021435</t>
+  </si>
+  <si>
+    <t>NIVEA STRW SHINE 4.8</t>
+  </si>
+  <si>
+    <t>36</t>
+  </si>
+  <si>
+    <t>20120259</t>
+  </si>
+  <si>
+    <t>HNSUI VT.C+CLG SRM20</t>
+  </si>
+  <si>
+    <t>20136024</t>
+  </si>
+  <si>
+    <t>DERMA PTCH PLS DAY6S</t>
+  </si>
+  <si>
+    <t>10029898</t>
+  </si>
+  <si>
+    <t>LIP ICE S.COLOR STR2</t>
+  </si>
+  <si>
+    <t>20094417</t>
+  </si>
+  <si>
+    <t>DRM ANGL PATCH NG 6S</t>
+  </si>
+  <si>
+    <t>20120258</t>
+  </si>
+  <si>
+    <t>HNSUI WH.GOLD SRM 20</t>
+  </si>
+  <si>
+    <t>20094416</t>
+  </si>
+  <si>
+    <t>DRM ANGL PATCH DAY6S</t>
+  </si>
+  <si>
+    <t>20098761</t>
+  </si>
+  <si>
+    <t>EMINA BS T-UP GEL20</t>
+  </si>
+  <si>
+    <t>20137692</t>
+  </si>
+  <si>
+    <t>HNSUI PWR PL.SRM 20</t>
+  </si>
+  <si>
+    <t>20094772</t>
+  </si>
+  <si>
+    <t>EMINA BS MOIS.CRM 20</t>
+  </si>
+  <si>
+    <t>20107792</t>
+  </si>
+  <si>
+    <t>NOURISH ACNE-PL PINK</t>
+  </si>
+  <si>
+    <t>20130188</t>
+  </si>
+  <si>
+    <t>HANASUI BRGHT SRM 20</t>
+  </si>
+  <si>
+    <t>20088537</t>
+  </si>
+  <si>
+    <t>GRNR VIT.C SPF36-20</t>
+  </si>
+  <si>
+    <t>20135183</t>
+  </si>
+  <si>
+    <t>VIO ACNE PATCH 18'S</t>
+  </si>
+  <si>
+    <t>20137411</t>
+  </si>
+  <si>
+    <t>SHINZUI SRM BRGHT 20</t>
+  </si>
+  <si>
+    <t>20056601</t>
+  </si>
+  <si>
+    <t>MYBLN MSC HYPRCL BLS</t>
+  </si>
+  <si>
+    <t>20090447</t>
+  </si>
+  <si>
+    <t>GRNR SRM CR SPF30-20</t>
+  </si>
+  <si>
+    <t>20102837</t>
+  </si>
+  <si>
+    <t>GRNR BS.SRM VIT C7.5</t>
+  </si>
+  <si>
+    <t>20049429</t>
+  </si>
+  <si>
+    <t>WARDAH DAY CRM 20G</t>
+  </si>
+  <si>
+    <t>20132418</t>
+  </si>
+  <si>
+    <t>VIVA E/BRW D.BRWN1.3</t>
+  </si>
+  <si>
+    <t>20138591</t>
+  </si>
+  <si>
+    <t>HNSUI RTNL MOIST 30G</t>
+  </si>
+  <si>
+    <t>10019513</t>
+  </si>
+  <si>
+    <t>VIVA E/BROW PNCL 1.3</t>
+  </si>
+  <si>
+    <t>20038958</t>
+  </si>
+  <si>
+    <t>GLW&amp;LOVELY GLW.CRM23</t>
+  </si>
+  <si>
+    <t>20138590</t>
+  </si>
+  <si>
+    <t>HNSUI BRGH/E MOIS 30</t>
+  </si>
+  <si>
+    <t>20086026</t>
+  </si>
+  <si>
+    <t>G&amp;L 2IN1 PWD CRM 20G</t>
+  </si>
+  <si>
+    <t>20104076</t>
+  </si>
+  <si>
+    <t>EMINA BS LS.PWDR 55</t>
+  </si>
+  <si>
+    <t>20137607</t>
+  </si>
+  <si>
+    <t>PONDS SS HYDRATE 15G</t>
+  </si>
+  <si>
+    <t>10003931</t>
+  </si>
+  <si>
+    <t>MARCKS BEDAK CRM 40G</t>
+  </si>
+  <si>
+    <t>20038957</t>
+  </si>
+  <si>
+    <t>GLW&amp;LOVELY DRM.CRM46</t>
+  </si>
+  <si>
+    <t>20137589</t>
+  </si>
+  <si>
+    <t>PONDS SS BRIGHT 15G</t>
+  </si>
+  <si>
+    <t>20138102</t>
+  </si>
+  <si>
+    <t>SCORA SHEER GLOW 20G</t>
+  </si>
+  <si>
+    <t>20139420</t>
+  </si>
+  <si>
+    <t>FCTOLOGY TC.SS 30ML</t>
+  </si>
+  <si>
+    <t>20014028</t>
+  </si>
+  <si>
+    <t>BIORE PORE PCK BLC4S</t>
+  </si>
+  <si>
+    <t>20128963</t>
+  </si>
+  <si>
+    <t>KJSAN SL SOAP HDRO65</t>
+  </si>
+  <si>
+    <t>20083934</t>
+  </si>
+  <si>
+    <t>KOJIESAN SL SOAP 65</t>
+  </si>
+  <si>
+    <t>20083935</t>
+  </si>
+  <si>
+    <t>KOJIESAN DW SOAP 65</t>
+  </si>
+  <si>
+    <t>20139600</t>
+  </si>
+  <si>
+    <t>GRNIER MEN A.CLM 100</t>
+  </si>
+  <si>
+    <t>37</t>
+  </si>
+  <si>
+    <t>20053651</t>
+  </si>
+  <si>
+    <t>GRN MEN TB DUO.FM150</t>
+  </si>
+  <si>
+    <t>20142236</t>
+  </si>
+  <si>
+    <t>B/D BRIGHT RAD.MOIST</t>
+  </si>
+  <si>
+    <t>20141366</t>
+  </si>
+  <si>
+    <t>BARBER.D U/S FW 100</t>
+  </si>
+  <si>
+    <t>20137260</t>
+  </si>
+  <si>
+    <t>B/D FW ACNE CARE 100</t>
+  </si>
+  <si>
+    <t>20137413</t>
+  </si>
+  <si>
+    <t>B.DAILY BRIGHT 100</t>
+  </si>
+  <si>
+    <t>20046688</t>
+  </si>
+  <si>
+    <t>PONDS PW WHT.BS 100</t>
+  </si>
+  <si>
+    <t>20141137</t>
+  </si>
+  <si>
+    <t>MORRIS FW OC&amp;AC 100G</t>
+  </si>
+  <si>
+    <t>20046907</t>
+  </si>
+  <si>
+    <t>BIORE MEN COOL/O 100</t>
+  </si>
+  <si>
+    <t>20046908</t>
+  </si>
+  <si>
+    <t>BIORE MEN BRGHT/E100</t>
+  </si>
+  <si>
+    <t>20133062</t>
+  </si>
+  <si>
+    <t>BIORE MEN B/EXPRT100</t>
+  </si>
+  <si>
+    <t>20113111</t>
+  </si>
+  <si>
+    <t>BIORE MEN OIL CL 100</t>
+  </si>
+  <si>
+    <t>20129289</t>
+  </si>
+  <si>
+    <t>NIVEA MEN C&amp;HYA 100</t>
+  </si>
+  <si>
+    <t>20018965</t>
+  </si>
+  <si>
+    <t>NIVEA FF DRK.SPT 100</t>
+  </si>
+  <si>
+    <t>20053649</t>
+  </si>
+  <si>
+    <t>GRNIER MEN B+O/C 100</t>
+  </si>
+  <si>
+    <t>38</t>
+  </si>
+  <si>
+    <t>20037559</t>
+  </si>
+  <si>
+    <t>GRNR MEN COOL FM 100</t>
+  </si>
+  <si>
+    <t>20088539</t>
+  </si>
+  <si>
+    <t>GRNIER 3IN1 C.BLK100</t>
+  </si>
+  <si>
+    <t>20034274</t>
+  </si>
+  <si>
+    <t>GRNR MEN ICY SCRB100</t>
+  </si>
+  <si>
+    <t>20042866</t>
+  </si>
+  <si>
+    <t>GRNIER ACNO FIGHT150</t>
+  </si>
+  <si>
+    <t>20052043</t>
+  </si>
+  <si>
+    <t>GRNIER MEN WSABI 100</t>
+  </si>
+  <si>
+    <t>20113403</t>
+  </si>
+  <si>
+    <t>KAHF FC.WASH O&amp;C 100</t>
+  </si>
+  <si>
+    <t>20122091</t>
+  </si>
+  <si>
+    <t>KAHF FC.SCRB G/E 100</t>
+  </si>
+  <si>
+    <t>20113402</t>
+  </si>
+  <si>
+    <t>KAHF FC.WASH E&amp;B 100</t>
+  </si>
+  <si>
+    <t>20125542</t>
+  </si>
+  <si>
+    <t>KAHF OIL&amp;CMED DEF100</t>
+  </si>
+  <si>
+    <t>20135458</t>
+  </si>
+  <si>
+    <t>KAHF F/W ACNE&amp;POR100</t>
+  </si>
+  <si>
+    <t>20138905</t>
+  </si>
+  <si>
+    <t>KAHF FW ACNE.CR 100</t>
+  </si>
+  <si>
+    <t>20138904</t>
+  </si>
+  <si>
+    <t>KAHF FW BRG.REVT 100</t>
+  </si>
+  <si>
+    <t>20139366</t>
+  </si>
+  <si>
+    <t>NIVEA MEN EX.BRG 100</t>
+  </si>
+  <si>
+    <t>20048310</t>
+  </si>
+  <si>
+    <t>GRNIER ACNO FIGHT 50</t>
+  </si>
+  <si>
+    <t>39</t>
+  </si>
+  <si>
+    <t>20034678</t>
+  </si>
+  <si>
+    <t>GRNR MEN COOL FM 50</t>
+  </si>
+  <si>
+    <t>20097301</t>
+  </si>
+  <si>
+    <t>GRNIER 3IN1 CH.BLC50</t>
+  </si>
+  <si>
+    <t>20115160</t>
+  </si>
+  <si>
+    <t>GRNR MEN TB DUO.FM50</t>
+  </si>
+  <si>
+    <t>20141643</t>
+  </si>
+  <si>
+    <t>NEXTPRIMEMEN DEEP</t>
+  </si>
+  <si>
+    <t>RT,(E-27H)</t>
+  </si>
+  <si>
+    <t>20141642</t>
+  </si>
+  <si>
+    <t>NEXTPRIMEMEN BRIGHT</t>
+  </si>
+  <si>
+    <t>20103680</t>
+  </si>
+  <si>
+    <t>GATSBY EDT BLC.WD 50</t>
+  </si>
+  <si>
+    <t>20100915</t>
+  </si>
+  <si>
+    <t>GATSBY EDT SKY REF50</t>
+  </si>
+  <si>
+    <t>20135853</t>
+  </si>
+  <si>
+    <t>GATSBY EDP AIR COD75</t>
+  </si>
+  <si>
+    <t>20135855</t>
+  </si>
+  <si>
+    <t>GATSBY EDP STR COD75</t>
+  </si>
+  <si>
+    <t>20140973</t>
+  </si>
+  <si>
+    <t>ROMANO EDP ZENITH 50</t>
+  </si>
+  <si>
+    <t>20108294</t>
+  </si>
+  <si>
+    <t>ROMANO EDP ATTDE 100</t>
+  </si>
+  <si>
+    <t>20125158</t>
+  </si>
+  <si>
+    <t>ROMANO EDT GRND100</t>
+  </si>
+  <si>
+    <t>20134769</t>
+  </si>
+  <si>
+    <t>POSH MEN EDT BLCK100</t>
+  </si>
+  <si>
+    <t>20120927</t>
+  </si>
+  <si>
+    <t>KAHF SUNSCREEN 30ML</t>
+  </si>
+  <si>
+    <t>20139844</t>
+  </si>
+  <si>
+    <t>BELLAGIO EDP BLUE 50</t>
+  </si>
+  <si>
+    <t>40</t>
+  </si>
+  <si>
+    <t>20139843</t>
+  </si>
+  <si>
+    <t>BELLAGIO EDP BLCK 50</t>
+  </si>
+  <si>
+    <t>20141565</t>
+  </si>
+  <si>
+    <t>XCHANGE AQUA MYTH 50</t>
+  </si>
+  <si>
+    <t>20139975</t>
+  </si>
+  <si>
+    <t>CSBLNCA EDP CHLGR 50</t>
+  </si>
+  <si>
+    <t>10026626</t>
+  </si>
+  <si>
+    <t>CASA/B COL.AQUA100ML</t>
+  </si>
+  <si>
+    <t>20094874</t>
+  </si>
+  <si>
+    <t>BELLAGIO EDT SPRT100</t>
+  </si>
+  <si>
+    <t>20137253</t>
+  </si>
+  <si>
+    <t>BRAVEN EDP COOL 100M</t>
+  </si>
+  <si>
+    <t>20140807</t>
+  </si>
+  <si>
+    <t>BRAVEN EDP AQUA 100</t>
+  </si>
+  <si>
+    <t>20134768</t>
+  </si>
+  <si>
+    <t>BRAVEN FM.OUD WOD100</t>
+  </si>
+  <si>
+    <t>20129495</t>
+  </si>
+  <si>
+    <t>MORRIS EDP WOODY 100</t>
+  </si>
+  <si>
+    <t>20129494</t>
+  </si>
+  <si>
+    <t>MORRIS EDP AQUATC100</t>
+  </si>
+  <si>
+    <t>20134765</t>
+  </si>
+  <si>
+    <t>MORRIS EDP FRESH 100</t>
+  </si>
+  <si>
+    <t>20115271</t>
+  </si>
+  <si>
+    <t>MORRIS EDP MTRO 100</t>
+  </si>
+  <si>
+    <t>20120918</t>
+  </si>
+  <si>
+    <t>MORRIS EDP CRTVE 100</t>
+  </si>
+  <si>
+    <t>20128126</t>
+  </si>
+  <si>
+    <t>VTLIS EDP MORNING100</t>
+  </si>
+  <si>
+    <t>10004664</t>
+  </si>
+  <si>
+    <t>ALEXANDER DEO HT 3.7</t>
+  </si>
+  <si>
+    <t>10003511</t>
+  </si>
+  <si>
+    <t>PIERRE DEO PUTIH 150</t>
+  </si>
+  <si>
+    <t>20092367</t>
+  </si>
+  <si>
+    <t>NIVEA MEN INVS FRS50</t>
+  </si>
+  <si>
+    <t>41</t>
+  </si>
+  <si>
+    <t>20116990</t>
+  </si>
+  <si>
+    <t>POSH DEO ACT COOL 50</t>
+  </si>
+  <si>
+    <t>20133516</t>
+  </si>
+  <si>
+    <t>KAHF DEO COOL.PWR 45</t>
+  </si>
+  <si>
+    <t>20133517</t>
+  </si>
+  <si>
+    <t>KAHF DEO EXTR.DRY 45</t>
+  </si>
+  <si>
+    <t>20137605</t>
+  </si>
+  <si>
+    <t>KAHF DEO CLN.FRSH 45</t>
+  </si>
+  <si>
+    <t>20138588</t>
+  </si>
+  <si>
+    <t>GATSBY DEO BLUE 50ML</t>
+  </si>
+  <si>
+    <t>20138589</t>
+  </si>
+  <si>
+    <t>GATSBY DEO BOLD 50ML</t>
+  </si>
+  <si>
+    <t>10036357</t>
+  </si>
+  <si>
+    <t>CASA/B DEO MEN BLU50</t>
+  </si>
+  <si>
+    <t>10036356</t>
+  </si>
+  <si>
+    <t>CASA/B DEO MEN BLC50</t>
+  </si>
+  <si>
+    <t>20070151</t>
+  </si>
+  <si>
+    <t>BELLAGIO EDP RAVE 50</t>
+  </si>
+  <si>
+    <t>20024517</t>
+  </si>
+  <si>
+    <t>AXE DEO DARK 135ML</t>
+  </si>
+  <si>
+    <t>20075923</t>
+  </si>
+  <si>
+    <t>POSH BS BL.GOLD 150</t>
+  </si>
+  <si>
+    <t>20114433</t>
+  </si>
+  <si>
+    <t>POSH MEN GRN MT 150</t>
+  </si>
+  <si>
+    <t>20075924</t>
+  </si>
+  <si>
+    <t>POSH BS COOL.BL 150</t>
+  </si>
+  <si>
+    <t>20092190</t>
+  </si>
+  <si>
+    <t>POSH RED EXTREME 150</t>
+  </si>
+  <si>
+    <t>20134793</t>
+  </si>
+  <si>
+    <t>NPOLEON EDT NERO 100</t>
+  </si>
+  <si>
+    <t>20084999</t>
+  </si>
+  <si>
+    <t>CASA/B EDT AQUA 100</t>
+  </si>
+  <si>
+    <t>20091428</t>
+  </si>
+  <si>
+    <t>CLEAR/M SHP CL.SP160</t>
+  </si>
+  <si>
+    <t>20142237</t>
+  </si>
+  <si>
+    <t>BD R/O POWERSHIELD50</t>
+  </si>
+  <si>
+    <t>42</t>
+  </si>
+  <si>
+    <t>,(E-3B)</t>
+  </si>
+  <si>
+    <t>20139454</t>
+  </si>
+  <si>
+    <t>NIVEA MEN DEO DC 50</t>
+  </si>
+  <si>
+    <t>20120783</t>
+  </si>
+  <si>
+    <t>NIVEA MEN CK FGR 50</t>
+  </si>
+  <si>
+    <t>20088376</t>
+  </si>
+  <si>
+    <t>NVEA MEN R/ON DEEP50</t>
+  </si>
+  <si>
+    <t>20134496</t>
+  </si>
+  <si>
+    <t>20051842</t>
+  </si>
+  <si>
+    <t>NIVEA/M R/ON INVS 50</t>
+  </si>
+  <si>
+    <t>20054716</t>
+  </si>
+  <si>
+    <t>NIVEA/M R/ON COL/K50</t>
+  </si>
+  <si>
+    <t>20062306</t>
+  </si>
+  <si>
+    <t>RXONA MEN DEO ICE 45</t>
+  </si>
+  <si>
+    <t>20062309</t>
+  </si>
+  <si>
+    <t>RXNA MEN DEO ULTR 45</t>
+  </si>
+  <si>
+    <t>20062308</t>
+  </si>
+  <si>
+    <t>RXONA MEN DEO SPR 45</t>
+  </si>
+  <si>
+    <t>20062307</t>
+  </si>
+  <si>
+    <t>RXONA MEN DEO INV 50</t>
+  </si>
+  <si>
+    <t>20087201</t>
+  </si>
+  <si>
+    <t>RXNA MEN INV+A.BC 45</t>
+  </si>
+  <si>
+    <t>20111362</t>
+  </si>
+  <si>
+    <t>RXNA MEN LM COOL 45</t>
+  </si>
+  <si>
+    <t>20139354</t>
+  </si>
+  <si>
+    <t>RXONA MEN FR.STRK 40</t>
+  </si>
+  <si>
+    <t>20026865</t>
+  </si>
+  <si>
+    <t>GATSBY WAX PWR&amp;SPK75</t>
+  </si>
+  <si>
+    <t>10005133</t>
+  </si>
+  <si>
+    <t>GATSBY TREAT.NOR 125</t>
+  </si>
+  <si>
+    <t>20022917</t>
+  </si>
+  <si>
+    <t>GATSBY WGLOS H/SLD75</t>
+  </si>
+  <si>
+    <t>20053183</t>
+  </si>
+  <si>
+    <t>GTSBY STYL POMADE 75</t>
+  </si>
+  <si>
+    <t>20097521</t>
+  </si>
+  <si>
+    <t>MAGIC PWR CLASSIC 6S</t>
+  </si>
+  <si>
+    <t>43</t>
+  </si>
+  <si>
+    <t>20063363</t>
+  </si>
+  <si>
+    <t>OKAMOTO KNDM PLT 2'S</t>
+  </si>
+  <si>
+    <t>20139964</t>
+  </si>
+  <si>
+    <t>MAGIC PWR ICE BL 6'S</t>
+  </si>
+  <si>
+    <t>10008133</t>
+  </si>
+  <si>
+    <t>DUREX EXTRA3S</t>
+  </si>
+  <si>
+    <t>20078435</t>
+  </si>
+  <si>
+    <t>DUREX INVISIBLE 2'S</t>
+  </si>
+  <si>
+    <t>20035693</t>
+  </si>
+  <si>
+    <t>DUREX PERFORMA 3'S</t>
+  </si>
+  <si>
+    <t>20045107</t>
+  </si>
+  <si>
+    <t>DUREX LOVE BOX 3'S</t>
+  </si>
+  <si>
+    <t>20069205</t>
+  </si>
+  <si>
+    <t>FIESTA MAX DOT 3'S</t>
+  </si>
+  <si>
+    <t>20091579</t>
+  </si>
+  <si>
+    <t>SUTRA GERIGI 3'S</t>
+  </si>
+  <si>
+    <t>20022011</t>
+  </si>
+  <si>
+    <t>SUTRA OK 3'S</t>
+  </si>
+  <si>
+    <t>10004656</t>
+  </si>
+  <si>
+    <t>SUTRA KONDOM 3'S</t>
+  </si>
+  <si>
+    <t>20069204</t>
+  </si>
+  <si>
+    <t>SUTRA OK 12'S</t>
+  </si>
+  <si>
+    <t>10004655</t>
+  </si>
+  <si>
+    <t>SUTRA 12'S</t>
+  </si>
+  <si>
+    <t>10008992</t>
+  </si>
+  <si>
+    <t>GILLETE RAZOR VECTOR</t>
+  </si>
+  <si>
+    <t>44</t>
+  </si>
+  <si>
+    <t>PT</t>
+  </si>
+  <si>
+    <t>10009007</t>
+  </si>
+  <si>
+    <t>GILLETE CATR.VECTOR2</t>
+  </si>
+  <si>
+    <t>20086422</t>
+  </si>
+  <si>
+    <t>GILLETTE BLUE II 3+1</t>
+  </si>
+  <si>
+    <t>20139066</t>
+  </si>
+  <si>
+    <t>GLLTTE BLUE3 FLXI 3S</t>
+  </si>
+  <si>
+    <t>20135324</t>
+  </si>
+  <si>
+    <t>GLLETTE GOAL YLW 4'S</t>
+  </si>
+  <si>
+    <t>20033978</t>
+  </si>
+  <si>
+    <t>GILLETTE RAZOR BLUE3</t>
+  </si>
+  <si>
+    <t>20081456</t>
+  </si>
+  <si>
+    <t>GLLETTE BLUE3 SIMPLE</t>
+  </si>
+  <si>
+    <t>20137021</t>
+  </si>
+  <si>
+    <t>IDM PISAU CUKUR 3+1</t>
+  </si>
+  <si>
+    <t>20141365</t>
+  </si>
+  <si>
+    <t>BARBER.D 6 BL SHAVER</t>
+  </si>
+  <si>
+    <t>20014993</t>
+  </si>
+  <si>
+    <t>GILLETTE BLUE II PLS</t>
+  </si>
+  <si>
+    <t>20096659</t>
+  </si>
+  <si>
+    <t>IDM RAZOR 3MATA SLT</t>
+  </si>
+  <si>
+    <t>10000318</t>
+  </si>
+  <si>
+    <t>GLLETTE RZR GOAL YLW</t>
+  </si>
+  <si>
+    <t>20123700</t>
+  </si>
+  <si>
+    <t>GLTTE BLUE II FLEXI</t>
+  </si>
+  <si>
+    <t>20029237</t>
+  </si>
+  <si>
+    <t>IDM PISAU CUKUR 2MP</t>
+  </si>
+  <si>
+    <t>10013212</t>
+  </si>
+  <si>
+    <t>GILLETTE SMPLY VNS2S</t>
+  </si>
+  <si>
+    <t>20088267</t>
+  </si>
+  <si>
+    <t>BELLAGIO PMDE RED 80</t>
+  </si>
+  <si>
+    <t>45</t>
+  </si>
+  <si>
+    <t>20090906</t>
+  </si>
+  <si>
+    <t>BELLAGIO PMD BLCK 80</t>
+  </si>
+  <si>
+    <t>20128951</t>
+  </si>
+  <si>
+    <t>MORRIS PMD EXTR HL80</t>
+  </si>
+  <si>
+    <t>20136022</t>
+  </si>
+  <si>
+    <t>GTSBY FBR CLY MATT80</t>
+  </si>
+  <si>
+    <t>20136021</t>
+  </si>
+  <si>
+    <t>GTSBY FBR PMD GLOS80</t>
+  </si>
+  <si>
+    <t>20127064</t>
+  </si>
+  <si>
+    <t>S/R STYLING PMDE 75</t>
+  </si>
+  <si>
+    <t>20082862</t>
+  </si>
+  <si>
+    <t>GTSBY PMD PR.RISE 75</t>
+  </si>
+  <si>
+    <t>20136388</t>
+  </si>
+  <si>
+    <t>KAHF PMD SLK CLSY 70</t>
+  </si>
+  <si>
+    <t>20142118</t>
+  </si>
+  <si>
+    <t>B/D STRNG POMADE 75</t>
+  </si>
+  <si>
+    <t>20129578</t>
+  </si>
+  <si>
+    <t>GATSBY BALM PMADE 70</t>
+  </si>
+  <si>
+    <t>20129580</t>
+  </si>
+  <si>
+    <t>GATSBY BALM CLAY 70</t>
+  </si>
+  <si>
+    <t>20129581</t>
+  </si>
+  <si>
+    <t>GATSBY BALM CREAM 70</t>
+  </si>
+  <si>
+    <t>20139065</t>
+  </si>
+  <si>
+    <t>PONDS MEN AA&amp;PC 100</t>
+  </si>
+  <si>
+    <t>998</t>
+  </si>
+  <si>
     <t>20057362</t>
   </si>
   <si>
     <t>WRDH CRM.F SMTH/GL50</t>
   </si>
   <si>
-    <t>20093587</t>
-  </si>
-  <si>
-    <t>SENKA PRFCT WHIP 50</t>
-  </si>
-  <si>
-    <t>20135695</t>
-  </si>
-  <si>
-    <t>C&amp;C VITAMIN C FW 100</t>
-  </si>
-  <si>
-    <t>20008420</t>
-  </si>
-  <si>
-    <t>CLEAN&amp;CLEAR FAC100ML</t>
-  </si>
-  <si>
-    <t>20000765</t>
-  </si>
-  <si>
-    <t>CLEAN&amp;CLEAR FAC 50</t>
-  </si>
-  <si>
-    <t>20138028</t>
-  </si>
-  <si>
-    <t>G2G FW MILK AMINO 80</t>
-  </si>
-  <si>
-    <t>31</t>
-  </si>
-  <si>
-    <t>20139173</t>
-  </si>
-  <si>
-    <t>G2G FW P.VITA C 80G</t>
-  </si>
-  <si>
-    <t>20136004</t>
-  </si>
-  <si>
-    <t>GLAD2 CLNSR CNTELA70</t>
-  </si>
-  <si>
-    <t>20134060</t>
-  </si>
-  <si>
-    <t>GLAD2 CLNSR BLBRRY70</t>
-  </si>
-  <si>
-    <t>20140352</t>
-  </si>
-  <si>
-    <t>G2G FW DEEP PC 70ML</t>
-  </si>
-  <si>
-    <t>20141939</t>
-  </si>
-  <si>
-    <t>G2G SERUM FW NIACI70</t>
-  </si>
-  <si>
-    <t>10012397</t>
-  </si>
-  <si>
-    <t>NVEA SB FF PEARL 100</t>
-  </si>
-  <si>
-    <t>20067449</t>
-  </si>
-  <si>
-    <t>GLW&amp;LOVELY DRM.GL100</t>
-  </si>
-  <si>
-    <t>20110117</t>
-  </si>
-  <si>
-    <t>G&amp;L FC.FOAM VIT.C100</t>
-  </si>
-  <si>
-    <t>20130082</t>
-  </si>
-  <si>
-    <t>EMINA BS FACE WSH100</t>
-  </si>
-  <si>
-    <t>20134238</t>
-  </si>
-  <si>
-    <t>POISE FF OIL.CTRL100</t>
-  </si>
-  <si>
-    <t>20092317</t>
-  </si>
-  <si>
-    <t>POISE FAC.FM WHT 100</t>
-  </si>
-  <si>
-    <t>20127065</t>
-  </si>
-  <si>
-    <t>POISE FF ANT.ACNE100</t>
-  </si>
-  <si>
-    <t>20021810</t>
-  </si>
-  <si>
-    <t>ACNES CREAMY WASH100</t>
-  </si>
-  <si>
-    <t>20056357</t>
-  </si>
-  <si>
-    <t>ACNES FW CMP.WHT 100</t>
-  </si>
-  <si>
-    <t>20141979</t>
-  </si>
-  <si>
-    <t>GARNIER SKR GLOW 100</t>
-  </si>
-  <si>
-    <t>32</t>
-  </si>
-  <si>
-    <t>20141978</t>
-  </si>
-  <si>
-    <t>GARNIER VITC LWPH100</t>
-  </si>
-  <si>
-    <t>20136511</t>
-  </si>
-  <si>
-    <t>GRNR SRM CLNSR 100</t>
-  </si>
-  <si>
-    <t>20052782</t>
-  </si>
-  <si>
-    <t>GRNIER SKR GLW HY100</t>
-  </si>
-  <si>
-    <t>20025002</t>
-  </si>
-  <si>
-    <t>GRNIER BC FW VT.C100</t>
-  </si>
-  <si>
-    <t>20040194</t>
-  </si>
-  <si>
-    <t>GRNR BC FWS.VT.C100</t>
-  </si>
-  <si>
-    <t>20137610</t>
-  </si>
-  <si>
-    <t>PONDS HYDRA.MRCL 90G</t>
-  </si>
-  <si>
-    <t>20137608</t>
-  </si>
-  <si>
-    <t>PONDS BRGHT MRCL 90G</t>
-  </si>
-  <si>
-    <t>20067202</t>
-  </si>
-  <si>
-    <t>PONDS PW PR.CHR100G</t>
-  </si>
-  <si>
-    <t>20067210</t>
-  </si>
-  <si>
-    <t>PONDS PW NSRCNL 100G</t>
-  </si>
-  <si>
-    <t>20090023</t>
-  </si>
-  <si>
-    <t>WRDH BRGH MUG CLY100</t>
-  </si>
-  <si>
-    <t>20090022</t>
-  </si>
-  <si>
-    <t>WRDH BRG NOW ENZM100</t>
-  </si>
-  <si>
-    <t>20106672</t>
-  </si>
-  <si>
-    <t>WRDH LG FAC.FOAM 100</t>
-  </si>
-  <si>
-    <t>20071676</t>
-  </si>
-  <si>
-    <t>WRDH C/S CLRFY FW100</t>
-  </si>
-  <si>
-    <t>20078833</t>
-  </si>
-  <si>
-    <t>WRDAH C.WSH C-DEF100</t>
-  </si>
-  <si>
-    <t>20115358</t>
-  </si>
-  <si>
-    <t>HMLYA P.NEEM MASK100</t>
-  </si>
-  <si>
-    <t>33</t>
-  </si>
-  <si>
-    <t>20140296</t>
-  </si>
-  <si>
-    <t>D/A STCK ACNE.CR 20</t>
-  </si>
-  <si>
-    <t>20139950</t>
-  </si>
-  <si>
-    <t>HMLY TURMERIC CSM 30</t>
-  </si>
-  <si>
-    <t>TG,(E-3B)</t>
-  </si>
-  <si>
-    <t>20139313</t>
-  </si>
-  <si>
-    <t>HMLY PRFY N/C SM 30</t>
-  </si>
-  <si>
-    <t>20133290</t>
-  </si>
-  <si>
-    <t>GLAD2 MUGWORT ACID25</t>
-  </si>
-  <si>
-    <t>20139050</t>
-  </si>
-  <si>
-    <t>EMINA WTR UV GEL25ML</t>
-  </si>
-  <si>
-    <t>20139605</t>
-  </si>
-  <si>
-    <t>AZZURA SS SPF 50 30G</t>
-  </si>
-  <si>
-    <t>20139439</t>
-  </si>
-  <si>
-    <t>SCORA B.ME UP SS 30G</t>
-  </si>
-  <si>
-    <t>20135594</t>
-  </si>
-  <si>
-    <t>CARASUN SS UV.SUNS30</t>
-  </si>
-  <si>
-    <t>20133672</t>
-  </si>
-  <si>
-    <t>HNSUI COL.SUNS.SPF50</t>
-  </si>
-  <si>
-    <t>20139352</t>
-  </si>
-  <si>
-    <t>HNSUI SS LGHT.PRO 30</t>
-  </si>
-  <si>
-    <t>20130191</t>
-  </si>
-  <si>
-    <t>HNSUI COL.SUNSCRN 30</t>
-  </si>
-  <si>
-    <t>20134797</t>
-  </si>
-  <si>
-    <t>WRDH UV ACN/CL SUN35</t>
-  </si>
-  <si>
-    <t>20110001</t>
-  </si>
-  <si>
-    <t>WARDAH UV GRD GEL40</t>
-  </si>
-  <si>
-    <t>20131253</t>
-  </si>
-  <si>
-    <t>WARDAH UV AIRY SRM25</t>
-  </si>
-  <si>
-    <t>20138742</t>
-  </si>
-  <si>
-    <t>S/AYU T.UP SNSCRN 30</t>
-  </si>
-  <si>
-    <t>20072834</t>
-  </si>
-  <si>
-    <t>PONDS AM PLMB DAY 10</t>
-  </si>
-  <si>
-    <t>34</t>
-  </si>
-  <si>
-    <t>20140080</t>
-  </si>
-  <si>
-    <t>GRNR NCNAMIDE DTC 30</t>
-  </si>
-  <si>
-    <t>20140081</t>
-  </si>
-  <si>
-    <t>GRNR SALICYLC DTC 30</t>
-  </si>
-  <si>
-    <t>20140079</t>
-  </si>
-  <si>
-    <t>GRNIER VIT.C DTC 30</t>
-  </si>
-  <si>
-    <t>20139845</t>
-  </si>
-  <si>
-    <t>PONDS BIOME NIAR 15G</t>
-  </si>
-  <si>
-    <t>20139846</t>
-  </si>
-  <si>
-    <t>PONDS BIOME CERA 15G</t>
-  </si>
-  <si>
-    <t>20139604</t>
-  </si>
-  <si>
-    <t>AZZURA DB DAY CRM 30</t>
-  </si>
-  <si>
-    <t>20127466</t>
-  </si>
-  <si>
-    <t>IMPLRA SPF40 SS 50ML</t>
-  </si>
-  <si>
-    <t>20136433</t>
-  </si>
-  <si>
-    <t>PIGEON SUNSCREN 30ML</t>
-  </si>
-  <si>
-    <t>20134326</t>
-  </si>
-  <si>
-    <t>SCRLT ULT SUNSCRN 30</t>
-  </si>
-  <si>
-    <t>RT,(E-7.5B)</t>
-  </si>
-  <si>
-    <t>20137670</t>
-  </si>
-  <si>
-    <t>GRNR SPR UV COOL.WTR</t>
-  </si>
-  <si>
-    <t>20129129</t>
-  </si>
-  <si>
-    <t>AZARINE CALM MA SS40</t>
-  </si>
-  <si>
-    <t>20129130</t>
-  </si>
-  <si>
-    <t>AZARINE HYD SS.GEL30</t>
-  </si>
-  <si>
-    <t>20137412</t>
-  </si>
-  <si>
-    <t>SHNZUI BS SUNSCRN 30</t>
-  </si>
-  <si>
-    <t>20123451</t>
-  </si>
-  <si>
-    <t>EMINA SUN BT 30PA 20</t>
-  </si>
-  <si>
-    <t>20096136</t>
-  </si>
-  <si>
-    <t>EMINA SUN BT 30PA 50</t>
-  </si>
-  <si>
-    <t>20138347</t>
-  </si>
-  <si>
-    <t>G&amp;G SUNSSCREN 15G</t>
-  </si>
-  <si>
-    <t>20126525</t>
-  </si>
-  <si>
-    <t>G&amp;L ULTMTE UV VT.C20</t>
-  </si>
-  <si>
-    <t>20137409</t>
-  </si>
-  <si>
-    <t>SHNZUI BR.SRM MS.30G</t>
-  </si>
-  <si>
-    <t>35</t>
-  </si>
-  <si>
-    <t>20133739</t>
-  </si>
-  <si>
-    <t>T/O HYALUCERA MOIS50</t>
-  </si>
-  <si>
-    <t>20138027</t>
-  </si>
-  <si>
-    <t>WRDAH SYM MS.GEL 30G</t>
-  </si>
-  <si>
-    <t>20135184</t>
-  </si>
-  <si>
-    <t>HANASUI MOIST GEL 30</t>
-  </si>
-  <si>
-    <t>20137606</t>
-  </si>
-  <si>
-    <t>EMINA BRIGHT GLW 30G</t>
-  </si>
-  <si>
-    <t>20137609</t>
-  </si>
-  <si>
-    <t>EMINA BARRIER GEL 30</t>
-  </si>
-  <si>
-    <t>20133297</t>
-  </si>
-  <si>
-    <t>GLAD2 SOOTHNG GEL55G</t>
-  </si>
-  <si>
-    <t>20132715</t>
-  </si>
-  <si>
-    <t>GLAD2 MOIST BLBRRY30</t>
-  </si>
-  <si>
-    <t>20133309</t>
-  </si>
-  <si>
-    <t>GLAD2 POMEGRANATE 30</t>
-  </si>
-  <si>
-    <t>20135851</t>
-  </si>
-  <si>
-    <t>GLAD2 MOIST PEACH30</t>
-  </si>
-  <si>
-    <t>20134565</t>
-  </si>
-  <si>
-    <t>GLAD2 MOIST YUJA DRK</t>
-  </si>
-  <si>
-    <t>20139172</t>
-  </si>
-  <si>
-    <t>G2G VITA C MOIST 30G</t>
-  </si>
-  <si>
-    <t>20137696</t>
-  </si>
-  <si>
-    <t>GINZA TXA BR.MOIS 30</t>
-  </si>
-  <si>
-    <t>20138306</t>
-  </si>
-  <si>
-    <t>SCORA NIACINAMD HYDR</t>
-  </si>
-  <si>
-    <t>20138684</t>
-  </si>
-  <si>
-    <t>SCORA D-PANTNL MOIST</t>
-  </si>
-  <si>
-    <t>20021435</t>
-  </si>
-  <si>
-    <t>NIVEA STRW SHINE 4.8</t>
-  </si>
-  <si>
-    <t>36</t>
-  </si>
-  <si>
-    <t>20120259</t>
-  </si>
-  <si>
-    <t>HNSUI VT.C+CLG SRM20</t>
-  </si>
-  <si>
-    <t>20136024</t>
-  </si>
-  <si>
-    <t>DERMA PTCH PLS DAY6S</t>
-  </si>
-  <si>
-    <t>10029898</t>
-  </si>
-  <si>
-    <t>LIP ICE S.COLOR STR2</t>
-  </si>
-  <si>
-    <t>20094417</t>
-  </si>
-  <si>
-    <t>DRM ANGL PATCH NG 6S</t>
-  </si>
-  <si>
-    <t>20120258</t>
-  </si>
-  <si>
-    <t>HNSUI WH.GOLD SRM 20</t>
-  </si>
-  <si>
-    <t>20094416</t>
-  </si>
-  <si>
-    <t>DRM ANGL PATCH DAY6S</t>
-  </si>
-  <si>
-    <t>20098761</t>
-  </si>
-  <si>
-    <t>EMINA BS T-UP GEL20</t>
-  </si>
-  <si>
-    <t>20137692</t>
-  </si>
-  <si>
-    <t>HNSUI PWR PL.SRM 20</t>
-  </si>
-  <si>
-    <t>20094772</t>
-  </si>
-  <si>
-    <t>EMINA BS MOIS.CRM 20</t>
-  </si>
-  <si>
-    <t>20107792</t>
-  </si>
-  <si>
-    <t>NOURISH ACNE-PL PINK</t>
-  </si>
-  <si>
-    <t>20130188</t>
-  </si>
-  <si>
-    <t>HANASUI BRGHT SRM 20</t>
-  </si>
-  <si>
-    <t>20088537</t>
-  </si>
-  <si>
-    <t>GRNR VIT.C SPF36-20</t>
-  </si>
-  <si>
-    <t>20135183</t>
-  </si>
-  <si>
-    <t>VIO ACNE PATCH 18'S</t>
-  </si>
-  <si>
-    <t>20137411</t>
-  </si>
-  <si>
-    <t>SHINZUI SRM BRGHT 20</t>
-  </si>
-  <si>
-    <t>20056601</t>
-  </si>
-  <si>
-    <t>MYBLN MSC HYPRCL BLS</t>
-  </si>
-  <si>
-    <t>20090447</t>
-  </si>
-  <si>
-    <t>GRNR SRM CR SPF30-20</t>
-  </si>
-  <si>
-    <t>20102837</t>
-  </si>
-  <si>
-    <t>GRNR BS.SRM VIT C7.5</t>
-  </si>
-  <si>
-    <t>20049429</t>
-  </si>
-  <si>
-    <t>WARDAH DAY CRM 20G</t>
-  </si>
-  <si>
-    <t>20132418</t>
-  </si>
-  <si>
-    <t>VIVA E/BRW D.BRWN1.3</t>
-  </si>
-  <si>
-    <t>20138591</t>
-  </si>
-  <si>
-    <t>HNSUI RTNL MOIST 30G</t>
-  </si>
-  <si>
-    <t>10019513</t>
-  </si>
-  <si>
-    <t>VIVA E/BROW PNCL 1.3</t>
-  </si>
-  <si>
-    <t>20038958</t>
-  </si>
-  <si>
-    <t>GLW&amp;LOVELY GLW.CRM23</t>
-  </si>
-  <si>
-    <t>20138590</t>
-  </si>
-  <si>
-    <t>HNSUI BRGH/E MOIS 30</t>
-  </si>
-  <si>
-    <t>20086026</t>
-  </si>
-  <si>
-    <t>G&amp;L 2IN1 PWD CRM 20G</t>
-  </si>
-  <si>
-    <t>20104076</t>
-  </si>
-  <si>
-    <t>EMINA BS LS.PWDR 55</t>
-  </si>
-  <si>
-    <t>20137607</t>
-  </si>
-  <si>
-    <t>PONDS SS HYDRATE 15G</t>
-  </si>
-  <si>
-    <t>10003931</t>
-  </si>
-  <si>
-    <t>MARCKS BEDAK CRM 40G</t>
-  </si>
-  <si>
-    <t>20038957</t>
-  </si>
-  <si>
-    <t>GLW&amp;LOVELY DRM.CRM46</t>
-  </si>
-  <si>
-    <t>20137589</t>
-  </si>
-  <si>
-    <t>PONDS SS BRIGHT 15G</t>
-  </si>
-  <si>
-    <t>20138102</t>
-  </si>
-  <si>
-    <t>SCORA SHEER GLOW 20G</t>
-  </si>
-  <si>
-    <t>20139420</t>
-  </si>
-  <si>
-    <t>FCTOLOGY TC.SS 30ML</t>
-  </si>
-  <si>
-    <t>20014028</t>
-  </si>
-  <si>
-    <t>BIORE PORE PCK BLC4S</t>
-  </si>
-  <si>
-    <t>20128963</t>
-  </si>
-  <si>
-    <t>KJSAN SL SOAP HDRO65</t>
-  </si>
-  <si>
-    <t>20083934</t>
-  </si>
-  <si>
-    <t>KOJIESAN SL SOAP 65</t>
-  </si>
-  <si>
-    <t>20083935</t>
-  </si>
-  <si>
-    <t>KOJIESAN DW SOAP 65</t>
-  </si>
-  <si>
-    <t>20139600</t>
-  </si>
-  <si>
-    <t>GRNIER MEN A.CLM 100</t>
-  </si>
-  <si>
-    <t>37</t>
-  </si>
-  <si>
-    <t>20053651</t>
-  </si>
-  <si>
-    <t>GRN MEN TB DUO.FM150</t>
-  </si>
-  <si>
-    <t>20141366</t>
-  </si>
-  <si>
-    <t>BARBER.D U/S FW 100</t>
-  </si>
-  <si>
-    <t>20137260</t>
-  </si>
-  <si>
-    <t>B/D FW ACNE CARE 100</t>
-  </si>
-  <si>
-    <t>20137413</t>
-  </si>
-  <si>
-    <t>B.DAILY BRIGHT 100</t>
-  </si>
-  <si>
-    <t>20046688</t>
-  </si>
-  <si>
-    <t>PONDS PW WHT.BS 100</t>
-  </si>
-  <si>
-    <t>20139065</t>
-  </si>
-  <si>
-    <t>PONDS MEN AA&amp;PC 100</t>
-  </si>
-  <si>
-    <t>20141137</t>
-  </si>
-  <si>
-    <t>MORRIS FW OC&amp;AC 100G</t>
-  </si>
-  <si>
-    <t>20046907</t>
-  </si>
-  <si>
-    <t>BIORE MEN COOL/O 100</t>
-  </si>
-  <si>
-    <t>20046908</t>
-  </si>
-  <si>
-    <t>BIORE MEN BRGHT/E100</t>
-  </si>
-  <si>
-    <t>20133062</t>
-  </si>
-  <si>
-    <t>BIORE MEN B/EXPRT100</t>
-  </si>
-  <si>
-    <t>20113111</t>
-  </si>
-  <si>
-    <t>BIORE MEN OIL CL 100</t>
-  </si>
-  <si>
-    <t>20129289</t>
-  </si>
-  <si>
-    <t>NIVEA MEN C&amp;HYA 100</t>
-  </si>
-  <si>
-    <t>20018965</t>
-  </si>
-  <si>
-    <t>NIVEA FF DRK.SPT 100</t>
-  </si>
-  <si>
-    <t>20053649</t>
-  </si>
-  <si>
-    <t>GRNIER MEN B+O/C 100</t>
-  </si>
-  <si>
-    <t>38</t>
-  </si>
-  <si>
-    <t>20037559</t>
-  </si>
-  <si>
-    <t>GRNR MEN COOL FM 100</t>
-  </si>
-  <si>
-    <t>20088539</t>
-  </si>
-  <si>
-    <t>GRNIER 3IN1 C.BLK100</t>
-  </si>
-  <si>
-    <t>20034274</t>
-  </si>
-  <si>
-    <t>GRNR MEN ICY SCRB100</t>
-  </si>
-  <si>
-    <t>20042866</t>
-  </si>
-  <si>
-    <t>GRNIER ACNO FIGHT150</t>
-  </si>
-  <si>
-    <t>20052043</t>
-  </si>
-  <si>
-    <t>GRNIER MEN WSABI 100</t>
-  </si>
-  <si>
-    <t>20113403</t>
-  </si>
-  <si>
-    <t>KAHF FC.WASH O&amp;C 100</t>
-  </si>
-  <si>
-    <t>20122091</t>
-  </si>
-  <si>
-    <t>KAHF FC.SCRB G/E 100</t>
-  </si>
-  <si>
-    <t>20113402</t>
-  </si>
-  <si>
-    <t>KAHF FC.WASH E&amp;B 100</t>
-  </si>
-  <si>
-    <t>20125542</t>
-  </si>
-  <si>
-    <t>KAHF OIL&amp;CMED DEF100</t>
-  </si>
-  <si>
-    <t>20135458</t>
-  </si>
-  <si>
-    <t>KAHF F/W ACNE&amp;POR100</t>
-  </si>
-  <si>
-    <t>20138905</t>
-  </si>
-  <si>
-    <t>KAHF FW ACNE.CR 100</t>
-  </si>
-  <si>
-    <t>20138904</t>
-  </si>
-  <si>
-    <t>KAHF FW BRG.REVT 100</t>
-  </si>
-  <si>
-    <t>20139366</t>
-  </si>
-  <si>
-    <t>NIVEA MEN EX.BRG 100</t>
-  </si>
-  <si>
-    <t>20048310</t>
-  </si>
-  <si>
-    <t>GRNIER ACNO FIGHT 50</t>
-  </si>
-  <si>
-    <t>39</t>
-  </si>
-  <si>
-    <t>20034678</t>
-  </si>
-  <si>
-    <t>GRNR MEN COOL FM 50</t>
-  </si>
-  <si>
-    <t>20097301</t>
-  </si>
-  <si>
-    <t>GRNIER 3IN1 CH.BLC50</t>
-  </si>
-  <si>
-    <t>20115160</t>
-  </si>
-  <si>
-    <t>GRNR MEN TB DUO.FM50</t>
-  </si>
-  <si>
-    <t>20141643</t>
-  </si>
-  <si>
-    <t>NEXTPRIMEMEN DEEP</t>
-  </si>
-  <si>
-    <t>RT,(E-27H)</t>
-  </si>
-  <si>
-    <t>20141642</t>
-  </si>
-  <si>
-    <t>NEXTPRIMEMEN BRIGHT</t>
-  </si>
-  <si>
-    <t>20103680</t>
-  </si>
-  <si>
-    <t>GATSBY EDT BLC.WD 50</t>
-  </si>
-  <si>
-    <t>20100915</t>
-  </si>
-  <si>
-    <t>GATSBY EDT SKY REF50</t>
-  </si>
-  <si>
-    <t>20135853</t>
-  </si>
-  <si>
-    <t>GATSBY EDP AIR COD75</t>
-  </si>
-  <si>
-    <t>20135855</t>
-  </si>
-  <si>
-    <t>GATSBY EDP STR COD75</t>
-  </si>
-  <si>
-    <t>20140973</t>
-  </si>
-  <si>
-    <t>ROMANO EDP ZENITH 50</t>
-  </si>
-  <si>
-    <t>20108294</t>
-  </si>
-  <si>
-    <t>ROMANO EDP ATTDE 100</t>
-  </si>
-  <si>
-    <t>20125158</t>
-  </si>
-  <si>
-    <t>ROMANO EDT GRND100</t>
-  </si>
-  <si>
-    <t>20134769</t>
-  </si>
-  <si>
-    <t>POSH MEN EDT BLCK100</t>
-  </si>
-  <si>
-    <t>20120927</t>
-  </si>
-  <si>
-    <t>KAHF SUNSCREEN 30ML</t>
-  </si>
-  <si>
-    <t>20139844</t>
-  </si>
-  <si>
-    <t>BELLAGIO EDP BLUE 50</t>
-  </si>
-  <si>
-    <t>40</t>
-  </si>
-  <si>
-    <t>20139843</t>
-  </si>
-  <si>
-    <t>BELLAGIO EDP BLCK 50</t>
-  </si>
-  <si>
-    <t>20141565</t>
-  </si>
-  <si>
-    <t>XCHANGE AQUA MYTH 50</t>
-  </si>
-  <si>
-    <t>20139975</t>
-  </si>
-  <si>
-    <t>CSBLNCA EDP CHLGR 50</t>
-  </si>
-  <si>
-    <t>10026626</t>
-  </si>
-  <si>
-    <t>CASA/B COL.AQUA100ML</t>
-  </si>
-  <si>
-    <t>20094874</t>
-  </si>
-  <si>
-    <t>BELLAGIO EDT SPRT100</t>
-  </si>
-  <si>
-    <t>20137253</t>
-  </si>
-  <si>
-    <t>BRAVEN EDP COOL 100M</t>
-  </si>
-  <si>
-    <t>20140807</t>
-  </si>
-  <si>
-    <t>BRAVEN EDP AQUA 100</t>
-  </si>
-  <si>
-    <t>20134768</t>
-  </si>
-  <si>
-    <t>BRAVEN FM.OUD WOD100</t>
-  </si>
-  <si>
-    <t>20129495</t>
-  </si>
-  <si>
-    <t>MORRIS EDP WOODY 100</t>
-  </si>
-  <si>
-    <t>20129494</t>
-  </si>
-  <si>
-    <t>MORRIS EDP AQUATC100</t>
-  </si>
-  <si>
-    <t>20134765</t>
-  </si>
-  <si>
-    <t>MORRIS EDP FRESH 100</t>
-  </si>
-  <si>
-    <t>20115271</t>
-  </si>
-  <si>
-    <t>MORRIS EDP MTRO 100</t>
-  </si>
-  <si>
-    <t>20120918</t>
-  </si>
-  <si>
-    <t>MORRIS EDP CRTVE 100</t>
-  </si>
-  <si>
-    <t>20128126</t>
-  </si>
-  <si>
-    <t>VTLIS EDP MORNING100</t>
-  </si>
-  <si>
-    <t>10004664</t>
-  </si>
-  <si>
-    <t>ALEXANDER DEO HT 3.7</t>
-  </si>
-  <si>
-    <t>10003511</t>
-  </si>
-  <si>
-    <t>PIERRE DEO PUTIH 150</t>
-  </si>
-  <si>
-    <t>20092367</t>
-  </si>
-  <si>
-    <t>NIVEA MEN INVS FRS50</t>
-  </si>
-  <si>
-    <t>41</t>
-  </si>
-  <si>
-    <t>20116990</t>
-  </si>
-  <si>
-    <t>POSH DEO ACT COOL 50</t>
-  </si>
-  <si>
-    <t>20133516</t>
-  </si>
-  <si>
-    <t>KAHF DEO COOL.PWR 45</t>
-  </si>
-  <si>
-    <t>20133517</t>
-  </si>
-  <si>
-    <t>KAHF DEO EXTR.DRY 45</t>
-  </si>
-  <si>
-    <t>20137605</t>
-  </si>
-  <si>
-    <t>KAHF DEO CLN.FRSH 45</t>
-  </si>
-  <si>
-    <t>20138588</t>
-  </si>
-  <si>
-    <t>GATSBY DEO BLUE 50ML</t>
-  </si>
-  <si>
-    <t>20138589</t>
-  </si>
-  <si>
-    <t>GATSBY DEO BOLD 50ML</t>
-  </si>
-  <si>
-    <t>10036357</t>
-  </si>
-  <si>
-    <t>CASA/B DEO MEN BLU50</t>
-  </si>
-  <si>
-    <t>10036356</t>
-  </si>
-  <si>
-    <t>CASA/B DEO MEN BLC50</t>
-  </si>
-  <si>
-    <t>20070151</t>
-  </si>
-  <si>
-    <t>BELLAGIO EDP RAVE 50</t>
-  </si>
-  <si>
-    <t>20024517</t>
-  </si>
-  <si>
-    <t>AXE DEO DARK 135ML</t>
-  </si>
-  <si>
-    <t>20075923</t>
-  </si>
-  <si>
-    <t>POSH BS BL.GOLD 150</t>
-  </si>
-  <si>
-    <t>20114433</t>
-  </si>
-  <si>
-    <t>POSH MEN GRN MT 150</t>
-  </si>
-  <si>
-    <t>20075924</t>
-  </si>
-  <si>
-    <t>POSH BS COOL.BL 150</t>
-  </si>
-  <si>
-    <t>20092190</t>
-  </si>
-  <si>
-    <t>POSH RED EXTREME 150</t>
-  </si>
-  <si>
-    <t>20134793</t>
-  </si>
-  <si>
-    <t>NPOLEON EDT NERO 100</t>
-  </si>
-  <si>
-    <t>20084999</t>
-  </si>
-  <si>
-    <t>CASA/B EDT AQUA 100</t>
-  </si>
-  <si>
-    <t>20091428</t>
-  </si>
-  <si>
-    <t>CLEAR/M SHP CL.SP160</t>
-  </si>
-  <si>
-    <t>20139454</t>
-  </si>
-  <si>
-    <t>NIVEA MEN DEO DC 50</t>
-  </si>
-  <si>
-    <t>42</t>
-  </si>
-  <si>
-    <t>20120783</t>
-  </si>
-  <si>
-    <t>NIVEA MEN CK FGR 50</t>
-  </si>
-  <si>
-    <t>20088376</t>
-  </si>
-  <si>
-    <t>NVEA MEN R/ON DEEP50</t>
-  </si>
-  <si>
-    <t>20134496</t>
-  </si>
-  <si>
-    <t>20051842</t>
-  </si>
-  <si>
-    <t>NIVEA/M R/ON INVS 50</t>
-  </si>
-  <si>
-    <t>20054716</t>
-  </si>
-  <si>
-    <t>NIVEA/M R/ON COL/K50</t>
-  </si>
-  <si>
-    <t>20062306</t>
-  </si>
-  <si>
-    <t>RXONA MEN DEO ICE 45</t>
-  </si>
-  <si>
-    <t>20062309</t>
-  </si>
-  <si>
-    <t>RXNA MEN DEO ULTR 45</t>
-  </si>
-  <si>
-    <t>20062308</t>
-  </si>
-  <si>
-    <t>RXONA MEN DEO SPR 45</t>
-  </si>
-  <si>
-    <t>20062307</t>
-  </si>
-  <si>
-    <t>RXONA MEN DEO INV 50</t>
-  </si>
-  <si>
-    <t>20087201</t>
-  </si>
-  <si>
-    <t>RXNA MEN INV+A.BC 45</t>
-  </si>
-  <si>
-    <t>20111362</t>
-  </si>
-  <si>
-    <t>RXNA MEN LM COOL 45</t>
-  </si>
-  <si>
-    <t>20139354</t>
-  </si>
-  <si>
-    <t>RXONA MEN FR.STRK 40</t>
-  </si>
-  <si>
     <t>20139522</t>
   </si>
   <si>
     <t>RXONA MEN DRY DEF 40</t>
-  </si>
-  <si>
-    <t>20026865</t>
-  </si>
-  <si>
-    <t>GATSBY WAX PWR&amp;SPK75</t>
-  </si>
-  <si>
-    <t>10005133</t>
-  </si>
-  <si>
-    <t>GATSBY TREAT.NOR 125</t>
-  </si>
-  <si>
-    <t>20022917</t>
-  </si>
-  <si>
-    <t>GATSBY WGLOS H/SLD75</t>
-  </si>
-  <si>
-    <t>20053183</t>
-  </si>
-  <si>
-    <t>GTSBY STYL POMADE 75</t>
-  </si>
-  <si>
-    <t>20097521</t>
-  </si>
-  <si>
-    <t>MAGIC PWR CLASSIC 6S</t>
-  </si>
-  <si>
-    <t>43</t>
-  </si>
-  <si>
-    <t>20063363</t>
-  </si>
-  <si>
-    <t>OKAMOTO KNDM PLT 2'S</t>
-  </si>
-  <si>
-    <t>20139964</t>
-  </si>
-  <si>
-    <t>MAGIC PWR ICE BL 6'S</t>
-  </si>
-  <si>
-    <t>10008133</t>
-  </si>
-  <si>
-    <t>DUREX EXTRA3S</t>
-  </si>
-  <si>
-    <t>20078435</t>
-  </si>
-  <si>
-    <t>DUREX INVISIBLE 2'S</t>
-  </si>
-  <si>
-    <t>20035693</t>
-  </si>
-  <si>
-    <t>DUREX PERFORMA 3'S</t>
-  </si>
-  <si>
-    <t>20045107</t>
-  </si>
-  <si>
-    <t>DUREX LOVE BOX 3'S</t>
-  </si>
-  <si>
-    <t>20069205</t>
-  </si>
-  <si>
-    <t>FIESTA MAX DOT 3'S</t>
-  </si>
-  <si>
-    <t>20091579</t>
-  </si>
-  <si>
-    <t>SUTRA GERIGI 3'S</t>
-  </si>
-  <si>
-    <t>20022011</t>
-  </si>
-  <si>
-    <t>SUTRA OK 3'S</t>
-  </si>
-  <si>
-    <t>10004656</t>
-  </si>
-  <si>
-    <t>SUTRA KONDOM 3'S</t>
-  </si>
-  <si>
-    <t>20069204</t>
-  </si>
-  <si>
-    <t>SUTRA OK 12'S</t>
-  </si>
-  <si>
-    <t>10004655</t>
-  </si>
-  <si>
-    <t>SUTRA 12'S</t>
-  </si>
-  <si>
-    <t>10008992</t>
-  </si>
-  <si>
-    <t>GILLETE RAZOR VECTOR</t>
-  </si>
-  <si>
-    <t>44</t>
-  </si>
-  <si>
-    <t>PT</t>
-  </si>
-  <si>
-    <t>10009007</t>
-  </si>
-  <si>
-    <t>GILLETE CATR.VECTOR2</t>
-  </si>
-  <si>
-    <t>20086422</t>
-  </si>
-  <si>
-    <t>GILLETTE BLUE II 3+1</t>
-  </si>
-  <si>
-    <t>20139066</t>
-  </si>
-  <si>
-    <t>GLLTTE BLUE3 FLXI 3S</t>
-  </si>
-  <si>
-    <t>20135324</t>
-  </si>
-  <si>
-    <t>GLLETTE GOAL YLW 4'S</t>
-  </si>
-  <si>
-    <t>20033978</t>
-  </si>
-  <si>
-    <t>GILLETTE RAZOR BLUE3</t>
-  </si>
-  <si>
-    <t>20081456</t>
-  </si>
-  <si>
-    <t>GLLETTE BLUE3 SIMPLE</t>
-  </si>
-  <si>
-    <t>20137021</t>
-  </si>
-  <si>
-    <t>IDM PISAU CUKUR 3+1</t>
-  </si>
-  <si>
-    <t>20141365</t>
-  </si>
-  <si>
-    <t>BARBER.D 6 BL SHAVER</t>
-  </si>
-  <si>
-    <t>20014993</t>
-  </si>
-  <si>
-    <t>GILLETTE BLUE II PLS</t>
-  </si>
-  <si>
-    <t>20096659</t>
-  </si>
-  <si>
-    <t>IDM RAZOR 3MATA SLT</t>
-  </si>
-  <si>
-    <t>10000318</t>
-  </si>
-  <si>
-    <t>GLLETTE RZR GOAL YLW</t>
-  </si>
-  <si>
-    <t>20123700</t>
-  </si>
-  <si>
-    <t>GLTTE BLUE II FLEXI</t>
-  </si>
-  <si>
-    <t>20029237</t>
-  </si>
-  <si>
-    <t>IDM PISAU CUKUR 2MP</t>
-  </si>
-  <si>
-    <t>10013212</t>
-  </si>
-  <si>
-    <t>GILLETTE SMPLY VNS2S</t>
-  </si>
-  <si>
-    <t>20088267</t>
-  </si>
-  <si>
-    <t>BELLAGIO PMDE RED 80</t>
-  </si>
-  <si>
-    <t>45</t>
-  </si>
-  <si>
-    <t>20090906</t>
-  </si>
-  <si>
-    <t>BELLAGIO PMD BLCK 80</t>
-  </si>
-  <si>
-    <t>20128951</t>
-  </si>
-  <si>
-    <t>MORRIS PMD EXTR HL80</t>
-  </si>
-  <si>
-    <t>20136022</t>
-  </si>
-  <si>
-    <t>GTSBY FBR CLY MATT80</t>
-  </si>
-  <si>
-    <t>20136021</t>
-  </si>
-  <si>
-    <t>GTSBY FBR PMD GLOS80</t>
-  </si>
-  <si>
-    <t>20127064</t>
-  </si>
-  <si>
-    <t>S/R STYLING PMDE 75</t>
-  </si>
-  <si>
-    <t>20082862</t>
-  </si>
-  <si>
-    <t>GTSBY PMD PR.RISE 75</t>
-  </si>
-  <si>
-    <t>20136388</t>
-  </si>
-  <si>
-    <t>KAHF PMD SLK CLSY 70</t>
-  </si>
-  <si>
-    <t>20142118</t>
-  </si>
-  <si>
-    <t>B/D STRNG POMADE 75</t>
-  </si>
-  <si>
-    <t>20129578</t>
-  </si>
-  <si>
-    <t>GATSBY BALM PMADE 70</t>
-  </si>
-  <si>
-    <t>20129580</t>
-  </si>
-  <si>
-    <t>GATSBY BALM CLAY 70</t>
-  </si>
-  <si>
-    <t>20129581</t>
-  </si>
-  <si>
-    <t>GATSBY BALM CREAM 70</t>
-  </si>
-  <si>
-    <t>20098912</t>
-  </si>
-  <si>
-    <t>WRDH PB MCLR WTR 100</t>
-  </si>
-  <si>
-    <t>998</t>
   </si>
 </sst>
 </file>
@@ -4753,7 +4774,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F694"/>
+  <dimension ref="A1:F697"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
@@ -9838,7 +9859,7 @@
         <v>134</v>
       </c>
       <c r="E254" s="1" t="s">
-        <v>12</v>
+        <v>45</v>
       </c>
       <c r="F254" s="1" t="s">
         <v>13</v>
@@ -9858,7 +9879,7 @@
         <v>134</v>
       </c>
       <c r="E255" s="1" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="F255" s="1" t="s">
         <v>117</v>
@@ -9878,7 +9899,7 @@
         <v>134</v>
       </c>
       <c r="E256" s="1" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="F256" s="1" t="s">
         <v>13</v>
@@ -9898,7 +9919,7 @@
         <v>134</v>
       </c>
       <c r="E257" s="1" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="F257" s="1" t="s">
         <v>13</v>
@@ -9918,7 +9939,7 @@
         <v>134</v>
       </c>
       <c r="E258" s="1" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="F258" s="1" t="s">
         <v>13</v>
@@ -9938,7 +9959,7 @@
         <v>134</v>
       </c>
       <c r="E259" s="1" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="F259" s="1" t="s">
         <v>13</v>
@@ -13161,7 +13182,7 @@
         <v>4</v>
       </c>
       <c r="F420" s="1" t="s">
-        <v>117</v>
+        <v>5</v>
       </c>
     </row>
     <row r="421" spans="1:6" x14ac:dyDescent="0.25">
@@ -13181,7 +13202,7 @@
         <v>8</v>
       </c>
       <c r="F421" s="1" t="s">
-        <v>66</v>
+        <v>117</v>
       </c>
     </row>
     <row r="422" spans="1:6" x14ac:dyDescent="0.25">
@@ -13201,7 +13222,7 @@
         <v>45</v>
       </c>
       <c r="F422" s="1" t="s">
-        <v>231</v>
+        <v>66</v>
       </c>
     </row>
     <row r="423" spans="1:6" x14ac:dyDescent="0.25">
@@ -13221,7 +13242,7 @@
         <v>12</v>
       </c>
       <c r="F423" s="1" t="s">
-        <v>66</v>
+        <v>231</v>
       </c>
     </row>
     <row r="424" spans="1:6" x14ac:dyDescent="0.25">
@@ -13241,7 +13262,7 @@
         <v>16</v>
       </c>
       <c r="F424" s="1" t="s">
-        <v>162</v>
+        <v>66</v>
       </c>
     </row>
     <row r="425" spans="1:6" x14ac:dyDescent="0.25">
@@ -13281,7 +13302,7 @@
         <v>22</v>
       </c>
       <c r="F426" s="1" t="s">
-        <v>66</v>
+        <v>162</v>
       </c>
     </row>
     <row r="427" spans="1:6" x14ac:dyDescent="0.25">
@@ -13295,53 +13316,53 @@
         <v>3</v>
       </c>
       <c r="D427" s="1" t="s">
-        <v>895</v>
+        <v>880</v>
       </c>
       <c r="E427" s="1" t="s">
-        <v>4</v>
+        <v>25</v>
       </c>
       <c r="F427" s="1" t="s">
-        <v>5</v>
+        <v>66</v>
       </c>
     </row>
     <row r="428" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A428" s="1" t="s">
+        <v>895</v>
+      </c>
+      <c r="B428" s="1" t="s">
         <v>896</v>
       </c>
-      <c r="B428" s="1" t="s">
+      <c r="C428" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D428" s="1" t="s">
         <v>897</v>
       </c>
-      <c r="C428" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D428" s="1" t="s">
-        <v>895</v>
-      </c>
       <c r="E428" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F428" s="1" t="s">
-        <v>5</v>
+        <v>898</v>
       </c>
     </row>
     <row r="429" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A429" s="1" t="s">
-        <v>898</v>
+        <v>899</v>
       </c>
       <c r="B429" s="1" t="s">
-        <v>899</v>
+        <v>900</v>
       </c>
       <c r="C429" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D429" s="1" t="s">
-        <v>895</v>
+        <v>897</v>
       </c>
       <c r="E429" s="1" t="s">
-        <v>45</v>
+        <v>8</v>
       </c>
       <c r="F429" s="1" t="s">
-        <v>900</v>
+        <v>5</v>
       </c>
     </row>
     <row r="430" spans="1:6" x14ac:dyDescent="0.25">
@@ -13355,13 +13376,13 @@
         <v>3</v>
       </c>
       <c r="D430" s="1" t="s">
-        <v>895</v>
+        <v>897</v>
       </c>
       <c r="E430" s="1" t="s">
-        <v>12</v>
+        <v>45</v>
       </c>
       <c r="F430" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="431" spans="1:6" x14ac:dyDescent="0.25">
@@ -13375,190 +13396,190 @@
         <v>3</v>
       </c>
       <c r="D431" s="1" t="s">
-        <v>895</v>
+        <v>897</v>
       </c>
       <c r="E431" s="1" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="F431" s="1" t="s">
-        <v>5</v>
+        <v>905</v>
       </c>
     </row>
     <row r="432" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A432" s="1" t="s">
-        <v>905</v>
+        <v>906</v>
       </c>
       <c r="B432" s="1" t="s">
-        <v>906</v>
+        <v>907</v>
       </c>
       <c r="C432" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D432" s="1" t="s">
-        <v>895</v>
+        <v>897</v>
       </c>
       <c r="E432" s="1" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="F432" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="433" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A433" s="1" t="s">
-        <v>907</v>
+        <v>908</v>
       </c>
       <c r="B433" s="1" t="s">
-        <v>908</v>
+        <v>909</v>
       </c>
       <c r="C433" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D433" s="1" t="s">
-        <v>895</v>
+        <v>897</v>
       </c>
       <c r="E433" s="1" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="F433" s="1" t="s">
-        <v>66</v>
+        <v>5</v>
       </c>
     </row>
     <row r="434" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A434" s="1" t="s">
-        <v>909</v>
+        <v>910</v>
       </c>
       <c r="B434" s="1" t="s">
-        <v>910</v>
+        <v>911</v>
       </c>
       <c r="C434" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D434" s="1" t="s">
-        <v>895</v>
+        <v>897</v>
       </c>
       <c r="E434" s="1" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="F434" s="1" t="s">
-        <v>13</v>
+        <v>5</v>
       </c>
     </row>
     <row r="435" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A435" s="1" t="s">
-        <v>911</v>
+        <v>912</v>
       </c>
       <c r="B435" s="1" t="s">
-        <v>912</v>
+        <v>913</v>
       </c>
       <c r="C435" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D435" s="1" t="s">
-        <v>895</v>
+        <v>897</v>
       </c>
       <c r="E435" s="1" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="F435" s="1" t="s">
-        <v>5</v>
+        <v>66</v>
       </c>
     </row>
     <row r="436" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A436" s="1" t="s">
-        <v>913</v>
+        <v>914</v>
       </c>
       <c r="B436" s="1" t="s">
-        <v>914</v>
+        <v>915</v>
       </c>
       <c r="C436" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D436" s="1" t="s">
-        <v>895</v>
+        <v>897</v>
       </c>
       <c r="E436" s="1" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="F436" s="1" t="s">
-        <v>5</v>
+        <v>13</v>
       </c>
     </row>
     <row r="437" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A437" s="1" t="s">
-        <v>915</v>
+        <v>916</v>
       </c>
       <c r="B437" s="1" t="s">
-        <v>916</v>
+        <v>917</v>
       </c>
       <c r="C437" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D437" s="1" t="s">
-        <v>895</v>
+        <v>897</v>
       </c>
       <c r="E437" s="1" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="F437" s="1" t="s">
-        <v>13</v>
+        <v>5</v>
       </c>
     </row>
     <row r="438" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A438" s="1" t="s">
-        <v>917</v>
+        <v>918</v>
       </c>
       <c r="B438" s="1" t="s">
-        <v>918</v>
+        <v>919</v>
       </c>
       <c r="C438" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D438" s="1" t="s">
-        <v>895</v>
+        <v>897</v>
       </c>
       <c r="E438" s="1" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="F438" s="1" t="s">
-        <v>66</v>
+        <v>5</v>
       </c>
     </row>
     <row r="439" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A439" s="1" t="s">
-        <v>919</v>
+        <v>920</v>
       </c>
       <c r="B439" s="1" t="s">
-        <v>920</v>
+        <v>921</v>
       </c>
       <c r="C439" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D439" s="1" t="s">
-        <v>895</v>
+        <v>897</v>
       </c>
       <c r="E439" s="1" t="s">
-        <v>90</v>
+        <v>38</v>
       </c>
       <c r="F439" s="1" t="s">
-        <v>5</v>
+        <v>13</v>
       </c>
     </row>
     <row r="440" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A440" s="1" t="s">
-        <v>921</v>
+        <v>922</v>
       </c>
       <c r="B440" s="1" t="s">
-        <v>922</v>
+        <v>923</v>
       </c>
       <c r="C440" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D440" s="1" t="s">
-        <v>895</v>
+        <v>897</v>
       </c>
       <c r="E440" s="1" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="F440" s="1" t="s">
         <v>5</v>
@@ -13566,19 +13587,19 @@
     </row>
     <row r="441" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A441" s="1" t="s">
-        <v>923</v>
+        <v>924</v>
       </c>
       <c r="B441" s="1" t="s">
-        <v>924</v>
+        <v>925</v>
       </c>
       <c r="C441" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D441" s="1" t="s">
-        <v>895</v>
+        <v>897</v>
       </c>
       <c r="E441" s="1" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="F441" s="1" t="s">
         <v>5</v>
@@ -13586,19 +13607,19 @@
     </row>
     <row r="442" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A442" s="1" t="s">
-        <v>925</v>
+        <v>926</v>
       </c>
       <c r="B442" s="1" t="s">
-        <v>926</v>
+        <v>927</v>
       </c>
       <c r="C442" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D442" s="1" t="s">
-        <v>895</v>
+        <v>897</v>
       </c>
       <c r="E442" s="1" t="s">
-        <v>131</v>
+        <v>96</v>
       </c>
       <c r="F442" s="1" t="s">
         <v>5</v>
@@ -13606,19 +13627,19 @@
     </row>
     <row r="443" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A443" s="1" t="s">
-        <v>927</v>
+        <v>928</v>
       </c>
       <c r="B443" s="1" t="s">
-        <v>928</v>
+        <v>929</v>
       </c>
       <c r="C443" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D443" s="1" t="s">
-        <v>929</v>
+        <v>897</v>
       </c>
       <c r="E443" s="1" t="s">
-        <v>4</v>
+        <v>131</v>
       </c>
       <c r="F443" s="1" t="s">
         <v>5</v>
@@ -13635,10 +13656,10 @@
         <v>3</v>
       </c>
       <c r="D444" s="1" t="s">
-        <v>929</v>
+        <v>932</v>
       </c>
       <c r="E444" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F444" s="1" t="s">
         <v>5</v>
@@ -13646,19 +13667,19 @@
     </row>
     <row r="445" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A445" s="1" t="s">
+        <v>933</v>
+      </c>
+      <c r="B445" s="1" t="s">
+        <v>934</v>
+      </c>
+      <c r="C445" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D445" s="1" t="s">
         <v>932</v>
       </c>
-      <c r="B445" s="1" t="s">
-        <v>933</v>
-      </c>
-      <c r="C445" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D445" s="1" t="s">
-        <v>929</v>
-      </c>
       <c r="E445" s="1" t="s">
-        <v>45</v>
+        <v>8</v>
       </c>
       <c r="F445" s="1" t="s">
         <v>5</v>
@@ -13666,19 +13687,19 @@
     </row>
     <row r="446" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A446" s="1" t="s">
-        <v>934</v>
+        <v>935</v>
       </c>
       <c r="B446" s="1" t="s">
-        <v>935</v>
+        <v>936</v>
       </c>
       <c r="C446" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D446" s="1" t="s">
-        <v>929</v>
+        <v>932</v>
       </c>
       <c r="E446" s="1" t="s">
-        <v>12</v>
+        <v>45</v>
       </c>
       <c r="F446" s="1" t="s">
         <v>5</v>
@@ -13686,39 +13707,39 @@
     </row>
     <row r="447" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A447" s="1" t="s">
-        <v>936</v>
+        <v>937</v>
       </c>
       <c r="B447" s="1" t="s">
-        <v>937</v>
+        <v>938</v>
       </c>
       <c r="C447" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D447" s="1" t="s">
-        <v>929</v>
+        <v>932</v>
       </c>
       <c r="E447" s="1" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="F447" s="1" t="s">
-        <v>29</v>
+        <v>5</v>
       </c>
     </row>
     <row r="448" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A448" s="1" t="s">
-        <v>938</v>
+        <v>939</v>
       </c>
       <c r="B448" s="1" t="s">
-        <v>939</v>
+        <v>940</v>
       </c>
       <c r="C448" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D448" s="1" t="s">
-        <v>929</v>
+        <v>932</v>
       </c>
       <c r="E448" s="1" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="F448" s="1" t="s">
         <v>29</v>
@@ -13726,119 +13747,119 @@
     </row>
     <row r="449" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A449" s="1" t="s">
-        <v>940</v>
+        <v>941</v>
       </c>
       <c r="B449" s="1" t="s">
-        <v>941</v>
+        <v>942</v>
       </c>
       <c r="C449" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D449" s="1" t="s">
-        <v>929</v>
+        <v>932</v>
       </c>
       <c r="E449" s="1" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="F449" s="1" t="s">
-        <v>66</v>
+        <v>29</v>
       </c>
     </row>
     <row r="450" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A450" s="1" t="s">
-        <v>942</v>
+        <v>943</v>
       </c>
       <c r="B450" s="1" t="s">
-        <v>943</v>
+        <v>944</v>
       </c>
       <c r="C450" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D450" s="1" t="s">
-        <v>929</v>
+        <v>932</v>
       </c>
       <c r="E450" s="1" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="F450" s="1" t="s">
-        <v>162</v>
+        <v>66</v>
       </c>
     </row>
     <row r="451" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A451" s="1" t="s">
-        <v>944</v>
+        <v>945</v>
       </c>
       <c r="B451" s="1" t="s">
-        <v>945</v>
+        <v>946</v>
       </c>
       <c r="C451" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D451" s="1" t="s">
-        <v>929</v>
+        <v>932</v>
       </c>
       <c r="E451" s="1" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="F451" s="1" t="s">
-        <v>13</v>
+        <v>162</v>
       </c>
     </row>
     <row r="452" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A452" s="1" t="s">
-        <v>946</v>
+        <v>947</v>
       </c>
       <c r="B452" s="1" t="s">
-        <v>947</v>
+        <v>948</v>
       </c>
       <c r="C452" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D452" s="1" t="s">
-        <v>929</v>
+        <v>932</v>
       </c>
       <c r="E452" s="1" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="F452" s="1" t="s">
-        <v>5</v>
+        <v>13</v>
       </c>
     </row>
     <row r="453" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A453" s="1" t="s">
-        <v>948</v>
+        <v>949</v>
       </c>
       <c r="B453" s="1" t="s">
-        <v>949</v>
+        <v>950</v>
       </c>
       <c r="C453" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D453" s="1" t="s">
-        <v>929</v>
+        <v>932</v>
       </c>
       <c r="E453" s="1" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="F453" s="1" t="s">
-        <v>29</v>
+        <v>5</v>
       </c>
     </row>
     <row r="454" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A454" s="1" t="s">
-        <v>950</v>
+        <v>951</v>
       </c>
       <c r="B454" s="1" t="s">
-        <v>951</v>
+        <v>952</v>
       </c>
       <c r="C454" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D454" s="1" t="s">
-        <v>929</v>
+        <v>932</v>
       </c>
       <c r="E454" s="1" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="F454" s="1" t="s">
         <v>29</v>
@@ -13846,19 +13867,19 @@
     </row>
     <row r="455" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A455" s="1" t="s">
-        <v>952</v>
+        <v>953</v>
       </c>
       <c r="B455" s="1" t="s">
-        <v>953</v>
+        <v>954</v>
       </c>
       <c r="C455" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D455" s="1" t="s">
-        <v>929</v>
+        <v>932</v>
       </c>
       <c r="E455" s="1" t="s">
-        <v>90</v>
+        <v>38</v>
       </c>
       <c r="F455" s="1" t="s">
         <v>29</v>
@@ -13866,62 +13887,62 @@
     </row>
     <row r="456" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A456" s="1" t="s">
-        <v>954</v>
+        <v>955</v>
       </c>
       <c r="B456" s="1" t="s">
-        <v>955</v>
+        <v>956</v>
       </c>
       <c r="C456" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D456" s="1" t="s">
-        <v>929</v>
+        <v>932</v>
       </c>
       <c r="E456" s="1" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="F456" s="1" t="s">
-        <v>9</v>
+        <v>29</v>
       </c>
     </row>
     <row r="457" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A457" s="1" t="s">
-        <v>956</v>
+        <v>957</v>
       </c>
       <c r="B457" s="1" t="s">
-        <v>957</v>
+        <v>958</v>
       </c>
       <c r="C457" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D457" s="1" t="s">
-        <v>929</v>
+        <v>932</v>
       </c>
       <c r="E457" s="1" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="F457" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="458" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A458" s="1" t="s">
-        <v>958</v>
+        <v>959</v>
       </c>
       <c r="B458" s="1" t="s">
-        <v>959</v>
+        <v>960</v>
       </c>
       <c r="C458" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D458" s="1" t="s">
-        <v>960</v>
+        <v>932</v>
       </c>
       <c r="E458" s="1" t="s">
-        <v>4</v>
+        <v>96</v>
       </c>
       <c r="F458" s="1" t="s">
-        <v>66</v>
+        <v>5</v>
       </c>
     </row>
     <row r="459" spans="1:6" x14ac:dyDescent="0.25">
@@ -13935,10 +13956,10 @@
         <v>3</v>
       </c>
       <c r="D459" s="1" t="s">
-        <v>960</v>
+        <v>963</v>
       </c>
       <c r="E459" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F459" s="1" t="s">
         <v>66</v>
@@ -13946,19 +13967,19 @@
     </row>
     <row r="460" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A460" s="1" t="s">
+        <v>964</v>
+      </c>
+      <c r="B460" s="1" t="s">
+        <v>965</v>
+      </c>
+      <c r="C460" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D460" s="1" t="s">
         <v>963</v>
       </c>
-      <c r="B460" s="1" t="s">
-        <v>964</v>
-      </c>
-      <c r="C460" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D460" s="1" t="s">
-        <v>960</v>
-      </c>
       <c r="E460" s="1" t="s">
-        <v>45</v>
+        <v>8</v>
       </c>
       <c r="F460" s="1" t="s">
         <v>66</v>
@@ -13966,19 +13987,19 @@
     </row>
     <row r="461" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A461" s="1" t="s">
-        <v>965</v>
+        <v>966</v>
       </c>
       <c r="B461" s="1" t="s">
-        <v>966</v>
+        <v>967</v>
       </c>
       <c r="C461" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D461" s="1" t="s">
-        <v>960</v>
+        <v>963</v>
       </c>
       <c r="E461" s="1" t="s">
-        <v>12</v>
+        <v>45</v>
       </c>
       <c r="F461" s="1" t="s">
         <v>66</v>
@@ -13986,19 +14007,19 @@
     </row>
     <row r="462" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A462" s="1" t="s">
-        <v>967</v>
+        <v>968</v>
       </c>
       <c r="B462" s="1" t="s">
-        <v>968</v>
+        <v>969</v>
       </c>
       <c r="C462" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D462" s="1" t="s">
-        <v>960</v>
+        <v>963</v>
       </c>
       <c r="E462" s="1" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="F462" s="1" t="s">
         <v>66</v>
@@ -14006,19 +14027,19 @@
     </row>
     <row r="463" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A463" s="1" t="s">
-        <v>969</v>
+        <v>970</v>
       </c>
       <c r="B463" s="1" t="s">
-        <v>970</v>
+        <v>971</v>
       </c>
       <c r="C463" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D463" s="1" t="s">
-        <v>960</v>
+        <v>963</v>
       </c>
       <c r="E463" s="1" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="F463" s="1" t="s">
         <v>66</v>
@@ -14026,39 +14047,39 @@
     </row>
     <row r="464" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A464" s="1" t="s">
-        <v>971</v>
+        <v>972</v>
       </c>
       <c r="B464" s="1" t="s">
-        <v>972</v>
+        <v>973</v>
       </c>
       <c r="C464" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D464" s="1" t="s">
-        <v>960</v>
+        <v>963</v>
       </c>
       <c r="E464" s="1" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="F464" s="1" t="s">
-        <v>117</v>
+        <v>66</v>
       </c>
     </row>
     <row r="465" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A465" s="1" t="s">
-        <v>973</v>
+        <v>974</v>
       </c>
       <c r="B465" s="1" t="s">
-        <v>974</v>
+        <v>975</v>
       </c>
       <c r="C465" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D465" s="1" t="s">
-        <v>960</v>
+        <v>963</v>
       </c>
       <c r="E465" s="1" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="F465" s="1" t="s">
         <v>117</v>
@@ -14066,39 +14087,39 @@
     </row>
     <row r="466" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A466" s="1" t="s">
-        <v>975</v>
+        <v>976</v>
       </c>
       <c r="B466" s="1" t="s">
-        <v>976</v>
+        <v>977</v>
       </c>
       <c r="C466" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D466" s="1" t="s">
-        <v>960</v>
+        <v>963</v>
       </c>
       <c r="E466" s="1" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="F466" s="1" t="s">
-        <v>13</v>
+        <v>117</v>
       </c>
     </row>
     <row r="467" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A467" s="1" t="s">
-        <v>977</v>
+        <v>978</v>
       </c>
       <c r="B467" s="1" t="s">
-        <v>978</v>
+        <v>979</v>
       </c>
       <c r="C467" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D467" s="1" t="s">
-        <v>960</v>
+        <v>963</v>
       </c>
       <c r="E467" s="1" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="F467" s="1" t="s">
         <v>13</v>
@@ -14106,39 +14127,39 @@
     </row>
     <row r="468" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A468" s="1" t="s">
-        <v>979</v>
+        <v>980</v>
       </c>
       <c r="B468" s="1" t="s">
-        <v>980</v>
+        <v>981</v>
       </c>
       <c r="C468" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D468" s="1" t="s">
-        <v>960</v>
+        <v>963</v>
       </c>
       <c r="E468" s="1" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="F468" s="1" t="s">
-        <v>66</v>
+        <v>13</v>
       </c>
     </row>
     <row r="469" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A469" s="1" t="s">
-        <v>981</v>
+        <v>982</v>
       </c>
       <c r="B469" s="1" t="s">
-        <v>982</v>
+        <v>983</v>
       </c>
       <c r="C469" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D469" s="1" t="s">
-        <v>960</v>
+        <v>963</v>
       </c>
       <c r="E469" s="1" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="F469" s="1" t="s">
         <v>66</v>
@@ -14146,39 +14167,39 @@
     </row>
     <row r="470" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A470" s="1" t="s">
-        <v>983</v>
+        <v>984</v>
       </c>
       <c r="B470" s="1" t="s">
-        <v>984</v>
+        <v>985</v>
       </c>
       <c r="C470" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D470" s="1" t="s">
-        <v>960</v>
+        <v>963</v>
       </c>
       <c r="E470" s="1" t="s">
-        <v>90</v>
+        <v>38</v>
       </c>
       <c r="F470" s="1" t="s">
-        <v>5</v>
+        <v>66</v>
       </c>
     </row>
     <row r="471" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A471" s="1" t="s">
-        <v>985</v>
+        <v>986</v>
       </c>
       <c r="B471" s="1" t="s">
-        <v>986</v>
+        <v>987</v>
       </c>
       <c r="C471" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D471" s="1" t="s">
-        <v>960</v>
+        <v>963</v>
       </c>
       <c r="E471" s="1" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="F471" s="1" t="s">
         <v>5</v>
@@ -14186,19 +14207,19 @@
     </row>
     <row r="472" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A472" s="1" t="s">
-        <v>987</v>
+        <v>988</v>
       </c>
       <c r="B472" s="1" t="s">
-        <v>988</v>
+        <v>989</v>
       </c>
       <c r="C472" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D472" s="1" t="s">
-        <v>960</v>
+        <v>963</v>
       </c>
       <c r="E472" s="1" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="F472" s="1" t="s">
         <v>5</v>
@@ -14206,22 +14227,22 @@
     </row>
     <row r="473" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A473" s="1" t="s">
-        <v>989</v>
+        <v>990</v>
       </c>
       <c r="B473" s="1" t="s">
-        <v>990</v>
+        <v>991</v>
       </c>
       <c r="C473" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D473" s="1" t="s">
-        <v>991</v>
+        <v>963</v>
       </c>
       <c r="E473" s="1" t="s">
-        <v>4</v>
+        <v>96</v>
       </c>
       <c r="F473" s="1" t="s">
-        <v>66</v>
+        <v>5</v>
       </c>
     </row>
     <row r="474" spans="1:6" x14ac:dyDescent="0.25">
@@ -14235,33 +14256,33 @@
         <v>3</v>
       </c>
       <c r="D474" s="1" t="s">
-        <v>991</v>
+        <v>994</v>
       </c>
       <c r="E474" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F474" s="1" t="s">
-        <v>5</v>
+        <v>66</v>
       </c>
     </row>
     <row r="475" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A475" s="1" t="s">
+        <v>995</v>
+      </c>
+      <c r="B475" s="1" t="s">
+        <v>996</v>
+      </c>
+      <c r="C475" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D475" s="1" t="s">
         <v>994</v>
       </c>
-      <c r="B475" s="1" t="s">
-        <v>995</v>
-      </c>
-      <c r="C475" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D475" s="1" t="s">
-        <v>991</v>
-      </c>
       <c r="E475" s="1" t="s">
-        <v>45</v>
+        <v>8</v>
       </c>
       <c r="F475" s="1" t="s">
-        <v>996</v>
+        <v>5</v>
       </c>
     </row>
     <row r="476" spans="1:6" x14ac:dyDescent="0.25">
@@ -14275,13 +14296,13 @@
         <v>3</v>
       </c>
       <c r="D476" s="1" t="s">
-        <v>991</v>
+        <v>994</v>
       </c>
       <c r="E476" s="1" t="s">
-        <v>12</v>
+        <v>45</v>
       </c>
       <c r="F476" s="1" t="s">
-        <v>996</v>
+        <v>898</v>
       </c>
     </row>
     <row r="477" spans="1:6" x14ac:dyDescent="0.25">
@@ -14295,13 +14316,13 @@
         <v>3</v>
       </c>
       <c r="D477" s="1" t="s">
-        <v>991</v>
+        <v>994</v>
       </c>
       <c r="E477" s="1" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="F477" s="1" t="s">
-        <v>5</v>
+        <v>898</v>
       </c>
     </row>
     <row r="478" spans="1:6" x14ac:dyDescent="0.25">
@@ -14315,10 +14336,10 @@
         <v>3</v>
       </c>
       <c r="D478" s="1" t="s">
-        <v>991</v>
+        <v>994</v>
       </c>
       <c r="E478" s="1" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="F478" s="1" t="s">
         <v>5</v>
@@ -14335,10 +14356,10 @@
         <v>3</v>
       </c>
       <c r="D479" s="1" t="s">
-        <v>991</v>
+        <v>994</v>
       </c>
       <c r="E479" s="1" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="F479" s="1" t="s">
         <v>5</v>
@@ -14355,10 +14376,10 @@
         <v>3</v>
       </c>
       <c r="D480" s="1" t="s">
-        <v>991</v>
+        <v>994</v>
       </c>
       <c r="E480" s="1" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="F480" s="1" t="s">
         <v>5</v>
@@ -14375,10 +14396,10 @@
         <v>3</v>
       </c>
       <c r="D481" s="1" t="s">
-        <v>991</v>
+        <v>994</v>
       </c>
       <c r="E481" s="1" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="F481" s="1" t="s">
         <v>5</v>
@@ -14395,10 +14416,10 @@
         <v>3</v>
       </c>
       <c r="D482" s="1" t="s">
-        <v>991</v>
+        <v>994</v>
       </c>
       <c r="E482" s="1" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="F482" s="1" t="s">
         <v>5</v>
@@ -14415,10 +14436,10 @@
         <v>3</v>
       </c>
       <c r="D483" s="1" t="s">
-        <v>991</v>
+        <v>994</v>
       </c>
       <c r="E483" s="1" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="F483" s="1" t="s">
         <v>5</v>
@@ -14435,10 +14456,10 @@
         <v>3</v>
       </c>
       <c r="D484" s="1" t="s">
-        <v>991</v>
+        <v>994</v>
       </c>
       <c r="E484" s="1" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="F484" s="1" t="s">
         <v>5</v>
@@ -14455,10 +14476,10 @@
         <v>3</v>
       </c>
       <c r="D485" s="1" t="s">
-        <v>991</v>
+        <v>994</v>
       </c>
       <c r="E485" s="1" t="s">
-        <v>90</v>
+        <v>38</v>
       </c>
       <c r="F485" s="1" t="s">
         <v>5</v>
@@ -14475,10 +14496,10 @@
         <v>3</v>
       </c>
       <c r="D486" s="1" t="s">
-        <v>991</v>
+        <v>994</v>
       </c>
       <c r="E486" s="1" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="F486" s="1" t="s">
         <v>5</v>
@@ -14495,10 +14516,10 @@
         <v>3</v>
       </c>
       <c r="D487" s="1" t="s">
-        <v>991</v>
+        <v>994</v>
       </c>
       <c r="E487" s="1" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="F487" s="1" t="s">
         <v>5</v>
@@ -14515,10 +14536,10 @@
         <v>3</v>
       </c>
       <c r="D488" s="1" t="s">
-        <v>991</v>
+        <v>994</v>
       </c>
       <c r="E488" s="1" t="s">
-        <v>131</v>
+        <v>96</v>
       </c>
       <c r="F488" s="1" t="s">
         <v>5</v>
@@ -14535,33 +14556,33 @@
         <v>3</v>
       </c>
       <c r="D489" s="1" t="s">
-        <v>1025</v>
+        <v>994</v>
       </c>
       <c r="E489" s="1" t="s">
-        <v>4</v>
+        <v>131</v>
       </c>
       <c r="F489" s="1" t="s">
-        <v>13</v>
+        <v>5</v>
       </c>
     </row>
     <row r="490" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A490" s="1" t="s">
+        <v>1025</v>
+      </c>
+      <c r="B490" s="1" t="s">
         <v>1026</v>
       </c>
-      <c r="B490" s="1" t="s">
+      <c r="C490" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D490" s="1" t="s">
         <v>1027</v>
       </c>
-      <c r="C490" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D490" s="1" t="s">
-        <v>1025</v>
-      </c>
       <c r="E490" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F490" s="1" t="s">
-        <v>5</v>
+        <v>13</v>
       </c>
     </row>
     <row r="491" spans="1:6" x14ac:dyDescent="0.25">
@@ -14575,10 +14596,10 @@
         <v>3</v>
       </c>
       <c r="D491" s="1" t="s">
-        <v>1025</v>
+        <v>1027</v>
       </c>
       <c r="E491" s="1" t="s">
-        <v>45</v>
+        <v>8</v>
       </c>
       <c r="F491" s="1" t="s">
         <v>5</v>
@@ -14595,10 +14616,10 @@
         <v>3</v>
       </c>
       <c r="D492" s="1" t="s">
-        <v>1025</v>
+        <v>1027</v>
       </c>
       <c r="E492" s="1" t="s">
-        <v>12</v>
+        <v>45</v>
       </c>
       <c r="F492" s="1" t="s">
         <v>5</v>
@@ -14615,13 +14636,13 @@
         <v>3</v>
       </c>
       <c r="D493" s="1" t="s">
-        <v>1025</v>
+        <v>1027</v>
       </c>
       <c r="E493" s="1" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="F493" s="1" t="s">
-        <v>117</v>
+        <v>5</v>
       </c>
     </row>
     <row r="494" spans="1:6" x14ac:dyDescent="0.25">
@@ -14635,10 +14656,10 @@
         <v>3</v>
       </c>
       <c r="D494" s="1" t="s">
-        <v>1025</v>
+        <v>1027</v>
       </c>
       <c r="E494" s="1" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="F494" s="1" t="s">
         <v>117</v>
@@ -14655,13 +14676,13 @@
         <v>3</v>
       </c>
       <c r="D495" s="1" t="s">
-        <v>1025</v>
+        <v>1027</v>
       </c>
       <c r="E495" s="1" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="F495" s="1" t="s">
-        <v>5</v>
+        <v>117</v>
       </c>
     </row>
     <row r="496" spans="1:6" x14ac:dyDescent="0.25">
@@ -14675,10 +14696,10 @@
         <v>3</v>
       </c>
       <c r="D496" s="1" t="s">
-        <v>1025</v>
+        <v>1027</v>
       </c>
       <c r="E496" s="1" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="F496" s="1" t="s">
         <v>5</v>
@@ -14695,10 +14716,10 @@
         <v>3</v>
       </c>
       <c r="D497" s="1" t="s">
-        <v>1025</v>
+        <v>1027</v>
       </c>
       <c r="E497" s="1" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="F497" s="1" t="s">
         <v>5</v>
@@ -14715,33 +14736,33 @@
         <v>3</v>
       </c>
       <c r="D498" s="1" t="s">
-        <v>1025</v>
+        <v>1027</v>
       </c>
       <c r="E498" s="1" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="F498" s="1" t="s">
-        <v>1044</v>
+        <v>5</v>
       </c>
     </row>
     <row r="499" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A499" s="1" t="s">
+        <v>1044</v>
+      </c>
+      <c r="B499" s="1" t="s">
         <v>1045</v>
       </c>
-      <c r="B499" s="1" t="s">
+      <c r="C499" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D499" s="1" t="s">
+        <v>1027</v>
+      </c>
+      <c r="E499" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="F499" s="1" t="s">
         <v>1046</v>
-      </c>
-      <c r="C499" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D499" s="1" t="s">
-        <v>1025</v>
-      </c>
-      <c r="E499" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="F499" s="1" t="s">
-        <v>5</v>
       </c>
     </row>
     <row r="500" spans="1:6" x14ac:dyDescent="0.25">
@@ -14755,10 +14776,10 @@
         <v>3</v>
       </c>
       <c r="D500" s="1" t="s">
-        <v>1025</v>
+        <v>1027</v>
       </c>
       <c r="E500" s="1" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="F500" s="1" t="s">
         <v>5</v>
@@ -14775,10 +14796,10 @@
         <v>3</v>
       </c>
       <c r="D501" s="1" t="s">
-        <v>1025</v>
+        <v>1027</v>
       </c>
       <c r="E501" s="1" t="s">
-        <v>90</v>
+        <v>38</v>
       </c>
       <c r="F501" s="1" t="s">
         <v>5</v>
@@ -14795,10 +14816,10 @@
         <v>3</v>
       </c>
       <c r="D502" s="1" t="s">
-        <v>1025</v>
+        <v>1027</v>
       </c>
       <c r="E502" s="1" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="F502" s="1" t="s">
         <v>5</v>
@@ -14815,10 +14836,10 @@
         <v>3</v>
       </c>
       <c r="D503" s="1" t="s">
-        <v>1025</v>
+        <v>1027</v>
       </c>
       <c r="E503" s="1" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="F503" s="1" t="s">
         <v>5</v>
@@ -14835,10 +14856,10 @@
         <v>3</v>
       </c>
       <c r="D504" s="1" t="s">
-        <v>1025</v>
+        <v>1027</v>
       </c>
       <c r="E504" s="1" t="s">
-        <v>131</v>
+        <v>96</v>
       </c>
       <c r="F504" s="1" t="s">
         <v>5</v>
@@ -14855,13 +14876,13 @@
         <v>3</v>
       </c>
       <c r="D505" s="1" t="s">
-        <v>1025</v>
+        <v>1027</v>
       </c>
       <c r="E505" s="1" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="F505" s="1" t="s">
-        <v>13</v>
+        <v>5</v>
       </c>
     </row>
     <row r="506" spans="1:6" x14ac:dyDescent="0.25">
@@ -14875,10 +14896,10 @@
         <v>3</v>
       </c>
       <c r="D506" s="1" t="s">
-        <v>1025</v>
+        <v>1027</v>
       </c>
       <c r="E506" s="1" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="F506" s="1" t="s">
         <v>13</v>
@@ -14895,30 +14916,30 @@
         <v>3</v>
       </c>
       <c r="D507" s="1" t="s">
-        <v>1063</v>
+        <v>1027</v>
       </c>
       <c r="E507" s="1" t="s">
-        <v>4</v>
+        <v>137</v>
       </c>
       <c r="F507" s="1" t="s">
-        <v>5</v>
+        <v>13</v>
       </c>
     </row>
     <row r="508" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A508" s="1" t="s">
+        <v>1063</v>
+      </c>
+      <c r="B508" s="1" t="s">
         <v>1064</v>
       </c>
-      <c r="B508" s="1" t="s">
+      <c r="C508" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D508" s="1" t="s">
         <v>1065</v>
       </c>
-      <c r="C508" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D508" s="1" t="s">
-        <v>1063</v>
-      </c>
       <c r="E508" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F508" s="1" t="s">
         <v>5</v>
@@ -14935,10 +14956,10 @@
         <v>3</v>
       </c>
       <c r="D509" s="1" t="s">
-        <v>1063</v>
+        <v>1065</v>
       </c>
       <c r="E509" s="1" t="s">
-        <v>45</v>
+        <v>8</v>
       </c>
       <c r="F509" s="1" t="s">
         <v>5</v>
@@ -14955,10 +14976,10 @@
         <v>3</v>
       </c>
       <c r="D510" s="1" t="s">
-        <v>1063</v>
+        <v>1065</v>
       </c>
       <c r="E510" s="1" t="s">
-        <v>12</v>
+        <v>45</v>
       </c>
       <c r="F510" s="1" t="s">
         <v>5</v>
@@ -14975,10 +14996,10 @@
         <v>3</v>
       </c>
       <c r="D511" s="1" t="s">
-        <v>1063</v>
+        <v>1065</v>
       </c>
       <c r="E511" s="1" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="F511" s="1" t="s">
         <v>5</v>
@@ -14995,10 +15016,10 @@
         <v>3</v>
       </c>
       <c r="D512" s="1" t="s">
-        <v>1063</v>
+        <v>1065</v>
       </c>
       <c r="E512" s="1" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="F512" s="1" t="s">
         <v>5</v>
@@ -15015,10 +15036,10 @@
         <v>3</v>
       </c>
       <c r="D513" s="1" t="s">
-        <v>1063</v>
+        <v>1065</v>
       </c>
       <c r="E513" s="1" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="F513" s="1" t="s">
         <v>5</v>
@@ -15035,10 +15056,10 @@
         <v>3</v>
       </c>
       <c r="D514" s="1" t="s">
-        <v>1063</v>
+        <v>1065</v>
       </c>
       <c r="E514" s="1" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="F514" s="1" t="s">
         <v>5</v>
@@ -15055,10 +15076,10 @@
         <v>3</v>
       </c>
       <c r="D515" s="1" t="s">
-        <v>1063</v>
+        <v>1065</v>
       </c>
       <c r="E515" s="1" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="F515" s="1" t="s">
         <v>5</v>
@@ -15075,10 +15096,10 @@
         <v>3</v>
       </c>
       <c r="D516" s="1" t="s">
-        <v>1063</v>
+        <v>1065</v>
       </c>
       <c r="E516" s="1" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="F516" s="1" t="s">
         <v>5</v>
@@ -15095,10 +15116,10 @@
         <v>3</v>
       </c>
       <c r="D517" s="1" t="s">
-        <v>1063</v>
+        <v>1065</v>
       </c>
       <c r="E517" s="1" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="F517" s="1" t="s">
         <v>5</v>
@@ -15115,10 +15136,10 @@
         <v>3</v>
       </c>
       <c r="D518" s="1" t="s">
-        <v>1063</v>
+        <v>1065</v>
       </c>
       <c r="E518" s="1" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="F518" s="1" t="s">
         <v>5</v>
@@ -15135,10 +15156,10 @@
         <v>3</v>
       </c>
       <c r="D519" s="1" t="s">
-        <v>1063</v>
+        <v>1065</v>
       </c>
       <c r="E519" s="1" t="s">
-        <v>90</v>
+        <v>38</v>
       </c>
       <c r="F519" s="1" t="s">
         <v>5</v>
@@ -15155,10 +15176,10 @@
         <v>3</v>
       </c>
       <c r="D520" s="1" t="s">
-        <v>1063</v>
+        <v>1065</v>
       </c>
       <c r="E520" s="1" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="F520" s="1" t="s">
         <v>5</v>
@@ -15175,10 +15196,10 @@
         <v>3</v>
       </c>
       <c r="D521" s="1" t="s">
-        <v>1063</v>
+        <v>1065</v>
       </c>
       <c r="E521" s="1" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="F521" s="1" t="s">
         <v>5</v>
@@ -15195,33 +15216,33 @@
         <v>3</v>
       </c>
       <c r="D522" s="1" t="s">
-        <v>1094</v>
+        <v>1065</v>
       </c>
       <c r="E522" s="1" t="s">
-        <v>4</v>
+        <v>96</v>
       </c>
       <c r="F522" s="1" t="s">
-        <v>66</v>
+        <v>5</v>
       </c>
     </row>
     <row r="523" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A523" s="1" t="s">
+        <v>1094</v>
+      </c>
+      <c r="B523" s="1" t="s">
         <v>1095</v>
       </c>
-      <c r="B523" s="1" t="s">
+      <c r="C523" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D523" s="1" t="s">
         <v>1096</v>
-      </c>
-      <c r="C523" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D523" s="1" t="s">
-        <v>1094</v>
       </c>
       <c r="E523" s="1" t="s">
         <v>4</v>
       </c>
       <c r="F523" s="1" t="s">
-        <v>5</v>
+        <v>66</v>
       </c>
     </row>
     <row r="524" spans="1:6" x14ac:dyDescent="0.25">
@@ -15235,7 +15256,7 @@
         <v>3</v>
       </c>
       <c r="D524" s="1" t="s">
-        <v>1094</v>
+        <v>1096</v>
       </c>
       <c r="E524" s="1" t="s">
         <v>4</v>
@@ -15255,13 +15276,13 @@
         <v>3</v>
       </c>
       <c r="D525" s="1" t="s">
-        <v>1094</v>
+        <v>1096</v>
       </c>
       <c r="E525" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F525" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="526" spans="1:6" x14ac:dyDescent="0.25">
@@ -15275,13 +15296,13 @@
         <v>3</v>
       </c>
       <c r="D526" s="1" t="s">
-        <v>1094</v>
+        <v>1096</v>
       </c>
       <c r="E526" s="1" t="s">
         <v>8</v>
       </c>
       <c r="F526" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="527" spans="1:6" x14ac:dyDescent="0.25">
@@ -15295,7 +15316,7 @@
         <v>3</v>
       </c>
       <c r="D527" s="1" t="s">
-        <v>1094</v>
+        <v>1096</v>
       </c>
       <c r="E527" s="1" t="s">
         <v>8</v>
@@ -15315,10 +15336,10 @@
         <v>3</v>
       </c>
       <c r="D528" s="1" t="s">
-        <v>1094</v>
+        <v>1096</v>
       </c>
       <c r="E528" s="1" t="s">
-        <v>45</v>
+        <v>8</v>
       </c>
       <c r="F528" s="1" t="s">
         <v>5</v>
@@ -15335,7 +15356,7 @@
         <v>3</v>
       </c>
       <c r="D529" s="1" t="s">
-        <v>1094</v>
+        <v>1096</v>
       </c>
       <c r="E529" s="1" t="s">
         <v>45</v>
@@ -15355,7 +15376,7 @@
         <v>3</v>
       </c>
       <c r="D530" s="1" t="s">
-        <v>1094</v>
+        <v>1096</v>
       </c>
       <c r="E530" s="1" t="s">
         <v>45</v>
@@ -15375,10 +15396,10 @@
         <v>3</v>
       </c>
       <c r="D531" s="1" t="s">
-        <v>1094</v>
+        <v>1096</v>
       </c>
       <c r="E531" s="1" t="s">
-        <v>12</v>
+        <v>45</v>
       </c>
       <c r="F531" s="1" t="s">
         <v>5</v>
@@ -15395,7 +15416,7 @@
         <v>3</v>
       </c>
       <c r="D532" s="1" t="s">
-        <v>1094</v>
+        <v>1096</v>
       </c>
       <c r="E532" s="1" t="s">
         <v>12</v>
@@ -15415,7 +15436,7 @@
         <v>3</v>
       </c>
       <c r="D533" s="1" t="s">
-        <v>1094</v>
+        <v>1096</v>
       </c>
       <c r="E533" s="1" t="s">
         <v>12</v>
@@ -15435,10 +15456,10 @@
         <v>3</v>
       </c>
       <c r="D534" s="1" t="s">
-        <v>1094</v>
+        <v>1096</v>
       </c>
       <c r="E534" s="1" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="F534" s="1" t="s">
         <v>5</v>
@@ -15455,7 +15476,7 @@
         <v>3</v>
       </c>
       <c r="D535" s="1" t="s">
-        <v>1094</v>
+        <v>1096</v>
       </c>
       <c r="E535" s="1" t="s">
         <v>16</v>
@@ -15475,7 +15496,7 @@
         <v>3</v>
       </c>
       <c r="D536" s="1" t="s">
-        <v>1094</v>
+        <v>1096</v>
       </c>
       <c r="E536" s="1" t="s">
         <v>16</v>
@@ -15495,13 +15516,13 @@
         <v>3</v>
       </c>
       <c r="D537" s="1" t="s">
-        <v>1094</v>
+        <v>1096</v>
       </c>
       <c r="E537" s="1" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="F537" s="1" t="s">
-        <v>66</v>
+        <v>5</v>
       </c>
     </row>
     <row r="538" spans="1:6" x14ac:dyDescent="0.25">
@@ -15515,13 +15536,13 @@
         <v>3</v>
       </c>
       <c r="D538" s="1" t="s">
-        <v>1094</v>
+        <v>1096</v>
       </c>
       <c r="E538" s="1" t="s">
         <v>19</v>
       </c>
       <c r="F538" s="1" t="s">
-        <v>5</v>
+        <v>66</v>
       </c>
     </row>
     <row r="539" spans="1:6" x14ac:dyDescent="0.25">
@@ -15535,7 +15556,7 @@
         <v>3</v>
       </c>
       <c r="D539" s="1" t="s">
-        <v>1094</v>
+        <v>1096</v>
       </c>
       <c r="E539" s="1" t="s">
         <v>19</v>
@@ -15555,13 +15576,13 @@
         <v>3</v>
       </c>
       <c r="D540" s="1" t="s">
-        <v>1094</v>
+        <v>1096</v>
       </c>
       <c r="E540" s="1" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="F540" s="1" t="s">
-        <v>66</v>
+        <v>5</v>
       </c>
     </row>
     <row r="541" spans="1:6" x14ac:dyDescent="0.25">
@@ -15575,7 +15596,7 @@
         <v>3</v>
       </c>
       <c r="D541" s="1" t="s">
-        <v>1094</v>
+        <v>1096</v>
       </c>
       <c r="E541" s="1" t="s">
         <v>22</v>
@@ -15595,13 +15616,13 @@
         <v>3</v>
       </c>
       <c r="D542" s="1" t="s">
-        <v>1094</v>
+        <v>1096</v>
       </c>
       <c r="E542" s="1" t="s">
         <v>22</v>
       </c>
       <c r="F542" s="1" t="s">
-        <v>5</v>
+        <v>66</v>
       </c>
     </row>
     <row r="543" spans="1:6" x14ac:dyDescent="0.25">
@@ -15615,13 +15636,13 @@
         <v>3</v>
       </c>
       <c r="D543" s="1" t="s">
-        <v>1094</v>
+        <v>1096</v>
       </c>
       <c r="E543" s="1" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="F543" s="1" t="s">
-        <v>66</v>
+        <v>5</v>
       </c>
     </row>
     <row r="544" spans="1:6" x14ac:dyDescent="0.25">
@@ -15635,13 +15656,13 @@
         <v>3</v>
       </c>
       <c r="D544" s="1" t="s">
-        <v>1094</v>
+        <v>1096</v>
       </c>
       <c r="E544" s="1" t="s">
         <v>25</v>
       </c>
       <c r="F544" s="1" t="s">
-        <v>13</v>
+        <v>66</v>
       </c>
     </row>
     <row r="545" spans="1:6" x14ac:dyDescent="0.25">
@@ -15655,13 +15676,13 @@
         <v>3</v>
       </c>
       <c r="D545" s="1" t="s">
-        <v>1094</v>
+        <v>1096</v>
       </c>
       <c r="E545" s="1" t="s">
         <v>25</v>
       </c>
       <c r="F545" s="1" t="s">
-        <v>5</v>
+        <v>13</v>
       </c>
     </row>
     <row r="546" spans="1:6" x14ac:dyDescent="0.25">
@@ -15675,13 +15696,13 @@
         <v>3</v>
       </c>
       <c r="D546" s="1" t="s">
-        <v>1094</v>
+        <v>1096</v>
       </c>
       <c r="E546" s="1" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="F546" s="1" t="s">
-        <v>13</v>
+        <v>5</v>
       </c>
     </row>
     <row r="547" spans="1:6" x14ac:dyDescent="0.25">
@@ -15695,13 +15716,13 @@
         <v>3</v>
       </c>
       <c r="D547" s="1" t="s">
-        <v>1094</v>
+        <v>1096</v>
       </c>
       <c r="E547" s="1" t="s">
         <v>28</v>
       </c>
       <c r="F547" s="1" t="s">
-        <v>5</v>
+        <v>13</v>
       </c>
     </row>
     <row r="548" spans="1:6" x14ac:dyDescent="0.25">
@@ -15715,13 +15736,13 @@
         <v>3</v>
       </c>
       <c r="D548" s="1" t="s">
-        <v>1094</v>
+        <v>1096</v>
       </c>
       <c r="E548" s="1" t="s">
         <v>28</v>
       </c>
       <c r="F548" s="1" t="s">
-        <v>117</v>
+        <v>5</v>
       </c>
     </row>
     <row r="549" spans="1:6" x14ac:dyDescent="0.25">
@@ -15735,13 +15756,13 @@
         <v>3</v>
       </c>
       <c r="D549" s="1" t="s">
-        <v>1094</v>
+        <v>1096</v>
       </c>
       <c r="E549" s="1" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="F549" s="1" t="s">
-        <v>9</v>
+        <v>117</v>
       </c>
     </row>
     <row r="550" spans="1:6" x14ac:dyDescent="0.25">
@@ -15755,13 +15776,13 @@
         <v>3</v>
       </c>
       <c r="D550" s="1" t="s">
-        <v>1094</v>
+        <v>1096</v>
       </c>
       <c r="E550" s="1" t="s">
         <v>32</v>
       </c>
       <c r="F550" s="1" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
     </row>
     <row r="551" spans="1:6" x14ac:dyDescent="0.25">
@@ -15775,13 +15796,13 @@
         <v>3</v>
       </c>
       <c r="D551" s="1" t="s">
-        <v>1094</v>
+        <v>1096</v>
       </c>
       <c r="E551" s="1" t="s">
         <v>32</v>
       </c>
       <c r="F551" s="1" t="s">
-        <v>117</v>
+        <v>13</v>
       </c>
     </row>
     <row r="552" spans="1:6" x14ac:dyDescent="0.25">
@@ -15795,13 +15816,13 @@
         <v>3</v>
       </c>
       <c r="D552" s="1" t="s">
-        <v>1094</v>
+        <v>1096</v>
       </c>
       <c r="E552" s="1" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="F552" s="1" t="s">
-        <v>5</v>
+        <v>117</v>
       </c>
     </row>
     <row r="553" spans="1:6" x14ac:dyDescent="0.25">
@@ -15815,7 +15836,7 @@
         <v>3</v>
       </c>
       <c r="D553" s="1" t="s">
-        <v>1094</v>
+        <v>1096</v>
       </c>
       <c r="E553" s="1" t="s">
         <v>35</v>
@@ -15835,13 +15856,13 @@
         <v>3</v>
       </c>
       <c r="D554" s="1" t="s">
-        <v>1094</v>
+        <v>1096</v>
       </c>
       <c r="E554" s="1" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="F554" s="1" t="s">
-        <v>66</v>
+        <v>5</v>
       </c>
     </row>
     <row r="555" spans="1:6" x14ac:dyDescent="0.25">
@@ -15855,13 +15876,13 @@
         <v>3</v>
       </c>
       <c r="D555" s="1" t="s">
-        <v>1094</v>
+        <v>1096</v>
       </c>
       <c r="E555" s="1" t="s">
-        <v>90</v>
+        <v>38</v>
       </c>
       <c r="F555" s="1" t="s">
-        <v>5</v>
+        <v>66</v>
       </c>
     </row>
     <row r="556" spans="1:6" x14ac:dyDescent="0.25">
@@ -15875,10 +15896,10 @@
         <v>3</v>
       </c>
       <c r="D556" s="1" t="s">
-        <v>1094</v>
+        <v>1096</v>
       </c>
       <c r="E556" s="1" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="F556" s="1" t="s">
         <v>5</v>
@@ -15895,10 +15916,10 @@
         <v>3</v>
       </c>
       <c r="D557" s="1" t="s">
-        <v>1094</v>
+        <v>1096</v>
       </c>
       <c r="E557" s="1" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="F557" s="1" t="s">
         <v>5</v>
@@ -15915,10 +15936,10 @@
         <v>3</v>
       </c>
       <c r="D558" s="1" t="s">
-        <v>1167</v>
+        <v>1096</v>
       </c>
       <c r="E558" s="1" t="s">
-        <v>4</v>
+        <v>96</v>
       </c>
       <c r="F558" s="1" t="s">
         <v>5</v>
@@ -15926,22 +15947,22 @@
     </row>
     <row r="559" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A559" s="1" t="s">
+        <v>1167</v>
+      </c>
+      <c r="B559" s="1" t="s">
         <v>1168</v>
       </c>
-      <c r="B559" s="1" t="s">
+      <c r="C559" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D559" s="1" t="s">
         <v>1169</v>
       </c>
-      <c r="C559" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D559" s="1" t="s">
-        <v>1167</v>
-      </c>
       <c r="E559" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F559" s="1" t="s">
-        <v>66</v>
+        <v>5</v>
       </c>
     </row>
     <row r="560" spans="1:6" x14ac:dyDescent="0.25">
@@ -15955,13 +15976,13 @@
         <v>3</v>
       </c>
       <c r="D560" s="1" t="s">
-        <v>1167</v>
+        <v>1169</v>
       </c>
       <c r="E560" s="1" t="s">
-        <v>45</v>
+        <v>8</v>
       </c>
       <c r="F560" s="1" t="s">
-        <v>5</v>
+        <v>66</v>
       </c>
     </row>
     <row r="561" spans="1:6" x14ac:dyDescent="0.25">
@@ -15975,10 +15996,10 @@
         <v>3</v>
       </c>
       <c r="D561" s="1" t="s">
-        <v>1167</v>
+        <v>1169</v>
       </c>
       <c r="E561" s="1" t="s">
-        <v>12</v>
+        <v>45</v>
       </c>
       <c r="F561" s="1" t="s">
         <v>5</v>
@@ -15995,10 +16016,10 @@
         <v>3</v>
       </c>
       <c r="D562" s="1" t="s">
-        <v>1167</v>
+        <v>1169</v>
       </c>
       <c r="E562" s="1" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="F562" s="1" t="s">
         <v>5</v>
@@ -16015,13 +16036,13 @@
         <v>3</v>
       </c>
       <c r="D563" s="1" t="s">
-        <v>1167</v>
+        <v>1169</v>
       </c>
       <c r="E563" s="1" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="F563" s="1" t="s">
-        <v>13</v>
+        <v>5</v>
       </c>
     </row>
     <row r="564" spans="1:6" x14ac:dyDescent="0.25">
@@ -16035,13 +16056,13 @@
         <v>3</v>
       </c>
       <c r="D564" s="1" t="s">
-        <v>1167</v>
+        <v>1169</v>
       </c>
       <c r="E564" s="1" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="F564" s="1" t="s">
-        <v>13</v>
+        <v>5</v>
       </c>
     </row>
     <row r="565" spans="1:6" x14ac:dyDescent="0.25">
@@ -16055,13 +16076,13 @@
         <v>3</v>
       </c>
       <c r="D565" s="1" t="s">
-        <v>1167</v>
+        <v>1169</v>
       </c>
       <c r="E565" s="1" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="F565" s="1" t="s">
-        <v>5</v>
+        <v>13</v>
       </c>
     </row>
     <row r="566" spans="1:6" x14ac:dyDescent="0.25">
@@ -16075,13 +16096,13 @@
         <v>3</v>
       </c>
       <c r="D566" s="1" t="s">
-        <v>1167</v>
+        <v>1169</v>
       </c>
       <c r="E566" s="1" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="F566" s="1" t="s">
-        <v>66</v>
+        <v>5</v>
       </c>
     </row>
     <row r="567" spans="1:6" x14ac:dyDescent="0.25">
@@ -16095,10 +16116,10 @@
         <v>3</v>
       </c>
       <c r="D567" s="1" t="s">
-        <v>1167</v>
+        <v>1169</v>
       </c>
       <c r="E567" s="1" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="F567" s="1" t="s">
         <v>66</v>
@@ -16115,13 +16136,13 @@
         <v>3</v>
       </c>
       <c r="D568" s="1" t="s">
-        <v>1167</v>
+        <v>1169</v>
       </c>
       <c r="E568" s="1" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="F568" s="1" t="s">
-        <v>5</v>
+        <v>66</v>
       </c>
     </row>
     <row r="569" spans="1:6" x14ac:dyDescent="0.25">
@@ -16135,10 +16156,10 @@
         <v>3</v>
       </c>
       <c r="D569" s="1" t="s">
-        <v>1167</v>
+        <v>1169</v>
       </c>
       <c r="E569" s="1" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="F569" s="1" t="s">
         <v>5</v>
@@ -16155,10 +16176,10 @@
         <v>3</v>
       </c>
       <c r="D570" s="1" t="s">
-        <v>1167</v>
+        <v>1169</v>
       </c>
       <c r="E570" s="1" t="s">
-        <v>90</v>
+        <v>38</v>
       </c>
       <c r="F570" s="1" t="s">
         <v>5</v>
@@ -16175,13 +16196,13 @@
         <v>3</v>
       </c>
       <c r="D571" s="1" t="s">
-        <v>1167</v>
+        <v>1169</v>
       </c>
       <c r="E571" s="1" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="F571" s="1" t="s">
-        <v>66</v>
+        <v>5</v>
       </c>
     </row>
     <row r="572" spans="1:6" x14ac:dyDescent="0.25">
@@ -16195,10 +16216,10 @@
         <v>3</v>
       </c>
       <c r="D572" s="1" t="s">
-        <v>1196</v>
+        <v>1169</v>
       </c>
       <c r="E572" s="1" t="s">
-        <v>4</v>
+        <v>93</v>
       </c>
       <c r="F572" s="1" t="s">
         <v>66</v>
@@ -16206,19 +16227,19 @@
     </row>
     <row r="573" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A573" s="1" t="s">
+        <v>1196</v>
+      </c>
+      <c r="B573" s="1" t="s">
         <v>1197</v>
       </c>
-      <c r="B573" s="1" t="s">
+      <c r="C573" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D573" s="1" t="s">
         <v>1198</v>
       </c>
-      <c r="C573" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D573" s="1" t="s">
-        <v>1196</v>
-      </c>
       <c r="E573" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F573" s="1" t="s">
         <v>66</v>
@@ -16235,13 +16256,13 @@
         <v>3</v>
       </c>
       <c r="D574" s="1" t="s">
-        <v>1196</v>
+        <v>1198</v>
       </c>
       <c r="E574" s="1" t="s">
-        <v>45</v>
+        <v>8</v>
       </c>
       <c r="F574" s="1" t="s">
-        <v>5</v>
+        <v>66</v>
       </c>
     </row>
     <row r="575" spans="1:6" x14ac:dyDescent="0.25">
@@ -16255,13 +16276,13 @@
         <v>3</v>
       </c>
       <c r="D575" s="1" t="s">
-        <v>1196</v>
+        <v>1198</v>
       </c>
       <c r="E575" s="1" t="s">
-        <v>12</v>
+        <v>45</v>
       </c>
       <c r="F575" s="1" t="s">
-        <v>66</v>
+        <v>5</v>
       </c>
     </row>
     <row r="576" spans="1:6" x14ac:dyDescent="0.25">
@@ -16275,10 +16296,10 @@
         <v>3</v>
       </c>
       <c r="D576" s="1" t="s">
-        <v>1196</v>
+        <v>1198</v>
       </c>
       <c r="E576" s="1" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="F576" s="1" t="s">
         <v>66</v>
@@ -16295,10 +16316,10 @@
         <v>3</v>
       </c>
       <c r="D577" s="1" t="s">
-        <v>1196</v>
+        <v>1198</v>
       </c>
       <c r="E577" s="1" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="F577" s="1" t="s">
         <v>66</v>
@@ -16315,13 +16336,13 @@
         <v>3</v>
       </c>
       <c r="D578" s="1" t="s">
-        <v>1196</v>
+        <v>1198</v>
       </c>
       <c r="E578" s="1" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="F578" s="1" t="s">
-        <v>5</v>
+        <v>66</v>
       </c>
     </row>
     <row r="579" spans="1:6" x14ac:dyDescent="0.25">
@@ -16335,10 +16356,10 @@
         <v>3</v>
       </c>
       <c r="D579" s="1" t="s">
-        <v>1196</v>
+        <v>1198</v>
       </c>
       <c r="E579" s="1" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="F579" s="1" t="s">
         <v>5</v>
@@ -16355,10 +16376,10 @@
         <v>3</v>
       </c>
       <c r="D580" s="1" t="s">
-        <v>1196</v>
+        <v>1198</v>
       </c>
       <c r="E580" s="1" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="F580" s="1" t="s">
         <v>5</v>
@@ -16375,10 +16396,10 @@
         <v>3</v>
       </c>
       <c r="D581" s="1" t="s">
-        <v>1196</v>
+        <v>1198</v>
       </c>
       <c r="E581" s="1" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="F581" s="1" t="s">
         <v>5</v>
@@ -16395,10 +16416,10 @@
         <v>3</v>
       </c>
       <c r="D582" s="1" t="s">
-        <v>1196</v>
+        <v>1198</v>
       </c>
       <c r="E582" s="1" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="F582" s="1" t="s">
         <v>5</v>
@@ -16415,10 +16436,10 @@
         <v>3</v>
       </c>
       <c r="D583" s="1" t="s">
-        <v>1196</v>
+        <v>1198</v>
       </c>
       <c r="E583" s="1" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="F583" s="1" t="s">
         <v>5</v>
@@ -16435,10 +16456,10 @@
         <v>3</v>
       </c>
       <c r="D584" s="1" t="s">
-        <v>1196</v>
+        <v>1198</v>
       </c>
       <c r="E584" s="1" t="s">
-        <v>90</v>
+        <v>38</v>
       </c>
       <c r="F584" s="1" t="s">
         <v>5</v>
@@ -16455,10 +16476,10 @@
         <v>3</v>
       </c>
       <c r="D585" s="1" t="s">
-        <v>1196</v>
+        <v>1198</v>
       </c>
       <c r="E585" s="1" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="F585" s="1" t="s">
         <v>5</v>
@@ -16475,10 +16496,10 @@
         <v>3</v>
       </c>
       <c r="D586" s="1" t="s">
-        <v>1225</v>
+        <v>1198</v>
       </c>
       <c r="E586" s="1" t="s">
-        <v>4</v>
+        <v>93</v>
       </c>
       <c r="F586" s="1" t="s">
         <v>5</v>
@@ -16486,22 +16507,22 @@
     </row>
     <row r="587" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A587" s="1" t="s">
+        <v>1225</v>
+      </c>
+      <c r="B587" s="1" t="s">
         <v>1226</v>
       </c>
-      <c r="B587" s="1" t="s">
+      <c r="C587" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D587" s="1" t="s">
         <v>1227</v>
       </c>
-      <c r="C587" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D587" s="1" t="s">
-        <v>1225</v>
-      </c>
       <c r="E587" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F587" s="1" t="s">
-        <v>66</v>
+        <v>5</v>
       </c>
     </row>
     <row r="588" spans="1:6" x14ac:dyDescent="0.25">
@@ -16515,13 +16536,13 @@
         <v>3</v>
       </c>
       <c r="D588" s="1" t="s">
-        <v>1225</v>
+        <v>1227</v>
       </c>
       <c r="E588" s="1" t="s">
-        <v>45</v>
+        <v>8</v>
       </c>
       <c r="F588" s="1" t="s">
-        <v>5</v>
+        <v>66</v>
       </c>
     </row>
     <row r="589" spans="1:6" x14ac:dyDescent="0.25">
@@ -16535,10 +16556,10 @@
         <v>3</v>
       </c>
       <c r="D589" s="1" t="s">
-        <v>1225</v>
+        <v>1227</v>
       </c>
       <c r="E589" s="1" t="s">
-        <v>12</v>
+        <v>45</v>
       </c>
       <c r="F589" s="1" t="s">
         <v>5</v>
@@ -16555,33 +16576,33 @@
         <v>3</v>
       </c>
       <c r="D590" s="1" t="s">
-        <v>1225</v>
+        <v>1227</v>
       </c>
       <c r="E590" s="1" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="F590" s="1" t="s">
-        <v>1234</v>
+        <v>5</v>
       </c>
     </row>
     <row r="591" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A591" s="1" t="s">
+        <v>1234</v>
+      </c>
+      <c r="B591" s="1" t="s">
         <v>1235</v>
       </c>
-      <c r="B591" s="1" t="s">
+      <c r="C591" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D591" s="1" t="s">
+        <v>1227</v>
+      </c>
+      <c r="E591" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="F591" s="1" t="s">
         <v>1236</v>
-      </c>
-      <c r="C591" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D591" s="1" t="s">
-        <v>1225</v>
-      </c>
-      <c r="E591" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="F591" s="1" t="s">
-        <v>1234</v>
       </c>
     </row>
     <row r="592" spans="1:6" x14ac:dyDescent="0.25">
@@ -16595,13 +16616,13 @@
         <v>3</v>
       </c>
       <c r="D592" s="1" t="s">
-        <v>1225</v>
+        <v>1227</v>
       </c>
       <c r="E592" s="1" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="F592" s="1" t="s">
-        <v>5</v>
+        <v>1236</v>
       </c>
     </row>
     <row r="593" spans="1:6" x14ac:dyDescent="0.25">
@@ -16615,10 +16636,10 @@
         <v>3</v>
       </c>
       <c r="D593" s="1" t="s">
-        <v>1225</v>
+        <v>1227</v>
       </c>
       <c r="E593" s="1" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="F593" s="1" t="s">
         <v>5</v>
@@ -16635,10 +16656,10 @@
         <v>3</v>
       </c>
       <c r="D594" s="1" t="s">
-        <v>1225</v>
+        <v>1227</v>
       </c>
       <c r="E594" s="1" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="F594" s="1" t="s">
         <v>5</v>
@@ -16655,10 +16676,10 @@
         <v>3</v>
       </c>
       <c r="D595" s="1" t="s">
-        <v>1225</v>
+        <v>1227</v>
       </c>
       <c r="E595" s="1" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="F595" s="1" t="s">
         <v>5</v>
@@ -16675,13 +16696,13 @@
         <v>3</v>
       </c>
       <c r="D596" s="1" t="s">
-        <v>1225</v>
+        <v>1227</v>
       </c>
       <c r="E596" s="1" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="F596" s="1" t="s">
-        <v>29</v>
+        <v>5</v>
       </c>
     </row>
     <row r="597" spans="1:6" x14ac:dyDescent="0.25">
@@ -16695,13 +16716,13 @@
         <v>3</v>
       </c>
       <c r="D597" s="1" t="s">
-        <v>1225</v>
+        <v>1227</v>
       </c>
       <c r="E597" s="1" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="F597" s="1" t="s">
-        <v>5</v>
+        <v>29</v>
       </c>
     </row>
     <row r="598" spans="1:6" x14ac:dyDescent="0.25">
@@ -16715,10 +16736,10 @@
         <v>3</v>
       </c>
       <c r="D598" s="1" t="s">
-        <v>1225</v>
+        <v>1227</v>
       </c>
       <c r="E598" s="1" t="s">
-        <v>90</v>
+        <v>38</v>
       </c>
       <c r="F598" s="1" t="s">
         <v>5</v>
@@ -16735,10 +16756,10 @@
         <v>3</v>
       </c>
       <c r="D599" s="1" t="s">
-        <v>1225</v>
+        <v>1227</v>
       </c>
       <c r="E599" s="1" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="F599" s="1" t="s">
         <v>5</v>
@@ -16755,10 +16776,10 @@
         <v>3</v>
       </c>
       <c r="D600" s="1" t="s">
-        <v>1225</v>
+        <v>1227</v>
       </c>
       <c r="E600" s="1" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="F600" s="1" t="s">
         <v>5</v>
@@ -16775,30 +16796,30 @@
         <v>3</v>
       </c>
       <c r="D601" s="1" t="s">
-        <v>1257</v>
+        <v>1227</v>
       </c>
       <c r="E601" s="1" t="s">
-        <v>4</v>
+        <v>96</v>
       </c>
       <c r="F601" s="1" t="s">
-        <v>29</v>
+        <v>5</v>
       </c>
     </row>
     <row r="602" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A602" s="1" t="s">
+        <v>1257</v>
+      </c>
+      <c r="B602" s="1" t="s">
         <v>1258</v>
       </c>
-      <c r="B602" s="1" t="s">
+      <c r="C602" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D602" s="1" t="s">
         <v>1259</v>
       </c>
-      <c r="C602" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D602" s="1" t="s">
-        <v>1257</v>
-      </c>
       <c r="E602" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F602" s="1" t="s">
         <v>29</v>
@@ -16815,10 +16836,10 @@
         <v>3</v>
       </c>
       <c r="D603" s="1" t="s">
-        <v>1257</v>
+        <v>1259</v>
       </c>
       <c r="E603" s="1" t="s">
-        <v>45</v>
+        <v>8</v>
       </c>
       <c r="F603" s="1" t="s">
         <v>29</v>
@@ -16835,13 +16856,13 @@
         <v>3</v>
       </c>
       <c r="D604" s="1" t="s">
-        <v>1257</v>
+        <v>1259</v>
       </c>
       <c r="E604" s="1" t="s">
-        <v>12</v>
+        <v>45</v>
       </c>
       <c r="F604" s="1" t="s">
-        <v>117</v>
+        <v>29</v>
       </c>
     </row>
     <row r="605" spans="1:6" x14ac:dyDescent="0.25">
@@ -16855,13 +16876,13 @@
         <v>3</v>
       </c>
       <c r="D605" s="1" t="s">
-        <v>1257</v>
+        <v>1259</v>
       </c>
       <c r="E605" s="1" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="F605" s="1" t="s">
-        <v>5</v>
+        <v>117</v>
       </c>
     </row>
     <row r="606" spans="1:6" x14ac:dyDescent="0.25">
@@ -16875,10 +16896,10 @@
         <v>3</v>
       </c>
       <c r="D606" s="1" t="s">
-        <v>1257</v>
+        <v>1259</v>
       </c>
       <c r="E606" s="1" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="F606" s="1" t="s">
         <v>5</v>
@@ -16895,10 +16916,10 @@
         <v>3</v>
       </c>
       <c r="D607" s="1" t="s">
-        <v>1257</v>
+        <v>1259</v>
       </c>
       <c r="E607" s="1" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="F607" s="1" t="s">
         <v>5</v>
@@ -16915,10 +16936,10 @@
         <v>3</v>
       </c>
       <c r="D608" s="1" t="s">
-        <v>1257</v>
+        <v>1259</v>
       </c>
       <c r="E608" s="1" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="F608" s="1" t="s">
         <v>5</v>
@@ -16935,10 +16956,10 @@
         <v>3</v>
       </c>
       <c r="D609" s="1" t="s">
-        <v>1257</v>
+        <v>1259</v>
       </c>
       <c r="E609" s="1" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="F609" s="1" t="s">
         <v>5</v>
@@ -16955,10 +16976,10 @@
         <v>3</v>
       </c>
       <c r="D610" s="1" t="s">
-        <v>1257</v>
+        <v>1259</v>
       </c>
       <c r="E610" s="1" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="F610" s="1" t="s">
         <v>5</v>
@@ -16975,10 +16996,10 @@
         <v>3</v>
       </c>
       <c r="D611" s="1" t="s">
-        <v>1257</v>
+        <v>1259</v>
       </c>
       <c r="E611" s="1" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="F611" s="1" t="s">
         <v>5</v>
@@ -16995,10 +17016,10 @@
         <v>3</v>
       </c>
       <c r="D612" s="1" t="s">
-        <v>1257</v>
+        <v>1259</v>
       </c>
       <c r="E612" s="1" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="F612" s="1" t="s">
         <v>5</v>
@@ -17015,10 +17036,10 @@
         <v>3</v>
       </c>
       <c r="D613" s="1" t="s">
-        <v>1257</v>
+        <v>1259</v>
       </c>
       <c r="E613" s="1" t="s">
-        <v>90</v>
+        <v>38</v>
       </c>
       <c r="F613" s="1" t="s">
         <v>5</v>
@@ -17035,10 +17056,10 @@
         <v>3</v>
       </c>
       <c r="D614" s="1" t="s">
-        <v>1257</v>
+        <v>1259</v>
       </c>
       <c r="E614" s="1" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="F614" s="1" t="s">
         <v>5</v>
@@ -17055,13 +17076,13 @@
         <v>3</v>
       </c>
       <c r="D615" s="1" t="s">
-        <v>1257</v>
+        <v>1259</v>
       </c>
       <c r="E615" s="1" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="F615" s="1" t="s">
-        <v>29</v>
+        <v>5</v>
       </c>
     </row>
     <row r="616" spans="1:6" x14ac:dyDescent="0.25">
@@ -17075,13 +17096,13 @@
         <v>3</v>
       </c>
       <c r="D616" s="1" t="s">
-        <v>1257</v>
+        <v>1259</v>
       </c>
       <c r="E616" s="1" t="s">
-        <v>131</v>
+        <v>96</v>
       </c>
       <c r="F616" s="1" t="s">
-        <v>5</v>
+        <v>29</v>
       </c>
     </row>
     <row r="617" spans="1:6" x14ac:dyDescent="0.25">
@@ -17095,10 +17116,10 @@
         <v>3</v>
       </c>
       <c r="D617" s="1" t="s">
-        <v>1257</v>
+        <v>1259</v>
       </c>
       <c r="E617" s="1" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="F617" s="1" t="s">
         <v>5</v>
@@ -17115,33 +17136,33 @@
         <v>3</v>
       </c>
       <c r="D618" s="1" t="s">
-        <v>1292</v>
+        <v>1259</v>
       </c>
       <c r="E618" s="1" t="s">
-        <v>4</v>
+        <v>134</v>
       </c>
       <c r="F618" s="1" t="s">
-        <v>66</v>
+        <v>5</v>
       </c>
     </row>
     <row r="619" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A619" s="1" t="s">
+        <v>1292</v>
+      </c>
+      <c r="B619" s="1" t="s">
         <v>1293</v>
       </c>
-      <c r="B619" s="1" t="s">
+      <c r="C619" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D619" s="1" t="s">
         <v>1294</v>
       </c>
-      <c r="C619" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D619" s="1" t="s">
-        <v>1292</v>
-      </c>
       <c r="E619" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F619" s="1" t="s">
-        <v>29</v>
+        <v>66</v>
       </c>
     </row>
     <row r="620" spans="1:6" x14ac:dyDescent="0.25">
@@ -17155,13 +17176,13 @@
         <v>3</v>
       </c>
       <c r="D620" s="1" t="s">
-        <v>1292</v>
+        <v>1294</v>
       </c>
       <c r="E620" s="1" t="s">
-        <v>45</v>
+        <v>8</v>
       </c>
       <c r="F620" s="1" t="s">
-        <v>5</v>
+        <v>29</v>
       </c>
     </row>
     <row r="621" spans="1:6" x14ac:dyDescent="0.25">
@@ -17175,10 +17196,10 @@
         <v>3</v>
       </c>
       <c r="D621" s="1" t="s">
-        <v>1292</v>
+        <v>1294</v>
       </c>
       <c r="E621" s="1" t="s">
-        <v>12</v>
+        <v>45</v>
       </c>
       <c r="F621" s="1" t="s">
         <v>5</v>
@@ -17195,10 +17216,10 @@
         <v>3</v>
       </c>
       <c r="D622" s="1" t="s">
-        <v>1292</v>
+        <v>1294</v>
       </c>
       <c r="E622" s="1" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="F622" s="1" t="s">
         <v>5</v>
@@ -17215,13 +17236,13 @@
         <v>3</v>
       </c>
       <c r="D623" s="1" t="s">
-        <v>1292</v>
+        <v>1294</v>
       </c>
       <c r="E623" s="1" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="F623" s="1" t="s">
-        <v>29</v>
+        <v>5</v>
       </c>
     </row>
     <row r="624" spans="1:6" x14ac:dyDescent="0.25">
@@ -17235,10 +17256,10 @@
         <v>3</v>
       </c>
       <c r="D624" s="1" t="s">
-        <v>1292</v>
+        <v>1294</v>
       </c>
       <c r="E624" s="1" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="F624" s="1" t="s">
         <v>29</v>
@@ -17255,13 +17276,13 @@
         <v>3</v>
       </c>
       <c r="D625" s="1" t="s">
-        <v>1292</v>
+        <v>1294</v>
       </c>
       <c r="E625" s="1" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="F625" s="1" t="s">
-        <v>5</v>
+        <v>29</v>
       </c>
     </row>
     <row r="626" spans="1:6" x14ac:dyDescent="0.25">
@@ -17275,10 +17296,10 @@
         <v>3</v>
       </c>
       <c r="D626" s="1" t="s">
-        <v>1292</v>
+        <v>1294</v>
       </c>
       <c r="E626" s="1" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="F626" s="1" t="s">
         <v>5</v>
@@ -17295,13 +17316,13 @@
         <v>3</v>
       </c>
       <c r="D627" s="1" t="s">
-        <v>1292</v>
+        <v>1294</v>
       </c>
       <c r="E627" s="1" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="F627" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="628" spans="1:6" x14ac:dyDescent="0.25">
@@ -17315,13 +17336,13 @@
         <v>3</v>
       </c>
       <c r="D628" s="1" t="s">
-        <v>1292</v>
+        <v>1294</v>
       </c>
       <c r="E628" s="1" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="F628" s="1" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
     </row>
     <row r="629" spans="1:6" x14ac:dyDescent="0.25">
@@ -17335,13 +17356,13 @@
         <v>3</v>
       </c>
       <c r="D629" s="1" t="s">
-        <v>1292</v>
+        <v>1294</v>
       </c>
       <c r="E629" s="1" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="F629" s="1" t="s">
-        <v>29</v>
+        <v>13</v>
       </c>
     </row>
     <row r="630" spans="1:6" x14ac:dyDescent="0.25">
@@ -17355,10 +17376,10 @@
         <v>3</v>
       </c>
       <c r="D630" s="1" t="s">
-        <v>1292</v>
+        <v>1294</v>
       </c>
       <c r="E630" s="1" t="s">
-        <v>90</v>
+        <v>38</v>
       </c>
       <c r="F630" s="1" t="s">
         <v>29</v>
@@ -17375,10 +17396,10 @@
         <v>3</v>
       </c>
       <c r="D631" s="1" t="s">
-        <v>1292</v>
+        <v>1294</v>
       </c>
       <c r="E631" s="1" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="F631" s="1" t="s">
         <v>29</v>
@@ -17395,10 +17416,10 @@
         <v>3</v>
       </c>
       <c r="D632" s="1" t="s">
-        <v>1292</v>
+        <v>1294</v>
       </c>
       <c r="E632" s="1" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="F632" s="1" t="s">
         <v>29</v>
@@ -17415,13 +17436,13 @@
         <v>3</v>
       </c>
       <c r="D633" s="1" t="s">
-        <v>1292</v>
+        <v>1294</v>
       </c>
       <c r="E633" s="1" t="s">
-        <v>131</v>
+        <v>96</v>
       </c>
       <c r="F633" s="1" t="s">
-        <v>5</v>
+        <v>29</v>
       </c>
     </row>
     <row r="634" spans="1:6" x14ac:dyDescent="0.25">
@@ -17435,13 +17456,13 @@
         <v>3</v>
       </c>
       <c r="D634" s="1" t="s">
-        <v>1292</v>
+        <v>1294</v>
       </c>
       <c r="E634" s="1" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="F634" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="635" spans="1:6" x14ac:dyDescent="0.25">
@@ -17455,13 +17476,13 @@
         <v>3</v>
       </c>
       <c r="D635" s="1" t="s">
-        <v>1292</v>
+        <v>1294</v>
       </c>
       <c r="E635" s="1" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="F635" s="1" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
     </row>
     <row r="636" spans="1:6" x14ac:dyDescent="0.25">
@@ -17475,70 +17496,70 @@
         <v>3</v>
       </c>
       <c r="D636" s="1" t="s">
-        <v>1329</v>
+        <v>1294</v>
       </c>
       <c r="E636" s="1" t="s">
-        <v>4</v>
+        <v>137</v>
       </c>
       <c r="F636" s="1" t="s">
-        <v>29</v>
+        <v>13</v>
       </c>
     </row>
     <row r="637" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A637" s="1" t="s">
+        <v>1329</v>
+      </c>
+      <c r="B637" s="1" t="s">
         <v>1330</v>
       </c>
-      <c r="B637" s="1" t="s">
+      <c r="C637" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D637" s="1" t="s">
         <v>1331</v>
       </c>
-      <c r="C637" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D637" s="1" t="s">
-        <v>1329</v>
-      </c>
       <c r="E637" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F637" s="1" t="s">
-        <v>5</v>
+        <v>1332</v>
       </c>
     </row>
     <row r="638" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A638" s="1" t="s">
-        <v>1332</v>
+        <v>1333</v>
       </c>
       <c r="B638" s="1" t="s">
-        <v>1333</v>
+        <v>1334</v>
       </c>
       <c r="C638" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D638" s="1" t="s">
-        <v>1329</v>
+        <v>1331</v>
       </c>
       <c r="E638" s="1" t="s">
-        <v>45</v>
+        <v>8</v>
       </c>
       <c r="F638" s="1" t="s">
-        <v>5</v>
+        <v>29</v>
       </c>
     </row>
     <row r="639" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A639" s="1" t="s">
-        <v>1334</v>
+        <v>1335</v>
       </c>
       <c r="B639" s="1" t="s">
-        <v>1333</v>
+        <v>1336</v>
       </c>
       <c r="C639" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D639" s="1" t="s">
-        <v>1329</v>
+        <v>1331</v>
       </c>
       <c r="E639" s="1" t="s">
-        <v>12</v>
+        <v>45</v>
       </c>
       <c r="F639" s="1" t="s">
         <v>5</v>
@@ -17546,27 +17567,27 @@
     </row>
     <row r="640" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A640" s="1" t="s">
-        <v>1335</v>
+        <v>1337</v>
       </c>
       <c r="B640" s="1" t="s">
-        <v>1336</v>
+        <v>1338</v>
       </c>
       <c r="C640" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D640" s="1" t="s">
-        <v>1329</v>
+        <v>1331</v>
       </c>
       <c r="E640" s="1" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="F640" s="1" t="s">
-        <v>66</v>
+        <v>5</v>
       </c>
     </row>
     <row r="641" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A641" s="1" t="s">
-        <v>1337</v>
+        <v>1339</v>
       </c>
       <c r="B641" s="1" t="s">
         <v>1338</v>
@@ -17575,70 +17596,70 @@
         <v>3</v>
       </c>
       <c r="D641" s="1" t="s">
-        <v>1329</v>
+        <v>1331</v>
       </c>
       <c r="E641" s="1" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="F641" s="1" t="s">
-        <v>66</v>
+        <v>5</v>
       </c>
     </row>
     <row r="642" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A642" s="1" t="s">
-        <v>1339</v>
+        <v>1340</v>
       </c>
       <c r="B642" s="1" t="s">
-        <v>1340</v>
+        <v>1341</v>
       </c>
       <c r="C642" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D642" s="1" t="s">
-        <v>1329</v>
+        <v>1331</v>
       </c>
       <c r="E642" s="1" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="F642" s="1" t="s">
-        <v>13</v>
+        <v>66</v>
       </c>
     </row>
     <row r="643" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A643" s="1" t="s">
-        <v>1341</v>
+        <v>1342</v>
       </c>
       <c r="B643" s="1" t="s">
-        <v>1342</v>
+        <v>1343</v>
       </c>
       <c r="C643" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D643" s="1" t="s">
-        <v>1329</v>
+        <v>1331</v>
       </c>
       <c r="E643" s="1" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="F643" s="1" t="s">
-        <v>13</v>
+        <v>66</v>
       </c>
     </row>
     <row r="644" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A644" s="1" t="s">
-        <v>1343</v>
+        <v>1344</v>
       </c>
       <c r="B644" s="1" t="s">
-        <v>1344</v>
+        <v>1345</v>
       </c>
       <c r="C644" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D644" s="1" t="s">
-        <v>1329</v>
+        <v>1331</v>
       </c>
       <c r="E644" s="1" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="F644" s="1" t="s">
         <v>13</v>
@@ -17646,19 +17667,19 @@
     </row>
     <row r="645" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A645" s="1" t="s">
-        <v>1345</v>
+        <v>1346</v>
       </c>
       <c r="B645" s="1" t="s">
-        <v>1346</v>
+        <v>1347</v>
       </c>
       <c r="C645" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D645" s="1" t="s">
-        <v>1329</v>
+        <v>1331</v>
       </c>
       <c r="E645" s="1" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="F645" s="1" t="s">
         <v>13</v>
@@ -17666,19 +17687,19 @@
     </row>
     <row r="646" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A646" s="1" t="s">
-        <v>1347</v>
+        <v>1348</v>
       </c>
       <c r="B646" s="1" t="s">
-        <v>1348</v>
+        <v>1349</v>
       </c>
       <c r="C646" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D646" s="1" t="s">
-        <v>1329</v>
+        <v>1331</v>
       </c>
       <c r="E646" s="1" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="F646" s="1" t="s">
         <v>13</v>
@@ -17686,19 +17707,19 @@
     </row>
     <row r="647" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A647" s="1" t="s">
-        <v>1349</v>
+        <v>1350</v>
       </c>
       <c r="B647" s="1" t="s">
-        <v>1350</v>
+        <v>1351</v>
       </c>
       <c r="C647" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D647" s="1" t="s">
-        <v>1329</v>
+        <v>1331</v>
       </c>
       <c r="E647" s="1" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="F647" s="1" t="s">
         <v>13</v>
@@ -17706,79 +17727,79 @@
     </row>
     <row r="648" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A648" s="1" t="s">
-        <v>1351</v>
+        <v>1352</v>
       </c>
       <c r="B648" s="1" t="s">
-        <v>1352</v>
+        <v>1353</v>
       </c>
       <c r="C648" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D648" s="1" t="s">
-        <v>1329</v>
+        <v>1331</v>
       </c>
       <c r="E648" s="1" t="s">
-        <v>90</v>
+        <v>38</v>
       </c>
       <c r="F648" s="1" t="s">
-        <v>117</v>
+        <v>13</v>
       </c>
     </row>
     <row r="649" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A649" s="1" t="s">
-        <v>1353</v>
+        <v>1354</v>
       </c>
       <c r="B649" s="1" t="s">
-        <v>1354</v>
+        <v>1355</v>
       </c>
       <c r="C649" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D649" s="1" t="s">
-        <v>1329</v>
+        <v>1331</v>
       </c>
       <c r="E649" s="1" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="F649" s="1" t="s">
-        <v>117</v>
+        <v>13</v>
       </c>
     </row>
     <row r="650" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A650" s="1" t="s">
-        <v>1355</v>
+        <v>1356</v>
       </c>
       <c r="B650" s="1" t="s">
-        <v>1356</v>
+        <v>1357</v>
       </c>
       <c r="C650" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D650" s="1" t="s">
-        <v>1329</v>
+        <v>1331</v>
       </c>
       <c r="E650" s="1" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="F650" s="1" t="s">
-        <v>9</v>
+        <v>117</v>
       </c>
     </row>
     <row r="651" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A651" s="1" t="s">
-        <v>1357</v>
+        <v>1358</v>
       </c>
       <c r="B651" s="1" t="s">
-        <v>1358</v>
+        <v>1359</v>
       </c>
       <c r="C651" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D651" s="1" t="s">
-        <v>1329</v>
+        <v>1331</v>
       </c>
       <c r="E651" s="1" t="s">
-        <v>131</v>
+        <v>96</v>
       </c>
       <c r="F651" s="1" t="s">
         <v>9</v>
@@ -17786,19 +17807,19 @@
     </row>
     <row r="652" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A652" s="1" t="s">
-        <v>1359</v>
+        <v>1360</v>
       </c>
       <c r="B652" s="1" t="s">
-        <v>1360</v>
+        <v>1361</v>
       </c>
       <c r="C652" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D652" s="1" t="s">
-        <v>1329</v>
+        <v>1331</v>
       </c>
       <c r="E652" s="1" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="F652" s="1" t="s">
         <v>9</v>
@@ -17806,19 +17827,19 @@
     </row>
     <row r="653" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A653" s="1" t="s">
-        <v>1361</v>
+        <v>1362</v>
       </c>
       <c r="B653" s="1" t="s">
-        <v>1362</v>
+        <v>1363</v>
       </c>
       <c r="C653" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D653" s="1" t="s">
-        <v>1329</v>
+        <v>1331</v>
       </c>
       <c r="E653" s="1" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="F653" s="1" t="s">
         <v>9</v>
@@ -17826,19 +17847,19 @@
     </row>
     <row r="654" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A654" s="1" t="s">
-        <v>1363</v>
+        <v>1364</v>
       </c>
       <c r="B654" s="1" t="s">
-        <v>1364</v>
+        <v>1365</v>
       </c>
       <c r="C654" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D654" s="1" t="s">
-        <v>1365</v>
+        <v>1331</v>
       </c>
       <c r="E654" s="1" t="s">
-        <v>4</v>
+        <v>137</v>
       </c>
       <c r="F654" s="1" t="s">
         <v>9</v>
@@ -17855,10 +17876,10 @@
         <v>3</v>
       </c>
       <c r="D655" s="1" t="s">
-        <v>1365</v>
+        <v>1368</v>
       </c>
       <c r="E655" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F655" s="1" t="s">
         <v>9</v>
@@ -17866,19 +17887,19 @@
     </row>
     <row r="656" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A656" s="1" t="s">
+        <v>1369</v>
+      </c>
+      <c r="B656" s="1" t="s">
+        <v>1370</v>
+      </c>
+      <c r="C656" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D656" s="1" t="s">
         <v>1368</v>
       </c>
-      <c r="B656" s="1" t="s">
-        <v>1369</v>
-      </c>
-      <c r="C656" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D656" s="1" t="s">
-        <v>1365</v>
-      </c>
       <c r="E656" s="1" t="s">
-        <v>45</v>
+        <v>8</v>
       </c>
       <c r="F656" s="1" t="s">
         <v>9</v>
@@ -17886,19 +17907,19 @@
     </row>
     <row r="657" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A657" s="1" t="s">
-        <v>1370</v>
+        <v>1371</v>
       </c>
       <c r="B657" s="1" t="s">
-        <v>1371</v>
+        <v>1372</v>
       </c>
       <c r="C657" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D657" s="1" t="s">
-        <v>1365</v>
+        <v>1368</v>
       </c>
       <c r="E657" s="1" t="s">
-        <v>12</v>
+        <v>45</v>
       </c>
       <c r="F657" s="1" t="s">
         <v>9</v>
@@ -17906,139 +17927,139 @@
     </row>
     <row r="658" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A658" s="1" t="s">
-        <v>1372</v>
+        <v>1373</v>
       </c>
       <c r="B658" s="1" t="s">
-        <v>1373</v>
+        <v>1374</v>
       </c>
       <c r="C658" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D658" s="1" t="s">
-        <v>1365</v>
+        <v>1368</v>
       </c>
       <c r="E658" s="1" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="F658" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="659" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A659" s="1" t="s">
-        <v>1374</v>
+        <v>1375</v>
       </c>
       <c r="B659" s="1" t="s">
-        <v>1375</v>
+        <v>1376</v>
       </c>
       <c r="C659" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D659" s="1" t="s">
-        <v>1365</v>
+        <v>1368</v>
       </c>
       <c r="E659" s="1" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="F659" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="660" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A660" s="1" t="s">
-        <v>1376</v>
+        <v>1377</v>
       </c>
       <c r="B660" s="1" t="s">
-        <v>1377</v>
+        <v>1378</v>
       </c>
       <c r="C660" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D660" s="1" t="s">
-        <v>1365</v>
+        <v>1368</v>
       </c>
       <c r="E660" s="1" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="F660" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="661" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A661" s="1" t="s">
-        <v>1378</v>
+        <v>1379</v>
       </c>
       <c r="B661" s="1" t="s">
-        <v>1379</v>
+        <v>1380</v>
       </c>
       <c r="C661" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D661" s="1" t="s">
-        <v>1365</v>
+        <v>1368</v>
       </c>
       <c r="E661" s="1" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="F661" s="1" t="s">
-        <v>13</v>
+        <v>5</v>
       </c>
     </row>
     <row r="662" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A662" s="1" t="s">
-        <v>1380</v>
+        <v>1381</v>
       </c>
       <c r="B662" s="1" t="s">
-        <v>1381</v>
+        <v>1382</v>
       </c>
       <c r="C662" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D662" s="1" t="s">
-        <v>1365</v>
+        <v>1368</v>
       </c>
       <c r="E662" s="1" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="F662" s="1" t="s">
-        <v>5</v>
+        <v>13</v>
       </c>
     </row>
     <row r="663" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A663" s="1" t="s">
-        <v>1382</v>
+        <v>1383</v>
       </c>
       <c r="B663" s="1" t="s">
-        <v>1383</v>
+        <v>1384</v>
       </c>
       <c r="C663" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D663" s="1" t="s">
-        <v>1365</v>
+        <v>1368</v>
       </c>
       <c r="E663" s="1" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="F663" s="1" t="s">
-        <v>13</v>
+        <v>5</v>
       </c>
     </row>
     <row r="664" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A664" s="1" t="s">
-        <v>1384</v>
+        <v>1385</v>
       </c>
       <c r="B664" s="1" t="s">
-        <v>1385</v>
+        <v>1386</v>
       </c>
       <c r="C664" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D664" s="1" t="s">
-        <v>1365</v>
+        <v>1368</v>
       </c>
       <c r="E664" s="1" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="F664" s="1" t="s">
         <v>13</v>
@@ -18046,19 +18067,19 @@
     </row>
     <row r="665" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A665" s="1" t="s">
-        <v>1386</v>
+        <v>1387</v>
       </c>
       <c r="B665" s="1" t="s">
-        <v>1387</v>
+        <v>1388</v>
       </c>
       <c r="C665" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D665" s="1" t="s">
-        <v>1365</v>
+        <v>1368</v>
       </c>
       <c r="E665" s="1" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="F665" s="1" t="s">
         <v>13</v>
@@ -18066,19 +18087,19 @@
     </row>
     <row r="666" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A666" s="1" t="s">
-        <v>1388</v>
+        <v>1389</v>
       </c>
       <c r="B666" s="1" t="s">
-        <v>1389</v>
+        <v>1390</v>
       </c>
       <c r="C666" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D666" s="1" t="s">
-        <v>1365</v>
+        <v>1368</v>
       </c>
       <c r="E666" s="1" t="s">
-        <v>90</v>
+        <v>38</v>
       </c>
       <c r="F666" s="1" t="s">
         <v>13</v>
@@ -18086,322 +18107,322 @@
     </row>
     <row r="667" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A667" s="1" t="s">
-        <v>1390</v>
+        <v>1391</v>
       </c>
       <c r="B667" s="1" t="s">
-        <v>1391</v>
+        <v>1392</v>
       </c>
       <c r="C667" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D667" s="1" t="s">
-        <v>1392</v>
+        <v>1368</v>
       </c>
       <c r="E667" s="1" t="s">
-        <v>4</v>
+        <v>90</v>
       </c>
       <c r="F667" s="1" t="s">
-        <v>1393</v>
+        <v>13</v>
       </c>
     </row>
     <row r="668" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A668" s="1" t="s">
+        <v>1393</v>
+      </c>
+      <c r="B668" s="1" t="s">
         <v>1394</v>
       </c>
-      <c r="B668" s="1" t="s">
+      <c r="C668" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D668" s="1" t="s">
         <v>1395</v>
       </c>
-      <c r="C668" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D668" s="1" t="s">
-        <v>1392</v>
-      </c>
       <c r="E668" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F668" s="1" t="s">
-        <v>1393</v>
+        <v>1396</v>
       </c>
     </row>
     <row r="669" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A669" s="1" t="s">
+        <v>1397</v>
+      </c>
+      <c r="B669" s="1" t="s">
+        <v>1398</v>
+      </c>
+      <c r="C669" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D669" s="1" t="s">
+        <v>1395</v>
+      </c>
+      <c r="E669" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="F669" s="1" t="s">
         <v>1396</v>
-      </c>
-      <c r="B669" s="1" t="s">
-        <v>1397</v>
-      </c>
-      <c r="C669" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D669" s="1" t="s">
-        <v>1392</v>
-      </c>
-      <c r="E669" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="F669" s="1" t="s">
-        <v>1393</v>
       </c>
     </row>
     <row r="670" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A670" s="1" t="s">
-        <v>1398</v>
+        <v>1399</v>
       </c>
       <c r="B670" s="1" t="s">
-        <v>1399</v>
+        <v>1400</v>
       </c>
       <c r="C670" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D670" s="1" t="s">
-        <v>1392</v>
+        <v>1395</v>
       </c>
       <c r="E670" s="1" t="s">
-        <v>12</v>
+        <v>45</v>
       </c>
       <c r="F670" s="1" t="s">
-        <v>1393</v>
+        <v>1396</v>
       </c>
     </row>
     <row r="671" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A671" s="1" t="s">
-        <v>1400</v>
+        <v>1401</v>
       </c>
       <c r="B671" s="1" t="s">
-        <v>1401</v>
+        <v>1402</v>
       </c>
       <c r="C671" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D671" s="1" t="s">
-        <v>1392</v>
+        <v>1395</v>
       </c>
       <c r="E671" s="1" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="F671" s="1" t="s">
-        <v>1393</v>
+        <v>1396</v>
       </c>
     </row>
     <row r="672" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A672" s="1" t="s">
-        <v>1402</v>
+        <v>1403</v>
       </c>
       <c r="B672" s="1" t="s">
-        <v>1403</v>
+        <v>1404</v>
       </c>
       <c r="C672" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D672" s="1" t="s">
-        <v>1392</v>
+        <v>1395</v>
       </c>
       <c r="E672" s="1" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="F672" s="1" t="s">
-        <v>1393</v>
+        <v>1396</v>
       </c>
     </row>
     <row r="673" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A673" s="1" t="s">
-        <v>1404</v>
+        <v>1405</v>
       </c>
       <c r="B673" s="1" t="s">
-        <v>1405</v>
+        <v>1406</v>
       </c>
       <c r="C673" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D673" s="1" t="s">
-        <v>1392</v>
+        <v>1395</v>
       </c>
       <c r="E673" s="1" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="F673" s="1" t="s">
-        <v>1393</v>
+        <v>1396</v>
       </c>
     </row>
     <row r="674" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A674" s="1" t="s">
-        <v>1406</v>
+        <v>1407</v>
       </c>
       <c r="B674" s="1" t="s">
-        <v>1407</v>
+        <v>1408</v>
       </c>
       <c r="C674" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D674" s="1" t="s">
-        <v>1392</v>
+        <v>1395</v>
       </c>
       <c r="E674" s="1" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="F674" s="1" t="s">
-        <v>231</v>
+        <v>1396</v>
       </c>
     </row>
     <row r="675" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A675" s="1" t="s">
-        <v>1408</v>
+        <v>1409</v>
       </c>
       <c r="B675" s="1" t="s">
-        <v>1409</v>
+        <v>1410</v>
       </c>
       <c r="C675" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D675" s="1" t="s">
-        <v>1392</v>
+        <v>1395</v>
       </c>
       <c r="E675" s="1" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="F675" s="1" t="s">
-        <v>5</v>
+        <v>231</v>
       </c>
     </row>
     <row r="676" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A676" s="1" t="s">
-        <v>1410</v>
+        <v>1411</v>
       </c>
       <c r="B676" s="1" t="s">
-        <v>1411</v>
+        <v>1412</v>
       </c>
       <c r="C676" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D676" s="1" t="s">
-        <v>1392</v>
+        <v>1395</v>
       </c>
       <c r="E676" s="1" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="F676" s="1" t="s">
-        <v>1393</v>
+        <v>5</v>
       </c>
     </row>
     <row r="677" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A677" s="1" t="s">
-        <v>1412</v>
+        <v>1413</v>
       </c>
       <c r="B677" s="1" t="s">
-        <v>1413</v>
+        <v>1414</v>
       </c>
       <c r="C677" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D677" s="1" t="s">
-        <v>1392</v>
+        <v>1395</v>
       </c>
       <c r="E677" s="1" t="s">
         <v>32</v>
       </c>
       <c r="F677" s="1" t="s">
-        <v>1393</v>
+        <v>1396</v>
       </c>
     </row>
     <row r="678" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A678" s="1" t="s">
-        <v>1414</v>
+        <v>1415</v>
       </c>
       <c r="B678" s="1" t="s">
-        <v>1415</v>
+        <v>1416</v>
       </c>
       <c r="C678" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D678" s="1" t="s">
-        <v>1392</v>
+        <v>1395</v>
       </c>
       <c r="E678" s="1" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="F678" s="1" t="s">
-        <v>1393</v>
+        <v>1396</v>
       </c>
     </row>
     <row r="679" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A679" s="1" t="s">
-        <v>1416</v>
+        <v>1417</v>
       </c>
       <c r="B679" s="1" t="s">
-        <v>1417</v>
+        <v>1418</v>
       </c>
       <c r="C679" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D679" s="1" t="s">
-        <v>1392</v>
+        <v>1395</v>
       </c>
       <c r="E679" s="1" t="s">
         <v>35</v>
       </c>
       <c r="F679" s="1" t="s">
-        <v>1393</v>
+        <v>1396</v>
       </c>
     </row>
     <row r="680" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A680" s="1" t="s">
-        <v>1418</v>
+        <v>1419</v>
       </c>
       <c r="B680" s="1" t="s">
-        <v>1419</v>
+        <v>1420</v>
       </c>
       <c r="C680" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D680" s="1" t="s">
-        <v>1392</v>
+        <v>1395</v>
       </c>
       <c r="E680" s="1" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="F680" s="1" t="s">
-        <v>231</v>
+        <v>1396</v>
       </c>
     </row>
     <row r="681" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A681" s="1" t="s">
-        <v>1420</v>
+        <v>1421</v>
       </c>
       <c r="B681" s="1" t="s">
-        <v>1421</v>
+        <v>1422</v>
       </c>
       <c r="C681" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D681" s="1" t="s">
-        <v>1392</v>
+        <v>1395</v>
       </c>
       <c r="E681" s="1" t="s">
-        <v>90</v>
+        <v>38</v>
       </c>
       <c r="F681" s="1" t="s">
-        <v>1393</v>
+        <v>231</v>
       </c>
     </row>
     <row r="682" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A682" s="1" t="s">
-        <v>1422</v>
+        <v>1423</v>
       </c>
       <c r="B682" s="1" t="s">
-        <v>1423</v>
+        <v>1424</v>
       </c>
       <c r="C682" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D682" s="1" t="s">
-        <v>1424</v>
+        <v>1395</v>
       </c>
       <c r="E682" s="1" t="s">
-        <v>4</v>
+        <v>90</v>
       </c>
       <c r="F682" s="1" t="s">
-        <v>5</v>
+        <v>1396</v>
       </c>
     </row>
     <row r="683" spans="1:6" x14ac:dyDescent="0.25">
@@ -18415,10 +18436,10 @@
         <v>3</v>
       </c>
       <c r="D683" s="1" t="s">
-        <v>1424</v>
+        <v>1427</v>
       </c>
       <c r="E683" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F683" s="1" t="s">
         <v>5</v>
@@ -18426,19 +18447,19 @@
     </row>
     <row r="684" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A684" s="1" t="s">
+        <v>1428</v>
+      </c>
+      <c r="B684" s="1" t="s">
+        <v>1429</v>
+      </c>
+      <c r="C684" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D684" s="1" t="s">
         <v>1427</v>
       </c>
-      <c r="B684" s="1" t="s">
-        <v>1428</v>
-      </c>
-      <c r="C684" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D684" s="1" t="s">
-        <v>1424</v>
-      </c>
       <c r="E684" s="1" t="s">
-        <v>45</v>
+        <v>8</v>
       </c>
       <c r="F684" s="1" t="s">
         <v>5</v>
@@ -18446,39 +18467,39 @@
     </row>
     <row r="685" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A685" s="1" t="s">
-        <v>1429</v>
+        <v>1430</v>
       </c>
       <c r="B685" s="1" t="s">
-        <v>1430</v>
+        <v>1431</v>
       </c>
       <c r="C685" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D685" s="1" t="s">
-        <v>1424</v>
+        <v>1427</v>
       </c>
       <c r="E685" s="1" t="s">
-        <v>12</v>
+        <v>45</v>
       </c>
       <c r="F685" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="686" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A686" s="1" t="s">
-        <v>1431</v>
+        <v>1432</v>
       </c>
       <c r="B686" s="1" t="s">
-        <v>1432</v>
+        <v>1433</v>
       </c>
       <c r="C686" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D686" s="1" t="s">
-        <v>1424</v>
+        <v>1427</v>
       </c>
       <c r="E686" s="1" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="F686" s="1" t="s">
         <v>9</v>
@@ -18486,119 +18507,119 @@
     </row>
     <row r="687" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A687" s="1" t="s">
-        <v>1433</v>
+        <v>1434</v>
       </c>
       <c r="B687" s="1" t="s">
-        <v>1434</v>
+        <v>1435</v>
       </c>
       <c r="C687" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D687" s="1" t="s">
-        <v>1424</v>
+        <v>1427</v>
       </c>
       <c r="E687" s="1" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="F687" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="688" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A688" s="1" t="s">
-        <v>1435</v>
+        <v>1436</v>
       </c>
       <c r="B688" s="1" t="s">
-        <v>1436</v>
+        <v>1437</v>
       </c>
       <c r="C688" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D688" s="1" t="s">
-        <v>1424</v>
+        <v>1427</v>
       </c>
       <c r="E688" s="1" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="F688" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="689" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A689" s="1" t="s">
-        <v>1437</v>
+        <v>1438</v>
       </c>
       <c r="B689" s="1" t="s">
-        <v>1438</v>
+        <v>1439</v>
       </c>
       <c r="C689" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D689" s="1" t="s">
-        <v>1424</v>
+        <v>1427</v>
       </c>
       <c r="E689" s="1" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="F689" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="690" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A690" s="1" t="s">
-        <v>1439</v>
+        <v>1440</v>
       </c>
       <c r="B690" s="1" t="s">
-        <v>1440</v>
+        <v>1441</v>
       </c>
       <c r="C690" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D690" s="1" t="s">
-        <v>1424</v>
+        <v>1427</v>
       </c>
       <c r="E690" s="1" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="F690" s="1" t="s">
-        <v>29</v>
+        <v>5</v>
       </c>
     </row>
     <row r="691" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A691" s="1" t="s">
-        <v>1441</v>
+        <v>1442</v>
       </c>
       <c r="B691" s="1" t="s">
-        <v>1442</v>
+        <v>1443</v>
       </c>
       <c r="C691" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D691" s="1" t="s">
-        <v>1424</v>
+        <v>1427</v>
       </c>
       <c r="E691" s="1" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="F691" s="1" t="s">
-        <v>9</v>
+        <v>29</v>
       </c>
     </row>
     <row r="692" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A692" s="1" t="s">
-        <v>1443</v>
+        <v>1444</v>
       </c>
       <c r="B692" s="1" t="s">
-        <v>1444</v>
+        <v>1445</v>
       </c>
       <c r="C692" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D692" s="1" t="s">
-        <v>1424</v>
+        <v>1427</v>
       </c>
       <c r="E692" s="1" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="F692" s="1" t="s">
         <v>9</v>
@@ -18606,19 +18627,19 @@
     </row>
     <row r="693" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A693" s="1" t="s">
-        <v>1445</v>
+        <v>1446</v>
       </c>
       <c r="B693" s="1" t="s">
-        <v>1446</v>
+        <v>1447</v>
       </c>
       <c r="C693" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D693" s="1" t="s">
-        <v>1424</v>
+        <v>1427</v>
       </c>
       <c r="E693" s="1" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="F693" s="1" t="s">
         <v>9</v>
@@ -18626,22 +18647,82 @@
     </row>
     <row r="694" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A694" s="1" t="s">
-        <v>1447</v>
+        <v>1448</v>
       </c>
       <c r="B694" s="1" t="s">
-        <v>1448</v>
+        <v>1449</v>
       </c>
       <c r="C694" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D694" s="1" t="s">
-        <v>1449</v>
+        <v>1427</v>
       </c>
       <c r="E694" s="1" t="s">
-        <v>8</v>
+        <v>38</v>
       </c>
       <c r="F694" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
+      </c>
+    </row>
+    <row r="695" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A695" s="1" t="s">
+        <v>1450</v>
+      </c>
+      <c r="B695" s="1" t="s">
+        <v>1451</v>
+      </c>
+      <c r="C695" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D695" s="1" t="s">
+        <v>1452</v>
+      </c>
+      <c r="E695" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="F695" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="696" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A696" s="1" t="s">
+        <v>1453</v>
+      </c>
+      <c r="B696" s="1" t="s">
+        <v>1454</v>
+      </c>
+      <c r="C696" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D696" s="1" t="s">
+        <v>1452</v>
+      </c>
+      <c r="E696" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="F696" s="1" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="697" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A697" s="1" t="s">
+        <v>1455</v>
+      </c>
+      <c r="B697" s="1" t="s">
+        <v>1456</v>
+      </c>
+      <c r="C697" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D697" s="1" t="s">
+        <v>1452</v>
+      </c>
+      <c r="E697" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="F697" s="1" t="s">
+        <v>117</v>
       </c>
     </row>
   </sheetData>

--- a/PCE06D.xlsx
+++ b/PCE06D.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4200" uniqueCount="1463">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4158" uniqueCount="1449">
   <si>
     <t/>
   </si>
@@ -2092,12 +2092,6 @@
     <t>VIVA MIC WTR SENS100</t>
   </si>
   <si>
-    <t>20134003</t>
-  </si>
-  <si>
-    <t>GRNR MCLR.WTR BHA 50</t>
-  </si>
-  <si>
     <t>20093906</t>
   </si>
   <si>
@@ -2161,102 +2155,102 @@
     <t>EMRN B/RM APR ORG400</t>
   </si>
   <si>
+    <t>20103168</t>
+  </si>
+  <si>
+    <t>MARINA HBL E COLL185</t>
+  </si>
+  <si>
+    <t>20007302</t>
+  </si>
+  <si>
+    <t>MARINA LOT H&amp;GLW 185</t>
+  </si>
+  <si>
+    <t>20021330</t>
+  </si>
+  <si>
+    <t>MARINA HBL AVCDO 190</t>
+  </si>
+  <si>
+    <t>20055144</t>
+  </si>
+  <si>
+    <t>MARINA HBL SPF30/185</t>
+  </si>
+  <si>
+    <t>20031999</t>
+  </si>
+  <si>
+    <t>VASE/L H.WHT SPF 100</t>
+  </si>
+  <si>
+    <t>25</t>
+  </si>
+  <si>
+    <t>20020977</t>
+  </si>
+  <si>
+    <t>VSLNE LOT BRIGHT 100</t>
+  </si>
+  <si>
+    <t>20071707</t>
+  </si>
+  <si>
+    <t>NIVEA LOT.EXT BRI190</t>
+  </si>
+  <si>
+    <t>20030179</t>
+  </si>
+  <si>
+    <t>NIVEA LOT INTSV 190</t>
+  </si>
+  <si>
+    <t>20124789</t>
+  </si>
+  <si>
+    <t>NIVEA B/S SPR.VIT180</t>
+  </si>
+  <si>
+    <t>20045924</t>
+  </si>
+  <si>
+    <t>NIVEA B.SRM CRE&amp;P180</t>
+  </si>
+  <si>
+    <t>20139972</t>
+  </si>
+  <si>
+    <t>G2G BS CRM.BERRY 180</t>
+  </si>
+  <si>
+    <t>20140874</t>
+  </si>
+  <si>
+    <t>G2G NIACND B.SRM 180</t>
+  </si>
+  <si>
+    <t>20131721</t>
+  </si>
+  <si>
+    <t>SCRLET LOT CHARM 180</t>
+  </si>
+  <si>
+    <t>20133795</t>
+  </si>
+  <si>
+    <t>SCRLET LOT JOLLY 180</t>
+  </si>
+  <si>
+    <t>20142344</t>
+  </si>
+  <si>
+    <t>WHITE INC BL ALPH180</t>
+  </si>
+  <si>
     <t>,(E-3B)</t>
   </si>
   <si>
-    <t>20103168</t>
-  </si>
-  <si>
-    <t>MARINA HBL E COLL185</t>
-  </si>
-  <si>
-    <t>20007302</t>
-  </si>
-  <si>
-    <t>MARINA LOT H&amp;GLW 185</t>
-  </si>
-  <si>
-    <t>20021330</t>
-  </si>
-  <si>
-    <t>MARINA HBL AVCDO 190</t>
-  </si>
-  <si>
-    <t>20055144</t>
-  </si>
-  <si>
-    <t>MARINA HBL SPF30/185</t>
-  </si>
-  <si>
-    <t>20031999</t>
-  </si>
-  <si>
-    <t>VASE/L H.WHT SPF 100</t>
-  </si>
-  <si>
-    <t>25</t>
-  </si>
-  <si>
-    <t>20020977</t>
-  </si>
-  <si>
-    <t>VSLNE LOT BRIGHT 100</t>
-  </si>
-  <si>
-    <t>20071707</t>
-  </si>
-  <si>
-    <t>NIVEA LOT.EXT BRI190</t>
-  </si>
-  <si>
-    <t>20030179</t>
-  </si>
-  <si>
-    <t>NIVEA LOT INTSV 190</t>
-  </si>
-  <si>
-    <t>20124789</t>
-  </si>
-  <si>
-    <t>NIVEA B/S SPR.VIT180</t>
-  </si>
-  <si>
-    <t>20045924</t>
-  </si>
-  <si>
-    <t>NIVEA B.SRM CRE&amp;P180</t>
-  </si>
-  <si>
-    <t>20139972</t>
-  </si>
-  <si>
-    <t>G2G BS CRM.BERRY 180</t>
-  </si>
-  <si>
-    <t>20140874</t>
-  </si>
-  <si>
-    <t>G2G NIACND B.SRM 180</t>
-  </si>
-  <si>
-    <t>20142344</t>
-  </si>
-  <si>
-    <t>WHITE INC BL ALPH180</t>
-  </si>
-  <si>
-    <t>20131721</t>
-  </si>
-  <si>
-    <t>SCRLET LOT CHARM 180</t>
-  </si>
-  <si>
-    <t>20133795</t>
-  </si>
-  <si>
-    <t>SCRLET LOT JOLLY 180</t>
-  </si>
-  <si>
     <t>20136931</t>
   </si>
   <si>
@@ -3694,24 +3688,12 @@
     <t>39</t>
   </si>
   <si>
-    <t>20034678</t>
-  </si>
-  <si>
-    <t>GRNR MEN COOL FM 50</t>
-  </si>
-  <si>
     <t>20097301</t>
   </si>
   <si>
     <t>GRNIER 3IN1 CH.BLC50</t>
   </si>
   <si>
-    <t>20115160</t>
-  </si>
-  <si>
-    <t>GRNR MEN TB DUO.FM50</t>
-  </si>
-  <si>
     <t>20141643</t>
   </si>
   <si>
@@ -4363,37 +4345,13 @@
     <t>GATSBY BALM CREAM 70</t>
   </si>
   <si>
-    <t>20140271</t>
-  </si>
-  <si>
-    <t>EVRSNSE XDP CLSTR 30</t>
+    <t>20139065</t>
+  </si>
+  <si>
+    <t>PONDS MEN AA&amp;PC 100</t>
   </si>
   <si>
     <t>998</t>
-  </si>
-  <si>
-    <t>20139452</t>
-  </si>
-  <si>
-    <t>NIVEA BS SUPER C 70</t>
-  </si>
-  <si>
-    <t>20139455</t>
-  </si>
-  <si>
-    <t>NIVEA BS C&amp;AHA 170ML</t>
-  </si>
-  <si>
-    <t>20138022</t>
-  </si>
-  <si>
-    <t>SNSLK CRMBTH S.SL 30</t>
-  </si>
-  <si>
-    <t>20139065</t>
-  </si>
-  <si>
-    <t>PONDS MEN AA&amp;PC 100</t>
   </si>
   <si>
     <t>20137609</t>
@@ -4792,7 +4750,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F700"/>
+  <dimension ref="A1:F693"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
@@ -11434,30 +11392,30 @@
         <v>3</v>
       </c>
       <c r="D332" s="1" t="s">
-        <v>664</v>
+        <v>699</v>
       </c>
       <c r="E332" s="1" t="s">
-        <v>112</v>
+        <v>4</v>
       </c>
       <c r="F332" s="1" t="s">
-        <v>5</v>
+        <v>25</v>
       </c>
     </row>
     <row r="333" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A333" s="1" t="s">
+        <v>700</v>
+      </c>
+      <c r="B333" s="1" t="s">
+        <v>701</v>
+      </c>
+      <c r="C333" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D333" s="1" t="s">
         <v>699</v>
       </c>
-      <c r="B333" s="1" t="s">
-        <v>700</v>
-      </c>
-      <c r="C333" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D333" s="1" t="s">
-        <v>701</v>
-      </c>
       <c r="E333" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F333" s="1" t="s">
         <v>25</v>
@@ -11474,10 +11432,10 @@
         <v>3</v>
       </c>
       <c r="D334" s="1" t="s">
-        <v>701</v>
+        <v>699</v>
       </c>
       <c r="E334" s="1" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="F334" s="1" t="s">
         <v>25</v>
@@ -11494,10 +11452,10 @@
         <v>3</v>
       </c>
       <c r="D335" s="1" t="s">
-        <v>701</v>
+        <v>699</v>
       </c>
       <c r="E335" s="1" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="F335" s="1" t="s">
         <v>25</v>
@@ -11514,13 +11472,13 @@
         <v>3</v>
       </c>
       <c r="D336" s="1" t="s">
-        <v>701</v>
+        <v>699</v>
       </c>
       <c r="E336" s="1" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="F336" s="1" t="s">
-        <v>25</v>
+        <v>41</v>
       </c>
     </row>
     <row r="337" spans="1:6" x14ac:dyDescent="0.25">
@@ -11534,10 +11492,10 @@
         <v>3</v>
       </c>
       <c r="D337" s="1" t="s">
-        <v>701</v>
+        <v>699</v>
       </c>
       <c r="E337" s="1" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="F337" s="1" t="s">
         <v>41</v>
@@ -11554,13 +11512,13 @@
         <v>3</v>
       </c>
       <c r="D338" s="1" t="s">
-        <v>701</v>
+        <v>699</v>
       </c>
       <c r="E338" s="1" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="F338" s="1" t="s">
-        <v>41</v>
+        <v>5</v>
       </c>
     </row>
     <row r="339" spans="1:6" x14ac:dyDescent="0.25">
@@ -11574,10 +11532,10 @@
         <v>3</v>
       </c>
       <c r="D339" s="1" t="s">
-        <v>701</v>
+        <v>699</v>
       </c>
       <c r="E339" s="1" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="F339" s="1" t="s">
         <v>5</v>
@@ -11594,30 +11552,30 @@
         <v>3</v>
       </c>
       <c r="D340" s="1" t="s">
-        <v>701</v>
+        <v>699</v>
       </c>
       <c r="E340" s="1" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="F340" s="1" t="s">
-        <v>716</v>
+        <v>5</v>
       </c>
     </row>
     <row r="341" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A341" s="1" t="s">
+        <v>716</v>
+      </c>
+      <c r="B341" s="1" t="s">
         <v>717</v>
       </c>
-      <c r="B341" s="1" t="s">
-        <v>718</v>
-      </c>
       <c r="C341" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D341" s="1" t="s">
-        <v>701</v>
+        <v>699</v>
       </c>
       <c r="E341" s="1" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="F341" s="1" t="s">
         <v>5</v>
@@ -11625,19 +11583,19 @@
     </row>
     <row r="342" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A342" s="1" t="s">
+        <v>718</v>
+      </c>
+      <c r="B342" s="1" t="s">
         <v>719</v>
       </c>
-      <c r="B342" s="1" t="s">
-        <v>720</v>
-      </c>
       <c r="C342" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D342" s="1" t="s">
-        <v>701</v>
+        <v>699</v>
       </c>
       <c r="E342" s="1" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="F342" s="1" t="s">
         <v>5</v>
@@ -11645,19 +11603,19 @@
     </row>
     <row r="343" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A343" s="1" t="s">
+        <v>720</v>
+      </c>
+      <c r="B343" s="1" t="s">
         <v>721</v>
       </c>
-      <c r="B343" s="1" t="s">
-        <v>722</v>
-      </c>
       <c r="C343" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D343" s="1" t="s">
-        <v>701</v>
+        <v>699</v>
       </c>
       <c r="E343" s="1" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="F343" s="1" t="s">
         <v>5</v>
@@ -11665,22 +11623,22 @@
     </row>
     <row r="344" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A344" s="1" t="s">
+        <v>722</v>
+      </c>
+      <c r="B344" s="1" t="s">
         <v>723</v>
       </c>
-      <c r="B344" s="1" t="s">
+      <c r="C344" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D344" s="1" t="s">
         <v>724</v>
       </c>
-      <c r="C344" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D344" s="1" t="s">
-        <v>701</v>
-      </c>
       <c r="E344" s="1" t="s">
-        <v>40</v>
+        <v>4</v>
       </c>
       <c r="F344" s="1" t="s">
-        <v>5</v>
+        <v>25</v>
       </c>
     </row>
     <row r="345" spans="1:6" x14ac:dyDescent="0.25">
@@ -11694,10 +11652,10 @@
         <v>3</v>
       </c>
       <c r="D345" s="1" t="s">
-        <v>727</v>
+        <v>724</v>
       </c>
       <c r="E345" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F345" s="1" t="s">
         <v>25</v>
@@ -11705,39 +11663,39 @@
     </row>
     <row r="346" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A346" s="1" t="s">
+        <v>727</v>
+      </c>
+      <c r="B346" s="1" t="s">
         <v>728</v>
       </c>
-      <c r="B346" s="1" t="s">
-        <v>729</v>
-      </c>
       <c r="C346" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D346" s="1" t="s">
-        <v>727</v>
+        <v>724</v>
       </c>
       <c r="E346" s="1" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="F346" s="1" t="s">
-        <v>25</v>
+        <v>80</v>
       </c>
     </row>
     <row r="347" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A347" s="1" t="s">
+        <v>729</v>
+      </c>
+      <c r="B347" s="1" t="s">
         <v>730</v>
       </c>
-      <c r="B347" s="1" t="s">
-        <v>731</v>
-      </c>
       <c r="C347" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D347" s="1" t="s">
-        <v>727</v>
+        <v>724</v>
       </c>
       <c r="E347" s="1" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="F347" s="1" t="s">
         <v>80</v>
@@ -11745,142 +11703,142 @@
     </row>
     <row r="348" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A348" s="1" t="s">
+        <v>731</v>
+      </c>
+      <c r="B348" s="1" t="s">
         <v>732</v>
       </c>
-      <c r="B348" s="1" t="s">
-        <v>733</v>
-      </c>
       <c r="C348" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D348" s="1" t="s">
-        <v>727</v>
+        <v>724</v>
       </c>
       <c r="E348" s="1" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="F348" s="1" t="s">
-        <v>80</v>
+        <v>5</v>
       </c>
     </row>
     <row r="349" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A349" s="1" t="s">
+        <v>733</v>
+      </c>
+      <c r="B349" s="1" t="s">
         <v>734</v>
       </c>
-      <c r="B349" s="1" t="s">
-        <v>735</v>
-      </c>
       <c r="C349" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D349" s="1" t="s">
-        <v>727</v>
+        <v>724</v>
       </c>
       <c r="E349" s="1" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="F349" s="1" t="s">
-        <v>5</v>
+        <v>80</v>
       </c>
     </row>
     <row r="350" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A350" s="1" t="s">
+        <v>735</v>
+      </c>
+      <c r="B350" s="1" t="s">
         <v>736</v>
       </c>
-      <c r="B350" s="1" t="s">
-        <v>737</v>
-      </c>
       <c r="C350" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D350" s="1" t="s">
-        <v>727</v>
+        <v>724</v>
       </c>
       <c r="E350" s="1" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="F350" s="1" t="s">
-        <v>80</v>
+        <v>5</v>
       </c>
     </row>
     <row r="351" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A351" s="1" t="s">
+        <v>737</v>
+      </c>
+      <c r="B351" s="1" t="s">
         <v>738</v>
       </c>
-      <c r="B351" s="1" t="s">
-        <v>739</v>
-      </c>
       <c r="C351" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D351" s="1" t="s">
-        <v>727</v>
+        <v>724</v>
       </c>
       <c r="E351" s="1" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="F351" s="1" t="s">
-        <v>5</v>
+        <v>41</v>
       </c>
     </row>
     <row r="352" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A352" s="1" t="s">
+        <v>739</v>
+      </c>
+      <c r="B352" s="1" t="s">
         <v>740</v>
       </c>
-      <c r="B352" s="1" t="s">
-        <v>741</v>
-      </c>
       <c r="C352" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D352" s="1" t="s">
-        <v>727</v>
+        <v>724</v>
       </c>
       <c r="E352" s="1" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="F352" s="1" t="s">
-        <v>41</v>
+        <v>5</v>
       </c>
     </row>
     <row r="353" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A353" s="1" t="s">
+        <v>741</v>
+      </c>
+      <c r="B353" s="1" t="s">
         <v>742</v>
       </c>
-      <c r="B353" s="1" t="s">
-        <v>743</v>
-      </c>
       <c r="C353" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D353" s="1" t="s">
-        <v>727</v>
+        <v>724</v>
       </c>
       <c r="E353" s="1" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="F353" s="1" t="s">
-        <v>716</v>
+        <v>5</v>
       </c>
     </row>
     <row r="354" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A354" s="1" t="s">
+        <v>743</v>
+      </c>
+      <c r="B354" s="1" t="s">
         <v>744</v>
       </c>
-      <c r="B354" s="1" t="s">
+      <c r="C354" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D354" s="1" t="s">
+        <v>724</v>
+      </c>
+      <c r="E354" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="F354" s="1" t="s">
         <v>745</v>
-      </c>
-      <c r="C354" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D354" s="1" t="s">
-        <v>727</v>
-      </c>
-      <c r="E354" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="F354" s="1" t="s">
-        <v>5</v>
       </c>
     </row>
     <row r="355" spans="1:6" x14ac:dyDescent="0.25">
@@ -11894,13 +11852,13 @@
         <v>3</v>
       </c>
       <c r="D355" s="1" t="s">
-        <v>727</v>
+        <v>724</v>
       </c>
       <c r="E355" s="1" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="F355" s="1" t="s">
-        <v>5</v>
+        <v>25</v>
       </c>
     </row>
     <row r="356" spans="1:6" x14ac:dyDescent="0.25">
@@ -11914,10 +11872,10 @@
         <v>3</v>
       </c>
       <c r="D356" s="1" t="s">
-        <v>727</v>
+        <v>724</v>
       </c>
       <c r="E356" s="1" t="s">
-        <v>40</v>
+        <v>68</v>
       </c>
       <c r="F356" s="1" t="s">
         <v>25</v>
@@ -11934,10 +11892,10 @@
         <v>3</v>
       </c>
       <c r="D357" s="1" t="s">
-        <v>727</v>
+        <v>724</v>
       </c>
       <c r="E357" s="1" t="s">
-        <v>68</v>
+        <v>100</v>
       </c>
       <c r="F357" s="1" t="s">
         <v>25</v>
@@ -11954,30 +11912,30 @@
         <v>3</v>
       </c>
       <c r="D358" s="1" t="s">
-        <v>727</v>
+        <v>754</v>
       </c>
       <c r="E358" s="1" t="s">
-        <v>100</v>
+        <v>4</v>
       </c>
       <c r="F358" s="1" t="s">
-        <v>25</v>
+        <v>5</v>
       </c>
     </row>
     <row r="359" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A359" s="1" t="s">
+        <v>755</v>
+      </c>
+      <c r="B359" s="1" t="s">
+        <v>756</v>
+      </c>
+      <c r="C359" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D359" s="1" t="s">
         <v>754</v>
       </c>
-      <c r="B359" s="1" t="s">
-        <v>755</v>
-      </c>
-      <c r="C359" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D359" s="1" t="s">
-        <v>756</v>
-      </c>
       <c r="E359" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F359" s="1" t="s">
         <v>5</v>
@@ -11994,10 +11952,10 @@
         <v>3</v>
       </c>
       <c r="D360" s="1" t="s">
-        <v>756</v>
+        <v>754</v>
       </c>
       <c r="E360" s="1" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="F360" s="1" t="s">
         <v>5</v>
@@ -12014,10 +11972,10 @@
         <v>3</v>
       </c>
       <c r="D361" s="1" t="s">
-        <v>756</v>
+        <v>754</v>
       </c>
       <c r="E361" s="1" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="F361" s="1" t="s">
         <v>5</v>
@@ -12034,10 +11992,10 @@
         <v>3</v>
       </c>
       <c r="D362" s="1" t="s">
-        <v>756</v>
+        <v>754</v>
       </c>
       <c r="E362" s="1" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="F362" s="1" t="s">
         <v>5</v>
@@ -12054,13 +12012,13 @@
         <v>3</v>
       </c>
       <c r="D363" s="1" t="s">
-        <v>756</v>
+        <v>754</v>
       </c>
       <c r="E363" s="1" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="F363" s="1" t="s">
-        <v>5</v>
+        <v>41</v>
       </c>
     </row>
     <row r="364" spans="1:6" x14ac:dyDescent="0.25">
@@ -12074,13 +12032,13 @@
         <v>3</v>
       </c>
       <c r="D364" s="1" t="s">
-        <v>756</v>
+        <v>754</v>
       </c>
       <c r="E364" s="1" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="F364" s="1" t="s">
-        <v>41</v>
+        <v>5</v>
       </c>
     </row>
     <row r="365" spans="1:6" x14ac:dyDescent="0.25">
@@ -12094,13 +12052,13 @@
         <v>3</v>
       </c>
       <c r="D365" s="1" t="s">
-        <v>756</v>
+        <v>754</v>
       </c>
       <c r="E365" s="1" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="F365" s="1" t="s">
-        <v>5</v>
+        <v>41</v>
       </c>
     </row>
     <row r="366" spans="1:6" x14ac:dyDescent="0.25">
@@ -12114,10 +12072,10 @@
         <v>3</v>
       </c>
       <c r="D366" s="1" t="s">
-        <v>756</v>
+        <v>754</v>
       </c>
       <c r="E366" s="1" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="F366" s="1" t="s">
         <v>41</v>
@@ -12134,10 +12092,10 @@
         <v>3</v>
       </c>
       <c r="D367" s="1" t="s">
-        <v>756</v>
+        <v>754</v>
       </c>
       <c r="E367" s="1" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="F367" s="1" t="s">
         <v>41</v>
@@ -12154,10 +12112,10 @@
         <v>3</v>
       </c>
       <c r="D368" s="1" t="s">
-        <v>756</v>
+        <v>754</v>
       </c>
       <c r="E368" s="1" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="F368" s="1" t="s">
         <v>41</v>
@@ -12174,13 +12132,13 @@
         <v>3</v>
       </c>
       <c r="D369" s="1" t="s">
-        <v>756</v>
+        <v>754</v>
       </c>
       <c r="E369" s="1" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="F369" s="1" t="s">
-        <v>41</v>
+        <v>9</v>
       </c>
     </row>
     <row r="370" spans="1:6" x14ac:dyDescent="0.25">
@@ -12194,13 +12152,13 @@
         <v>3</v>
       </c>
       <c r="D370" s="1" t="s">
-        <v>756</v>
+        <v>754</v>
       </c>
       <c r="E370" s="1" t="s">
-        <v>40</v>
+        <v>68</v>
       </c>
       <c r="F370" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="371" spans="1:6" x14ac:dyDescent="0.25">
@@ -12214,10 +12172,10 @@
         <v>3</v>
       </c>
       <c r="D371" s="1" t="s">
-        <v>756</v>
+        <v>754</v>
       </c>
       <c r="E371" s="1" t="s">
-        <v>68</v>
+        <v>100</v>
       </c>
       <c r="F371" s="1" t="s">
         <v>5</v>
@@ -12234,10 +12192,10 @@
         <v>3</v>
       </c>
       <c r="D372" s="1" t="s">
-        <v>756</v>
+        <v>754</v>
       </c>
       <c r="E372" s="1" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="F372" s="1" t="s">
         <v>5</v>
@@ -12254,10 +12212,10 @@
         <v>3</v>
       </c>
       <c r="D373" s="1" t="s">
-        <v>756</v>
+        <v>754</v>
       </c>
       <c r="E373" s="1" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="F373" s="1" t="s">
         <v>5</v>
@@ -12274,13 +12232,13 @@
         <v>3</v>
       </c>
       <c r="D374" s="1" t="s">
-        <v>756</v>
+        <v>754</v>
       </c>
       <c r="E374" s="1" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="F374" s="1" t="s">
-        <v>5</v>
+        <v>41</v>
       </c>
     </row>
     <row r="375" spans="1:6" x14ac:dyDescent="0.25">
@@ -12294,10 +12252,10 @@
         <v>3</v>
       </c>
       <c r="D375" s="1" t="s">
-        <v>756</v>
+        <v>754</v>
       </c>
       <c r="E375" s="1" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="F375" s="1" t="s">
         <v>41</v>
@@ -12314,10 +12272,10 @@
         <v>3</v>
       </c>
       <c r="D376" s="1" t="s">
-        <v>756</v>
+        <v>754</v>
       </c>
       <c r="E376" s="1" t="s">
-        <v>112</v>
+        <v>152</v>
       </c>
       <c r="F376" s="1" t="s">
         <v>41</v>
@@ -12334,10 +12292,10 @@
         <v>3</v>
       </c>
       <c r="D377" s="1" t="s">
-        <v>756</v>
+        <v>793</v>
       </c>
       <c r="E377" s="1" t="s">
-        <v>152</v>
+        <v>4</v>
       </c>
       <c r="F377" s="1" t="s">
         <v>41</v>
@@ -12345,22 +12303,22 @@
     </row>
     <row r="378" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A378" s="1" t="s">
+        <v>794</v>
+      </c>
+      <c r="B378" s="1" t="s">
+        <v>795</v>
+      </c>
+      <c r="C378" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D378" s="1" t="s">
         <v>793</v>
       </c>
-      <c r="B378" s="1" t="s">
-        <v>794</v>
-      </c>
-      <c r="C378" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D378" s="1" t="s">
-        <v>795</v>
-      </c>
       <c r="E378" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F378" s="1" t="s">
-        <v>41</v>
+        <v>5</v>
       </c>
     </row>
     <row r="379" spans="1:6" x14ac:dyDescent="0.25">
@@ -12374,10 +12332,10 @@
         <v>3</v>
       </c>
       <c r="D379" s="1" t="s">
-        <v>795</v>
+        <v>793</v>
       </c>
       <c r="E379" s="1" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="F379" s="1" t="s">
         <v>5</v>
@@ -12394,10 +12352,10 @@
         <v>3</v>
       </c>
       <c r="D380" s="1" t="s">
-        <v>795</v>
+        <v>793</v>
       </c>
       <c r="E380" s="1" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="F380" s="1" t="s">
         <v>5</v>
@@ -12414,10 +12372,10 @@
         <v>3</v>
       </c>
       <c r="D381" s="1" t="s">
-        <v>795</v>
+        <v>793</v>
       </c>
       <c r="E381" s="1" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="F381" s="1" t="s">
         <v>5</v>
@@ -12434,13 +12392,13 @@
         <v>3</v>
       </c>
       <c r="D382" s="1" t="s">
-        <v>795</v>
+        <v>793</v>
       </c>
       <c r="E382" s="1" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="F382" s="1" t="s">
-        <v>5</v>
+        <v>41</v>
       </c>
     </row>
     <row r="383" spans="1:6" x14ac:dyDescent="0.25">
@@ -12454,13 +12412,13 @@
         <v>3</v>
       </c>
       <c r="D383" s="1" t="s">
-        <v>795</v>
+        <v>793</v>
       </c>
       <c r="E383" s="1" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="F383" s="1" t="s">
-        <v>41</v>
+        <v>5</v>
       </c>
     </row>
     <row r="384" spans="1:6" x14ac:dyDescent="0.25">
@@ -12474,10 +12432,10 @@
         <v>3</v>
       </c>
       <c r="D384" s="1" t="s">
-        <v>795</v>
+        <v>793</v>
       </c>
       <c r="E384" s="1" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="F384" s="1" t="s">
         <v>5</v>
@@ -12494,10 +12452,10 @@
         <v>3</v>
       </c>
       <c r="D385" s="1" t="s">
-        <v>795</v>
+        <v>793</v>
       </c>
       <c r="E385" s="1" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="F385" s="1" t="s">
         <v>5</v>
@@ -12514,10 +12472,10 @@
         <v>3</v>
       </c>
       <c r="D386" s="1" t="s">
-        <v>795</v>
+        <v>793</v>
       </c>
       <c r="E386" s="1" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="F386" s="1" t="s">
         <v>5</v>
@@ -12534,13 +12492,13 @@
         <v>3</v>
       </c>
       <c r="D387" s="1" t="s">
-        <v>795</v>
+        <v>793</v>
       </c>
       <c r="E387" s="1" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="F387" s="1" t="s">
-        <v>5</v>
+        <v>41</v>
       </c>
     </row>
     <row r="388" spans="1:6" x14ac:dyDescent="0.25">
@@ -12554,10 +12512,10 @@
         <v>3</v>
       </c>
       <c r="D388" s="1" t="s">
-        <v>795</v>
+        <v>793</v>
       </c>
       <c r="E388" s="1" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="F388" s="1" t="s">
         <v>41</v>
@@ -12574,13 +12532,13 @@
         <v>3</v>
       </c>
       <c r="D389" s="1" t="s">
-        <v>795</v>
+        <v>793</v>
       </c>
       <c r="E389" s="1" t="s">
-        <v>40</v>
+        <v>68</v>
       </c>
       <c r="F389" s="1" t="s">
-        <v>41</v>
+        <v>5</v>
       </c>
     </row>
     <row r="390" spans="1:6" x14ac:dyDescent="0.25">
@@ -12594,13 +12552,13 @@
         <v>3</v>
       </c>
       <c r="D390" s="1" t="s">
-        <v>795</v>
+        <v>793</v>
       </c>
       <c r="E390" s="1" t="s">
-        <v>68</v>
+        <v>100</v>
       </c>
       <c r="F390" s="1" t="s">
-        <v>5</v>
+        <v>41</v>
       </c>
     </row>
     <row r="391" spans="1:6" x14ac:dyDescent="0.25">
@@ -12614,10 +12572,10 @@
         <v>3</v>
       </c>
       <c r="D391" s="1" t="s">
-        <v>795</v>
+        <v>793</v>
       </c>
       <c r="E391" s="1" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="F391" s="1" t="s">
         <v>41</v>
@@ -12634,13 +12592,13 @@
         <v>3</v>
       </c>
       <c r="D392" s="1" t="s">
-        <v>795</v>
+        <v>793</v>
       </c>
       <c r="E392" s="1" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="F392" s="1" t="s">
-        <v>41</v>
+        <v>5</v>
       </c>
     </row>
     <row r="393" spans="1:6" x14ac:dyDescent="0.25">
@@ -12654,10 +12612,10 @@
         <v>3</v>
       </c>
       <c r="D393" s="1" t="s">
-        <v>795</v>
+        <v>793</v>
       </c>
       <c r="E393" s="1" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="F393" s="1" t="s">
         <v>5</v>
@@ -12674,13 +12632,13 @@
         <v>3</v>
       </c>
       <c r="D394" s="1" t="s">
-        <v>795</v>
+        <v>793</v>
       </c>
       <c r="E394" s="1" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="F394" s="1" t="s">
-        <v>5</v>
+        <v>41</v>
       </c>
     </row>
     <row r="395" spans="1:6" x14ac:dyDescent="0.25">
@@ -12694,13 +12652,13 @@
         <v>3</v>
       </c>
       <c r="D395" s="1" t="s">
-        <v>795</v>
+        <v>793</v>
       </c>
       <c r="E395" s="1" t="s">
-        <v>112</v>
+        <v>152</v>
       </c>
       <c r="F395" s="1" t="s">
-        <v>41</v>
+        <v>9</v>
       </c>
     </row>
     <row r="396" spans="1:6" x14ac:dyDescent="0.25">
@@ -12714,10 +12672,10 @@
         <v>3</v>
       </c>
       <c r="D396" s="1" t="s">
-        <v>795</v>
+        <v>793</v>
       </c>
       <c r="E396" s="1" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="F396" s="1" t="s">
         <v>9</v>
@@ -12734,33 +12692,33 @@
         <v>3</v>
       </c>
       <c r="D397" s="1" t="s">
-        <v>795</v>
+        <v>834</v>
       </c>
       <c r="E397" s="1" t="s">
-        <v>155</v>
+        <v>4</v>
       </c>
       <c r="F397" s="1" t="s">
-        <v>9</v>
+        <v>41</v>
       </c>
     </row>
     <row r="398" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A398" s="1" t="s">
+        <v>835</v>
+      </c>
+      <c r="B398" s="1" t="s">
+        <v>836</v>
+      </c>
+      <c r="C398" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D398" s="1" t="s">
         <v>834</v>
       </c>
-      <c r="B398" s="1" t="s">
-        <v>835</v>
-      </c>
-      <c r="C398" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D398" s="1" t="s">
-        <v>836</v>
-      </c>
       <c r="E398" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F398" s="1" t="s">
-        <v>41</v>
+        <v>80</v>
       </c>
     </row>
     <row r="399" spans="1:6" x14ac:dyDescent="0.25">
@@ -12774,10 +12732,10 @@
         <v>3</v>
       </c>
       <c r="D399" s="1" t="s">
-        <v>836</v>
+        <v>834</v>
       </c>
       <c r="E399" s="1" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="F399" s="1" t="s">
         <v>80</v>
@@ -12794,10 +12752,10 @@
         <v>3</v>
       </c>
       <c r="D400" s="1" t="s">
-        <v>836</v>
+        <v>834</v>
       </c>
       <c r="E400" s="1" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="F400" s="1" t="s">
         <v>80</v>
@@ -12814,10 +12772,10 @@
         <v>3</v>
       </c>
       <c r="D401" s="1" t="s">
-        <v>836</v>
+        <v>834</v>
       </c>
       <c r="E401" s="1" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="F401" s="1" t="s">
         <v>80</v>
@@ -12834,13 +12792,13 @@
         <v>3</v>
       </c>
       <c r="D402" s="1" t="s">
-        <v>836</v>
+        <v>834</v>
       </c>
       <c r="E402" s="1" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="F402" s="1" t="s">
-        <v>80</v>
+        <v>5</v>
       </c>
     </row>
     <row r="403" spans="1:6" x14ac:dyDescent="0.25">
@@ -12854,10 +12812,10 @@
         <v>3</v>
       </c>
       <c r="D403" s="1" t="s">
-        <v>836</v>
+        <v>834</v>
       </c>
       <c r="E403" s="1" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="F403" s="1" t="s">
         <v>5</v>
@@ -12874,13 +12832,13 @@
         <v>3</v>
       </c>
       <c r="D404" s="1" t="s">
-        <v>836</v>
+        <v>834</v>
       </c>
       <c r="E404" s="1" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="F404" s="1" t="s">
-        <v>5</v>
+        <v>25</v>
       </c>
     </row>
     <row r="405" spans="1:6" x14ac:dyDescent="0.25">
@@ -12894,10 +12852,10 @@
         <v>3</v>
       </c>
       <c r="D405" s="1" t="s">
-        <v>836</v>
+        <v>834</v>
       </c>
       <c r="E405" s="1" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="F405" s="1" t="s">
         <v>25</v>
@@ -12914,10 +12872,10 @@
         <v>3</v>
       </c>
       <c r="D406" s="1" t="s">
-        <v>836</v>
+        <v>834</v>
       </c>
       <c r="E406" s="1" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="F406" s="1" t="s">
         <v>25</v>
@@ -12934,10 +12892,10 @@
         <v>3</v>
       </c>
       <c r="D407" s="1" t="s">
-        <v>836</v>
+        <v>834</v>
       </c>
       <c r="E407" s="1" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="F407" s="1" t="s">
         <v>25</v>
@@ -12954,10 +12912,10 @@
         <v>3</v>
       </c>
       <c r="D408" s="1" t="s">
-        <v>836</v>
+        <v>834</v>
       </c>
       <c r="E408" s="1" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="F408" s="1" t="s">
         <v>25</v>
@@ -12974,10 +12932,10 @@
         <v>3</v>
       </c>
       <c r="D409" s="1" t="s">
-        <v>836</v>
+        <v>834</v>
       </c>
       <c r="E409" s="1" t="s">
-        <v>40</v>
+        <v>68</v>
       </c>
       <c r="F409" s="1" t="s">
         <v>25</v>
@@ -12994,10 +12952,10 @@
         <v>3</v>
       </c>
       <c r="D410" s="1" t="s">
-        <v>836</v>
+        <v>834</v>
       </c>
       <c r="E410" s="1" t="s">
-        <v>68</v>
+        <v>100</v>
       </c>
       <c r="F410" s="1" t="s">
         <v>25</v>
@@ -13014,10 +12972,10 @@
         <v>3</v>
       </c>
       <c r="D411" s="1" t="s">
-        <v>836</v>
+        <v>834</v>
       </c>
       <c r="E411" s="1" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="F411" s="1" t="s">
         <v>25</v>
@@ -13034,10 +12992,10 @@
         <v>3</v>
       </c>
       <c r="D412" s="1" t="s">
-        <v>836</v>
+        <v>834</v>
       </c>
       <c r="E412" s="1" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="F412" s="1" t="s">
         <v>25</v>
@@ -13054,10 +13012,10 @@
         <v>3</v>
       </c>
       <c r="D413" s="1" t="s">
-        <v>836</v>
+        <v>834</v>
       </c>
       <c r="E413" s="1" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="F413" s="1" t="s">
         <v>25</v>
@@ -13074,10 +13032,10 @@
         <v>3</v>
       </c>
       <c r="D414" s="1" t="s">
-        <v>836</v>
+        <v>834</v>
       </c>
       <c r="E414" s="1" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="F414" s="1" t="s">
         <v>25</v>
@@ -13094,13 +13052,13 @@
         <v>3</v>
       </c>
       <c r="D415" s="1" t="s">
-        <v>836</v>
+        <v>834</v>
       </c>
       <c r="E415" s="1" t="s">
-        <v>112</v>
+        <v>152</v>
       </c>
       <c r="F415" s="1" t="s">
-        <v>25</v>
+        <v>5</v>
       </c>
     </row>
     <row r="416" spans="1:6" x14ac:dyDescent="0.25">
@@ -13114,13 +13072,13 @@
         <v>3</v>
       </c>
       <c r="D416" s="1" t="s">
-        <v>836</v>
+        <v>834</v>
       </c>
       <c r="E416" s="1" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="F416" s="1" t="s">
-        <v>5</v>
+        <v>41</v>
       </c>
     </row>
     <row r="417" spans="1:6" x14ac:dyDescent="0.25">
@@ -13134,10 +13092,10 @@
         <v>3</v>
       </c>
       <c r="D417" s="1" t="s">
-        <v>836</v>
+        <v>834</v>
       </c>
       <c r="E417" s="1" t="s">
-        <v>155</v>
+        <v>158</v>
       </c>
       <c r="F417" s="1" t="s">
         <v>41</v>
@@ -13154,33 +13112,33 @@
         <v>3</v>
       </c>
       <c r="D418" s="1" t="s">
-        <v>836</v>
+        <v>877</v>
       </c>
       <c r="E418" s="1" t="s">
-        <v>158</v>
+        <v>4</v>
       </c>
       <c r="F418" s="1" t="s">
-        <v>41</v>
+        <v>5</v>
       </c>
     </row>
     <row r="419" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A419" s="1" t="s">
+        <v>878</v>
+      </c>
+      <c r="B419" s="1" t="s">
+        <v>879</v>
+      </c>
+      <c r="C419" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D419" s="1" t="s">
         <v>877</v>
       </c>
-      <c r="B419" s="1" t="s">
-        <v>878</v>
-      </c>
-      <c r="C419" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D419" s="1" t="s">
-        <v>879</v>
-      </c>
       <c r="E419" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F419" s="1" t="s">
-        <v>5</v>
+        <v>133</v>
       </c>
     </row>
     <row r="420" spans="1:6" x14ac:dyDescent="0.25">
@@ -13194,13 +13152,13 @@
         <v>3</v>
       </c>
       <c r="D420" s="1" t="s">
-        <v>879</v>
+        <v>877</v>
       </c>
       <c r="E420" s="1" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="F420" s="1" t="s">
-        <v>133</v>
+        <v>80</v>
       </c>
     </row>
     <row r="421" spans="1:6" x14ac:dyDescent="0.25">
@@ -13214,13 +13172,13 @@
         <v>3</v>
       </c>
       <c r="D421" s="1" t="s">
-        <v>879</v>
+        <v>877</v>
       </c>
       <c r="E421" s="1" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="F421" s="1" t="s">
-        <v>80</v>
+        <v>231</v>
       </c>
     </row>
     <row r="422" spans="1:6" x14ac:dyDescent="0.25">
@@ -13234,13 +13192,13 @@
         <v>3</v>
       </c>
       <c r="D422" s="1" t="s">
-        <v>879</v>
+        <v>877</v>
       </c>
       <c r="E422" s="1" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="F422" s="1" t="s">
-        <v>231</v>
+        <v>80</v>
       </c>
     </row>
     <row r="423" spans="1:6" x14ac:dyDescent="0.25">
@@ -13254,13 +13212,13 @@
         <v>3</v>
       </c>
       <c r="D423" s="1" t="s">
-        <v>879</v>
+        <v>877</v>
       </c>
       <c r="E423" s="1" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="F423" s="1" t="s">
-        <v>80</v>
+        <v>168</v>
       </c>
     </row>
     <row r="424" spans="1:6" x14ac:dyDescent="0.25">
@@ -13274,10 +13232,10 @@
         <v>3</v>
       </c>
       <c r="D424" s="1" t="s">
-        <v>879</v>
+        <v>877</v>
       </c>
       <c r="E424" s="1" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="F424" s="1" t="s">
         <v>168</v>
@@ -13294,13 +13252,13 @@
         <v>3</v>
       </c>
       <c r="D425" s="1" t="s">
-        <v>879</v>
+        <v>877</v>
       </c>
       <c r="E425" s="1" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="F425" s="1" t="s">
-        <v>168</v>
+        <v>80</v>
       </c>
     </row>
     <row r="426" spans="1:6" x14ac:dyDescent="0.25">
@@ -13314,30 +13272,30 @@
         <v>3</v>
       </c>
       <c r="D426" s="1" t="s">
-        <v>879</v>
+        <v>894</v>
       </c>
       <c r="E426" s="1" t="s">
-        <v>28</v>
+        <v>4</v>
       </c>
       <c r="F426" s="1" t="s">
-        <v>80</v>
+        <v>5</v>
       </c>
     </row>
     <row r="427" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A427" s="1" t="s">
+        <v>895</v>
+      </c>
+      <c r="B427" s="1" t="s">
+        <v>896</v>
+      </c>
+      <c r="C427" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D427" s="1" t="s">
         <v>894</v>
       </c>
-      <c r="B427" s="1" t="s">
-        <v>895</v>
-      </c>
-      <c r="C427" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D427" s="1" t="s">
-        <v>896</v>
-      </c>
       <c r="E427" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F427" s="1" t="s">
         <v>5</v>
@@ -13354,10 +13312,10 @@
         <v>3</v>
       </c>
       <c r="D428" s="1" t="s">
-        <v>896</v>
+        <v>894</v>
       </c>
       <c r="E428" s="1" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="F428" s="1" t="s">
         <v>5</v>
@@ -13374,33 +13332,33 @@
         <v>3</v>
       </c>
       <c r="D429" s="1" t="s">
-        <v>896</v>
+        <v>894</v>
       </c>
       <c r="E429" s="1" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="F429" s="1" t="s">
-        <v>5</v>
+        <v>901</v>
       </c>
     </row>
     <row r="430" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A430" s="1" t="s">
-        <v>901</v>
+        <v>902</v>
       </c>
       <c r="B430" s="1" t="s">
-        <v>902</v>
+        <v>903</v>
       </c>
       <c r="C430" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D430" s="1" t="s">
-        <v>896</v>
+        <v>894</v>
       </c>
       <c r="E430" s="1" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="F430" s="1" t="s">
-        <v>903</v>
+        <v>9</v>
       </c>
     </row>
     <row r="431" spans="1:6" x14ac:dyDescent="0.25">
@@ -13414,13 +13372,13 @@
         <v>3</v>
       </c>
       <c r="D431" s="1" t="s">
-        <v>896</v>
+        <v>894</v>
       </c>
       <c r="E431" s="1" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="F431" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="432" spans="1:6" x14ac:dyDescent="0.25">
@@ -13434,10 +13392,10 @@
         <v>3</v>
       </c>
       <c r="D432" s="1" t="s">
-        <v>896</v>
+        <v>894</v>
       </c>
       <c r="E432" s="1" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="F432" s="1" t="s">
         <v>5</v>
@@ -13454,13 +13412,13 @@
         <v>3</v>
       </c>
       <c r="D433" s="1" t="s">
-        <v>896</v>
+        <v>894</v>
       </c>
       <c r="E433" s="1" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="F433" s="1" t="s">
-        <v>5</v>
+        <v>80</v>
       </c>
     </row>
     <row r="434" spans="1:6" x14ac:dyDescent="0.25">
@@ -13474,13 +13432,13 @@
         <v>3</v>
       </c>
       <c r="D434" s="1" t="s">
-        <v>896</v>
+        <v>894</v>
       </c>
       <c r="E434" s="1" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="F434" s="1" t="s">
-        <v>80</v>
+        <v>25</v>
       </c>
     </row>
     <row r="435" spans="1:6" x14ac:dyDescent="0.25">
@@ -13494,13 +13452,13 @@
         <v>3</v>
       </c>
       <c r="D435" s="1" t="s">
-        <v>896</v>
+        <v>894</v>
       </c>
       <c r="E435" s="1" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="F435" s="1" t="s">
-        <v>25</v>
+        <v>5</v>
       </c>
     </row>
     <row r="436" spans="1:6" x14ac:dyDescent="0.25">
@@ -13514,10 +13472,10 @@
         <v>3</v>
       </c>
       <c r="D436" s="1" t="s">
-        <v>896</v>
+        <v>894</v>
       </c>
       <c r="E436" s="1" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="F436" s="1" t="s">
         <v>5</v>
@@ -13534,13 +13492,13 @@
         <v>3</v>
       </c>
       <c r="D437" s="1" t="s">
-        <v>896</v>
+        <v>894</v>
       </c>
       <c r="E437" s="1" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="F437" s="1" t="s">
-        <v>5</v>
+        <v>25</v>
       </c>
     </row>
     <row r="438" spans="1:6" x14ac:dyDescent="0.25">
@@ -13554,13 +13512,13 @@
         <v>3</v>
       </c>
       <c r="D438" s="1" t="s">
-        <v>896</v>
+        <v>894</v>
       </c>
       <c r="E438" s="1" t="s">
-        <v>40</v>
+        <v>68</v>
       </c>
       <c r="F438" s="1" t="s">
-        <v>25</v>
+        <v>5</v>
       </c>
     </row>
     <row r="439" spans="1:6" x14ac:dyDescent="0.25">
@@ -13574,10 +13532,10 @@
         <v>3</v>
       </c>
       <c r="D439" s="1" t="s">
-        <v>896</v>
+        <v>894</v>
       </c>
       <c r="E439" s="1" t="s">
-        <v>68</v>
+        <v>100</v>
       </c>
       <c r="F439" s="1" t="s">
         <v>5</v>
@@ -13594,10 +13552,10 @@
         <v>3</v>
       </c>
       <c r="D440" s="1" t="s">
-        <v>896</v>
+        <v>894</v>
       </c>
       <c r="E440" s="1" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="F440" s="1" t="s">
         <v>5</v>
@@ -13614,10 +13572,10 @@
         <v>3</v>
       </c>
       <c r="D441" s="1" t="s">
-        <v>896</v>
+        <v>894</v>
       </c>
       <c r="E441" s="1" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="F441" s="1" t="s">
         <v>5</v>
@@ -13634,10 +13592,10 @@
         <v>3</v>
       </c>
       <c r="D442" s="1" t="s">
-        <v>896</v>
+        <v>928</v>
       </c>
       <c r="E442" s="1" t="s">
-        <v>106</v>
+        <v>4</v>
       </c>
       <c r="F442" s="1" t="s">
         <v>5</v>
@@ -13645,19 +13603,19 @@
     </row>
     <row r="443" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A443" s="1" t="s">
+        <v>929</v>
+      </c>
+      <c r="B443" s="1" t="s">
+        <v>930</v>
+      </c>
+      <c r="C443" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D443" s="1" t="s">
         <v>928</v>
       </c>
-      <c r="B443" s="1" t="s">
-        <v>929</v>
-      </c>
-      <c r="C443" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D443" s="1" t="s">
-        <v>930</v>
-      </c>
       <c r="E443" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F443" s="1" t="s">
         <v>5</v>
@@ -13674,10 +13632,10 @@
         <v>3</v>
       </c>
       <c r="D444" s="1" t="s">
-        <v>930</v>
+        <v>928</v>
       </c>
       <c r="E444" s="1" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="F444" s="1" t="s">
         <v>5</v>
@@ -13694,10 +13652,10 @@
         <v>3</v>
       </c>
       <c r="D445" s="1" t="s">
-        <v>930</v>
+        <v>928</v>
       </c>
       <c r="E445" s="1" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="F445" s="1" t="s">
         <v>5</v>
@@ -13714,13 +13672,13 @@
         <v>3</v>
       </c>
       <c r="D446" s="1" t="s">
-        <v>930</v>
+        <v>928</v>
       </c>
       <c r="E446" s="1" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="F446" s="1" t="s">
-        <v>5</v>
+        <v>41</v>
       </c>
     </row>
     <row r="447" spans="1:6" x14ac:dyDescent="0.25">
@@ -13734,10 +13692,10 @@
         <v>3</v>
       </c>
       <c r="D447" s="1" t="s">
-        <v>930</v>
+        <v>928</v>
       </c>
       <c r="E447" s="1" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="F447" s="1" t="s">
         <v>41</v>
@@ -13754,13 +13712,13 @@
         <v>3</v>
       </c>
       <c r="D448" s="1" t="s">
-        <v>930</v>
+        <v>928</v>
       </c>
       <c r="E448" s="1" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="F448" s="1" t="s">
-        <v>41</v>
+        <v>80</v>
       </c>
     </row>
     <row r="449" spans="1:6" x14ac:dyDescent="0.25">
@@ -13774,13 +13732,13 @@
         <v>3</v>
       </c>
       <c r="D449" s="1" t="s">
-        <v>930</v>
+        <v>928</v>
       </c>
       <c r="E449" s="1" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="F449" s="1" t="s">
-        <v>80</v>
+        <v>168</v>
       </c>
     </row>
     <row r="450" spans="1:6" x14ac:dyDescent="0.25">
@@ -13794,13 +13752,13 @@
         <v>3</v>
       </c>
       <c r="D450" s="1" t="s">
-        <v>930</v>
+        <v>928</v>
       </c>
       <c r="E450" s="1" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="F450" s="1" t="s">
-        <v>168</v>
+        <v>25</v>
       </c>
     </row>
     <row r="451" spans="1:6" x14ac:dyDescent="0.25">
@@ -13814,13 +13772,13 @@
         <v>3</v>
       </c>
       <c r="D451" s="1" t="s">
-        <v>930</v>
+        <v>928</v>
       </c>
       <c r="E451" s="1" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="F451" s="1" t="s">
-        <v>25</v>
+        <v>5</v>
       </c>
     </row>
     <row r="452" spans="1:6" x14ac:dyDescent="0.25">
@@ -13834,13 +13792,13 @@
         <v>3</v>
       </c>
       <c r="D452" s="1" t="s">
-        <v>930</v>
+        <v>928</v>
       </c>
       <c r="E452" s="1" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="F452" s="1" t="s">
-        <v>5</v>
+        <v>41</v>
       </c>
     </row>
     <row r="453" spans="1:6" x14ac:dyDescent="0.25">
@@ -13854,10 +13812,10 @@
         <v>3</v>
       </c>
       <c r="D453" s="1" t="s">
-        <v>930</v>
+        <v>928</v>
       </c>
       <c r="E453" s="1" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="F453" s="1" t="s">
         <v>41</v>
@@ -13874,10 +13832,10 @@
         <v>3</v>
       </c>
       <c r="D454" s="1" t="s">
-        <v>930</v>
+        <v>928</v>
       </c>
       <c r="E454" s="1" t="s">
-        <v>40</v>
+        <v>68</v>
       </c>
       <c r="F454" s="1" t="s">
         <v>41</v>
@@ -13894,13 +13852,13 @@
         <v>3</v>
       </c>
       <c r="D455" s="1" t="s">
-        <v>930</v>
+        <v>928</v>
       </c>
       <c r="E455" s="1" t="s">
-        <v>68</v>
+        <v>100</v>
       </c>
       <c r="F455" s="1" t="s">
-        <v>41</v>
+        <v>9</v>
       </c>
     </row>
     <row r="456" spans="1:6" x14ac:dyDescent="0.25">
@@ -13914,13 +13872,13 @@
         <v>3</v>
       </c>
       <c r="D456" s="1" t="s">
-        <v>930</v>
+        <v>928</v>
       </c>
       <c r="E456" s="1" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="F456" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="457" spans="1:6" x14ac:dyDescent="0.25">
@@ -13934,30 +13892,30 @@
         <v>3</v>
       </c>
       <c r="D457" s="1" t="s">
-        <v>930</v>
+        <v>959</v>
       </c>
       <c r="E457" s="1" t="s">
-        <v>103</v>
+        <v>4</v>
       </c>
       <c r="F457" s="1" t="s">
-        <v>5</v>
+        <v>80</v>
       </c>
     </row>
     <row r="458" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A458" s="1" t="s">
+        <v>960</v>
+      </c>
+      <c r="B458" s="1" t="s">
+        <v>961</v>
+      </c>
+      <c r="C458" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D458" s="1" t="s">
         <v>959</v>
       </c>
-      <c r="B458" s="1" t="s">
-        <v>960</v>
-      </c>
-      <c r="C458" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D458" s="1" t="s">
-        <v>961</v>
-      </c>
       <c r="E458" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F458" s="1" t="s">
         <v>80</v>
@@ -13974,10 +13932,10 @@
         <v>3</v>
       </c>
       <c r="D459" s="1" t="s">
-        <v>961</v>
+        <v>959</v>
       </c>
       <c r="E459" s="1" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="F459" s="1" t="s">
         <v>80</v>
@@ -13994,10 +13952,10 @@
         <v>3</v>
       </c>
       <c r="D460" s="1" t="s">
-        <v>961</v>
+        <v>959</v>
       </c>
       <c r="E460" s="1" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="F460" s="1" t="s">
         <v>80</v>
@@ -14014,10 +13972,10 @@
         <v>3</v>
       </c>
       <c r="D461" s="1" t="s">
-        <v>961</v>
+        <v>959</v>
       </c>
       <c r="E461" s="1" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="F461" s="1" t="s">
         <v>80</v>
@@ -14034,10 +13992,10 @@
         <v>3</v>
       </c>
       <c r="D462" s="1" t="s">
-        <v>961</v>
+        <v>959</v>
       </c>
       <c r="E462" s="1" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="F462" s="1" t="s">
         <v>80</v>
@@ -14054,13 +14012,13 @@
         <v>3</v>
       </c>
       <c r="D463" s="1" t="s">
-        <v>961</v>
+        <v>959</v>
       </c>
       <c r="E463" s="1" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="F463" s="1" t="s">
-        <v>80</v>
+        <v>133</v>
       </c>
     </row>
     <row r="464" spans="1:6" x14ac:dyDescent="0.25">
@@ -14074,10 +14032,10 @@
         <v>3</v>
       </c>
       <c r="D464" s="1" t="s">
-        <v>961</v>
+        <v>959</v>
       </c>
       <c r="E464" s="1" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="F464" s="1" t="s">
         <v>133</v>
@@ -14094,13 +14052,13 @@
         <v>3</v>
       </c>
       <c r="D465" s="1" t="s">
-        <v>961</v>
+        <v>959</v>
       </c>
       <c r="E465" s="1" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="F465" s="1" t="s">
-        <v>133</v>
+        <v>25</v>
       </c>
     </row>
     <row r="466" spans="1:6" x14ac:dyDescent="0.25">
@@ -14114,10 +14072,10 @@
         <v>3</v>
       </c>
       <c r="D466" s="1" t="s">
-        <v>961</v>
+        <v>959</v>
       </c>
       <c r="E466" s="1" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="F466" s="1" t="s">
         <v>25</v>
@@ -14134,13 +14092,13 @@
         <v>3</v>
       </c>
       <c r="D467" s="1" t="s">
-        <v>961</v>
+        <v>959</v>
       </c>
       <c r="E467" s="1" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="F467" s="1" t="s">
-        <v>25</v>
+        <v>80</v>
       </c>
     </row>
     <row r="468" spans="1:6" x14ac:dyDescent="0.25">
@@ -14154,10 +14112,10 @@
         <v>3</v>
       </c>
       <c r="D468" s="1" t="s">
-        <v>961</v>
+        <v>959</v>
       </c>
       <c r="E468" s="1" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="F468" s="1" t="s">
         <v>80</v>
@@ -14174,13 +14132,13 @@
         <v>3</v>
       </c>
       <c r="D469" s="1" t="s">
-        <v>961</v>
+        <v>959</v>
       </c>
       <c r="E469" s="1" t="s">
-        <v>40</v>
+        <v>68</v>
       </c>
       <c r="F469" s="1" t="s">
-        <v>80</v>
+        <v>5</v>
       </c>
     </row>
     <row r="470" spans="1:6" x14ac:dyDescent="0.25">
@@ -14194,10 +14152,10 @@
         <v>3</v>
       </c>
       <c r="D470" s="1" t="s">
-        <v>961</v>
+        <v>959</v>
       </c>
       <c r="E470" s="1" t="s">
-        <v>68</v>
+        <v>100</v>
       </c>
       <c r="F470" s="1" t="s">
         <v>5</v>
@@ -14214,10 +14172,10 @@
         <v>3</v>
       </c>
       <c r="D471" s="1" t="s">
-        <v>961</v>
+        <v>959</v>
       </c>
       <c r="E471" s="1" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="F471" s="1" t="s">
         <v>5</v>
@@ -14234,33 +14192,33 @@
         <v>3</v>
       </c>
       <c r="D472" s="1" t="s">
-        <v>961</v>
+        <v>990</v>
       </c>
       <c r="E472" s="1" t="s">
-        <v>103</v>
+        <v>4</v>
       </c>
       <c r="F472" s="1" t="s">
-        <v>5</v>
+        <v>80</v>
       </c>
     </row>
     <row r="473" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A473" s="1" t="s">
+        <v>991</v>
+      </c>
+      <c r="B473" s="1" t="s">
+        <v>992</v>
+      </c>
+      <c r="C473" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D473" s="1" t="s">
         <v>990</v>
       </c>
-      <c r="B473" s="1" t="s">
-        <v>991</v>
-      </c>
-      <c r="C473" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D473" s="1" t="s">
-        <v>992</v>
-      </c>
       <c r="E473" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F473" s="1" t="s">
-        <v>80</v>
+        <v>5</v>
       </c>
     </row>
     <row r="474" spans="1:6" x14ac:dyDescent="0.25">
@@ -14274,33 +14232,33 @@
         <v>3</v>
       </c>
       <c r="D474" s="1" t="s">
-        <v>992</v>
+        <v>990</v>
       </c>
       <c r="E474" s="1" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="F474" s="1" t="s">
-        <v>5</v>
+        <v>995</v>
       </c>
     </row>
     <row r="475" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A475" s="1" t="s">
+        <v>996</v>
+      </c>
+      <c r="B475" s="1" t="s">
+        <v>997</v>
+      </c>
+      <c r="C475" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D475" s="1" t="s">
+        <v>990</v>
+      </c>
+      <c r="E475" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="F475" s="1" t="s">
         <v>995</v>
-      </c>
-      <c r="B475" s="1" t="s">
-        <v>996</v>
-      </c>
-      <c r="C475" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D475" s="1" t="s">
-        <v>992</v>
-      </c>
-      <c r="E475" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="F475" s="1" t="s">
-        <v>997</v>
       </c>
     </row>
     <row r="476" spans="1:6" x14ac:dyDescent="0.25">
@@ -14314,13 +14272,13 @@
         <v>3</v>
       </c>
       <c r="D476" s="1" t="s">
-        <v>992</v>
+        <v>990</v>
       </c>
       <c r="E476" s="1" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="F476" s="1" t="s">
-        <v>997</v>
+        <v>5</v>
       </c>
     </row>
     <row r="477" spans="1:6" x14ac:dyDescent="0.25">
@@ -14334,10 +14292,10 @@
         <v>3</v>
       </c>
       <c r="D477" s="1" t="s">
-        <v>992</v>
+        <v>990</v>
       </c>
       <c r="E477" s="1" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="F477" s="1" t="s">
         <v>5</v>
@@ -14354,10 +14312,10 @@
         <v>3</v>
       </c>
       <c r="D478" s="1" t="s">
-        <v>992</v>
+        <v>990</v>
       </c>
       <c r="E478" s="1" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="F478" s="1" t="s">
         <v>5</v>
@@ -14374,10 +14332,10 @@
         <v>3</v>
       </c>
       <c r="D479" s="1" t="s">
-        <v>992</v>
+        <v>990</v>
       </c>
       <c r="E479" s="1" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="F479" s="1" t="s">
         <v>5</v>
@@ -14394,10 +14352,10 @@
         <v>3</v>
       </c>
       <c r="D480" s="1" t="s">
-        <v>992</v>
+        <v>990</v>
       </c>
       <c r="E480" s="1" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="F480" s="1" t="s">
         <v>5</v>
@@ -14414,10 +14372,10 @@
         <v>3</v>
       </c>
       <c r="D481" s="1" t="s">
-        <v>992</v>
+        <v>990</v>
       </c>
       <c r="E481" s="1" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="F481" s="1" t="s">
         <v>5</v>
@@ -14434,10 +14392,10 @@
         <v>3</v>
       </c>
       <c r="D482" s="1" t="s">
-        <v>992</v>
+        <v>990</v>
       </c>
       <c r="E482" s="1" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="F482" s="1" t="s">
         <v>5</v>
@@ -14454,10 +14412,10 @@
         <v>3</v>
       </c>
       <c r="D483" s="1" t="s">
-        <v>992</v>
+        <v>990</v>
       </c>
       <c r="E483" s="1" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="F483" s="1" t="s">
         <v>5</v>
@@ -14474,10 +14432,10 @@
         <v>3</v>
       </c>
       <c r="D484" s="1" t="s">
-        <v>992</v>
+        <v>990</v>
       </c>
       <c r="E484" s="1" t="s">
-        <v>40</v>
+        <v>68</v>
       </c>
       <c r="F484" s="1" t="s">
         <v>5</v>
@@ -14494,10 +14452,10 @@
         <v>3</v>
       </c>
       <c r="D485" s="1" t="s">
-        <v>992</v>
+        <v>990</v>
       </c>
       <c r="E485" s="1" t="s">
-        <v>68</v>
+        <v>100</v>
       </c>
       <c r="F485" s="1" t="s">
         <v>5</v>
@@ -14514,10 +14472,10 @@
         <v>3</v>
       </c>
       <c r="D486" s="1" t="s">
-        <v>992</v>
+        <v>990</v>
       </c>
       <c r="E486" s="1" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="F486" s="1" t="s">
         <v>5</v>
@@ -14534,10 +14492,10 @@
         <v>3</v>
       </c>
       <c r="D487" s="1" t="s">
-        <v>992</v>
+        <v>990</v>
       </c>
       <c r="E487" s="1" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="F487" s="1" t="s">
         <v>5</v>
@@ -14554,33 +14512,33 @@
         <v>3</v>
       </c>
       <c r="D488" s="1" t="s">
-        <v>992</v>
+        <v>1024</v>
       </c>
       <c r="E488" s="1" t="s">
-        <v>106</v>
+        <v>4</v>
       </c>
       <c r="F488" s="1" t="s">
-        <v>5</v>
+        <v>25</v>
       </c>
     </row>
     <row r="489" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A489" s="1" t="s">
+        <v>1025</v>
+      </c>
+      <c r="B489" s="1" t="s">
+        <v>1026</v>
+      </c>
+      <c r="C489" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D489" s="1" t="s">
         <v>1024</v>
       </c>
-      <c r="B489" s="1" t="s">
-        <v>1025</v>
-      </c>
-      <c r="C489" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D489" s="1" t="s">
-        <v>1026</v>
-      </c>
       <c r="E489" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F489" s="1" t="s">
-        <v>25</v>
+        <v>5</v>
       </c>
     </row>
     <row r="490" spans="1:6" x14ac:dyDescent="0.25">
@@ -14594,10 +14552,10 @@
         <v>3</v>
       </c>
       <c r="D490" s="1" t="s">
-        <v>1026</v>
+        <v>1024</v>
       </c>
       <c r="E490" s="1" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="F490" s="1" t="s">
         <v>5</v>
@@ -14614,10 +14572,10 @@
         <v>3</v>
       </c>
       <c r="D491" s="1" t="s">
-        <v>1026</v>
+        <v>1024</v>
       </c>
       <c r="E491" s="1" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="F491" s="1" t="s">
         <v>5</v>
@@ -14634,13 +14592,13 @@
         <v>3</v>
       </c>
       <c r="D492" s="1" t="s">
-        <v>1026</v>
+        <v>1024</v>
       </c>
       <c r="E492" s="1" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="F492" s="1" t="s">
-        <v>5</v>
+        <v>133</v>
       </c>
     </row>
     <row r="493" spans="1:6" x14ac:dyDescent="0.25">
@@ -14654,10 +14612,10 @@
         <v>3</v>
       </c>
       <c r="D493" s="1" t="s">
-        <v>1026</v>
+        <v>1024</v>
       </c>
       <c r="E493" s="1" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="F493" s="1" t="s">
         <v>133</v>
@@ -14674,13 +14632,13 @@
         <v>3</v>
       </c>
       <c r="D494" s="1" t="s">
-        <v>1026</v>
+        <v>1024</v>
       </c>
       <c r="E494" s="1" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="F494" s="1" t="s">
-        <v>133</v>
+        <v>5</v>
       </c>
     </row>
     <row r="495" spans="1:6" x14ac:dyDescent="0.25">
@@ -14694,10 +14652,10 @@
         <v>3</v>
       </c>
       <c r="D495" s="1" t="s">
-        <v>1026</v>
+        <v>1024</v>
       </c>
       <c r="E495" s="1" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="F495" s="1" t="s">
         <v>5</v>
@@ -14714,10 +14672,10 @@
         <v>3</v>
       </c>
       <c r="D496" s="1" t="s">
-        <v>1026</v>
+        <v>1024</v>
       </c>
       <c r="E496" s="1" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="F496" s="1" t="s">
         <v>5</v>
@@ -14734,33 +14692,33 @@
         <v>3</v>
       </c>
       <c r="D497" s="1" t="s">
-        <v>1026</v>
+        <v>1024</v>
       </c>
       <c r="E497" s="1" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="F497" s="1" t="s">
-        <v>5</v>
+        <v>1043</v>
       </c>
     </row>
     <row r="498" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A498" s="1" t="s">
-        <v>1043</v>
+        <v>1044</v>
       </c>
       <c r="B498" s="1" t="s">
-        <v>1044</v>
+        <v>1045</v>
       </c>
       <c r="C498" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D498" s="1" t="s">
-        <v>1026</v>
+        <v>1024</v>
       </c>
       <c r="E498" s="1" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="F498" s="1" t="s">
-        <v>1045</v>
+        <v>5</v>
       </c>
     </row>
     <row r="499" spans="1:6" x14ac:dyDescent="0.25">
@@ -14774,10 +14732,10 @@
         <v>3</v>
       </c>
       <c r="D499" s="1" t="s">
-        <v>1026</v>
+        <v>1024</v>
       </c>
       <c r="E499" s="1" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="F499" s="1" t="s">
         <v>5</v>
@@ -14794,10 +14752,10 @@
         <v>3</v>
       </c>
       <c r="D500" s="1" t="s">
-        <v>1026</v>
+        <v>1024</v>
       </c>
       <c r="E500" s="1" t="s">
-        <v>40</v>
+        <v>68</v>
       </c>
       <c r="F500" s="1" t="s">
         <v>5</v>
@@ -14814,10 +14772,10 @@
         <v>3</v>
       </c>
       <c r="D501" s="1" t="s">
-        <v>1026</v>
+        <v>1024</v>
       </c>
       <c r="E501" s="1" t="s">
-        <v>68</v>
+        <v>100</v>
       </c>
       <c r="F501" s="1" t="s">
         <v>5</v>
@@ -14834,10 +14792,10 @@
         <v>3</v>
       </c>
       <c r="D502" s="1" t="s">
-        <v>1026</v>
+        <v>1024</v>
       </c>
       <c r="E502" s="1" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="F502" s="1" t="s">
         <v>5</v>
@@ -14854,10 +14812,10 @@
         <v>3</v>
       </c>
       <c r="D503" s="1" t="s">
-        <v>1026</v>
+        <v>1024</v>
       </c>
       <c r="E503" s="1" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="F503" s="1" t="s">
         <v>5</v>
@@ -14874,13 +14832,13 @@
         <v>3</v>
       </c>
       <c r="D504" s="1" t="s">
-        <v>1026</v>
+        <v>1024</v>
       </c>
       <c r="E504" s="1" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="F504" s="1" t="s">
-        <v>5</v>
+        <v>25</v>
       </c>
     </row>
     <row r="505" spans="1:6" x14ac:dyDescent="0.25">
@@ -14894,10 +14852,10 @@
         <v>3</v>
       </c>
       <c r="D505" s="1" t="s">
-        <v>1026</v>
+        <v>1024</v>
       </c>
       <c r="E505" s="1" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="F505" s="1" t="s">
         <v>25</v>
@@ -14914,33 +14872,33 @@
         <v>3</v>
       </c>
       <c r="D506" s="1" t="s">
-        <v>1026</v>
+        <v>1062</v>
       </c>
       <c r="E506" s="1" t="s">
-        <v>112</v>
+        <v>4</v>
       </c>
       <c r="F506" s="1" t="s">
-        <v>25</v>
+        <v>5</v>
       </c>
     </row>
     <row r="507" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A507" s="1" t="s">
+        <v>1063</v>
+      </c>
+      <c r="B507" s="1" t="s">
+        <v>1064</v>
+      </c>
+      <c r="C507" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D507" s="1" t="s">
         <v>1062</v>
       </c>
-      <c r="B507" s="1" t="s">
-        <v>1063</v>
-      </c>
-      <c r="C507" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D507" s="1" t="s">
-        <v>1064</v>
-      </c>
       <c r="E507" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F507" s="1" t="s">
-        <v>716</v>
+        <v>5</v>
       </c>
     </row>
     <row r="508" spans="1:6" x14ac:dyDescent="0.25">
@@ -14954,10 +14912,10 @@
         <v>3</v>
       </c>
       <c r="D508" s="1" t="s">
-        <v>1064</v>
+        <v>1062</v>
       </c>
       <c r="E508" s="1" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="F508" s="1" t="s">
         <v>5</v>
@@ -14974,10 +14932,10 @@
         <v>3</v>
       </c>
       <c r="D509" s="1" t="s">
-        <v>1064</v>
+        <v>1062</v>
       </c>
       <c r="E509" s="1" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="F509" s="1" t="s">
         <v>5</v>
@@ -14994,10 +14952,10 @@
         <v>3</v>
       </c>
       <c r="D510" s="1" t="s">
-        <v>1064</v>
+        <v>1062</v>
       </c>
       <c r="E510" s="1" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="F510" s="1" t="s">
         <v>5</v>
@@ -15014,10 +14972,10 @@
         <v>3</v>
       </c>
       <c r="D511" s="1" t="s">
-        <v>1064</v>
+        <v>1062</v>
       </c>
       <c r="E511" s="1" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="F511" s="1" t="s">
         <v>5</v>
@@ -15034,10 +14992,10 @@
         <v>3</v>
       </c>
       <c r="D512" s="1" t="s">
-        <v>1064</v>
+        <v>1062</v>
       </c>
       <c r="E512" s="1" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="F512" s="1" t="s">
         <v>5</v>
@@ -15054,10 +15012,10 @@
         <v>3</v>
       </c>
       <c r="D513" s="1" t="s">
-        <v>1064</v>
+        <v>1062</v>
       </c>
       <c r="E513" s="1" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="F513" s="1" t="s">
         <v>5</v>
@@ -15074,10 +15032,10 @@
         <v>3</v>
       </c>
       <c r="D514" s="1" t="s">
-        <v>1064</v>
+        <v>1062</v>
       </c>
       <c r="E514" s="1" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="F514" s="1" t="s">
         <v>5</v>
@@ -15094,10 +15052,10 @@
         <v>3</v>
       </c>
       <c r="D515" s="1" t="s">
-        <v>1064</v>
+        <v>1062</v>
       </c>
       <c r="E515" s="1" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="F515" s="1" t="s">
         <v>5</v>
@@ -15114,10 +15072,10 @@
         <v>3</v>
       </c>
       <c r="D516" s="1" t="s">
-        <v>1064</v>
+        <v>1062</v>
       </c>
       <c r="E516" s="1" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="F516" s="1" t="s">
         <v>5</v>
@@ -15134,10 +15092,10 @@
         <v>3</v>
       </c>
       <c r="D517" s="1" t="s">
-        <v>1064</v>
+        <v>1062</v>
       </c>
       <c r="E517" s="1" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="F517" s="1" t="s">
         <v>5</v>
@@ -15154,10 +15112,10 @@
         <v>3</v>
       </c>
       <c r="D518" s="1" t="s">
-        <v>1064</v>
+        <v>1062</v>
       </c>
       <c r="E518" s="1" t="s">
-        <v>40</v>
+        <v>68</v>
       </c>
       <c r="F518" s="1" t="s">
         <v>5</v>
@@ -15174,10 +15132,10 @@
         <v>3</v>
       </c>
       <c r="D519" s="1" t="s">
-        <v>1064</v>
+        <v>1062</v>
       </c>
       <c r="E519" s="1" t="s">
-        <v>68</v>
+        <v>100</v>
       </c>
       <c r="F519" s="1" t="s">
         <v>5</v>
@@ -15194,10 +15152,10 @@
         <v>3</v>
       </c>
       <c r="D520" s="1" t="s">
-        <v>1064</v>
+        <v>1062</v>
       </c>
       <c r="E520" s="1" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="F520" s="1" t="s">
         <v>5</v>
@@ -15214,33 +15172,33 @@
         <v>3</v>
       </c>
       <c r="D521" s="1" t="s">
-        <v>1064</v>
+        <v>1093</v>
       </c>
       <c r="E521" s="1" t="s">
-        <v>103</v>
+        <v>4</v>
       </c>
       <c r="F521" s="1" t="s">
-        <v>5</v>
+        <v>80</v>
       </c>
     </row>
     <row r="522" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A522" s="1" t="s">
+        <v>1094</v>
+      </c>
+      <c r="B522" s="1" t="s">
+        <v>1095</v>
+      </c>
+      <c r="C522" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D522" s="1" t="s">
         <v>1093</v>
-      </c>
-      <c r="B522" s="1" t="s">
-        <v>1094</v>
-      </c>
-      <c r="C522" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D522" s="1" t="s">
-        <v>1095</v>
       </c>
       <c r="E522" s="1" t="s">
         <v>4</v>
       </c>
       <c r="F522" s="1" t="s">
-        <v>80</v>
+        <v>25</v>
       </c>
     </row>
     <row r="523" spans="1:6" x14ac:dyDescent="0.25">
@@ -15254,13 +15212,13 @@
         <v>3</v>
       </c>
       <c r="D523" s="1" t="s">
-        <v>1095</v>
+        <v>1093</v>
       </c>
       <c r="E523" s="1" t="s">
         <v>4</v>
       </c>
       <c r="F523" s="1" t="s">
-        <v>25</v>
+        <v>5</v>
       </c>
     </row>
     <row r="524" spans="1:6" x14ac:dyDescent="0.25">
@@ -15274,13 +15232,13 @@
         <v>3</v>
       </c>
       <c r="D524" s="1" t="s">
-        <v>1095</v>
+        <v>1093</v>
       </c>
       <c r="E524" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F524" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="525" spans="1:6" x14ac:dyDescent="0.25">
@@ -15294,13 +15252,13 @@
         <v>3</v>
       </c>
       <c r="D525" s="1" t="s">
-        <v>1095</v>
+        <v>1093</v>
       </c>
       <c r="E525" s="1" t="s">
         <v>8</v>
       </c>
       <c r="F525" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="526" spans="1:6" x14ac:dyDescent="0.25">
@@ -15314,7 +15272,7 @@
         <v>3</v>
       </c>
       <c r="D526" s="1" t="s">
-        <v>1095</v>
+        <v>1093</v>
       </c>
       <c r="E526" s="1" t="s">
         <v>8</v>
@@ -15334,10 +15292,10 @@
         <v>3</v>
       </c>
       <c r="D527" s="1" t="s">
-        <v>1095</v>
+        <v>1093</v>
       </c>
       <c r="E527" s="1" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="F527" s="1" t="s">
         <v>5</v>
@@ -15354,7 +15312,7 @@
         <v>3</v>
       </c>
       <c r="D528" s="1" t="s">
-        <v>1095</v>
+        <v>1093</v>
       </c>
       <c r="E528" s="1" t="s">
         <v>12</v>
@@ -15374,7 +15332,7 @@
         <v>3</v>
       </c>
       <c r="D529" s="1" t="s">
-        <v>1095</v>
+        <v>1093</v>
       </c>
       <c r="E529" s="1" t="s">
         <v>12</v>
@@ -15394,10 +15352,10 @@
         <v>3</v>
       </c>
       <c r="D530" s="1" t="s">
-        <v>1095</v>
+        <v>1093</v>
       </c>
       <c r="E530" s="1" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="F530" s="1" t="s">
         <v>5</v>
@@ -15414,7 +15372,7 @@
         <v>3</v>
       </c>
       <c r="D531" s="1" t="s">
-        <v>1095</v>
+        <v>1093</v>
       </c>
       <c r="E531" s="1" t="s">
         <v>15</v>
@@ -15434,7 +15392,7 @@
         <v>3</v>
       </c>
       <c r="D532" s="1" t="s">
-        <v>1095</v>
+        <v>1093</v>
       </c>
       <c r="E532" s="1" t="s">
         <v>15</v>
@@ -15454,10 +15412,10 @@
         <v>3</v>
       </c>
       <c r="D533" s="1" t="s">
-        <v>1095</v>
+        <v>1093</v>
       </c>
       <c r="E533" s="1" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="F533" s="1" t="s">
         <v>5</v>
@@ -15474,7 +15432,7 @@
         <v>3</v>
       </c>
       <c r="D534" s="1" t="s">
-        <v>1095</v>
+        <v>1093</v>
       </c>
       <c r="E534" s="1" t="s">
         <v>18</v>
@@ -15494,7 +15452,7 @@
         <v>3</v>
       </c>
       <c r="D535" s="1" t="s">
-        <v>1095</v>
+        <v>1093</v>
       </c>
       <c r="E535" s="1" t="s">
         <v>18</v>
@@ -15514,13 +15472,13 @@
         <v>3</v>
       </c>
       <c r="D536" s="1" t="s">
-        <v>1095</v>
+        <v>1093</v>
       </c>
       <c r="E536" s="1" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="F536" s="1" t="s">
-        <v>5</v>
+        <v>80</v>
       </c>
     </row>
     <row r="537" spans="1:6" x14ac:dyDescent="0.25">
@@ -15534,13 +15492,13 @@
         <v>3</v>
       </c>
       <c r="D537" s="1" t="s">
-        <v>1095</v>
+        <v>1093</v>
       </c>
       <c r="E537" s="1" t="s">
         <v>21</v>
       </c>
       <c r="F537" s="1" t="s">
-        <v>80</v>
+        <v>5</v>
       </c>
     </row>
     <row r="538" spans="1:6" x14ac:dyDescent="0.25">
@@ -15554,7 +15512,7 @@
         <v>3</v>
       </c>
       <c r="D538" s="1" t="s">
-        <v>1095</v>
+        <v>1093</v>
       </c>
       <c r="E538" s="1" t="s">
         <v>21</v>
@@ -15574,13 +15532,13 @@
         <v>3</v>
       </c>
       <c r="D539" s="1" t="s">
-        <v>1095</v>
+        <v>1093</v>
       </c>
       <c r="E539" s="1" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="F539" s="1" t="s">
-        <v>5</v>
+        <v>80</v>
       </c>
     </row>
     <row r="540" spans="1:6" x14ac:dyDescent="0.25">
@@ -15594,13 +15552,13 @@
         <v>3</v>
       </c>
       <c r="D540" s="1" t="s">
-        <v>1095</v>
+        <v>1093</v>
       </c>
       <c r="E540" s="1" t="s">
         <v>24</v>
       </c>
       <c r="F540" s="1" t="s">
-        <v>80</v>
+        <v>5</v>
       </c>
     </row>
     <row r="541" spans="1:6" x14ac:dyDescent="0.25">
@@ -15614,13 +15572,13 @@
         <v>3</v>
       </c>
       <c r="D541" s="1" t="s">
-        <v>1095</v>
+        <v>1093</v>
       </c>
       <c r="E541" s="1" t="s">
         <v>24</v>
       </c>
       <c r="F541" s="1" t="s">
-        <v>5</v>
+        <v>80</v>
       </c>
     </row>
     <row r="542" spans="1:6" x14ac:dyDescent="0.25">
@@ -15634,10 +15592,10 @@
         <v>3</v>
       </c>
       <c r="D542" s="1" t="s">
-        <v>1095</v>
+        <v>1093</v>
       </c>
       <c r="E542" s="1" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="F542" s="1" t="s">
         <v>80</v>
@@ -15654,13 +15612,13 @@
         <v>3</v>
       </c>
       <c r="D543" s="1" t="s">
-        <v>1095</v>
+        <v>1093</v>
       </c>
       <c r="E543" s="1" t="s">
         <v>28</v>
       </c>
       <c r="F543" s="1" t="s">
-        <v>80</v>
+        <v>25</v>
       </c>
     </row>
     <row r="544" spans="1:6" x14ac:dyDescent="0.25">
@@ -15674,13 +15632,13 @@
         <v>3</v>
       </c>
       <c r="D544" s="1" t="s">
-        <v>1095</v>
+        <v>1093</v>
       </c>
       <c r="E544" s="1" t="s">
         <v>28</v>
       </c>
       <c r="F544" s="1" t="s">
-        <v>25</v>
+        <v>5</v>
       </c>
     </row>
     <row r="545" spans="1:6" x14ac:dyDescent="0.25">
@@ -15694,13 +15652,13 @@
         <v>3</v>
       </c>
       <c r="D545" s="1" t="s">
-        <v>1095</v>
+        <v>1093</v>
       </c>
       <c r="E545" s="1" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="F545" s="1" t="s">
-        <v>5</v>
+        <v>25</v>
       </c>
     </row>
     <row r="546" spans="1:6" x14ac:dyDescent="0.25">
@@ -15714,13 +15672,13 @@
         <v>3</v>
       </c>
       <c r="D546" s="1" t="s">
-        <v>1095</v>
+        <v>1093</v>
       </c>
       <c r="E546" s="1" t="s">
         <v>31</v>
       </c>
       <c r="F546" s="1" t="s">
-        <v>25</v>
+        <v>133</v>
       </c>
     </row>
     <row r="547" spans="1:6" x14ac:dyDescent="0.25">
@@ -15734,13 +15692,13 @@
         <v>3</v>
       </c>
       <c r="D547" s="1" t="s">
-        <v>1095</v>
+        <v>1093</v>
       </c>
       <c r="E547" s="1" t="s">
         <v>31</v>
       </c>
       <c r="F547" s="1" t="s">
-        <v>133</v>
+        <v>5</v>
       </c>
     </row>
     <row r="548" spans="1:6" x14ac:dyDescent="0.25">
@@ -15754,13 +15712,13 @@
         <v>3</v>
       </c>
       <c r="D548" s="1" t="s">
-        <v>1095</v>
+        <v>1093</v>
       </c>
       <c r="E548" s="1" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="F548" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="549" spans="1:6" x14ac:dyDescent="0.25">
@@ -15774,13 +15732,13 @@
         <v>3</v>
       </c>
       <c r="D549" s="1" t="s">
-        <v>1095</v>
+        <v>1093</v>
       </c>
       <c r="E549" s="1" t="s">
         <v>34</v>
       </c>
       <c r="F549" s="1" t="s">
-        <v>9</v>
+        <v>25</v>
       </c>
     </row>
     <row r="550" spans="1:6" x14ac:dyDescent="0.25">
@@ -15794,13 +15752,13 @@
         <v>3</v>
       </c>
       <c r="D550" s="1" t="s">
-        <v>1095</v>
+        <v>1093</v>
       </c>
       <c r="E550" s="1" t="s">
         <v>34</v>
       </c>
       <c r="F550" s="1" t="s">
-        <v>25</v>
+        <v>133</v>
       </c>
     </row>
     <row r="551" spans="1:6" x14ac:dyDescent="0.25">
@@ -15814,13 +15772,13 @@
         <v>3</v>
       </c>
       <c r="D551" s="1" t="s">
-        <v>1095</v>
+        <v>1093</v>
       </c>
       <c r="E551" s="1" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="F551" s="1" t="s">
-        <v>133</v>
+        <v>5</v>
       </c>
     </row>
     <row r="552" spans="1:6" x14ac:dyDescent="0.25">
@@ -15834,7 +15792,7 @@
         <v>3</v>
       </c>
       <c r="D552" s="1" t="s">
-        <v>1095</v>
+        <v>1093</v>
       </c>
       <c r="E552" s="1" t="s">
         <v>37</v>
@@ -15854,13 +15812,13 @@
         <v>3</v>
       </c>
       <c r="D553" s="1" t="s">
-        <v>1095</v>
+        <v>1093</v>
       </c>
       <c r="E553" s="1" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="F553" s="1" t="s">
-        <v>5</v>
+        <v>80</v>
       </c>
     </row>
     <row r="554" spans="1:6" x14ac:dyDescent="0.25">
@@ -15874,13 +15832,13 @@
         <v>3</v>
       </c>
       <c r="D554" s="1" t="s">
-        <v>1095</v>
+        <v>1093</v>
       </c>
       <c r="E554" s="1" t="s">
         <v>40</v>
       </c>
       <c r="F554" s="1" t="s">
-        <v>80</v>
+        <v>5</v>
       </c>
     </row>
     <row r="555" spans="1:6" x14ac:dyDescent="0.25">
@@ -15894,10 +15852,10 @@
         <v>3</v>
       </c>
       <c r="D555" s="1" t="s">
-        <v>1095</v>
+        <v>1093</v>
       </c>
       <c r="E555" s="1" t="s">
-        <v>40</v>
+        <v>68</v>
       </c>
       <c r="F555" s="1" t="s">
         <v>5</v>
@@ -15914,10 +15872,10 @@
         <v>3</v>
       </c>
       <c r="D556" s="1" t="s">
-        <v>1095</v>
+        <v>1093</v>
       </c>
       <c r="E556" s="1" t="s">
-        <v>68</v>
+        <v>100</v>
       </c>
       <c r="F556" s="1" t="s">
         <v>5</v>
@@ -15934,10 +15892,10 @@
         <v>3</v>
       </c>
       <c r="D557" s="1" t="s">
-        <v>1095</v>
+        <v>1093</v>
       </c>
       <c r="E557" s="1" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="F557" s="1" t="s">
         <v>5</v>
@@ -15954,10 +15912,10 @@
         <v>3</v>
       </c>
       <c r="D558" s="1" t="s">
-        <v>1095</v>
+        <v>1168</v>
       </c>
       <c r="E558" s="1" t="s">
-        <v>103</v>
+        <v>4</v>
       </c>
       <c r="F558" s="1" t="s">
         <v>5</v>
@@ -15965,22 +15923,22 @@
     </row>
     <row r="559" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A559" s="1" t="s">
+        <v>1169</v>
+      </c>
+      <c r="B559" s="1" t="s">
+        <v>1170</v>
+      </c>
+      <c r="C559" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D559" s="1" t="s">
         <v>1168</v>
       </c>
-      <c r="B559" s="1" t="s">
-        <v>1169</v>
-      </c>
-      <c r="C559" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D559" s="1" t="s">
-        <v>1170</v>
-      </c>
       <c r="E559" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F559" s="1" t="s">
-        <v>5</v>
+        <v>80</v>
       </c>
     </row>
     <row r="560" spans="1:6" x14ac:dyDescent="0.25">
@@ -15994,13 +15952,13 @@
         <v>3</v>
       </c>
       <c r="D560" s="1" t="s">
-        <v>1170</v>
+        <v>1168</v>
       </c>
       <c r="E560" s="1" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="F560" s="1" t="s">
-        <v>80</v>
+        <v>5</v>
       </c>
     </row>
     <row r="561" spans="1:6" x14ac:dyDescent="0.25">
@@ -16014,10 +15972,10 @@
         <v>3</v>
       </c>
       <c r="D561" s="1" t="s">
-        <v>1170</v>
+        <v>1168</v>
       </c>
       <c r="E561" s="1" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="F561" s="1" t="s">
         <v>5</v>
@@ -16034,10 +15992,10 @@
         <v>3</v>
       </c>
       <c r="D562" s="1" t="s">
-        <v>1170</v>
+        <v>1168</v>
       </c>
       <c r="E562" s="1" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="F562" s="1" t="s">
         <v>5</v>
@@ -16054,10 +16012,10 @@
         <v>3</v>
       </c>
       <c r="D563" s="1" t="s">
-        <v>1170</v>
+        <v>1168</v>
       </c>
       <c r="E563" s="1" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="F563" s="1" t="s">
         <v>5</v>
@@ -16074,13 +16032,13 @@
         <v>3</v>
       </c>
       <c r="D564" s="1" t="s">
-        <v>1170</v>
+        <v>1168</v>
       </c>
       <c r="E564" s="1" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="F564" s="1" t="s">
-        <v>5</v>
+        <v>25</v>
       </c>
     </row>
     <row r="565" spans="1:6" x14ac:dyDescent="0.25">
@@ -16094,13 +16052,13 @@
         <v>3</v>
       </c>
       <c r="D565" s="1" t="s">
-        <v>1170</v>
+        <v>1168</v>
       </c>
       <c r="E565" s="1" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="F565" s="1" t="s">
-        <v>25</v>
+        <v>5</v>
       </c>
     </row>
     <row r="566" spans="1:6" x14ac:dyDescent="0.25">
@@ -16114,13 +16072,13 @@
         <v>3</v>
       </c>
       <c r="D566" s="1" t="s">
-        <v>1170</v>
+        <v>1168</v>
       </c>
       <c r="E566" s="1" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="F566" s="1" t="s">
-        <v>5</v>
+        <v>80</v>
       </c>
     </row>
     <row r="567" spans="1:6" x14ac:dyDescent="0.25">
@@ -16134,10 +16092,10 @@
         <v>3</v>
       </c>
       <c r="D567" s="1" t="s">
-        <v>1170</v>
+        <v>1168</v>
       </c>
       <c r="E567" s="1" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="F567" s="1" t="s">
         <v>80</v>
@@ -16154,13 +16112,13 @@
         <v>3</v>
       </c>
       <c r="D568" s="1" t="s">
-        <v>1170</v>
+        <v>1168</v>
       </c>
       <c r="E568" s="1" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="F568" s="1" t="s">
-        <v>80</v>
+        <v>5</v>
       </c>
     </row>
     <row r="569" spans="1:6" x14ac:dyDescent="0.25">
@@ -16174,10 +16132,10 @@
         <v>3</v>
       </c>
       <c r="D569" s="1" t="s">
-        <v>1170</v>
+        <v>1168</v>
       </c>
       <c r="E569" s="1" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="F569" s="1" t="s">
         <v>5</v>
@@ -16194,10 +16152,10 @@
         <v>3</v>
       </c>
       <c r="D570" s="1" t="s">
-        <v>1170</v>
+        <v>1168</v>
       </c>
       <c r="E570" s="1" t="s">
-        <v>40</v>
+        <v>68</v>
       </c>
       <c r="F570" s="1" t="s">
         <v>5</v>
@@ -16214,13 +16172,13 @@
         <v>3</v>
       </c>
       <c r="D571" s="1" t="s">
-        <v>1170</v>
+        <v>1168</v>
       </c>
       <c r="E571" s="1" t="s">
-        <v>68</v>
+        <v>100</v>
       </c>
       <c r="F571" s="1" t="s">
-        <v>5</v>
+        <v>80</v>
       </c>
     </row>
     <row r="572" spans="1:6" x14ac:dyDescent="0.25">
@@ -16234,10 +16192,10 @@
         <v>3</v>
       </c>
       <c r="D572" s="1" t="s">
-        <v>1170</v>
+        <v>1197</v>
       </c>
       <c r="E572" s="1" t="s">
-        <v>100</v>
+        <v>4</v>
       </c>
       <c r="F572" s="1" t="s">
         <v>80</v>
@@ -16245,22 +16203,22 @@
     </row>
     <row r="573" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A573" s="1" t="s">
+        <v>1198</v>
+      </c>
+      <c r="B573" s="1" t="s">
+        <v>1199</v>
+      </c>
+      <c r="C573" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D573" s="1" t="s">
         <v>1197</v>
-      </c>
-      <c r="B573" s="1" t="s">
-        <v>1198</v>
-      </c>
-      <c r="C573" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D573" s="1" t="s">
-        <v>1199</v>
       </c>
       <c r="E573" s="1" t="s">
         <v>8</v>
       </c>
       <c r="F573" s="1" t="s">
-        <v>80</v>
+        <v>5</v>
       </c>
     </row>
     <row r="574" spans="1:6" x14ac:dyDescent="0.25">
@@ -16274,13 +16232,13 @@
         <v>3</v>
       </c>
       <c r="D574" s="1" t="s">
-        <v>1199</v>
+        <v>1197</v>
       </c>
       <c r="E574" s="1" t="s">
         <v>12</v>
       </c>
       <c r="F574" s="1" t="s">
-        <v>5</v>
+        <v>80</v>
       </c>
     </row>
     <row r="575" spans="1:6" x14ac:dyDescent="0.25">
@@ -16294,7 +16252,7 @@
         <v>3</v>
       </c>
       <c r="D575" s="1" t="s">
-        <v>1199</v>
+        <v>1197</v>
       </c>
       <c r="E575" s="1" t="s">
         <v>15</v>
@@ -16314,7 +16272,7 @@
         <v>3</v>
       </c>
       <c r="D576" s="1" t="s">
-        <v>1199</v>
+        <v>1197</v>
       </c>
       <c r="E576" s="1" t="s">
         <v>18</v>
@@ -16334,13 +16292,13 @@
         <v>3</v>
       </c>
       <c r="D577" s="1" t="s">
-        <v>1199</v>
+        <v>1197</v>
       </c>
       <c r="E577" s="1" t="s">
         <v>21</v>
       </c>
       <c r="F577" s="1" t="s">
-        <v>80</v>
+        <v>5</v>
       </c>
     </row>
     <row r="578" spans="1:6" x14ac:dyDescent="0.25">
@@ -16354,7 +16312,7 @@
         <v>3</v>
       </c>
       <c r="D578" s="1" t="s">
-        <v>1199</v>
+        <v>1197</v>
       </c>
       <c r="E578" s="1" t="s">
         <v>24</v>
@@ -16374,7 +16332,7 @@
         <v>3</v>
       </c>
       <c r="D579" s="1" t="s">
-        <v>1199</v>
+        <v>1197</v>
       </c>
       <c r="E579" s="1" t="s">
         <v>28</v>
@@ -16394,7 +16352,7 @@
         <v>3</v>
       </c>
       <c r="D580" s="1" t="s">
-        <v>1199</v>
+        <v>1197</v>
       </c>
       <c r="E580" s="1" t="s">
         <v>31</v>
@@ -16414,7 +16372,7 @@
         <v>3</v>
       </c>
       <c r="D581" s="1" t="s">
-        <v>1199</v>
+        <v>1197</v>
       </c>
       <c r="E581" s="1" t="s">
         <v>34</v>
@@ -16434,7 +16392,7 @@
         <v>3</v>
       </c>
       <c r="D582" s="1" t="s">
-        <v>1199</v>
+        <v>1197</v>
       </c>
       <c r="E582" s="1" t="s">
         <v>37</v>
@@ -16454,7 +16412,7 @@
         <v>3</v>
       </c>
       <c r="D583" s="1" t="s">
-        <v>1199</v>
+        <v>1197</v>
       </c>
       <c r="E583" s="1" t="s">
         <v>40</v>
@@ -16474,7 +16432,7 @@
         <v>3</v>
       </c>
       <c r="D584" s="1" t="s">
-        <v>1199</v>
+        <v>1197</v>
       </c>
       <c r="E584" s="1" t="s">
         <v>68</v>
@@ -16494,10 +16452,10 @@
         <v>3</v>
       </c>
       <c r="D585" s="1" t="s">
-        <v>1199</v>
+        <v>1224</v>
       </c>
       <c r="E585" s="1" t="s">
-        <v>100</v>
+        <v>4</v>
       </c>
       <c r="F585" s="1" t="s">
         <v>5</v>
@@ -16505,19 +16463,19 @@
     </row>
     <row r="586" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A586" s="1" t="s">
+        <v>1225</v>
+      </c>
+      <c r="B586" s="1" t="s">
+        <v>1226</v>
+      </c>
+      <c r="C586" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D586" s="1" t="s">
         <v>1224</v>
       </c>
-      <c r="B586" s="1" t="s">
-        <v>1225</v>
-      </c>
-      <c r="C586" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D586" s="1" t="s">
-        <v>1226</v>
-      </c>
       <c r="E586" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F586" s="1" t="s">
         <v>5</v>
@@ -16534,50 +16492,50 @@
         <v>3</v>
       </c>
       <c r="D587" s="1" t="s">
-        <v>1226</v>
+        <v>1224</v>
       </c>
       <c r="E587" s="1" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="F587" s="1" t="s">
-        <v>80</v>
+        <v>1229</v>
       </c>
     </row>
     <row r="588" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A588" s="1" t="s">
+        <v>1230</v>
+      </c>
+      <c r="B588" s="1" t="s">
+        <v>1231</v>
+      </c>
+      <c r="C588" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D588" s="1" t="s">
+        <v>1224</v>
+      </c>
+      <c r="E588" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="F588" s="1" t="s">
         <v>1229</v>
-      </c>
-      <c r="B588" s="1" t="s">
-        <v>1230</v>
-      </c>
-      <c r="C588" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D588" s="1" t="s">
-        <v>1226</v>
-      </c>
-      <c r="E588" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="F588" s="1" t="s">
-        <v>5</v>
       </c>
     </row>
     <row r="589" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A589" s="1" t="s">
-        <v>1231</v>
+        <v>1232</v>
       </c>
       <c r="B589" s="1" t="s">
-        <v>1232</v>
+        <v>1233</v>
       </c>
       <c r="C589" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D589" s="1" t="s">
-        <v>1226</v>
+        <v>1224</v>
       </c>
       <c r="E589" s="1" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="F589" s="1" t="s">
         <v>5</v>
@@ -16585,22 +16543,22 @@
     </row>
     <row r="590" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A590" s="1" t="s">
-        <v>1233</v>
+        <v>1234</v>
       </c>
       <c r="B590" s="1" t="s">
-        <v>1234</v>
+        <v>1235</v>
       </c>
       <c r="C590" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D590" s="1" t="s">
-        <v>1226</v>
+        <v>1224</v>
       </c>
       <c r="E590" s="1" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="F590" s="1" t="s">
-        <v>1235</v>
+        <v>5</v>
       </c>
     </row>
     <row r="591" spans="1:6" x14ac:dyDescent="0.25">
@@ -16614,13 +16572,13 @@
         <v>3</v>
       </c>
       <c r="D591" s="1" t="s">
-        <v>1226</v>
+        <v>1224</v>
       </c>
       <c r="E591" s="1" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="F591" s="1" t="s">
-        <v>1235</v>
+        <v>5</v>
       </c>
     </row>
     <row r="592" spans="1:6" x14ac:dyDescent="0.25">
@@ -16634,10 +16592,10 @@
         <v>3</v>
       </c>
       <c r="D592" s="1" t="s">
-        <v>1226</v>
+        <v>1224</v>
       </c>
       <c r="E592" s="1" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="F592" s="1" t="s">
         <v>5</v>
@@ -16654,13 +16612,13 @@
         <v>3</v>
       </c>
       <c r="D593" s="1" t="s">
-        <v>1226</v>
+        <v>1224</v>
       </c>
       <c r="E593" s="1" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="F593" s="1" t="s">
-        <v>5</v>
+        <v>41</v>
       </c>
     </row>
     <row r="594" spans="1:6" x14ac:dyDescent="0.25">
@@ -16674,10 +16632,10 @@
         <v>3</v>
       </c>
       <c r="D594" s="1" t="s">
-        <v>1226</v>
+        <v>1224</v>
       </c>
       <c r="E594" s="1" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="F594" s="1" t="s">
         <v>5</v>
@@ -16694,10 +16652,10 @@
         <v>3</v>
       </c>
       <c r="D595" s="1" t="s">
-        <v>1226</v>
+        <v>1224</v>
       </c>
       <c r="E595" s="1" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="F595" s="1" t="s">
         <v>5</v>
@@ -16714,13 +16672,13 @@
         <v>3</v>
       </c>
       <c r="D596" s="1" t="s">
-        <v>1226</v>
+        <v>1224</v>
       </c>
       <c r="E596" s="1" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="F596" s="1" t="s">
-        <v>41</v>
+        <v>5</v>
       </c>
     </row>
     <row r="597" spans="1:6" x14ac:dyDescent="0.25">
@@ -16734,10 +16692,10 @@
         <v>3</v>
       </c>
       <c r="D597" s="1" t="s">
-        <v>1226</v>
+        <v>1224</v>
       </c>
       <c r="E597" s="1" t="s">
-        <v>40</v>
+        <v>68</v>
       </c>
       <c r="F597" s="1" t="s">
         <v>5</v>
@@ -16754,73 +16712,73 @@
         <v>3</v>
       </c>
       <c r="D598" s="1" t="s">
-        <v>1226</v>
+        <v>1252</v>
       </c>
       <c r="E598" s="1" t="s">
-        <v>68</v>
+        <v>4</v>
       </c>
       <c r="F598" s="1" t="s">
-        <v>5</v>
+        <v>41</v>
       </c>
     </row>
     <row r="599" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A599" s="1" t="s">
+        <v>1253</v>
+      </c>
+      <c r="B599" s="1" t="s">
+        <v>1254</v>
+      </c>
+      <c r="C599" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D599" s="1" t="s">
         <v>1252</v>
       </c>
-      <c r="B599" s="1" t="s">
-        <v>1253</v>
-      </c>
-      <c r="C599" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D599" s="1" t="s">
-        <v>1226</v>
-      </c>
       <c r="E599" s="1" t="s">
-        <v>100</v>
+        <v>8</v>
       </c>
       <c r="F599" s="1" t="s">
-        <v>5</v>
+        <v>41</v>
       </c>
     </row>
     <row r="600" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A600" s="1" t="s">
-        <v>1254</v>
+        <v>1255</v>
       </c>
       <c r="B600" s="1" t="s">
-        <v>1255</v>
+        <v>1256</v>
       </c>
       <c r="C600" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D600" s="1" t="s">
-        <v>1226</v>
+        <v>1252</v>
       </c>
       <c r="E600" s="1" t="s">
-        <v>103</v>
+        <v>12</v>
       </c>
       <c r="F600" s="1" t="s">
-        <v>5</v>
+        <v>41</v>
       </c>
     </row>
     <row r="601" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A601" s="1" t="s">
-        <v>1256</v>
+        <v>1257</v>
       </c>
       <c r="B601" s="1" t="s">
-        <v>1257</v>
+        <v>1258</v>
       </c>
       <c r="C601" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D601" s="1" t="s">
-        <v>1258</v>
+        <v>1252</v>
       </c>
       <c r="E601" s="1" t="s">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="F601" s="1" t="s">
-        <v>41</v>
+        <v>133</v>
       </c>
     </row>
     <row r="602" spans="1:6" x14ac:dyDescent="0.25">
@@ -16834,13 +16792,13 @@
         <v>3</v>
       </c>
       <c r="D602" s="1" t="s">
-        <v>1258</v>
+        <v>1252</v>
       </c>
       <c r="E602" s="1" t="s">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="F602" s="1" t="s">
-        <v>41</v>
+        <v>5</v>
       </c>
     </row>
     <row r="603" spans="1:6" x14ac:dyDescent="0.25">
@@ -16854,13 +16812,13 @@
         <v>3</v>
       </c>
       <c r="D603" s="1" t="s">
-        <v>1258</v>
+        <v>1252</v>
       </c>
       <c r="E603" s="1" t="s">
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="F603" s="1" t="s">
-        <v>41</v>
+        <v>5</v>
       </c>
     </row>
     <row r="604" spans="1:6" x14ac:dyDescent="0.25">
@@ -16874,13 +16832,13 @@
         <v>3</v>
       </c>
       <c r="D604" s="1" t="s">
-        <v>1258</v>
+        <v>1252</v>
       </c>
       <c r="E604" s="1" t="s">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="F604" s="1" t="s">
-        <v>133</v>
+        <v>5</v>
       </c>
     </row>
     <row r="605" spans="1:6" x14ac:dyDescent="0.25">
@@ -16894,10 +16852,10 @@
         <v>3</v>
       </c>
       <c r="D605" s="1" t="s">
-        <v>1258</v>
+        <v>1252</v>
       </c>
       <c r="E605" s="1" t="s">
-        <v>18</v>
+        <v>28</v>
       </c>
       <c r="F605" s="1" t="s">
         <v>5</v>
@@ -16914,10 +16872,10 @@
         <v>3</v>
       </c>
       <c r="D606" s="1" t="s">
-        <v>1258</v>
+        <v>1252</v>
       </c>
       <c r="E606" s="1" t="s">
-        <v>21</v>
+        <v>31</v>
       </c>
       <c r="F606" s="1" t="s">
         <v>5</v>
@@ -16934,10 +16892,10 @@
         <v>3</v>
       </c>
       <c r="D607" s="1" t="s">
-        <v>1258</v>
+        <v>1252</v>
       </c>
       <c r="E607" s="1" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
       <c r="F607" s="1" t="s">
         <v>5</v>
@@ -16954,10 +16912,10 @@
         <v>3</v>
       </c>
       <c r="D608" s="1" t="s">
-        <v>1258</v>
+        <v>1252</v>
       </c>
       <c r="E608" s="1" t="s">
-        <v>28</v>
+        <v>37</v>
       </c>
       <c r="F608" s="1" t="s">
         <v>5</v>
@@ -16974,10 +16932,10 @@
         <v>3</v>
       </c>
       <c r="D609" s="1" t="s">
-        <v>1258</v>
+        <v>1252</v>
       </c>
       <c r="E609" s="1" t="s">
-        <v>31</v>
+        <v>40</v>
       </c>
       <c r="F609" s="1" t="s">
         <v>5</v>
@@ -16994,10 +16952,10 @@
         <v>3</v>
       </c>
       <c r="D610" s="1" t="s">
-        <v>1258</v>
+        <v>1252</v>
       </c>
       <c r="E610" s="1" t="s">
-        <v>34</v>
+        <v>68</v>
       </c>
       <c r="F610" s="1" t="s">
         <v>5</v>
@@ -17014,10 +16972,10 @@
         <v>3</v>
       </c>
       <c r="D611" s="1" t="s">
-        <v>1258</v>
+        <v>1252</v>
       </c>
       <c r="E611" s="1" t="s">
-        <v>37</v>
+        <v>100</v>
       </c>
       <c r="F611" s="1" t="s">
         <v>5</v>
@@ -17034,13 +16992,13 @@
         <v>3</v>
       </c>
       <c r="D612" s="1" t="s">
-        <v>1258</v>
+        <v>1252</v>
       </c>
       <c r="E612" s="1" t="s">
-        <v>40</v>
+        <v>103</v>
       </c>
       <c r="F612" s="1" t="s">
-        <v>5</v>
+        <v>41</v>
       </c>
     </row>
     <row r="613" spans="1:6" x14ac:dyDescent="0.25">
@@ -17054,10 +17012,10 @@
         <v>3</v>
       </c>
       <c r="D613" s="1" t="s">
-        <v>1258</v>
+        <v>1252</v>
       </c>
       <c r="E613" s="1" t="s">
-        <v>68</v>
+        <v>106</v>
       </c>
       <c r="F613" s="1" t="s">
         <v>5</v>
@@ -17074,10 +17032,10 @@
         <v>3</v>
       </c>
       <c r="D614" s="1" t="s">
-        <v>1258</v>
+        <v>1252</v>
       </c>
       <c r="E614" s="1" t="s">
-        <v>100</v>
+        <v>109</v>
       </c>
       <c r="F614" s="1" t="s">
         <v>5</v>
@@ -17094,50 +17052,50 @@
         <v>3</v>
       </c>
       <c r="D615" s="1" t="s">
-        <v>1258</v>
+        <v>1287</v>
       </c>
       <c r="E615" s="1" t="s">
-        <v>103</v>
+        <v>4</v>
       </c>
       <c r="F615" s="1" t="s">
-        <v>41</v>
+        <v>80</v>
       </c>
     </row>
     <row r="616" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A616" s="1" t="s">
+        <v>1288</v>
+      </c>
+      <c r="B616" s="1" t="s">
+        <v>1289</v>
+      </c>
+      <c r="C616" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D616" s="1" t="s">
         <v>1287</v>
       </c>
-      <c r="B616" s="1" t="s">
-        <v>1288</v>
-      </c>
-      <c r="C616" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D616" s="1" t="s">
-        <v>1258</v>
-      </c>
       <c r="E616" s="1" t="s">
-        <v>106</v>
+        <v>8</v>
       </c>
       <c r="F616" s="1" t="s">
-        <v>5</v>
+        <v>41</v>
       </c>
     </row>
     <row r="617" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A617" s="1" t="s">
-        <v>1289</v>
+        <v>1290</v>
       </c>
       <c r="B617" s="1" t="s">
-        <v>1290</v>
+        <v>1291</v>
       </c>
       <c r="C617" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D617" s="1" t="s">
-        <v>1258</v>
+        <v>1287</v>
       </c>
       <c r="E617" s="1" t="s">
-        <v>109</v>
+        <v>12</v>
       </c>
       <c r="F617" s="1" t="s">
         <v>5</v>
@@ -17145,22 +17103,22 @@
     </row>
     <row r="618" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A618" s="1" t="s">
-        <v>1291</v>
+        <v>1292</v>
       </c>
       <c r="B618" s="1" t="s">
-        <v>1292</v>
+        <v>1293</v>
       </c>
       <c r="C618" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D618" s="1" t="s">
-        <v>1293</v>
+        <v>1287</v>
       </c>
       <c r="E618" s="1" t="s">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="F618" s="1" t="s">
-        <v>80</v>
+        <v>5</v>
       </c>
     </row>
     <row r="619" spans="1:6" x14ac:dyDescent="0.25">
@@ -17174,13 +17132,13 @@
         <v>3</v>
       </c>
       <c r="D619" s="1" t="s">
-        <v>1293</v>
+        <v>1287</v>
       </c>
       <c r="E619" s="1" t="s">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="F619" s="1" t="s">
-        <v>41</v>
+        <v>5</v>
       </c>
     </row>
     <row r="620" spans="1:6" x14ac:dyDescent="0.25">
@@ -17194,13 +17152,13 @@
         <v>3</v>
       </c>
       <c r="D620" s="1" t="s">
-        <v>1293</v>
+        <v>1287</v>
       </c>
       <c r="E620" s="1" t="s">
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="F620" s="1" t="s">
-        <v>5</v>
+        <v>41</v>
       </c>
     </row>
     <row r="621" spans="1:6" x14ac:dyDescent="0.25">
@@ -17214,13 +17172,13 @@
         <v>3</v>
       </c>
       <c r="D621" s="1" t="s">
-        <v>1293</v>
+        <v>1287</v>
       </c>
       <c r="E621" s="1" t="s">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="F621" s="1" t="s">
-        <v>5</v>
+        <v>41</v>
       </c>
     </row>
     <row r="622" spans="1:6" x14ac:dyDescent="0.25">
@@ -17234,10 +17192,10 @@
         <v>3</v>
       </c>
       <c r="D622" s="1" t="s">
-        <v>1293</v>
+        <v>1287</v>
       </c>
       <c r="E622" s="1" t="s">
-        <v>18</v>
+        <v>28</v>
       </c>
       <c r="F622" s="1" t="s">
         <v>5</v>
@@ -17254,13 +17212,13 @@
         <v>3</v>
       </c>
       <c r="D623" s="1" t="s">
-        <v>1293</v>
+        <v>1287</v>
       </c>
       <c r="E623" s="1" t="s">
-        <v>21</v>
+        <v>31</v>
       </c>
       <c r="F623" s="1" t="s">
-        <v>41</v>
+        <v>5</v>
       </c>
     </row>
     <row r="624" spans="1:6" x14ac:dyDescent="0.25">
@@ -17274,13 +17232,13 @@
         <v>3</v>
       </c>
       <c r="D624" s="1" t="s">
-        <v>1293</v>
+        <v>1287</v>
       </c>
       <c r="E624" s="1" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
       <c r="F624" s="1" t="s">
-        <v>41</v>
+        <v>9</v>
       </c>
     </row>
     <row r="625" spans="1:6" x14ac:dyDescent="0.25">
@@ -17294,13 +17252,13 @@
         <v>3</v>
       </c>
       <c r="D625" s="1" t="s">
-        <v>1293</v>
+        <v>1287</v>
       </c>
       <c r="E625" s="1" t="s">
-        <v>28</v>
+        <v>37</v>
       </c>
       <c r="F625" s="1" t="s">
-        <v>5</v>
+        <v>25</v>
       </c>
     </row>
     <row r="626" spans="1:6" x14ac:dyDescent="0.25">
@@ -17314,13 +17272,13 @@
         <v>3</v>
       </c>
       <c r="D626" s="1" t="s">
-        <v>1293</v>
+        <v>1287</v>
       </c>
       <c r="E626" s="1" t="s">
-        <v>31</v>
+        <v>40</v>
       </c>
       <c r="F626" s="1" t="s">
-        <v>5</v>
+        <v>41</v>
       </c>
     </row>
     <row r="627" spans="1:6" x14ac:dyDescent="0.25">
@@ -17334,13 +17292,13 @@
         <v>3</v>
       </c>
       <c r="D627" s="1" t="s">
-        <v>1293</v>
+        <v>1287</v>
       </c>
       <c r="E627" s="1" t="s">
-        <v>34</v>
+        <v>68</v>
       </c>
       <c r="F627" s="1" t="s">
-        <v>9</v>
+        <v>41</v>
       </c>
     </row>
     <row r="628" spans="1:6" x14ac:dyDescent="0.25">
@@ -17354,13 +17312,13 @@
         <v>3</v>
       </c>
       <c r="D628" s="1" t="s">
-        <v>1293</v>
+        <v>1287</v>
       </c>
       <c r="E628" s="1" t="s">
-        <v>37</v>
+        <v>100</v>
       </c>
       <c r="F628" s="1" t="s">
-        <v>25</v>
+        <v>41</v>
       </c>
     </row>
     <row r="629" spans="1:6" x14ac:dyDescent="0.25">
@@ -17374,10 +17332,10 @@
         <v>3</v>
       </c>
       <c r="D629" s="1" t="s">
-        <v>1293</v>
+        <v>1287</v>
       </c>
       <c r="E629" s="1" t="s">
-        <v>40</v>
+        <v>103</v>
       </c>
       <c r="F629" s="1" t="s">
         <v>41</v>
@@ -17394,13 +17352,13 @@
         <v>3</v>
       </c>
       <c r="D630" s="1" t="s">
-        <v>1293</v>
+        <v>1287</v>
       </c>
       <c r="E630" s="1" t="s">
-        <v>68</v>
+        <v>106</v>
       </c>
       <c r="F630" s="1" t="s">
-        <v>41</v>
+        <v>5</v>
       </c>
     </row>
     <row r="631" spans="1:6" x14ac:dyDescent="0.25">
@@ -17414,13 +17372,13 @@
         <v>3</v>
       </c>
       <c r="D631" s="1" t="s">
-        <v>1293</v>
+        <v>1287</v>
       </c>
       <c r="E631" s="1" t="s">
-        <v>100</v>
+        <v>109</v>
       </c>
       <c r="F631" s="1" t="s">
-        <v>41</v>
+        <v>9</v>
       </c>
     </row>
     <row r="632" spans="1:6" x14ac:dyDescent="0.25">
@@ -17434,13 +17392,13 @@
         <v>3</v>
       </c>
       <c r="D632" s="1" t="s">
-        <v>1293</v>
+        <v>1287</v>
       </c>
       <c r="E632" s="1" t="s">
-        <v>103</v>
+        <v>112</v>
       </c>
       <c r="F632" s="1" t="s">
-        <v>41</v>
+        <v>25</v>
       </c>
     </row>
     <row r="633" spans="1:6" x14ac:dyDescent="0.25">
@@ -17454,10 +17412,10 @@
         <v>3</v>
       </c>
       <c r="D633" s="1" t="s">
-        <v>1293</v>
+        <v>1324</v>
       </c>
       <c r="E633" s="1" t="s">
-        <v>106</v>
+        <v>4</v>
       </c>
       <c r="F633" s="1" t="s">
         <v>5</v>
@@ -17465,59 +17423,59 @@
     </row>
     <row r="634" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A634" s="1" t="s">
+        <v>1325</v>
+      </c>
+      <c r="B634" s="1" t="s">
+        <v>1326</v>
+      </c>
+      <c r="C634" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D634" s="1" t="s">
         <v>1324</v>
       </c>
-      <c r="B634" s="1" t="s">
-        <v>1325</v>
-      </c>
-      <c r="C634" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D634" s="1" t="s">
-        <v>1293</v>
-      </c>
       <c r="E634" s="1" t="s">
-        <v>109</v>
+        <v>8</v>
       </c>
       <c r="F634" s="1" t="s">
-        <v>9</v>
+        <v>41</v>
       </c>
     </row>
     <row r="635" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A635" s="1" t="s">
-        <v>1326</v>
+        <v>1327</v>
       </c>
       <c r="B635" s="1" t="s">
-        <v>1327</v>
+        <v>1328</v>
       </c>
       <c r="C635" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D635" s="1" t="s">
-        <v>1293</v>
+        <v>1324</v>
       </c>
       <c r="E635" s="1" t="s">
-        <v>112</v>
+        <v>12</v>
       </c>
       <c r="F635" s="1" t="s">
-        <v>25</v>
+        <v>5</v>
       </c>
     </row>
     <row r="636" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A636" s="1" t="s">
-        <v>1328</v>
+        <v>1329</v>
       </c>
       <c r="B636" s="1" t="s">
-        <v>1329</v>
+        <v>1330</v>
       </c>
       <c r="C636" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D636" s="1" t="s">
-        <v>1330</v>
+        <v>1324</v>
       </c>
       <c r="E636" s="1" t="s">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="F636" s="1" t="s">
         <v>5</v>
@@ -17528,79 +17486,79 @@
         <v>1331</v>
       </c>
       <c r="B637" s="1" t="s">
-        <v>1332</v>
+        <v>1330</v>
       </c>
       <c r="C637" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D637" s="1" t="s">
-        <v>1330</v>
+        <v>1324</v>
       </c>
       <c r="E637" s="1" t="s">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="F637" s="1" t="s">
-        <v>41</v>
+        <v>5</v>
       </c>
     </row>
     <row r="638" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A638" s="1" t="s">
+        <v>1332</v>
+      </c>
+      <c r="B638" s="1" t="s">
         <v>1333</v>
       </c>
-      <c r="B638" s="1" t="s">
-        <v>1334</v>
-      </c>
       <c r="C638" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D638" s="1" t="s">
-        <v>1330</v>
+        <v>1324</v>
       </c>
       <c r="E638" s="1" t="s">
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="F638" s="1" t="s">
-        <v>5</v>
+        <v>80</v>
       </c>
     </row>
     <row r="639" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A639" s="1" t="s">
+        <v>1334</v>
+      </c>
+      <c r="B639" s="1" t="s">
         <v>1335</v>
       </c>
-      <c r="B639" s="1" t="s">
-        <v>1336</v>
-      </c>
       <c r="C639" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D639" s="1" t="s">
-        <v>1330</v>
+        <v>1324</v>
       </c>
       <c r="E639" s="1" t="s">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="F639" s="1" t="s">
-        <v>5</v>
+        <v>80</v>
       </c>
     </row>
     <row r="640" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A640" s="1" t="s">
+        <v>1336</v>
+      </c>
+      <c r="B640" s="1" t="s">
         <v>1337</v>
       </c>
-      <c r="B640" s="1" t="s">
-        <v>1336</v>
-      </c>
       <c r="C640" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D640" s="1" t="s">
-        <v>1330</v>
+        <v>1324</v>
       </c>
       <c r="E640" s="1" t="s">
-        <v>18</v>
+        <v>28</v>
       </c>
       <c r="F640" s="1" t="s">
-        <v>5</v>
+        <v>25</v>
       </c>
     </row>
     <row r="641" spans="1:6" x14ac:dyDescent="0.25">
@@ -17614,13 +17572,13 @@
         <v>3</v>
       </c>
       <c r="D641" s="1" t="s">
-        <v>1330</v>
+        <v>1324</v>
       </c>
       <c r="E641" s="1" t="s">
-        <v>21</v>
+        <v>31</v>
       </c>
       <c r="F641" s="1" t="s">
-        <v>80</v>
+        <v>25</v>
       </c>
     </row>
     <row r="642" spans="1:6" x14ac:dyDescent="0.25">
@@ -17634,13 +17592,13 @@
         <v>3</v>
       </c>
       <c r="D642" s="1" t="s">
-        <v>1330</v>
+        <v>1324</v>
       </c>
       <c r="E642" s="1" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
       <c r="F642" s="1" t="s">
-        <v>80</v>
+        <v>25</v>
       </c>
     </row>
     <row r="643" spans="1:6" x14ac:dyDescent="0.25">
@@ -17654,10 +17612,10 @@
         <v>3</v>
       </c>
       <c r="D643" s="1" t="s">
-        <v>1330</v>
+        <v>1324</v>
       </c>
       <c r="E643" s="1" t="s">
-        <v>28</v>
+        <v>37</v>
       </c>
       <c r="F643" s="1" t="s">
         <v>25</v>
@@ -17674,10 +17632,10 @@
         <v>3</v>
       </c>
       <c r="D644" s="1" t="s">
-        <v>1330</v>
+        <v>1324</v>
       </c>
       <c r="E644" s="1" t="s">
-        <v>31</v>
+        <v>40</v>
       </c>
       <c r="F644" s="1" t="s">
         <v>25</v>
@@ -17694,10 +17652,10 @@
         <v>3</v>
       </c>
       <c r="D645" s="1" t="s">
-        <v>1330</v>
+        <v>1324</v>
       </c>
       <c r="E645" s="1" t="s">
-        <v>34</v>
+        <v>68</v>
       </c>
       <c r="F645" s="1" t="s">
         <v>25</v>
@@ -17714,13 +17672,13 @@
         <v>3</v>
       </c>
       <c r="D646" s="1" t="s">
-        <v>1330</v>
+        <v>1324</v>
       </c>
       <c r="E646" s="1" t="s">
-        <v>37</v>
+        <v>100</v>
       </c>
       <c r="F646" s="1" t="s">
-        <v>25</v>
+        <v>133</v>
       </c>
     </row>
     <row r="647" spans="1:6" x14ac:dyDescent="0.25">
@@ -17734,13 +17692,13 @@
         <v>3</v>
       </c>
       <c r="D647" s="1" t="s">
-        <v>1330</v>
+        <v>1324</v>
       </c>
       <c r="E647" s="1" t="s">
-        <v>40</v>
+        <v>103</v>
       </c>
       <c r="F647" s="1" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
     </row>
     <row r="648" spans="1:6" x14ac:dyDescent="0.25">
@@ -17754,13 +17712,13 @@
         <v>3</v>
       </c>
       <c r="D648" s="1" t="s">
-        <v>1330</v>
+        <v>1324</v>
       </c>
       <c r="E648" s="1" t="s">
-        <v>68</v>
+        <v>106</v>
       </c>
       <c r="F648" s="1" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
     </row>
     <row r="649" spans="1:6" x14ac:dyDescent="0.25">
@@ -17774,13 +17732,13 @@
         <v>3</v>
       </c>
       <c r="D649" s="1" t="s">
-        <v>1330</v>
+        <v>1324</v>
       </c>
       <c r="E649" s="1" t="s">
-        <v>100</v>
+        <v>109</v>
       </c>
       <c r="F649" s="1" t="s">
-        <v>133</v>
+        <v>9</v>
       </c>
     </row>
     <row r="650" spans="1:6" x14ac:dyDescent="0.25">
@@ -17794,10 +17752,10 @@
         <v>3</v>
       </c>
       <c r="D650" s="1" t="s">
-        <v>1330</v>
+        <v>1324</v>
       </c>
       <c r="E650" s="1" t="s">
-        <v>103</v>
+        <v>112</v>
       </c>
       <c r="F650" s="1" t="s">
         <v>9</v>
@@ -17814,30 +17772,30 @@
         <v>3</v>
       </c>
       <c r="D651" s="1" t="s">
-        <v>1330</v>
+        <v>1360</v>
       </c>
       <c r="E651" s="1" t="s">
-        <v>106</v>
+        <v>4</v>
       </c>
       <c r="F651" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="652" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A652" s="1" t="s">
+        <v>1361</v>
+      </c>
+      <c r="B652" s="1" t="s">
+        <v>1362</v>
+      </c>
+      <c r="C652" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D652" s="1" t="s">
         <v>1360</v>
       </c>
-      <c r="B652" s="1" t="s">
-        <v>1361</v>
-      </c>
-      <c r="C652" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D652" s="1" t="s">
-        <v>1330</v>
-      </c>
       <c r="E652" s="1" t="s">
-        <v>109</v>
+        <v>8</v>
       </c>
       <c r="F652" s="1" t="s">
         <v>9</v>
@@ -17845,19 +17803,19 @@
     </row>
     <row r="653" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A653" s="1" t="s">
-        <v>1362</v>
+        <v>1363</v>
       </c>
       <c r="B653" s="1" t="s">
-        <v>1363</v>
+        <v>1364</v>
       </c>
       <c r="C653" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D653" s="1" t="s">
-        <v>1330</v>
+        <v>1360</v>
       </c>
       <c r="E653" s="1" t="s">
-        <v>112</v>
+        <v>12</v>
       </c>
       <c r="F653" s="1" t="s">
         <v>9</v>
@@ -17865,22 +17823,22 @@
     </row>
     <row r="654" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A654" s="1" t="s">
-        <v>1364</v>
+        <v>1365</v>
       </c>
       <c r="B654" s="1" t="s">
-        <v>1365</v>
+        <v>1366</v>
       </c>
       <c r="C654" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D654" s="1" t="s">
-        <v>1366</v>
+        <v>1360</v>
       </c>
       <c r="E654" s="1" t="s">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="F654" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="655" spans="1:6" x14ac:dyDescent="0.25">
@@ -17894,10 +17852,10 @@
         <v>3</v>
       </c>
       <c r="D655" s="1" t="s">
-        <v>1366</v>
+        <v>1360</v>
       </c>
       <c r="E655" s="1" t="s">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="F655" s="1" t="s">
         <v>9</v>
@@ -17914,13 +17872,13 @@
         <v>3</v>
       </c>
       <c r="D656" s="1" t="s">
-        <v>1366</v>
+        <v>1360</v>
       </c>
       <c r="E656" s="1" t="s">
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="F656" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="657" spans="1:6" x14ac:dyDescent="0.25">
@@ -17934,10 +17892,10 @@
         <v>3</v>
       </c>
       <c r="D657" s="1" t="s">
-        <v>1366</v>
+        <v>1360</v>
       </c>
       <c r="E657" s="1" t="s">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="F657" s="1" t="s">
         <v>9</v>
@@ -17954,13 +17912,13 @@
         <v>3</v>
       </c>
       <c r="D658" s="1" t="s">
-        <v>1366</v>
+        <v>1360</v>
       </c>
       <c r="E658" s="1" t="s">
-        <v>18</v>
+        <v>28</v>
       </c>
       <c r="F658" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="659" spans="1:6" x14ac:dyDescent="0.25">
@@ -17974,13 +17932,13 @@
         <v>3</v>
       </c>
       <c r="D659" s="1" t="s">
-        <v>1366</v>
+        <v>1360</v>
       </c>
       <c r="E659" s="1" t="s">
-        <v>21</v>
+        <v>31</v>
       </c>
       <c r="F659" s="1" t="s">
-        <v>5</v>
+        <v>25</v>
       </c>
     </row>
     <row r="660" spans="1:6" x14ac:dyDescent="0.25">
@@ -17994,13 +17952,13 @@
         <v>3</v>
       </c>
       <c r="D660" s="1" t="s">
-        <v>1366</v>
+        <v>1360</v>
       </c>
       <c r="E660" s="1" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
       <c r="F660" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="661" spans="1:6" x14ac:dyDescent="0.25">
@@ -18014,13 +17972,13 @@
         <v>3</v>
       </c>
       <c r="D661" s="1" t="s">
-        <v>1366</v>
+        <v>1360</v>
       </c>
       <c r="E661" s="1" t="s">
-        <v>28</v>
+        <v>37</v>
       </c>
       <c r="F661" s="1" t="s">
-        <v>5</v>
+        <v>25</v>
       </c>
     </row>
     <row r="662" spans="1:6" x14ac:dyDescent="0.25">
@@ -18034,10 +17992,10 @@
         <v>3</v>
       </c>
       <c r="D662" s="1" t="s">
-        <v>1366</v>
+        <v>1360</v>
       </c>
       <c r="E662" s="1" t="s">
-        <v>31</v>
+        <v>40</v>
       </c>
       <c r="F662" s="1" t="s">
         <v>25</v>
@@ -18054,13 +18012,13 @@
         <v>3</v>
       </c>
       <c r="D663" s="1" t="s">
-        <v>1366</v>
+        <v>1360</v>
       </c>
       <c r="E663" s="1" t="s">
-        <v>34</v>
+        <v>68</v>
       </c>
       <c r="F663" s="1" t="s">
-        <v>5</v>
+        <v>25</v>
       </c>
     </row>
     <row r="664" spans="1:6" x14ac:dyDescent="0.25">
@@ -18074,10 +18032,10 @@
         <v>3</v>
       </c>
       <c r="D664" s="1" t="s">
-        <v>1366</v>
+        <v>1360</v>
       </c>
       <c r="E664" s="1" t="s">
-        <v>37</v>
+        <v>100</v>
       </c>
       <c r="F664" s="1" t="s">
         <v>25</v>
@@ -18094,73 +18052,73 @@
         <v>3</v>
       </c>
       <c r="D665" s="1" t="s">
-        <v>1366</v>
+        <v>1389</v>
       </c>
       <c r="E665" s="1" t="s">
-        <v>40</v>
+        <v>4</v>
       </c>
       <c r="F665" s="1" t="s">
-        <v>25</v>
+        <v>1390</v>
       </c>
     </row>
     <row r="666" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A666" s="1" t="s">
+        <v>1391</v>
+      </c>
+      <c r="B666" s="1" t="s">
+        <v>1392</v>
+      </c>
+      <c r="C666" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D666" s="1" t="s">
         <v>1389</v>
       </c>
-      <c r="B666" s="1" t="s">
+      <c r="E666" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="F666" s="1" t="s">
         <v>1390</v>
-      </c>
-      <c r="C666" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D666" s="1" t="s">
-        <v>1366</v>
-      </c>
-      <c r="E666" s="1" t="s">
-        <v>68</v>
-      </c>
-      <c r="F666" s="1" t="s">
-        <v>25</v>
       </c>
     </row>
     <row r="667" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A667" s="1" t="s">
-        <v>1391</v>
+        <v>1393</v>
       </c>
       <c r="B667" s="1" t="s">
-        <v>1392</v>
+        <v>1394</v>
       </c>
       <c r="C667" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D667" s="1" t="s">
-        <v>1366</v>
+        <v>1389</v>
       </c>
       <c r="E667" s="1" t="s">
-        <v>100</v>
+        <v>12</v>
       </c>
       <c r="F667" s="1" t="s">
-        <v>25</v>
+        <v>1390</v>
       </c>
     </row>
     <row r="668" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A668" s="1" t="s">
-        <v>1393</v>
+        <v>1395</v>
       </c>
       <c r="B668" s="1" t="s">
-        <v>1394</v>
+        <v>1396</v>
       </c>
       <c r="C668" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D668" s="1" t="s">
-        <v>1395</v>
+        <v>1389</v>
       </c>
       <c r="E668" s="1" t="s">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="F668" s="1" t="s">
-        <v>1396</v>
+        <v>1390</v>
       </c>
     </row>
     <row r="669" spans="1:6" x14ac:dyDescent="0.25">
@@ -18174,13 +18132,13 @@
         <v>3</v>
       </c>
       <c r="D669" s="1" t="s">
-        <v>1395</v>
+        <v>1389</v>
       </c>
       <c r="E669" s="1" t="s">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="F669" s="1" t="s">
-        <v>1396</v>
+        <v>1390</v>
       </c>
     </row>
     <row r="670" spans="1:6" x14ac:dyDescent="0.25">
@@ -18194,13 +18152,13 @@
         <v>3</v>
       </c>
       <c r="D670" s="1" t="s">
-        <v>1395</v>
+        <v>1389</v>
       </c>
       <c r="E670" s="1" t="s">
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="F670" s="1" t="s">
-        <v>1396</v>
+        <v>1390</v>
       </c>
     </row>
     <row r="671" spans="1:6" x14ac:dyDescent="0.25">
@@ -18214,13 +18172,13 @@
         <v>3</v>
       </c>
       <c r="D671" s="1" t="s">
-        <v>1395</v>
+        <v>1389</v>
       </c>
       <c r="E671" s="1" t="s">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="F671" s="1" t="s">
-        <v>1396</v>
+        <v>1390</v>
       </c>
     </row>
     <row r="672" spans="1:6" x14ac:dyDescent="0.25">
@@ -18234,13 +18192,13 @@
         <v>3</v>
       </c>
       <c r="D672" s="1" t="s">
-        <v>1395</v>
+        <v>1389</v>
       </c>
       <c r="E672" s="1" t="s">
-        <v>18</v>
+        <v>28</v>
       </c>
       <c r="F672" s="1" t="s">
-        <v>1396</v>
+        <v>231</v>
       </c>
     </row>
     <row r="673" spans="1:6" x14ac:dyDescent="0.25">
@@ -18254,13 +18212,13 @@
         <v>3</v>
       </c>
       <c r="D673" s="1" t="s">
-        <v>1395</v>
+        <v>1389</v>
       </c>
       <c r="E673" s="1" t="s">
-        <v>21</v>
+        <v>31</v>
       </c>
       <c r="F673" s="1" t="s">
-        <v>1396</v>
+        <v>5</v>
       </c>
     </row>
     <row r="674" spans="1:6" x14ac:dyDescent="0.25">
@@ -18274,13 +18232,13 @@
         <v>3</v>
       </c>
       <c r="D674" s="1" t="s">
-        <v>1395</v>
+        <v>1389</v>
       </c>
       <c r="E674" s="1" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
       <c r="F674" s="1" t="s">
-        <v>1396</v>
+        <v>1390</v>
       </c>
     </row>
     <row r="675" spans="1:6" x14ac:dyDescent="0.25">
@@ -18294,13 +18252,13 @@
         <v>3</v>
       </c>
       <c r="D675" s="1" t="s">
-        <v>1395</v>
+        <v>1389</v>
       </c>
       <c r="E675" s="1" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="F675" s="1" t="s">
-        <v>231</v>
+        <v>1390</v>
       </c>
     </row>
     <row r="676" spans="1:6" x14ac:dyDescent="0.25">
@@ -18314,13 +18272,13 @@
         <v>3</v>
       </c>
       <c r="D676" s="1" t="s">
-        <v>1395</v>
+        <v>1389</v>
       </c>
       <c r="E676" s="1" t="s">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="F676" s="1" t="s">
-        <v>5</v>
+        <v>1390</v>
       </c>
     </row>
     <row r="677" spans="1:6" x14ac:dyDescent="0.25">
@@ -18334,13 +18292,13 @@
         <v>3</v>
       </c>
       <c r="D677" s="1" t="s">
-        <v>1395</v>
+        <v>1389</v>
       </c>
       <c r="E677" s="1" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="F677" s="1" t="s">
-        <v>1396</v>
+        <v>1390</v>
       </c>
     </row>
     <row r="678" spans="1:6" x14ac:dyDescent="0.25">
@@ -18354,13 +18312,13 @@
         <v>3</v>
       </c>
       <c r="D678" s="1" t="s">
-        <v>1395</v>
+        <v>1389</v>
       </c>
       <c r="E678" s="1" t="s">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="F678" s="1" t="s">
-        <v>1396</v>
+        <v>231</v>
       </c>
     </row>
     <row r="679" spans="1:6" x14ac:dyDescent="0.25">
@@ -18374,13 +18332,13 @@
         <v>3</v>
       </c>
       <c r="D679" s="1" t="s">
-        <v>1395</v>
+        <v>1389</v>
       </c>
       <c r="E679" s="1" t="s">
-        <v>37</v>
+        <v>68</v>
       </c>
       <c r="F679" s="1" t="s">
-        <v>1396</v>
+        <v>1390</v>
       </c>
     </row>
     <row r="680" spans="1:6" x14ac:dyDescent="0.25">
@@ -18394,73 +18352,73 @@
         <v>3</v>
       </c>
       <c r="D680" s="1" t="s">
-        <v>1395</v>
+        <v>1421</v>
       </c>
       <c r="E680" s="1" t="s">
-        <v>37</v>
+        <v>4</v>
       </c>
       <c r="F680" s="1" t="s">
-        <v>1396</v>
+        <v>5</v>
       </c>
     </row>
     <row r="681" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A681" s="1" t="s">
+        <v>1422</v>
+      </c>
+      <c r="B681" s="1" t="s">
+        <v>1423</v>
+      </c>
+      <c r="C681" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D681" s="1" t="s">
         <v>1421</v>
       </c>
-      <c r="B681" s="1" t="s">
-        <v>1422</v>
-      </c>
-      <c r="C681" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D681" s="1" t="s">
-        <v>1395</v>
-      </c>
       <c r="E681" s="1" t="s">
-        <v>40</v>
+        <v>8</v>
       </c>
       <c r="F681" s="1" t="s">
-        <v>231</v>
+        <v>5</v>
       </c>
     </row>
     <row r="682" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A682" s="1" t="s">
-        <v>1423</v>
+        <v>1424</v>
       </c>
       <c r="B682" s="1" t="s">
-        <v>1424</v>
+        <v>1425</v>
       </c>
       <c r="C682" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D682" s="1" t="s">
-        <v>1395</v>
+        <v>1421</v>
       </c>
       <c r="E682" s="1" t="s">
-        <v>68</v>
+        <v>12</v>
       </c>
       <c r="F682" s="1" t="s">
-        <v>1396</v>
+        <v>5</v>
       </c>
     </row>
     <row r="683" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A683" s="1" t="s">
-        <v>1425</v>
+        <v>1426</v>
       </c>
       <c r="B683" s="1" t="s">
-        <v>1426</v>
+        <v>1427</v>
       </c>
       <c r="C683" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D683" s="1" t="s">
-        <v>1427</v>
+        <v>1421</v>
       </c>
       <c r="E683" s="1" t="s">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="F683" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="684" spans="1:6" x14ac:dyDescent="0.25">
@@ -18474,13 +18432,13 @@
         <v>3</v>
       </c>
       <c r="D684" s="1" t="s">
-        <v>1427</v>
+        <v>1421</v>
       </c>
       <c r="E684" s="1" t="s">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="F684" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="685" spans="1:6" x14ac:dyDescent="0.25">
@@ -18494,10 +18452,10 @@
         <v>3</v>
       </c>
       <c r="D685" s="1" t="s">
-        <v>1427</v>
+        <v>1421</v>
       </c>
       <c r="E685" s="1" t="s">
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="F685" s="1" t="s">
         <v>5</v>
@@ -18514,10 +18472,10 @@
         <v>3</v>
       </c>
       <c r="D686" s="1" t="s">
-        <v>1427</v>
+        <v>1421</v>
       </c>
       <c r="E686" s="1" t="s">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="F686" s="1" t="s">
         <v>9</v>
@@ -18534,13 +18492,13 @@
         <v>3</v>
       </c>
       <c r="D687" s="1" t="s">
-        <v>1427</v>
+        <v>1421</v>
       </c>
       <c r="E687" s="1" t="s">
-        <v>18</v>
+        <v>28</v>
       </c>
       <c r="F687" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="688" spans="1:6" x14ac:dyDescent="0.25">
@@ -18554,13 +18512,13 @@
         <v>3</v>
       </c>
       <c r="D688" s="1" t="s">
-        <v>1427</v>
+        <v>1421</v>
       </c>
       <c r="E688" s="1" t="s">
-        <v>21</v>
+        <v>31</v>
       </c>
       <c r="F688" s="1" t="s">
-        <v>5</v>
+        <v>41</v>
       </c>
     </row>
     <row r="689" spans="1:6" x14ac:dyDescent="0.25">
@@ -18574,10 +18532,10 @@
         <v>3</v>
       </c>
       <c r="D689" s="1" t="s">
-        <v>1427</v>
+        <v>1421</v>
       </c>
       <c r="E689" s="1" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
       <c r="F689" s="1" t="s">
         <v>9</v>
@@ -18594,13 +18552,13 @@
         <v>3</v>
       </c>
       <c r="D690" s="1" t="s">
-        <v>1427</v>
+        <v>1421</v>
       </c>
       <c r="E690" s="1" t="s">
-        <v>28</v>
+        <v>37</v>
       </c>
       <c r="F690" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="691" spans="1:6" x14ac:dyDescent="0.25">
@@ -18614,13 +18572,13 @@
         <v>3</v>
       </c>
       <c r="D691" s="1" t="s">
-        <v>1427</v>
+        <v>1421</v>
       </c>
       <c r="E691" s="1" t="s">
-        <v>31</v>
+        <v>40</v>
       </c>
       <c r="F691" s="1" t="s">
-        <v>41</v>
+        <v>9</v>
       </c>
     </row>
     <row r="692" spans="1:6" x14ac:dyDescent="0.25">
@@ -18634,172 +18592,32 @@
         <v>3</v>
       </c>
       <c r="D692" s="1" t="s">
-        <v>1427</v>
+        <v>1446</v>
       </c>
       <c r="E692" s="1" t="s">
-        <v>34</v>
+        <v>8</v>
       </c>
       <c r="F692" s="1" t="s">
-        <v>9</v>
+        <v>25</v>
       </c>
     </row>
     <row r="693" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A693" s="1" t="s">
+        <v>1447</v>
+      </c>
+      <c r="B693" s="1" t="s">
+        <v>1448</v>
+      </c>
+      <c r="C693" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D693" s="1" t="s">
         <v>1446</v>
       </c>
-      <c r="B693" s="1" t="s">
-        <v>1447</v>
-      </c>
-      <c r="C693" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D693" s="1" t="s">
-        <v>1427</v>
-      </c>
       <c r="E693" s="1" t="s">
-        <v>37</v>
+        <v>12</v>
       </c>
       <c r="F693" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="694" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A694" s="1" t="s">
-        <v>1448</v>
-      </c>
-      <c r="B694" s="1" t="s">
-        <v>1449</v>
-      </c>
-      <c r="C694" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D694" s="1" t="s">
-        <v>1427</v>
-      </c>
-      <c r="E694" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="F694" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="695" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A695" s="1" t="s">
-        <v>1450</v>
-      </c>
-      <c r="B695" s="1" t="s">
-        <v>1451</v>
-      </c>
-      <c r="C695" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D695" s="1" t="s">
-        <v>1452</v>
-      </c>
-      <c r="E695" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="F695" s="1" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="696" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A696" s="1" t="s">
-        <v>1453</v>
-      </c>
-      <c r="B696" s="1" t="s">
-        <v>1454</v>
-      </c>
-      <c r="C696" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D696" s="1" t="s">
-        <v>1452</v>
-      </c>
-      <c r="E696" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="F696" s="1" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="697" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A697" s="1" t="s">
-        <v>1455</v>
-      </c>
-      <c r="B697" s="1" t="s">
-        <v>1456</v>
-      </c>
-      <c r="C697" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D697" s="1" t="s">
-        <v>1452</v>
-      </c>
-      <c r="E697" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="F697" s="1" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="698" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A698" s="1" t="s">
-        <v>1457</v>
-      </c>
-      <c r="B698" s="1" t="s">
-        <v>1458</v>
-      </c>
-      <c r="C698" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D698" s="1" t="s">
-        <v>1452</v>
-      </c>
-      <c r="E698" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="F698" s="1" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="699" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A699" s="1" t="s">
-        <v>1459</v>
-      </c>
-      <c r="B699" s="1" t="s">
-        <v>1460</v>
-      </c>
-      <c r="C699" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D699" s="1" t="s">
-        <v>1452</v>
-      </c>
-      <c r="E699" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="F699" s="1" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="700" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A700" s="1" t="s">
-        <v>1461</v>
-      </c>
-      <c r="B700" s="1" t="s">
-        <v>1462</v>
-      </c>
-      <c r="C700" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D700" s="1" t="s">
-        <v>1452</v>
-      </c>
-      <c r="E700" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="F700" s="1" t="s">
         <v>5</v>
       </c>
     </row>

--- a/PCE06D.xlsx
+++ b/PCE06D.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4158" uniqueCount="1449">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4158" uniqueCount="1448">
   <si>
     <t/>
   </si>
@@ -2246,9 +2246,6 @@
   </si>
   <si>
     <t>WHITE INC BL ALPH180</t>
-  </si>
-  <si>
-    <t>,(E-3B)</t>
   </si>
   <si>
     <t>20136931</t>
@@ -11838,15 +11835,15 @@
         <v>37</v>
       </c>
       <c r="F354" s="1" t="s">
-        <v>745</v>
+        <v>5</v>
       </c>
     </row>
     <row r="355" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A355" s="1" t="s">
+        <v>745</v>
+      </c>
+      <c r="B355" s="1" t="s">
         <v>746</v>
-      </c>
-      <c r="B355" s="1" t="s">
-        <v>747</v>
       </c>
       <c r="C355" s="1" t="s">
         <v>3</v>
@@ -11863,10 +11860,10 @@
     </row>
     <row r="356" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A356" s="1" t="s">
+        <v>747</v>
+      </c>
+      <c r="B356" s="1" t="s">
         <v>748</v>
-      </c>
-      <c r="B356" s="1" t="s">
-        <v>749</v>
       </c>
       <c r="C356" s="1" t="s">
         <v>3</v>
@@ -11883,10 +11880,10 @@
     </row>
     <row r="357" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A357" s="1" t="s">
+        <v>749</v>
+      </c>
+      <c r="B357" s="1" t="s">
         <v>750</v>
-      </c>
-      <c r="B357" s="1" t="s">
-        <v>751</v>
       </c>
       <c r="C357" s="1" t="s">
         <v>3</v>
@@ -11903,16 +11900,16 @@
     </row>
     <row r="358" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A358" s="1" t="s">
+        <v>751</v>
+      </c>
+      <c r="B358" s="1" t="s">
         <v>752</v>
       </c>
-      <c r="B358" s="1" t="s">
+      <c r="C358" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D358" s="1" t="s">
         <v>753</v>
-      </c>
-      <c r="C358" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D358" s="1" t="s">
-        <v>754</v>
       </c>
       <c r="E358" s="1" t="s">
         <v>4</v>
@@ -11923,16 +11920,16 @@
     </row>
     <row r="359" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A359" s="1" t="s">
+        <v>754</v>
+      </c>
+      <c r="B359" s="1" t="s">
         <v>755</v>
       </c>
-      <c r="B359" s="1" t="s">
-        <v>756</v>
-      </c>
       <c r="C359" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D359" s="1" t="s">
-        <v>754</v>
+        <v>753</v>
       </c>
       <c r="E359" s="1" t="s">
         <v>8</v>
@@ -11943,16 +11940,16 @@
     </row>
     <row r="360" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A360" s="1" t="s">
+        <v>756</v>
+      </c>
+      <c r="B360" s="1" t="s">
         <v>757</v>
       </c>
-      <c r="B360" s="1" t="s">
-        <v>758</v>
-      </c>
       <c r="C360" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D360" s="1" t="s">
-        <v>754</v>
+        <v>753</v>
       </c>
       <c r="E360" s="1" t="s">
         <v>12</v>
@@ -11963,16 +11960,16 @@
     </row>
     <row r="361" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A361" s="1" t="s">
+        <v>758</v>
+      </c>
+      <c r="B361" s="1" t="s">
         <v>759</v>
       </c>
-      <c r="B361" s="1" t="s">
-        <v>760</v>
-      </c>
       <c r="C361" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D361" s="1" t="s">
-        <v>754</v>
+        <v>753</v>
       </c>
       <c r="E361" s="1" t="s">
         <v>15</v>
@@ -11983,16 +11980,16 @@
     </row>
     <row r="362" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A362" s="1" t="s">
+        <v>760</v>
+      </c>
+      <c r="B362" s="1" t="s">
         <v>761</v>
       </c>
-      <c r="B362" s="1" t="s">
-        <v>762</v>
-      </c>
       <c r="C362" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D362" s="1" t="s">
-        <v>754</v>
+        <v>753</v>
       </c>
       <c r="E362" s="1" t="s">
         <v>18</v>
@@ -12003,16 +12000,16 @@
     </row>
     <row r="363" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A363" s="1" t="s">
+        <v>762</v>
+      </c>
+      <c r="B363" s="1" t="s">
         <v>763</v>
       </c>
-      <c r="B363" s="1" t="s">
-        <v>764</v>
-      </c>
       <c r="C363" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D363" s="1" t="s">
-        <v>754</v>
+        <v>753</v>
       </c>
       <c r="E363" s="1" t="s">
         <v>21</v>
@@ -12023,16 +12020,16 @@
     </row>
     <row r="364" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A364" s="1" t="s">
+        <v>764</v>
+      </c>
+      <c r="B364" s="1" t="s">
         <v>765</v>
       </c>
-      <c r="B364" s="1" t="s">
-        <v>766</v>
-      </c>
       <c r="C364" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D364" s="1" t="s">
-        <v>754</v>
+        <v>753</v>
       </c>
       <c r="E364" s="1" t="s">
         <v>24</v>
@@ -12043,16 +12040,16 @@
     </row>
     <row r="365" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A365" s="1" t="s">
+        <v>766</v>
+      </c>
+      <c r="B365" s="1" t="s">
         <v>767</v>
       </c>
-      <c r="B365" s="1" t="s">
-        <v>768</v>
-      </c>
       <c r="C365" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D365" s="1" t="s">
-        <v>754</v>
+        <v>753</v>
       </c>
       <c r="E365" s="1" t="s">
         <v>28</v>
@@ -12063,16 +12060,16 @@
     </row>
     <row r="366" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A366" s="1" t="s">
+        <v>768</v>
+      </c>
+      <c r="B366" s="1" t="s">
         <v>769</v>
       </c>
-      <c r="B366" s="1" t="s">
-        <v>770</v>
-      </c>
       <c r="C366" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D366" s="1" t="s">
-        <v>754</v>
+        <v>753</v>
       </c>
       <c r="E366" s="1" t="s">
         <v>31</v>
@@ -12083,16 +12080,16 @@
     </row>
     <row r="367" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A367" s="1" t="s">
+        <v>770</v>
+      </c>
+      <c r="B367" s="1" t="s">
         <v>771</v>
       </c>
-      <c r="B367" s="1" t="s">
-        <v>772</v>
-      </c>
       <c r="C367" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D367" s="1" t="s">
-        <v>754</v>
+        <v>753</v>
       </c>
       <c r="E367" s="1" t="s">
         <v>34</v>
@@ -12103,16 +12100,16 @@
     </row>
     <row r="368" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A368" s="1" t="s">
+        <v>772</v>
+      </c>
+      <c r="B368" s="1" t="s">
         <v>773</v>
       </c>
-      <c r="B368" s="1" t="s">
-        <v>774</v>
-      </c>
       <c r="C368" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D368" s="1" t="s">
-        <v>754</v>
+        <v>753</v>
       </c>
       <c r="E368" s="1" t="s">
         <v>37</v>
@@ -12123,16 +12120,16 @@
     </row>
     <row r="369" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A369" s="1" t="s">
+        <v>774</v>
+      </c>
+      <c r="B369" s="1" t="s">
         <v>775</v>
       </c>
-      <c r="B369" s="1" t="s">
-        <v>776</v>
-      </c>
       <c r="C369" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D369" s="1" t="s">
-        <v>754</v>
+        <v>753</v>
       </c>
       <c r="E369" s="1" t="s">
         <v>40</v>
@@ -12143,16 +12140,16 @@
     </row>
     <row r="370" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A370" s="1" t="s">
+        <v>776</v>
+      </c>
+      <c r="B370" s="1" t="s">
         <v>777</v>
       </c>
-      <c r="B370" s="1" t="s">
-        <v>778</v>
-      </c>
       <c r="C370" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D370" s="1" t="s">
-        <v>754</v>
+        <v>753</v>
       </c>
       <c r="E370" s="1" t="s">
         <v>68</v>
@@ -12163,16 +12160,16 @@
     </row>
     <row r="371" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A371" s="1" t="s">
+        <v>778</v>
+      </c>
+      <c r="B371" s="1" t="s">
         <v>779</v>
       </c>
-      <c r="B371" s="1" t="s">
-        <v>780</v>
-      </c>
       <c r="C371" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D371" s="1" t="s">
-        <v>754</v>
+        <v>753</v>
       </c>
       <c r="E371" s="1" t="s">
         <v>100</v>
@@ -12183,16 +12180,16 @@
     </row>
     <row r="372" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A372" s="1" t="s">
+        <v>780</v>
+      </c>
+      <c r="B372" s="1" t="s">
         <v>781</v>
       </c>
-      <c r="B372" s="1" t="s">
-        <v>782</v>
-      </c>
       <c r="C372" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D372" s="1" t="s">
-        <v>754</v>
+        <v>753</v>
       </c>
       <c r="E372" s="1" t="s">
         <v>103</v>
@@ -12203,16 +12200,16 @@
     </row>
     <row r="373" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A373" s="1" t="s">
+        <v>782</v>
+      </c>
+      <c r="B373" s="1" t="s">
         <v>783</v>
       </c>
-      <c r="B373" s="1" t="s">
-        <v>784</v>
-      </c>
       <c r="C373" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D373" s="1" t="s">
-        <v>754</v>
+        <v>753</v>
       </c>
       <c r="E373" s="1" t="s">
         <v>106</v>
@@ -12223,16 +12220,16 @@
     </row>
     <row r="374" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A374" s="1" t="s">
+        <v>784</v>
+      </c>
+      <c r="B374" s="1" t="s">
         <v>785</v>
       </c>
-      <c r="B374" s="1" t="s">
-        <v>786</v>
-      </c>
       <c r="C374" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D374" s="1" t="s">
-        <v>754</v>
+        <v>753</v>
       </c>
       <c r="E374" s="1" t="s">
         <v>109</v>
@@ -12243,16 +12240,16 @@
     </row>
     <row r="375" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A375" s="1" t="s">
+        <v>786</v>
+      </c>
+      <c r="B375" s="1" t="s">
         <v>787</v>
       </c>
-      <c r="B375" s="1" t="s">
-        <v>788</v>
-      </c>
       <c r="C375" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D375" s="1" t="s">
-        <v>754</v>
+        <v>753</v>
       </c>
       <c r="E375" s="1" t="s">
         <v>112</v>
@@ -12263,16 +12260,16 @@
     </row>
     <row r="376" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A376" s="1" t="s">
+        <v>788</v>
+      </c>
+      <c r="B376" s="1" t="s">
         <v>789</v>
       </c>
-      <c r="B376" s="1" t="s">
-        <v>790</v>
-      </c>
       <c r="C376" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D376" s="1" t="s">
-        <v>754</v>
+        <v>753</v>
       </c>
       <c r="E376" s="1" t="s">
         <v>152</v>
@@ -12283,16 +12280,16 @@
     </row>
     <row r="377" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A377" s="1" t="s">
+        <v>790</v>
+      </c>
+      <c r="B377" s="1" t="s">
         <v>791</v>
       </c>
-      <c r="B377" s="1" t="s">
+      <c r="C377" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D377" s="1" t="s">
         <v>792</v>
-      </c>
-      <c r="C377" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D377" s="1" t="s">
-        <v>793</v>
       </c>
       <c r="E377" s="1" t="s">
         <v>4</v>
@@ -12303,16 +12300,16 @@
     </row>
     <row r="378" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A378" s="1" t="s">
+        <v>793</v>
+      </c>
+      <c r="B378" s="1" t="s">
         <v>794</v>
       </c>
-      <c r="B378" s="1" t="s">
-        <v>795</v>
-      </c>
       <c r="C378" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D378" s="1" t="s">
-        <v>793</v>
+        <v>792</v>
       </c>
       <c r="E378" s="1" t="s">
         <v>8</v>
@@ -12323,16 +12320,16 @@
     </row>
     <row r="379" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A379" s="1" t="s">
+        <v>795</v>
+      </c>
+      <c r="B379" s="1" t="s">
         <v>796</v>
       </c>
-      <c r="B379" s="1" t="s">
-        <v>797</v>
-      </c>
       <c r="C379" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D379" s="1" t="s">
-        <v>793</v>
+        <v>792</v>
       </c>
       <c r="E379" s="1" t="s">
         <v>12</v>
@@ -12343,16 +12340,16 @@
     </row>
     <row r="380" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A380" s="1" t="s">
+        <v>797</v>
+      </c>
+      <c r="B380" s="1" t="s">
         <v>798</v>
       </c>
-      <c r="B380" s="1" t="s">
-        <v>799</v>
-      </c>
       <c r="C380" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D380" s="1" t="s">
-        <v>793</v>
+        <v>792</v>
       </c>
       <c r="E380" s="1" t="s">
         <v>15</v>
@@ -12363,16 +12360,16 @@
     </row>
     <row r="381" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A381" s="1" t="s">
+        <v>799</v>
+      </c>
+      <c r="B381" s="1" t="s">
         <v>800</v>
       </c>
-      <c r="B381" s="1" t="s">
-        <v>801</v>
-      </c>
       <c r="C381" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D381" s="1" t="s">
-        <v>793</v>
+        <v>792</v>
       </c>
       <c r="E381" s="1" t="s">
         <v>18</v>
@@ -12383,16 +12380,16 @@
     </row>
     <row r="382" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A382" s="1" t="s">
+        <v>801</v>
+      </c>
+      <c r="B382" s="1" t="s">
         <v>802</v>
       </c>
-      <c r="B382" s="1" t="s">
-        <v>803</v>
-      </c>
       <c r="C382" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D382" s="1" t="s">
-        <v>793</v>
+        <v>792</v>
       </c>
       <c r="E382" s="1" t="s">
         <v>21</v>
@@ -12403,16 +12400,16 @@
     </row>
     <row r="383" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A383" s="1" t="s">
+        <v>803</v>
+      </c>
+      <c r="B383" s="1" t="s">
         <v>804</v>
       </c>
-      <c r="B383" s="1" t="s">
-        <v>805</v>
-      </c>
       <c r="C383" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D383" s="1" t="s">
-        <v>793</v>
+        <v>792</v>
       </c>
       <c r="E383" s="1" t="s">
         <v>24</v>
@@ -12423,16 +12420,16 @@
     </row>
     <row r="384" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A384" s="1" t="s">
+        <v>805</v>
+      </c>
+      <c r="B384" s="1" t="s">
         <v>806</v>
       </c>
-      <c r="B384" s="1" t="s">
-        <v>807</v>
-      </c>
       <c r="C384" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D384" s="1" t="s">
-        <v>793</v>
+        <v>792</v>
       </c>
       <c r="E384" s="1" t="s">
         <v>28</v>
@@ -12443,16 +12440,16 @@
     </row>
     <row r="385" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A385" s="1" t="s">
+        <v>807</v>
+      </c>
+      <c r="B385" s="1" t="s">
         <v>808</v>
       </c>
-      <c r="B385" s="1" t="s">
-        <v>809</v>
-      </c>
       <c r="C385" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D385" s="1" t="s">
-        <v>793</v>
+        <v>792</v>
       </c>
       <c r="E385" s="1" t="s">
         <v>31</v>
@@ -12463,16 +12460,16 @@
     </row>
     <row r="386" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A386" s="1" t="s">
+        <v>809</v>
+      </c>
+      <c r="B386" s="1" t="s">
         <v>810</v>
       </c>
-      <c r="B386" s="1" t="s">
-        <v>811</v>
-      </c>
       <c r="C386" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D386" s="1" t="s">
-        <v>793</v>
+        <v>792</v>
       </c>
       <c r="E386" s="1" t="s">
         <v>34</v>
@@ -12483,16 +12480,16 @@
     </row>
     <row r="387" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A387" s="1" t="s">
+        <v>811</v>
+      </c>
+      <c r="B387" s="1" t="s">
         <v>812</v>
       </c>
-      <c r="B387" s="1" t="s">
-        <v>813</v>
-      </c>
       <c r="C387" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D387" s="1" t="s">
-        <v>793</v>
+        <v>792</v>
       </c>
       <c r="E387" s="1" t="s">
         <v>37</v>
@@ -12503,16 +12500,16 @@
     </row>
     <row r="388" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A388" s="1" t="s">
+        <v>813</v>
+      </c>
+      <c r="B388" s="1" t="s">
         <v>814</v>
       </c>
-      <c r="B388" s="1" t="s">
-        <v>815</v>
-      </c>
       <c r="C388" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D388" s="1" t="s">
-        <v>793</v>
+        <v>792</v>
       </c>
       <c r="E388" s="1" t="s">
         <v>40</v>
@@ -12523,16 +12520,16 @@
     </row>
     <row r="389" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A389" s="1" t="s">
+        <v>815</v>
+      </c>
+      <c r="B389" s="1" t="s">
         <v>816</v>
       </c>
-      <c r="B389" s="1" t="s">
-        <v>817</v>
-      </c>
       <c r="C389" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D389" s="1" t="s">
-        <v>793</v>
+        <v>792</v>
       </c>
       <c r="E389" s="1" t="s">
         <v>68</v>
@@ -12543,16 +12540,16 @@
     </row>
     <row r="390" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A390" s="1" t="s">
+        <v>817</v>
+      </c>
+      <c r="B390" s="1" t="s">
         <v>818</v>
       </c>
-      <c r="B390" s="1" t="s">
-        <v>819</v>
-      </c>
       <c r="C390" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D390" s="1" t="s">
-        <v>793</v>
+        <v>792</v>
       </c>
       <c r="E390" s="1" t="s">
         <v>100</v>
@@ -12563,16 +12560,16 @@
     </row>
     <row r="391" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A391" s="1" t="s">
+        <v>819</v>
+      </c>
+      <c r="B391" s="1" t="s">
         <v>820</v>
       </c>
-      <c r="B391" s="1" t="s">
-        <v>821</v>
-      </c>
       <c r="C391" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D391" s="1" t="s">
-        <v>793</v>
+        <v>792</v>
       </c>
       <c r="E391" s="1" t="s">
         <v>103</v>
@@ -12583,16 +12580,16 @@
     </row>
     <row r="392" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A392" s="1" t="s">
+        <v>821</v>
+      </c>
+      <c r="B392" s="1" t="s">
         <v>822</v>
       </c>
-      <c r="B392" s="1" t="s">
-        <v>823</v>
-      </c>
       <c r="C392" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D392" s="1" t="s">
-        <v>793</v>
+        <v>792</v>
       </c>
       <c r="E392" s="1" t="s">
         <v>106</v>
@@ -12603,16 +12600,16 @@
     </row>
     <row r="393" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A393" s="1" t="s">
+        <v>823</v>
+      </c>
+      <c r="B393" s="1" t="s">
         <v>824</v>
       </c>
-      <c r="B393" s="1" t="s">
-        <v>825</v>
-      </c>
       <c r="C393" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D393" s="1" t="s">
-        <v>793</v>
+        <v>792</v>
       </c>
       <c r="E393" s="1" t="s">
         <v>109</v>
@@ -12623,16 +12620,16 @@
     </row>
     <row r="394" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A394" s="1" t="s">
+        <v>825</v>
+      </c>
+      <c r="B394" s="1" t="s">
         <v>826</v>
       </c>
-      <c r="B394" s="1" t="s">
-        <v>827</v>
-      </c>
       <c r="C394" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D394" s="1" t="s">
-        <v>793</v>
+        <v>792</v>
       </c>
       <c r="E394" s="1" t="s">
         <v>112</v>
@@ -12643,16 +12640,16 @@
     </row>
     <row r="395" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A395" s="1" t="s">
+        <v>827</v>
+      </c>
+      <c r="B395" s="1" t="s">
         <v>828</v>
       </c>
-      <c r="B395" s="1" t="s">
-        <v>829</v>
-      </c>
       <c r="C395" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D395" s="1" t="s">
-        <v>793</v>
+        <v>792</v>
       </c>
       <c r="E395" s="1" t="s">
         <v>152</v>
@@ -12663,16 +12660,16 @@
     </row>
     <row r="396" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A396" s="1" t="s">
+        <v>829</v>
+      </c>
+      <c r="B396" s="1" t="s">
         <v>830</v>
       </c>
-      <c r="B396" s="1" t="s">
-        <v>831</v>
-      </c>
       <c r="C396" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D396" s="1" t="s">
-        <v>793</v>
+        <v>792</v>
       </c>
       <c r="E396" s="1" t="s">
         <v>155</v>
@@ -12683,16 +12680,16 @@
     </row>
     <row r="397" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A397" s="1" t="s">
+        <v>831</v>
+      </c>
+      <c r="B397" s="1" t="s">
         <v>832</v>
       </c>
-      <c r="B397" s="1" t="s">
+      <c r="C397" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D397" s="1" t="s">
         <v>833</v>
-      </c>
-      <c r="C397" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D397" s="1" t="s">
-        <v>834</v>
       </c>
       <c r="E397" s="1" t="s">
         <v>4</v>
@@ -12703,16 +12700,16 @@
     </row>
     <row r="398" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A398" s="1" t="s">
+        <v>834</v>
+      </c>
+      <c r="B398" s="1" t="s">
         <v>835</v>
       </c>
-      <c r="B398" s="1" t="s">
-        <v>836</v>
-      </c>
       <c r="C398" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D398" s="1" t="s">
-        <v>834</v>
+        <v>833</v>
       </c>
       <c r="E398" s="1" t="s">
         <v>8</v>
@@ -12723,16 +12720,16 @@
     </row>
     <row r="399" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A399" s="1" t="s">
+        <v>836</v>
+      </c>
+      <c r="B399" s="1" t="s">
         <v>837</v>
       </c>
-      <c r="B399" s="1" t="s">
-        <v>838</v>
-      </c>
       <c r="C399" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D399" s="1" t="s">
-        <v>834</v>
+        <v>833</v>
       </c>
       <c r="E399" s="1" t="s">
         <v>12</v>
@@ -12743,16 +12740,16 @@
     </row>
     <row r="400" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A400" s="1" t="s">
+        <v>838</v>
+      </c>
+      <c r="B400" s="1" t="s">
         <v>839</v>
       </c>
-      <c r="B400" s="1" t="s">
-        <v>840</v>
-      </c>
       <c r="C400" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D400" s="1" t="s">
-        <v>834</v>
+        <v>833</v>
       </c>
       <c r="E400" s="1" t="s">
         <v>15</v>
@@ -12763,16 +12760,16 @@
     </row>
     <row r="401" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A401" s="1" t="s">
+        <v>840</v>
+      </c>
+      <c r="B401" s="1" t="s">
         <v>841</v>
       </c>
-      <c r="B401" s="1" t="s">
-        <v>842</v>
-      </c>
       <c r="C401" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D401" s="1" t="s">
-        <v>834</v>
+        <v>833</v>
       </c>
       <c r="E401" s="1" t="s">
         <v>18</v>
@@ -12783,16 +12780,16 @@
     </row>
     <row r="402" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A402" s="1" t="s">
+        <v>842</v>
+      </c>
+      <c r="B402" s="1" t="s">
         <v>843</v>
       </c>
-      <c r="B402" s="1" t="s">
-        <v>844</v>
-      </c>
       <c r="C402" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D402" s="1" t="s">
-        <v>834</v>
+        <v>833</v>
       </c>
       <c r="E402" s="1" t="s">
         <v>21</v>
@@ -12803,16 +12800,16 @@
     </row>
     <row r="403" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A403" s="1" t="s">
+        <v>844</v>
+      </c>
+      <c r="B403" s="1" t="s">
         <v>845</v>
       </c>
-      <c r="B403" s="1" t="s">
-        <v>846</v>
-      </c>
       <c r="C403" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D403" s="1" t="s">
-        <v>834</v>
+        <v>833</v>
       </c>
       <c r="E403" s="1" t="s">
         <v>24</v>
@@ -12823,16 +12820,16 @@
     </row>
     <row r="404" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A404" s="1" t="s">
+        <v>846</v>
+      </c>
+      <c r="B404" s="1" t="s">
         <v>847</v>
       </c>
-      <c r="B404" s="1" t="s">
-        <v>848</v>
-      </c>
       <c r="C404" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D404" s="1" t="s">
-        <v>834</v>
+        <v>833</v>
       </c>
       <c r="E404" s="1" t="s">
         <v>28</v>
@@ -12843,16 +12840,16 @@
     </row>
     <row r="405" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A405" s="1" t="s">
+        <v>848</v>
+      </c>
+      <c r="B405" s="1" t="s">
         <v>849</v>
       </c>
-      <c r="B405" s="1" t="s">
-        <v>850</v>
-      </c>
       <c r="C405" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D405" s="1" t="s">
-        <v>834</v>
+        <v>833</v>
       </c>
       <c r="E405" s="1" t="s">
         <v>31</v>
@@ -12863,16 +12860,16 @@
     </row>
     <row r="406" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A406" s="1" t="s">
+        <v>850</v>
+      </c>
+      <c r="B406" s="1" t="s">
         <v>851</v>
       </c>
-      <c r="B406" s="1" t="s">
-        <v>852</v>
-      </c>
       <c r="C406" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D406" s="1" t="s">
-        <v>834</v>
+        <v>833</v>
       </c>
       <c r="E406" s="1" t="s">
         <v>34</v>
@@ -12883,16 +12880,16 @@
     </row>
     <row r="407" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A407" s="1" t="s">
+        <v>852</v>
+      </c>
+      <c r="B407" s="1" t="s">
         <v>853</v>
       </c>
-      <c r="B407" s="1" t="s">
-        <v>854</v>
-      </c>
       <c r="C407" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D407" s="1" t="s">
-        <v>834</v>
+        <v>833</v>
       </c>
       <c r="E407" s="1" t="s">
         <v>37</v>
@@ -12903,16 +12900,16 @@
     </row>
     <row r="408" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A408" s="1" t="s">
+        <v>854</v>
+      </c>
+      <c r="B408" s="1" t="s">
         <v>855</v>
       </c>
-      <c r="B408" s="1" t="s">
-        <v>856</v>
-      </c>
       <c r="C408" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D408" s="1" t="s">
-        <v>834</v>
+        <v>833</v>
       </c>
       <c r="E408" s="1" t="s">
         <v>40</v>
@@ -12923,16 +12920,16 @@
     </row>
     <row r="409" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A409" s="1" t="s">
+        <v>856</v>
+      </c>
+      <c r="B409" s="1" t="s">
         <v>857</v>
       </c>
-      <c r="B409" s="1" t="s">
-        <v>858</v>
-      </c>
       <c r="C409" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D409" s="1" t="s">
-        <v>834</v>
+        <v>833</v>
       </c>
       <c r="E409" s="1" t="s">
         <v>68</v>
@@ -12943,16 +12940,16 @@
     </row>
     <row r="410" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A410" s="1" t="s">
+        <v>858</v>
+      </c>
+      <c r="B410" s="1" t="s">
         <v>859</v>
       </c>
-      <c r="B410" s="1" t="s">
-        <v>860</v>
-      </c>
       <c r="C410" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D410" s="1" t="s">
-        <v>834</v>
+        <v>833</v>
       </c>
       <c r="E410" s="1" t="s">
         <v>100</v>
@@ -12963,16 +12960,16 @@
     </row>
     <row r="411" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A411" s="1" t="s">
+        <v>860</v>
+      </c>
+      <c r="B411" s="1" t="s">
         <v>861</v>
       </c>
-      <c r="B411" s="1" t="s">
-        <v>862</v>
-      </c>
       <c r="C411" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D411" s="1" t="s">
-        <v>834</v>
+        <v>833</v>
       </c>
       <c r="E411" s="1" t="s">
         <v>103</v>
@@ -12983,16 +12980,16 @@
     </row>
     <row r="412" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A412" s="1" t="s">
+        <v>862</v>
+      </c>
+      <c r="B412" s="1" t="s">
         <v>863</v>
       </c>
-      <c r="B412" s="1" t="s">
-        <v>864</v>
-      </c>
       <c r="C412" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D412" s="1" t="s">
-        <v>834</v>
+        <v>833</v>
       </c>
       <c r="E412" s="1" t="s">
         <v>106</v>
@@ -13003,16 +13000,16 @@
     </row>
     <row r="413" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A413" s="1" t="s">
+        <v>864</v>
+      </c>
+      <c r="B413" s="1" t="s">
         <v>865</v>
       </c>
-      <c r="B413" s="1" t="s">
-        <v>866</v>
-      </c>
       <c r="C413" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D413" s="1" t="s">
-        <v>834</v>
+        <v>833</v>
       </c>
       <c r="E413" s="1" t="s">
         <v>109</v>
@@ -13023,16 +13020,16 @@
     </row>
     <row r="414" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A414" s="1" t="s">
+        <v>866</v>
+      </c>
+      <c r="B414" s="1" t="s">
         <v>867</v>
       </c>
-      <c r="B414" s="1" t="s">
-        <v>868</v>
-      </c>
       <c r="C414" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D414" s="1" t="s">
-        <v>834</v>
+        <v>833</v>
       </c>
       <c r="E414" s="1" t="s">
         <v>112</v>
@@ -13043,16 +13040,16 @@
     </row>
     <row r="415" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A415" s="1" t="s">
+        <v>868</v>
+      </c>
+      <c r="B415" s="1" t="s">
         <v>869</v>
       </c>
-      <c r="B415" s="1" t="s">
-        <v>870</v>
-      </c>
       <c r="C415" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D415" s="1" t="s">
-        <v>834</v>
+        <v>833</v>
       </c>
       <c r="E415" s="1" t="s">
         <v>152</v>
@@ -13063,16 +13060,16 @@
     </row>
     <row r="416" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A416" s="1" t="s">
+        <v>870</v>
+      </c>
+      <c r="B416" s="1" t="s">
         <v>871</v>
       </c>
-      <c r="B416" s="1" t="s">
-        <v>872</v>
-      </c>
       <c r="C416" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D416" s="1" t="s">
-        <v>834</v>
+        <v>833</v>
       </c>
       <c r="E416" s="1" t="s">
         <v>155</v>
@@ -13083,16 +13080,16 @@
     </row>
     <row r="417" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A417" s="1" t="s">
+        <v>872</v>
+      </c>
+      <c r="B417" s="1" t="s">
         <v>873</v>
       </c>
-      <c r="B417" s="1" t="s">
-        <v>874</v>
-      </c>
       <c r="C417" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D417" s="1" t="s">
-        <v>834</v>
+        <v>833</v>
       </c>
       <c r="E417" s="1" t="s">
         <v>158</v>
@@ -13103,16 +13100,16 @@
     </row>
     <row r="418" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A418" s="1" t="s">
+        <v>874</v>
+      </c>
+      <c r="B418" s="1" t="s">
         <v>875</v>
       </c>
-      <c r="B418" s="1" t="s">
+      <c r="C418" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D418" s="1" t="s">
         <v>876</v>
-      </c>
-      <c r="C418" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D418" s="1" t="s">
-        <v>877</v>
       </c>
       <c r="E418" s="1" t="s">
         <v>4</v>
@@ -13123,16 +13120,16 @@
     </row>
     <row r="419" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A419" s="1" t="s">
+        <v>877</v>
+      </c>
+      <c r="B419" s="1" t="s">
         <v>878</v>
       </c>
-      <c r="B419" s="1" t="s">
-        <v>879</v>
-      </c>
       <c r="C419" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D419" s="1" t="s">
-        <v>877</v>
+        <v>876</v>
       </c>
       <c r="E419" s="1" t="s">
         <v>8</v>
@@ -13143,16 +13140,16 @@
     </row>
     <row r="420" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A420" s="1" t="s">
+        <v>879</v>
+      </c>
+      <c r="B420" s="1" t="s">
         <v>880</v>
       </c>
-      <c r="B420" s="1" t="s">
-        <v>881</v>
-      </c>
       <c r="C420" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D420" s="1" t="s">
-        <v>877</v>
+        <v>876</v>
       </c>
       <c r="E420" s="1" t="s">
         <v>12</v>
@@ -13163,16 +13160,16 @@
     </row>
     <row r="421" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A421" s="1" t="s">
+        <v>881</v>
+      </c>
+      <c r="B421" s="1" t="s">
         <v>882</v>
       </c>
-      <c r="B421" s="1" t="s">
-        <v>883</v>
-      </c>
       <c r="C421" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D421" s="1" t="s">
-        <v>877</v>
+        <v>876</v>
       </c>
       <c r="E421" s="1" t="s">
         <v>15</v>
@@ -13183,16 +13180,16 @@
     </row>
     <row r="422" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A422" s="1" t="s">
+        <v>883</v>
+      </c>
+      <c r="B422" s="1" t="s">
         <v>884</v>
       </c>
-      <c r="B422" s="1" t="s">
-        <v>885</v>
-      </c>
       <c r="C422" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D422" s="1" t="s">
-        <v>877</v>
+        <v>876</v>
       </c>
       <c r="E422" s="1" t="s">
         <v>18</v>
@@ -13203,16 +13200,16 @@
     </row>
     <row r="423" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A423" s="1" t="s">
+        <v>885</v>
+      </c>
+      <c r="B423" s="1" t="s">
         <v>886</v>
       </c>
-      <c r="B423" s="1" t="s">
-        <v>887</v>
-      </c>
       <c r="C423" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D423" s="1" t="s">
-        <v>877</v>
+        <v>876</v>
       </c>
       <c r="E423" s="1" t="s">
         <v>21</v>
@@ -13223,16 +13220,16 @@
     </row>
     <row r="424" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A424" s="1" t="s">
+        <v>887</v>
+      </c>
+      <c r="B424" s="1" t="s">
         <v>888</v>
       </c>
-      <c r="B424" s="1" t="s">
-        <v>889</v>
-      </c>
       <c r="C424" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D424" s="1" t="s">
-        <v>877</v>
+        <v>876</v>
       </c>
       <c r="E424" s="1" t="s">
         <v>24</v>
@@ -13243,16 +13240,16 @@
     </row>
     <row r="425" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A425" s="1" t="s">
+        <v>889</v>
+      </c>
+      <c r="B425" s="1" t="s">
         <v>890</v>
       </c>
-      <c r="B425" s="1" t="s">
-        <v>891</v>
-      </c>
       <c r="C425" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D425" s="1" t="s">
-        <v>877</v>
+        <v>876</v>
       </c>
       <c r="E425" s="1" t="s">
         <v>28</v>
@@ -13263,16 +13260,16 @@
     </row>
     <row r="426" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A426" s="1" t="s">
+        <v>891</v>
+      </c>
+      <c r="B426" s="1" t="s">
         <v>892</v>
       </c>
-      <c r="B426" s="1" t="s">
+      <c r="C426" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D426" s="1" t="s">
         <v>893</v>
-      </c>
-      <c r="C426" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D426" s="1" t="s">
-        <v>894</v>
       </c>
       <c r="E426" s="1" t="s">
         <v>4</v>
@@ -13283,16 +13280,16 @@
     </row>
     <row r="427" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A427" s="1" t="s">
+        <v>894</v>
+      </c>
+      <c r="B427" s="1" t="s">
         <v>895</v>
       </c>
-      <c r="B427" s="1" t="s">
-        <v>896</v>
-      </c>
       <c r="C427" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D427" s="1" t="s">
-        <v>894</v>
+        <v>893</v>
       </c>
       <c r="E427" s="1" t="s">
         <v>8</v>
@@ -13303,16 +13300,16 @@
     </row>
     <row r="428" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A428" s="1" t="s">
+        <v>896</v>
+      </c>
+      <c r="B428" s="1" t="s">
         <v>897</v>
       </c>
-      <c r="B428" s="1" t="s">
-        <v>898</v>
-      </c>
       <c r="C428" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D428" s="1" t="s">
-        <v>894</v>
+        <v>893</v>
       </c>
       <c r="E428" s="1" t="s">
         <v>12</v>
@@ -13323,36 +13320,36 @@
     </row>
     <row r="429" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A429" s="1" t="s">
+        <v>898</v>
+      </c>
+      <c r="B429" s="1" t="s">
         <v>899</v>
       </c>
-      <c r="B429" s="1" t="s">
-        <v>900</v>
-      </c>
       <c r="C429" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D429" s="1" t="s">
-        <v>894</v>
+        <v>893</v>
       </c>
       <c r="E429" s="1" t="s">
         <v>15</v>
       </c>
       <c r="F429" s="1" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
     </row>
     <row r="430" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A430" s="1" t="s">
+        <v>901</v>
+      </c>
+      <c r="B430" s="1" t="s">
         <v>902</v>
       </c>
-      <c r="B430" s="1" t="s">
-        <v>903</v>
-      </c>
       <c r="C430" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D430" s="1" t="s">
-        <v>894</v>
+        <v>893</v>
       </c>
       <c r="E430" s="1" t="s">
         <v>18</v>
@@ -13363,16 +13360,16 @@
     </row>
     <row r="431" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A431" s="1" t="s">
+        <v>903</v>
+      </c>
+      <c r="B431" s="1" t="s">
         <v>904</v>
       </c>
-      <c r="B431" s="1" t="s">
-        <v>905</v>
-      </c>
       <c r="C431" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D431" s="1" t="s">
-        <v>894</v>
+        <v>893</v>
       </c>
       <c r="E431" s="1" t="s">
         <v>21</v>
@@ -13383,16 +13380,16 @@
     </row>
     <row r="432" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A432" s="1" t="s">
+        <v>905</v>
+      </c>
+      <c r="B432" s="1" t="s">
         <v>906</v>
       </c>
-      <c r="B432" s="1" t="s">
-        <v>907</v>
-      </c>
       <c r="C432" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D432" s="1" t="s">
-        <v>894</v>
+        <v>893</v>
       </c>
       <c r="E432" s="1" t="s">
         <v>24</v>
@@ -13403,16 +13400,16 @@
     </row>
     <row r="433" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A433" s="1" t="s">
+        <v>907</v>
+      </c>
+      <c r="B433" s="1" t="s">
         <v>908</v>
       </c>
-      <c r="B433" s="1" t="s">
-        <v>909</v>
-      </c>
       <c r="C433" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D433" s="1" t="s">
-        <v>894</v>
+        <v>893</v>
       </c>
       <c r="E433" s="1" t="s">
         <v>28</v>
@@ -13423,16 +13420,16 @@
     </row>
     <row r="434" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A434" s="1" t="s">
+        <v>909</v>
+      </c>
+      <c r="B434" s="1" t="s">
         <v>910</v>
       </c>
-      <c r="B434" s="1" t="s">
-        <v>911</v>
-      </c>
       <c r="C434" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D434" s="1" t="s">
-        <v>894</v>
+        <v>893</v>
       </c>
       <c r="E434" s="1" t="s">
         <v>31</v>
@@ -13443,16 +13440,16 @@
     </row>
     <row r="435" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A435" s="1" t="s">
+        <v>911</v>
+      </c>
+      <c r="B435" s="1" t="s">
         <v>912</v>
       </c>
-      <c r="B435" s="1" t="s">
-        <v>913</v>
-      </c>
       <c r="C435" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D435" s="1" t="s">
-        <v>894</v>
+        <v>893</v>
       </c>
       <c r="E435" s="1" t="s">
         <v>34</v>
@@ -13463,16 +13460,16 @@
     </row>
     <row r="436" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A436" s="1" t="s">
+        <v>913</v>
+      </c>
+      <c r="B436" s="1" t="s">
         <v>914</v>
       </c>
-      <c r="B436" s="1" t="s">
-        <v>915</v>
-      </c>
       <c r="C436" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D436" s="1" t="s">
-        <v>894</v>
+        <v>893</v>
       </c>
       <c r="E436" s="1" t="s">
         <v>37</v>
@@ -13483,16 +13480,16 @@
     </row>
     <row r="437" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A437" s="1" t="s">
+        <v>915</v>
+      </c>
+      <c r="B437" s="1" t="s">
         <v>916</v>
       </c>
-      <c r="B437" s="1" t="s">
-        <v>917</v>
-      </c>
       <c r="C437" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D437" s="1" t="s">
-        <v>894</v>
+        <v>893</v>
       </c>
       <c r="E437" s="1" t="s">
         <v>40</v>
@@ -13503,16 +13500,16 @@
     </row>
     <row r="438" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A438" s="1" t="s">
+        <v>917</v>
+      </c>
+      <c r="B438" s="1" t="s">
         <v>918</v>
       </c>
-      <c r="B438" s="1" t="s">
-        <v>919</v>
-      </c>
       <c r="C438" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D438" s="1" t="s">
-        <v>894</v>
+        <v>893</v>
       </c>
       <c r="E438" s="1" t="s">
         <v>68</v>
@@ -13523,16 +13520,16 @@
     </row>
     <row r="439" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A439" s="1" t="s">
+        <v>919</v>
+      </c>
+      <c r="B439" s="1" t="s">
         <v>920</v>
       </c>
-      <c r="B439" s="1" t="s">
-        <v>921</v>
-      </c>
       <c r="C439" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D439" s="1" t="s">
-        <v>894</v>
+        <v>893</v>
       </c>
       <c r="E439" s="1" t="s">
         <v>100</v>
@@ -13543,16 +13540,16 @@
     </row>
     <row r="440" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A440" s="1" t="s">
+        <v>921</v>
+      </c>
+      <c r="B440" s="1" t="s">
         <v>922</v>
       </c>
-      <c r="B440" s="1" t="s">
-        <v>923</v>
-      </c>
       <c r="C440" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D440" s="1" t="s">
-        <v>894</v>
+        <v>893</v>
       </c>
       <c r="E440" s="1" t="s">
         <v>103</v>
@@ -13563,16 +13560,16 @@
     </row>
     <row r="441" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A441" s="1" t="s">
+        <v>923</v>
+      </c>
+      <c r="B441" s="1" t="s">
         <v>924</v>
       </c>
-      <c r="B441" s="1" t="s">
-        <v>925</v>
-      </c>
       <c r="C441" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D441" s="1" t="s">
-        <v>894</v>
+        <v>893</v>
       </c>
       <c r="E441" s="1" t="s">
         <v>106</v>
@@ -13583,16 +13580,16 @@
     </row>
     <row r="442" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A442" s="1" t="s">
+        <v>925</v>
+      </c>
+      <c r="B442" s="1" t="s">
         <v>926</v>
       </c>
-      <c r="B442" s="1" t="s">
+      <c r="C442" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D442" s="1" t="s">
         <v>927</v>
-      </c>
-      <c r="C442" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D442" s="1" t="s">
-        <v>928</v>
       </c>
       <c r="E442" s="1" t="s">
         <v>4</v>
@@ -13603,16 +13600,16 @@
     </row>
     <row r="443" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A443" s="1" t="s">
+        <v>928</v>
+      </c>
+      <c r="B443" s="1" t="s">
         <v>929</v>
       </c>
-      <c r="B443" s="1" t="s">
-        <v>930</v>
-      </c>
       <c r="C443" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D443" s="1" t="s">
-        <v>928</v>
+        <v>927</v>
       </c>
       <c r="E443" s="1" t="s">
         <v>8</v>
@@ -13623,16 +13620,16 @@
     </row>
     <row r="444" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A444" s="1" t="s">
+        <v>930</v>
+      </c>
+      <c r="B444" s="1" t="s">
         <v>931</v>
       </c>
-      <c r="B444" s="1" t="s">
-        <v>932</v>
-      </c>
       <c r="C444" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D444" s="1" t="s">
-        <v>928</v>
+        <v>927</v>
       </c>
       <c r="E444" s="1" t="s">
         <v>12</v>
@@ -13643,16 +13640,16 @@
     </row>
     <row r="445" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A445" s="1" t="s">
+        <v>932</v>
+      </c>
+      <c r="B445" s="1" t="s">
         <v>933</v>
       </c>
-      <c r="B445" s="1" t="s">
-        <v>934</v>
-      </c>
       <c r="C445" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D445" s="1" t="s">
-        <v>928</v>
+        <v>927</v>
       </c>
       <c r="E445" s="1" t="s">
         <v>15</v>
@@ -13663,16 +13660,16 @@
     </row>
     <row r="446" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A446" s="1" t="s">
+        <v>934</v>
+      </c>
+      <c r="B446" s="1" t="s">
         <v>935</v>
       </c>
-      <c r="B446" s="1" t="s">
-        <v>936</v>
-      </c>
       <c r="C446" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D446" s="1" t="s">
-        <v>928</v>
+        <v>927</v>
       </c>
       <c r="E446" s="1" t="s">
         <v>18</v>
@@ -13683,16 +13680,16 @@
     </row>
     <row r="447" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A447" s="1" t="s">
+        <v>936</v>
+      </c>
+      <c r="B447" s="1" t="s">
         <v>937</v>
       </c>
-      <c r="B447" s="1" t="s">
-        <v>938</v>
-      </c>
       <c r="C447" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D447" s="1" t="s">
-        <v>928</v>
+        <v>927</v>
       </c>
       <c r="E447" s="1" t="s">
         <v>21</v>
@@ -13703,16 +13700,16 @@
     </row>
     <row r="448" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A448" s="1" t="s">
+        <v>938</v>
+      </c>
+      <c r="B448" s="1" t="s">
         <v>939</v>
       </c>
-      <c r="B448" s="1" t="s">
-        <v>940</v>
-      </c>
       <c r="C448" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D448" s="1" t="s">
-        <v>928</v>
+        <v>927</v>
       </c>
       <c r="E448" s="1" t="s">
         <v>24</v>
@@ -13723,16 +13720,16 @@
     </row>
     <row r="449" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A449" s="1" t="s">
+        <v>940</v>
+      </c>
+      <c r="B449" s="1" t="s">
         <v>941</v>
       </c>
-      <c r="B449" s="1" t="s">
-        <v>942</v>
-      </c>
       <c r="C449" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D449" s="1" t="s">
-        <v>928</v>
+        <v>927</v>
       </c>
       <c r="E449" s="1" t="s">
         <v>28</v>
@@ -13743,16 +13740,16 @@
     </row>
     <row r="450" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A450" s="1" t="s">
+        <v>942</v>
+      </c>
+      <c r="B450" s="1" t="s">
         <v>943</v>
       </c>
-      <c r="B450" s="1" t="s">
-        <v>944</v>
-      </c>
       <c r="C450" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D450" s="1" t="s">
-        <v>928</v>
+        <v>927</v>
       </c>
       <c r="E450" s="1" t="s">
         <v>31</v>
@@ -13763,16 +13760,16 @@
     </row>
     <row r="451" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A451" s="1" t="s">
+        <v>944</v>
+      </c>
+      <c r="B451" s="1" t="s">
         <v>945</v>
       </c>
-      <c r="B451" s="1" t="s">
-        <v>946</v>
-      </c>
       <c r="C451" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D451" s="1" t="s">
-        <v>928</v>
+        <v>927</v>
       </c>
       <c r="E451" s="1" t="s">
         <v>34</v>
@@ -13783,16 +13780,16 @@
     </row>
     <row r="452" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A452" s="1" t="s">
+        <v>946</v>
+      </c>
+      <c r="B452" s="1" t="s">
         <v>947</v>
       </c>
-      <c r="B452" s="1" t="s">
-        <v>948</v>
-      </c>
       <c r="C452" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D452" s="1" t="s">
-        <v>928</v>
+        <v>927</v>
       </c>
       <c r="E452" s="1" t="s">
         <v>37</v>
@@ -13803,16 +13800,16 @@
     </row>
     <row r="453" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A453" s="1" t="s">
+        <v>948</v>
+      </c>
+      <c r="B453" s="1" t="s">
         <v>949</v>
       </c>
-      <c r="B453" s="1" t="s">
-        <v>950</v>
-      </c>
       <c r="C453" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D453" s="1" t="s">
-        <v>928</v>
+        <v>927</v>
       </c>
       <c r="E453" s="1" t="s">
         <v>40</v>
@@ -13823,16 +13820,16 @@
     </row>
     <row r="454" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A454" s="1" t="s">
+        <v>950</v>
+      </c>
+      <c r="B454" s="1" t="s">
         <v>951</v>
       </c>
-      <c r="B454" s="1" t="s">
-        <v>952</v>
-      </c>
       <c r="C454" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D454" s="1" t="s">
-        <v>928</v>
+        <v>927</v>
       </c>
       <c r="E454" s="1" t="s">
         <v>68</v>
@@ -13843,16 +13840,16 @@
     </row>
     <row r="455" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A455" s="1" t="s">
+        <v>952</v>
+      </c>
+      <c r="B455" s="1" t="s">
         <v>953</v>
       </c>
-      <c r="B455" s="1" t="s">
-        <v>954</v>
-      </c>
       <c r="C455" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D455" s="1" t="s">
-        <v>928</v>
+        <v>927</v>
       </c>
       <c r="E455" s="1" t="s">
         <v>100</v>
@@ -13863,16 +13860,16 @@
     </row>
     <row r="456" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A456" s="1" t="s">
+        <v>954</v>
+      </c>
+      <c r="B456" s="1" t="s">
         <v>955</v>
       </c>
-      <c r="B456" s="1" t="s">
-        <v>956</v>
-      </c>
       <c r="C456" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D456" s="1" t="s">
-        <v>928</v>
+        <v>927</v>
       </c>
       <c r="E456" s="1" t="s">
         <v>103</v>
@@ -13883,16 +13880,16 @@
     </row>
     <row r="457" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A457" s="1" t="s">
+        <v>956</v>
+      </c>
+      <c r="B457" s="1" t="s">
         <v>957</v>
       </c>
-      <c r="B457" s="1" t="s">
+      <c r="C457" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D457" s="1" t="s">
         <v>958</v>
-      </c>
-      <c r="C457" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D457" s="1" t="s">
-        <v>959</v>
       </c>
       <c r="E457" s="1" t="s">
         <v>4</v>
@@ -13903,16 +13900,16 @@
     </row>
     <row r="458" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A458" s="1" t="s">
+        <v>959</v>
+      </c>
+      <c r="B458" s="1" t="s">
         <v>960</v>
       </c>
-      <c r="B458" s="1" t="s">
-        <v>961</v>
-      </c>
       <c r="C458" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D458" s="1" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
       <c r="E458" s="1" t="s">
         <v>8</v>
@@ -13923,16 +13920,16 @@
     </row>
     <row r="459" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A459" s="1" t="s">
+        <v>961</v>
+      </c>
+      <c r="B459" s="1" t="s">
         <v>962</v>
       </c>
-      <c r="B459" s="1" t="s">
-        <v>963</v>
-      </c>
       <c r="C459" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D459" s="1" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
       <c r="E459" s="1" t="s">
         <v>12</v>
@@ -13943,16 +13940,16 @@
     </row>
     <row r="460" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A460" s="1" t="s">
+        <v>963</v>
+      </c>
+      <c r="B460" s="1" t="s">
         <v>964</v>
       </c>
-      <c r="B460" s="1" t="s">
-        <v>965</v>
-      </c>
       <c r="C460" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D460" s="1" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
       <c r="E460" s="1" t="s">
         <v>15</v>
@@ -13963,16 +13960,16 @@
     </row>
     <row r="461" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A461" s="1" t="s">
+        <v>965</v>
+      </c>
+      <c r="B461" s="1" t="s">
         <v>966</v>
       </c>
-      <c r="B461" s="1" t="s">
-        <v>967</v>
-      </c>
       <c r="C461" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D461" s="1" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
       <c r="E461" s="1" t="s">
         <v>18</v>
@@ -13983,16 +13980,16 @@
     </row>
     <row r="462" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A462" s="1" t="s">
+        <v>967</v>
+      </c>
+      <c r="B462" s="1" t="s">
         <v>968</v>
       </c>
-      <c r="B462" s="1" t="s">
-        <v>969</v>
-      </c>
       <c r="C462" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D462" s="1" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
       <c r="E462" s="1" t="s">
         <v>21</v>
@@ -14003,16 +14000,16 @@
     </row>
     <row r="463" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A463" s="1" t="s">
+        <v>969</v>
+      </c>
+      <c r="B463" s="1" t="s">
         <v>970</v>
       </c>
-      <c r="B463" s="1" t="s">
-        <v>971</v>
-      </c>
       <c r="C463" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D463" s="1" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
       <c r="E463" s="1" t="s">
         <v>24</v>
@@ -14023,16 +14020,16 @@
     </row>
     <row r="464" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A464" s="1" t="s">
+        <v>971</v>
+      </c>
+      <c r="B464" s="1" t="s">
         <v>972</v>
       </c>
-      <c r="B464" s="1" t="s">
-        <v>973</v>
-      </c>
       <c r="C464" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D464" s="1" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
       <c r="E464" s="1" t="s">
         <v>28</v>
@@ -14043,16 +14040,16 @@
     </row>
     <row r="465" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A465" s="1" t="s">
+        <v>973</v>
+      </c>
+      <c r="B465" s="1" t="s">
         <v>974</v>
       </c>
-      <c r="B465" s="1" t="s">
-        <v>975</v>
-      </c>
       <c r="C465" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D465" s="1" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
       <c r="E465" s="1" t="s">
         <v>31</v>
@@ -14063,16 +14060,16 @@
     </row>
     <row r="466" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A466" s="1" t="s">
+        <v>975</v>
+      </c>
+      <c r="B466" s="1" t="s">
         <v>976</v>
       </c>
-      <c r="B466" s="1" t="s">
-        <v>977</v>
-      </c>
       <c r="C466" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D466" s="1" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
       <c r="E466" s="1" t="s">
         <v>34</v>
@@ -14083,16 +14080,16 @@
     </row>
     <row r="467" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A467" s="1" t="s">
+        <v>977</v>
+      </c>
+      <c r="B467" s="1" t="s">
         <v>978</v>
       </c>
-      <c r="B467" s="1" t="s">
-        <v>979</v>
-      </c>
       <c r="C467" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D467" s="1" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
       <c r="E467" s="1" t="s">
         <v>37</v>
@@ -14103,16 +14100,16 @@
     </row>
     <row r="468" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A468" s="1" t="s">
+        <v>979</v>
+      </c>
+      <c r="B468" s="1" t="s">
         <v>980</v>
       </c>
-      <c r="B468" s="1" t="s">
-        <v>981</v>
-      </c>
       <c r="C468" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D468" s="1" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
       <c r="E468" s="1" t="s">
         <v>40</v>
@@ -14123,16 +14120,16 @@
     </row>
     <row r="469" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A469" s="1" t="s">
+        <v>981</v>
+      </c>
+      <c r="B469" s="1" t="s">
         <v>982</v>
       </c>
-      <c r="B469" s="1" t="s">
-        <v>983</v>
-      </c>
       <c r="C469" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D469" s="1" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
       <c r="E469" s="1" t="s">
         <v>68</v>
@@ -14143,16 +14140,16 @@
     </row>
     <row r="470" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A470" s="1" t="s">
+        <v>983</v>
+      </c>
+      <c r="B470" s="1" t="s">
         <v>984</v>
       </c>
-      <c r="B470" s="1" t="s">
-        <v>985</v>
-      </c>
       <c r="C470" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D470" s="1" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
       <c r="E470" s="1" t="s">
         <v>100</v>
@@ -14163,16 +14160,16 @@
     </row>
     <row r="471" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A471" s="1" t="s">
+        <v>985</v>
+      </c>
+      <c r="B471" s="1" t="s">
         <v>986</v>
       </c>
-      <c r="B471" s="1" t="s">
-        <v>987</v>
-      </c>
       <c r="C471" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D471" s="1" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
       <c r="E471" s="1" t="s">
         <v>103</v>
@@ -14183,16 +14180,16 @@
     </row>
     <row r="472" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A472" s="1" t="s">
+        <v>987</v>
+      </c>
+      <c r="B472" s="1" t="s">
         <v>988</v>
       </c>
-      <c r="B472" s="1" t="s">
+      <c r="C472" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D472" s="1" t="s">
         <v>989</v>
-      </c>
-      <c r="C472" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D472" s="1" t="s">
-        <v>990</v>
       </c>
       <c r="E472" s="1" t="s">
         <v>4</v>
@@ -14203,16 +14200,16 @@
     </row>
     <row r="473" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A473" s="1" t="s">
+        <v>990</v>
+      </c>
+      <c r="B473" s="1" t="s">
         <v>991</v>
       </c>
-      <c r="B473" s="1" t="s">
-        <v>992</v>
-      </c>
       <c r="C473" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D473" s="1" t="s">
-        <v>990</v>
+        <v>989</v>
       </c>
       <c r="E473" s="1" t="s">
         <v>8</v>
@@ -14223,56 +14220,56 @@
     </row>
     <row r="474" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A474" s="1" t="s">
+        <v>992</v>
+      </c>
+      <c r="B474" s="1" t="s">
         <v>993</v>
       </c>
-      <c r="B474" s="1" t="s">
-        <v>994</v>
-      </c>
       <c r="C474" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D474" s="1" t="s">
-        <v>990</v>
+        <v>989</v>
       </c>
       <c r="E474" s="1" t="s">
         <v>12</v>
       </c>
       <c r="F474" s="1" t="s">
-        <v>995</v>
+        <v>994</v>
       </c>
     </row>
     <row r="475" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A475" s="1" t="s">
+        <v>995</v>
+      </c>
+      <c r="B475" s="1" t="s">
         <v>996</v>
       </c>
-      <c r="B475" s="1" t="s">
-        <v>997</v>
-      </c>
       <c r="C475" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D475" s="1" t="s">
-        <v>990</v>
+        <v>989</v>
       </c>
       <c r="E475" s="1" t="s">
         <v>15</v>
       </c>
       <c r="F475" s="1" t="s">
-        <v>995</v>
+        <v>994</v>
       </c>
     </row>
     <row r="476" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A476" s="1" t="s">
+        <v>997</v>
+      </c>
+      <c r="B476" s="1" t="s">
         <v>998</v>
       </c>
-      <c r="B476" s="1" t="s">
-        <v>999</v>
-      </c>
       <c r="C476" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D476" s="1" t="s">
-        <v>990</v>
+        <v>989</v>
       </c>
       <c r="E476" s="1" t="s">
         <v>18</v>
@@ -14283,16 +14280,16 @@
     </row>
     <row r="477" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A477" s="1" t="s">
+        <v>999</v>
+      </c>
+      <c r="B477" s="1" t="s">
         <v>1000</v>
       </c>
-      <c r="B477" s="1" t="s">
-        <v>1001</v>
-      </c>
       <c r="C477" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D477" s="1" t="s">
-        <v>990</v>
+        <v>989</v>
       </c>
       <c r="E477" s="1" t="s">
         <v>21</v>
@@ -14303,16 +14300,16 @@
     </row>
     <row r="478" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A478" s="1" t="s">
+        <v>1001</v>
+      </c>
+      <c r="B478" s="1" t="s">
         <v>1002</v>
       </c>
-      <c r="B478" s="1" t="s">
-        <v>1003</v>
-      </c>
       <c r="C478" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D478" s="1" t="s">
-        <v>990</v>
+        <v>989</v>
       </c>
       <c r="E478" s="1" t="s">
         <v>24</v>
@@ -14323,16 +14320,16 @@
     </row>
     <row r="479" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A479" s="1" t="s">
+        <v>1003</v>
+      </c>
+      <c r="B479" s="1" t="s">
         <v>1004</v>
       </c>
-      <c r="B479" s="1" t="s">
-        <v>1005</v>
-      </c>
       <c r="C479" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D479" s="1" t="s">
-        <v>990</v>
+        <v>989</v>
       </c>
       <c r="E479" s="1" t="s">
         <v>28</v>
@@ -14343,16 +14340,16 @@
     </row>
     <row r="480" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A480" s="1" t="s">
+        <v>1005</v>
+      </c>
+      <c r="B480" s="1" t="s">
         <v>1006</v>
       </c>
-      <c r="B480" s="1" t="s">
-        <v>1007</v>
-      </c>
       <c r="C480" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D480" s="1" t="s">
-        <v>990</v>
+        <v>989</v>
       </c>
       <c r="E480" s="1" t="s">
         <v>31</v>
@@ -14363,16 +14360,16 @@
     </row>
     <row r="481" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A481" s="1" t="s">
+        <v>1007</v>
+      </c>
+      <c r="B481" s="1" t="s">
         <v>1008</v>
       </c>
-      <c r="B481" s="1" t="s">
-        <v>1009</v>
-      </c>
       <c r="C481" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D481" s="1" t="s">
-        <v>990</v>
+        <v>989</v>
       </c>
       <c r="E481" s="1" t="s">
         <v>34</v>
@@ -14383,16 +14380,16 @@
     </row>
     <row r="482" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A482" s="1" t="s">
+        <v>1009</v>
+      </c>
+      <c r="B482" s="1" t="s">
         <v>1010</v>
       </c>
-      <c r="B482" s="1" t="s">
-        <v>1011</v>
-      </c>
       <c r="C482" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D482" s="1" t="s">
-        <v>990</v>
+        <v>989</v>
       </c>
       <c r="E482" s="1" t="s">
         <v>37</v>
@@ -14403,16 +14400,16 @@
     </row>
     <row r="483" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A483" s="1" t="s">
+        <v>1011</v>
+      </c>
+      <c r="B483" s="1" t="s">
         <v>1012</v>
       </c>
-      <c r="B483" s="1" t="s">
-        <v>1013</v>
-      </c>
       <c r="C483" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D483" s="1" t="s">
-        <v>990</v>
+        <v>989</v>
       </c>
       <c r="E483" s="1" t="s">
         <v>40</v>
@@ -14423,16 +14420,16 @@
     </row>
     <row r="484" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A484" s="1" t="s">
+        <v>1013</v>
+      </c>
+      <c r="B484" s="1" t="s">
         <v>1014</v>
       </c>
-      <c r="B484" s="1" t="s">
-        <v>1015</v>
-      </c>
       <c r="C484" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D484" s="1" t="s">
-        <v>990</v>
+        <v>989</v>
       </c>
       <c r="E484" s="1" t="s">
         <v>68</v>
@@ -14443,16 +14440,16 @@
     </row>
     <row r="485" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A485" s="1" t="s">
+        <v>1015</v>
+      </c>
+      <c r="B485" s="1" t="s">
         <v>1016</v>
       </c>
-      <c r="B485" s="1" t="s">
-        <v>1017</v>
-      </c>
       <c r="C485" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D485" s="1" t="s">
-        <v>990</v>
+        <v>989</v>
       </c>
       <c r="E485" s="1" t="s">
         <v>100</v>
@@ -14463,16 +14460,16 @@
     </row>
     <row r="486" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A486" s="1" t="s">
+        <v>1017</v>
+      </c>
+      <c r="B486" s="1" t="s">
         <v>1018</v>
       </c>
-      <c r="B486" s="1" t="s">
-        <v>1019</v>
-      </c>
       <c r="C486" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D486" s="1" t="s">
-        <v>990</v>
+        <v>989</v>
       </c>
       <c r="E486" s="1" t="s">
         <v>103</v>
@@ -14483,16 +14480,16 @@
     </row>
     <row r="487" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A487" s="1" t="s">
+        <v>1019</v>
+      </c>
+      <c r="B487" s="1" t="s">
         <v>1020</v>
       </c>
-      <c r="B487" s="1" t="s">
-        <v>1021</v>
-      </c>
       <c r="C487" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D487" s="1" t="s">
-        <v>990</v>
+        <v>989</v>
       </c>
       <c r="E487" s="1" t="s">
         <v>106</v>
@@ -14503,16 +14500,16 @@
     </row>
     <row r="488" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A488" s="1" t="s">
+        <v>1021</v>
+      </c>
+      <c r="B488" s="1" t="s">
         <v>1022</v>
       </c>
-      <c r="B488" s="1" t="s">
+      <c r="C488" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D488" s="1" t="s">
         <v>1023</v>
-      </c>
-      <c r="C488" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D488" s="1" t="s">
-        <v>1024</v>
       </c>
       <c r="E488" s="1" t="s">
         <v>4</v>
@@ -14523,16 +14520,16 @@
     </row>
     <row r="489" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A489" s="1" t="s">
+        <v>1024</v>
+      </c>
+      <c r="B489" s="1" t="s">
         <v>1025</v>
       </c>
-      <c r="B489" s="1" t="s">
-        <v>1026</v>
-      </c>
       <c r="C489" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D489" s="1" t="s">
-        <v>1024</v>
+        <v>1023</v>
       </c>
       <c r="E489" s="1" t="s">
         <v>8</v>
@@ -14543,16 +14540,16 @@
     </row>
     <row r="490" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A490" s="1" t="s">
+        <v>1026</v>
+      </c>
+      <c r="B490" s="1" t="s">
         <v>1027</v>
       </c>
-      <c r="B490" s="1" t="s">
-        <v>1028</v>
-      </c>
       <c r="C490" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D490" s="1" t="s">
-        <v>1024</v>
+        <v>1023</v>
       </c>
       <c r="E490" s="1" t="s">
         <v>12</v>
@@ -14563,16 +14560,16 @@
     </row>
     <row r="491" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A491" s="1" t="s">
+        <v>1028</v>
+      </c>
+      <c r="B491" s="1" t="s">
         <v>1029</v>
       </c>
-      <c r="B491" s="1" t="s">
-        <v>1030</v>
-      </c>
       <c r="C491" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D491" s="1" t="s">
-        <v>1024</v>
+        <v>1023</v>
       </c>
       <c r="E491" s="1" t="s">
         <v>15</v>
@@ -14583,16 +14580,16 @@
     </row>
     <row r="492" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A492" s="1" t="s">
+        <v>1030</v>
+      </c>
+      <c r="B492" s="1" t="s">
         <v>1031</v>
       </c>
-      <c r="B492" s="1" t="s">
-        <v>1032</v>
-      </c>
       <c r="C492" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D492" s="1" t="s">
-        <v>1024</v>
+        <v>1023</v>
       </c>
       <c r="E492" s="1" t="s">
         <v>18</v>
@@ -14603,16 +14600,16 @@
     </row>
     <row r="493" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A493" s="1" t="s">
+        <v>1032</v>
+      </c>
+      <c r="B493" s="1" t="s">
         <v>1033</v>
       </c>
-      <c r="B493" s="1" t="s">
-        <v>1034</v>
-      </c>
       <c r="C493" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D493" s="1" t="s">
-        <v>1024</v>
+        <v>1023</v>
       </c>
       <c r="E493" s="1" t="s">
         <v>21</v>
@@ -14623,16 +14620,16 @@
     </row>
     <row r="494" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A494" s="1" t="s">
+        <v>1034</v>
+      </c>
+      <c r="B494" s="1" t="s">
         <v>1035</v>
       </c>
-      <c r="B494" s="1" t="s">
-        <v>1036</v>
-      </c>
       <c r="C494" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D494" s="1" t="s">
-        <v>1024</v>
+        <v>1023</v>
       </c>
       <c r="E494" s="1" t="s">
         <v>24</v>
@@ -14643,16 +14640,16 @@
     </row>
     <row r="495" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A495" s="1" t="s">
+        <v>1036</v>
+      </c>
+      <c r="B495" s="1" t="s">
         <v>1037</v>
       </c>
-      <c r="B495" s="1" t="s">
-        <v>1038</v>
-      </c>
       <c r="C495" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D495" s="1" t="s">
-        <v>1024</v>
+        <v>1023</v>
       </c>
       <c r="E495" s="1" t="s">
         <v>28</v>
@@ -14663,16 +14660,16 @@
     </row>
     <row r="496" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A496" s="1" t="s">
+        <v>1038</v>
+      </c>
+      <c r="B496" s="1" t="s">
         <v>1039</v>
       </c>
-      <c r="B496" s="1" t="s">
-        <v>1040</v>
-      </c>
       <c r="C496" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D496" s="1" t="s">
-        <v>1024</v>
+        <v>1023</v>
       </c>
       <c r="E496" s="1" t="s">
         <v>31</v>
@@ -14683,36 +14680,36 @@
     </row>
     <row r="497" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A497" s="1" t="s">
+        <v>1040</v>
+      </c>
+      <c r="B497" s="1" t="s">
         <v>1041</v>
       </c>
-      <c r="B497" s="1" t="s">
-        <v>1042</v>
-      </c>
       <c r="C497" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D497" s="1" t="s">
-        <v>1024</v>
+        <v>1023</v>
       </c>
       <c r="E497" s="1" t="s">
         <v>34</v>
       </c>
       <c r="F497" s="1" t="s">
-        <v>1043</v>
+        <v>1042</v>
       </c>
     </row>
     <row r="498" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A498" s="1" t="s">
+        <v>1043</v>
+      </c>
+      <c r="B498" s="1" t="s">
         <v>1044</v>
       </c>
-      <c r="B498" s="1" t="s">
-        <v>1045</v>
-      </c>
       <c r="C498" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D498" s="1" t="s">
-        <v>1024</v>
+        <v>1023</v>
       </c>
       <c r="E498" s="1" t="s">
         <v>37</v>
@@ -14723,16 +14720,16 @@
     </row>
     <row r="499" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A499" s="1" t="s">
+        <v>1045</v>
+      </c>
+      <c r="B499" s="1" t="s">
         <v>1046</v>
       </c>
-      <c r="B499" s="1" t="s">
-        <v>1047</v>
-      </c>
       <c r="C499" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D499" s="1" t="s">
-        <v>1024</v>
+        <v>1023</v>
       </c>
       <c r="E499" s="1" t="s">
         <v>40</v>
@@ -14743,16 +14740,16 @@
     </row>
     <row r="500" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A500" s="1" t="s">
+        <v>1047</v>
+      </c>
+      <c r="B500" s="1" t="s">
         <v>1048</v>
       </c>
-      <c r="B500" s="1" t="s">
-        <v>1049</v>
-      </c>
       <c r="C500" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D500" s="1" t="s">
-        <v>1024</v>
+        <v>1023</v>
       </c>
       <c r="E500" s="1" t="s">
         <v>68</v>
@@ -14763,16 +14760,16 @@
     </row>
     <row r="501" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A501" s="1" t="s">
+        <v>1049</v>
+      </c>
+      <c r="B501" s="1" t="s">
         <v>1050</v>
       </c>
-      <c r="B501" s="1" t="s">
-        <v>1051</v>
-      </c>
       <c r="C501" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D501" s="1" t="s">
-        <v>1024</v>
+        <v>1023</v>
       </c>
       <c r="E501" s="1" t="s">
         <v>100</v>
@@ -14783,16 +14780,16 @@
     </row>
     <row r="502" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A502" s="1" t="s">
+        <v>1051</v>
+      </c>
+      <c r="B502" s="1" t="s">
         <v>1052</v>
       </c>
-      <c r="B502" s="1" t="s">
-        <v>1053</v>
-      </c>
       <c r="C502" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D502" s="1" t="s">
-        <v>1024</v>
+        <v>1023</v>
       </c>
       <c r="E502" s="1" t="s">
         <v>103</v>
@@ -14803,16 +14800,16 @@
     </row>
     <row r="503" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A503" s="1" t="s">
+        <v>1053</v>
+      </c>
+      <c r="B503" s="1" t="s">
         <v>1054</v>
       </c>
-      <c r="B503" s="1" t="s">
-        <v>1055</v>
-      </c>
       <c r="C503" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D503" s="1" t="s">
-        <v>1024</v>
+        <v>1023</v>
       </c>
       <c r="E503" s="1" t="s">
         <v>106</v>
@@ -14823,16 +14820,16 @@
     </row>
     <row r="504" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A504" s="1" t="s">
+        <v>1055</v>
+      </c>
+      <c r="B504" s="1" t="s">
         <v>1056</v>
       </c>
-      <c r="B504" s="1" t="s">
-        <v>1057</v>
-      </c>
       <c r="C504" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D504" s="1" t="s">
-        <v>1024</v>
+        <v>1023</v>
       </c>
       <c r="E504" s="1" t="s">
         <v>109</v>
@@ -14843,16 +14840,16 @@
     </row>
     <row r="505" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A505" s="1" t="s">
+        <v>1057</v>
+      </c>
+      <c r="B505" s="1" t="s">
         <v>1058</v>
       </c>
-      <c r="B505" s="1" t="s">
-        <v>1059</v>
-      </c>
       <c r="C505" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D505" s="1" t="s">
-        <v>1024</v>
+        <v>1023</v>
       </c>
       <c r="E505" s="1" t="s">
         <v>112</v>
@@ -14863,16 +14860,16 @@
     </row>
     <row r="506" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A506" s="1" t="s">
+        <v>1059</v>
+      </c>
+      <c r="B506" s="1" t="s">
         <v>1060</v>
       </c>
-      <c r="B506" s="1" t="s">
+      <c r="C506" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D506" s="1" t="s">
         <v>1061</v>
-      </c>
-      <c r="C506" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D506" s="1" t="s">
-        <v>1062</v>
       </c>
       <c r="E506" s="1" t="s">
         <v>4</v>
@@ -14883,16 +14880,16 @@
     </row>
     <row r="507" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A507" s="1" t="s">
+        <v>1062</v>
+      </c>
+      <c r="B507" s="1" t="s">
         <v>1063</v>
       </c>
-      <c r="B507" s="1" t="s">
-        <v>1064</v>
-      </c>
       <c r="C507" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D507" s="1" t="s">
-        <v>1062</v>
+        <v>1061</v>
       </c>
       <c r="E507" s="1" t="s">
         <v>8</v>
@@ -14903,16 +14900,16 @@
     </row>
     <row r="508" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A508" s="1" t="s">
+        <v>1064</v>
+      </c>
+      <c r="B508" s="1" t="s">
         <v>1065</v>
       </c>
-      <c r="B508" s="1" t="s">
-        <v>1066</v>
-      </c>
       <c r="C508" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D508" s="1" t="s">
-        <v>1062</v>
+        <v>1061</v>
       </c>
       <c r="E508" s="1" t="s">
         <v>12</v>
@@ -14923,16 +14920,16 @@
     </row>
     <row r="509" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A509" s="1" t="s">
+        <v>1066</v>
+      </c>
+      <c r="B509" s="1" t="s">
         <v>1067</v>
       </c>
-      <c r="B509" s="1" t="s">
-        <v>1068</v>
-      </c>
       <c r="C509" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D509" s="1" t="s">
-        <v>1062</v>
+        <v>1061</v>
       </c>
       <c r="E509" s="1" t="s">
         <v>15</v>
@@ -14943,16 +14940,16 @@
     </row>
     <row r="510" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A510" s="1" t="s">
+        <v>1068</v>
+      </c>
+      <c r="B510" s="1" t="s">
         <v>1069</v>
       </c>
-      <c r="B510" s="1" t="s">
-        <v>1070</v>
-      </c>
       <c r="C510" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D510" s="1" t="s">
-        <v>1062</v>
+        <v>1061</v>
       </c>
       <c r="E510" s="1" t="s">
         <v>18</v>
@@ -14963,16 +14960,16 @@
     </row>
     <row r="511" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A511" s="1" t="s">
+        <v>1070</v>
+      </c>
+      <c r="B511" s="1" t="s">
         <v>1071</v>
       </c>
-      <c r="B511" s="1" t="s">
-        <v>1072</v>
-      </c>
       <c r="C511" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D511" s="1" t="s">
-        <v>1062</v>
+        <v>1061</v>
       </c>
       <c r="E511" s="1" t="s">
         <v>21</v>
@@ -14983,16 +14980,16 @@
     </row>
     <row r="512" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A512" s="1" t="s">
+        <v>1072</v>
+      </c>
+      <c r="B512" s="1" t="s">
         <v>1073</v>
       </c>
-      <c r="B512" s="1" t="s">
-        <v>1074</v>
-      </c>
       <c r="C512" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D512" s="1" t="s">
-        <v>1062</v>
+        <v>1061</v>
       </c>
       <c r="E512" s="1" t="s">
         <v>24</v>
@@ -15003,16 +15000,16 @@
     </row>
     <row r="513" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A513" s="1" t="s">
+        <v>1074</v>
+      </c>
+      <c r="B513" s="1" t="s">
         <v>1075</v>
       </c>
-      <c r="B513" s="1" t="s">
-        <v>1076</v>
-      </c>
       <c r="C513" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D513" s="1" t="s">
-        <v>1062</v>
+        <v>1061</v>
       </c>
       <c r="E513" s="1" t="s">
         <v>28</v>
@@ -15023,16 +15020,16 @@
     </row>
     <row r="514" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A514" s="1" t="s">
+        <v>1076</v>
+      </c>
+      <c r="B514" s="1" t="s">
         <v>1077</v>
       </c>
-      <c r="B514" s="1" t="s">
-        <v>1078</v>
-      </c>
       <c r="C514" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D514" s="1" t="s">
-        <v>1062</v>
+        <v>1061</v>
       </c>
       <c r="E514" s="1" t="s">
         <v>31</v>
@@ -15043,16 +15040,16 @@
     </row>
     <row r="515" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A515" s="1" t="s">
+        <v>1078</v>
+      </c>
+      <c r="B515" s="1" t="s">
         <v>1079</v>
       </c>
-      <c r="B515" s="1" t="s">
-        <v>1080</v>
-      </c>
       <c r="C515" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D515" s="1" t="s">
-        <v>1062</v>
+        <v>1061</v>
       </c>
       <c r="E515" s="1" t="s">
         <v>34</v>
@@ -15063,16 +15060,16 @@
     </row>
     <row r="516" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A516" s="1" t="s">
+        <v>1080</v>
+      </c>
+      <c r="B516" s="1" t="s">
         <v>1081</v>
       </c>
-      <c r="B516" s="1" t="s">
-        <v>1082</v>
-      </c>
       <c r="C516" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D516" s="1" t="s">
-        <v>1062</v>
+        <v>1061</v>
       </c>
       <c r="E516" s="1" t="s">
         <v>37</v>
@@ -15083,16 +15080,16 @@
     </row>
     <row r="517" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A517" s="1" t="s">
+        <v>1082</v>
+      </c>
+      <c r="B517" s="1" t="s">
         <v>1083</v>
       </c>
-      <c r="B517" s="1" t="s">
-        <v>1084</v>
-      </c>
       <c r="C517" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D517" s="1" t="s">
-        <v>1062</v>
+        <v>1061</v>
       </c>
       <c r="E517" s="1" t="s">
         <v>40</v>
@@ -15103,16 +15100,16 @@
     </row>
     <row r="518" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A518" s="1" t="s">
+        <v>1084</v>
+      </c>
+      <c r="B518" s="1" t="s">
         <v>1085</v>
       </c>
-      <c r="B518" s="1" t="s">
-        <v>1086</v>
-      </c>
       <c r="C518" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D518" s="1" t="s">
-        <v>1062</v>
+        <v>1061</v>
       </c>
       <c r="E518" s="1" t="s">
         <v>68</v>
@@ -15123,16 +15120,16 @@
     </row>
     <row r="519" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A519" s="1" t="s">
+        <v>1086</v>
+      </c>
+      <c r="B519" s="1" t="s">
         <v>1087</v>
       </c>
-      <c r="B519" s="1" t="s">
-        <v>1088</v>
-      </c>
       <c r="C519" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D519" s="1" t="s">
-        <v>1062</v>
+        <v>1061</v>
       </c>
       <c r="E519" s="1" t="s">
         <v>100</v>
@@ -15143,16 +15140,16 @@
     </row>
     <row r="520" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A520" s="1" t="s">
+        <v>1088</v>
+      </c>
+      <c r="B520" s="1" t="s">
         <v>1089</v>
       </c>
-      <c r="B520" s="1" t="s">
-        <v>1090</v>
-      </c>
       <c r="C520" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D520" s="1" t="s">
-        <v>1062</v>
+        <v>1061</v>
       </c>
       <c r="E520" s="1" t="s">
         <v>103</v>
@@ -15163,16 +15160,16 @@
     </row>
     <row r="521" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A521" s="1" t="s">
+        <v>1090</v>
+      </c>
+      <c r="B521" s="1" t="s">
         <v>1091</v>
       </c>
-      <c r="B521" s="1" t="s">
+      <c r="C521" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D521" s="1" t="s">
         <v>1092</v>
-      </c>
-      <c r="C521" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D521" s="1" t="s">
-        <v>1093</v>
       </c>
       <c r="E521" s="1" t="s">
         <v>4</v>
@@ -15183,16 +15180,16 @@
     </row>
     <row r="522" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A522" s="1" t="s">
+        <v>1093</v>
+      </c>
+      <c r="B522" s="1" t="s">
         <v>1094</v>
       </c>
-      <c r="B522" s="1" t="s">
-        <v>1095</v>
-      </c>
       <c r="C522" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D522" s="1" t="s">
-        <v>1093</v>
+        <v>1092</v>
       </c>
       <c r="E522" s="1" t="s">
         <v>4</v>
@@ -15203,16 +15200,16 @@
     </row>
     <row r="523" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A523" s="1" t="s">
+        <v>1095</v>
+      </c>
+      <c r="B523" s="1" t="s">
         <v>1096</v>
       </c>
-      <c r="B523" s="1" t="s">
-        <v>1097</v>
-      </c>
       <c r="C523" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D523" s="1" t="s">
-        <v>1093</v>
+        <v>1092</v>
       </c>
       <c r="E523" s="1" t="s">
         <v>4</v>
@@ -15223,16 +15220,16 @@
     </row>
     <row r="524" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A524" s="1" t="s">
+        <v>1097</v>
+      </c>
+      <c r="B524" s="1" t="s">
         <v>1098</v>
       </c>
-      <c r="B524" s="1" t="s">
-        <v>1099</v>
-      </c>
       <c r="C524" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D524" s="1" t="s">
-        <v>1093</v>
+        <v>1092</v>
       </c>
       <c r="E524" s="1" t="s">
         <v>8</v>
@@ -15243,16 +15240,16 @@
     </row>
     <row r="525" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A525" s="1" t="s">
+        <v>1099</v>
+      </c>
+      <c r="B525" s="1" t="s">
         <v>1100</v>
       </c>
-      <c r="B525" s="1" t="s">
-        <v>1101</v>
-      </c>
       <c r="C525" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D525" s="1" t="s">
-        <v>1093</v>
+        <v>1092</v>
       </c>
       <c r="E525" s="1" t="s">
         <v>8</v>
@@ -15263,16 +15260,16 @@
     </row>
     <row r="526" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A526" s="1" t="s">
+        <v>1101</v>
+      </c>
+      <c r="B526" s="1" t="s">
         <v>1102</v>
       </c>
-      <c r="B526" s="1" t="s">
-        <v>1103</v>
-      </c>
       <c r="C526" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D526" s="1" t="s">
-        <v>1093</v>
+        <v>1092</v>
       </c>
       <c r="E526" s="1" t="s">
         <v>8</v>
@@ -15283,16 +15280,16 @@
     </row>
     <row r="527" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A527" s="1" t="s">
+        <v>1103</v>
+      </c>
+      <c r="B527" s="1" t="s">
         <v>1104</v>
       </c>
-      <c r="B527" s="1" t="s">
-        <v>1105</v>
-      </c>
       <c r="C527" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D527" s="1" t="s">
-        <v>1093</v>
+        <v>1092</v>
       </c>
       <c r="E527" s="1" t="s">
         <v>12</v>
@@ -15303,16 +15300,16 @@
     </row>
     <row r="528" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A528" s="1" t="s">
+        <v>1105</v>
+      </c>
+      <c r="B528" s="1" t="s">
         <v>1106</v>
       </c>
-      <c r="B528" s="1" t="s">
-        <v>1107</v>
-      </c>
       <c r="C528" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D528" s="1" t="s">
-        <v>1093</v>
+        <v>1092</v>
       </c>
       <c r="E528" s="1" t="s">
         <v>12</v>
@@ -15323,16 +15320,16 @@
     </row>
     <row r="529" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A529" s="1" t="s">
+        <v>1107</v>
+      </c>
+      <c r="B529" s="1" t="s">
         <v>1108</v>
       </c>
-      <c r="B529" s="1" t="s">
-        <v>1109</v>
-      </c>
       <c r="C529" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D529" s="1" t="s">
-        <v>1093</v>
+        <v>1092</v>
       </c>
       <c r="E529" s="1" t="s">
         <v>12</v>
@@ -15343,16 +15340,16 @@
     </row>
     <row r="530" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A530" s="1" t="s">
+        <v>1109</v>
+      </c>
+      <c r="B530" s="1" t="s">
         <v>1110</v>
       </c>
-      <c r="B530" s="1" t="s">
-        <v>1111</v>
-      </c>
       <c r="C530" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D530" s="1" t="s">
-        <v>1093</v>
+        <v>1092</v>
       </c>
       <c r="E530" s="1" t="s">
         <v>15</v>
@@ -15363,16 +15360,16 @@
     </row>
     <row r="531" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A531" s="1" t="s">
+        <v>1111</v>
+      </c>
+      <c r="B531" s="1" t="s">
         <v>1112</v>
       </c>
-      <c r="B531" s="1" t="s">
-        <v>1113</v>
-      </c>
       <c r="C531" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D531" s="1" t="s">
-        <v>1093</v>
+        <v>1092</v>
       </c>
       <c r="E531" s="1" t="s">
         <v>15</v>
@@ -15383,16 +15380,16 @@
     </row>
     <row r="532" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A532" s="1" t="s">
+        <v>1113</v>
+      </c>
+      <c r="B532" s="1" t="s">
         <v>1114</v>
       </c>
-      <c r="B532" s="1" t="s">
-        <v>1115</v>
-      </c>
       <c r="C532" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D532" s="1" t="s">
-        <v>1093</v>
+        <v>1092</v>
       </c>
       <c r="E532" s="1" t="s">
         <v>15</v>
@@ -15403,16 +15400,16 @@
     </row>
     <row r="533" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A533" s="1" t="s">
+        <v>1115</v>
+      </c>
+      <c r="B533" s="1" t="s">
         <v>1116</v>
       </c>
-      <c r="B533" s="1" t="s">
-        <v>1117</v>
-      </c>
       <c r="C533" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D533" s="1" t="s">
-        <v>1093</v>
+        <v>1092</v>
       </c>
       <c r="E533" s="1" t="s">
         <v>18</v>
@@ -15423,16 +15420,16 @@
     </row>
     <row r="534" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A534" s="1" t="s">
+        <v>1117</v>
+      </c>
+      <c r="B534" s="1" t="s">
         <v>1118</v>
       </c>
-      <c r="B534" s="1" t="s">
-        <v>1119</v>
-      </c>
       <c r="C534" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D534" s="1" t="s">
-        <v>1093</v>
+        <v>1092</v>
       </c>
       <c r="E534" s="1" t="s">
         <v>18</v>
@@ -15443,16 +15440,16 @@
     </row>
     <row r="535" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A535" s="1" t="s">
+        <v>1119</v>
+      </c>
+      <c r="B535" s="1" t="s">
         <v>1120</v>
       </c>
-      <c r="B535" s="1" t="s">
-        <v>1121</v>
-      </c>
       <c r="C535" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D535" s="1" t="s">
-        <v>1093</v>
+        <v>1092</v>
       </c>
       <c r="E535" s="1" t="s">
         <v>18</v>
@@ -15463,16 +15460,16 @@
     </row>
     <row r="536" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A536" s="1" t="s">
+        <v>1121</v>
+      </c>
+      <c r="B536" s="1" t="s">
         <v>1122</v>
       </c>
-      <c r="B536" s="1" t="s">
-        <v>1123</v>
-      </c>
       <c r="C536" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D536" s="1" t="s">
-        <v>1093</v>
+        <v>1092</v>
       </c>
       <c r="E536" s="1" t="s">
         <v>21</v>
@@ -15483,16 +15480,16 @@
     </row>
     <row r="537" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A537" s="1" t="s">
+        <v>1123</v>
+      </c>
+      <c r="B537" s="1" t="s">
         <v>1124</v>
       </c>
-      <c r="B537" s="1" t="s">
-        <v>1125</v>
-      </c>
       <c r="C537" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D537" s="1" t="s">
-        <v>1093</v>
+        <v>1092</v>
       </c>
       <c r="E537" s="1" t="s">
         <v>21</v>
@@ -15503,16 +15500,16 @@
     </row>
     <row r="538" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A538" s="1" t="s">
+        <v>1125</v>
+      </c>
+      <c r="B538" s="1" t="s">
         <v>1126</v>
       </c>
-      <c r="B538" s="1" t="s">
-        <v>1127</v>
-      </c>
       <c r="C538" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D538" s="1" t="s">
-        <v>1093</v>
+        <v>1092</v>
       </c>
       <c r="E538" s="1" t="s">
         <v>21</v>
@@ -15523,16 +15520,16 @@
     </row>
     <row r="539" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A539" s="1" t="s">
+        <v>1127</v>
+      </c>
+      <c r="B539" s="1" t="s">
         <v>1128</v>
       </c>
-      <c r="B539" s="1" t="s">
-        <v>1129</v>
-      </c>
       <c r="C539" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D539" s="1" t="s">
-        <v>1093</v>
+        <v>1092</v>
       </c>
       <c r="E539" s="1" t="s">
         <v>24</v>
@@ -15543,16 +15540,16 @@
     </row>
     <row r="540" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A540" s="1" t="s">
+        <v>1129</v>
+      </c>
+      <c r="B540" s="1" t="s">
         <v>1130</v>
       </c>
-      <c r="B540" s="1" t="s">
-        <v>1131</v>
-      </c>
       <c r="C540" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D540" s="1" t="s">
-        <v>1093</v>
+        <v>1092</v>
       </c>
       <c r="E540" s="1" t="s">
         <v>24</v>
@@ -15563,16 +15560,16 @@
     </row>
     <row r="541" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A541" s="1" t="s">
+        <v>1131</v>
+      </c>
+      <c r="B541" s="1" t="s">
         <v>1132</v>
       </c>
-      <c r="B541" s="1" t="s">
-        <v>1133</v>
-      </c>
       <c r="C541" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D541" s="1" t="s">
-        <v>1093</v>
+        <v>1092</v>
       </c>
       <c r="E541" s="1" t="s">
         <v>24</v>
@@ -15583,16 +15580,16 @@
     </row>
     <row r="542" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A542" s="1" t="s">
+        <v>1133</v>
+      </c>
+      <c r="B542" s="1" t="s">
         <v>1134</v>
       </c>
-      <c r="B542" s="1" t="s">
-        <v>1135</v>
-      </c>
       <c r="C542" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D542" s="1" t="s">
-        <v>1093</v>
+        <v>1092</v>
       </c>
       <c r="E542" s="1" t="s">
         <v>28</v>
@@ -15603,16 +15600,16 @@
     </row>
     <row r="543" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A543" s="1" t="s">
+        <v>1135</v>
+      </c>
+      <c r="B543" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B543" s="1" t="s">
-        <v>1137</v>
-      </c>
       <c r="C543" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D543" s="1" t="s">
-        <v>1093</v>
+        <v>1092</v>
       </c>
       <c r="E543" s="1" t="s">
         <v>28</v>
@@ -15623,16 +15620,16 @@
     </row>
     <row r="544" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A544" s="1" t="s">
+        <v>1137</v>
+      </c>
+      <c r="B544" s="1" t="s">
         <v>1138</v>
       </c>
-      <c r="B544" s="1" t="s">
-        <v>1139</v>
-      </c>
       <c r="C544" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D544" s="1" t="s">
-        <v>1093</v>
+        <v>1092</v>
       </c>
       <c r="E544" s="1" t="s">
         <v>28</v>
@@ -15643,16 +15640,16 @@
     </row>
     <row r="545" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A545" s="1" t="s">
+        <v>1139</v>
+      </c>
+      <c r="B545" s="1" t="s">
         <v>1140</v>
       </c>
-      <c r="B545" s="1" t="s">
-        <v>1141</v>
-      </c>
       <c r="C545" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D545" s="1" t="s">
-        <v>1093</v>
+        <v>1092</v>
       </c>
       <c r="E545" s="1" t="s">
         <v>31</v>
@@ -15663,16 +15660,16 @@
     </row>
     <row r="546" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A546" s="1" t="s">
+        <v>1141</v>
+      </c>
+      <c r="B546" s="1" t="s">
         <v>1142</v>
       </c>
-      <c r="B546" s="1" t="s">
-        <v>1143</v>
-      </c>
       <c r="C546" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D546" s="1" t="s">
-        <v>1093</v>
+        <v>1092</v>
       </c>
       <c r="E546" s="1" t="s">
         <v>31</v>
@@ -15683,16 +15680,16 @@
     </row>
     <row r="547" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A547" s="1" t="s">
+        <v>1143</v>
+      </c>
+      <c r="B547" s="1" t="s">
         <v>1144</v>
       </c>
-      <c r="B547" s="1" t="s">
-        <v>1145</v>
-      </c>
       <c r="C547" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D547" s="1" t="s">
-        <v>1093</v>
+        <v>1092</v>
       </c>
       <c r="E547" s="1" t="s">
         <v>31</v>
@@ -15703,16 +15700,16 @@
     </row>
     <row r="548" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A548" s="1" t="s">
+        <v>1145</v>
+      </c>
+      <c r="B548" s="1" t="s">
         <v>1146</v>
       </c>
-      <c r="B548" s="1" t="s">
-        <v>1147</v>
-      </c>
       <c r="C548" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D548" s="1" t="s">
-        <v>1093</v>
+        <v>1092</v>
       </c>
       <c r="E548" s="1" t="s">
         <v>34</v>
@@ -15723,16 +15720,16 @@
     </row>
     <row r="549" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A549" s="1" t="s">
+        <v>1147</v>
+      </c>
+      <c r="B549" s="1" t="s">
         <v>1148</v>
       </c>
-      <c r="B549" s="1" t="s">
-        <v>1149</v>
-      </c>
       <c r="C549" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D549" s="1" t="s">
-        <v>1093</v>
+        <v>1092</v>
       </c>
       <c r="E549" s="1" t="s">
         <v>34</v>
@@ -15743,16 +15740,16 @@
     </row>
     <row r="550" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A550" s="1" t="s">
+        <v>1149</v>
+      </c>
+      <c r="B550" s="1" t="s">
         <v>1150</v>
       </c>
-      <c r="B550" s="1" t="s">
-        <v>1151</v>
-      </c>
       <c r="C550" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D550" s="1" t="s">
-        <v>1093</v>
+        <v>1092</v>
       </c>
       <c r="E550" s="1" t="s">
         <v>34</v>
@@ -15763,16 +15760,16 @@
     </row>
     <row r="551" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A551" s="1" t="s">
+        <v>1151</v>
+      </c>
+      <c r="B551" s="1" t="s">
         <v>1152</v>
       </c>
-      <c r="B551" s="1" t="s">
-        <v>1153</v>
-      </c>
       <c r="C551" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D551" s="1" t="s">
-        <v>1093</v>
+        <v>1092</v>
       </c>
       <c r="E551" s="1" t="s">
         <v>37</v>
@@ -15783,16 +15780,16 @@
     </row>
     <row r="552" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A552" s="1" t="s">
+        <v>1153</v>
+      </c>
+      <c r="B552" s="1" t="s">
         <v>1154</v>
       </c>
-      <c r="B552" s="1" t="s">
-        <v>1155</v>
-      </c>
       <c r="C552" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D552" s="1" t="s">
-        <v>1093</v>
+        <v>1092</v>
       </c>
       <c r="E552" s="1" t="s">
         <v>37</v>
@@ -15803,16 +15800,16 @@
     </row>
     <row r="553" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A553" s="1" t="s">
+        <v>1155</v>
+      </c>
+      <c r="B553" s="1" t="s">
         <v>1156</v>
       </c>
-      <c r="B553" s="1" t="s">
-        <v>1157</v>
-      </c>
       <c r="C553" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D553" s="1" t="s">
-        <v>1093</v>
+        <v>1092</v>
       </c>
       <c r="E553" s="1" t="s">
         <v>40</v>
@@ -15823,16 +15820,16 @@
     </row>
     <row r="554" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A554" s="1" t="s">
+        <v>1157</v>
+      </c>
+      <c r="B554" s="1" t="s">
         <v>1158</v>
       </c>
-      <c r="B554" s="1" t="s">
-        <v>1159</v>
-      </c>
       <c r="C554" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D554" s="1" t="s">
-        <v>1093</v>
+        <v>1092</v>
       </c>
       <c r="E554" s="1" t="s">
         <v>40</v>
@@ -15843,16 +15840,16 @@
     </row>
     <row r="555" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A555" s="1" t="s">
+        <v>1159</v>
+      </c>
+      <c r="B555" s="1" t="s">
         <v>1160</v>
       </c>
-      <c r="B555" s="1" t="s">
-        <v>1161</v>
-      </c>
       <c r="C555" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D555" s="1" t="s">
-        <v>1093</v>
+        <v>1092</v>
       </c>
       <c r="E555" s="1" t="s">
         <v>68</v>
@@ -15863,16 +15860,16 @@
     </row>
     <row r="556" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A556" s="1" t="s">
+        <v>1161</v>
+      </c>
+      <c r="B556" s="1" t="s">
         <v>1162</v>
       </c>
-      <c r="B556" s="1" t="s">
-        <v>1163</v>
-      </c>
       <c r="C556" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D556" s="1" t="s">
-        <v>1093</v>
+        <v>1092</v>
       </c>
       <c r="E556" s="1" t="s">
         <v>100</v>
@@ -15883,16 +15880,16 @@
     </row>
     <row r="557" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A557" s="1" t="s">
+        <v>1163</v>
+      </c>
+      <c r="B557" s="1" t="s">
         <v>1164</v>
       </c>
-      <c r="B557" s="1" t="s">
-        <v>1165</v>
-      </c>
       <c r="C557" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D557" s="1" t="s">
-        <v>1093</v>
+        <v>1092</v>
       </c>
       <c r="E557" s="1" t="s">
         <v>103</v>
@@ -15903,16 +15900,16 @@
     </row>
     <row r="558" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A558" s="1" t="s">
+        <v>1165</v>
+      </c>
+      <c r="B558" s="1" t="s">
         <v>1166</v>
       </c>
-      <c r="B558" s="1" t="s">
+      <c r="C558" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D558" s="1" t="s">
         <v>1167</v>
-      </c>
-      <c r="C558" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D558" s="1" t="s">
-        <v>1168</v>
       </c>
       <c r="E558" s="1" t="s">
         <v>4</v>
@@ -15923,16 +15920,16 @@
     </row>
     <row r="559" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A559" s="1" t="s">
+        <v>1168</v>
+      </c>
+      <c r="B559" s="1" t="s">
         <v>1169</v>
       </c>
-      <c r="B559" s="1" t="s">
-        <v>1170</v>
-      </c>
       <c r="C559" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D559" s="1" t="s">
-        <v>1168</v>
+        <v>1167</v>
       </c>
       <c r="E559" s="1" t="s">
         <v>8</v>
@@ -15943,16 +15940,16 @@
     </row>
     <row r="560" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A560" s="1" t="s">
+        <v>1170</v>
+      </c>
+      <c r="B560" s="1" t="s">
         <v>1171</v>
       </c>
-      <c r="B560" s="1" t="s">
-        <v>1172</v>
-      </c>
       <c r="C560" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D560" s="1" t="s">
-        <v>1168</v>
+        <v>1167</v>
       </c>
       <c r="E560" s="1" t="s">
         <v>12</v>
@@ -15963,16 +15960,16 @@
     </row>
     <row r="561" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A561" s="1" t="s">
+        <v>1172</v>
+      </c>
+      <c r="B561" s="1" t="s">
         <v>1173</v>
       </c>
-      <c r="B561" s="1" t="s">
-        <v>1174</v>
-      </c>
       <c r="C561" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D561" s="1" t="s">
-        <v>1168</v>
+        <v>1167</v>
       </c>
       <c r="E561" s="1" t="s">
         <v>15</v>
@@ -15983,16 +15980,16 @@
     </row>
     <row r="562" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A562" s="1" t="s">
+        <v>1174</v>
+      </c>
+      <c r="B562" s="1" t="s">
         <v>1175</v>
       </c>
-      <c r="B562" s="1" t="s">
-        <v>1176</v>
-      </c>
       <c r="C562" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D562" s="1" t="s">
-        <v>1168</v>
+        <v>1167</v>
       </c>
       <c r="E562" s="1" t="s">
         <v>18</v>
@@ -16003,16 +16000,16 @@
     </row>
     <row r="563" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A563" s="1" t="s">
+        <v>1176</v>
+      </c>
+      <c r="B563" s="1" t="s">
         <v>1177</v>
       </c>
-      <c r="B563" s="1" t="s">
-        <v>1178</v>
-      </c>
       <c r="C563" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D563" s="1" t="s">
-        <v>1168</v>
+        <v>1167</v>
       </c>
       <c r="E563" s="1" t="s">
         <v>21</v>
@@ -16023,16 +16020,16 @@
     </row>
     <row r="564" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A564" s="1" t="s">
+        <v>1178</v>
+      </c>
+      <c r="B564" s="1" t="s">
         <v>1179</v>
       </c>
-      <c r="B564" s="1" t="s">
-        <v>1180</v>
-      </c>
       <c r="C564" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D564" s="1" t="s">
-        <v>1168</v>
+        <v>1167</v>
       </c>
       <c r="E564" s="1" t="s">
         <v>24</v>
@@ -16043,16 +16040,16 @@
     </row>
     <row r="565" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A565" s="1" t="s">
+        <v>1180</v>
+      </c>
+      <c r="B565" s="1" t="s">
         <v>1181</v>
       </c>
-      <c r="B565" s="1" t="s">
-        <v>1182</v>
-      </c>
       <c r="C565" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D565" s="1" t="s">
-        <v>1168</v>
+        <v>1167</v>
       </c>
       <c r="E565" s="1" t="s">
         <v>28</v>
@@ -16063,16 +16060,16 @@
     </row>
     <row r="566" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A566" s="1" t="s">
+        <v>1182</v>
+      </c>
+      <c r="B566" s="1" t="s">
         <v>1183</v>
       </c>
-      <c r="B566" s="1" t="s">
-        <v>1184</v>
-      </c>
       <c r="C566" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D566" s="1" t="s">
-        <v>1168</v>
+        <v>1167</v>
       </c>
       <c r="E566" s="1" t="s">
         <v>31</v>
@@ -16083,16 +16080,16 @@
     </row>
     <row r="567" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A567" s="1" t="s">
+        <v>1184</v>
+      </c>
+      <c r="B567" s="1" t="s">
         <v>1185</v>
       </c>
-      <c r="B567" s="1" t="s">
-        <v>1186</v>
-      </c>
       <c r="C567" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D567" s="1" t="s">
-        <v>1168</v>
+        <v>1167</v>
       </c>
       <c r="E567" s="1" t="s">
         <v>34</v>
@@ -16103,16 +16100,16 @@
     </row>
     <row r="568" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A568" s="1" t="s">
+        <v>1186</v>
+      </c>
+      <c r="B568" s="1" t="s">
         <v>1187</v>
       </c>
-      <c r="B568" s="1" t="s">
-        <v>1188</v>
-      </c>
       <c r="C568" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D568" s="1" t="s">
-        <v>1168</v>
+        <v>1167</v>
       </c>
       <c r="E568" s="1" t="s">
         <v>37</v>
@@ -16123,16 +16120,16 @@
     </row>
     <row r="569" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A569" s="1" t="s">
+        <v>1188</v>
+      </c>
+      <c r="B569" s="1" t="s">
         <v>1189</v>
       </c>
-      <c r="B569" s="1" t="s">
-        <v>1190</v>
-      </c>
       <c r="C569" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D569" s="1" t="s">
-        <v>1168</v>
+        <v>1167</v>
       </c>
       <c r="E569" s="1" t="s">
         <v>40</v>
@@ -16143,16 +16140,16 @@
     </row>
     <row r="570" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A570" s="1" t="s">
+        <v>1190</v>
+      </c>
+      <c r="B570" s="1" t="s">
         <v>1191</v>
       </c>
-      <c r="B570" s="1" t="s">
-        <v>1192</v>
-      </c>
       <c r="C570" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D570" s="1" t="s">
-        <v>1168</v>
+        <v>1167</v>
       </c>
       <c r="E570" s="1" t="s">
         <v>68</v>
@@ -16163,16 +16160,16 @@
     </row>
     <row r="571" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A571" s="1" t="s">
+        <v>1192</v>
+      </c>
+      <c r="B571" s="1" t="s">
         <v>1193</v>
       </c>
-      <c r="B571" s="1" t="s">
-        <v>1194</v>
-      </c>
       <c r="C571" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D571" s="1" t="s">
-        <v>1168</v>
+        <v>1167</v>
       </c>
       <c r="E571" s="1" t="s">
         <v>100</v>
@@ -16183,16 +16180,16 @@
     </row>
     <row r="572" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A572" s="1" t="s">
+        <v>1194</v>
+      </c>
+      <c r="B572" s="1" t="s">
         <v>1195</v>
       </c>
-      <c r="B572" s="1" t="s">
+      <c r="C572" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D572" s="1" t="s">
         <v>1196</v>
-      </c>
-      <c r="C572" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D572" s="1" t="s">
-        <v>1197</v>
       </c>
       <c r="E572" s="1" t="s">
         <v>4</v>
@@ -16203,16 +16200,16 @@
     </row>
     <row r="573" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A573" s="1" t="s">
+        <v>1197</v>
+      </c>
+      <c r="B573" s="1" t="s">
         <v>1198</v>
       </c>
-      <c r="B573" s="1" t="s">
-        <v>1199</v>
-      </c>
       <c r="C573" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D573" s="1" t="s">
-        <v>1197</v>
+        <v>1196</v>
       </c>
       <c r="E573" s="1" t="s">
         <v>8</v>
@@ -16223,16 +16220,16 @@
     </row>
     <row r="574" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A574" s="1" t="s">
+        <v>1199</v>
+      </c>
+      <c r="B574" s="1" t="s">
         <v>1200</v>
       </c>
-      <c r="B574" s="1" t="s">
-        <v>1201</v>
-      </c>
       <c r="C574" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D574" s="1" t="s">
-        <v>1197</v>
+        <v>1196</v>
       </c>
       <c r="E574" s="1" t="s">
         <v>12</v>
@@ -16243,16 +16240,16 @@
     </row>
     <row r="575" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A575" s="1" t="s">
+        <v>1201</v>
+      </c>
+      <c r="B575" s="1" t="s">
         <v>1202</v>
       </c>
-      <c r="B575" s="1" t="s">
-        <v>1203</v>
-      </c>
       <c r="C575" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D575" s="1" t="s">
-        <v>1197</v>
+        <v>1196</v>
       </c>
       <c r="E575" s="1" t="s">
         <v>15</v>
@@ -16263,16 +16260,16 @@
     </row>
     <row r="576" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A576" s="1" t="s">
+        <v>1203</v>
+      </c>
+      <c r="B576" s="1" t="s">
         <v>1204</v>
       </c>
-      <c r="B576" s="1" t="s">
-        <v>1205</v>
-      </c>
       <c r="C576" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D576" s="1" t="s">
-        <v>1197</v>
+        <v>1196</v>
       </c>
       <c r="E576" s="1" t="s">
         <v>18</v>
@@ -16283,16 +16280,16 @@
     </row>
     <row r="577" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A577" s="1" t="s">
+        <v>1205</v>
+      </c>
+      <c r="B577" s="1" t="s">
         <v>1206</v>
       </c>
-      <c r="B577" s="1" t="s">
-        <v>1207</v>
-      </c>
       <c r="C577" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D577" s="1" t="s">
-        <v>1197</v>
+        <v>1196</v>
       </c>
       <c r="E577" s="1" t="s">
         <v>21</v>
@@ -16303,16 +16300,16 @@
     </row>
     <row r="578" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A578" s="1" t="s">
+        <v>1207</v>
+      </c>
+      <c r="B578" s="1" t="s">
         <v>1208</v>
       </c>
-      <c r="B578" s="1" t="s">
-        <v>1209</v>
-      </c>
       <c r="C578" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D578" s="1" t="s">
-        <v>1197</v>
+        <v>1196</v>
       </c>
       <c r="E578" s="1" t="s">
         <v>24</v>
@@ -16323,16 +16320,16 @@
     </row>
     <row r="579" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A579" s="1" t="s">
+        <v>1209</v>
+      </c>
+      <c r="B579" s="1" t="s">
         <v>1210</v>
       </c>
-      <c r="B579" s="1" t="s">
-        <v>1211</v>
-      </c>
       <c r="C579" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D579" s="1" t="s">
-        <v>1197</v>
+        <v>1196</v>
       </c>
       <c r="E579" s="1" t="s">
         <v>28</v>
@@ -16343,16 +16340,16 @@
     </row>
     <row r="580" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A580" s="1" t="s">
+        <v>1211</v>
+      </c>
+      <c r="B580" s="1" t="s">
         <v>1212</v>
       </c>
-      <c r="B580" s="1" t="s">
-        <v>1213</v>
-      </c>
       <c r="C580" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D580" s="1" t="s">
-        <v>1197</v>
+        <v>1196</v>
       </c>
       <c r="E580" s="1" t="s">
         <v>31</v>
@@ -16363,16 +16360,16 @@
     </row>
     <row r="581" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A581" s="1" t="s">
+        <v>1213</v>
+      </c>
+      <c r="B581" s="1" t="s">
         <v>1214</v>
       </c>
-      <c r="B581" s="1" t="s">
-        <v>1215</v>
-      </c>
       <c r="C581" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D581" s="1" t="s">
-        <v>1197</v>
+        <v>1196</v>
       </c>
       <c r="E581" s="1" t="s">
         <v>34</v>
@@ -16383,16 +16380,16 @@
     </row>
     <row r="582" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A582" s="1" t="s">
+        <v>1215</v>
+      </c>
+      <c r="B582" s="1" t="s">
         <v>1216</v>
       </c>
-      <c r="B582" s="1" t="s">
-        <v>1217</v>
-      </c>
       <c r="C582" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D582" s="1" t="s">
-        <v>1197</v>
+        <v>1196</v>
       </c>
       <c r="E582" s="1" t="s">
         <v>37</v>
@@ -16403,16 +16400,16 @@
     </row>
     <row r="583" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A583" s="1" t="s">
+        <v>1217</v>
+      </c>
+      <c r="B583" s="1" t="s">
         <v>1218</v>
       </c>
-      <c r="B583" s="1" t="s">
-        <v>1219</v>
-      </c>
       <c r="C583" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D583" s="1" t="s">
-        <v>1197</v>
+        <v>1196</v>
       </c>
       <c r="E583" s="1" t="s">
         <v>40</v>
@@ -16423,16 +16420,16 @@
     </row>
     <row r="584" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A584" s="1" t="s">
+        <v>1219</v>
+      </c>
+      <c r="B584" s="1" t="s">
         <v>1220</v>
       </c>
-      <c r="B584" s="1" t="s">
-        <v>1221</v>
-      </c>
       <c r="C584" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D584" s="1" t="s">
-        <v>1197</v>
+        <v>1196</v>
       </c>
       <c r="E584" s="1" t="s">
         <v>68</v>
@@ -16443,16 +16440,16 @@
     </row>
     <row r="585" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A585" s="1" t="s">
+        <v>1221</v>
+      </c>
+      <c r="B585" s="1" t="s">
         <v>1222</v>
       </c>
-      <c r="B585" s="1" t="s">
+      <c r="C585" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D585" s="1" t="s">
         <v>1223</v>
-      </c>
-      <c r="C585" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D585" s="1" t="s">
-        <v>1224</v>
       </c>
       <c r="E585" s="1" t="s">
         <v>4</v>
@@ -16463,16 +16460,16 @@
     </row>
     <row r="586" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A586" s="1" t="s">
+        <v>1224</v>
+      </c>
+      <c r="B586" s="1" t="s">
         <v>1225</v>
       </c>
-      <c r="B586" s="1" t="s">
-        <v>1226</v>
-      </c>
       <c r="C586" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D586" s="1" t="s">
-        <v>1224</v>
+        <v>1223</v>
       </c>
       <c r="E586" s="1" t="s">
         <v>8</v>
@@ -16483,56 +16480,56 @@
     </row>
     <row r="587" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A587" s="1" t="s">
+        <v>1226</v>
+      </c>
+      <c r="B587" s="1" t="s">
         <v>1227</v>
       </c>
-      <c r="B587" s="1" t="s">
-        <v>1228</v>
-      </c>
       <c r="C587" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D587" s="1" t="s">
-        <v>1224</v>
+        <v>1223</v>
       </c>
       <c r="E587" s="1" t="s">
         <v>12</v>
       </c>
       <c r="F587" s="1" t="s">
-        <v>1229</v>
+        <v>1228</v>
       </c>
     </row>
     <row r="588" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A588" s="1" t="s">
+        <v>1229</v>
+      </c>
+      <c r="B588" s="1" t="s">
         <v>1230</v>
       </c>
-      <c r="B588" s="1" t="s">
-        <v>1231</v>
-      </c>
       <c r="C588" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D588" s="1" t="s">
-        <v>1224</v>
+        <v>1223</v>
       </c>
       <c r="E588" s="1" t="s">
         <v>15</v>
       </c>
       <c r="F588" s="1" t="s">
-        <v>1229</v>
+        <v>1228</v>
       </c>
     </row>
     <row r="589" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A589" s="1" t="s">
+        <v>1231</v>
+      </c>
+      <c r="B589" s="1" t="s">
         <v>1232</v>
       </c>
-      <c r="B589" s="1" t="s">
-        <v>1233</v>
-      </c>
       <c r="C589" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D589" s="1" t="s">
-        <v>1224</v>
+        <v>1223</v>
       </c>
       <c r="E589" s="1" t="s">
         <v>18</v>
@@ -16543,16 +16540,16 @@
     </row>
     <row r="590" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A590" s="1" t="s">
+        <v>1233</v>
+      </c>
+      <c r="B590" s="1" t="s">
         <v>1234</v>
       </c>
-      <c r="B590" s="1" t="s">
-        <v>1235</v>
-      </c>
       <c r="C590" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D590" s="1" t="s">
-        <v>1224</v>
+        <v>1223</v>
       </c>
       <c r="E590" s="1" t="s">
         <v>21</v>
@@ -16563,16 +16560,16 @@
     </row>
     <row r="591" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A591" s="1" t="s">
+        <v>1235</v>
+      </c>
+      <c r="B591" s="1" t="s">
         <v>1236</v>
       </c>
-      <c r="B591" s="1" t="s">
-        <v>1237</v>
-      </c>
       <c r="C591" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D591" s="1" t="s">
-        <v>1224</v>
+        <v>1223</v>
       </c>
       <c r="E591" s="1" t="s">
         <v>24</v>
@@ -16583,16 +16580,16 @@
     </row>
     <row r="592" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A592" s="1" t="s">
+        <v>1237</v>
+      </c>
+      <c r="B592" s="1" t="s">
         <v>1238</v>
       </c>
-      <c r="B592" s="1" t="s">
-        <v>1239</v>
-      </c>
       <c r="C592" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D592" s="1" t="s">
-        <v>1224</v>
+        <v>1223</v>
       </c>
       <c r="E592" s="1" t="s">
         <v>28</v>
@@ -16603,16 +16600,16 @@
     </row>
     <row r="593" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A593" s="1" t="s">
+        <v>1239</v>
+      </c>
+      <c r="B593" s="1" t="s">
         <v>1240</v>
       </c>
-      <c r="B593" s="1" t="s">
-        <v>1241</v>
-      </c>
       <c r="C593" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D593" s="1" t="s">
-        <v>1224</v>
+        <v>1223</v>
       </c>
       <c r="E593" s="1" t="s">
         <v>31</v>
@@ -16623,16 +16620,16 @@
     </row>
     <row r="594" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A594" s="1" t="s">
+        <v>1241</v>
+      </c>
+      <c r="B594" s="1" t="s">
         <v>1242</v>
       </c>
-      <c r="B594" s="1" t="s">
-        <v>1243</v>
-      </c>
       <c r="C594" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D594" s="1" t="s">
-        <v>1224</v>
+        <v>1223</v>
       </c>
       <c r="E594" s="1" t="s">
         <v>34</v>
@@ -16643,16 +16640,16 @@
     </row>
     <row r="595" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A595" s="1" t="s">
+        <v>1243</v>
+      </c>
+      <c r="B595" s="1" t="s">
         <v>1244</v>
       </c>
-      <c r="B595" s="1" t="s">
-        <v>1245</v>
-      </c>
       <c r="C595" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D595" s="1" t="s">
-        <v>1224</v>
+        <v>1223</v>
       </c>
       <c r="E595" s="1" t="s">
         <v>37</v>
@@ -16663,16 +16660,16 @@
     </row>
     <row r="596" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A596" s="1" t="s">
+        <v>1245</v>
+      </c>
+      <c r="B596" s="1" t="s">
         <v>1246</v>
       </c>
-      <c r="B596" s="1" t="s">
-        <v>1247</v>
-      </c>
       <c r="C596" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D596" s="1" t="s">
-        <v>1224</v>
+        <v>1223</v>
       </c>
       <c r="E596" s="1" t="s">
         <v>40</v>
@@ -16683,16 +16680,16 @@
     </row>
     <row r="597" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A597" s="1" t="s">
+        <v>1247</v>
+      </c>
+      <c r="B597" s="1" t="s">
         <v>1248</v>
       </c>
-      <c r="B597" s="1" t="s">
-        <v>1249</v>
-      </c>
       <c r="C597" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D597" s="1" t="s">
-        <v>1224</v>
+        <v>1223</v>
       </c>
       <c r="E597" s="1" t="s">
         <v>68</v>
@@ -16703,16 +16700,16 @@
     </row>
     <row r="598" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A598" s="1" t="s">
+        <v>1249</v>
+      </c>
+      <c r="B598" s="1" t="s">
         <v>1250</v>
       </c>
-      <c r="B598" s="1" t="s">
+      <c r="C598" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D598" s="1" t="s">
         <v>1251</v>
-      </c>
-      <c r="C598" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D598" s="1" t="s">
-        <v>1252</v>
       </c>
       <c r="E598" s="1" t="s">
         <v>4</v>
@@ -16723,16 +16720,16 @@
     </row>
     <row r="599" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A599" s="1" t="s">
+        <v>1252</v>
+      </c>
+      <c r="B599" s="1" t="s">
         <v>1253</v>
       </c>
-      <c r="B599" s="1" t="s">
-        <v>1254</v>
-      </c>
       <c r="C599" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D599" s="1" t="s">
-        <v>1252</v>
+        <v>1251</v>
       </c>
       <c r="E599" s="1" t="s">
         <v>8</v>
@@ -16743,16 +16740,16 @@
     </row>
     <row r="600" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A600" s="1" t="s">
+        <v>1254</v>
+      </c>
+      <c r="B600" s="1" t="s">
         <v>1255</v>
       </c>
-      <c r="B600" s="1" t="s">
-        <v>1256</v>
-      </c>
       <c r="C600" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D600" s="1" t="s">
-        <v>1252</v>
+        <v>1251</v>
       </c>
       <c r="E600" s="1" t="s">
         <v>12</v>
@@ -16763,16 +16760,16 @@
     </row>
     <row r="601" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A601" s="1" t="s">
+        <v>1256</v>
+      </c>
+      <c r="B601" s="1" t="s">
         <v>1257</v>
       </c>
-      <c r="B601" s="1" t="s">
-        <v>1258</v>
-      </c>
       <c r="C601" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D601" s="1" t="s">
-        <v>1252</v>
+        <v>1251</v>
       </c>
       <c r="E601" s="1" t="s">
         <v>15</v>
@@ -16783,16 +16780,16 @@
     </row>
     <row r="602" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A602" s="1" t="s">
+        <v>1258</v>
+      </c>
+      <c r="B602" s="1" t="s">
         <v>1259</v>
       </c>
-      <c r="B602" s="1" t="s">
-        <v>1260</v>
-      </c>
       <c r="C602" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D602" s="1" t="s">
-        <v>1252</v>
+        <v>1251</v>
       </c>
       <c r="E602" s="1" t="s">
         <v>18</v>
@@ -16803,16 +16800,16 @@
     </row>
     <row r="603" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A603" s="1" t="s">
+        <v>1260</v>
+      </c>
+      <c r="B603" s="1" t="s">
         <v>1261</v>
       </c>
-      <c r="B603" s="1" t="s">
-        <v>1262</v>
-      </c>
       <c r="C603" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D603" s="1" t="s">
-        <v>1252</v>
+        <v>1251</v>
       </c>
       <c r="E603" s="1" t="s">
         <v>21</v>
@@ -16823,16 +16820,16 @@
     </row>
     <row r="604" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A604" s="1" t="s">
+        <v>1262</v>
+      </c>
+      <c r="B604" s="1" t="s">
         <v>1263</v>
       </c>
-      <c r="B604" s="1" t="s">
-        <v>1264</v>
-      </c>
       <c r="C604" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D604" s="1" t="s">
-        <v>1252</v>
+        <v>1251</v>
       </c>
       <c r="E604" s="1" t="s">
         <v>24</v>
@@ -16843,16 +16840,16 @@
     </row>
     <row r="605" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A605" s="1" t="s">
+        <v>1264</v>
+      </c>
+      <c r="B605" s="1" t="s">
         <v>1265</v>
       </c>
-      <c r="B605" s="1" t="s">
-        <v>1266</v>
-      </c>
       <c r="C605" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D605" s="1" t="s">
-        <v>1252</v>
+        <v>1251</v>
       </c>
       <c r="E605" s="1" t="s">
         <v>28</v>
@@ -16863,16 +16860,16 @@
     </row>
     <row r="606" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A606" s="1" t="s">
+        <v>1266</v>
+      </c>
+      <c r="B606" s="1" t="s">
         <v>1267</v>
       </c>
-      <c r="B606" s="1" t="s">
-        <v>1268</v>
-      </c>
       <c r="C606" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D606" s="1" t="s">
-        <v>1252</v>
+        <v>1251</v>
       </c>
       <c r="E606" s="1" t="s">
         <v>31</v>
@@ -16883,16 +16880,16 @@
     </row>
     <row r="607" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A607" s="1" t="s">
+        <v>1268</v>
+      </c>
+      <c r="B607" s="1" t="s">
         <v>1269</v>
       </c>
-      <c r="B607" s="1" t="s">
-        <v>1270</v>
-      </c>
       <c r="C607" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D607" s="1" t="s">
-        <v>1252</v>
+        <v>1251</v>
       </c>
       <c r="E607" s="1" t="s">
         <v>34</v>
@@ -16903,16 +16900,16 @@
     </row>
     <row r="608" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A608" s="1" t="s">
+        <v>1270</v>
+      </c>
+      <c r="B608" s="1" t="s">
         <v>1271</v>
       </c>
-      <c r="B608" s="1" t="s">
-        <v>1272</v>
-      </c>
       <c r="C608" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D608" s="1" t="s">
-        <v>1252</v>
+        <v>1251</v>
       </c>
       <c r="E608" s="1" t="s">
         <v>37</v>
@@ -16923,16 +16920,16 @@
     </row>
     <row r="609" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A609" s="1" t="s">
+        <v>1272</v>
+      </c>
+      <c r="B609" s="1" t="s">
         <v>1273</v>
       </c>
-      <c r="B609" s="1" t="s">
-        <v>1274</v>
-      </c>
       <c r="C609" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D609" s="1" t="s">
-        <v>1252</v>
+        <v>1251</v>
       </c>
       <c r="E609" s="1" t="s">
         <v>40</v>
@@ -16943,16 +16940,16 @@
     </row>
     <row r="610" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A610" s="1" t="s">
+        <v>1274</v>
+      </c>
+      <c r="B610" s="1" t="s">
         <v>1275</v>
       </c>
-      <c r="B610" s="1" t="s">
-        <v>1276</v>
-      </c>
       <c r="C610" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D610" s="1" t="s">
-        <v>1252</v>
+        <v>1251</v>
       </c>
       <c r="E610" s="1" t="s">
         <v>68</v>
@@ -16963,16 +16960,16 @@
     </row>
     <row r="611" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A611" s="1" t="s">
+        <v>1276</v>
+      </c>
+      <c r="B611" s="1" t="s">
         <v>1277</v>
       </c>
-      <c r="B611" s="1" t="s">
-        <v>1278</v>
-      </c>
       <c r="C611" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D611" s="1" t="s">
-        <v>1252</v>
+        <v>1251</v>
       </c>
       <c r="E611" s="1" t="s">
         <v>100</v>
@@ -16983,16 +16980,16 @@
     </row>
     <row r="612" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A612" s="1" t="s">
+        <v>1278</v>
+      </c>
+      <c r="B612" s="1" t="s">
         <v>1279</v>
       </c>
-      <c r="B612" s="1" t="s">
-        <v>1280</v>
-      </c>
       <c r="C612" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D612" s="1" t="s">
-        <v>1252</v>
+        <v>1251</v>
       </c>
       <c r="E612" s="1" t="s">
         <v>103</v>
@@ -17003,16 +17000,16 @@
     </row>
     <row r="613" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A613" s="1" t="s">
+        <v>1280</v>
+      </c>
+      <c r="B613" s="1" t="s">
         <v>1281</v>
       </c>
-      <c r="B613" s="1" t="s">
-        <v>1282</v>
-      </c>
       <c r="C613" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D613" s="1" t="s">
-        <v>1252</v>
+        <v>1251</v>
       </c>
       <c r="E613" s="1" t="s">
         <v>106</v>
@@ -17023,16 +17020,16 @@
     </row>
     <row r="614" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A614" s="1" t="s">
+        <v>1282</v>
+      </c>
+      <c r="B614" s="1" t="s">
         <v>1283</v>
       </c>
-      <c r="B614" s="1" t="s">
-        <v>1284</v>
-      </c>
       <c r="C614" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D614" s="1" t="s">
-        <v>1252</v>
+        <v>1251</v>
       </c>
       <c r="E614" s="1" t="s">
         <v>109</v>
@@ -17043,16 +17040,16 @@
     </row>
     <row r="615" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A615" s="1" t="s">
+        <v>1284</v>
+      </c>
+      <c r="B615" s="1" t="s">
         <v>1285</v>
       </c>
-      <c r="B615" s="1" t="s">
+      <c r="C615" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D615" s="1" t="s">
         <v>1286</v>
-      </c>
-      <c r="C615" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D615" s="1" t="s">
-        <v>1287</v>
       </c>
       <c r="E615" s="1" t="s">
         <v>4</v>
@@ -17063,16 +17060,16 @@
     </row>
     <row r="616" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A616" s="1" t="s">
+        <v>1287</v>
+      </c>
+      <c r="B616" s="1" t="s">
         <v>1288</v>
       </c>
-      <c r="B616" s="1" t="s">
-        <v>1289</v>
-      </c>
       <c r="C616" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D616" s="1" t="s">
-        <v>1287</v>
+        <v>1286</v>
       </c>
       <c r="E616" s="1" t="s">
         <v>8</v>
@@ -17083,16 +17080,16 @@
     </row>
     <row r="617" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A617" s="1" t="s">
+        <v>1289</v>
+      </c>
+      <c r="B617" s="1" t="s">
         <v>1290</v>
       </c>
-      <c r="B617" s="1" t="s">
-        <v>1291</v>
-      </c>
       <c r="C617" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D617" s="1" t="s">
-        <v>1287</v>
+        <v>1286</v>
       </c>
       <c r="E617" s="1" t="s">
         <v>12</v>
@@ -17103,16 +17100,16 @@
     </row>
     <row r="618" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A618" s="1" t="s">
+        <v>1291</v>
+      </c>
+      <c r="B618" s="1" t="s">
         <v>1292</v>
       </c>
-      <c r="B618" s="1" t="s">
-        <v>1293</v>
-      </c>
       <c r="C618" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D618" s="1" t="s">
-        <v>1287</v>
+        <v>1286</v>
       </c>
       <c r="E618" s="1" t="s">
         <v>15</v>
@@ -17123,16 +17120,16 @@
     </row>
     <row r="619" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A619" s="1" t="s">
+        <v>1293</v>
+      </c>
+      <c r="B619" s="1" t="s">
         <v>1294</v>
       </c>
-      <c r="B619" s="1" t="s">
-        <v>1295</v>
-      </c>
       <c r="C619" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D619" s="1" t="s">
-        <v>1287</v>
+        <v>1286</v>
       </c>
       <c r="E619" s="1" t="s">
         <v>18</v>
@@ -17143,16 +17140,16 @@
     </row>
     <row r="620" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A620" s="1" t="s">
+        <v>1295</v>
+      </c>
+      <c r="B620" s="1" t="s">
         <v>1296</v>
       </c>
-      <c r="B620" s="1" t="s">
-        <v>1297</v>
-      </c>
       <c r="C620" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D620" s="1" t="s">
-        <v>1287</v>
+        <v>1286</v>
       </c>
       <c r="E620" s="1" t="s">
         <v>21</v>
@@ -17163,16 +17160,16 @@
     </row>
     <row r="621" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A621" s="1" t="s">
+        <v>1297</v>
+      </c>
+      <c r="B621" s="1" t="s">
         <v>1298</v>
       </c>
-      <c r="B621" s="1" t="s">
-        <v>1299</v>
-      </c>
       <c r="C621" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D621" s="1" t="s">
-        <v>1287</v>
+        <v>1286</v>
       </c>
       <c r="E621" s="1" t="s">
         <v>24</v>
@@ -17183,16 +17180,16 @@
     </row>
     <row r="622" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A622" s="1" t="s">
+        <v>1299</v>
+      </c>
+      <c r="B622" s="1" t="s">
         <v>1300</v>
       </c>
-      <c r="B622" s="1" t="s">
-        <v>1301</v>
-      </c>
       <c r="C622" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D622" s="1" t="s">
-        <v>1287</v>
+        <v>1286</v>
       </c>
       <c r="E622" s="1" t="s">
         <v>28</v>
@@ -17203,16 +17200,16 @@
     </row>
     <row r="623" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A623" s="1" t="s">
+        <v>1301</v>
+      </c>
+      <c r="B623" s="1" t="s">
         <v>1302</v>
       </c>
-      <c r="B623" s="1" t="s">
-        <v>1303</v>
-      </c>
       <c r="C623" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D623" s="1" t="s">
-        <v>1287</v>
+        <v>1286</v>
       </c>
       <c r="E623" s="1" t="s">
         <v>31</v>
@@ -17223,16 +17220,16 @@
     </row>
     <row r="624" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A624" s="1" t="s">
+        <v>1303</v>
+      </c>
+      <c r="B624" s="1" t="s">
         <v>1304</v>
       </c>
-      <c r="B624" s="1" t="s">
-        <v>1305</v>
-      </c>
       <c r="C624" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D624" s="1" t="s">
-        <v>1287</v>
+        <v>1286</v>
       </c>
       <c r="E624" s="1" t="s">
         <v>34</v>
@@ -17243,16 +17240,16 @@
     </row>
     <row r="625" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A625" s="1" t="s">
+        <v>1305</v>
+      </c>
+      <c r="B625" s="1" t="s">
         <v>1306</v>
       </c>
-      <c r="B625" s="1" t="s">
-        <v>1307</v>
-      </c>
       <c r="C625" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D625" s="1" t="s">
-        <v>1287</v>
+        <v>1286</v>
       </c>
       <c r="E625" s="1" t="s">
         <v>37</v>
@@ -17263,16 +17260,16 @@
     </row>
     <row r="626" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A626" s="1" t="s">
+        <v>1307</v>
+      </c>
+      <c r="B626" s="1" t="s">
         <v>1308</v>
       </c>
-      <c r="B626" s="1" t="s">
-        <v>1309</v>
-      </c>
       <c r="C626" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D626" s="1" t="s">
-        <v>1287</v>
+        <v>1286</v>
       </c>
       <c r="E626" s="1" t="s">
         <v>40</v>
@@ -17283,16 +17280,16 @@
     </row>
     <row r="627" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A627" s="1" t="s">
+        <v>1309</v>
+      </c>
+      <c r="B627" s="1" t="s">
         <v>1310</v>
       </c>
-      <c r="B627" s="1" t="s">
-        <v>1311</v>
-      </c>
       <c r="C627" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D627" s="1" t="s">
-        <v>1287</v>
+        <v>1286</v>
       </c>
       <c r="E627" s="1" t="s">
         <v>68</v>
@@ -17303,16 +17300,16 @@
     </row>
     <row r="628" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A628" s="1" t="s">
+        <v>1311</v>
+      </c>
+      <c r="B628" s="1" t="s">
         <v>1312</v>
       </c>
-      <c r="B628" s="1" t="s">
-        <v>1313</v>
-      </c>
       <c r="C628" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D628" s="1" t="s">
-        <v>1287</v>
+        <v>1286</v>
       </c>
       <c r="E628" s="1" t="s">
         <v>100</v>
@@ -17323,16 +17320,16 @@
     </row>
     <row r="629" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A629" s="1" t="s">
+        <v>1313</v>
+      </c>
+      <c r="B629" s="1" t="s">
         <v>1314</v>
       </c>
-      <c r="B629" s="1" t="s">
-        <v>1315</v>
-      </c>
       <c r="C629" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D629" s="1" t="s">
-        <v>1287</v>
+        <v>1286</v>
       </c>
       <c r="E629" s="1" t="s">
         <v>103</v>
@@ -17343,16 +17340,16 @@
     </row>
     <row r="630" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A630" s="1" t="s">
+        <v>1315</v>
+      </c>
+      <c r="B630" s="1" t="s">
         <v>1316</v>
       </c>
-      <c r="B630" s="1" t="s">
-        <v>1317</v>
-      </c>
       <c r="C630" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D630" s="1" t="s">
-        <v>1287</v>
+        <v>1286</v>
       </c>
       <c r="E630" s="1" t="s">
         <v>106</v>
@@ -17363,16 +17360,16 @@
     </row>
     <row r="631" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A631" s="1" t="s">
+        <v>1317</v>
+      </c>
+      <c r="B631" s="1" t="s">
         <v>1318</v>
       </c>
-      <c r="B631" s="1" t="s">
-        <v>1319</v>
-      </c>
       <c r="C631" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D631" s="1" t="s">
-        <v>1287</v>
+        <v>1286</v>
       </c>
       <c r="E631" s="1" t="s">
         <v>109</v>
@@ -17383,16 +17380,16 @@
     </row>
     <row r="632" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A632" s="1" t="s">
+        <v>1319</v>
+      </c>
+      <c r="B632" s="1" t="s">
         <v>1320</v>
       </c>
-      <c r="B632" s="1" t="s">
-        <v>1321</v>
-      </c>
       <c r="C632" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D632" s="1" t="s">
-        <v>1287</v>
+        <v>1286</v>
       </c>
       <c r="E632" s="1" t="s">
         <v>112</v>
@@ -17403,16 +17400,16 @@
     </row>
     <row r="633" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A633" s="1" t="s">
+        <v>1321</v>
+      </c>
+      <c r="B633" s="1" t="s">
         <v>1322</v>
       </c>
-      <c r="B633" s="1" t="s">
+      <c r="C633" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D633" s="1" t="s">
         <v>1323</v>
-      </c>
-      <c r="C633" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D633" s="1" t="s">
-        <v>1324</v>
       </c>
       <c r="E633" s="1" t="s">
         <v>4</v>
@@ -17423,16 +17420,16 @@
     </row>
     <row r="634" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A634" s="1" t="s">
+        <v>1324</v>
+      </c>
+      <c r="B634" s="1" t="s">
         <v>1325</v>
       </c>
-      <c r="B634" s="1" t="s">
-        <v>1326</v>
-      </c>
       <c r="C634" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D634" s="1" t="s">
-        <v>1324</v>
+        <v>1323</v>
       </c>
       <c r="E634" s="1" t="s">
         <v>8</v>
@@ -17443,16 +17440,16 @@
     </row>
     <row r="635" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A635" s="1" t="s">
+        <v>1326</v>
+      </c>
+      <c r="B635" s="1" t="s">
         <v>1327</v>
       </c>
-      <c r="B635" s="1" t="s">
-        <v>1328</v>
-      </c>
       <c r="C635" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D635" s="1" t="s">
-        <v>1324</v>
+        <v>1323</v>
       </c>
       <c r="E635" s="1" t="s">
         <v>12</v>
@@ -17463,16 +17460,16 @@
     </row>
     <row r="636" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A636" s="1" t="s">
+        <v>1328</v>
+      </c>
+      <c r="B636" s="1" t="s">
         <v>1329</v>
       </c>
-      <c r="B636" s="1" t="s">
-        <v>1330</v>
-      </c>
       <c r="C636" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D636" s="1" t="s">
-        <v>1324</v>
+        <v>1323</v>
       </c>
       <c r="E636" s="1" t="s">
         <v>15</v>
@@ -17483,16 +17480,16 @@
     </row>
     <row r="637" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A637" s="1" t="s">
-        <v>1331</v>
+        <v>1330</v>
       </c>
       <c r="B637" s="1" t="s">
-        <v>1330</v>
+        <v>1329</v>
       </c>
       <c r="C637" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D637" s="1" t="s">
-        <v>1324</v>
+        <v>1323</v>
       </c>
       <c r="E637" s="1" t="s">
         <v>18</v>
@@ -17503,16 +17500,16 @@
     </row>
     <row r="638" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A638" s="1" t="s">
+        <v>1331</v>
+      </c>
+      <c r="B638" s="1" t="s">
         <v>1332</v>
       </c>
-      <c r="B638" s="1" t="s">
-        <v>1333</v>
-      </c>
       <c r="C638" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D638" s="1" t="s">
-        <v>1324</v>
+        <v>1323</v>
       </c>
       <c r="E638" s="1" t="s">
         <v>21</v>
@@ -17523,16 +17520,16 @@
     </row>
     <row r="639" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A639" s="1" t="s">
+        <v>1333</v>
+      </c>
+      <c r="B639" s="1" t="s">
         <v>1334</v>
       </c>
-      <c r="B639" s="1" t="s">
-        <v>1335</v>
-      </c>
       <c r="C639" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D639" s="1" t="s">
-        <v>1324</v>
+        <v>1323</v>
       </c>
       <c r="E639" s="1" t="s">
         <v>24</v>
@@ -17543,16 +17540,16 @@
     </row>
     <row r="640" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A640" s="1" t="s">
+        <v>1335</v>
+      </c>
+      <c r="B640" s="1" t="s">
         <v>1336</v>
       </c>
-      <c r="B640" s="1" t="s">
-        <v>1337</v>
-      </c>
       <c r="C640" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D640" s="1" t="s">
-        <v>1324</v>
+        <v>1323</v>
       </c>
       <c r="E640" s="1" t="s">
         <v>28</v>
@@ -17563,16 +17560,16 @@
     </row>
     <row r="641" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A641" s="1" t="s">
+        <v>1337</v>
+      </c>
+      <c r="B641" s="1" t="s">
         <v>1338</v>
       </c>
-      <c r="B641" s="1" t="s">
-        <v>1339</v>
-      </c>
       <c r="C641" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D641" s="1" t="s">
-        <v>1324</v>
+        <v>1323</v>
       </c>
       <c r="E641" s="1" t="s">
         <v>31</v>
@@ -17583,16 +17580,16 @@
     </row>
     <row r="642" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A642" s="1" t="s">
+        <v>1339</v>
+      </c>
+      <c r="B642" s="1" t="s">
         <v>1340</v>
       </c>
-      <c r="B642" s="1" t="s">
-        <v>1341</v>
-      </c>
       <c r="C642" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D642" s="1" t="s">
-        <v>1324</v>
+        <v>1323</v>
       </c>
       <c r="E642" s="1" t="s">
         <v>34</v>
@@ -17603,16 +17600,16 @@
     </row>
     <row r="643" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A643" s="1" t="s">
+        <v>1341</v>
+      </c>
+      <c r="B643" s="1" t="s">
         <v>1342</v>
       </c>
-      <c r="B643" s="1" t="s">
-        <v>1343</v>
-      </c>
       <c r="C643" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D643" s="1" t="s">
-        <v>1324</v>
+        <v>1323</v>
       </c>
       <c r="E643" s="1" t="s">
         <v>37</v>
@@ -17623,16 +17620,16 @@
     </row>
     <row r="644" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A644" s="1" t="s">
+        <v>1343</v>
+      </c>
+      <c r="B644" s="1" t="s">
         <v>1344</v>
       </c>
-      <c r="B644" s="1" t="s">
-        <v>1345</v>
-      </c>
       <c r="C644" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D644" s="1" t="s">
-        <v>1324</v>
+        <v>1323</v>
       </c>
       <c r="E644" s="1" t="s">
         <v>40</v>
@@ -17643,16 +17640,16 @@
     </row>
     <row r="645" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A645" s="1" t="s">
+        <v>1345</v>
+      </c>
+      <c r="B645" s="1" t="s">
         <v>1346</v>
       </c>
-      <c r="B645" s="1" t="s">
-        <v>1347</v>
-      </c>
       <c r="C645" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D645" s="1" t="s">
-        <v>1324</v>
+        <v>1323</v>
       </c>
       <c r="E645" s="1" t="s">
         <v>68</v>
@@ -17663,16 +17660,16 @@
     </row>
     <row r="646" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A646" s="1" t="s">
+        <v>1347</v>
+      </c>
+      <c r="B646" s="1" t="s">
         <v>1348</v>
       </c>
-      <c r="B646" s="1" t="s">
-        <v>1349</v>
-      </c>
       <c r="C646" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D646" s="1" t="s">
-        <v>1324</v>
+        <v>1323</v>
       </c>
       <c r="E646" s="1" t="s">
         <v>100</v>
@@ -17683,16 +17680,16 @@
     </row>
     <row r="647" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A647" s="1" t="s">
+        <v>1349</v>
+      </c>
+      <c r="B647" s="1" t="s">
         <v>1350</v>
       </c>
-      <c r="B647" s="1" t="s">
-        <v>1351</v>
-      </c>
       <c r="C647" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D647" s="1" t="s">
-        <v>1324</v>
+        <v>1323</v>
       </c>
       <c r="E647" s="1" t="s">
         <v>103</v>
@@ -17703,16 +17700,16 @@
     </row>
     <row r="648" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A648" s="1" t="s">
+        <v>1351</v>
+      </c>
+      <c r="B648" s="1" t="s">
         <v>1352</v>
       </c>
-      <c r="B648" s="1" t="s">
-        <v>1353</v>
-      </c>
       <c r="C648" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D648" s="1" t="s">
-        <v>1324</v>
+        <v>1323</v>
       </c>
       <c r="E648" s="1" t="s">
         <v>106</v>
@@ -17723,16 +17720,16 @@
     </row>
     <row r="649" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A649" s="1" t="s">
+        <v>1353</v>
+      </c>
+      <c r="B649" s="1" t="s">
         <v>1354</v>
       </c>
-      <c r="B649" s="1" t="s">
-        <v>1355</v>
-      </c>
       <c r="C649" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D649" s="1" t="s">
-        <v>1324</v>
+        <v>1323</v>
       </c>
       <c r="E649" s="1" t="s">
         <v>109</v>
@@ -17743,16 +17740,16 @@
     </row>
     <row r="650" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A650" s="1" t="s">
+        <v>1355</v>
+      </c>
+      <c r="B650" s="1" t="s">
         <v>1356</v>
       </c>
-      <c r="B650" s="1" t="s">
-        <v>1357</v>
-      </c>
       <c r="C650" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D650" s="1" t="s">
-        <v>1324</v>
+        <v>1323</v>
       </c>
       <c r="E650" s="1" t="s">
         <v>112</v>
@@ -17763,16 +17760,16 @@
     </row>
     <row r="651" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A651" s="1" t="s">
+        <v>1357</v>
+      </c>
+      <c r="B651" s="1" t="s">
         <v>1358</v>
       </c>
-      <c r="B651" s="1" t="s">
+      <c r="C651" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D651" s="1" t="s">
         <v>1359</v>
-      </c>
-      <c r="C651" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D651" s="1" t="s">
-        <v>1360</v>
       </c>
       <c r="E651" s="1" t="s">
         <v>4</v>
@@ -17783,16 +17780,16 @@
     </row>
     <row r="652" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A652" s="1" t="s">
+        <v>1360</v>
+      </c>
+      <c r="B652" s="1" t="s">
         <v>1361</v>
       </c>
-      <c r="B652" s="1" t="s">
-        <v>1362</v>
-      </c>
       <c r="C652" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D652" s="1" t="s">
-        <v>1360</v>
+        <v>1359</v>
       </c>
       <c r="E652" s="1" t="s">
         <v>8</v>
@@ -17803,16 +17800,16 @@
     </row>
     <row r="653" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A653" s="1" t="s">
+        <v>1362</v>
+      </c>
+      <c r="B653" s="1" t="s">
         <v>1363</v>
       </c>
-      <c r="B653" s="1" t="s">
-        <v>1364</v>
-      </c>
       <c r="C653" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D653" s="1" t="s">
-        <v>1360</v>
+        <v>1359</v>
       </c>
       <c r="E653" s="1" t="s">
         <v>12</v>
@@ -17823,16 +17820,16 @@
     </row>
     <row r="654" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A654" s="1" t="s">
+        <v>1364</v>
+      </c>
+      <c r="B654" s="1" t="s">
         <v>1365</v>
       </c>
-      <c r="B654" s="1" t="s">
-        <v>1366</v>
-      </c>
       <c r="C654" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D654" s="1" t="s">
-        <v>1360</v>
+        <v>1359</v>
       </c>
       <c r="E654" s="1" t="s">
         <v>15</v>
@@ -17843,16 +17840,16 @@
     </row>
     <row r="655" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A655" s="1" t="s">
+        <v>1366</v>
+      </c>
+      <c r="B655" s="1" t="s">
         <v>1367</v>
       </c>
-      <c r="B655" s="1" t="s">
-        <v>1368</v>
-      </c>
       <c r="C655" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D655" s="1" t="s">
-        <v>1360</v>
+        <v>1359</v>
       </c>
       <c r="E655" s="1" t="s">
         <v>18</v>
@@ -17863,16 +17860,16 @@
     </row>
     <row r="656" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A656" s="1" t="s">
+        <v>1368</v>
+      </c>
+      <c r="B656" s="1" t="s">
         <v>1369</v>
       </c>
-      <c r="B656" s="1" t="s">
-        <v>1370</v>
-      </c>
       <c r="C656" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D656" s="1" t="s">
-        <v>1360</v>
+        <v>1359</v>
       </c>
       <c r="E656" s="1" t="s">
         <v>21</v>
@@ -17883,16 +17880,16 @@
     </row>
     <row r="657" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A657" s="1" t="s">
+        <v>1370</v>
+      </c>
+      <c r="B657" s="1" t="s">
         <v>1371</v>
       </c>
-      <c r="B657" s="1" t="s">
-        <v>1372</v>
-      </c>
       <c r="C657" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D657" s="1" t="s">
-        <v>1360</v>
+        <v>1359</v>
       </c>
       <c r="E657" s="1" t="s">
         <v>24</v>
@@ -17903,16 +17900,16 @@
     </row>
     <row r="658" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A658" s="1" t="s">
+        <v>1372</v>
+      </c>
+      <c r="B658" s="1" t="s">
         <v>1373</v>
       </c>
-      <c r="B658" s="1" t="s">
-        <v>1374</v>
-      </c>
       <c r="C658" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D658" s="1" t="s">
-        <v>1360</v>
+        <v>1359</v>
       </c>
       <c r="E658" s="1" t="s">
         <v>28</v>
@@ -17923,16 +17920,16 @@
     </row>
     <row r="659" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A659" s="1" t="s">
+        <v>1374</v>
+      </c>
+      <c r="B659" s="1" t="s">
         <v>1375</v>
       </c>
-      <c r="B659" s="1" t="s">
-        <v>1376</v>
-      </c>
       <c r="C659" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D659" s="1" t="s">
-        <v>1360</v>
+        <v>1359</v>
       </c>
       <c r="E659" s="1" t="s">
         <v>31</v>
@@ -17943,16 +17940,16 @@
     </row>
     <row r="660" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A660" s="1" t="s">
+        <v>1376</v>
+      </c>
+      <c r="B660" s="1" t="s">
         <v>1377</v>
       </c>
-      <c r="B660" s="1" t="s">
-        <v>1378</v>
-      </c>
       <c r="C660" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D660" s="1" t="s">
-        <v>1360</v>
+        <v>1359</v>
       </c>
       <c r="E660" s="1" t="s">
         <v>34</v>
@@ -17963,16 +17960,16 @@
     </row>
     <row r="661" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A661" s="1" t="s">
+        <v>1378</v>
+      </c>
+      <c r="B661" s="1" t="s">
         <v>1379</v>
       </c>
-      <c r="B661" s="1" t="s">
-        <v>1380</v>
-      </c>
       <c r="C661" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D661" s="1" t="s">
-        <v>1360</v>
+        <v>1359</v>
       </c>
       <c r="E661" s="1" t="s">
         <v>37</v>
@@ -17983,16 +17980,16 @@
     </row>
     <row r="662" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A662" s="1" t="s">
+        <v>1380</v>
+      </c>
+      <c r="B662" s="1" t="s">
         <v>1381</v>
       </c>
-      <c r="B662" s="1" t="s">
-        <v>1382</v>
-      </c>
       <c r="C662" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D662" s="1" t="s">
-        <v>1360</v>
+        <v>1359</v>
       </c>
       <c r="E662" s="1" t="s">
         <v>40</v>
@@ -18003,16 +18000,16 @@
     </row>
     <row r="663" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A663" s="1" t="s">
+        <v>1382</v>
+      </c>
+      <c r="B663" s="1" t="s">
         <v>1383</v>
       </c>
-      <c r="B663" s="1" t="s">
-        <v>1384</v>
-      </c>
       <c r="C663" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D663" s="1" t="s">
-        <v>1360</v>
+        <v>1359</v>
       </c>
       <c r="E663" s="1" t="s">
         <v>68</v>
@@ -18023,16 +18020,16 @@
     </row>
     <row r="664" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A664" s="1" t="s">
+        <v>1384</v>
+      </c>
+      <c r="B664" s="1" t="s">
         <v>1385</v>
       </c>
-      <c r="B664" s="1" t="s">
-        <v>1386</v>
-      </c>
       <c r="C664" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D664" s="1" t="s">
-        <v>1360</v>
+        <v>1359</v>
       </c>
       <c r="E664" s="1" t="s">
         <v>100</v>
@@ -18043,156 +18040,156 @@
     </row>
     <row r="665" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A665" s="1" t="s">
+        <v>1386</v>
+      </c>
+      <c r="B665" s="1" t="s">
         <v>1387</v>
       </c>
-      <c r="B665" s="1" t="s">
+      <c r="C665" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D665" s="1" t="s">
         <v>1388</v>
-      </c>
-      <c r="C665" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D665" s="1" t="s">
-        <v>1389</v>
       </c>
       <c r="E665" s="1" t="s">
         <v>4</v>
       </c>
       <c r="F665" s="1" t="s">
-        <v>1390</v>
+        <v>1389</v>
       </c>
     </row>
     <row r="666" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A666" s="1" t="s">
+        <v>1390</v>
+      </c>
+      <c r="B666" s="1" t="s">
         <v>1391</v>
       </c>
-      <c r="B666" s="1" t="s">
-        <v>1392</v>
-      </c>
       <c r="C666" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D666" s="1" t="s">
-        <v>1389</v>
+        <v>1388</v>
       </c>
       <c r="E666" s="1" t="s">
         <v>8</v>
       </c>
       <c r="F666" s="1" t="s">
-        <v>1390</v>
+        <v>1389</v>
       </c>
     </row>
     <row r="667" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A667" s="1" t="s">
+        <v>1392</v>
+      </c>
+      <c r="B667" s="1" t="s">
         <v>1393</v>
       </c>
-      <c r="B667" s="1" t="s">
-        <v>1394</v>
-      </c>
       <c r="C667" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D667" s="1" t="s">
-        <v>1389</v>
+        <v>1388</v>
       </c>
       <c r="E667" s="1" t="s">
         <v>12</v>
       </c>
       <c r="F667" s="1" t="s">
-        <v>1390</v>
+        <v>1389</v>
       </c>
     </row>
     <row r="668" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A668" s="1" t="s">
+        <v>1394</v>
+      </c>
+      <c r="B668" s="1" t="s">
         <v>1395</v>
       </c>
-      <c r="B668" s="1" t="s">
-        <v>1396</v>
-      </c>
       <c r="C668" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D668" s="1" t="s">
-        <v>1389</v>
+        <v>1388</v>
       </c>
       <c r="E668" s="1" t="s">
         <v>15</v>
       </c>
       <c r="F668" s="1" t="s">
-        <v>1390</v>
+        <v>1389</v>
       </c>
     </row>
     <row r="669" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A669" s="1" t="s">
+        <v>1396</v>
+      </c>
+      <c r="B669" s="1" t="s">
         <v>1397</v>
       </c>
-      <c r="B669" s="1" t="s">
-        <v>1398</v>
-      </c>
       <c r="C669" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D669" s="1" t="s">
-        <v>1389</v>
+        <v>1388</v>
       </c>
       <c r="E669" s="1" t="s">
         <v>18</v>
       </c>
       <c r="F669" s="1" t="s">
-        <v>1390</v>
+        <v>1389</v>
       </c>
     </row>
     <row r="670" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A670" s="1" t="s">
+        <v>1398</v>
+      </c>
+      <c r="B670" s="1" t="s">
         <v>1399</v>
       </c>
-      <c r="B670" s="1" t="s">
-        <v>1400</v>
-      </c>
       <c r="C670" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D670" s="1" t="s">
-        <v>1389</v>
+        <v>1388</v>
       </c>
       <c r="E670" s="1" t="s">
         <v>21</v>
       </c>
       <c r="F670" s="1" t="s">
-        <v>1390</v>
+        <v>1389</v>
       </c>
     </row>
     <row r="671" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A671" s="1" t="s">
+        <v>1400</v>
+      </c>
+      <c r="B671" s="1" t="s">
         <v>1401</v>
       </c>
-      <c r="B671" s="1" t="s">
-        <v>1402</v>
-      </c>
       <c r="C671" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D671" s="1" t="s">
-        <v>1389</v>
+        <v>1388</v>
       </c>
       <c r="E671" s="1" t="s">
         <v>24</v>
       </c>
       <c r="F671" s="1" t="s">
-        <v>1390</v>
+        <v>1389</v>
       </c>
     </row>
     <row r="672" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A672" s="1" t="s">
+        <v>1402</v>
+      </c>
+      <c r="B672" s="1" t="s">
         <v>1403</v>
       </c>
-      <c r="B672" s="1" t="s">
-        <v>1404</v>
-      </c>
       <c r="C672" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D672" s="1" t="s">
-        <v>1389</v>
+        <v>1388</v>
       </c>
       <c r="E672" s="1" t="s">
         <v>28</v>
@@ -18203,16 +18200,16 @@
     </row>
     <row r="673" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A673" s="1" t="s">
+        <v>1404</v>
+      </c>
+      <c r="B673" s="1" t="s">
         <v>1405</v>
       </c>
-      <c r="B673" s="1" t="s">
-        <v>1406</v>
-      </c>
       <c r="C673" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D673" s="1" t="s">
-        <v>1389</v>
+        <v>1388</v>
       </c>
       <c r="E673" s="1" t="s">
         <v>31</v>
@@ -18223,96 +18220,96 @@
     </row>
     <row r="674" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A674" s="1" t="s">
+        <v>1406</v>
+      </c>
+      <c r="B674" s="1" t="s">
         <v>1407</v>
       </c>
-      <c r="B674" s="1" t="s">
-        <v>1408</v>
-      </c>
       <c r="C674" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D674" s="1" t="s">
-        <v>1389</v>
+        <v>1388</v>
       </c>
       <c r="E674" s="1" t="s">
         <v>34</v>
       </c>
       <c r="F674" s="1" t="s">
-        <v>1390</v>
+        <v>1389</v>
       </c>
     </row>
     <row r="675" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A675" s="1" t="s">
+        <v>1408</v>
+      </c>
+      <c r="B675" s="1" t="s">
         <v>1409</v>
       </c>
-      <c r="B675" s="1" t="s">
-        <v>1410</v>
-      </c>
       <c r="C675" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D675" s="1" t="s">
-        <v>1389</v>
+        <v>1388</v>
       </c>
       <c r="E675" s="1" t="s">
         <v>34</v>
       </c>
       <c r="F675" s="1" t="s">
-        <v>1390</v>
+        <v>1389</v>
       </c>
     </row>
     <row r="676" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A676" s="1" t="s">
+        <v>1410</v>
+      </c>
+      <c r="B676" s="1" t="s">
         <v>1411</v>
       </c>
-      <c r="B676" s="1" t="s">
-        <v>1412</v>
-      </c>
       <c r="C676" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D676" s="1" t="s">
-        <v>1389</v>
+        <v>1388</v>
       </c>
       <c r="E676" s="1" t="s">
         <v>37</v>
       </c>
       <c r="F676" s="1" t="s">
-        <v>1390</v>
+        <v>1389</v>
       </c>
     </row>
     <row r="677" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A677" s="1" t="s">
+        <v>1412</v>
+      </c>
+      <c r="B677" s="1" t="s">
         <v>1413</v>
       </c>
-      <c r="B677" s="1" t="s">
-        <v>1414</v>
-      </c>
       <c r="C677" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D677" s="1" t="s">
-        <v>1389</v>
+        <v>1388</v>
       </c>
       <c r="E677" s="1" t="s">
         <v>37</v>
       </c>
       <c r="F677" s="1" t="s">
-        <v>1390</v>
+        <v>1389</v>
       </c>
     </row>
     <row r="678" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A678" s="1" t="s">
+        <v>1414</v>
+      </c>
+      <c r="B678" s="1" t="s">
         <v>1415</v>
       </c>
-      <c r="B678" s="1" t="s">
-        <v>1416</v>
-      </c>
       <c r="C678" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D678" s="1" t="s">
-        <v>1389</v>
+        <v>1388</v>
       </c>
       <c r="E678" s="1" t="s">
         <v>40</v>
@@ -18323,36 +18320,36 @@
     </row>
     <row r="679" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A679" s="1" t="s">
+        <v>1416</v>
+      </c>
+      <c r="B679" s="1" t="s">
         <v>1417</v>
       </c>
-      <c r="B679" s="1" t="s">
-        <v>1418</v>
-      </c>
       <c r="C679" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D679" s="1" t="s">
-        <v>1389</v>
+        <v>1388</v>
       </c>
       <c r="E679" s="1" t="s">
         <v>68</v>
       </c>
       <c r="F679" s="1" t="s">
-        <v>1390</v>
+        <v>1389</v>
       </c>
     </row>
     <row r="680" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A680" s="1" t="s">
+        <v>1418</v>
+      </c>
+      <c r="B680" s="1" t="s">
         <v>1419</v>
       </c>
-      <c r="B680" s="1" t="s">
+      <c r="C680" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D680" s="1" t="s">
         <v>1420</v>
-      </c>
-      <c r="C680" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D680" s="1" t="s">
-        <v>1421</v>
       </c>
       <c r="E680" s="1" t="s">
         <v>4</v>
@@ -18363,16 +18360,16 @@
     </row>
     <row r="681" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A681" s="1" t="s">
+        <v>1421</v>
+      </c>
+      <c r="B681" s="1" t="s">
         <v>1422</v>
       </c>
-      <c r="B681" s="1" t="s">
-        <v>1423</v>
-      </c>
       <c r="C681" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D681" s="1" t="s">
-        <v>1421</v>
+        <v>1420</v>
       </c>
       <c r="E681" s="1" t="s">
         <v>8</v>
@@ -18383,16 +18380,16 @@
     </row>
     <row r="682" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A682" s="1" t="s">
+        <v>1423</v>
+      </c>
+      <c r="B682" s="1" t="s">
         <v>1424</v>
       </c>
-      <c r="B682" s="1" t="s">
-        <v>1425</v>
-      </c>
       <c r="C682" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D682" s="1" t="s">
-        <v>1421</v>
+        <v>1420</v>
       </c>
       <c r="E682" s="1" t="s">
         <v>12</v>
@@ -18403,16 +18400,16 @@
     </row>
     <row r="683" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A683" s="1" t="s">
+        <v>1425</v>
+      </c>
+      <c r="B683" s="1" t="s">
         <v>1426</v>
       </c>
-      <c r="B683" s="1" t="s">
-        <v>1427</v>
-      </c>
       <c r="C683" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D683" s="1" t="s">
-        <v>1421</v>
+        <v>1420</v>
       </c>
       <c r="E683" s="1" t="s">
         <v>15</v>
@@ -18423,16 +18420,16 @@
     </row>
     <row r="684" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A684" s="1" t="s">
+        <v>1427</v>
+      </c>
+      <c r="B684" s="1" t="s">
         <v>1428</v>
       </c>
-      <c r="B684" s="1" t="s">
-        <v>1429</v>
-      </c>
       <c r="C684" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D684" s="1" t="s">
-        <v>1421</v>
+        <v>1420</v>
       </c>
       <c r="E684" s="1" t="s">
         <v>18</v>
@@ -18443,16 +18440,16 @@
     </row>
     <row r="685" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A685" s="1" t="s">
+        <v>1429</v>
+      </c>
+      <c r="B685" s="1" t="s">
         <v>1430</v>
       </c>
-      <c r="B685" s="1" t="s">
-        <v>1431</v>
-      </c>
       <c r="C685" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D685" s="1" t="s">
-        <v>1421</v>
+        <v>1420</v>
       </c>
       <c r="E685" s="1" t="s">
         <v>21</v>
@@ -18463,16 +18460,16 @@
     </row>
     <row r="686" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A686" s="1" t="s">
+        <v>1431</v>
+      </c>
+      <c r="B686" s="1" t="s">
         <v>1432</v>
       </c>
-      <c r="B686" s="1" t="s">
-        <v>1433</v>
-      </c>
       <c r="C686" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D686" s="1" t="s">
-        <v>1421</v>
+        <v>1420</v>
       </c>
       <c r="E686" s="1" t="s">
         <v>24</v>
@@ -18483,16 +18480,16 @@
     </row>
     <row r="687" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A687" s="1" t="s">
+        <v>1433</v>
+      </c>
+      <c r="B687" s="1" t="s">
         <v>1434</v>
       </c>
-      <c r="B687" s="1" t="s">
-        <v>1435</v>
-      </c>
       <c r="C687" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D687" s="1" t="s">
-        <v>1421</v>
+        <v>1420</v>
       </c>
       <c r="E687" s="1" t="s">
         <v>28</v>
@@ -18503,16 +18500,16 @@
     </row>
     <row r="688" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A688" s="1" t="s">
+        <v>1435</v>
+      </c>
+      <c r="B688" s="1" t="s">
         <v>1436</v>
       </c>
-      <c r="B688" s="1" t="s">
-        <v>1437</v>
-      </c>
       <c r="C688" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D688" s="1" t="s">
-        <v>1421</v>
+        <v>1420</v>
       </c>
       <c r="E688" s="1" t="s">
         <v>31</v>
@@ -18523,16 +18520,16 @@
     </row>
     <row r="689" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A689" s="1" t="s">
+        <v>1437</v>
+      </c>
+      <c r="B689" s="1" t="s">
         <v>1438</v>
       </c>
-      <c r="B689" s="1" t="s">
-        <v>1439</v>
-      </c>
       <c r="C689" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D689" s="1" t="s">
-        <v>1421</v>
+        <v>1420</v>
       </c>
       <c r="E689" s="1" t="s">
         <v>34</v>
@@ -18543,16 +18540,16 @@
     </row>
     <row r="690" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A690" s="1" t="s">
+        <v>1439</v>
+      </c>
+      <c r="B690" s="1" t="s">
         <v>1440</v>
       </c>
-      <c r="B690" s="1" t="s">
-        <v>1441</v>
-      </c>
       <c r="C690" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D690" s="1" t="s">
-        <v>1421</v>
+        <v>1420</v>
       </c>
       <c r="E690" s="1" t="s">
         <v>37</v>
@@ -18563,16 +18560,16 @@
     </row>
     <row r="691" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A691" s="1" t="s">
+        <v>1441</v>
+      </c>
+      <c r="B691" s="1" t="s">
         <v>1442</v>
       </c>
-      <c r="B691" s="1" t="s">
-        <v>1443</v>
-      </c>
       <c r="C691" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D691" s="1" t="s">
-        <v>1421</v>
+        <v>1420</v>
       </c>
       <c r="E691" s="1" t="s">
         <v>40</v>
@@ -18583,16 +18580,16 @@
     </row>
     <row r="692" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A692" s="1" t="s">
+        <v>1443</v>
+      </c>
+      <c r="B692" s="1" t="s">
         <v>1444</v>
       </c>
-      <c r="B692" s="1" t="s">
+      <c r="C692" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D692" s="1" t="s">
         <v>1445</v>
-      </c>
-      <c r="C692" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D692" s="1" t="s">
-        <v>1446</v>
       </c>
       <c r="E692" s="1" t="s">
         <v>8</v>
@@ -18603,16 +18600,16 @@
     </row>
     <row r="693" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A693" s="1" t="s">
+        <v>1446</v>
+      </c>
+      <c r="B693" s="1" t="s">
         <v>1447</v>
       </c>
-      <c r="B693" s="1" t="s">
-        <v>1448</v>
-      </c>
       <c r="C693" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D693" s="1" t="s">
-        <v>1446</v>
+        <v>1445</v>
       </c>
       <c r="E693" s="1" t="s">
         <v>12</v>

--- a/PCE06D.xlsx
+++ b/PCE06D.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4098" uniqueCount="1428">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4068" uniqueCount="1418">
   <si>
     <t/>
   </si>
@@ -682,12 +682,6 @@
     <t>PEPSODENT PG FIFA95</t>
   </si>
   <si>
-    <t>20024922</t>
-  </si>
-  <si>
-    <t>ORAL B SG RND 123 3M</t>
-  </si>
-  <si>
     <t>20067198</t>
   </si>
   <si>
@@ -751,91 +745,313 @@
     <t>CPTDNT SG DM.C/SF 3S</t>
   </si>
   <si>
-    <t>20131631</t>
-  </si>
-  <si>
-    <t>ORAL B SG S&amp;S U/LMBT</t>
-  </si>
-  <si>
-    <t>20037986</t>
-  </si>
-  <si>
-    <t>ORAL B M-THN CLN E/S</t>
+    <t>20129309</t>
+  </si>
+  <si>
+    <t>FORMULA SG MAXI SF3S</t>
+  </si>
+  <si>
+    <t>20075742</t>
+  </si>
+  <si>
+    <t>PPSODENT SG SL.CHAR</t>
+  </si>
+  <si>
+    <t>10026612</t>
+  </si>
+  <si>
+    <t>PPSODENT SG SENSI SF</t>
+  </si>
+  <si>
+    <t>20036082</t>
+  </si>
+  <si>
+    <t>P/SODENT S/G SENS2+1</t>
+  </si>
+  <si>
+    <t>20139778</t>
+  </si>
+  <si>
+    <t>SYSTEMA SG NINE.D 3S</t>
+  </si>
+  <si>
+    <t>20096495</t>
+  </si>
+  <si>
+    <t>SNSODYN SG SNSTV 2 S</t>
+  </si>
+  <si>
+    <t>20051952</t>
+  </si>
+  <si>
+    <t>FRMULA S/G PP N/C SF</t>
+  </si>
+  <si>
+    <t>10032483</t>
+  </si>
+  <si>
+    <t>FORMULA S/G P.PRO SF</t>
+  </si>
+  <si>
+    <t>20119092</t>
+  </si>
+  <si>
+    <t>PSODENT SG SIWAK 2'S</t>
+  </si>
+  <si>
+    <t>20136689</t>
+  </si>
+  <si>
+    <t>PSODENT SG G.CARE 3S</t>
+  </si>
+  <si>
+    <t>20137410</t>
+  </si>
+  <si>
+    <t>CLS.UP SG PR.CLN 2S</t>
+  </si>
+  <si>
+    <t>20022015</t>
+  </si>
+  <si>
+    <t>FORMULA EX.CLEAN 3'S</t>
+  </si>
+  <si>
+    <t>20115976</t>
+  </si>
+  <si>
+    <t>CPTADENT SG PRFCT 3S</t>
+  </si>
+  <si>
+    <t>20023627</t>
+  </si>
+  <si>
+    <t>REJOICE SHP.RICH 340</t>
   </si>
   <si>
     <t>PT,(E-5B)</t>
   </si>
   <si>
-    <t>20075742</t>
-  </si>
-  <si>
-    <t>PPSODENT SG SL.CHAR</t>
-  </si>
-  <si>
-    <t>10026612</t>
-  </si>
-  <si>
-    <t>PPSODENT SG SENSI SF</t>
-  </si>
-  <si>
-    <t>20036082</t>
-  </si>
-  <si>
-    <t>P/SODENT S/G SENS2+1</t>
-  </si>
-  <si>
-    <t>20139778</t>
-  </si>
-  <si>
-    <t>SYSTEMA SG NINE.D 3S</t>
-  </si>
-  <si>
-    <t>20096495</t>
-  </si>
-  <si>
-    <t>SNSODYN SG SNSTV 2 S</t>
-  </si>
-  <si>
-    <t>20051952</t>
-  </si>
-  <si>
-    <t>FRMULA S/G PP N/C SF</t>
-  </si>
-  <si>
-    <t>10032483</t>
-  </si>
-  <si>
-    <t>FORMULA S/G P.PRO SF</t>
-  </si>
-  <si>
-    <t>20119092</t>
-  </si>
-  <si>
-    <t>PSODENT SG SIWAK 2'S</t>
-  </si>
-  <si>
-    <t>20136689</t>
-  </si>
-  <si>
-    <t>PSODENT SG G.CARE 3S</t>
-  </si>
-  <si>
-    <t>20137410</t>
-  </si>
-  <si>
-    <t>CLS.UP SG PR.CLN 2S</t>
-  </si>
-  <si>
-    <t>20022015</t>
-  </si>
-  <si>
-    <t>FORMULA EX.CLEAN 3'S</t>
-  </si>
-  <si>
-    <t>20115976</t>
-  </si>
-  <si>
-    <t>CPTADENT SG PRFCT 3S</t>
+    <t>20133332</t>
+  </si>
+  <si>
+    <t>ZINC REFRSH COOL 450</t>
+  </si>
+  <si>
+    <t>20099181</t>
+  </si>
+  <si>
+    <t>ZINC REFRSH COOL 340</t>
+  </si>
+  <si>
+    <t>20131028</t>
+  </si>
+  <si>
+    <t>ZINC SHP LMN MINT340</t>
+  </si>
+  <si>
+    <t>20141072</t>
+  </si>
+  <si>
+    <t>H&amp;S SHP SPR.COOL 300</t>
+  </si>
+  <si>
+    <t>20139706</t>
+  </si>
+  <si>
+    <t>H&amp;S 2IN1 MNTHL 300</t>
+  </si>
+  <si>
+    <t>20010383</t>
+  </si>
+  <si>
+    <t>LIFEBUOY SHP A/D 340</t>
+  </si>
+  <si>
+    <t>20138903</t>
+  </si>
+  <si>
+    <t>SNSLK SHP G.BLCK 320</t>
+  </si>
+  <si>
+    <t>20138902</t>
+  </si>
+  <si>
+    <t>SNSLK SHP S.SMTH 320</t>
+  </si>
+  <si>
+    <t>10003336</t>
+  </si>
+  <si>
+    <t>EMERON SHP BLK&amp;S 170</t>
+  </si>
+  <si>
+    <t>10003337</t>
+  </si>
+  <si>
+    <t>EMERON SHP H/F CN170</t>
+  </si>
+  <si>
+    <t>20091271</t>
+  </si>
+  <si>
+    <t>EMRN SHP HJB C&amp;F 170</t>
+  </si>
+  <si>
+    <t>20138898</t>
+  </si>
+  <si>
+    <t>SNSLK SHP S.SMTH 160</t>
+  </si>
+  <si>
+    <t>20140086</t>
+  </si>
+  <si>
+    <t>SUNSLK COND S.SM 160</t>
+  </si>
+  <si>
+    <t>20138899</t>
+  </si>
+  <si>
+    <t>SNSLK SHP G.BLCK 160</t>
+  </si>
+  <si>
+    <t>20138900</t>
+  </si>
+  <si>
+    <t>SNSLK SHP AD</t>
+  </si>
+  <si>
+    <t>20067359</t>
+  </si>
+  <si>
+    <t>SUNSLK SHP HJB RE160</t>
+  </si>
+  <si>
+    <t>20030118</t>
+  </si>
+  <si>
+    <t>REJOICE SHP 3IN1 150</t>
+  </si>
+  <si>
+    <t>20033003</t>
+  </si>
+  <si>
+    <t>REJOICE CND RICH 150</t>
+  </si>
+  <si>
+    <t>10019725</t>
+  </si>
+  <si>
+    <t>REJOICE SHP RICH 150</t>
+  </si>
+  <si>
+    <t>20140224</t>
+  </si>
+  <si>
+    <t>LOREAL SHP G.GLS 200</t>
+  </si>
+  <si>
+    <t>20140225</t>
+  </si>
+  <si>
+    <t>LOREAL CND G.GLS 175</t>
+  </si>
+  <si>
+    <t>20140223</t>
+  </si>
+  <si>
+    <t>LOREAL SHP F.R3X 200</t>
+  </si>
+  <si>
+    <t>20091347</t>
+  </si>
+  <si>
+    <t>TRESEMME SHP KS 170</t>
+  </si>
+  <si>
+    <t>10004513</t>
+  </si>
+  <si>
+    <t>NATUR P/RMB RNTK 140</t>
+  </si>
+  <si>
+    <t>20138649</t>
+  </si>
+  <si>
+    <t>EMRN SHP BT21 AK 340</t>
+  </si>
+  <si>
+    <t>20038766</t>
+  </si>
+  <si>
+    <t>PANTENE SHP HFC 160</t>
+  </si>
+  <si>
+    <t>20038758</t>
+  </si>
+  <si>
+    <t>PANTENE CND HFC 160</t>
+  </si>
+  <si>
+    <t>20038763</t>
+  </si>
+  <si>
+    <t>PNTENE SHP ANT/D 160</t>
+  </si>
+  <si>
+    <t>20038770</t>
+  </si>
+  <si>
+    <t>PNTENE SHP SM.CR 160</t>
+  </si>
+  <si>
+    <t>20038986</t>
+  </si>
+  <si>
+    <t>PNTENE SHP LG BLK160</t>
+  </si>
+  <si>
+    <t>20134589</t>
+  </si>
+  <si>
+    <t>PANTENE SHP HFC 110</t>
+  </si>
+  <si>
+    <t>20134590</t>
+  </si>
+  <si>
+    <t>PNTENE SHP A/DAN 110</t>
+  </si>
+  <si>
+    <t>20075945</t>
+  </si>
+  <si>
+    <t>MR HR ENG RYL JL 170</t>
+  </si>
+  <si>
+    <t>20075943</t>
+  </si>
+  <si>
+    <t>MKRZO SHP ALOE&amp;M 170</t>
+  </si>
+  <si>
+    <t>20082206</t>
+  </si>
+  <si>
+    <t>SERASOFT SHP DT 170</t>
+  </si>
+  <si>
+    <t>20082205</t>
+  </si>
+  <si>
+    <t>SERASOFT SHP HFT 170</t>
+  </si>
+  <si>
+    <t>20135632</t>
+  </si>
+  <si>
+    <t>SERASOFT SHP SMTH170</t>
   </si>
   <si>
     <t>20127437</t>
@@ -844,154 +1060,190 @@
     <t>SERASOFT SHP HFT 340</t>
   </si>
   <si>
-    <t>20023627</t>
-  </si>
-  <si>
-    <t>REJOICE SHP.RICH 340</t>
-  </si>
-  <si>
-    <t>20133332</t>
-  </si>
-  <si>
-    <t>ZINC REFRSH COOL 450</t>
-  </si>
-  <si>
-    <t>20099181</t>
-  </si>
-  <si>
-    <t>ZINC REFRSH COOL 340</t>
-  </si>
-  <si>
-    <t>20131028</t>
-  </si>
-  <si>
-    <t>ZINC SHP LMN MINT340</t>
-  </si>
-  <si>
-    <t>20141072</t>
-  </si>
-  <si>
-    <t>H&amp;S SHP SPR.COOL 300</t>
-  </si>
-  <si>
-    <t>20139706</t>
-  </si>
-  <si>
-    <t>H&amp;S 2IN1 MNTHL 300</t>
-  </si>
-  <si>
-    <t>20010383</t>
-  </si>
-  <si>
-    <t>LIFEBUOY SHP A/D 340</t>
-  </si>
-  <si>
-    <t>20138903</t>
-  </si>
-  <si>
-    <t>SNSLK SHP G.BLCK 320</t>
-  </si>
-  <si>
-    <t>20138902</t>
-  </si>
-  <si>
-    <t>SNSLK SHP S.SMTH 320</t>
-  </si>
-  <si>
-    <t>10003336</t>
-  </si>
-  <si>
-    <t>EMERON SHP BLK&amp;S 170</t>
-  </si>
-  <si>
-    <t>10003337</t>
-  </si>
-  <si>
-    <t>EMERON SHP H/F CN170</t>
-  </si>
-  <si>
-    <t>20091271</t>
-  </si>
-  <si>
-    <t>EMRN SHP HJB C&amp;F 170</t>
-  </si>
-  <si>
-    <t>20138898</t>
-  </si>
-  <si>
-    <t>SNSLK SHP S.SMTH 160</t>
-  </si>
-  <si>
-    <t>20140086</t>
-  </si>
-  <si>
-    <t>SUNSLK COND S.SM 160</t>
-  </si>
-  <si>
-    <t>20138899</t>
-  </si>
-  <si>
-    <t>SNSLK SHP G.BLCK 160</t>
-  </si>
-  <si>
-    <t>20138900</t>
-  </si>
-  <si>
-    <t>SNSLK SHP AD</t>
-  </si>
-  <si>
-    <t>20067359</t>
-  </si>
-  <si>
-    <t>SUNSLK SHP HJB RE160</t>
-  </si>
-  <si>
-    <t>20030118</t>
-  </si>
-  <si>
-    <t>REJOICE SHP 3IN1 150</t>
-  </si>
-  <si>
-    <t>20033003</t>
-  </si>
-  <si>
-    <t>REJOICE CND RICH 150</t>
-  </si>
-  <si>
-    <t>10019725</t>
-  </si>
-  <si>
-    <t>REJOICE SHP RICH 150</t>
-  </si>
-  <si>
-    <t>20140224</t>
-  </si>
-  <si>
-    <t>LOREAL SHP G.GLS 200</t>
-  </si>
-  <si>
-    <t>20140225</t>
-  </si>
-  <si>
-    <t>LOREAL CND G.GLS 175</t>
-  </si>
-  <si>
-    <t>20140223</t>
-  </si>
-  <si>
-    <t>LOREAL SHP F.R3X 200</t>
-  </si>
-  <si>
-    <t>20091347</t>
-  </si>
-  <si>
-    <t>TRESEMME SHP KS 170</t>
-  </si>
-  <si>
-    <t>20138649</t>
-  </si>
-  <si>
-    <t>EMRN SHP BT21 AK 340</t>
+    <t>20139083</t>
+  </si>
+  <si>
+    <t>H&amp;S SHP MNTHL 110ML</t>
+  </si>
+  <si>
+    <t>20136586</t>
+  </si>
+  <si>
+    <t>H&amp;S 2IN1 MNTHL 160</t>
+  </si>
+  <si>
+    <t>10011850</t>
+  </si>
+  <si>
+    <t>H&amp;S SHP MNT DNGN 160</t>
+  </si>
+  <si>
+    <t>20049799</t>
+  </si>
+  <si>
+    <t>H&amp;S SHP LMON FRS 160</t>
+  </si>
+  <si>
+    <t>20138023</t>
+  </si>
+  <si>
+    <t>H&amp;S 2IN1 SUTERA 160</t>
+  </si>
+  <si>
+    <t>20118299</t>
+  </si>
+  <si>
+    <t>H&amp;S SHP SPRM A.HF135</t>
+  </si>
+  <si>
+    <t>10011851</t>
+  </si>
+  <si>
+    <t>H&amp;S A/D SMTH&amp;SLK 160</t>
+  </si>
+  <si>
+    <t>20103818</t>
+  </si>
+  <si>
+    <t>H&amp;S SHP SUB ZERO 160</t>
+  </si>
+  <si>
+    <t>20091441</t>
+  </si>
+  <si>
+    <t>CLEAR SHP KOMPLIT160</t>
+  </si>
+  <si>
+    <t>20091440</t>
+  </si>
+  <si>
+    <t>CLEAR SHP MENTHOL160</t>
+  </si>
+  <si>
+    <t>20132698</t>
+  </si>
+  <si>
+    <t>CLEAR SHP AK&amp;RNTK160</t>
+  </si>
+  <si>
+    <t>20040608</t>
+  </si>
+  <si>
+    <t>ZINC SHP HFT GNSG170</t>
+  </si>
+  <si>
+    <t>20040609</t>
+  </si>
+  <si>
+    <t>ZINC RE-FRSH COOL170</t>
+  </si>
+  <si>
+    <t>20109265</t>
+  </si>
+  <si>
+    <t>ZINC SHP LMN MINT170</t>
+  </si>
+  <si>
+    <t>20136708</t>
+  </si>
+  <si>
+    <t>ZINC SHP COOL.BS 170</t>
+  </si>
+  <si>
+    <t>20118252</t>
+  </si>
+  <si>
+    <t>PTNE COLLAGEN COND70</t>
+  </si>
+  <si>
+    <t>20118290</t>
+  </si>
+  <si>
+    <t>PTNE BIOTIN S COND70</t>
+  </si>
+  <si>
+    <t>10000632</t>
+  </si>
+  <si>
+    <t>MR. HAIR TONIC 175ML</t>
+  </si>
+  <si>
+    <t>20075951</t>
+  </si>
+  <si>
+    <t>MKRZO HES MR.DEW 100</t>
+  </si>
+  <si>
+    <t>20078998</t>
+  </si>
+  <si>
+    <t>MKRZO SCNT WHT MS100</t>
+  </si>
+  <si>
+    <t>20129466</t>
+  </si>
+  <si>
+    <t>MKRZO SCNT AMB WD100</t>
+  </si>
+  <si>
+    <t>20058061</t>
+  </si>
+  <si>
+    <t>MKRZO SCNT CHR/B 100</t>
+  </si>
+  <si>
+    <t>20131993</t>
+  </si>
+  <si>
+    <t>ELLIPS VIT.HM F&amp;S100</t>
+  </si>
+  <si>
+    <t>20128430</t>
+  </si>
+  <si>
+    <t>ELLIPS VIT.HM S&amp;S100</t>
+  </si>
+  <si>
+    <t>20136299</t>
+  </si>
+  <si>
+    <t>SUNSLK HR PRFM 100ML</t>
+  </si>
+  <si>
+    <t>20139069</t>
+  </si>
+  <si>
+    <t>SNSLK SHP GL.BLCK 70</t>
+  </si>
+  <si>
+    <t>20038765</t>
+  </si>
+  <si>
+    <t>PANTENE SHP ANT/D 70</t>
+  </si>
+  <si>
+    <t>20010379</t>
+  </si>
+  <si>
+    <t>LIFEBUOY SHP A/D 70</t>
+  </si>
+  <si>
+    <t>20091437</t>
+  </si>
+  <si>
+    <t>CLEAR SHP MENTHOL 70</t>
+  </si>
+  <si>
+    <t>20036191</t>
+  </si>
+  <si>
+    <t>H&amp;S SHP.MN/DINGIN 70</t>
+  </si>
+  <si>
+    <t>20140792</t>
+  </si>
+  <si>
+    <t>DOVE MCLAR SHP 150ML</t>
   </si>
   <si>
     <t>20028001</t>
@@ -1006,276 +1258,6 @@
     <t>LIFEBUOY SHP A/D 170</t>
   </si>
   <si>
-    <t>20038766</t>
-  </si>
-  <si>
-    <t>PANTENE SHP HFC 160</t>
-  </si>
-  <si>
-    <t>20038758</t>
-  </si>
-  <si>
-    <t>PANTENE CND HFC 160</t>
-  </si>
-  <si>
-    <t>20038763</t>
-  </si>
-  <si>
-    <t>PNTENE SHP ANT/D 160</t>
-  </si>
-  <si>
-    <t>20038770</t>
-  </si>
-  <si>
-    <t>PNTENE SHP SM.CR 160</t>
-  </si>
-  <si>
-    <t>20038986</t>
-  </si>
-  <si>
-    <t>PNTENE SHP LG BLK160</t>
-  </si>
-  <si>
-    <t>20134589</t>
-  </si>
-  <si>
-    <t>PANTENE SHP HFC 110</t>
-  </si>
-  <si>
-    <t>20134590</t>
-  </si>
-  <si>
-    <t>PNTENE SHP A/DAN 110</t>
-  </si>
-  <si>
-    <t>20075945</t>
-  </si>
-  <si>
-    <t>MR HR ENG RYL JL 170</t>
-  </si>
-  <si>
-    <t>20075943</t>
-  </si>
-  <si>
-    <t>MKRZO SHP ALOE&amp;M 170</t>
-  </si>
-  <si>
-    <t>20082206</t>
-  </si>
-  <si>
-    <t>SERASOFT SHP DT 170</t>
-  </si>
-  <si>
-    <t>20082205</t>
-  </si>
-  <si>
-    <t>SERASOFT SHP HFT 170</t>
-  </si>
-  <si>
-    <t>20135632</t>
-  </si>
-  <si>
-    <t>SERASOFT SHP SMTH170</t>
-  </si>
-  <si>
-    <t>20139083</t>
-  </si>
-  <si>
-    <t>H&amp;S SHP MNTHL 110ML</t>
-  </si>
-  <si>
-    <t>20136586</t>
-  </si>
-  <si>
-    <t>H&amp;S 2IN1 MNTHL 160</t>
-  </si>
-  <si>
-    <t>10011850</t>
-  </si>
-  <si>
-    <t>H&amp;S SHP MNT DNGN 160</t>
-  </si>
-  <si>
-    <t>20049799</t>
-  </si>
-  <si>
-    <t>H&amp;S SHP LMON FRS 160</t>
-  </si>
-  <si>
-    <t>20138023</t>
-  </si>
-  <si>
-    <t>H&amp;S 2IN1 SUTERA 160</t>
-  </si>
-  <si>
-    <t>20118299</t>
-  </si>
-  <si>
-    <t>H&amp;S SHP SPRM A.HF135</t>
-  </si>
-  <si>
-    <t>10011851</t>
-  </si>
-  <si>
-    <t>H&amp;S A/D SMTH&amp;SLK 160</t>
-  </si>
-  <si>
-    <t>20103818</t>
-  </si>
-  <si>
-    <t>H&amp;S SHP SUB ZERO 160</t>
-  </si>
-  <si>
-    <t>20091441</t>
-  </si>
-  <si>
-    <t>CLEAR SHP KOMPLIT160</t>
-  </si>
-  <si>
-    <t>20091440</t>
-  </si>
-  <si>
-    <t>CLEAR SHP MENTHOL160</t>
-  </si>
-  <si>
-    <t>20132698</t>
-  </si>
-  <si>
-    <t>CLEAR SHP AK&amp;RNTK160</t>
-  </si>
-  <si>
-    <t>20040608</t>
-  </si>
-  <si>
-    <t>ZINC SHP HFT GNSG170</t>
-  </si>
-  <si>
-    <t>20040609</t>
-  </si>
-  <si>
-    <t>ZINC RE-FRSH COOL170</t>
-  </si>
-  <si>
-    <t>20109265</t>
-  </si>
-  <si>
-    <t>ZINC SHP LMN MINT170</t>
-  </si>
-  <si>
-    <t>20136708</t>
-  </si>
-  <si>
-    <t>ZINC SHP COOL.BS 170</t>
-  </si>
-  <si>
-    <t>20118252</t>
-  </si>
-  <si>
-    <t>PTNE COLLAGEN COND70</t>
-  </si>
-  <si>
-    <t>20118290</t>
-  </si>
-  <si>
-    <t>PTNE BIOTIN S COND70</t>
-  </si>
-  <si>
-    <t>10000632</t>
-  </si>
-  <si>
-    <t>MR. HAIR TONIC 175ML</t>
-  </si>
-  <si>
-    <t>20075951</t>
-  </si>
-  <si>
-    <t>MKRZO HES MR.DEW 100</t>
-  </si>
-  <si>
-    <t>20078998</t>
-  </si>
-  <si>
-    <t>MKRZO SCNT WHT MS100</t>
-  </si>
-  <si>
-    <t>20129466</t>
-  </si>
-  <si>
-    <t>MKRZO SCNT AMB WD100</t>
-  </si>
-  <si>
-    <t>20058061</t>
-  </si>
-  <si>
-    <t>MKRZO SCNT CHR/B 100</t>
-  </si>
-  <si>
-    <t>20131993</t>
-  </si>
-  <si>
-    <t>ELLIPS VIT.HM F&amp;S100</t>
-  </si>
-  <si>
-    <t>20128430</t>
-  </si>
-  <si>
-    <t>ELLIPS VIT.HM S&amp;S100</t>
-  </si>
-  <si>
-    <t>20136299</t>
-  </si>
-  <si>
-    <t>SUNSLK HR PRFM 100ML</t>
-  </si>
-  <si>
-    <t>20139069</t>
-  </si>
-  <si>
-    <t>SNSLK SHP GL.BLCK 70</t>
-  </si>
-  <si>
-    <t>20038765</t>
-  </si>
-  <si>
-    <t>PANTENE SHP ANT/D 70</t>
-  </si>
-  <si>
-    <t>20010379</t>
-  </si>
-  <si>
-    <t>LIFEBUOY SHP A/D 70</t>
-  </si>
-  <si>
-    <t>20091437</t>
-  </si>
-  <si>
-    <t>CLEAR SHP MENTHOL 70</t>
-  </si>
-  <si>
-    <t>20036191</t>
-  </si>
-  <si>
-    <t>H&amp;S SHP.MN/DINGIN 70</t>
-  </si>
-  <si>
-    <t>10004513</t>
-  </si>
-  <si>
-    <t>NATUR P/RMB RNTK 140</t>
-  </si>
-  <si>
-    <t>20140792</t>
-  </si>
-  <si>
-    <t>DOVE MCLAR SHP 150ML</t>
-  </si>
-  <si>
-    <t>20140791</t>
-  </si>
-  <si>
-    <t>DOVE BIOTIN SHP 150</t>
-  </si>
-  <si>
     <t>20055602</t>
   </si>
   <si>
@@ -1366,6 +1348,12 @@
     <t>GRNIER ASH BLNDE PCK</t>
   </si>
   <si>
+    <t>20013925</t>
+  </si>
+  <si>
+    <t>MRNDA BLCG/DCLR MC-6</t>
+  </si>
+  <si>
     <t>20085008</t>
   </si>
   <si>
@@ -1378,48 +1366,54 @@
     <t>GRNR CLR.NAT 6.62 CR</t>
   </si>
   <si>
-    <t>20013925</t>
-  </si>
-  <si>
-    <t>MRNDA BLCG/DCLR MC-6</t>
-  </si>
-  <si>
     <t>20082864</t>
   </si>
   <si>
     <t>GRNR CLR.NAT HTM PCK</t>
   </si>
   <si>
+    <t>20120451</t>
+  </si>
+  <si>
+    <t>NYU/H SHP NAT BLAK20</t>
+  </si>
+  <si>
+    <t>20120459</t>
+  </si>
+  <si>
+    <t>NYU/H SHP NAT BRWN20</t>
+  </si>
+  <si>
+    <t>20142682</t>
+  </si>
+  <si>
+    <t>GRNR HC GLW MILKTEA</t>
+  </si>
+  <si>
+    <t>20068904</t>
+  </si>
+  <si>
+    <t>NONI MGC BLCK HS2X20</t>
+  </si>
+  <si>
     <t>20111612</t>
   </si>
   <si>
     <t>GARNIER MEN SC 1.0</t>
   </si>
   <si>
-    <t>20120451</t>
-  </si>
-  <si>
-    <t>NYU/H SHP NAT BLAK20</t>
-  </si>
-  <si>
-    <t>20120459</t>
-  </si>
-  <si>
-    <t>NYU/H SHP NAT BRWN20</t>
-  </si>
-  <si>
-    <t>20068904</t>
-  </si>
-  <si>
-    <t>NONI MGC BLCK HS2X20</t>
-  </si>
-  <si>
     <t>20122044</t>
   </si>
   <si>
     <t>GARNIER MEN SC 3.0</t>
   </si>
   <si>
+    <t>20142683</t>
+  </si>
+  <si>
+    <t>GRNR HC CRMEL MOCHA</t>
+  </si>
+  <si>
     <t>20093143</t>
   </si>
   <si>
@@ -1597,6 +1591,12 @@
     <t>LIFEBUOY BW SHISO300</t>
   </si>
   <si>
+    <t>20133508</t>
+  </si>
+  <si>
+    <t>BIORE DEO P. T&amp;M 400</t>
+  </si>
+  <si>
     <t>20060393</t>
   </si>
   <si>
@@ -1684,6 +1684,12 @@
     <t>GIV BW HJB SAF&amp;N 400</t>
   </si>
   <si>
+    <t>20142623</t>
+  </si>
+  <si>
+    <t>GIV BW PEACH 400ML</t>
+  </si>
+  <si>
     <t>20120923</t>
   </si>
   <si>
@@ -1702,12 +1708,6 @@
     <t>K.NAT BW JJ LEMON400</t>
   </si>
   <si>
-    <t>20133508</t>
-  </si>
-  <si>
-    <t>BIORE DEO P. T&amp;M 400</t>
-  </si>
-  <si>
     <t>20130824</t>
   </si>
   <si>
@@ -2146,18 +2146,18 @@
     <t>NIVEA B.SRM CRE&amp;P180</t>
   </si>
   <si>
-    <t>20139972</t>
-  </si>
-  <si>
-    <t>G2G BS CRM.BERRY 180</t>
-  </si>
-  <si>
     <t>20140874</t>
   </si>
   <si>
     <t>G2G NIACND B.SRM 180</t>
   </si>
   <si>
+    <t>20142600</t>
+  </si>
+  <si>
+    <t>G2G RETINOL BS180ML</t>
+  </si>
+  <si>
     <t>20131721</t>
   </si>
   <si>
@@ -3322,12 +3322,6 @@
     <t>WARDAH DAY CRM 20G</t>
   </si>
   <si>
-    <t>20102837</t>
-  </si>
-  <si>
-    <t>GRNR BS.SRM VIT C7.5</t>
-  </si>
-  <si>
     <t>20132418</t>
   </si>
   <si>
@@ -4258,43 +4252,19 @@
     <t>GATSBY BALM CREAM 70</t>
   </si>
   <si>
-    <t>20075930</t>
-  </si>
-  <si>
-    <t>MKRZO H/E ALOE.MLN6S</t>
+    <t>20120878</t>
+  </si>
+  <si>
+    <t>L/BUOY BW MCH&amp;ALO380</t>
   </si>
   <si>
     <t>998</t>
   </si>
   <si>
-    <t>20021482</t>
-  </si>
-  <si>
-    <t>MKARIZO AD V.MAX 3'S</t>
-  </si>
-  <si>
-    <t>10003616</t>
-  </si>
-  <si>
-    <t>TANCHO HAIR DYE 40ML</t>
-  </si>
-  <si>
-    <t>20120878</t>
-  </si>
-  <si>
-    <t>L/BUOY BW MCH&amp;ALO380</t>
-  </si>
-  <si>
     <t>20115145</t>
   </si>
   <si>
     <t>L/BUOY BW JPN.SHS380</t>
-  </si>
-  <si>
-    <t>20013699</t>
-  </si>
-  <si>
-    <t>SASHA CLRNT NT.BLACK</t>
   </si>
 </sst>
 </file>
@@ -4687,7 +4657,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F683"/>
+  <dimension ref="A1:F678"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
@@ -6635,7 +6605,7 @@
         <v>4</v>
       </c>
       <c r="F97" s="1" t="s">
-        <v>25</v>
+        <v>168</v>
       </c>
     </row>
     <row r="98" spans="1:6" x14ac:dyDescent="0.25">
@@ -6695,15 +6665,15 @@
         <v>15</v>
       </c>
       <c r="F100" s="1" t="s">
-        <v>168</v>
+        <v>231</v>
       </c>
     </row>
     <row r="101" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A101" s="1" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="B101" s="1" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="C101" s="1" t="s">
         <v>3</v>
@@ -6715,7 +6685,7 @@
         <v>18</v>
       </c>
       <c r="F101" s="1" t="s">
-        <v>233</v>
+        <v>133</v>
       </c>
     </row>
     <row r="102" spans="1:6" x14ac:dyDescent="0.25">
@@ -6735,7 +6705,7 @@
         <v>21</v>
       </c>
       <c r="F102" s="1" t="s">
-        <v>133</v>
+        <v>25</v>
       </c>
     </row>
     <row r="103" spans="1:6" x14ac:dyDescent="0.25">
@@ -6755,7 +6725,7 @@
         <v>24</v>
       </c>
       <c r="F103" s="1" t="s">
-        <v>25</v>
+        <v>80</v>
       </c>
     </row>
     <row r="104" spans="1:6" x14ac:dyDescent="0.25">
@@ -6795,7 +6765,7 @@
         <v>31</v>
       </c>
       <c r="F105" s="1" t="s">
-        <v>80</v>
+        <v>5</v>
       </c>
     </row>
     <row r="106" spans="1:6" x14ac:dyDescent="0.25">
@@ -6815,7 +6785,7 @@
         <v>34</v>
       </c>
       <c r="F106" s="1" t="s">
-        <v>5</v>
+        <v>41</v>
       </c>
     </row>
     <row r="107" spans="1:6" x14ac:dyDescent="0.25">
@@ -6835,7 +6805,7 @@
         <v>37</v>
       </c>
       <c r="F107" s="1" t="s">
-        <v>41</v>
+        <v>5</v>
       </c>
     </row>
     <row r="108" spans="1:6" x14ac:dyDescent="0.25">
@@ -6855,7 +6825,7 @@
         <v>4</v>
       </c>
       <c r="F108" s="1" t="s">
-        <v>25</v>
+        <v>73</v>
       </c>
     </row>
     <row r="109" spans="1:6" x14ac:dyDescent="0.25">
@@ -6875,15 +6845,15 @@
         <v>8</v>
       </c>
       <c r="F109" s="1" t="s">
-        <v>250</v>
+        <v>73</v>
       </c>
     </row>
     <row r="110" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A110" s="1" t="s">
+        <v>250</v>
+      </c>
+      <c r="B110" s="1" t="s">
         <v>251</v>
-      </c>
-      <c r="B110" s="1" t="s">
-        <v>252</v>
       </c>
       <c r="C110" s="1" t="s">
         <v>3</v>
@@ -6900,10 +6870,10 @@
     </row>
     <row r="111" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A111" s="1" t="s">
+        <v>252</v>
+      </c>
+      <c r="B111" s="1" t="s">
         <v>253</v>
-      </c>
-      <c r="B111" s="1" t="s">
-        <v>254</v>
       </c>
       <c r="C111" s="1" t="s">
         <v>3</v>
@@ -6915,15 +6885,15 @@
         <v>15</v>
       </c>
       <c r="F111" s="1" t="s">
-        <v>73</v>
+        <v>231</v>
       </c>
     </row>
     <row r="112" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A112" s="1" t="s">
+        <v>254</v>
+      </c>
+      <c r="B112" s="1" t="s">
         <v>255</v>
-      </c>
-      <c r="B112" s="1" t="s">
-        <v>256</v>
       </c>
       <c r="C112" s="1" t="s">
         <v>3</v>
@@ -6935,15 +6905,15 @@
         <v>18</v>
       </c>
       <c r="F112" s="1" t="s">
-        <v>73</v>
+        <v>5</v>
       </c>
     </row>
     <row r="113" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A113" s="1" t="s">
+        <v>256</v>
+      </c>
+      <c r="B113" s="1" t="s">
         <v>257</v>
-      </c>
-      <c r="B113" s="1" t="s">
-        <v>258</v>
       </c>
       <c r="C113" s="1" t="s">
         <v>3</v>
@@ -6955,15 +6925,15 @@
         <v>21</v>
       </c>
       <c r="F113" s="1" t="s">
-        <v>233</v>
+        <v>80</v>
       </c>
     </row>
     <row r="114" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A114" s="1" t="s">
+        <v>258</v>
+      </c>
+      <c r="B114" s="1" t="s">
         <v>259</v>
-      </c>
-      <c r="B114" s="1" t="s">
-        <v>260</v>
       </c>
       <c r="C114" s="1" t="s">
         <v>3</v>
@@ -6975,15 +6945,15 @@
         <v>24</v>
       </c>
       <c r="F114" s="1" t="s">
-        <v>5</v>
+        <v>80</v>
       </c>
     </row>
     <row r="115" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A115" s="1" t="s">
+        <v>260</v>
+      </c>
+      <c r="B115" s="1" t="s">
         <v>261</v>
-      </c>
-      <c r="B115" s="1" t="s">
-        <v>262</v>
       </c>
       <c r="C115" s="1" t="s">
         <v>3</v>
@@ -6995,15 +6965,15 @@
         <v>28</v>
       </c>
       <c r="F115" s="1" t="s">
-        <v>80</v>
+        <v>25</v>
       </c>
     </row>
     <row r="116" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A116" s="1" t="s">
+        <v>262</v>
+      </c>
+      <c r="B116" s="1" t="s">
         <v>263</v>
-      </c>
-      <c r="B116" s="1" t="s">
-        <v>264</v>
       </c>
       <c r="C116" s="1" t="s">
         <v>3</v>
@@ -7015,15 +6985,15 @@
         <v>31</v>
       </c>
       <c r="F116" s="1" t="s">
-        <v>80</v>
+        <v>133</v>
       </c>
     </row>
     <row r="117" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A117" s="1" t="s">
+        <v>264</v>
+      </c>
+      <c r="B117" s="1" t="s">
         <v>265</v>
-      </c>
-      <c r="B117" s="1" t="s">
-        <v>266</v>
       </c>
       <c r="C117" s="1" t="s">
         <v>3</v>
@@ -7035,15 +7005,15 @@
         <v>34</v>
       </c>
       <c r="F117" s="1" t="s">
-        <v>25</v>
+        <v>133</v>
       </c>
     </row>
     <row r="118" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A118" s="1" t="s">
+        <v>266</v>
+      </c>
+      <c r="B118" s="1" t="s">
         <v>267</v>
-      </c>
-      <c r="B118" s="1" t="s">
-        <v>268</v>
       </c>
       <c r="C118" s="1" t="s">
         <v>3</v>
@@ -7055,15 +7025,15 @@
         <v>37</v>
       </c>
       <c r="F118" s="1" t="s">
-        <v>133</v>
+        <v>80</v>
       </c>
     </row>
     <row r="119" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A119" s="1" t="s">
+        <v>268</v>
+      </c>
+      <c r="B119" s="1" t="s">
         <v>269</v>
-      </c>
-      <c r="B119" s="1" t="s">
-        <v>270</v>
       </c>
       <c r="C119" s="1" t="s">
         <v>3</v>
@@ -7075,27 +7045,27 @@
         <v>40</v>
       </c>
       <c r="F119" s="1" t="s">
-        <v>133</v>
+        <v>41</v>
       </c>
     </row>
     <row r="120" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A120" s="1" t="s">
+        <v>270</v>
+      </c>
+      <c r="B120" s="1" t="s">
         <v>271</v>
       </c>
-      <c r="B120" s="1" t="s">
+      <c r="C120" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D120" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="E120" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F120" s="1" t="s">
         <v>272</v>
-      </c>
-      <c r="C120" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D120" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="E120" s="1" t="s">
-        <v>68</v>
-      </c>
-      <c r="F120" s="1" t="s">
-        <v>80</v>
       </c>
     </row>
     <row r="121" spans="1:6" x14ac:dyDescent="0.25">
@@ -7109,10 +7079,10 @@
         <v>3</v>
       </c>
       <c r="D121" s="1" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="E121" s="1" t="s">
-        <v>100</v>
+        <v>8</v>
       </c>
       <c r="F121" s="1" t="s">
         <v>41</v>
@@ -7132,7 +7102,7 @@
         <v>31</v>
       </c>
       <c r="E122" s="1" t="s">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="F122" s="1" t="s">
         <v>41</v>
@@ -7152,10 +7122,10 @@
         <v>31</v>
       </c>
       <c r="E123" s="1" t="s">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="F123" s="1" t="s">
-        <v>250</v>
+        <v>41</v>
       </c>
     </row>
     <row r="124" spans="1:6" x14ac:dyDescent="0.25">
@@ -7172,10 +7142,10 @@
         <v>31</v>
       </c>
       <c r="E124" s="1" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="F124" s="1" t="s">
-        <v>41</v>
+        <v>25</v>
       </c>
     </row>
     <row r="125" spans="1:6" x14ac:dyDescent="0.25">
@@ -7192,10 +7162,10 @@
         <v>31</v>
       </c>
       <c r="E125" s="1" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="F125" s="1" t="s">
-        <v>41</v>
+        <v>25</v>
       </c>
     </row>
     <row r="126" spans="1:6" x14ac:dyDescent="0.25">
@@ -7212,10 +7182,10 @@
         <v>31</v>
       </c>
       <c r="E126" s="1" t="s">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="F126" s="1" t="s">
-        <v>41</v>
+        <v>73</v>
       </c>
     </row>
     <row r="127" spans="1:6" x14ac:dyDescent="0.25">
@@ -7232,7 +7202,7 @@
         <v>31</v>
       </c>
       <c r="E127" s="1" t="s">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="F127" s="1" t="s">
         <v>25</v>
@@ -7252,7 +7222,7 @@
         <v>31</v>
       </c>
       <c r="E128" s="1" t="s">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="F128" s="1" t="s">
         <v>25</v>
@@ -7272,10 +7242,10 @@
         <v>31</v>
       </c>
       <c r="E129" s="1" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="F129" s="1" t="s">
-        <v>73</v>
+        <v>41</v>
       </c>
     </row>
     <row r="130" spans="1:6" x14ac:dyDescent="0.25">
@@ -7292,10 +7262,10 @@
         <v>31</v>
       </c>
       <c r="E130" s="1" t="s">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="F130" s="1" t="s">
-        <v>25</v>
+        <v>41</v>
       </c>
     </row>
     <row r="131" spans="1:6" x14ac:dyDescent="0.25">
@@ -7312,10 +7282,10 @@
         <v>31</v>
       </c>
       <c r="E131" s="1" t="s">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="F131" s="1" t="s">
-        <v>25</v>
+        <v>41</v>
       </c>
     </row>
     <row r="132" spans="1:6" x14ac:dyDescent="0.25">
@@ -7329,13 +7299,13 @@
         <v>3</v>
       </c>
       <c r="D132" s="1" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="E132" s="1" t="s">
-        <v>37</v>
+        <v>4</v>
       </c>
       <c r="F132" s="1" t="s">
-        <v>41</v>
+        <v>25</v>
       </c>
     </row>
     <row r="133" spans="1:6" x14ac:dyDescent="0.25">
@@ -7349,13 +7319,13 @@
         <v>3</v>
       </c>
       <c r="D133" s="1" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="E133" s="1" t="s">
-        <v>40</v>
+        <v>8</v>
       </c>
       <c r="F133" s="1" t="s">
-        <v>41</v>
+        <v>25</v>
       </c>
     </row>
     <row r="134" spans="1:6" x14ac:dyDescent="0.25">
@@ -7369,13 +7339,13 @@
         <v>3</v>
       </c>
       <c r="D134" s="1" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="E134" s="1" t="s">
-        <v>68</v>
+        <v>12</v>
       </c>
       <c r="F134" s="1" t="s">
-        <v>41</v>
+        <v>25</v>
       </c>
     </row>
     <row r="135" spans="1:6" x14ac:dyDescent="0.25">
@@ -7392,7 +7362,7 @@
         <v>34</v>
       </c>
       <c r="E135" s="1" t="s">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="F135" s="1" t="s">
         <v>25</v>
@@ -7412,7 +7382,7 @@
         <v>34</v>
       </c>
       <c r="E136" s="1" t="s">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="F136" s="1" t="s">
         <v>25</v>
@@ -7432,10 +7402,10 @@
         <v>34</v>
       </c>
       <c r="E137" s="1" t="s">
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="F137" s="1" t="s">
-        <v>25</v>
+        <v>272</v>
       </c>
     </row>
     <row r="138" spans="1:6" x14ac:dyDescent="0.25">
@@ -7452,10 +7422,10 @@
         <v>34</v>
       </c>
       <c r="E138" s="1" t="s">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="F138" s="1" t="s">
-        <v>25</v>
+        <v>272</v>
       </c>
     </row>
     <row r="139" spans="1:6" x14ac:dyDescent="0.25">
@@ -7472,10 +7442,10 @@
         <v>34</v>
       </c>
       <c r="E139" s="1" t="s">
-        <v>18</v>
+        <v>28</v>
       </c>
       <c r="F139" s="1" t="s">
-        <v>25</v>
+        <v>272</v>
       </c>
     </row>
     <row r="140" spans="1:6" x14ac:dyDescent="0.25">
@@ -7492,10 +7462,10 @@
         <v>34</v>
       </c>
       <c r="E140" s="1" t="s">
-        <v>21</v>
+        <v>31</v>
       </c>
       <c r="F140" s="1" t="s">
-        <v>250</v>
+        <v>5</v>
       </c>
     </row>
     <row r="141" spans="1:6" x14ac:dyDescent="0.25">
@@ -7512,10 +7482,10 @@
         <v>34</v>
       </c>
       <c r="E141" s="1" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
       <c r="F141" s="1" t="s">
-        <v>250</v>
+        <v>5</v>
       </c>
     </row>
     <row r="142" spans="1:6" x14ac:dyDescent="0.25">
@@ -7532,10 +7502,10 @@
         <v>34</v>
       </c>
       <c r="E142" s="1" t="s">
-        <v>28</v>
+        <v>37</v>
       </c>
       <c r="F142" s="1" t="s">
-        <v>250</v>
+        <v>5</v>
       </c>
     </row>
     <row r="143" spans="1:6" x14ac:dyDescent="0.25">
@@ -7552,10 +7522,10 @@
         <v>34</v>
       </c>
       <c r="E143" s="1" t="s">
-        <v>31</v>
+        <v>40</v>
       </c>
       <c r="F143" s="1" t="s">
-        <v>5</v>
+        <v>25</v>
       </c>
     </row>
     <row r="144" spans="1:6" x14ac:dyDescent="0.25">
@@ -7572,10 +7542,10 @@
         <v>34</v>
       </c>
       <c r="E144" s="1" t="s">
-        <v>34</v>
+        <v>68</v>
       </c>
       <c r="F144" s="1" t="s">
-        <v>5</v>
+        <v>91</v>
       </c>
     </row>
     <row r="145" spans="1:6" x14ac:dyDescent="0.25">
@@ -7592,7 +7562,7 @@
         <v>34</v>
       </c>
       <c r="E145" s="1" t="s">
-        <v>37</v>
+        <v>100</v>
       </c>
       <c r="F145" s="1" t="s">
         <v>5</v>
@@ -7609,13 +7579,13 @@
         <v>3</v>
       </c>
       <c r="D146" s="1" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="E146" s="1" t="s">
-        <v>40</v>
+        <v>4</v>
       </c>
       <c r="F146" s="1" t="s">
-        <v>25</v>
+        <v>272</v>
       </c>
     </row>
     <row r="147" spans="1:6" x14ac:dyDescent="0.25">
@@ -7629,13 +7599,13 @@
         <v>3</v>
       </c>
       <c r="D147" s="1" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="E147" s="1" t="s">
-        <v>68</v>
+        <v>8</v>
       </c>
       <c r="F147" s="1" t="s">
-        <v>5</v>
+        <v>272</v>
       </c>
     </row>
     <row r="148" spans="1:6" x14ac:dyDescent="0.25">
@@ -7652,10 +7622,10 @@
         <v>37</v>
       </c>
       <c r="E148" s="1" t="s">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="F148" s="1" t="s">
-        <v>73</v>
+        <v>272</v>
       </c>
     </row>
     <row r="149" spans="1:6" x14ac:dyDescent="0.25">
@@ -7672,10 +7642,10 @@
         <v>37</v>
       </c>
       <c r="E149" s="1" t="s">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="F149" s="1" t="s">
-        <v>73</v>
+        <v>272</v>
       </c>
     </row>
     <row r="150" spans="1:6" x14ac:dyDescent="0.25">
@@ -7692,10 +7662,10 @@
         <v>37</v>
       </c>
       <c r="E150" s="1" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="F150" s="1" t="s">
-        <v>250</v>
+        <v>272</v>
       </c>
     </row>
     <row r="151" spans="1:6" x14ac:dyDescent="0.25">
@@ -7712,10 +7682,10 @@
         <v>37</v>
       </c>
       <c r="E151" s="1" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="F151" s="1" t="s">
-        <v>250</v>
+        <v>25</v>
       </c>
     </row>
     <row r="152" spans="1:6" x14ac:dyDescent="0.25">
@@ -7732,10 +7702,10 @@
         <v>37</v>
       </c>
       <c r="E152" s="1" t="s">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="F152" s="1" t="s">
-        <v>250</v>
+        <v>25</v>
       </c>
     </row>
     <row r="153" spans="1:6" x14ac:dyDescent="0.25">
@@ -7752,10 +7722,10 @@
         <v>37</v>
       </c>
       <c r="E153" s="1" t="s">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="F153" s="1" t="s">
-        <v>250</v>
+        <v>5</v>
       </c>
     </row>
     <row r="154" spans="1:6" x14ac:dyDescent="0.25">
@@ -7772,10 +7742,10 @@
         <v>37</v>
       </c>
       <c r="E154" s="1" t="s">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="F154" s="1" t="s">
-        <v>250</v>
+        <v>5</v>
       </c>
     </row>
     <row r="155" spans="1:6" x14ac:dyDescent="0.25">
@@ -7792,10 +7762,10 @@
         <v>37</v>
       </c>
       <c r="E155" s="1" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="F155" s="1" t="s">
-        <v>25</v>
+        <v>41</v>
       </c>
     </row>
     <row r="156" spans="1:6" x14ac:dyDescent="0.25">
@@ -7812,10 +7782,10 @@
         <v>37</v>
       </c>
       <c r="E156" s="1" t="s">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="F156" s="1" t="s">
-        <v>25</v>
+        <v>41</v>
       </c>
     </row>
     <row r="157" spans="1:6" x14ac:dyDescent="0.25">
@@ -7832,7 +7802,7 @@
         <v>37</v>
       </c>
       <c r="E157" s="1" t="s">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="F157" s="1" t="s">
         <v>5</v>
@@ -7852,10 +7822,10 @@
         <v>37</v>
       </c>
       <c r="E158" s="1" t="s">
-        <v>37</v>
+        <v>68</v>
       </c>
       <c r="F158" s="1" t="s">
-        <v>5</v>
+        <v>41</v>
       </c>
     </row>
     <row r="159" spans="1:6" x14ac:dyDescent="0.25">
@@ -7869,13 +7839,13 @@
         <v>3</v>
       </c>
       <c r="D159" s="1" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="E159" s="1" t="s">
-        <v>40</v>
+        <v>4</v>
       </c>
       <c r="F159" s="1" t="s">
-        <v>41</v>
+        <v>25</v>
       </c>
     </row>
     <row r="160" spans="1:6" x14ac:dyDescent="0.25">
@@ -7889,13 +7859,13 @@
         <v>3</v>
       </c>
       <c r="D160" s="1" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="E160" s="1" t="s">
-        <v>68</v>
+        <v>8</v>
       </c>
       <c r="F160" s="1" t="s">
-        <v>41</v>
+        <v>25</v>
       </c>
     </row>
     <row r="161" spans="1:6" x14ac:dyDescent="0.25">
@@ -7909,13 +7879,13 @@
         <v>3</v>
       </c>
       <c r="D161" s="1" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="E161" s="1" t="s">
-        <v>100</v>
+        <v>12</v>
       </c>
       <c r="F161" s="1" t="s">
-        <v>5</v>
+        <v>272</v>
       </c>
     </row>
     <row r="162" spans="1:6" x14ac:dyDescent="0.25">
@@ -7932,7 +7902,7 @@
         <v>40</v>
       </c>
       <c r="E162" s="1" t="s">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="F162" s="1" t="s">
         <v>25</v>
@@ -7952,7 +7922,7 @@
         <v>40</v>
       </c>
       <c r="E163" s="1" t="s">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="F163" s="1" t="s">
         <v>25</v>
@@ -7972,10 +7942,10 @@
         <v>40</v>
       </c>
       <c r="E164" s="1" t="s">
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="F164" s="1" t="s">
-        <v>250</v>
+        <v>25</v>
       </c>
     </row>
     <row r="165" spans="1:6" x14ac:dyDescent="0.25">
@@ -7992,10 +7962,10 @@
         <v>40</v>
       </c>
       <c r="E165" s="1" t="s">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="F165" s="1" t="s">
-        <v>25</v>
+        <v>272</v>
       </c>
     </row>
     <row r="166" spans="1:6" x14ac:dyDescent="0.25">
@@ -8012,7 +7982,7 @@
         <v>40</v>
       </c>
       <c r="E166" s="1" t="s">
-        <v>18</v>
+        <v>28</v>
       </c>
       <c r="F166" s="1" t="s">
         <v>25</v>
@@ -8032,7 +8002,7 @@
         <v>40</v>
       </c>
       <c r="E167" s="1" t="s">
-        <v>21</v>
+        <v>31</v>
       </c>
       <c r="F167" s="1" t="s">
         <v>25</v>
@@ -8052,10 +8022,10 @@
         <v>40</v>
       </c>
       <c r="E168" s="1" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
       <c r="F168" s="1" t="s">
-        <v>250</v>
+        <v>25</v>
       </c>
     </row>
     <row r="169" spans="1:6" x14ac:dyDescent="0.25">
@@ -8072,7 +8042,7 @@
         <v>40</v>
       </c>
       <c r="E169" s="1" t="s">
-        <v>28</v>
+        <v>37</v>
       </c>
       <c r="F169" s="1" t="s">
         <v>25</v>
@@ -8092,10 +8062,10 @@
         <v>40</v>
       </c>
       <c r="E170" s="1" t="s">
-        <v>31</v>
+        <v>40</v>
       </c>
       <c r="F170" s="1" t="s">
-        <v>25</v>
+        <v>41</v>
       </c>
     </row>
     <row r="171" spans="1:6" x14ac:dyDescent="0.25">
@@ -8112,10 +8082,10 @@
         <v>40</v>
       </c>
       <c r="E171" s="1" t="s">
-        <v>34</v>
+        <v>68</v>
       </c>
       <c r="F171" s="1" t="s">
-        <v>25</v>
+        <v>41</v>
       </c>
     </row>
     <row r="172" spans="1:6" x14ac:dyDescent="0.25">
@@ -8132,10 +8102,10 @@
         <v>40</v>
       </c>
       <c r="E172" s="1" t="s">
-        <v>37</v>
+        <v>100</v>
       </c>
       <c r="F172" s="1" t="s">
-        <v>25</v>
+        <v>41</v>
       </c>
     </row>
     <row r="173" spans="1:6" x14ac:dyDescent="0.25">
@@ -8152,7 +8122,7 @@
         <v>40</v>
       </c>
       <c r="E173" s="1" t="s">
-        <v>40</v>
+        <v>103</v>
       </c>
       <c r="F173" s="1" t="s">
         <v>41</v>
@@ -8169,13 +8139,13 @@
         <v>3</v>
       </c>
       <c r="D174" s="1" t="s">
-        <v>40</v>
+        <v>68</v>
       </c>
       <c r="E174" s="1" t="s">
-        <v>68</v>
+        <v>4</v>
       </c>
       <c r="F174" s="1" t="s">
-        <v>41</v>
+        <v>25</v>
       </c>
     </row>
     <row r="175" spans="1:6" x14ac:dyDescent="0.25">
@@ -8189,13 +8159,13 @@
         <v>3</v>
       </c>
       <c r="D175" s="1" t="s">
-        <v>40</v>
+        <v>68</v>
       </c>
       <c r="E175" s="1" t="s">
-        <v>100</v>
+        <v>8</v>
       </c>
       <c r="F175" s="1" t="s">
-        <v>41</v>
+        <v>25</v>
       </c>
     </row>
     <row r="176" spans="1:6" x14ac:dyDescent="0.25">
@@ -8209,13 +8179,13 @@
         <v>3</v>
       </c>
       <c r="D176" s="1" t="s">
-        <v>40</v>
+        <v>68</v>
       </c>
       <c r="E176" s="1" t="s">
-        <v>103</v>
+        <v>12</v>
       </c>
       <c r="F176" s="1" t="s">
-        <v>41</v>
+        <v>80</v>
       </c>
     </row>
     <row r="177" spans="1:6" x14ac:dyDescent="0.25">
@@ -8232,10 +8202,10 @@
         <v>68</v>
       </c>
       <c r="E177" s="1" t="s">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="F177" s="1" t="s">
-        <v>25</v>
+        <v>5</v>
       </c>
     </row>
     <row r="178" spans="1:6" x14ac:dyDescent="0.25">
@@ -8252,10 +8222,10 @@
         <v>68</v>
       </c>
       <c r="E178" s="1" t="s">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="F178" s="1" t="s">
-        <v>25</v>
+        <v>5</v>
       </c>
     </row>
     <row r="179" spans="1:6" x14ac:dyDescent="0.25">
@@ -8272,10 +8242,10 @@
         <v>68</v>
       </c>
       <c r="E179" s="1" t="s">
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="F179" s="1" t="s">
-        <v>80</v>
+        <v>5</v>
       </c>
     </row>
     <row r="180" spans="1:6" x14ac:dyDescent="0.25">
@@ -8292,7 +8262,7 @@
         <v>68</v>
       </c>
       <c r="E180" s="1" t="s">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="F180" s="1" t="s">
         <v>5</v>
@@ -8312,7 +8282,7 @@
         <v>68</v>
       </c>
       <c r="E181" s="1" t="s">
-        <v>18</v>
+        <v>28</v>
       </c>
       <c r="F181" s="1" t="s">
         <v>5</v>
@@ -8332,7 +8302,7 @@
         <v>68</v>
       </c>
       <c r="E182" s="1" t="s">
-        <v>21</v>
+        <v>31</v>
       </c>
       <c r="F182" s="1" t="s">
         <v>5</v>
@@ -8352,10 +8322,10 @@
         <v>68</v>
       </c>
       <c r="E183" s="1" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
       <c r="F183" s="1" t="s">
-        <v>5</v>
+        <v>133</v>
       </c>
     </row>
     <row r="184" spans="1:6" x14ac:dyDescent="0.25">
@@ -8372,10 +8342,10 @@
         <v>68</v>
       </c>
       <c r="E184" s="1" t="s">
-        <v>28</v>
+        <v>37</v>
       </c>
       <c r="F184" s="1" t="s">
-        <v>5</v>
+        <v>25</v>
       </c>
     </row>
     <row r="185" spans="1:6" x14ac:dyDescent="0.25">
@@ -8392,10 +8362,10 @@
         <v>68</v>
       </c>
       <c r="E185" s="1" t="s">
-        <v>31</v>
+        <v>40</v>
       </c>
       <c r="F185" s="1" t="s">
-        <v>5</v>
+        <v>272</v>
       </c>
     </row>
     <row r="186" spans="1:6" x14ac:dyDescent="0.25">
@@ -8412,10 +8382,10 @@
         <v>68</v>
       </c>
       <c r="E186" s="1" t="s">
-        <v>34</v>
+        <v>68</v>
       </c>
       <c r="F186" s="1" t="s">
-        <v>133</v>
+        <v>73</v>
       </c>
     </row>
     <row r="187" spans="1:6" x14ac:dyDescent="0.25">
@@ -8432,7 +8402,7 @@
         <v>68</v>
       </c>
       <c r="E187" s="1" t="s">
-        <v>37</v>
+        <v>100</v>
       </c>
       <c r="F187" s="1" t="s">
         <v>25</v>
@@ -8452,10 +8422,10 @@
         <v>68</v>
       </c>
       <c r="E188" s="1" t="s">
-        <v>40</v>
+        <v>103</v>
       </c>
       <c r="F188" s="1" t="s">
-        <v>250</v>
+        <v>272</v>
       </c>
     </row>
     <row r="189" spans="1:6" x14ac:dyDescent="0.25">
@@ -8472,10 +8442,10 @@
         <v>68</v>
       </c>
       <c r="E189" s="1" t="s">
-        <v>68</v>
+        <v>106</v>
       </c>
       <c r="F189" s="1" t="s">
-        <v>73</v>
+        <v>25</v>
       </c>
     </row>
     <row r="190" spans="1:6" x14ac:dyDescent="0.25">
@@ -8492,10 +8462,10 @@
         <v>68</v>
       </c>
       <c r="E190" s="1" t="s">
-        <v>100</v>
+        <v>109</v>
       </c>
       <c r="F190" s="1" t="s">
-        <v>25</v>
+        <v>73</v>
       </c>
     </row>
     <row r="191" spans="1:6" x14ac:dyDescent="0.25">
@@ -8512,10 +8482,10 @@
         <v>68</v>
       </c>
       <c r="E191" s="1" t="s">
-        <v>103</v>
+        <v>112</v>
       </c>
       <c r="F191" s="1" t="s">
-        <v>250</v>
+        <v>73</v>
       </c>
     </row>
     <row r="192" spans="1:6" x14ac:dyDescent="0.25">
@@ -8529,13 +8499,13 @@
         <v>3</v>
       </c>
       <c r="D192" s="1" t="s">
-        <v>68</v>
+        <v>100</v>
       </c>
       <c r="E192" s="1" t="s">
-        <v>106</v>
+        <v>4</v>
       </c>
       <c r="F192" s="1" t="s">
-        <v>91</v>
+        <v>9</v>
       </c>
     </row>
     <row r="193" spans="1:6" x14ac:dyDescent="0.25">
@@ -8549,10 +8519,10 @@
         <v>3</v>
       </c>
       <c r="D193" s="1" t="s">
-        <v>68</v>
+        <v>100</v>
       </c>
       <c r="E193" s="1" t="s">
-        <v>109</v>
+        <v>4</v>
       </c>
       <c r="F193" s="1" t="s">
         <v>25</v>
@@ -8569,13 +8539,13 @@
         <v>3</v>
       </c>
       <c r="D194" s="1" t="s">
-        <v>68</v>
+        <v>100</v>
       </c>
       <c r="E194" s="1" t="s">
-        <v>112</v>
+        <v>4</v>
       </c>
       <c r="F194" s="1" t="s">
-        <v>25</v>
+        <v>5</v>
       </c>
     </row>
     <row r="195" spans="1:6" x14ac:dyDescent="0.25">
@@ -8592,7 +8562,7 @@
         <v>100</v>
       </c>
       <c r="E195" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F195" s="1" t="s">
         <v>9</v>
@@ -8612,10 +8582,10 @@
         <v>100</v>
       </c>
       <c r="E196" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F196" s="1" t="s">
-        <v>25</v>
+        <v>91</v>
       </c>
     </row>
     <row r="197" spans="1:6" x14ac:dyDescent="0.25">
@@ -8632,7 +8602,7 @@
         <v>100</v>
       </c>
       <c r="E197" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F197" s="1" t="s">
         <v>5</v>
@@ -8652,7 +8622,7 @@
         <v>100</v>
       </c>
       <c r="E198" s="1" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="F198" s="1" t="s">
         <v>9</v>
@@ -8672,7 +8642,7 @@
         <v>100</v>
       </c>
       <c r="E199" s="1" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="F199" s="1" t="s">
         <v>91</v>
@@ -8692,10 +8662,10 @@
         <v>100</v>
       </c>
       <c r="E200" s="1" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="F200" s="1" t="s">
-        <v>5</v>
+        <v>41</v>
       </c>
     </row>
     <row r="201" spans="1:6" x14ac:dyDescent="0.25">
@@ -8712,10 +8682,10 @@
         <v>100</v>
       </c>
       <c r="E201" s="1" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="F201" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="202" spans="1:6" x14ac:dyDescent="0.25">
@@ -8732,10 +8702,10 @@
         <v>100</v>
       </c>
       <c r="E202" s="1" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="F202" s="1" t="s">
-        <v>91</v>
+        <v>5</v>
       </c>
     </row>
     <row r="203" spans="1:6" x14ac:dyDescent="0.25">
@@ -8752,10 +8722,10 @@
         <v>100</v>
       </c>
       <c r="E203" s="1" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="F203" s="1" t="s">
-        <v>41</v>
+        <v>5</v>
       </c>
     </row>
     <row r="204" spans="1:6" x14ac:dyDescent="0.25">
@@ -8772,10 +8742,10 @@
         <v>100</v>
       </c>
       <c r="E204" s="1" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="F204" s="1" t="s">
-        <v>5</v>
+        <v>41</v>
       </c>
     </row>
     <row r="205" spans="1:6" x14ac:dyDescent="0.25">
@@ -8792,7 +8762,7 @@
         <v>100</v>
       </c>
       <c r="E205" s="1" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="F205" s="1" t="s">
         <v>5</v>
@@ -8812,7 +8782,7 @@
         <v>100</v>
       </c>
       <c r="E206" s="1" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="F206" s="1" t="s">
         <v>5</v>
@@ -8832,10 +8802,10 @@
         <v>100</v>
       </c>
       <c r="E207" s="1" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="F207" s="1" t="s">
-        <v>41</v>
+        <v>5</v>
       </c>
     </row>
     <row r="208" spans="1:6" x14ac:dyDescent="0.25">
@@ -8852,10 +8822,10 @@
         <v>100</v>
       </c>
       <c r="E208" s="1" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="F208" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="209" spans="1:6" x14ac:dyDescent="0.25">
@@ -8872,7 +8842,7 @@
         <v>100</v>
       </c>
       <c r="E209" s="1" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="F209" s="1" t="s">
         <v>5</v>
@@ -8892,10 +8862,10 @@
         <v>100</v>
       </c>
       <c r="E210" s="1" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="F210" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="211" spans="1:6" x14ac:dyDescent="0.25">
@@ -8912,7 +8882,7 @@
         <v>100</v>
       </c>
       <c r="E211" s="1" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="F211" s="1" t="s">
         <v>5</v>
@@ -8935,7 +8905,7 @@
         <v>24</v>
       </c>
       <c r="F212" s="1" t="s">
-        <v>5</v>
+        <v>41</v>
       </c>
     </row>
     <row r="213" spans="1:6" x14ac:dyDescent="0.25">
@@ -8955,7 +8925,7 @@
         <v>24</v>
       </c>
       <c r="F213" s="1" t="s">
-        <v>5</v>
+        <v>41</v>
       </c>
     </row>
     <row r="214" spans="1:6" x14ac:dyDescent="0.25">
@@ -8975,7 +8945,7 @@
         <v>28</v>
       </c>
       <c r="F214" s="1" t="s">
-        <v>5</v>
+        <v>25</v>
       </c>
     </row>
     <row r="215" spans="1:6" x14ac:dyDescent="0.25">
@@ -9015,7 +8985,7 @@
         <v>28</v>
       </c>
       <c r="F216" s="1" t="s">
-        <v>41</v>
+        <v>5</v>
       </c>
     </row>
     <row r="217" spans="1:6" x14ac:dyDescent="0.25">
@@ -9032,10 +9002,10 @@
         <v>100</v>
       </c>
       <c r="E217" s="1" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="F217" s="1" t="s">
-        <v>25</v>
+        <v>41</v>
       </c>
     </row>
     <row r="218" spans="1:6" x14ac:dyDescent="0.25">
@@ -9055,7 +9025,7 @@
         <v>31</v>
       </c>
       <c r="F218" s="1" t="s">
-        <v>5</v>
+        <v>25</v>
       </c>
     </row>
     <row r="219" spans="1:6" x14ac:dyDescent="0.25">
@@ -9069,13 +9039,13 @@
         <v>3</v>
       </c>
       <c r="D219" s="1" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="E219" s="1" t="s">
-        <v>34</v>
+        <v>4</v>
       </c>
       <c r="F219" s="1" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
     </row>
     <row r="220" spans="1:6" x14ac:dyDescent="0.25">
@@ -9092,10 +9062,10 @@
         <v>103</v>
       </c>
       <c r="E220" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F220" s="1" t="s">
-        <v>9</v>
+        <v>25</v>
       </c>
     </row>
     <row r="221" spans="1:6" x14ac:dyDescent="0.25">
@@ -9112,10 +9082,10 @@
         <v>103</v>
       </c>
       <c r="E221" s="1" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="F221" s="1" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
     </row>
     <row r="222" spans="1:6" x14ac:dyDescent="0.25">
@@ -9132,10 +9102,10 @@
         <v>103</v>
       </c>
       <c r="E222" s="1" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="F222" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="223" spans="1:6" x14ac:dyDescent="0.25">
@@ -9152,10 +9122,10 @@
         <v>103</v>
       </c>
       <c r="E223" s="1" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="F223" s="1" t="s">
-        <v>5</v>
+        <v>25</v>
       </c>
     </row>
     <row r="224" spans="1:6" x14ac:dyDescent="0.25">
@@ -9172,7 +9142,7 @@
         <v>103</v>
       </c>
       <c r="E224" s="1" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="F224" s="1" t="s">
         <v>25</v>
@@ -9192,10 +9162,10 @@
         <v>103</v>
       </c>
       <c r="E225" s="1" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="F225" s="1" t="s">
-        <v>25</v>
+        <v>41</v>
       </c>
     </row>
     <row r="226" spans="1:6" x14ac:dyDescent="0.25">
@@ -9212,10 +9182,10 @@
         <v>103</v>
       </c>
       <c r="E226" s="1" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="F226" s="1" t="s">
-        <v>41</v>
+        <v>5</v>
       </c>
     </row>
     <row r="227" spans="1:6" x14ac:dyDescent="0.25">
@@ -9232,7 +9202,7 @@
         <v>103</v>
       </c>
       <c r="E227" s="1" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="F227" s="1" t="s">
         <v>5</v>
@@ -9252,10 +9222,10 @@
         <v>103</v>
       </c>
       <c r="E228" s="1" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="F228" s="1" t="s">
-        <v>5</v>
+        <v>41</v>
       </c>
     </row>
     <row r="229" spans="1:6" x14ac:dyDescent="0.25">
@@ -9269,13 +9239,13 @@
         <v>3</v>
       </c>
       <c r="D229" s="1" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="E229" s="1" t="s">
-        <v>34</v>
+        <v>4</v>
       </c>
       <c r="F229" s="1" t="s">
-        <v>41</v>
+        <v>25</v>
       </c>
     </row>
     <row r="230" spans="1:6" x14ac:dyDescent="0.25">
@@ -9292,7 +9262,7 @@
         <v>106</v>
       </c>
       <c r="E230" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F230" s="1" t="s">
         <v>25</v>
@@ -9312,7 +9282,7 @@
         <v>106</v>
       </c>
       <c r="E231" s="1" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="F231" s="1" t="s">
         <v>25</v>
@@ -9332,10 +9302,10 @@
         <v>106</v>
       </c>
       <c r="E232" s="1" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="F232" s="1" t="s">
-        <v>25</v>
+        <v>133</v>
       </c>
     </row>
     <row r="233" spans="1:6" x14ac:dyDescent="0.25">
@@ -9352,10 +9322,10 @@
         <v>106</v>
       </c>
       <c r="E233" s="1" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="F233" s="1" t="s">
-        <v>133</v>
+        <v>25</v>
       </c>
     </row>
     <row r="234" spans="1:6" x14ac:dyDescent="0.25">
@@ -9372,7 +9342,7 @@
         <v>106</v>
       </c>
       <c r="E234" s="1" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="F234" s="1" t="s">
         <v>25</v>
@@ -9392,10 +9362,10 @@
         <v>106</v>
       </c>
       <c r="E235" s="1" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="F235" s="1" t="s">
-        <v>25</v>
+        <v>5</v>
       </c>
     </row>
     <row r="236" spans="1:6" x14ac:dyDescent="0.25">
@@ -9412,7 +9382,7 @@
         <v>106</v>
       </c>
       <c r="E236" s="1" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="F236" s="1" t="s">
         <v>5</v>
@@ -9432,7 +9402,7 @@
         <v>106</v>
       </c>
       <c r="E237" s="1" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="F237" s="1" t="s">
         <v>5</v>
@@ -9452,10 +9422,10 @@
         <v>106</v>
       </c>
       <c r="E238" s="1" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="F238" s="1" t="s">
-        <v>5</v>
+        <v>41</v>
       </c>
     </row>
     <row r="239" spans="1:6" x14ac:dyDescent="0.25">
@@ -9469,13 +9439,13 @@
         <v>3</v>
       </c>
       <c r="D239" s="1" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="E239" s="1" t="s">
-        <v>34</v>
+        <v>4</v>
       </c>
       <c r="F239" s="1" t="s">
-        <v>41</v>
+        <v>9</v>
       </c>
     </row>
     <row r="240" spans="1:6" x14ac:dyDescent="0.25">
@@ -9492,7 +9462,7 @@
         <v>109</v>
       </c>
       <c r="E240" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F240" s="1" t="s">
         <v>9</v>
@@ -9512,10 +9482,10 @@
         <v>109</v>
       </c>
       <c r="E241" s="1" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="F241" s="1" t="s">
-        <v>9</v>
+        <v>133</v>
       </c>
     </row>
     <row r="242" spans="1:6" x14ac:dyDescent="0.25">
@@ -9532,10 +9502,10 @@
         <v>109</v>
       </c>
       <c r="E242" s="1" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="F242" s="1" t="s">
-        <v>133</v>
+        <v>25</v>
       </c>
     </row>
     <row r="243" spans="1:6" x14ac:dyDescent="0.25">
@@ -9552,7 +9522,7 @@
         <v>109</v>
       </c>
       <c r="E243" s="1" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="F243" s="1" t="s">
         <v>25</v>
@@ -9572,7 +9542,7 @@
         <v>109</v>
       </c>
       <c r="E244" s="1" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="F244" s="1" t="s">
         <v>25</v>
@@ -9592,18 +9562,18 @@
         <v>109</v>
       </c>
       <c r="E245" s="1" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="F245" s="1" t="s">
-        <v>25</v>
+        <v>523</v>
       </c>
     </row>
     <row r="246" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A246" s="1" t="s">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="B246" s="1" t="s">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="C246" s="1" t="s">
         <v>3</v>
@@ -9612,10 +9582,10 @@
         <v>109</v>
       </c>
       <c r="E246" s="1" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="F246" s="1" t="s">
-        <v>525</v>
+        <v>523</v>
       </c>
     </row>
     <row r="247" spans="1:6" x14ac:dyDescent="0.25">
@@ -9632,10 +9602,10 @@
         <v>109</v>
       </c>
       <c r="E247" s="1" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="F247" s="1" t="s">
-        <v>525</v>
+        <v>5</v>
       </c>
     </row>
     <row r="248" spans="1:6" x14ac:dyDescent="0.25">
@@ -10015,7 +9985,7 @@
         <v>31</v>
       </c>
       <c r="F266" s="1" t="s">
-        <v>5</v>
+        <v>41</v>
       </c>
     </row>
     <row r="267" spans="1:6" x14ac:dyDescent="0.25">
@@ -11035,7 +11005,7 @@
         <v>103</v>
       </c>
       <c r="F317" s="1" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
     </row>
     <row r="318" spans="1:6" x14ac:dyDescent="0.25">
@@ -11455,7 +11425,7 @@
         <v>24</v>
       </c>
       <c r="F338" s="1" t="s">
-        <v>5</v>
+        <v>41</v>
       </c>
     </row>
     <row r="339" spans="1:6" x14ac:dyDescent="0.25">
@@ -12855,7 +12825,7 @@
         <v>12</v>
       </c>
       <c r="F408" s="1" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
     </row>
     <row r="409" spans="1:6" x14ac:dyDescent="0.25">
@@ -15235,7 +15205,7 @@
         <v>24</v>
       </c>
       <c r="F527" s="1" t="s">
-        <v>5</v>
+        <v>80</v>
       </c>
     </row>
     <row r="528" spans="1:6" x14ac:dyDescent="0.25">
@@ -15252,7 +15222,7 @@
         <v>1066</v>
       </c>
       <c r="E528" s="1" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="F528" s="1" t="s">
         <v>80</v>
@@ -15275,7 +15245,7 @@
         <v>28</v>
       </c>
       <c r="F529" s="1" t="s">
-        <v>80</v>
+        <v>25</v>
       </c>
     </row>
     <row r="530" spans="1:6" x14ac:dyDescent="0.25">
@@ -15295,7 +15265,7 @@
         <v>28</v>
       </c>
       <c r="F530" s="1" t="s">
-        <v>25</v>
+        <v>5</v>
       </c>
     </row>
     <row r="531" spans="1:6" x14ac:dyDescent="0.25">
@@ -15312,10 +15282,10 @@
         <v>1066</v>
       </c>
       <c r="E531" s="1" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="F531" s="1" t="s">
-        <v>5</v>
+        <v>25</v>
       </c>
     </row>
     <row r="532" spans="1:6" x14ac:dyDescent="0.25">
@@ -15335,7 +15305,7 @@
         <v>31</v>
       </c>
       <c r="F532" s="1" t="s">
-        <v>25</v>
+        <v>133</v>
       </c>
     </row>
     <row r="533" spans="1:6" x14ac:dyDescent="0.25">
@@ -15355,7 +15325,7 @@
         <v>31</v>
       </c>
       <c r="F533" s="1" t="s">
-        <v>133</v>
+        <v>5</v>
       </c>
     </row>
     <row r="534" spans="1:6" x14ac:dyDescent="0.25">
@@ -15372,10 +15342,10 @@
         <v>1066</v>
       </c>
       <c r="E534" s="1" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="F534" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="535" spans="1:6" x14ac:dyDescent="0.25">
@@ -15395,7 +15365,7 @@
         <v>34</v>
       </c>
       <c r="F535" s="1" t="s">
-        <v>9</v>
+        <v>25</v>
       </c>
     </row>
     <row r="536" spans="1:6" x14ac:dyDescent="0.25">
@@ -15415,7 +15385,7 @@
         <v>34</v>
       </c>
       <c r="F536" s="1" t="s">
-        <v>25</v>
+        <v>133</v>
       </c>
     </row>
     <row r="537" spans="1:6" x14ac:dyDescent="0.25">
@@ -15432,10 +15402,10 @@
         <v>1066</v>
       </c>
       <c r="E537" s="1" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="F537" s="1" t="s">
-        <v>133</v>
+        <v>5</v>
       </c>
     </row>
     <row r="538" spans="1:6" x14ac:dyDescent="0.25">
@@ -15472,10 +15442,10 @@
         <v>1066</v>
       </c>
       <c r="E539" s="1" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="F539" s="1" t="s">
-        <v>5</v>
+        <v>80</v>
       </c>
     </row>
     <row r="540" spans="1:6" x14ac:dyDescent="0.25">
@@ -15495,7 +15465,7 @@
         <v>40</v>
       </c>
       <c r="F540" s="1" t="s">
-        <v>80</v>
+        <v>5</v>
       </c>
     </row>
     <row r="541" spans="1:6" x14ac:dyDescent="0.25">
@@ -15512,7 +15482,7 @@
         <v>1066</v>
       </c>
       <c r="E541" s="1" t="s">
-        <v>40</v>
+        <v>68</v>
       </c>
       <c r="F541" s="1" t="s">
         <v>5</v>
@@ -15532,7 +15502,7 @@
         <v>1066</v>
       </c>
       <c r="E542" s="1" t="s">
-        <v>68</v>
+        <v>100</v>
       </c>
       <c r="F542" s="1" t="s">
         <v>5</v>
@@ -15552,7 +15522,7 @@
         <v>1066</v>
       </c>
       <c r="E543" s="1" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="F543" s="1" t="s">
         <v>5</v>
@@ -15569,10 +15539,10 @@
         <v>3</v>
       </c>
       <c r="D544" s="1" t="s">
-        <v>1066</v>
+        <v>1139</v>
       </c>
       <c r="E544" s="1" t="s">
-        <v>103</v>
+        <v>4</v>
       </c>
       <c r="F544" s="1" t="s">
         <v>5</v>
@@ -15580,22 +15550,22 @@
     </row>
     <row r="545" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A545" s="1" t="s">
+        <v>1140</v>
+      </c>
+      <c r="B545" s="1" t="s">
+        <v>1141</v>
+      </c>
+      <c r="C545" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D545" s="1" t="s">
         <v>1139</v>
       </c>
-      <c r="B545" s="1" t="s">
-        <v>1140</v>
-      </c>
-      <c r="C545" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D545" s="1" t="s">
-        <v>1141</v>
-      </c>
       <c r="E545" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F545" s="1" t="s">
-        <v>5</v>
+        <v>80</v>
       </c>
     </row>
     <row r="546" spans="1:6" x14ac:dyDescent="0.25">
@@ -15609,13 +15579,13 @@
         <v>3</v>
       </c>
       <c r="D546" s="1" t="s">
-        <v>1141</v>
+        <v>1139</v>
       </c>
       <c r="E546" s="1" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="F546" s="1" t="s">
-        <v>80</v>
+        <v>5</v>
       </c>
     </row>
     <row r="547" spans="1:6" x14ac:dyDescent="0.25">
@@ -15629,10 +15599,10 @@
         <v>3</v>
       </c>
       <c r="D547" s="1" t="s">
-        <v>1141</v>
+        <v>1139</v>
       </c>
       <c r="E547" s="1" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="F547" s="1" t="s">
         <v>5</v>
@@ -15649,10 +15619,10 @@
         <v>3</v>
       </c>
       <c r="D548" s="1" t="s">
-        <v>1141</v>
+        <v>1139</v>
       </c>
       <c r="E548" s="1" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="F548" s="1" t="s">
         <v>5</v>
@@ -15669,10 +15639,10 @@
         <v>3</v>
       </c>
       <c r="D549" s="1" t="s">
-        <v>1141</v>
+        <v>1139</v>
       </c>
       <c r="E549" s="1" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="F549" s="1" t="s">
         <v>5</v>
@@ -15689,13 +15659,13 @@
         <v>3</v>
       </c>
       <c r="D550" s="1" t="s">
-        <v>1141</v>
+        <v>1139</v>
       </c>
       <c r="E550" s="1" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="F550" s="1" t="s">
-        <v>5</v>
+        <v>25</v>
       </c>
     </row>
     <row r="551" spans="1:6" x14ac:dyDescent="0.25">
@@ -15709,13 +15679,13 @@
         <v>3</v>
       </c>
       <c r="D551" s="1" t="s">
-        <v>1141</v>
+        <v>1139</v>
       </c>
       <c r="E551" s="1" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="F551" s="1" t="s">
-        <v>25</v>
+        <v>5</v>
       </c>
     </row>
     <row r="552" spans="1:6" x14ac:dyDescent="0.25">
@@ -15729,13 +15699,13 @@
         <v>3</v>
       </c>
       <c r="D552" s="1" t="s">
-        <v>1141</v>
+        <v>1139</v>
       </c>
       <c r="E552" s="1" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="F552" s="1" t="s">
-        <v>5</v>
+        <v>80</v>
       </c>
     </row>
     <row r="553" spans="1:6" x14ac:dyDescent="0.25">
@@ -15749,10 +15719,10 @@
         <v>3</v>
       </c>
       <c r="D553" s="1" t="s">
-        <v>1141</v>
+        <v>1139</v>
       </c>
       <c r="E553" s="1" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="F553" s="1" t="s">
         <v>80</v>
@@ -15769,13 +15739,13 @@
         <v>3</v>
       </c>
       <c r="D554" s="1" t="s">
-        <v>1141</v>
+        <v>1139</v>
       </c>
       <c r="E554" s="1" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="F554" s="1" t="s">
-        <v>80</v>
+        <v>5</v>
       </c>
     </row>
     <row r="555" spans="1:6" x14ac:dyDescent="0.25">
@@ -15789,10 +15759,10 @@
         <v>3</v>
       </c>
       <c r="D555" s="1" t="s">
-        <v>1141</v>
+        <v>1139</v>
       </c>
       <c r="E555" s="1" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="F555" s="1" t="s">
         <v>5</v>
@@ -15809,10 +15779,10 @@
         <v>3</v>
       </c>
       <c r="D556" s="1" t="s">
-        <v>1141</v>
+        <v>1139</v>
       </c>
       <c r="E556" s="1" t="s">
-        <v>40</v>
+        <v>68</v>
       </c>
       <c r="F556" s="1" t="s">
         <v>5</v>
@@ -15829,13 +15799,13 @@
         <v>3</v>
       </c>
       <c r="D557" s="1" t="s">
-        <v>1141</v>
+        <v>1139</v>
       </c>
       <c r="E557" s="1" t="s">
-        <v>68</v>
+        <v>100</v>
       </c>
       <c r="F557" s="1" t="s">
-        <v>5</v>
+        <v>80</v>
       </c>
     </row>
     <row r="558" spans="1:6" x14ac:dyDescent="0.25">
@@ -15849,10 +15819,10 @@
         <v>3</v>
       </c>
       <c r="D558" s="1" t="s">
-        <v>1141</v>
+        <v>1168</v>
       </c>
       <c r="E558" s="1" t="s">
-        <v>100</v>
+        <v>4</v>
       </c>
       <c r="F558" s="1" t="s">
         <v>80</v>
@@ -15860,22 +15830,22 @@
     </row>
     <row r="559" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A559" s="1" t="s">
+        <v>1169</v>
+      </c>
+      <c r="B559" s="1" t="s">
+        <v>1170</v>
+      </c>
+      <c r="C559" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D559" s="1" t="s">
         <v>1168</v>
       </c>
-      <c r="B559" s="1" t="s">
-        <v>1169</v>
-      </c>
-      <c r="C559" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D559" s="1" t="s">
-        <v>1170</v>
-      </c>
       <c r="E559" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F559" s="1" t="s">
-        <v>80</v>
+        <v>5</v>
       </c>
     </row>
     <row r="560" spans="1:6" x14ac:dyDescent="0.25">
@@ -15889,13 +15859,13 @@
         <v>3</v>
       </c>
       <c r="D560" s="1" t="s">
-        <v>1170</v>
+        <v>1168</v>
       </c>
       <c r="E560" s="1" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="F560" s="1" t="s">
-        <v>5</v>
+        <v>80</v>
       </c>
     </row>
     <row r="561" spans="1:6" x14ac:dyDescent="0.25">
@@ -15909,10 +15879,10 @@
         <v>3</v>
       </c>
       <c r="D561" s="1" t="s">
-        <v>1170</v>
+        <v>1168</v>
       </c>
       <c r="E561" s="1" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="F561" s="1" t="s">
         <v>80</v>
@@ -15929,10 +15899,10 @@
         <v>3</v>
       </c>
       <c r="D562" s="1" t="s">
-        <v>1170</v>
+        <v>1168</v>
       </c>
       <c r="E562" s="1" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="F562" s="1" t="s">
         <v>80</v>
@@ -15949,13 +15919,13 @@
         <v>3</v>
       </c>
       <c r="D563" s="1" t="s">
-        <v>1170</v>
+        <v>1168</v>
       </c>
       <c r="E563" s="1" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="F563" s="1" t="s">
-        <v>80</v>
+        <v>5</v>
       </c>
     </row>
     <row r="564" spans="1:6" x14ac:dyDescent="0.25">
@@ -15969,10 +15939,10 @@
         <v>3</v>
       </c>
       <c r="D564" s="1" t="s">
-        <v>1170</v>
+        <v>1168</v>
       </c>
       <c r="E564" s="1" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="F564" s="1" t="s">
         <v>5</v>
@@ -15989,10 +15959,10 @@
         <v>3</v>
       </c>
       <c r="D565" s="1" t="s">
-        <v>1170</v>
+        <v>1168</v>
       </c>
       <c r="E565" s="1" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="F565" s="1" t="s">
         <v>5</v>
@@ -16009,10 +15979,10 @@
         <v>3</v>
       </c>
       <c r="D566" s="1" t="s">
-        <v>1170</v>
+        <v>1168</v>
       </c>
       <c r="E566" s="1" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="F566" s="1" t="s">
         <v>5</v>
@@ -16029,10 +15999,10 @@
         <v>3</v>
       </c>
       <c r="D567" s="1" t="s">
-        <v>1170</v>
+        <v>1168</v>
       </c>
       <c r="E567" s="1" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="F567" s="1" t="s">
         <v>5</v>
@@ -16049,10 +16019,10 @@
         <v>3</v>
       </c>
       <c r="D568" s="1" t="s">
-        <v>1170</v>
+        <v>1168</v>
       </c>
       <c r="E568" s="1" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="F568" s="1" t="s">
         <v>5</v>
@@ -16069,10 +16039,10 @@
         <v>3</v>
       </c>
       <c r="D569" s="1" t="s">
-        <v>1170</v>
+        <v>1168</v>
       </c>
       <c r="E569" s="1" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="F569" s="1" t="s">
         <v>5</v>
@@ -16089,10 +16059,10 @@
         <v>3</v>
       </c>
       <c r="D570" s="1" t="s">
-        <v>1170</v>
+        <v>1168</v>
       </c>
       <c r="E570" s="1" t="s">
-        <v>40</v>
+        <v>68</v>
       </c>
       <c r="F570" s="1" t="s">
         <v>5</v>
@@ -16109,10 +16079,10 @@
         <v>3</v>
       </c>
       <c r="D571" s="1" t="s">
-        <v>1170</v>
+        <v>1195</v>
       </c>
       <c r="E571" s="1" t="s">
-        <v>68</v>
+        <v>4</v>
       </c>
       <c r="F571" s="1" t="s">
         <v>5</v>
@@ -16120,19 +16090,19 @@
     </row>
     <row r="572" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A572" s="1" t="s">
+        <v>1196</v>
+      </c>
+      <c r="B572" s="1" t="s">
+        <v>1197</v>
+      </c>
+      <c r="C572" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D572" s="1" t="s">
         <v>1195</v>
       </c>
-      <c r="B572" s="1" t="s">
-        <v>1196</v>
-      </c>
-      <c r="C572" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D572" s="1" t="s">
-        <v>1197</v>
-      </c>
       <c r="E572" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F572" s="1" t="s">
         <v>5</v>
@@ -16149,33 +16119,33 @@
         <v>3</v>
       </c>
       <c r="D573" s="1" t="s">
-        <v>1197</v>
+        <v>1195</v>
       </c>
       <c r="E573" s="1" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="F573" s="1" t="s">
-        <v>5</v>
+        <v>1200</v>
       </c>
     </row>
     <row r="574" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A574" s="1" t="s">
+        <v>1201</v>
+      </c>
+      <c r="B574" s="1" t="s">
+        <v>1202</v>
+      </c>
+      <c r="C574" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D574" s="1" t="s">
+        <v>1195</v>
+      </c>
+      <c r="E574" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="F574" s="1" t="s">
         <v>1200</v>
-      </c>
-      <c r="B574" s="1" t="s">
-        <v>1201</v>
-      </c>
-      <c r="C574" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D574" s="1" t="s">
-        <v>1197</v>
-      </c>
-      <c r="E574" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="F574" s="1" t="s">
-        <v>1202</v>
       </c>
     </row>
     <row r="575" spans="1:6" x14ac:dyDescent="0.25">
@@ -16189,13 +16159,13 @@
         <v>3</v>
       </c>
       <c r="D575" s="1" t="s">
-        <v>1197</v>
+        <v>1195</v>
       </c>
       <c r="E575" s="1" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="F575" s="1" t="s">
-        <v>1202</v>
+        <v>5</v>
       </c>
     </row>
     <row r="576" spans="1:6" x14ac:dyDescent="0.25">
@@ -16209,10 +16179,10 @@
         <v>3</v>
       </c>
       <c r="D576" s="1" t="s">
-        <v>1197</v>
+        <v>1195</v>
       </c>
       <c r="E576" s="1" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="F576" s="1" t="s">
         <v>5</v>
@@ -16229,10 +16199,10 @@
         <v>3</v>
       </c>
       <c r="D577" s="1" t="s">
-        <v>1197</v>
+        <v>1195</v>
       </c>
       <c r="E577" s="1" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="F577" s="1" t="s">
         <v>5</v>
@@ -16249,10 +16219,10 @@
         <v>3</v>
       </c>
       <c r="D578" s="1" t="s">
-        <v>1197</v>
+        <v>1195</v>
       </c>
       <c r="E578" s="1" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="F578" s="1" t="s">
         <v>5</v>
@@ -16269,13 +16239,13 @@
         <v>3</v>
       </c>
       <c r="D579" s="1" t="s">
-        <v>1197</v>
+        <v>1195</v>
       </c>
       <c r="E579" s="1" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="F579" s="1" t="s">
-        <v>5</v>
+        <v>41</v>
       </c>
     </row>
     <row r="580" spans="1:6" x14ac:dyDescent="0.25">
@@ -16289,13 +16259,13 @@
         <v>3</v>
       </c>
       <c r="D580" s="1" t="s">
-        <v>1197</v>
+        <v>1195</v>
       </c>
       <c r="E580" s="1" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="F580" s="1" t="s">
-        <v>41</v>
+        <v>5</v>
       </c>
     </row>
     <row r="581" spans="1:6" x14ac:dyDescent="0.25">
@@ -16309,10 +16279,10 @@
         <v>3</v>
       </c>
       <c r="D581" s="1" t="s">
-        <v>1197</v>
+        <v>1195</v>
       </c>
       <c r="E581" s="1" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="F581" s="1" t="s">
         <v>5</v>
@@ -16329,10 +16299,10 @@
         <v>3</v>
       </c>
       <c r="D582" s="1" t="s">
-        <v>1197</v>
+        <v>1195</v>
       </c>
       <c r="E582" s="1" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="F582" s="1" t="s">
         <v>5</v>
@@ -16349,10 +16319,10 @@
         <v>3</v>
       </c>
       <c r="D583" s="1" t="s">
-        <v>1197</v>
+        <v>1195</v>
       </c>
       <c r="E583" s="1" t="s">
-        <v>40</v>
+        <v>68</v>
       </c>
       <c r="F583" s="1" t="s">
         <v>5</v>
@@ -16369,30 +16339,30 @@
         <v>3</v>
       </c>
       <c r="D584" s="1" t="s">
-        <v>1197</v>
+        <v>1223</v>
       </c>
       <c r="E584" s="1" t="s">
-        <v>68</v>
+        <v>4</v>
       </c>
       <c r="F584" s="1" t="s">
-        <v>5</v>
+        <v>41</v>
       </c>
     </row>
     <row r="585" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A585" s="1" t="s">
+        <v>1224</v>
+      </c>
+      <c r="B585" s="1" t="s">
+        <v>1225</v>
+      </c>
+      <c r="C585" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D585" s="1" t="s">
         <v>1223</v>
       </c>
-      <c r="B585" s="1" t="s">
-        <v>1224</v>
-      </c>
-      <c r="C585" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D585" s="1" t="s">
-        <v>1225</v>
-      </c>
       <c r="E585" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F585" s="1" t="s">
         <v>41</v>
@@ -16409,10 +16379,10 @@
         <v>3</v>
       </c>
       <c r="D586" s="1" t="s">
-        <v>1225</v>
+        <v>1223</v>
       </c>
       <c r="E586" s="1" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="F586" s="1" t="s">
         <v>41</v>
@@ -16429,13 +16399,13 @@
         <v>3</v>
       </c>
       <c r="D587" s="1" t="s">
-        <v>1225</v>
+        <v>1223</v>
       </c>
       <c r="E587" s="1" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="F587" s="1" t="s">
-        <v>41</v>
+        <v>133</v>
       </c>
     </row>
     <row r="588" spans="1:6" x14ac:dyDescent="0.25">
@@ -16449,13 +16419,13 @@
         <v>3</v>
       </c>
       <c r="D588" s="1" t="s">
-        <v>1225</v>
+        <v>1223</v>
       </c>
       <c r="E588" s="1" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="F588" s="1" t="s">
-        <v>133</v>
+        <v>5</v>
       </c>
     </row>
     <row r="589" spans="1:6" x14ac:dyDescent="0.25">
@@ -16469,10 +16439,10 @@
         <v>3</v>
       </c>
       <c r="D589" s="1" t="s">
-        <v>1225</v>
+        <v>1223</v>
       </c>
       <c r="E589" s="1" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="F589" s="1" t="s">
         <v>5</v>
@@ -16489,10 +16459,10 @@
         <v>3</v>
       </c>
       <c r="D590" s="1" t="s">
-        <v>1225</v>
+        <v>1223</v>
       </c>
       <c r="E590" s="1" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="F590" s="1" t="s">
         <v>5</v>
@@ -16509,10 +16479,10 @@
         <v>3</v>
       </c>
       <c r="D591" s="1" t="s">
-        <v>1225</v>
+        <v>1223</v>
       </c>
       <c r="E591" s="1" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="F591" s="1" t="s">
         <v>5</v>
@@ -16529,10 +16499,10 @@
         <v>3</v>
       </c>
       <c r="D592" s="1" t="s">
-        <v>1225</v>
+        <v>1223</v>
       </c>
       <c r="E592" s="1" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="F592" s="1" t="s">
         <v>5</v>
@@ -16549,10 +16519,10 @@
         <v>3</v>
       </c>
       <c r="D593" s="1" t="s">
-        <v>1225</v>
+        <v>1223</v>
       </c>
       <c r="E593" s="1" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="F593" s="1" t="s">
         <v>5</v>
@@ -16569,10 +16539,10 @@
         <v>3</v>
       </c>
       <c r="D594" s="1" t="s">
-        <v>1225</v>
+        <v>1223</v>
       </c>
       <c r="E594" s="1" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="F594" s="1" t="s">
         <v>5</v>
@@ -16589,10 +16559,10 @@
         <v>3</v>
       </c>
       <c r="D595" s="1" t="s">
-        <v>1225</v>
+        <v>1223</v>
       </c>
       <c r="E595" s="1" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="F595" s="1" t="s">
         <v>5</v>
@@ -16609,10 +16579,10 @@
         <v>3</v>
       </c>
       <c r="D596" s="1" t="s">
-        <v>1225</v>
+        <v>1223</v>
       </c>
       <c r="E596" s="1" t="s">
-        <v>40</v>
+        <v>68</v>
       </c>
       <c r="F596" s="1" t="s">
         <v>5</v>
@@ -16629,10 +16599,10 @@
         <v>3</v>
       </c>
       <c r="D597" s="1" t="s">
-        <v>1225</v>
+        <v>1223</v>
       </c>
       <c r="E597" s="1" t="s">
-        <v>68</v>
+        <v>100</v>
       </c>
       <c r="F597" s="1" t="s">
         <v>5</v>
@@ -16649,13 +16619,13 @@
         <v>3</v>
       </c>
       <c r="D598" s="1" t="s">
-        <v>1225</v>
+        <v>1223</v>
       </c>
       <c r="E598" s="1" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="F598" s="1" t="s">
-        <v>5</v>
+        <v>41</v>
       </c>
     </row>
     <row r="599" spans="1:6" x14ac:dyDescent="0.25">
@@ -16669,13 +16639,13 @@
         <v>3</v>
       </c>
       <c r="D599" s="1" t="s">
-        <v>1225</v>
+        <v>1223</v>
       </c>
       <c r="E599" s="1" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="F599" s="1" t="s">
-        <v>41</v>
+        <v>5</v>
       </c>
     </row>
     <row r="600" spans="1:6" x14ac:dyDescent="0.25">
@@ -16689,10 +16659,10 @@
         <v>3</v>
       </c>
       <c r="D600" s="1" t="s">
-        <v>1225</v>
+        <v>1223</v>
       </c>
       <c r="E600" s="1" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="F600" s="1" t="s">
         <v>5</v>
@@ -16709,33 +16679,33 @@
         <v>3</v>
       </c>
       <c r="D601" s="1" t="s">
-        <v>1225</v>
+        <v>1258</v>
       </c>
       <c r="E601" s="1" t="s">
-        <v>109</v>
+        <v>4</v>
       </c>
       <c r="F601" s="1" t="s">
-        <v>5</v>
+        <v>80</v>
       </c>
     </row>
     <row r="602" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A602" s="1" t="s">
+        <v>1259</v>
+      </c>
+      <c r="B602" s="1" t="s">
+        <v>1260</v>
+      </c>
+      <c r="C602" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D602" s="1" t="s">
         <v>1258</v>
       </c>
-      <c r="B602" s="1" t="s">
-        <v>1259</v>
-      </c>
-      <c r="C602" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D602" s="1" t="s">
-        <v>1260</v>
-      </c>
       <c r="E602" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F602" s="1" t="s">
-        <v>80</v>
+        <v>41</v>
       </c>
     </row>
     <row r="603" spans="1:6" x14ac:dyDescent="0.25">
@@ -16749,13 +16719,13 @@
         <v>3</v>
       </c>
       <c r="D603" s="1" t="s">
-        <v>1260</v>
+        <v>1258</v>
       </c>
       <c r="E603" s="1" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="F603" s="1" t="s">
-        <v>41</v>
+        <v>5</v>
       </c>
     </row>
     <row r="604" spans="1:6" x14ac:dyDescent="0.25">
@@ -16769,10 +16739,10 @@
         <v>3</v>
       </c>
       <c r="D604" s="1" t="s">
-        <v>1260</v>
+        <v>1258</v>
       </c>
       <c r="E604" s="1" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="F604" s="1" t="s">
         <v>5</v>
@@ -16789,10 +16759,10 @@
         <v>3</v>
       </c>
       <c r="D605" s="1" t="s">
-        <v>1260</v>
+        <v>1258</v>
       </c>
       <c r="E605" s="1" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="F605" s="1" t="s">
         <v>5</v>
@@ -16809,13 +16779,13 @@
         <v>3</v>
       </c>
       <c r="D606" s="1" t="s">
-        <v>1260</v>
+        <v>1258</v>
       </c>
       <c r="E606" s="1" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="F606" s="1" t="s">
-        <v>5</v>
+        <v>41</v>
       </c>
     </row>
     <row r="607" spans="1:6" x14ac:dyDescent="0.25">
@@ -16829,10 +16799,10 @@
         <v>3</v>
       </c>
       <c r="D607" s="1" t="s">
-        <v>1260</v>
+        <v>1258</v>
       </c>
       <c r="E607" s="1" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="F607" s="1" t="s">
         <v>41</v>
@@ -16849,13 +16819,13 @@
         <v>3</v>
       </c>
       <c r="D608" s="1" t="s">
-        <v>1260</v>
+        <v>1258</v>
       </c>
       <c r="E608" s="1" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="F608" s="1" t="s">
-        <v>41</v>
+        <v>5</v>
       </c>
     </row>
     <row r="609" spans="1:6" x14ac:dyDescent="0.25">
@@ -16869,10 +16839,10 @@
         <v>3</v>
       </c>
       <c r="D609" s="1" t="s">
-        <v>1260</v>
+        <v>1258</v>
       </c>
       <c r="E609" s="1" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="F609" s="1" t="s">
         <v>5</v>
@@ -16889,13 +16859,13 @@
         <v>3</v>
       </c>
       <c r="D610" s="1" t="s">
-        <v>1260</v>
+        <v>1258</v>
       </c>
       <c r="E610" s="1" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="F610" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="611" spans="1:6" x14ac:dyDescent="0.25">
@@ -16909,13 +16879,13 @@
         <v>3</v>
       </c>
       <c r="D611" s="1" t="s">
-        <v>1260</v>
+        <v>1258</v>
       </c>
       <c r="E611" s="1" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="F611" s="1" t="s">
-        <v>9</v>
+        <v>25</v>
       </c>
     </row>
     <row r="612" spans="1:6" x14ac:dyDescent="0.25">
@@ -16929,13 +16899,13 @@
         <v>3</v>
       </c>
       <c r="D612" s="1" t="s">
-        <v>1260</v>
+        <v>1258</v>
       </c>
       <c r="E612" s="1" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="F612" s="1" t="s">
-        <v>25</v>
+        <v>41</v>
       </c>
     </row>
     <row r="613" spans="1:6" x14ac:dyDescent="0.25">
@@ -16949,10 +16919,10 @@
         <v>3</v>
       </c>
       <c r="D613" s="1" t="s">
-        <v>1260</v>
+        <v>1258</v>
       </c>
       <c r="E613" s="1" t="s">
-        <v>40</v>
+        <v>68</v>
       </c>
       <c r="F613" s="1" t="s">
         <v>41</v>
@@ -16969,10 +16939,10 @@
         <v>3</v>
       </c>
       <c r="D614" s="1" t="s">
-        <v>1260</v>
+        <v>1258</v>
       </c>
       <c r="E614" s="1" t="s">
-        <v>68</v>
+        <v>100</v>
       </c>
       <c r="F614" s="1" t="s">
         <v>41</v>
@@ -16989,10 +16959,10 @@
         <v>3</v>
       </c>
       <c r="D615" s="1" t="s">
-        <v>1260</v>
+        <v>1258</v>
       </c>
       <c r="E615" s="1" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="F615" s="1" t="s">
         <v>41</v>
@@ -17009,13 +16979,13 @@
         <v>3</v>
       </c>
       <c r="D616" s="1" t="s">
-        <v>1260</v>
+        <v>1258</v>
       </c>
       <c r="E616" s="1" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="F616" s="1" t="s">
-        <v>41</v>
+        <v>5</v>
       </c>
     </row>
     <row r="617" spans="1:6" x14ac:dyDescent="0.25">
@@ -17029,13 +16999,13 @@
         <v>3</v>
       </c>
       <c r="D617" s="1" t="s">
-        <v>1260</v>
+        <v>1258</v>
       </c>
       <c r="E617" s="1" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="F617" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="618" spans="1:6" x14ac:dyDescent="0.25">
@@ -17049,33 +17019,33 @@
         <v>3</v>
       </c>
       <c r="D618" s="1" t="s">
-        <v>1260</v>
+        <v>1293</v>
       </c>
       <c r="E618" s="1" t="s">
-        <v>109</v>
+        <v>4</v>
       </c>
       <c r="F618" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="619" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A619" s="1" t="s">
+        <v>1294</v>
+      </c>
+      <c r="B619" s="1" t="s">
+        <v>1295</v>
+      </c>
+      <c r="C619" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D619" s="1" t="s">
         <v>1293</v>
       </c>
-      <c r="B619" s="1" t="s">
-        <v>1294</v>
-      </c>
-      <c r="C619" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D619" s="1" t="s">
-        <v>1295</v>
-      </c>
       <c r="E619" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F619" s="1" t="s">
-        <v>5</v>
+        <v>41</v>
       </c>
     </row>
     <row r="620" spans="1:6" x14ac:dyDescent="0.25">
@@ -17089,13 +17059,13 @@
         <v>3</v>
       </c>
       <c r="D620" s="1" t="s">
-        <v>1295</v>
+        <v>1293</v>
       </c>
       <c r="E620" s="1" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="F620" s="1" t="s">
-        <v>41</v>
+        <v>5</v>
       </c>
     </row>
     <row r="621" spans="1:6" x14ac:dyDescent="0.25">
@@ -17109,10 +17079,10 @@
         <v>3</v>
       </c>
       <c r="D621" s="1" t="s">
-        <v>1295</v>
+        <v>1293</v>
       </c>
       <c r="E621" s="1" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="F621" s="1" t="s">
         <v>5</v>
@@ -17123,16 +17093,16 @@
         <v>1300</v>
       </c>
       <c r="B622" s="1" t="s">
-        <v>1301</v>
+        <v>1299</v>
       </c>
       <c r="C622" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D622" s="1" t="s">
-        <v>1295</v>
+        <v>1293</v>
       </c>
       <c r="E622" s="1" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="F622" s="1" t="s">
         <v>5</v>
@@ -17140,22 +17110,22 @@
     </row>
     <row r="623" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A623" s="1" t="s">
+        <v>1301</v>
+      </c>
+      <c r="B623" s="1" t="s">
         <v>1302</v>
       </c>
-      <c r="B623" s="1" t="s">
-        <v>1301</v>
-      </c>
       <c r="C623" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D623" s="1" t="s">
-        <v>1295</v>
+        <v>1293</v>
       </c>
       <c r="E623" s="1" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="F623" s="1" t="s">
-        <v>5</v>
+        <v>80</v>
       </c>
     </row>
     <row r="624" spans="1:6" x14ac:dyDescent="0.25">
@@ -17169,10 +17139,10 @@
         <v>3</v>
       </c>
       <c r="D624" s="1" t="s">
-        <v>1295</v>
+        <v>1293</v>
       </c>
       <c r="E624" s="1" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="F624" s="1" t="s">
         <v>80</v>
@@ -17189,13 +17159,13 @@
         <v>3</v>
       </c>
       <c r="D625" s="1" t="s">
-        <v>1295</v>
+        <v>1293</v>
       </c>
       <c r="E625" s="1" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="F625" s="1" t="s">
-        <v>80</v>
+        <v>25</v>
       </c>
     </row>
     <row r="626" spans="1:6" x14ac:dyDescent="0.25">
@@ -17209,10 +17179,10 @@
         <v>3</v>
       </c>
       <c r="D626" s="1" t="s">
-        <v>1295</v>
+        <v>1293</v>
       </c>
       <c r="E626" s="1" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="F626" s="1" t="s">
         <v>25</v>
@@ -17229,10 +17199,10 @@
         <v>3</v>
       </c>
       <c r="D627" s="1" t="s">
-        <v>1295</v>
+        <v>1293</v>
       </c>
       <c r="E627" s="1" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="F627" s="1" t="s">
         <v>25</v>
@@ -17249,10 +17219,10 @@
         <v>3</v>
       </c>
       <c r="D628" s="1" t="s">
-        <v>1295</v>
+        <v>1293</v>
       </c>
       <c r="E628" s="1" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="F628" s="1" t="s">
         <v>25</v>
@@ -17269,10 +17239,10 @@
         <v>3</v>
       </c>
       <c r="D629" s="1" t="s">
-        <v>1295</v>
+        <v>1293</v>
       </c>
       <c r="E629" s="1" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="F629" s="1" t="s">
         <v>25</v>
@@ -17289,10 +17259,10 @@
         <v>3</v>
       </c>
       <c r="D630" s="1" t="s">
-        <v>1295</v>
+        <v>1293</v>
       </c>
       <c r="E630" s="1" t="s">
-        <v>40</v>
+        <v>68</v>
       </c>
       <c r="F630" s="1" t="s">
         <v>25</v>
@@ -17309,13 +17279,13 @@
         <v>3</v>
       </c>
       <c r="D631" s="1" t="s">
-        <v>1295</v>
+        <v>1293</v>
       </c>
       <c r="E631" s="1" t="s">
-        <v>68</v>
+        <v>100</v>
       </c>
       <c r="F631" s="1" t="s">
-        <v>25</v>
+        <v>133</v>
       </c>
     </row>
     <row r="632" spans="1:6" x14ac:dyDescent="0.25">
@@ -17329,13 +17299,13 @@
         <v>3</v>
       </c>
       <c r="D632" s="1" t="s">
-        <v>1295</v>
+        <v>1293</v>
       </c>
       <c r="E632" s="1" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="F632" s="1" t="s">
-        <v>133</v>
+        <v>9</v>
       </c>
     </row>
     <row r="633" spans="1:6" x14ac:dyDescent="0.25">
@@ -17349,10 +17319,10 @@
         <v>3</v>
       </c>
       <c r="D633" s="1" t="s">
-        <v>1295</v>
+        <v>1293</v>
       </c>
       <c r="E633" s="1" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="F633" s="1" t="s">
         <v>9</v>
@@ -17369,10 +17339,10 @@
         <v>3</v>
       </c>
       <c r="D634" s="1" t="s">
-        <v>1295</v>
+        <v>1293</v>
       </c>
       <c r="E634" s="1" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="F634" s="1" t="s">
         <v>9</v>
@@ -17389,10 +17359,10 @@
         <v>3</v>
       </c>
       <c r="D635" s="1" t="s">
-        <v>1295</v>
+        <v>1293</v>
       </c>
       <c r="E635" s="1" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="F635" s="1" t="s">
         <v>9</v>
@@ -17409,33 +17379,33 @@
         <v>3</v>
       </c>
       <c r="D636" s="1" t="s">
-        <v>1295</v>
+        <v>1329</v>
       </c>
       <c r="E636" s="1" t="s">
-        <v>112</v>
+        <v>4</v>
       </c>
       <c r="F636" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="637" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A637" s="1" t="s">
+        <v>1330</v>
+      </c>
+      <c r="B637" s="1" t="s">
+        <v>1331</v>
+      </c>
+      <c r="C637" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D637" s="1" t="s">
         <v>1329</v>
       </c>
-      <c r="B637" s="1" t="s">
-        <v>1330</v>
-      </c>
-      <c r="C637" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D637" s="1" t="s">
-        <v>1331</v>
-      </c>
       <c r="E637" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F637" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="638" spans="1:6" x14ac:dyDescent="0.25">
@@ -17449,10 +17419,10 @@
         <v>3</v>
       </c>
       <c r="D638" s="1" t="s">
-        <v>1331</v>
+        <v>1329</v>
       </c>
       <c r="E638" s="1" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="F638" s="1" t="s">
         <v>9</v>
@@ -17469,10 +17439,10 @@
         <v>3</v>
       </c>
       <c r="D639" s="1" t="s">
-        <v>1331</v>
+        <v>1329</v>
       </c>
       <c r="E639" s="1" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="F639" s="1" t="s">
         <v>9</v>
@@ -17489,10 +17459,10 @@
         <v>3</v>
       </c>
       <c r="D640" s="1" t="s">
-        <v>1331</v>
+        <v>1329</v>
       </c>
       <c r="E640" s="1" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="F640" s="1" t="s">
         <v>9</v>
@@ -17509,13 +17479,13 @@
         <v>3</v>
       </c>
       <c r="D641" s="1" t="s">
-        <v>1331</v>
+        <v>1329</v>
       </c>
       <c r="E641" s="1" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="F641" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="642" spans="1:6" x14ac:dyDescent="0.25">
@@ -17529,13 +17499,13 @@
         <v>3</v>
       </c>
       <c r="D642" s="1" t="s">
-        <v>1331</v>
+        <v>1329</v>
       </c>
       <c r="E642" s="1" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="F642" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="643" spans="1:6" x14ac:dyDescent="0.25">
@@ -17549,13 +17519,13 @@
         <v>3</v>
       </c>
       <c r="D643" s="1" t="s">
-        <v>1331</v>
+        <v>1329</v>
       </c>
       <c r="E643" s="1" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="F643" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="644" spans="1:6" x14ac:dyDescent="0.25">
@@ -17569,13 +17539,13 @@
         <v>3</v>
       </c>
       <c r="D644" s="1" t="s">
-        <v>1331</v>
+        <v>1329</v>
       </c>
       <c r="E644" s="1" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="F644" s="1" t="s">
-        <v>5</v>
+        <v>25</v>
       </c>
     </row>
     <row r="645" spans="1:6" x14ac:dyDescent="0.25">
@@ -17589,13 +17559,13 @@
         <v>3</v>
       </c>
       <c r="D645" s="1" t="s">
-        <v>1331</v>
+        <v>1329</v>
       </c>
       <c r="E645" s="1" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="F645" s="1" t="s">
-        <v>25</v>
+        <v>5</v>
       </c>
     </row>
     <row r="646" spans="1:6" x14ac:dyDescent="0.25">
@@ -17609,13 +17579,13 @@
         <v>3</v>
       </c>
       <c r="D646" s="1" t="s">
-        <v>1331</v>
+        <v>1329</v>
       </c>
       <c r="E646" s="1" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="F646" s="1" t="s">
-        <v>5</v>
+        <v>25</v>
       </c>
     </row>
     <row r="647" spans="1:6" x14ac:dyDescent="0.25">
@@ -17629,10 +17599,10 @@
         <v>3</v>
       </c>
       <c r="D647" s="1" t="s">
-        <v>1331</v>
+        <v>1329</v>
       </c>
       <c r="E647" s="1" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="F647" s="1" t="s">
         <v>25</v>
@@ -17649,10 +17619,10 @@
         <v>3</v>
       </c>
       <c r="D648" s="1" t="s">
-        <v>1331</v>
+        <v>1329</v>
       </c>
       <c r="E648" s="1" t="s">
-        <v>40</v>
+        <v>68</v>
       </c>
       <c r="F648" s="1" t="s">
         <v>25</v>
@@ -17669,10 +17639,10 @@
         <v>3</v>
       </c>
       <c r="D649" s="1" t="s">
-        <v>1331</v>
+        <v>1329</v>
       </c>
       <c r="E649" s="1" t="s">
-        <v>68</v>
+        <v>100</v>
       </c>
       <c r="F649" s="1" t="s">
         <v>25</v>
@@ -17689,33 +17659,33 @@
         <v>3</v>
       </c>
       <c r="D650" s="1" t="s">
-        <v>1331</v>
+        <v>1358</v>
       </c>
       <c r="E650" s="1" t="s">
-        <v>100</v>
+        <v>4</v>
       </c>
       <c r="F650" s="1" t="s">
-        <v>25</v>
+        <v>1359</v>
       </c>
     </row>
     <row r="651" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A651" s="1" t="s">
+        <v>1360</v>
+      </c>
+      <c r="B651" s="1" t="s">
+        <v>1361</v>
+      </c>
+      <c r="C651" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D651" s="1" t="s">
         <v>1358</v>
       </c>
-      <c r="B651" s="1" t="s">
+      <c r="E651" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="F651" s="1" t="s">
         <v>1359</v>
-      </c>
-      <c r="C651" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D651" s="1" t="s">
-        <v>1360</v>
-      </c>
-      <c r="E651" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F651" s="1" t="s">
-        <v>1361</v>
       </c>
     </row>
     <row r="652" spans="1:6" x14ac:dyDescent="0.25">
@@ -17729,13 +17699,13 @@
         <v>3</v>
       </c>
       <c r="D652" s="1" t="s">
-        <v>1360</v>
+        <v>1358</v>
       </c>
       <c r="E652" s="1" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="F652" s="1" t="s">
-        <v>1361</v>
+        <v>1359</v>
       </c>
     </row>
     <row r="653" spans="1:6" x14ac:dyDescent="0.25">
@@ -17749,13 +17719,13 @@
         <v>3</v>
       </c>
       <c r="D653" s="1" t="s">
-        <v>1360</v>
+        <v>1358</v>
       </c>
       <c r="E653" s="1" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="F653" s="1" t="s">
-        <v>1361</v>
+        <v>1359</v>
       </c>
     </row>
     <row r="654" spans="1:6" x14ac:dyDescent="0.25">
@@ -17769,13 +17739,13 @@
         <v>3</v>
       </c>
       <c r="D654" s="1" t="s">
-        <v>1360</v>
+        <v>1358</v>
       </c>
       <c r="E654" s="1" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="F654" s="1" t="s">
-        <v>1361</v>
+        <v>1359</v>
       </c>
     </row>
     <row r="655" spans="1:6" x14ac:dyDescent="0.25">
@@ -17789,13 +17759,13 @@
         <v>3</v>
       </c>
       <c r="D655" s="1" t="s">
-        <v>1360</v>
+        <v>1358</v>
       </c>
       <c r="E655" s="1" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="F655" s="1" t="s">
-        <v>1361</v>
+        <v>1359</v>
       </c>
     </row>
     <row r="656" spans="1:6" x14ac:dyDescent="0.25">
@@ -17809,13 +17779,13 @@
         <v>3</v>
       </c>
       <c r="D656" s="1" t="s">
-        <v>1360</v>
+        <v>1358</v>
       </c>
       <c r="E656" s="1" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="F656" s="1" t="s">
-        <v>1361</v>
+        <v>1359</v>
       </c>
     </row>
     <row r="657" spans="1:6" x14ac:dyDescent="0.25">
@@ -17829,13 +17799,13 @@
         <v>3</v>
       </c>
       <c r="D657" s="1" t="s">
-        <v>1360</v>
+        <v>1358</v>
       </c>
       <c r="E657" s="1" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="F657" s="1" t="s">
-        <v>1361</v>
+        <v>231</v>
       </c>
     </row>
     <row r="658" spans="1:6" x14ac:dyDescent="0.25">
@@ -17849,13 +17819,13 @@
         <v>3</v>
       </c>
       <c r="D658" s="1" t="s">
-        <v>1360</v>
+        <v>1358</v>
       </c>
       <c r="E658" s="1" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="F658" s="1" t="s">
-        <v>233</v>
+        <v>5</v>
       </c>
     </row>
     <row r="659" spans="1:6" x14ac:dyDescent="0.25">
@@ -17869,13 +17839,13 @@
         <v>3</v>
       </c>
       <c r="D659" s="1" t="s">
-        <v>1360</v>
+        <v>1358</v>
       </c>
       <c r="E659" s="1" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="F659" s="1" t="s">
-        <v>5</v>
+        <v>1359</v>
       </c>
     </row>
     <row r="660" spans="1:6" x14ac:dyDescent="0.25">
@@ -17889,13 +17859,13 @@
         <v>3</v>
       </c>
       <c r="D660" s="1" t="s">
-        <v>1360</v>
+        <v>1358</v>
       </c>
       <c r="E660" s="1" t="s">
         <v>34</v>
       </c>
       <c r="F660" s="1" t="s">
-        <v>1361</v>
+        <v>1359</v>
       </c>
     </row>
     <row r="661" spans="1:6" x14ac:dyDescent="0.25">
@@ -17909,13 +17879,13 @@
         <v>3</v>
       </c>
       <c r="D661" s="1" t="s">
-        <v>1360</v>
+        <v>1358</v>
       </c>
       <c r="E661" s="1" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="F661" s="1" t="s">
-        <v>1361</v>
+        <v>1359</v>
       </c>
     </row>
     <row r="662" spans="1:6" x14ac:dyDescent="0.25">
@@ -17929,13 +17899,13 @@
         <v>3</v>
       </c>
       <c r="D662" s="1" t="s">
-        <v>1360</v>
+        <v>1358</v>
       </c>
       <c r="E662" s="1" t="s">
         <v>37</v>
       </c>
       <c r="F662" s="1" t="s">
-        <v>1361</v>
+        <v>1359</v>
       </c>
     </row>
     <row r="663" spans="1:6" x14ac:dyDescent="0.25">
@@ -17949,13 +17919,13 @@
         <v>3</v>
       </c>
       <c r="D663" s="1" t="s">
-        <v>1360</v>
+        <v>1358</v>
       </c>
       <c r="E663" s="1" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="F663" s="1" t="s">
-        <v>1361</v>
+        <v>231</v>
       </c>
     </row>
     <row r="664" spans="1:6" x14ac:dyDescent="0.25">
@@ -17969,13 +17939,13 @@
         <v>3</v>
       </c>
       <c r="D664" s="1" t="s">
-        <v>1360</v>
+        <v>1358</v>
       </c>
       <c r="E664" s="1" t="s">
-        <v>40</v>
+        <v>68</v>
       </c>
       <c r="F664" s="1" t="s">
-        <v>233</v>
+        <v>1359</v>
       </c>
     </row>
     <row r="665" spans="1:6" x14ac:dyDescent="0.25">
@@ -17989,30 +17959,30 @@
         <v>3</v>
       </c>
       <c r="D665" s="1" t="s">
-        <v>1360</v>
+        <v>1390</v>
       </c>
       <c r="E665" s="1" t="s">
-        <v>68</v>
+        <v>4</v>
       </c>
       <c r="F665" s="1" t="s">
-        <v>1361</v>
+        <v>5</v>
       </c>
     </row>
     <row r="666" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A666" s="1" t="s">
+        <v>1391</v>
+      </c>
+      <c r="B666" s="1" t="s">
+        <v>1392</v>
+      </c>
+      <c r="C666" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D666" s="1" t="s">
         <v>1390</v>
       </c>
-      <c r="B666" s="1" t="s">
-        <v>1391</v>
-      </c>
-      <c r="C666" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D666" s="1" t="s">
-        <v>1392</v>
-      </c>
       <c r="E666" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F666" s="1" t="s">
         <v>5</v>
@@ -18029,10 +17999,10 @@
         <v>3</v>
       </c>
       <c r="D667" s="1" t="s">
-        <v>1392</v>
+        <v>1390</v>
       </c>
       <c r="E667" s="1" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="F667" s="1" t="s">
         <v>5</v>
@@ -18049,13 +18019,13 @@
         <v>3</v>
       </c>
       <c r="D668" s="1" t="s">
-        <v>1392</v>
+        <v>1390</v>
       </c>
       <c r="E668" s="1" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="F668" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="669" spans="1:6" x14ac:dyDescent="0.25">
@@ -18069,10 +18039,10 @@
         <v>3</v>
       </c>
       <c r="D669" s="1" t="s">
-        <v>1392</v>
+        <v>1390</v>
       </c>
       <c r="E669" s="1" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="F669" s="1" t="s">
         <v>9</v>
@@ -18089,13 +18059,13 @@
         <v>3</v>
       </c>
       <c r="D670" s="1" t="s">
-        <v>1392</v>
+        <v>1390</v>
       </c>
       <c r="E670" s="1" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="F670" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="671" spans="1:6" x14ac:dyDescent="0.25">
@@ -18109,13 +18079,13 @@
         <v>3</v>
       </c>
       <c r="D671" s="1" t="s">
-        <v>1392</v>
+        <v>1390</v>
       </c>
       <c r="E671" s="1" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="F671" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="672" spans="1:6" x14ac:dyDescent="0.25">
@@ -18129,13 +18099,13 @@
         <v>3</v>
       </c>
       <c r="D672" s="1" t="s">
-        <v>1392</v>
+        <v>1390</v>
       </c>
       <c r="E672" s="1" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="F672" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="673" spans="1:6" x14ac:dyDescent="0.25">
@@ -18149,13 +18119,13 @@
         <v>3</v>
       </c>
       <c r="D673" s="1" t="s">
-        <v>1392</v>
+        <v>1390</v>
       </c>
       <c r="E673" s="1" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="F673" s="1" t="s">
-        <v>5</v>
+        <v>41</v>
       </c>
     </row>
     <row r="674" spans="1:6" x14ac:dyDescent="0.25">
@@ -18169,13 +18139,13 @@
         <v>3</v>
       </c>
       <c r="D674" s="1" t="s">
-        <v>1392</v>
+        <v>1390</v>
       </c>
       <c r="E674" s="1" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="F674" s="1" t="s">
-        <v>41</v>
+        <v>9</v>
       </c>
     </row>
     <row r="675" spans="1:6" x14ac:dyDescent="0.25">
@@ -18189,10 +18159,10 @@
         <v>3</v>
       </c>
       <c r="D675" s="1" t="s">
-        <v>1392</v>
+        <v>1390</v>
       </c>
       <c r="E675" s="1" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="F675" s="1" t="s">
         <v>9</v>
@@ -18209,10 +18179,10 @@
         <v>3</v>
       </c>
       <c r="D676" s="1" t="s">
-        <v>1392</v>
+        <v>1390</v>
       </c>
       <c r="E676" s="1" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="F676" s="1" t="s">
         <v>9</v>
@@ -18229,133 +18199,33 @@
         <v>3</v>
       </c>
       <c r="D677" s="1" t="s">
-        <v>1392</v>
+        <v>1415</v>
       </c>
       <c r="E677" s="1" t="s">
-        <v>40</v>
+        <v>8</v>
       </c>
       <c r="F677" s="1" t="s">
-        <v>9</v>
+        <v>25</v>
       </c>
     </row>
     <row r="678" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A678" s="1" t="s">
+        <v>1416</v>
+      </c>
+      <c r="B678" s="1" t="s">
+        <v>1417</v>
+      </c>
+      <c r="C678" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D678" s="1" t="s">
         <v>1415</v>
       </c>
-      <c r="B678" s="1" t="s">
-        <v>1416</v>
-      </c>
-      <c r="C678" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D678" s="1" t="s">
-        <v>1417</v>
-      </c>
       <c r="E678" s="1" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="F678" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="679" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A679" s="1" t="s">
-        <v>1418</v>
-      </c>
-      <c r="B679" s="1" t="s">
-        <v>1419</v>
-      </c>
-      <c r="C679" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D679" s="1" t="s">
-        <v>1417</v>
-      </c>
-      <c r="E679" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="F679" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="680" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A680" s="1" t="s">
-        <v>1420</v>
-      </c>
-      <c r="B680" s="1" t="s">
-        <v>1421</v>
-      </c>
-      <c r="C680" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D680" s="1" t="s">
-        <v>1417</v>
-      </c>
-      <c r="E680" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="F680" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="681" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A681" s="1" t="s">
-        <v>1422</v>
-      </c>
-      <c r="B681" s="1" t="s">
-        <v>1423</v>
-      </c>
-      <c r="C681" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D681" s="1" t="s">
-        <v>1417</v>
-      </c>
-      <c r="E681" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="F681" s="1" t="s">
         <v>25</v>
-      </c>
-    </row>
-    <row r="682" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A682" s="1" t="s">
-        <v>1424</v>
-      </c>
-      <c r="B682" s="1" t="s">
-        <v>1425</v>
-      </c>
-      <c r="C682" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D682" s="1" t="s">
-        <v>1417</v>
-      </c>
-      <c r="E682" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="F682" s="1" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="683" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A683" s="1" t="s">
-        <v>1426</v>
-      </c>
-      <c r="B683" s="1" t="s">
-        <v>1427</v>
-      </c>
-      <c r="C683" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D683" s="1" t="s">
-        <v>1417</v>
-      </c>
-      <c r="E683" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="F683" s="1" t="s">
-        <v>5</v>
       </c>
     </row>
   </sheetData>

--- a/PCE06D.xlsx
+++ b/PCE06D.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4134" uniqueCount="1440">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4212" uniqueCount="1466">
   <si>
     <t/>
   </si>
@@ -4045,172 +4045,175 @@
     <t>GTSBY STYL POMADE 75</t>
   </si>
   <si>
+    <t>20090906</t>
+  </si>
+  <si>
+    <t>BELLAGIO PMD BLCK 80</t>
+  </si>
+  <si>
+    <t>43</t>
+  </si>
+  <si>
+    <t>20128951</t>
+  </si>
+  <si>
+    <t>MORRIS PMD EXTR HL80</t>
+  </si>
+  <si>
+    <t>20136022</t>
+  </si>
+  <si>
+    <t>GTSBY FBR CLY MATT80</t>
+  </si>
+  <si>
+    <t>20136021</t>
+  </si>
+  <si>
+    <t>GTSBY FBR PMD GLOS80</t>
+  </si>
+  <si>
+    <t>20127064</t>
+  </si>
+  <si>
+    <t>S/R STYLING PMDE 75</t>
+  </si>
+  <si>
+    <t>20082862</t>
+  </si>
+  <si>
+    <t>GTSBY PMD PR.RISE 75</t>
+  </si>
+  <si>
+    <t>20136388</t>
+  </si>
+  <si>
+    <t>KAHF PMD SLK CLSY 70</t>
+  </si>
+  <si>
+    <t>20142118</t>
+  </si>
+  <si>
+    <t>B/D STRNG POMADE 75</t>
+  </si>
+  <si>
+    <t>20129578</t>
+  </si>
+  <si>
+    <t>GATSBY BALM PMADE 70</t>
+  </si>
+  <si>
+    <t>20129580</t>
+  </si>
+  <si>
+    <t>GATSBY BALM CLAY 70</t>
+  </si>
+  <si>
+    <t>20129581</t>
+  </si>
+  <si>
+    <t>GATSBY BALM CREAM 70</t>
+  </si>
+  <si>
+    <t>10008992</t>
+  </si>
+  <si>
+    <t>GILLETE RAZOR VECTOR</t>
+  </si>
+  <si>
+    <t>44</t>
+  </si>
+  <si>
+    <t>10009007</t>
+  </si>
+  <si>
+    <t>GILLETE CATR.VECTOR2</t>
+  </si>
+  <si>
+    <t>20086422</t>
+  </si>
+  <si>
+    <t>GILLETTE BLUE II 3+1</t>
+  </si>
+  <si>
+    <t>20139066</t>
+  </si>
+  <si>
+    <t>GLLTTE BLUE3 FLXI 3S</t>
+  </si>
+  <si>
+    <t>20135324</t>
+  </si>
+  <si>
+    <t>GLLETTE GOAL YLW 4'S</t>
+  </si>
+  <si>
+    <t>20033978</t>
+  </si>
+  <si>
+    <t>GILLETTE RAZOR BLUE3</t>
+  </si>
+  <si>
+    <t>20081456</t>
+  </si>
+  <si>
+    <t>GLLETTE BLUE3 SIMPLE</t>
+  </si>
+  <si>
+    <t>20137021</t>
+  </si>
+  <si>
+    <t>IDM PISAU CUKUR 3+1</t>
+  </si>
+  <si>
+    <t>20141365</t>
+  </si>
+  <si>
+    <t>BARBER.D 6 BL SHAVER</t>
+  </si>
+  <si>
+    <t>20096659</t>
+  </si>
+  <si>
+    <t>IDM RAZOR 3MATA SLT</t>
+  </si>
+  <si>
+    <t>20014993</t>
+  </si>
+  <si>
+    <t>GILLETTE BLUE II PLS</t>
+  </si>
+  <si>
+    <t>20123700</t>
+  </si>
+  <si>
+    <t>GLTTE BLUE II FLEXI</t>
+  </si>
+  <si>
+    <t>10000318</t>
+  </si>
+  <si>
+    <t>GLLETTE RZR GOAL YLW</t>
+  </si>
+  <si>
+    <t>20029237</t>
+  </si>
+  <si>
+    <t>IDM PISAU CUKUR 2MP</t>
+  </si>
+  <si>
+    <t>10013212</t>
+  </si>
+  <si>
+    <t>GILLETTE SMPLY VNS2S</t>
+  </si>
+  <si>
     <t>20138844</t>
   </si>
   <si>
     <t>GATSBY PWDR CLAY 20G</t>
   </si>
   <si>
-    <t>43</t>
-  </si>
-  <si>
-    <t>20090906</t>
-  </si>
-  <si>
-    <t>BELLAGIO PMD BLCK 80</t>
-  </si>
-  <si>
-    <t>20128951</t>
-  </si>
-  <si>
-    <t>MORRIS PMD EXTR HL80</t>
-  </si>
-  <si>
-    <t>20136022</t>
-  </si>
-  <si>
-    <t>GTSBY FBR CLY MATT80</t>
-  </si>
-  <si>
-    <t>20136021</t>
-  </si>
-  <si>
-    <t>GTSBY FBR PMD GLOS80</t>
-  </si>
-  <si>
-    <t>20127064</t>
-  </si>
-  <si>
-    <t>S/R STYLING PMDE 75</t>
-  </si>
-  <si>
-    <t>20082862</t>
-  </si>
-  <si>
-    <t>GTSBY PMD PR.RISE 75</t>
-  </si>
-  <si>
-    <t>20136388</t>
-  </si>
-  <si>
-    <t>KAHF PMD SLK CLSY 70</t>
-  </si>
-  <si>
-    <t>20142118</t>
-  </si>
-  <si>
-    <t>B/D STRNG POMADE 75</t>
-  </si>
-  <si>
-    <t>20129578</t>
-  </si>
-  <si>
-    <t>GATSBY BALM PMADE 70</t>
-  </si>
-  <si>
-    <t>20129580</t>
-  </si>
-  <si>
-    <t>GATSBY BALM CLAY 70</t>
-  </si>
-  <si>
-    <t>20129581</t>
-  </si>
-  <si>
-    <t>GATSBY BALM CREAM 70</t>
-  </si>
-  <si>
-    <t>10008992</t>
-  </si>
-  <si>
-    <t>GILLETE RAZOR VECTOR</t>
-  </si>
-  <si>
-    <t>44</t>
-  </si>
-  <si>
-    <t>10009007</t>
-  </si>
-  <si>
-    <t>GILLETE CATR.VECTOR2</t>
-  </si>
-  <si>
-    <t>20086422</t>
-  </si>
-  <si>
-    <t>GILLETTE BLUE II 3+1</t>
-  </si>
-  <si>
-    <t>20139066</t>
-  </si>
-  <si>
-    <t>GLLTTE BLUE3 FLXI 3S</t>
-  </si>
-  <si>
-    <t>20135324</t>
-  </si>
-  <si>
-    <t>GLLETTE GOAL YLW 4'S</t>
-  </si>
-  <si>
-    <t>20033978</t>
-  </si>
-  <si>
-    <t>GILLETTE RAZOR BLUE3</t>
-  </si>
-  <si>
-    <t>20081456</t>
-  </si>
-  <si>
-    <t>GLLETTE BLUE3 SIMPLE</t>
-  </si>
-  <si>
-    <t>20137021</t>
-  </si>
-  <si>
-    <t>IDM PISAU CUKUR 3+1</t>
-  </si>
-  <si>
-    <t>20141365</t>
-  </si>
-  <si>
-    <t>BARBER.D 6 BL SHAVER</t>
-  </si>
-  <si>
-    <t>20096659</t>
-  </si>
-  <si>
-    <t>IDM RAZOR 3MATA SLT</t>
-  </si>
-  <si>
-    <t>20014993</t>
-  </si>
-  <si>
-    <t>GILLETTE BLUE II PLS</t>
-  </si>
-  <si>
-    <t>20123700</t>
-  </si>
-  <si>
-    <t>GLTTE BLUE II FLEXI</t>
-  </si>
-  <si>
-    <t>10000318</t>
-  </si>
-  <si>
-    <t>GLLETTE RZR GOAL YLW</t>
-  </si>
-  <si>
-    <t>20029237</t>
-  </si>
-  <si>
-    <t>IDM PISAU CUKUR 2MP</t>
-  </si>
-  <si>
-    <t>10013212</t>
-  </si>
-  <si>
-    <t>GILLETTE SMPLY VNS2S</t>
+    <t>45</t>
   </si>
   <si>
     <t>20140803</t>
@@ -4219,7 +4222,58 @@
     <t>ARJOENA SPRAY 15ML</t>
   </si>
   <si>
-    <t>45</t>
+    <t>10013365</t>
+  </si>
+  <si>
+    <t>AKURAT STRIP PCS</t>
+  </si>
+  <si>
+    <t>20124472</t>
+  </si>
+  <si>
+    <t>SNSTF VIVO 0.03 3'S</t>
+  </si>
+  <si>
+    <t>10007241</t>
+  </si>
+  <si>
+    <t>SENSITIF STRIP</t>
+  </si>
+  <si>
+    <t>20063363</t>
+  </si>
+  <si>
+    <t>OKAMOTO KNDM PLT 2'S</t>
+  </si>
+  <si>
+    <t>20045107</t>
+  </si>
+  <si>
+    <t>DUREX LOVE BOX 3'S</t>
+  </si>
+  <si>
+    <t>20097468</t>
+  </si>
+  <si>
+    <t>TESTPACK ALAT TES</t>
+  </si>
+  <si>
+    <t>20035693</t>
+  </si>
+  <si>
+    <t>DUREX PERFORMA 3'S</t>
+  </si>
+  <si>
+    <t>20139964</t>
+  </si>
+  <si>
+    <t>MAGIC PWR ICE BL 6'S</t>
+  </si>
+  <si>
+    <t>10008133</t>
+  </si>
+  <si>
+    <t>DUREX EXTRA3S</t>
   </si>
   <si>
     <t>20097521</t>
@@ -4228,40 +4282,22 @@
     <t>MAGIC PWR CLASSIC 6S</t>
   </si>
   <si>
-    <t>20139964</t>
-  </si>
-  <si>
-    <t>MAGIC PWR ICE BL 6'S</t>
-  </si>
-  <si>
-    <t>20063363</t>
-  </si>
-  <si>
-    <t>OKAMOTO KNDM PLT 2'S</t>
-  </si>
-  <si>
-    <t>10008133</t>
-  </si>
-  <si>
-    <t>DUREX EXTRA3S</t>
-  </si>
-  <si>
     <t>20078435</t>
   </si>
   <si>
     <t>DUREX INVISIBLE 2'S</t>
   </si>
   <si>
-    <t>20035693</t>
-  </si>
-  <si>
-    <t>DUREX PERFORMA 3'S</t>
-  </si>
-  <si>
-    <t>20045107</t>
-  </si>
-  <si>
-    <t>DUREX LOVE BOX 3'S</t>
+    <t>20095417</t>
+  </si>
+  <si>
+    <t>LOVERS FM TISSUE 6'S</t>
+  </si>
+  <si>
+    <t>20069204</t>
+  </si>
+  <si>
+    <t>SUTRA OK 12'S</t>
   </si>
   <si>
     <t>20069205</t>
@@ -4270,34 +4306,76 @@
     <t>FIESTA MAX DOT 3'S</t>
   </si>
   <si>
+    <t>10004655</t>
+  </si>
+  <si>
+    <t>SUTRA 12'S</t>
+  </si>
+  <si>
+    <t>10023214</t>
+  </si>
+  <si>
+    <t>FIESTA STRWBRY 3'S</t>
+  </si>
+  <si>
     <t>20091579</t>
   </si>
   <si>
     <t>SUTRA GERIGI 3'S</t>
   </si>
   <si>
+    <t>20134971</t>
+  </si>
+  <si>
+    <t>SUTRA KONDOM 003 2'S</t>
+  </si>
+  <si>
     <t>20022011</t>
   </si>
   <si>
     <t>SUTRA OK 3'S</t>
   </si>
   <si>
+    <t>20131512</t>
+  </si>
+  <si>
+    <t>SUTRA LUBRCNT GEL 50</t>
+  </si>
+  <si>
     <t>10004656</t>
   </si>
   <si>
     <t>SUTRA KONDOM 3'S</t>
   </si>
   <si>
-    <t>20069204</t>
-  </si>
-  <si>
-    <t>SUTRA OK 12'S</t>
-  </si>
-  <si>
-    <t>10004655</t>
-  </si>
-  <si>
-    <t>SUTRA 12'S</t>
+    <t>20141718</t>
+  </si>
+  <si>
+    <t>DUREX LUBESTRBRY50ML</t>
+  </si>
+  <si>
+    <t>20032984</t>
+  </si>
+  <si>
+    <t>DUREX PLY.LBE FEEL50</t>
+  </si>
+  <si>
+    <t>20141773</t>
+  </si>
+  <si>
+    <t>SUTRA KONDOM CINTA3S</t>
+  </si>
+  <si>
+    <t>10032002</t>
+  </si>
+  <si>
+    <t>VIGEL LUBRICATING 60</t>
+  </si>
+  <si>
+    <t>20142567</t>
+  </si>
+  <si>
+    <t>SUTRA KONDOM RAPET3S</t>
   </si>
   <si>
     <t>20142282</t>
@@ -4723,7 +4801,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F689"/>
+  <dimension ref="A1:F702"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
@@ -17188,7 +17266,7 @@
         <v>1277</v>
       </c>
       <c r="E623" s="1" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="F623" s="1" t="s">
         <v>5</v>
@@ -17208,7 +17286,7 @@
         <v>1277</v>
       </c>
       <c r="E624" s="1" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="F624" s="1" t="s">
         <v>5</v>
@@ -17228,7 +17306,7 @@
         <v>1277</v>
       </c>
       <c r="E625" s="1" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="F625" s="1" t="s">
         <v>5</v>
@@ -17248,7 +17326,7 @@
         <v>1277</v>
       </c>
       <c r="E626" s="1" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="F626" s="1" t="s">
         <v>9</v>
@@ -17651,7 +17729,7 @@
         <v>12</v>
       </c>
       <c r="F646" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="647" spans="1:6" x14ac:dyDescent="0.25">
@@ -17691,7 +17769,7 @@
         <v>18</v>
       </c>
       <c r="F648" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="649" spans="1:6" x14ac:dyDescent="0.25">
@@ -17711,7 +17789,7 @@
         <v>21</v>
       </c>
       <c r="F649" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="650" spans="1:6" x14ac:dyDescent="0.25">
@@ -17731,7 +17809,7 @@
         <v>24</v>
       </c>
       <c r="F650" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="651" spans="1:6" x14ac:dyDescent="0.25">
@@ -17751,7 +17829,7 @@
         <v>28</v>
       </c>
       <c r="F651" s="1" t="s">
-        <v>5</v>
+        <v>41</v>
       </c>
     </row>
     <row r="652" spans="1:6" x14ac:dyDescent="0.25">
@@ -17771,7 +17849,7 @@
         <v>31</v>
       </c>
       <c r="F652" s="1" t="s">
-        <v>41</v>
+        <v>9</v>
       </c>
     </row>
     <row r="653" spans="1:6" x14ac:dyDescent="0.25">
@@ -17825,30 +17903,30 @@
         <v>3</v>
       </c>
       <c r="D655" s="1" t="s">
-        <v>1346</v>
+        <v>1369</v>
       </c>
       <c r="E655" s="1" t="s">
-        <v>40</v>
+        <v>4</v>
       </c>
       <c r="F655" s="1" t="s">
-        <v>9</v>
+        <v>269</v>
       </c>
     </row>
     <row r="656" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A656" s="1" t="s">
+        <v>1370</v>
+      </c>
+      <c r="B656" s="1" t="s">
+        <v>1371</v>
+      </c>
+      <c r="C656" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D656" s="1" t="s">
         <v>1369</v>
       </c>
-      <c r="B656" s="1" t="s">
-        <v>1370</v>
-      </c>
-      <c r="C656" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D656" s="1" t="s">
-        <v>1371</v>
-      </c>
       <c r="E656" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F656" s="1" t="s">
         <v>269</v>
@@ -17865,10 +17943,10 @@
         <v>3</v>
       </c>
       <c r="D657" s="1" t="s">
-        <v>1371</v>
+        <v>1369</v>
       </c>
       <c r="E657" s="1" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="F657" s="1" t="s">
         <v>269</v>
@@ -17885,10 +17963,10 @@
         <v>3</v>
       </c>
       <c r="D658" s="1" t="s">
-        <v>1371</v>
+        <v>1369</v>
       </c>
       <c r="E658" s="1" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="F658" s="1" t="s">
         <v>269</v>
@@ -17905,10 +17983,10 @@
         <v>3</v>
       </c>
       <c r="D659" s="1" t="s">
-        <v>1371</v>
+        <v>1369</v>
       </c>
       <c r="E659" s="1" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="F659" s="1" t="s">
         <v>269</v>
@@ -17925,10 +18003,10 @@
         <v>3</v>
       </c>
       <c r="D660" s="1" t="s">
-        <v>1371</v>
+        <v>1369</v>
       </c>
       <c r="E660" s="1" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="F660" s="1" t="s">
         <v>269</v>
@@ -17945,10 +18023,10 @@
         <v>3</v>
       </c>
       <c r="D661" s="1" t="s">
-        <v>1371</v>
+        <v>1369</v>
       </c>
       <c r="E661" s="1" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="F661" s="1" t="s">
         <v>269</v>
@@ -17965,13 +18043,13 @@
         <v>3</v>
       </c>
       <c r="D662" s="1" t="s">
-        <v>1371</v>
+        <v>1369</v>
       </c>
       <c r="E662" s="1" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="F662" s="1" t="s">
-        <v>269</v>
+        <v>232</v>
       </c>
     </row>
     <row r="663" spans="1:6" x14ac:dyDescent="0.25">
@@ -17985,13 +18063,13 @@
         <v>3</v>
       </c>
       <c r="D663" s="1" t="s">
-        <v>1371</v>
+        <v>1369</v>
       </c>
       <c r="E663" s="1" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="F663" s="1" t="s">
-        <v>232</v>
+        <v>5</v>
       </c>
     </row>
     <row r="664" spans="1:6" x14ac:dyDescent="0.25">
@@ -18005,13 +18083,13 @@
         <v>3</v>
       </c>
       <c r="D664" s="1" t="s">
-        <v>1371</v>
+        <v>1369</v>
       </c>
       <c r="E664" s="1" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="F664" s="1" t="s">
-        <v>5</v>
+        <v>269</v>
       </c>
     </row>
     <row r="665" spans="1:6" x14ac:dyDescent="0.25">
@@ -18025,10 +18103,10 @@
         <v>3</v>
       </c>
       <c r="D665" s="1" t="s">
-        <v>1371</v>
+        <v>1369</v>
       </c>
       <c r="E665" s="1" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="F665" s="1" t="s">
         <v>269</v>
@@ -18045,7 +18123,7 @@
         <v>3</v>
       </c>
       <c r="D666" s="1" t="s">
-        <v>1371</v>
+        <v>1369</v>
       </c>
       <c r="E666" s="1" t="s">
         <v>37</v>
@@ -18065,10 +18143,10 @@
         <v>3</v>
       </c>
       <c r="D667" s="1" t="s">
-        <v>1371</v>
+        <v>1369</v>
       </c>
       <c r="E667" s="1" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="F667" s="1" t="s">
         <v>269</v>
@@ -18085,13 +18163,13 @@
         <v>3</v>
       </c>
       <c r="D668" s="1" t="s">
-        <v>1371</v>
+        <v>1369</v>
       </c>
       <c r="E668" s="1" t="s">
         <v>40</v>
       </c>
       <c r="F668" s="1" t="s">
-        <v>269</v>
+        <v>232</v>
       </c>
     </row>
     <row r="669" spans="1:6" x14ac:dyDescent="0.25">
@@ -18105,13 +18183,13 @@
         <v>3</v>
       </c>
       <c r="D669" s="1" t="s">
-        <v>1371</v>
+        <v>1369</v>
       </c>
       <c r="E669" s="1" t="s">
-        <v>40</v>
+        <v>68</v>
       </c>
       <c r="F669" s="1" t="s">
-        <v>232</v>
+        <v>269</v>
       </c>
     </row>
     <row r="670" spans="1:6" x14ac:dyDescent="0.25">
@@ -18125,27 +18203,27 @@
         <v>3</v>
       </c>
       <c r="D670" s="1" t="s">
-        <v>1371</v>
+        <v>1400</v>
       </c>
       <c r="E670" s="1" t="s">
-        <v>68</v>
+        <v>4</v>
       </c>
       <c r="F670" s="1" t="s">
-        <v>269</v>
+        <v>5</v>
       </c>
     </row>
     <row r="671" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A671" s="1" t="s">
+        <v>1401</v>
+      </c>
+      <c r="B671" s="1" t="s">
+        <v>1402</v>
+      </c>
+      <c r="C671" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D671" s="1" t="s">
         <v>1400</v>
-      </c>
-      <c r="B671" s="1" t="s">
-        <v>1401</v>
-      </c>
-      <c r="C671" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D671" s="1" t="s">
-        <v>1402</v>
       </c>
       <c r="E671" s="1" t="s">
         <v>4</v>
@@ -18165,13 +18243,13 @@
         <v>3</v>
       </c>
       <c r="D672" s="1" t="s">
-        <v>1402</v>
+        <v>1400</v>
       </c>
       <c r="E672" s="1" t="s">
         <v>8</v>
       </c>
       <c r="F672" s="1" t="s">
-        <v>9</v>
+        <v>80</v>
       </c>
     </row>
     <row r="673" spans="1:6" x14ac:dyDescent="0.25">
@@ -18185,13 +18263,13 @@
         <v>3</v>
       </c>
       <c r="D673" s="1" t="s">
-        <v>1402</v>
+        <v>1400</v>
       </c>
       <c r="E673" s="1" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="F673" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="674" spans="1:6" x14ac:dyDescent="0.25">
@@ -18205,13 +18283,13 @@
         <v>3</v>
       </c>
       <c r="D674" s="1" t="s">
-        <v>1402</v>
+        <v>1400</v>
       </c>
       <c r="E674" s="1" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="F674" s="1" t="s">
-        <v>9</v>
+        <v>41</v>
       </c>
     </row>
     <row r="675" spans="1:6" x14ac:dyDescent="0.25">
@@ -18225,10 +18303,10 @@
         <v>3</v>
       </c>
       <c r="D675" s="1" t="s">
-        <v>1402</v>
+        <v>1400</v>
       </c>
       <c r="E675" s="1" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="F675" s="1" t="s">
         <v>9</v>
@@ -18245,10 +18323,10 @@
         <v>3</v>
       </c>
       <c r="D676" s="1" t="s">
-        <v>1402</v>
+        <v>1400</v>
       </c>
       <c r="E676" s="1" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="F676" s="1" t="s">
         <v>5</v>
@@ -18265,13 +18343,13 @@
         <v>3</v>
       </c>
       <c r="D677" s="1" t="s">
-        <v>1402</v>
+        <v>1400</v>
       </c>
       <c r="E677" s="1" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="F677" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="678" spans="1:6" x14ac:dyDescent="0.25">
@@ -18285,13 +18363,13 @@
         <v>3</v>
       </c>
       <c r="D678" s="1" t="s">
-        <v>1402</v>
+        <v>1400</v>
       </c>
       <c r="E678" s="1" t="s">
-        <v>28</v>
+        <v>18</v>
       </c>
       <c r="F678" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="679" spans="1:6" x14ac:dyDescent="0.25">
@@ -18305,13 +18383,13 @@
         <v>3</v>
       </c>
       <c r="D679" s="1" t="s">
-        <v>1402</v>
+        <v>1400</v>
       </c>
       <c r="E679" s="1" t="s">
-        <v>31</v>
+        <v>18</v>
       </c>
       <c r="F679" s="1" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
     </row>
     <row r="680" spans="1:6" x14ac:dyDescent="0.25">
@@ -18325,13 +18403,13 @@
         <v>3</v>
       </c>
       <c r="D680" s="1" t="s">
-        <v>1402</v>
+        <v>1400</v>
       </c>
       <c r="E680" s="1" t="s">
-        <v>34</v>
+        <v>21</v>
       </c>
       <c r="F680" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="681" spans="1:6" x14ac:dyDescent="0.25">
@@ -18345,13 +18423,13 @@
         <v>3</v>
       </c>
       <c r="D681" s="1" t="s">
-        <v>1402</v>
+        <v>1400</v>
       </c>
       <c r="E681" s="1" t="s">
-        <v>37</v>
+        <v>21</v>
       </c>
       <c r="F681" s="1" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
     </row>
     <row r="682" spans="1:6" x14ac:dyDescent="0.25">
@@ -18365,13 +18443,13 @@
         <v>3</v>
       </c>
       <c r="D682" s="1" t="s">
-        <v>1402</v>
+        <v>1400</v>
       </c>
       <c r="E682" s="1" t="s">
-        <v>40</v>
+        <v>24</v>
       </c>
       <c r="F682" s="1" t="s">
-        <v>25</v>
+        <v>5</v>
       </c>
     </row>
     <row r="683" spans="1:6" x14ac:dyDescent="0.25">
@@ -18385,13 +18463,13 @@
         <v>3</v>
       </c>
       <c r="D683" s="1" t="s">
-        <v>1402</v>
+        <v>1400</v>
       </c>
       <c r="E683" s="1" t="s">
-        <v>68</v>
+        <v>24</v>
       </c>
       <c r="F683" s="1" t="s">
-        <v>25</v>
+        <v>41</v>
       </c>
     </row>
     <row r="684" spans="1:6" x14ac:dyDescent="0.25">
@@ -18405,10 +18483,10 @@
         <v>3</v>
       </c>
       <c r="D684" s="1" t="s">
-        <v>1402</v>
+        <v>1400</v>
       </c>
       <c r="E684" s="1" t="s">
-        <v>100</v>
+        <v>28</v>
       </c>
       <c r="F684" s="1" t="s">
         <v>25</v>
@@ -18425,92 +18503,352 @@
         <v>3</v>
       </c>
       <c r="D685" s="1" t="s">
-        <v>1431</v>
+        <v>1400</v>
       </c>
       <c r="E685" s="1" t="s">
-        <v>8</v>
+        <v>28</v>
       </c>
       <c r="F685" s="1" t="s">
-        <v>156</v>
+        <v>25</v>
       </c>
     </row>
     <row r="686" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A686" s="1" t="s">
+        <v>1431</v>
+      </c>
+      <c r="B686" s="1" t="s">
         <v>1432</v>
       </c>
-      <c r="B686" s="1" t="s">
-        <v>1433</v>
-      </c>
       <c r="C686" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D686" s="1" t="s">
-        <v>1431</v>
+        <v>1400</v>
       </c>
       <c r="E686" s="1" t="s">
-        <v>12</v>
+        <v>31</v>
       </c>
       <c r="F686" s="1" t="s">
-        <v>73</v>
+        <v>25</v>
       </c>
     </row>
     <row r="687" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A687" s="1" t="s">
+        <v>1433</v>
+      </c>
+      <c r="B687" s="1" t="s">
         <v>1434</v>
       </c>
-      <c r="B687" s="1" t="s">
-        <v>1435</v>
-      </c>
       <c r="C687" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D687" s="1" t="s">
-        <v>1431</v>
+        <v>1400</v>
       </c>
       <c r="E687" s="1" t="s">
-        <v>15</v>
+        <v>31</v>
       </c>
       <c r="F687" s="1" t="s">
-        <v>41</v>
+        <v>25</v>
       </c>
     </row>
     <row r="688" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A688" s="1" t="s">
+        <v>1435</v>
+      </c>
+      <c r="B688" s="1" t="s">
         <v>1436</v>
       </c>
-      <c r="B688" s="1" t="s">
-        <v>1437</v>
-      </c>
       <c r="C688" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D688" s="1" t="s">
-        <v>1431</v>
+        <v>1400</v>
       </c>
       <c r="E688" s="1" t="s">
-        <v>18</v>
+        <v>34</v>
       </c>
       <c r="F688" s="1" t="s">
-        <v>41</v>
+        <v>5</v>
       </c>
     </row>
     <row r="689" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A689" s="1" t="s">
+        <v>1437</v>
+      </c>
+      <c r="B689" s="1" t="s">
         <v>1438</v>
       </c>
-      <c r="B689" s="1" t="s">
+      <c r="C689" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D689" s="1" t="s">
+        <v>1400</v>
+      </c>
+      <c r="E689" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="F689" s="1" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="690" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A690" s="1" t="s">
         <v>1439</v>
       </c>
-      <c r="C689" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D689" s="1" t="s">
-        <v>1431</v>
-      </c>
-      <c r="E689" s="1" t="s">
+      <c r="B690" s="1" t="s">
+        <v>1440</v>
+      </c>
+      <c r="C690" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D690" s="1" t="s">
+        <v>1400</v>
+      </c>
+      <c r="E690" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="F690" s="1" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="691" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A691" s="1" t="s">
+        <v>1441</v>
+      </c>
+      <c r="B691" s="1" t="s">
+        <v>1442</v>
+      </c>
+      <c r="C691" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D691" s="1" t="s">
+        <v>1400</v>
+      </c>
+      <c r="E691" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="F691" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="692" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A692" s="1" t="s">
+        <v>1443</v>
+      </c>
+      <c r="B692" s="1" t="s">
+        <v>1444</v>
+      </c>
+      <c r="C692" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D692" s="1" t="s">
+        <v>1400</v>
+      </c>
+      <c r="E692" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="F692" s="1" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="693" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A693" s="1" t="s">
+        <v>1445</v>
+      </c>
+      <c r="B693" s="1" t="s">
+        <v>1446</v>
+      </c>
+      <c r="C693" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D693" s="1" t="s">
+        <v>1400</v>
+      </c>
+      <c r="E693" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="F693" s="1" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="694" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A694" s="1" t="s">
+        <v>1447</v>
+      </c>
+      <c r="B694" s="1" t="s">
+        <v>1448</v>
+      </c>
+      <c r="C694" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D694" s="1" t="s">
+        <v>1400</v>
+      </c>
+      <c r="E694" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="F694" s="1" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="695" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A695" s="1" t="s">
+        <v>1449</v>
+      </c>
+      <c r="B695" s="1" t="s">
+        <v>1450</v>
+      </c>
+      <c r="C695" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D695" s="1" t="s">
+        <v>1400</v>
+      </c>
+      <c r="E695" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="F695" s="1" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="696" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A696" s="1" t="s">
+        <v>1451</v>
+      </c>
+      <c r="B696" s="1" t="s">
+        <v>1452</v>
+      </c>
+      <c r="C696" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D696" s="1" t="s">
+        <v>1400</v>
+      </c>
+      <c r="E696" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="F696" s="1" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="697" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A697" s="1" t="s">
+        <v>1453</v>
+      </c>
+      <c r="B697" s="1" t="s">
+        <v>1454</v>
+      </c>
+      <c r="C697" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D697" s="1" t="s">
+        <v>1400</v>
+      </c>
+      <c r="E697" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="F697" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="698" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A698" s="1" t="s">
+        <v>1455</v>
+      </c>
+      <c r="B698" s="1" t="s">
+        <v>1456</v>
+      </c>
+      <c r="C698" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D698" s="1" t="s">
+        <v>1457</v>
+      </c>
+      <c r="E698" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="F698" s="1" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="699" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A699" s="1" t="s">
+        <v>1458</v>
+      </c>
+      <c r="B699" s="1" t="s">
+        <v>1459</v>
+      </c>
+      <c r="C699" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D699" s="1" t="s">
+        <v>1457</v>
+      </c>
+      <c r="E699" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="F699" s="1" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="700" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A700" s="1" t="s">
+        <v>1460</v>
+      </c>
+      <c r="B700" s="1" t="s">
+        <v>1461</v>
+      </c>
+      <c r="C700" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D700" s="1" t="s">
+        <v>1457</v>
+      </c>
+      <c r="E700" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="F700" s="1" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="701" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A701" s="1" t="s">
+        <v>1462</v>
+      </c>
+      <c r="B701" s="1" t="s">
+        <v>1463</v>
+      </c>
+      <c r="C701" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D701" s="1" t="s">
+        <v>1457</v>
+      </c>
+      <c r="E701" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="F701" s="1" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="702" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A702" s="1" t="s">
+        <v>1464</v>
+      </c>
+      <c r="B702" s="1" t="s">
+        <v>1465</v>
+      </c>
+      <c r="C702" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D702" s="1" t="s">
+        <v>1457</v>
+      </c>
+      <c r="E702" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="F689" s="1" t="s">
+      <c r="F702" s="1" t="s">
         <v>5</v>
       </c>
     </row>

--- a/PCE06D.xlsx
+++ b/PCE06D.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4260" uniqueCount="1484">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4260" uniqueCount="1483">
   <si>
     <t/>
   </si>
@@ -2108,9 +2108,6 @@
   </si>
   <si>
     <t>VSL G-H FLWS BRGT180</t>
-  </si>
-  <si>
-    <t>TG,(E-27H)</t>
   </si>
   <si>
     <t>20021816</t>
@@ -11483,15 +11480,15 @@
         <v>12</v>
       </c>
       <c r="F331" s="1" t="s">
-        <v>699</v>
+        <v>533</v>
       </c>
     </row>
     <row r="332" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A332" s="1" t="s">
+        <v>699</v>
+      </c>
+      <c r="B332" s="1" t="s">
         <v>700</v>
-      </c>
-      <c r="B332" s="1" t="s">
-        <v>701</v>
       </c>
       <c r="C332" s="1" t="s">
         <v>3</v>
@@ -11508,10 +11505,10 @@
     </row>
     <row r="333" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A333" s="1" t="s">
+        <v>701</v>
+      </c>
+      <c r="B333" s="1" t="s">
         <v>702</v>
-      </c>
-      <c r="B333" s="1" t="s">
-        <v>703</v>
       </c>
       <c r="C333" s="1" t="s">
         <v>3</v>
@@ -11528,10 +11525,10 @@
     </row>
     <row r="334" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A334" s="1" t="s">
+        <v>703</v>
+      </c>
+      <c r="B334" s="1" t="s">
         <v>704</v>
-      </c>
-      <c r="B334" s="1" t="s">
-        <v>705</v>
       </c>
       <c r="C334" s="1" t="s">
         <v>3</v>
@@ -11548,10 +11545,10 @@
     </row>
     <row r="335" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A335" s="1" t="s">
+        <v>705</v>
+      </c>
+      <c r="B335" s="1" t="s">
         <v>706</v>
-      </c>
-      <c r="B335" s="1" t="s">
-        <v>707</v>
       </c>
       <c r="C335" s="1" t="s">
         <v>3</v>
@@ -11568,10 +11565,10 @@
     </row>
     <row r="336" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A336" s="1" t="s">
+        <v>707</v>
+      </c>
+      <c r="B336" s="1" t="s">
         <v>708</v>
-      </c>
-      <c r="B336" s="1" t="s">
-        <v>709</v>
       </c>
       <c r="C336" s="1" t="s">
         <v>3</v>
@@ -11588,10 +11585,10 @@
     </row>
     <row r="337" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A337" s="1" t="s">
+        <v>709</v>
+      </c>
+      <c r="B337" s="1" t="s">
         <v>710</v>
-      </c>
-      <c r="B337" s="1" t="s">
-        <v>711</v>
       </c>
       <c r="C337" s="1" t="s">
         <v>3</v>
@@ -11608,10 +11605,10 @@
     </row>
     <row r="338" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A338" s="1" t="s">
+        <v>711</v>
+      </c>
+      <c r="B338" s="1" t="s">
         <v>712</v>
-      </c>
-      <c r="B338" s="1" t="s">
-        <v>713</v>
       </c>
       <c r="C338" s="1" t="s">
         <v>3</v>
@@ -11628,10 +11625,10 @@
     </row>
     <row r="339" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A339" s="1" t="s">
+        <v>713</v>
+      </c>
+      <c r="B339" s="1" t="s">
         <v>714</v>
-      </c>
-      <c r="B339" s="1" t="s">
-        <v>715</v>
       </c>
       <c r="C339" s="1" t="s">
         <v>3</v>
@@ -11648,10 +11645,10 @@
     </row>
     <row r="340" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A340" s="1" t="s">
+        <v>715</v>
+      </c>
+      <c r="B340" s="1" t="s">
         <v>716</v>
-      </c>
-      <c r="B340" s="1" t="s">
-        <v>717</v>
       </c>
       <c r="C340" s="1" t="s">
         <v>3</v>
@@ -11668,16 +11665,16 @@
     </row>
     <row r="341" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A341" s="1" t="s">
+        <v>717</v>
+      </c>
+      <c r="B341" s="1" t="s">
         <v>718</v>
       </c>
-      <c r="B341" s="1" t="s">
+      <c r="C341" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D341" s="1" t="s">
         <v>719</v>
-      </c>
-      <c r="C341" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D341" s="1" t="s">
-        <v>720</v>
       </c>
       <c r="E341" s="1" t="s">
         <v>4</v>
@@ -11688,16 +11685,16 @@
     </row>
     <row r="342" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A342" s="1" t="s">
+        <v>720</v>
+      </c>
+      <c r="B342" s="1" t="s">
         <v>721</v>
       </c>
-      <c r="B342" s="1" t="s">
-        <v>722</v>
-      </c>
       <c r="C342" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D342" s="1" t="s">
-        <v>720</v>
+        <v>719</v>
       </c>
       <c r="E342" s="1" t="s">
         <v>8</v>
@@ -11708,16 +11705,16 @@
     </row>
     <row r="343" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A343" s="1" t="s">
+        <v>722</v>
+      </c>
+      <c r="B343" s="1" t="s">
         <v>723</v>
       </c>
-      <c r="B343" s="1" t="s">
-        <v>724</v>
-      </c>
       <c r="C343" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D343" s="1" t="s">
-        <v>720</v>
+        <v>719</v>
       </c>
       <c r="E343" s="1" t="s">
         <v>12</v>
@@ -11728,16 +11725,16 @@
     </row>
     <row r="344" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A344" s="1" t="s">
+        <v>724</v>
+      </c>
+      <c r="B344" s="1" t="s">
         <v>725</v>
       </c>
-      <c r="B344" s="1" t="s">
-        <v>726</v>
-      </c>
       <c r="C344" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D344" s="1" t="s">
-        <v>720</v>
+        <v>719</v>
       </c>
       <c r="E344" s="1" t="s">
         <v>15</v>
@@ -11748,16 +11745,16 @@
     </row>
     <row r="345" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A345" s="1" t="s">
+        <v>726</v>
+      </c>
+      <c r="B345" s="1" t="s">
         <v>727</v>
       </c>
-      <c r="B345" s="1" t="s">
-        <v>728</v>
-      </c>
       <c r="C345" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D345" s="1" t="s">
-        <v>720</v>
+        <v>719</v>
       </c>
       <c r="E345" s="1" t="s">
         <v>18</v>
@@ -11768,16 +11765,16 @@
     </row>
     <row r="346" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A346" s="1" t="s">
+        <v>728</v>
+      </c>
+      <c r="B346" s="1" t="s">
         <v>729</v>
       </c>
-      <c r="B346" s="1" t="s">
-        <v>730</v>
-      </c>
       <c r="C346" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D346" s="1" t="s">
-        <v>720</v>
+        <v>719</v>
       </c>
       <c r="E346" s="1" t="s">
         <v>21</v>
@@ -11788,16 +11785,16 @@
     </row>
     <row r="347" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A347" s="1" t="s">
+        <v>730</v>
+      </c>
+      <c r="B347" s="1" t="s">
         <v>731</v>
       </c>
-      <c r="B347" s="1" t="s">
-        <v>732</v>
-      </c>
       <c r="C347" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D347" s="1" t="s">
-        <v>720</v>
+        <v>719</v>
       </c>
       <c r="E347" s="1" t="s">
         <v>24</v>
@@ -11808,16 +11805,16 @@
     </row>
     <row r="348" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A348" s="1" t="s">
+        <v>732</v>
+      </c>
+      <c r="B348" s="1" t="s">
         <v>733</v>
       </c>
-      <c r="B348" s="1" t="s">
-        <v>734</v>
-      </c>
       <c r="C348" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D348" s="1" t="s">
-        <v>720</v>
+        <v>719</v>
       </c>
       <c r="E348" s="1" t="s">
         <v>55</v>
@@ -11828,16 +11825,16 @@
     </row>
     <row r="349" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A349" s="1" t="s">
+        <v>734</v>
+      </c>
+      <c r="B349" s="1" t="s">
         <v>735</v>
       </c>
-      <c r="B349" s="1" t="s">
-        <v>736</v>
-      </c>
       <c r="C349" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D349" s="1" t="s">
-        <v>720</v>
+        <v>719</v>
       </c>
       <c r="E349" s="1" t="s">
         <v>28</v>
@@ -11848,16 +11845,16 @@
     </row>
     <row r="350" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A350" s="1" t="s">
+        <v>736</v>
+      </c>
+      <c r="B350" s="1" t="s">
         <v>737</v>
       </c>
-      <c r="B350" s="1" t="s">
-        <v>738</v>
-      </c>
       <c r="C350" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D350" s="1" t="s">
-        <v>720</v>
+        <v>719</v>
       </c>
       <c r="E350" s="1" t="s">
         <v>31</v>
@@ -11868,16 +11865,16 @@
     </row>
     <row r="351" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A351" s="1" t="s">
+        <v>738</v>
+      </c>
+      <c r="B351" s="1" t="s">
         <v>739</v>
       </c>
-      <c r="B351" s="1" t="s">
-        <v>740</v>
-      </c>
       <c r="C351" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D351" s="1" t="s">
-        <v>720</v>
+        <v>719</v>
       </c>
       <c r="E351" s="1" t="s">
         <v>34</v>
@@ -11888,16 +11885,16 @@
     </row>
     <row r="352" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A352" s="1" t="s">
+        <v>740</v>
+      </c>
+      <c r="B352" s="1" t="s">
         <v>741</v>
       </c>
-      <c r="B352" s="1" t="s">
-        <v>742</v>
-      </c>
       <c r="C352" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D352" s="1" t="s">
-        <v>720</v>
+        <v>719</v>
       </c>
       <c r="E352" s="1" t="s">
         <v>37</v>
@@ -11908,16 +11905,16 @@
     </row>
     <row r="353" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A353" s="1" t="s">
+        <v>742</v>
+      </c>
+      <c r="B353" s="1" t="s">
         <v>743</v>
       </c>
-      <c r="B353" s="1" t="s">
-        <v>744</v>
-      </c>
       <c r="C353" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D353" s="1" t="s">
-        <v>720</v>
+        <v>719</v>
       </c>
       <c r="E353" s="1" t="s">
         <v>66</v>
@@ -11928,16 +11925,16 @@
     </row>
     <row r="354" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A354" s="1" t="s">
+        <v>744</v>
+      </c>
+      <c r="B354" s="1" t="s">
         <v>745</v>
       </c>
-      <c r="B354" s="1" t="s">
-        <v>746</v>
-      </c>
       <c r="C354" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D354" s="1" t="s">
-        <v>720</v>
+        <v>719</v>
       </c>
       <c r="E354" s="1" t="s">
         <v>98</v>
@@ -11948,16 +11945,16 @@
     </row>
     <row r="355" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A355" s="1" t="s">
+        <v>746</v>
+      </c>
+      <c r="B355" s="1" t="s">
         <v>747</v>
       </c>
-      <c r="B355" s="1" t="s">
+      <c r="C355" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D355" s="1" t="s">
         <v>748</v>
-      </c>
-      <c r="C355" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D355" s="1" t="s">
-        <v>749</v>
       </c>
       <c r="E355" s="1" t="s">
         <v>4</v>
@@ -11968,16 +11965,16 @@
     </row>
     <row r="356" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A356" s="1" t="s">
+        <v>749</v>
+      </c>
+      <c r="B356" s="1" t="s">
         <v>750</v>
       </c>
-      <c r="B356" s="1" t="s">
-        <v>751</v>
-      </c>
       <c r="C356" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D356" s="1" t="s">
-        <v>749</v>
+        <v>748</v>
       </c>
       <c r="E356" s="1" t="s">
         <v>8</v>
@@ -11988,16 +11985,16 @@
     </row>
     <row r="357" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A357" s="1" t="s">
+        <v>751</v>
+      </c>
+      <c r="B357" s="1" t="s">
         <v>752</v>
       </c>
-      <c r="B357" s="1" t="s">
-        <v>753</v>
-      </c>
       <c r="C357" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D357" s="1" t="s">
-        <v>749</v>
+        <v>748</v>
       </c>
       <c r="E357" s="1" t="s">
         <v>12</v>
@@ -12008,16 +12005,16 @@
     </row>
     <row r="358" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A358" s="1" t="s">
+        <v>753</v>
+      </c>
+      <c r="B358" s="1" t="s">
         <v>754</v>
       </c>
-      <c r="B358" s="1" t="s">
-        <v>755</v>
-      </c>
       <c r="C358" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D358" s="1" t="s">
-        <v>749</v>
+        <v>748</v>
       </c>
       <c r="E358" s="1" t="s">
         <v>15</v>
@@ -12028,16 +12025,16 @@
     </row>
     <row r="359" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A359" s="1" t="s">
+        <v>755</v>
+      </c>
+      <c r="B359" s="1" t="s">
         <v>756</v>
       </c>
-      <c r="B359" s="1" t="s">
-        <v>757</v>
-      </c>
       <c r="C359" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D359" s="1" t="s">
-        <v>749</v>
+        <v>748</v>
       </c>
       <c r="E359" s="1" t="s">
         <v>18</v>
@@ -12048,16 +12045,16 @@
     </row>
     <row r="360" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A360" s="1" t="s">
+        <v>757</v>
+      </c>
+      <c r="B360" s="1" t="s">
         <v>758</v>
       </c>
-      <c r="B360" s="1" t="s">
-        <v>759</v>
-      </c>
       <c r="C360" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D360" s="1" t="s">
-        <v>749</v>
+        <v>748</v>
       </c>
       <c r="E360" s="1" t="s">
         <v>21</v>
@@ -12068,16 +12065,16 @@
     </row>
     <row r="361" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A361" s="1" t="s">
+        <v>759</v>
+      </c>
+      <c r="B361" s="1" t="s">
         <v>760</v>
       </c>
-      <c r="B361" s="1" t="s">
-        <v>761</v>
-      </c>
       <c r="C361" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D361" s="1" t="s">
-        <v>749</v>
+        <v>748</v>
       </c>
       <c r="E361" s="1" t="s">
         <v>24</v>
@@ -12088,16 +12085,16 @@
     </row>
     <row r="362" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A362" s="1" t="s">
+        <v>761</v>
+      </c>
+      <c r="B362" s="1" t="s">
         <v>762</v>
       </c>
-      <c r="B362" s="1" t="s">
-        <v>763</v>
-      </c>
       <c r="C362" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D362" s="1" t="s">
-        <v>749</v>
+        <v>748</v>
       </c>
       <c r="E362" s="1" t="s">
         <v>55</v>
@@ -12108,16 +12105,16 @@
     </row>
     <row r="363" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A363" s="1" t="s">
+        <v>763</v>
+      </c>
+      <c r="B363" s="1" t="s">
         <v>764</v>
       </c>
-      <c r="B363" s="1" t="s">
-        <v>765</v>
-      </c>
       <c r="C363" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D363" s="1" t="s">
-        <v>749</v>
+        <v>748</v>
       </c>
       <c r="E363" s="1" t="s">
         <v>28</v>
@@ -12128,16 +12125,16 @@
     </row>
     <row r="364" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A364" s="1" t="s">
+        <v>765</v>
+      </c>
+      <c r="B364" s="1" t="s">
         <v>766</v>
       </c>
-      <c r="B364" s="1" t="s">
-        <v>767</v>
-      </c>
       <c r="C364" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D364" s="1" t="s">
-        <v>749</v>
+        <v>748</v>
       </c>
       <c r="E364" s="1" t="s">
         <v>31</v>
@@ -12148,16 +12145,16 @@
     </row>
     <row r="365" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A365" s="1" t="s">
+        <v>767</v>
+      </c>
+      <c r="B365" s="1" t="s">
         <v>768</v>
       </c>
-      <c r="B365" s="1" t="s">
-        <v>769</v>
-      </c>
       <c r="C365" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D365" s="1" t="s">
-        <v>749</v>
+        <v>748</v>
       </c>
       <c r="E365" s="1" t="s">
         <v>34</v>
@@ -12168,16 +12165,16 @@
     </row>
     <row r="366" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A366" s="1" t="s">
+        <v>769</v>
+      </c>
+      <c r="B366" s="1" t="s">
         <v>770</v>
       </c>
-      <c r="B366" s="1" t="s">
-        <v>771</v>
-      </c>
       <c r="C366" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D366" s="1" t="s">
-        <v>749</v>
+        <v>748</v>
       </c>
       <c r="E366" s="1" t="s">
         <v>37</v>
@@ -12188,16 +12185,16 @@
     </row>
     <row r="367" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A367" s="1" t="s">
+        <v>771</v>
+      </c>
+      <c r="B367" s="1" t="s">
         <v>772</v>
       </c>
-      <c r="B367" s="1" t="s">
-        <v>773</v>
-      </c>
       <c r="C367" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D367" s="1" t="s">
-        <v>749</v>
+        <v>748</v>
       </c>
       <c r="E367" s="1" t="s">
         <v>66</v>
@@ -12208,16 +12205,16 @@
     </row>
     <row r="368" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A368" s="1" t="s">
+        <v>773</v>
+      </c>
+      <c r="B368" s="1" t="s">
         <v>774</v>
       </c>
-      <c r="B368" s="1" t="s">
-        <v>775</v>
-      </c>
       <c r="C368" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D368" s="1" t="s">
-        <v>749</v>
+        <v>748</v>
       </c>
       <c r="E368" s="1" t="s">
         <v>98</v>
@@ -12228,16 +12225,16 @@
     </row>
     <row r="369" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A369" s="1" t="s">
+        <v>775</v>
+      </c>
+      <c r="B369" s="1" t="s">
         <v>776</v>
       </c>
-      <c r="B369" s="1" t="s">
-        <v>777</v>
-      </c>
       <c r="C369" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D369" s="1" t="s">
-        <v>749</v>
+        <v>748</v>
       </c>
       <c r="E369" s="1" t="s">
         <v>101</v>
@@ -12248,16 +12245,16 @@
     </row>
     <row r="370" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A370" s="1" t="s">
+        <v>777</v>
+      </c>
+      <c r="B370" s="1" t="s">
         <v>778</v>
       </c>
-      <c r="B370" s="1" t="s">
-        <v>779</v>
-      </c>
       <c r="C370" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D370" s="1" t="s">
-        <v>749</v>
+        <v>748</v>
       </c>
       <c r="E370" s="1" t="s">
         <v>104</v>
@@ -12268,16 +12265,16 @@
     </row>
     <row r="371" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A371" s="1" t="s">
+        <v>779</v>
+      </c>
+      <c r="B371" s="1" t="s">
         <v>780</v>
       </c>
-      <c r="B371" s="1" t="s">
-        <v>781</v>
-      </c>
       <c r="C371" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D371" s="1" t="s">
-        <v>749</v>
+        <v>748</v>
       </c>
       <c r="E371" s="1" t="s">
         <v>107</v>
@@ -12288,16 +12285,16 @@
     </row>
     <row r="372" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A372" s="1" t="s">
+        <v>781</v>
+      </c>
+      <c r="B372" s="1" t="s">
         <v>782</v>
       </c>
-      <c r="B372" s="1" t="s">
-        <v>783</v>
-      </c>
       <c r="C372" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D372" s="1" t="s">
-        <v>749</v>
+        <v>748</v>
       </c>
       <c r="E372" s="1" t="s">
         <v>110</v>
@@ -12308,16 +12305,16 @@
     </row>
     <row r="373" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A373" s="1" t="s">
+        <v>783</v>
+      </c>
+      <c r="B373" s="1" t="s">
         <v>784</v>
       </c>
-      <c r="B373" s="1" t="s">
-        <v>785</v>
-      </c>
       <c r="C373" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D373" s="1" t="s">
-        <v>749</v>
+        <v>748</v>
       </c>
       <c r="E373" s="1" t="s">
         <v>150</v>
@@ -12328,16 +12325,16 @@
     </row>
     <row r="374" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A374" s="1" t="s">
+        <v>785</v>
+      </c>
+      <c r="B374" s="1" t="s">
         <v>786</v>
       </c>
-      <c r="B374" s="1" t="s">
+      <c r="C374" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D374" s="1" t="s">
         <v>787</v>
-      </c>
-      <c r="C374" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D374" s="1" t="s">
-        <v>788</v>
       </c>
       <c r="E374" s="1" t="s">
         <v>4</v>
@@ -12348,16 +12345,16 @@
     </row>
     <row r="375" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A375" s="1" t="s">
+        <v>788</v>
+      </c>
+      <c r="B375" s="1" t="s">
         <v>789</v>
       </c>
-      <c r="B375" s="1" t="s">
-        <v>790</v>
-      </c>
       <c r="C375" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D375" s="1" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="E375" s="1" t="s">
         <v>8</v>
@@ -12368,16 +12365,16 @@
     </row>
     <row r="376" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A376" s="1" t="s">
+        <v>790</v>
+      </c>
+      <c r="B376" s="1" t="s">
         <v>791</v>
       </c>
-      <c r="B376" s="1" t="s">
-        <v>792</v>
-      </c>
       <c r="C376" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D376" s="1" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="E376" s="1" t="s">
         <v>12</v>
@@ -12388,16 +12385,16 @@
     </row>
     <row r="377" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A377" s="1" t="s">
+        <v>792</v>
+      </c>
+      <c r="B377" s="1" t="s">
         <v>793</v>
       </c>
-      <c r="B377" s="1" t="s">
-        <v>794</v>
-      </c>
       <c r="C377" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D377" s="1" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="E377" s="1" t="s">
         <v>15</v>
@@ -12408,16 +12405,16 @@
     </row>
     <row r="378" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A378" s="1" t="s">
+        <v>794</v>
+      </c>
+      <c r="B378" s="1" t="s">
         <v>795</v>
       </c>
-      <c r="B378" s="1" t="s">
-        <v>796</v>
-      </c>
       <c r="C378" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D378" s="1" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="E378" s="1" t="s">
         <v>18</v>
@@ -12428,16 +12425,16 @@
     </row>
     <row r="379" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A379" s="1" t="s">
+        <v>796</v>
+      </c>
+      <c r="B379" s="1" t="s">
         <v>797</v>
       </c>
-      <c r="B379" s="1" t="s">
-        <v>798</v>
-      </c>
       <c r="C379" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D379" s="1" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="E379" s="1" t="s">
         <v>21</v>
@@ -12448,16 +12445,16 @@
     </row>
     <row r="380" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A380" s="1" t="s">
+        <v>798</v>
+      </c>
+      <c r="B380" s="1" t="s">
         <v>799</v>
       </c>
-      <c r="B380" s="1" t="s">
-        <v>800</v>
-      </c>
       <c r="C380" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D380" s="1" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="E380" s="1" t="s">
         <v>24</v>
@@ -12468,16 +12465,16 @@
     </row>
     <row r="381" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A381" s="1" t="s">
+        <v>800</v>
+      </c>
+      <c r="B381" s="1" t="s">
         <v>801</v>
       </c>
-      <c r="B381" s="1" t="s">
-        <v>802</v>
-      </c>
       <c r="C381" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D381" s="1" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="E381" s="1" t="s">
         <v>55</v>
@@ -12488,16 +12485,16 @@
     </row>
     <row r="382" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A382" s="1" t="s">
+        <v>802</v>
+      </c>
+      <c r="B382" s="1" t="s">
         <v>803</v>
       </c>
-      <c r="B382" s="1" t="s">
-        <v>804</v>
-      </c>
       <c r="C382" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D382" s="1" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="E382" s="1" t="s">
         <v>28</v>
@@ -12508,16 +12505,16 @@
     </row>
     <row r="383" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A383" s="1" t="s">
+        <v>804</v>
+      </c>
+      <c r="B383" s="1" t="s">
         <v>805</v>
       </c>
-      <c r="B383" s="1" t="s">
-        <v>806</v>
-      </c>
       <c r="C383" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D383" s="1" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="E383" s="1" t="s">
         <v>31</v>
@@ -12528,16 +12525,16 @@
     </row>
     <row r="384" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A384" s="1" t="s">
+        <v>806</v>
+      </c>
+      <c r="B384" s="1" t="s">
         <v>807</v>
       </c>
-      <c r="B384" s="1" t="s">
-        <v>808</v>
-      </c>
       <c r="C384" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D384" s="1" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="E384" s="1" t="s">
         <v>34</v>
@@ -12548,16 +12545,16 @@
     </row>
     <row r="385" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A385" s="1" t="s">
+        <v>808</v>
+      </c>
+      <c r="B385" s="1" t="s">
         <v>809</v>
       </c>
-      <c r="B385" s="1" t="s">
-        <v>810</v>
-      </c>
       <c r="C385" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D385" s="1" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="E385" s="1" t="s">
         <v>37</v>
@@ -12568,16 +12565,16 @@
     </row>
     <row r="386" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A386" s="1" t="s">
+        <v>810</v>
+      </c>
+      <c r="B386" s="1" t="s">
         <v>811</v>
       </c>
-      <c r="B386" s="1" t="s">
-        <v>812</v>
-      </c>
       <c r="C386" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D386" s="1" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="E386" s="1" t="s">
         <v>66</v>
@@ -12588,16 +12585,16 @@
     </row>
     <row r="387" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A387" s="1" t="s">
+        <v>812</v>
+      </c>
+      <c r="B387" s="1" t="s">
         <v>813</v>
       </c>
-      <c r="B387" s="1" t="s">
-        <v>814</v>
-      </c>
       <c r="C387" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D387" s="1" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="E387" s="1" t="s">
         <v>98</v>
@@ -12608,16 +12605,16 @@
     </row>
     <row r="388" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A388" s="1" t="s">
+        <v>814</v>
+      </c>
+      <c r="B388" s="1" t="s">
         <v>815</v>
       </c>
-      <c r="B388" s="1" t="s">
-        <v>816</v>
-      </c>
       <c r="C388" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D388" s="1" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="E388" s="1" t="s">
         <v>101</v>
@@ -12628,16 +12625,16 @@
     </row>
     <row r="389" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A389" s="1" t="s">
+        <v>816</v>
+      </c>
+      <c r="B389" s="1" t="s">
         <v>817</v>
       </c>
-      <c r="B389" s="1" t="s">
-        <v>818</v>
-      </c>
       <c r="C389" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D389" s="1" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="E389" s="1" t="s">
         <v>104</v>
@@ -12648,16 +12645,16 @@
     </row>
     <row r="390" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A390" s="1" t="s">
+        <v>818</v>
+      </c>
+      <c r="B390" s="1" t="s">
         <v>819</v>
       </c>
-      <c r="B390" s="1" t="s">
-        <v>820</v>
-      </c>
       <c r="C390" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D390" s="1" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="E390" s="1" t="s">
         <v>107</v>
@@ -12668,16 +12665,16 @@
     </row>
     <row r="391" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A391" s="1" t="s">
+        <v>820</v>
+      </c>
+      <c r="B391" s="1" t="s">
         <v>821</v>
       </c>
-      <c r="B391" s="1" t="s">
-        <v>822</v>
-      </c>
       <c r="C391" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D391" s="1" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="E391" s="1" t="s">
         <v>110</v>
@@ -12688,16 +12685,16 @@
     </row>
     <row r="392" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A392" s="1" t="s">
+        <v>822</v>
+      </c>
+      <c r="B392" s="1" t="s">
         <v>823</v>
       </c>
-      <c r="B392" s="1" t="s">
-        <v>824</v>
-      </c>
       <c r="C392" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D392" s="1" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="E392" s="1" t="s">
         <v>150</v>
@@ -12708,16 +12705,16 @@
     </row>
     <row r="393" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A393" s="1" t="s">
+        <v>824</v>
+      </c>
+      <c r="B393" s="1" t="s">
         <v>825</v>
       </c>
-      <c r="B393" s="1" t="s">
-        <v>826</v>
-      </c>
       <c r="C393" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D393" s="1" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="E393" s="1" t="s">
         <v>153</v>
@@ -12728,16 +12725,16 @@
     </row>
     <row r="394" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A394" s="1" t="s">
+        <v>826</v>
+      </c>
+      <c r="B394" s="1" t="s">
         <v>827</v>
       </c>
-      <c r="B394" s="1" t="s">
+      <c r="C394" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D394" s="1" t="s">
         <v>828</v>
-      </c>
-      <c r="C394" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D394" s="1" t="s">
-        <v>829</v>
       </c>
       <c r="E394" s="1" t="s">
         <v>4</v>
@@ -12748,16 +12745,16 @@
     </row>
     <row r="395" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A395" s="1" t="s">
+        <v>829</v>
+      </c>
+      <c r="B395" s="1" t="s">
         <v>830</v>
       </c>
-      <c r="B395" s="1" t="s">
-        <v>831</v>
-      </c>
       <c r="C395" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D395" s="1" t="s">
-        <v>829</v>
+        <v>828</v>
       </c>
       <c r="E395" s="1" t="s">
         <v>8</v>
@@ -12768,16 +12765,16 @@
     </row>
     <row r="396" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A396" s="1" t="s">
+        <v>831</v>
+      </c>
+      <c r="B396" s="1" t="s">
         <v>832</v>
       </c>
-      <c r="B396" s="1" t="s">
-        <v>833</v>
-      </c>
       <c r="C396" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D396" s="1" t="s">
-        <v>829</v>
+        <v>828</v>
       </c>
       <c r="E396" s="1" t="s">
         <v>12</v>
@@ -12788,16 +12785,16 @@
     </row>
     <row r="397" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A397" s="1" t="s">
+        <v>833</v>
+      </c>
+      <c r="B397" s="1" t="s">
         <v>834</v>
       </c>
-      <c r="B397" s="1" t="s">
-        <v>835</v>
-      </c>
       <c r="C397" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D397" s="1" t="s">
-        <v>829</v>
+        <v>828</v>
       </c>
       <c r="E397" s="1" t="s">
         <v>15</v>
@@ -12808,16 +12805,16 @@
     </row>
     <row r="398" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A398" s="1" t="s">
+        <v>835</v>
+      </c>
+      <c r="B398" s="1" t="s">
         <v>836</v>
       </c>
-      <c r="B398" s="1" t="s">
-        <v>837</v>
-      </c>
       <c r="C398" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D398" s="1" t="s">
-        <v>829</v>
+        <v>828</v>
       </c>
       <c r="E398" s="1" t="s">
         <v>18</v>
@@ -12828,16 +12825,16 @@
     </row>
     <row r="399" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A399" s="1" t="s">
+        <v>837</v>
+      </c>
+      <c r="B399" s="1" t="s">
         <v>838</v>
       </c>
-      <c r="B399" s="1" t="s">
-        <v>839</v>
-      </c>
       <c r="C399" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D399" s="1" t="s">
-        <v>829</v>
+        <v>828</v>
       </c>
       <c r="E399" s="1" t="s">
         <v>21</v>
@@ -12848,16 +12845,16 @@
     </row>
     <row r="400" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A400" s="1" t="s">
+        <v>839</v>
+      </c>
+      <c r="B400" s="1" t="s">
         <v>840</v>
       </c>
-      <c r="B400" s="1" t="s">
-        <v>841</v>
-      </c>
       <c r="C400" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D400" s="1" t="s">
-        <v>829</v>
+        <v>828</v>
       </c>
       <c r="E400" s="1" t="s">
         <v>24</v>
@@ -12868,16 +12865,16 @@
     </row>
     <row r="401" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A401" s="1" t="s">
+        <v>841</v>
+      </c>
+      <c r="B401" s="1" t="s">
         <v>842</v>
       </c>
-      <c r="B401" s="1" t="s">
-        <v>843</v>
-      </c>
       <c r="C401" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D401" s="1" t="s">
-        <v>829</v>
+        <v>828</v>
       </c>
       <c r="E401" s="1" t="s">
         <v>55</v>
@@ -12888,16 +12885,16 @@
     </row>
     <row r="402" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A402" s="1" t="s">
+        <v>843</v>
+      </c>
+      <c r="B402" s="1" t="s">
         <v>844</v>
       </c>
-      <c r="B402" s="1" t="s">
-        <v>845</v>
-      </c>
       <c r="C402" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D402" s="1" t="s">
-        <v>829</v>
+        <v>828</v>
       </c>
       <c r="E402" s="1" t="s">
         <v>28</v>
@@ -12908,16 +12905,16 @@
     </row>
     <row r="403" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A403" s="1" t="s">
+        <v>845</v>
+      </c>
+      <c r="B403" s="1" t="s">
         <v>846</v>
       </c>
-      <c r="B403" s="1" t="s">
-        <v>847</v>
-      </c>
       <c r="C403" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D403" s="1" t="s">
-        <v>829</v>
+        <v>828</v>
       </c>
       <c r="E403" s="1" t="s">
         <v>31</v>
@@ -12928,16 +12925,16 @@
     </row>
     <row r="404" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A404" s="1" t="s">
+        <v>847</v>
+      </c>
+      <c r="B404" s="1" t="s">
         <v>848</v>
       </c>
-      <c r="B404" s="1" t="s">
-        <v>849</v>
-      </c>
       <c r="C404" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D404" s="1" t="s">
-        <v>829</v>
+        <v>828</v>
       </c>
       <c r="E404" s="1" t="s">
         <v>34</v>
@@ -12948,16 +12945,16 @@
     </row>
     <row r="405" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A405" s="1" t="s">
+        <v>849</v>
+      </c>
+      <c r="B405" s="1" t="s">
         <v>850</v>
       </c>
-      <c r="B405" s="1" t="s">
-        <v>851</v>
-      </c>
       <c r="C405" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D405" s="1" t="s">
-        <v>829</v>
+        <v>828</v>
       </c>
       <c r="E405" s="1" t="s">
         <v>37</v>
@@ -12968,16 +12965,16 @@
     </row>
     <row r="406" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A406" s="1" t="s">
+        <v>851</v>
+      </c>
+      <c r="B406" s="1" t="s">
         <v>852</v>
       </c>
-      <c r="B406" s="1" t="s">
-        <v>853</v>
-      </c>
       <c r="C406" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D406" s="1" t="s">
-        <v>829</v>
+        <v>828</v>
       </c>
       <c r="E406" s="1" t="s">
         <v>66</v>
@@ -12988,16 +12985,16 @@
     </row>
     <row r="407" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A407" s="1" t="s">
+        <v>853</v>
+      </c>
+      <c r="B407" s="1" t="s">
         <v>854</v>
       </c>
-      <c r="B407" s="1" t="s">
-        <v>855</v>
-      </c>
       <c r="C407" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D407" s="1" t="s">
-        <v>829</v>
+        <v>828</v>
       </c>
       <c r="E407" s="1" t="s">
         <v>98</v>
@@ -13008,16 +13005,16 @@
     </row>
     <row r="408" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A408" s="1" t="s">
+        <v>855</v>
+      </c>
+      <c r="B408" s="1" t="s">
         <v>856</v>
       </c>
-      <c r="B408" s="1" t="s">
-        <v>857</v>
-      </c>
       <c r="C408" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D408" s="1" t="s">
-        <v>829</v>
+        <v>828</v>
       </c>
       <c r="E408" s="1" t="s">
         <v>101</v>
@@ -13028,16 +13025,16 @@
     </row>
     <row r="409" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A409" s="1" t="s">
+        <v>857</v>
+      </c>
+      <c r="B409" s="1" t="s">
         <v>858</v>
       </c>
-      <c r="B409" s="1" t="s">
-        <v>859</v>
-      </c>
       <c r="C409" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D409" s="1" t="s">
-        <v>829</v>
+        <v>828</v>
       </c>
       <c r="E409" s="1" t="s">
         <v>104</v>
@@ -13048,16 +13045,16 @@
     </row>
     <row r="410" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A410" s="1" t="s">
+        <v>859</v>
+      </c>
+      <c r="B410" s="1" t="s">
         <v>860</v>
       </c>
-      <c r="B410" s="1" t="s">
-        <v>861</v>
-      </c>
       <c r="C410" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D410" s="1" t="s">
-        <v>829</v>
+        <v>828</v>
       </c>
       <c r="E410" s="1" t="s">
         <v>107</v>
@@ -13068,16 +13065,16 @@
     </row>
     <row r="411" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A411" s="1" t="s">
+        <v>861</v>
+      </c>
+      <c r="B411" s="1" t="s">
         <v>862</v>
       </c>
-      <c r="B411" s="1" t="s">
-        <v>863</v>
-      </c>
       <c r="C411" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D411" s="1" t="s">
-        <v>829</v>
+        <v>828</v>
       </c>
       <c r="E411" s="1" t="s">
         <v>110</v>
@@ -13088,16 +13085,16 @@
     </row>
     <row r="412" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A412" s="1" t="s">
+        <v>863</v>
+      </c>
+      <c r="B412" s="1" t="s">
         <v>864</v>
       </c>
-      <c r="B412" s="1" t="s">
-        <v>865</v>
-      </c>
       <c r="C412" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D412" s="1" t="s">
-        <v>829</v>
+        <v>828</v>
       </c>
       <c r="E412" s="1" t="s">
         <v>150</v>
@@ -13108,16 +13105,16 @@
     </row>
     <row r="413" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A413" s="1" t="s">
+        <v>865</v>
+      </c>
+      <c r="B413" s="1" t="s">
         <v>866</v>
       </c>
-      <c r="B413" s="1" t="s">
-        <v>867</v>
-      </c>
       <c r="C413" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D413" s="1" t="s">
-        <v>829</v>
+        <v>828</v>
       </c>
       <c r="E413" s="1" t="s">
         <v>153</v>
@@ -13128,16 +13125,16 @@
     </row>
     <row r="414" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A414" s="1" t="s">
+        <v>867</v>
+      </c>
+      <c r="B414" s="1" t="s">
         <v>868</v>
       </c>
-      <c r="B414" s="1" t="s">
-        <v>869</v>
-      </c>
       <c r="C414" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D414" s="1" t="s">
-        <v>829</v>
+        <v>828</v>
       </c>
       <c r="E414" s="1" t="s">
         <v>197</v>
@@ -13148,16 +13145,16 @@
     </row>
     <row r="415" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A415" s="1" t="s">
+        <v>869</v>
+      </c>
+      <c r="B415" s="1" t="s">
         <v>870</v>
       </c>
-      <c r="B415" s="1" t="s">
+      <c r="C415" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D415" s="1" t="s">
         <v>871</v>
-      </c>
-      <c r="C415" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D415" s="1" t="s">
-        <v>872</v>
       </c>
       <c r="E415" s="1" t="s">
         <v>4</v>
@@ -13168,16 +13165,16 @@
     </row>
     <row r="416" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A416" s="1" t="s">
+        <v>872</v>
+      </c>
+      <c r="B416" s="1" t="s">
         <v>873</v>
       </c>
-      <c r="B416" s="1" t="s">
-        <v>874</v>
-      </c>
       <c r="C416" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D416" s="1" t="s">
-        <v>872</v>
+        <v>871</v>
       </c>
       <c r="E416" s="1" t="s">
         <v>8</v>
@@ -13188,16 +13185,16 @@
     </row>
     <row r="417" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A417" s="1" t="s">
+        <v>874</v>
+      </c>
+      <c r="B417" s="1" t="s">
         <v>875</v>
       </c>
-      <c r="B417" s="1" t="s">
-        <v>876</v>
-      </c>
       <c r="C417" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D417" s="1" t="s">
-        <v>872</v>
+        <v>871</v>
       </c>
       <c r="E417" s="1" t="s">
         <v>12</v>
@@ -13208,16 +13205,16 @@
     </row>
     <row r="418" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A418" s="1" t="s">
+        <v>876</v>
+      </c>
+      <c r="B418" s="1" t="s">
         <v>877</v>
       </c>
-      <c r="B418" s="1" t="s">
-        <v>878</v>
-      </c>
       <c r="C418" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D418" s="1" t="s">
-        <v>872</v>
+        <v>871</v>
       </c>
       <c r="E418" s="1" t="s">
         <v>15</v>
@@ -13228,16 +13225,16 @@
     </row>
     <row r="419" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A419" s="1" t="s">
+        <v>878</v>
+      </c>
+      <c r="B419" s="1" t="s">
         <v>879</v>
       </c>
-      <c r="B419" s="1" t="s">
-        <v>880</v>
-      </c>
       <c r="C419" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D419" s="1" t="s">
-        <v>872</v>
+        <v>871</v>
       </c>
       <c r="E419" s="1" t="s">
         <v>18</v>
@@ -13248,16 +13245,16 @@
     </row>
     <row r="420" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A420" s="1" t="s">
+        <v>880</v>
+      </c>
+      <c r="B420" s="1" t="s">
         <v>881</v>
       </c>
-      <c r="B420" s="1" t="s">
-        <v>882</v>
-      </c>
       <c r="C420" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D420" s="1" t="s">
-        <v>872</v>
+        <v>871</v>
       </c>
       <c r="E420" s="1" t="s">
         <v>21</v>
@@ -13268,16 +13265,16 @@
     </row>
     <row r="421" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A421" s="1" t="s">
+        <v>882</v>
+      </c>
+      <c r="B421" s="1" t="s">
         <v>883</v>
       </c>
-      <c r="B421" s="1" t="s">
-        <v>884</v>
-      </c>
       <c r="C421" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D421" s="1" t="s">
-        <v>872</v>
+        <v>871</v>
       </c>
       <c r="E421" s="1" t="s">
         <v>24</v>
@@ -13288,16 +13285,16 @@
     </row>
     <row r="422" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A422" s="1" t="s">
+        <v>884</v>
+      </c>
+      <c r="B422" s="1" t="s">
         <v>885</v>
       </c>
-      <c r="B422" s="1" t="s">
+      <c r="C422" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D422" s="1" t="s">
         <v>886</v>
-      </c>
-      <c r="C422" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D422" s="1" t="s">
-        <v>887</v>
       </c>
       <c r="E422" s="1" t="s">
         <v>4</v>
@@ -13308,16 +13305,16 @@
     </row>
     <row r="423" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A423" s="1" t="s">
+        <v>887</v>
+      </c>
+      <c r="B423" s="1" t="s">
         <v>888</v>
       </c>
-      <c r="B423" s="1" t="s">
-        <v>889</v>
-      </c>
       <c r="C423" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D423" s="1" t="s">
-        <v>887</v>
+        <v>886</v>
       </c>
       <c r="E423" s="1" t="s">
         <v>8</v>
@@ -13328,16 +13325,16 @@
     </row>
     <row r="424" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A424" s="1" t="s">
+        <v>889</v>
+      </c>
+      <c r="B424" s="1" t="s">
         <v>890</v>
       </c>
-      <c r="B424" s="1" t="s">
-        <v>891</v>
-      </c>
       <c r="C424" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D424" s="1" t="s">
-        <v>887</v>
+        <v>886</v>
       </c>
       <c r="E424" s="1" t="s">
         <v>12</v>
@@ -13348,36 +13345,36 @@
     </row>
     <row r="425" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A425" s="1" t="s">
+        <v>891</v>
+      </c>
+      <c r="B425" s="1" t="s">
         <v>892</v>
       </c>
-      <c r="B425" s="1" t="s">
-        <v>893</v>
-      </c>
       <c r="C425" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D425" s="1" t="s">
-        <v>887</v>
+        <v>886</v>
       </c>
       <c r="E425" s="1" t="s">
         <v>15</v>
       </c>
       <c r="F425" s="1" t="s">
-        <v>894</v>
+        <v>893</v>
       </c>
     </row>
     <row r="426" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A426" s="1" t="s">
+        <v>894</v>
+      </c>
+      <c r="B426" s="1" t="s">
         <v>895</v>
       </c>
-      <c r="B426" s="1" t="s">
-        <v>896</v>
-      </c>
       <c r="C426" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D426" s="1" t="s">
-        <v>887</v>
+        <v>886</v>
       </c>
       <c r="E426" s="1" t="s">
         <v>18</v>
@@ -13388,16 +13385,16 @@
     </row>
     <row r="427" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A427" s="1" t="s">
+        <v>896</v>
+      </c>
+      <c r="B427" s="1" t="s">
         <v>897</v>
       </c>
-      <c r="B427" s="1" t="s">
-        <v>898</v>
-      </c>
       <c r="C427" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D427" s="1" t="s">
-        <v>887</v>
+        <v>886</v>
       </c>
       <c r="E427" s="1" t="s">
         <v>21</v>
@@ -13408,16 +13405,16 @@
     </row>
     <row r="428" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A428" s="1" t="s">
+        <v>898</v>
+      </c>
+      <c r="B428" s="1" t="s">
         <v>899</v>
       </c>
-      <c r="B428" s="1" t="s">
-        <v>900</v>
-      </c>
       <c r="C428" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D428" s="1" t="s">
-        <v>887</v>
+        <v>886</v>
       </c>
       <c r="E428" s="1" t="s">
         <v>24</v>
@@ -13428,16 +13425,16 @@
     </row>
     <row r="429" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A429" s="1" t="s">
+        <v>900</v>
+      </c>
+      <c r="B429" s="1" t="s">
         <v>901</v>
       </c>
-      <c r="B429" s="1" t="s">
-        <v>902</v>
-      </c>
       <c r="C429" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D429" s="1" t="s">
-        <v>887</v>
+        <v>886</v>
       </c>
       <c r="E429" s="1" t="s">
         <v>55</v>
@@ -13448,16 +13445,16 @@
     </row>
     <row r="430" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A430" s="1" t="s">
+        <v>902</v>
+      </c>
+      <c r="B430" s="1" t="s">
         <v>903</v>
       </c>
-      <c r="B430" s="1" t="s">
-        <v>904</v>
-      </c>
       <c r="C430" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D430" s="1" t="s">
-        <v>887</v>
+        <v>886</v>
       </c>
       <c r="E430" s="1" t="s">
         <v>28</v>
@@ -13468,16 +13465,16 @@
     </row>
     <row r="431" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A431" s="1" t="s">
+        <v>904</v>
+      </c>
+      <c r="B431" s="1" t="s">
         <v>905</v>
       </c>
-      <c r="B431" s="1" t="s">
-        <v>906</v>
-      </c>
       <c r="C431" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D431" s="1" t="s">
-        <v>887</v>
+        <v>886</v>
       </c>
       <c r="E431" s="1" t="s">
         <v>31</v>
@@ -13488,16 +13485,16 @@
     </row>
     <row r="432" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A432" s="1" t="s">
+        <v>906</v>
+      </c>
+      <c r="B432" s="1" t="s">
         <v>907</v>
       </c>
-      <c r="B432" s="1" t="s">
-        <v>908</v>
-      </c>
       <c r="C432" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D432" s="1" t="s">
-        <v>887</v>
+        <v>886</v>
       </c>
       <c r="E432" s="1" t="s">
         <v>34</v>
@@ -13508,16 +13505,16 @@
     </row>
     <row r="433" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A433" s="1" t="s">
+        <v>908</v>
+      </c>
+      <c r="B433" s="1" t="s">
         <v>909</v>
       </c>
-      <c r="B433" s="1" t="s">
-        <v>910</v>
-      </c>
       <c r="C433" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D433" s="1" t="s">
-        <v>887</v>
+        <v>886</v>
       </c>
       <c r="E433" s="1" t="s">
         <v>37</v>
@@ -13528,16 +13525,16 @@
     </row>
     <row r="434" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A434" s="1" t="s">
+        <v>910</v>
+      </c>
+      <c r="B434" s="1" t="s">
         <v>911</v>
       </c>
-      <c r="B434" s="1" t="s">
-        <v>912</v>
-      </c>
       <c r="C434" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D434" s="1" t="s">
-        <v>887</v>
+        <v>886</v>
       </c>
       <c r="E434" s="1" t="s">
         <v>66</v>
@@ -13548,16 +13545,16 @@
     </row>
     <row r="435" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A435" s="1" t="s">
+        <v>912</v>
+      </c>
+      <c r="B435" s="1" t="s">
         <v>913</v>
       </c>
-      <c r="B435" s="1" t="s">
-        <v>914</v>
-      </c>
       <c r="C435" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D435" s="1" t="s">
-        <v>887</v>
+        <v>886</v>
       </c>
       <c r="E435" s="1" t="s">
         <v>98</v>
@@ -13568,16 +13565,16 @@
     </row>
     <row r="436" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A436" s="1" t="s">
+        <v>914</v>
+      </c>
+      <c r="B436" s="1" t="s">
         <v>915</v>
       </c>
-      <c r="B436" s="1" t="s">
-        <v>916</v>
-      </c>
       <c r="C436" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D436" s="1" t="s">
-        <v>887</v>
+        <v>886</v>
       </c>
       <c r="E436" s="1" t="s">
         <v>101</v>
@@ -13588,16 +13585,16 @@
     </row>
     <row r="437" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A437" s="1" t="s">
+        <v>916</v>
+      </c>
+      <c r="B437" s="1" t="s">
         <v>917</v>
       </c>
-      <c r="B437" s="1" t="s">
-        <v>918</v>
-      </c>
       <c r="C437" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D437" s="1" t="s">
-        <v>887</v>
+        <v>886</v>
       </c>
       <c r="E437" s="1" t="s">
         <v>104</v>
@@ -13608,16 +13605,16 @@
     </row>
     <row r="438" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A438" s="1" t="s">
+        <v>918</v>
+      </c>
+      <c r="B438" s="1" t="s">
         <v>919</v>
       </c>
-      <c r="B438" s="1" t="s">
+      <c r="C438" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D438" s="1" t="s">
         <v>920</v>
-      </c>
-      <c r="C438" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D438" s="1" t="s">
-        <v>921</v>
       </c>
       <c r="E438" s="1" t="s">
         <v>4</v>
@@ -13628,16 +13625,16 @@
     </row>
     <row r="439" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A439" s="1" t="s">
+        <v>921</v>
+      </c>
+      <c r="B439" s="1" t="s">
         <v>922</v>
       </c>
-      <c r="B439" s="1" t="s">
-        <v>923</v>
-      </c>
       <c r="C439" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D439" s="1" t="s">
-        <v>921</v>
+        <v>920</v>
       </c>
       <c r="E439" s="1" t="s">
         <v>8</v>
@@ -13648,16 +13645,16 @@
     </row>
     <row r="440" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A440" s="1" t="s">
+        <v>923</v>
+      </c>
+      <c r="B440" s="1" t="s">
         <v>924</v>
       </c>
-      <c r="B440" s="1" t="s">
-        <v>925</v>
-      </c>
       <c r="C440" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D440" s="1" t="s">
-        <v>921</v>
+        <v>920</v>
       </c>
       <c r="E440" s="1" t="s">
         <v>12</v>
@@ -13668,16 +13665,16 @@
     </row>
     <row r="441" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A441" s="1" t="s">
+        <v>925</v>
+      </c>
+      <c r="B441" s="1" t="s">
         <v>926</v>
       </c>
-      <c r="B441" s="1" t="s">
-        <v>927</v>
-      </c>
       <c r="C441" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D441" s="1" t="s">
-        <v>921</v>
+        <v>920</v>
       </c>
       <c r="E441" s="1" t="s">
         <v>15</v>
@@ -13688,16 +13685,16 @@
     </row>
     <row r="442" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A442" s="1" t="s">
+        <v>927</v>
+      </c>
+      <c r="B442" s="1" t="s">
         <v>928</v>
       </c>
-      <c r="B442" s="1" t="s">
-        <v>929</v>
-      </c>
       <c r="C442" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D442" s="1" t="s">
-        <v>921</v>
+        <v>920</v>
       </c>
       <c r="E442" s="1" t="s">
         <v>18</v>
@@ -13708,16 +13705,16 @@
     </row>
     <row r="443" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A443" s="1" t="s">
+        <v>929</v>
+      </c>
+      <c r="B443" s="1" t="s">
         <v>930</v>
       </c>
-      <c r="B443" s="1" t="s">
-        <v>931</v>
-      </c>
       <c r="C443" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D443" s="1" t="s">
-        <v>921</v>
+        <v>920</v>
       </c>
       <c r="E443" s="1" t="s">
         <v>21</v>
@@ -13728,16 +13725,16 @@
     </row>
     <row r="444" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A444" s="1" t="s">
+        <v>931</v>
+      </c>
+      <c r="B444" s="1" t="s">
         <v>932</v>
       </c>
-      <c r="B444" s="1" t="s">
-        <v>933</v>
-      </c>
       <c r="C444" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D444" s="1" t="s">
-        <v>921</v>
+        <v>920</v>
       </c>
       <c r="E444" s="1" t="s">
         <v>24</v>
@@ -13748,16 +13745,16 @@
     </row>
     <row r="445" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A445" s="1" t="s">
+        <v>933</v>
+      </c>
+      <c r="B445" s="1" t="s">
         <v>934</v>
       </c>
-      <c r="B445" s="1" t="s">
-        <v>935</v>
-      </c>
       <c r="C445" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D445" s="1" t="s">
-        <v>921</v>
+        <v>920</v>
       </c>
       <c r="E445" s="1" t="s">
         <v>55</v>
@@ -13768,16 +13765,16 @@
     </row>
     <row r="446" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A446" s="1" t="s">
+        <v>935</v>
+      </c>
+      <c r="B446" s="1" t="s">
         <v>936</v>
       </c>
-      <c r="B446" s="1" t="s">
-        <v>937</v>
-      </c>
       <c r="C446" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D446" s="1" t="s">
-        <v>921</v>
+        <v>920</v>
       </c>
       <c r="E446" s="1" t="s">
         <v>28</v>
@@ -13788,16 +13785,16 @@
     </row>
     <row r="447" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A447" s="1" t="s">
+        <v>937</v>
+      </c>
+      <c r="B447" s="1" t="s">
         <v>938</v>
       </c>
-      <c r="B447" s="1" t="s">
-        <v>939</v>
-      </c>
       <c r="C447" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D447" s="1" t="s">
-        <v>921</v>
+        <v>920</v>
       </c>
       <c r="E447" s="1" t="s">
         <v>31</v>
@@ -13808,16 +13805,16 @@
     </row>
     <row r="448" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A448" s="1" t="s">
+        <v>939</v>
+      </c>
+      <c r="B448" s="1" t="s">
         <v>940</v>
       </c>
-      <c r="B448" s="1" t="s">
-        <v>941</v>
-      </c>
       <c r="C448" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D448" s="1" t="s">
-        <v>921</v>
+        <v>920</v>
       </c>
       <c r="E448" s="1" t="s">
         <v>34</v>
@@ -13828,16 +13825,16 @@
     </row>
     <row r="449" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A449" s="1" t="s">
+        <v>941</v>
+      </c>
+      <c r="B449" s="1" t="s">
         <v>942</v>
       </c>
-      <c r="B449" s="1" t="s">
-        <v>943</v>
-      </c>
       <c r="C449" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D449" s="1" t="s">
-        <v>921</v>
+        <v>920</v>
       </c>
       <c r="E449" s="1" t="s">
         <v>37</v>
@@ -13848,16 +13845,16 @@
     </row>
     <row r="450" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A450" s="1" t="s">
+        <v>943</v>
+      </c>
+      <c r="B450" s="1" t="s">
         <v>944</v>
       </c>
-      <c r="B450" s="1" t="s">
-        <v>945</v>
-      </c>
       <c r="C450" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D450" s="1" t="s">
-        <v>921</v>
+        <v>920</v>
       </c>
       <c r="E450" s="1" t="s">
         <v>66</v>
@@ -13868,16 +13865,16 @@
     </row>
     <row r="451" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A451" s="1" t="s">
+        <v>945</v>
+      </c>
+      <c r="B451" s="1" t="s">
         <v>946</v>
       </c>
-      <c r="B451" s="1" t="s">
-        <v>947</v>
-      </c>
       <c r="C451" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D451" s="1" t="s">
-        <v>921</v>
+        <v>920</v>
       </c>
       <c r="E451" s="1" t="s">
         <v>98</v>
@@ -13888,16 +13885,16 @@
     </row>
     <row r="452" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A452" s="1" t="s">
+        <v>947</v>
+      </c>
+      <c r="B452" s="1" t="s">
         <v>948</v>
       </c>
-      <c r="B452" s="1" t="s">
-        <v>949</v>
-      </c>
       <c r="C452" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D452" s="1" t="s">
-        <v>921</v>
+        <v>920</v>
       </c>
       <c r="E452" s="1" t="s">
         <v>101</v>
@@ -13908,16 +13905,16 @@
     </row>
     <row r="453" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A453" s="1" t="s">
+        <v>949</v>
+      </c>
+      <c r="B453" s="1" t="s">
         <v>950</v>
       </c>
-      <c r="B453" s="1" t="s">
+      <c r="C453" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D453" s="1" t="s">
         <v>951</v>
-      </c>
-      <c r="C453" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D453" s="1" t="s">
-        <v>952</v>
       </c>
       <c r="E453" s="1" t="s">
         <v>4</v>
@@ -13928,16 +13925,16 @@
     </row>
     <row r="454" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A454" s="1" t="s">
+        <v>952</v>
+      </c>
+      <c r="B454" s="1" t="s">
         <v>953</v>
       </c>
-      <c r="B454" s="1" t="s">
-        <v>954</v>
-      </c>
       <c r="C454" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D454" s="1" t="s">
-        <v>952</v>
+        <v>951</v>
       </c>
       <c r="E454" s="1" t="s">
         <v>8</v>
@@ -13948,16 +13945,16 @@
     </row>
     <row r="455" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A455" s="1" t="s">
+        <v>954</v>
+      </c>
+      <c r="B455" s="1" t="s">
         <v>955</v>
       </c>
-      <c r="B455" s="1" t="s">
-        <v>956</v>
-      </c>
       <c r="C455" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D455" s="1" t="s">
-        <v>952</v>
+        <v>951</v>
       </c>
       <c r="E455" s="1" t="s">
         <v>12</v>
@@ -13968,16 +13965,16 @@
     </row>
     <row r="456" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A456" s="1" t="s">
+        <v>956</v>
+      </c>
+      <c r="B456" s="1" t="s">
         <v>957</v>
       </c>
-      <c r="B456" s="1" t="s">
-        <v>958</v>
-      </c>
       <c r="C456" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D456" s="1" t="s">
-        <v>952</v>
+        <v>951</v>
       </c>
       <c r="E456" s="1" t="s">
         <v>15</v>
@@ -13988,16 +13985,16 @@
     </row>
     <row r="457" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A457" s="1" t="s">
+        <v>958</v>
+      </c>
+      <c r="B457" s="1" t="s">
         <v>959</v>
       </c>
-      <c r="B457" s="1" t="s">
-        <v>960</v>
-      </c>
       <c r="C457" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D457" s="1" t="s">
-        <v>952</v>
+        <v>951</v>
       </c>
       <c r="E457" s="1" t="s">
         <v>18</v>
@@ -14008,16 +14005,16 @@
     </row>
     <row r="458" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A458" s="1" t="s">
+        <v>960</v>
+      </c>
+      <c r="B458" s="1" t="s">
         <v>961</v>
       </c>
-      <c r="B458" s="1" t="s">
-        <v>962</v>
-      </c>
       <c r="C458" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D458" s="1" t="s">
-        <v>952</v>
+        <v>951</v>
       </c>
       <c r="E458" s="1" t="s">
         <v>21</v>
@@ -14028,16 +14025,16 @@
     </row>
     <row r="459" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A459" s="1" t="s">
+        <v>962</v>
+      </c>
+      <c r="B459" s="1" t="s">
         <v>963</v>
       </c>
-      <c r="B459" s="1" t="s">
-        <v>964</v>
-      </c>
       <c r="C459" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D459" s="1" t="s">
-        <v>952</v>
+        <v>951</v>
       </c>
       <c r="E459" s="1" t="s">
         <v>24</v>
@@ -14048,16 +14045,16 @@
     </row>
     <row r="460" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A460" s="1" t="s">
+        <v>964</v>
+      </c>
+      <c r="B460" s="1" t="s">
         <v>965</v>
       </c>
-      <c r="B460" s="1" t="s">
-        <v>966</v>
-      </c>
       <c r="C460" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D460" s="1" t="s">
-        <v>952</v>
+        <v>951</v>
       </c>
       <c r="E460" s="1" t="s">
         <v>55</v>
@@ -14068,16 +14065,16 @@
     </row>
     <row r="461" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A461" s="1" t="s">
+        <v>966</v>
+      </c>
+      <c r="B461" s="1" t="s">
         <v>967</v>
       </c>
-      <c r="B461" s="1" t="s">
-        <v>968</v>
-      </c>
       <c r="C461" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D461" s="1" t="s">
-        <v>952</v>
+        <v>951</v>
       </c>
       <c r="E461" s="1" t="s">
         <v>28</v>
@@ -14088,16 +14085,16 @@
     </row>
     <row r="462" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A462" s="1" t="s">
+        <v>968</v>
+      </c>
+      <c r="B462" s="1" t="s">
         <v>969</v>
       </c>
-      <c r="B462" s="1" t="s">
-        <v>970</v>
-      </c>
       <c r="C462" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D462" s="1" t="s">
-        <v>952</v>
+        <v>951</v>
       </c>
       <c r="E462" s="1" t="s">
         <v>31</v>
@@ -14108,16 +14105,16 @@
     </row>
     <row r="463" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A463" s="1" t="s">
+        <v>970</v>
+      </c>
+      <c r="B463" s="1" t="s">
         <v>971</v>
       </c>
-      <c r="B463" s="1" t="s">
-        <v>972</v>
-      </c>
       <c r="C463" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D463" s="1" t="s">
-        <v>952</v>
+        <v>951</v>
       </c>
       <c r="E463" s="1" t="s">
         <v>34</v>
@@ -14128,16 +14125,16 @@
     </row>
     <row r="464" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A464" s="1" t="s">
+        <v>972</v>
+      </c>
+      <c r="B464" s="1" t="s">
         <v>973</v>
       </c>
-      <c r="B464" s="1" t="s">
-        <v>974</v>
-      </c>
       <c r="C464" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D464" s="1" t="s">
-        <v>952</v>
+        <v>951</v>
       </c>
       <c r="E464" s="1" t="s">
         <v>37</v>
@@ -14148,16 +14145,16 @@
     </row>
     <row r="465" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A465" s="1" t="s">
+        <v>974</v>
+      </c>
+      <c r="B465" s="1" t="s">
         <v>975</v>
       </c>
-      <c r="B465" s="1" t="s">
-        <v>976</v>
-      </c>
       <c r="C465" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D465" s="1" t="s">
-        <v>952</v>
+        <v>951</v>
       </c>
       <c r="E465" s="1" t="s">
         <v>66</v>
@@ -14168,16 +14165,16 @@
     </row>
     <row r="466" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A466" s="1" t="s">
+        <v>976</v>
+      </c>
+      <c r="B466" s="1" t="s">
         <v>977</v>
       </c>
-      <c r="B466" s="1" t="s">
-        <v>978</v>
-      </c>
       <c r="C466" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D466" s="1" t="s">
-        <v>952</v>
+        <v>951</v>
       </c>
       <c r="E466" s="1" t="s">
         <v>98</v>
@@ -14188,16 +14185,16 @@
     </row>
     <row r="467" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A467" s="1" t="s">
+        <v>978</v>
+      </c>
+      <c r="B467" s="1" t="s">
         <v>979</v>
       </c>
-      <c r="B467" s="1" t="s">
-        <v>980</v>
-      </c>
       <c r="C467" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D467" s="1" t="s">
-        <v>952</v>
+        <v>951</v>
       </c>
       <c r="E467" s="1" t="s">
         <v>101</v>
@@ -14208,16 +14205,16 @@
     </row>
     <row r="468" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A468" s="1" t="s">
+        <v>980</v>
+      </c>
+      <c r="B468" s="1" t="s">
         <v>981</v>
       </c>
-      <c r="B468" s="1" t="s">
+      <c r="C468" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D468" s="1" t="s">
         <v>982</v>
-      </c>
-      <c r="C468" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D468" s="1" t="s">
-        <v>983</v>
       </c>
       <c r="E468" s="1" t="s">
         <v>4</v>
@@ -14228,16 +14225,16 @@
     </row>
     <row r="469" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A469" s="1" t="s">
+        <v>983</v>
+      </c>
+      <c r="B469" s="1" t="s">
         <v>984</v>
       </c>
-      <c r="B469" s="1" t="s">
-        <v>985</v>
-      </c>
       <c r="C469" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D469" s="1" t="s">
-        <v>983</v>
+        <v>982</v>
       </c>
       <c r="E469" s="1" t="s">
         <v>8</v>
@@ -14248,56 +14245,56 @@
     </row>
     <row r="470" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A470" s="1" t="s">
+        <v>985</v>
+      </c>
+      <c r="B470" s="1" t="s">
         <v>986</v>
       </c>
-      <c r="B470" s="1" t="s">
-        <v>987</v>
-      </c>
       <c r="C470" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D470" s="1" t="s">
-        <v>983</v>
+        <v>982</v>
       </c>
       <c r="E470" s="1" t="s">
         <v>12</v>
       </c>
       <c r="F470" s="1" t="s">
-        <v>988</v>
+        <v>987</v>
       </c>
     </row>
     <row r="471" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A471" s="1" t="s">
+        <v>988</v>
+      </c>
+      <c r="B471" s="1" t="s">
         <v>989</v>
       </c>
-      <c r="B471" s="1" t="s">
-        <v>990</v>
-      </c>
       <c r="C471" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D471" s="1" t="s">
-        <v>983</v>
+        <v>982</v>
       </c>
       <c r="E471" s="1" t="s">
         <v>15</v>
       </c>
       <c r="F471" s="1" t="s">
-        <v>988</v>
+        <v>987</v>
       </c>
     </row>
     <row r="472" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A472" s="1" t="s">
+        <v>990</v>
+      </c>
+      <c r="B472" s="1" t="s">
         <v>991</v>
       </c>
-      <c r="B472" s="1" t="s">
-        <v>992</v>
-      </c>
       <c r="C472" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D472" s="1" t="s">
-        <v>983</v>
+        <v>982</v>
       </c>
       <c r="E472" s="1" t="s">
         <v>18</v>
@@ -14308,16 +14305,16 @@
     </row>
     <row r="473" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A473" s="1" t="s">
+        <v>992</v>
+      </c>
+      <c r="B473" s="1" t="s">
         <v>993</v>
       </c>
-      <c r="B473" s="1" t="s">
-        <v>994</v>
-      </c>
       <c r="C473" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D473" s="1" t="s">
-        <v>983</v>
+        <v>982</v>
       </c>
       <c r="E473" s="1" t="s">
         <v>21</v>
@@ -14328,16 +14325,16 @@
     </row>
     <row r="474" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A474" s="1" t="s">
+        <v>994</v>
+      </c>
+      <c r="B474" s="1" t="s">
         <v>995</v>
       </c>
-      <c r="B474" s="1" t="s">
-        <v>996</v>
-      </c>
       <c r="C474" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D474" s="1" t="s">
-        <v>983</v>
+        <v>982</v>
       </c>
       <c r="E474" s="1" t="s">
         <v>24</v>
@@ -14348,16 +14345,16 @@
     </row>
     <row r="475" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A475" s="1" t="s">
+        <v>996</v>
+      </c>
+      <c r="B475" s="1" t="s">
         <v>997</v>
       </c>
-      <c r="B475" s="1" t="s">
-        <v>998</v>
-      </c>
       <c r="C475" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D475" s="1" t="s">
-        <v>983</v>
+        <v>982</v>
       </c>
       <c r="E475" s="1" t="s">
         <v>55</v>
@@ -14368,16 +14365,16 @@
     </row>
     <row r="476" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A476" s="1" t="s">
+        <v>998</v>
+      </c>
+      <c r="B476" s="1" t="s">
         <v>999</v>
       </c>
-      <c r="B476" s="1" t="s">
-        <v>1000</v>
-      </c>
       <c r="C476" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D476" s="1" t="s">
-        <v>983</v>
+        <v>982</v>
       </c>
       <c r="E476" s="1" t="s">
         <v>28</v>
@@ -14388,16 +14385,16 @@
     </row>
     <row r="477" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A477" s="1" t="s">
+        <v>1000</v>
+      </c>
+      <c r="B477" s="1" t="s">
         <v>1001</v>
       </c>
-      <c r="B477" s="1" t="s">
-        <v>1002</v>
-      </c>
       <c r="C477" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D477" s="1" t="s">
-        <v>983</v>
+        <v>982</v>
       </c>
       <c r="E477" s="1" t="s">
         <v>31</v>
@@ -14408,16 +14405,16 @@
     </row>
     <row r="478" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A478" s="1" t="s">
+        <v>1002</v>
+      </c>
+      <c r="B478" s="1" t="s">
         <v>1003</v>
       </c>
-      <c r="B478" s="1" t="s">
-        <v>1004</v>
-      </c>
       <c r="C478" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D478" s="1" t="s">
-        <v>983</v>
+        <v>982</v>
       </c>
       <c r="E478" s="1" t="s">
         <v>34</v>
@@ -14428,16 +14425,16 @@
     </row>
     <row r="479" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A479" s="1" t="s">
+        <v>1004</v>
+      </c>
+      <c r="B479" s="1" t="s">
         <v>1005</v>
       </c>
-      <c r="B479" s="1" t="s">
-        <v>1006</v>
-      </c>
       <c r="C479" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D479" s="1" t="s">
-        <v>983</v>
+        <v>982</v>
       </c>
       <c r="E479" s="1" t="s">
         <v>37</v>
@@ -14448,16 +14445,16 @@
     </row>
     <row r="480" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A480" s="1" t="s">
+        <v>1006</v>
+      </c>
+      <c r="B480" s="1" t="s">
         <v>1007</v>
       </c>
-      <c r="B480" s="1" t="s">
-        <v>1008</v>
-      </c>
       <c r="C480" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D480" s="1" t="s">
-        <v>983</v>
+        <v>982</v>
       </c>
       <c r="E480" s="1" t="s">
         <v>66</v>
@@ -14468,16 +14465,16 @@
     </row>
     <row r="481" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A481" s="1" t="s">
+        <v>1008</v>
+      </c>
+      <c r="B481" s="1" t="s">
         <v>1009</v>
       </c>
-      <c r="B481" s="1" t="s">
-        <v>1010</v>
-      </c>
       <c r="C481" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D481" s="1" t="s">
-        <v>983</v>
+        <v>982</v>
       </c>
       <c r="E481" s="1" t="s">
         <v>98</v>
@@ -14488,16 +14485,16 @@
     </row>
     <row r="482" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A482" s="1" t="s">
+        <v>1010</v>
+      </c>
+      <c r="B482" s="1" t="s">
         <v>1011</v>
       </c>
-      <c r="B482" s="1" t="s">
-        <v>1012</v>
-      </c>
       <c r="C482" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D482" s="1" t="s">
-        <v>983</v>
+        <v>982</v>
       </c>
       <c r="E482" s="1" t="s">
         <v>101</v>
@@ -14508,16 +14505,16 @@
     </row>
     <row r="483" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A483" s="1" t="s">
+        <v>1012</v>
+      </c>
+      <c r="B483" s="1" t="s">
         <v>1013</v>
       </c>
-      <c r="B483" s="1" t="s">
-        <v>1014</v>
-      </c>
       <c r="C483" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D483" s="1" t="s">
-        <v>983</v>
+        <v>982</v>
       </c>
       <c r="E483" s="1" t="s">
         <v>104</v>
@@ -14528,16 +14525,16 @@
     </row>
     <row r="484" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A484" s="1" t="s">
+        <v>1014</v>
+      </c>
+      <c r="B484" s="1" t="s">
         <v>1015</v>
       </c>
-      <c r="B484" s="1" t="s">
+      <c r="C484" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D484" s="1" t="s">
         <v>1016</v>
-      </c>
-      <c r="C484" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D484" s="1" t="s">
-        <v>1017</v>
       </c>
       <c r="E484" s="1" t="s">
         <v>4</v>
@@ -14548,16 +14545,16 @@
     </row>
     <row r="485" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A485" s="1" t="s">
+        <v>1017</v>
+      </c>
+      <c r="B485" s="1" t="s">
         <v>1018</v>
       </c>
-      <c r="B485" s="1" t="s">
-        <v>1019</v>
-      </c>
       <c r="C485" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D485" s="1" t="s">
-        <v>1017</v>
+        <v>1016</v>
       </c>
       <c r="E485" s="1" t="s">
         <v>8</v>
@@ -14568,16 +14565,16 @@
     </row>
     <row r="486" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A486" s="1" t="s">
+        <v>1019</v>
+      </c>
+      <c r="B486" s="1" t="s">
         <v>1020</v>
       </c>
-      <c r="B486" s="1" t="s">
-        <v>1021</v>
-      </c>
       <c r="C486" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D486" s="1" t="s">
-        <v>1017</v>
+        <v>1016</v>
       </c>
       <c r="E486" s="1" t="s">
         <v>12</v>
@@ -14588,16 +14585,16 @@
     </row>
     <row r="487" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A487" s="1" t="s">
+        <v>1021</v>
+      </c>
+      <c r="B487" s="1" t="s">
         <v>1022</v>
       </c>
-      <c r="B487" s="1" t="s">
-        <v>1023</v>
-      </c>
       <c r="C487" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D487" s="1" t="s">
-        <v>1017</v>
+        <v>1016</v>
       </c>
       <c r="E487" s="1" t="s">
         <v>15</v>
@@ -14608,16 +14605,16 @@
     </row>
     <row r="488" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A488" s="1" t="s">
+        <v>1023</v>
+      </c>
+      <c r="B488" s="1" t="s">
         <v>1024</v>
       </c>
-      <c r="B488" s="1" t="s">
-        <v>1025</v>
-      </c>
       <c r="C488" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D488" s="1" t="s">
-        <v>1017</v>
+        <v>1016</v>
       </c>
       <c r="E488" s="1" t="s">
         <v>18</v>
@@ -14628,16 +14625,16 @@
     </row>
     <row r="489" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A489" s="1" t="s">
+        <v>1025</v>
+      </c>
+      <c r="B489" s="1" t="s">
         <v>1026</v>
       </c>
-      <c r="B489" s="1" t="s">
-        <v>1027</v>
-      </c>
       <c r="C489" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D489" s="1" t="s">
-        <v>1017</v>
+        <v>1016</v>
       </c>
       <c r="E489" s="1" t="s">
         <v>21</v>
@@ -14648,16 +14645,16 @@
     </row>
     <row r="490" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A490" s="1" t="s">
+        <v>1027</v>
+      </c>
+      <c r="B490" s="1" t="s">
         <v>1028</v>
       </c>
-      <c r="B490" s="1" t="s">
-        <v>1029</v>
-      </c>
       <c r="C490" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D490" s="1" t="s">
-        <v>1017</v>
+        <v>1016</v>
       </c>
       <c r="E490" s="1" t="s">
         <v>24</v>
@@ -14668,16 +14665,16 @@
     </row>
     <row r="491" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A491" s="1" t="s">
+        <v>1029</v>
+      </c>
+      <c r="B491" s="1" t="s">
         <v>1030</v>
       </c>
-      <c r="B491" s="1" t="s">
-        <v>1031</v>
-      </c>
       <c r="C491" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D491" s="1" t="s">
-        <v>1017</v>
+        <v>1016</v>
       </c>
       <c r="E491" s="1" t="s">
         <v>55</v>
@@ -14688,16 +14685,16 @@
     </row>
     <row r="492" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A492" s="1" t="s">
+        <v>1031</v>
+      </c>
+      <c r="B492" s="1" t="s">
         <v>1032</v>
       </c>
-      <c r="B492" s="1" t="s">
-        <v>1033</v>
-      </c>
       <c r="C492" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D492" s="1" t="s">
-        <v>1017</v>
+        <v>1016</v>
       </c>
       <c r="E492" s="1" t="s">
         <v>28</v>
@@ -14708,36 +14705,36 @@
     </row>
     <row r="493" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A493" s="1" t="s">
+        <v>1033</v>
+      </c>
+      <c r="B493" s="1" t="s">
         <v>1034</v>
       </c>
-      <c r="B493" s="1" t="s">
-        <v>1035</v>
-      </c>
       <c r="C493" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D493" s="1" t="s">
-        <v>1017</v>
+        <v>1016</v>
       </c>
       <c r="E493" s="1" t="s">
         <v>31</v>
       </c>
       <c r="F493" s="1" t="s">
-        <v>1036</v>
+        <v>1035</v>
       </c>
     </row>
     <row r="494" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A494" s="1" t="s">
+        <v>1036</v>
+      </c>
+      <c r="B494" s="1" t="s">
         <v>1037</v>
       </c>
-      <c r="B494" s="1" t="s">
-        <v>1038</v>
-      </c>
       <c r="C494" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D494" s="1" t="s">
-        <v>1017</v>
+        <v>1016</v>
       </c>
       <c r="E494" s="1" t="s">
         <v>34</v>
@@ -14748,16 +14745,16 @@
     </row>
     <row r="495" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A495" s="1" t="s">
+        <v>1038</v>
+      </c>
+      <c r="B495" s="1" t="s">
         <v>1039</v>
       </c>
-      <c r="B495" s="1" t="s">
-        <v>1040</v>
-      </c>
       <c r="C495" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D495" s="1" t="s">
-        <v>1017</v>
+        <v>1016</v>
       </c>
       <c r="E495" s="1" t="s">
         <v>37</v>
@@ -14768,16 +14765,16 @@
     </row>
     <row r="496" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A496" s="1" t="s">
+        <v>1040</v>
+      </c>
+      <c r="B496" s="1" t="s">
         <v>1041</v>
       </c>
-      <c r="B496" s="1" t="s">
-        <v>1042</v>
-      </c>
       <c r="C496" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D496" s="1" t="s">
-        <v>1017</v>
+        <v>1016</v>
       </c>
       <c r="E496" s="1" t="s">
         <v>66</v>
@@ -14788,16 +14785,16 @@
     </row>
     <row r="497" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A497" s="1" t="s">
+        <v>1042</v>
+      </c>
+      <c r="B497" s="1" t="s">
         <v>1043</v>
       </c>
-      <c r="B497" s="1" t="s">
-        <v>1044</v>
-      </c>
       <c r="C497" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D497" s="1" t="s">
-        <v>1017</v>
+        <v>1016</v>
       </c>
       <c r="E497" s="1" t="s">
         <v>98</v>
@@ -14808,16 +14805,16 @@
     </row>
     <row r="498" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A498" s="1" t="s">
+        <v>1044</v>
+      </c>
+      <c r="B498" s="1" t="s">
         <v>1045</v>
       </c>
-      <c r="B498" s="1" t="s">
-        <v>1046</v>
-      </c>
       <c r="C498" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D498" s="1" t="s">
-        <v>1017</v>
+        <v>1016</v>
       </c>
       <c r="E498" s="1" t="s">
         <v>101</v>
@@ -14828,16 +14825,16 @@
     </row>
     <row r="499" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A499" s="1" t="s">
+        <v>1046</v>
+      </c>
+      <c r="B499" s="1" t="s">
         <v>1047</v>
       </c>
-      <c r="B499" s="1" t="s">
-        <v>1048</v>
-      </c>
       <c r="C499" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D499" s="1" t="s">
-        <v>1017</v>
+        <v>1016</v>
       </c>
       <c r="E499" s="1" t="s">
         <v>104</v>
@@ -14848,16 +14845,16 @@
     </row>
     <row r="500" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A500" s="1" t="s">
+        <v>1048</v>
+      </c>
+      <c r="B500" s="1" t="s">
         <v>1049</v>
       </c>
-      <c r="B500" s="1" t="s">
-        <v>1050</v>
-      </c>
       <c r="C500" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D500" s="1" t="s">
-        <v>1017</v>
+        <v>1016</v>
       </c>
       <c r="E500" s="1" t="s">
         <v>107</v>
@@ -14868,16 +14865,16 @@
     </row>
     <row r="501" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A501" s="1" t="s">
+        <v>1050</v>
+      </c>
+      <c r="B501" s="1" t="s">
         <v>1051</v>
       </c>
-      <c r="B501" s="1" t="s">
-        <v>1052</v>
-      </c>
       <c r="C501" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D501" s="1" t="s">
-        <v>1017</v>
+        <v>1016</v>
       </c>
       <c r="E501" s="1" t="s">
         <v>110</v>
@@ -14888,16 +14885,16 @@
     </row>
     <row r="502" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A502" s="1" t="s">
+        <v>1052</v>
+      </c>
+      <c r="B502" s="1" t="s">
         <v>1053</v>
       </c>
-      <c r="B502" s="1" t="s">
+      <c r="C502" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D502" s="1" t="s">
         <v>1054</v>
-      </c>
-      <c r="C502" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D502" s="1" t="s">
-        <v>1055</v>
       </c>
       <c r="E502" s="1" t="s">
         <v>4</v>
@@ -14908,16 +14905,16 @@
     </row>
     <row r="503" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A503" s="1" t="s">
+        <v>1055</v>
+      </c>
+      <c r="B503" s="1" t="s">
         <v>1056</v>
       </c>
-      <c r="B503" s="1" t="s">
-        <v>1057</v>
-      </c>
       <c r="C503" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D503" s="1" t="s">
-        <v>1055</v>
+        <v>1054</v>
       </c>
       <c r="E503" s="1" t="s">
         <v>8</v>
@@ -14928,16 +14925,16 @@
     </row>
     <row r="504" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A504" s="1" t="s">
+        <v>1057</v>
+      </c>
+      <c r="B504" s="1" t="s">
         <v>1058</v>
       </c>
-      <c r="B504" s="1" t="s">
-        <v>1059</v>
-      </c>
       <c r="C504" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D504" s="1" t="s">
-        <v>1055</v>
+        <v>1054</v>
       </c>
       <c r="E504" s="1" t="s">
         <v>12</v>
@@ -14948,16 +14945,16 @@
     </row>
     <row r="505" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A505" s="1" t="s">
+        <v>1059</v>
+      </c>
+      <c r="B505" s="1" t="s">
         <v>1060</v>
       </c>
-      <c r="B505" s="1" t="s">
-        <v>1061</v>
-      </c>
       <c r="C505" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D505" s="1" t="s">
-        <v>1055</v>
+        <v>1054</v>
       </c>
       <c r="E505" s="1" t="s">
         <v>15</v>
@@ -14968,16 +14965,16 @@
     </row>
     <row r="506" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A506" s="1" t="s">
+        <v>1061</v>
+      </c>
+      <c r="B506" s="1" t="s">
         <v>1062</v>
       </c>
-      <c r="B506" s="1" t="s">
-        <v>1063</v>
-      </c>
       <c r="C506" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D506" s="1" t="s">
-        <v>1055</v>
+        <v>1054</v>
       </c>
       <c r="E506" s="1" t="s">
         <v>18</v>
@@ -14988,16 +14985,16 @@
     </row>
     <row r="507" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A507" s="1" t="s">
+        <v>1063</v>
+      </c>
+      <c r="B507" s="1" t="s">
         <v>1064</v>
       </c>
-      <c r="B507" s="1" t="s">
-        <v>1065</v>
-      </c>
       <c r="C507" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D507" s="1" t="s">
-        <v>1055</v>
+        <v>1054</v>
       </c>
       <c r="E507" s="1" t="s">
         <v>21</v>
@@ -15008,16 +15005,16 @@
     </row>
     <row r="508" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A508" s="1" t="s">
+        <v>1065</v>
+      </c>
+      <c r="B508" s="1" t="s">
         <v>1066</v>
       </c>
-      <c r="B508" s="1" t="s">
-        <v>1067</v>
-      </c>
       <c r="C508" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D508" s="1" t="s">
-        <v>1055</v>
+        <v>1054</v>
       </c>
       <c r="E508" s="1" t="s">
         <v>24</v>
@@ -15028,16 +15025,16 @@
     </row>
     <row r="509" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A509" s="1" t="s">
+        <v>1067</v>
+      </c>
+      <c r="B509" s="1" t="s">
         <v>1068</v>
       </c>
-      <c r="B509" s="1" t="s">
-        <v>1069</v>
-      </c>
       <c r="C509" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D509" s="1" t="s">
-        <v>1055</v>
+        <v>1054</v>
       </c>
       <c r="E509" s="1" t="s">
         <v>55</v>
@@ -15048,16 +15045,16 @@
     </row>
     <row r="510" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A510" s="1" t="s">
+        <v>1069</v>
+      </c>
+      <c r="B510" s="1" t="s">
         <v>1070</v>
       </c>
-      <c r="B510" s="1" t="s">
-        <v>1071</v>
-      </c>
       <c r="C510" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D510" s="1" t="s">
-        <v>1055</v>
+        <v>1054</v>
       </c>
       <c r="E510" s="1" t="s">
         <v>28</v>
@@ -15068,16 +15065,16 @@
     </row>
     <row r="511" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A511" s="1" t="s">
+        <v>1071</v>
+      </c>
+      <c r="B511" s="1" t="s">
         <v>1072</v>
       </c>
-      <c r="B511" s="1" t="s">
-        <v>1073</v>
-      </c>
       <c r="C511" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D511" s="1" t="s">
-        <v>1055</v>
+        <v>1054</v>
       </c>
       <c r="E511" s="1" t="s">
         <v>31</v>
@@ -15088,16 +15085,16 @@
     </row>
     <row r="512" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A512" s="1" t="s">
+        <v>1073</v>
+      </c>
+      <c r="B512" s="1" t="s">
         <v>1074</v>
       </c>
-      <c r="B512" s="1" t="s">
-        <v>1075</v>
-      </c>
       <c r="C512" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D512" s="1" t="s">
-        <v>1055</v>
+        <v>1054</v>
       </c>
       <c r="E512" s="1" t="s">
         <v>34</v>
@@ -15108,36 +15105,36 @@
     </row>
     <row r="513" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A513" s="1" t="s">
+        <v>1075</v>
+      </c>
+      <c r="B513" s="1" t="s">
         <v>1076</v>
       </c>
-      <c r="B513" s="1" t="s">
-        <v>1077</v>
-      </c>
       <c r="C513" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D513" s="1" t="s">
-        <v>1055</v>
+        <v>1054</v>
       </c>
       <c r="E513" s="1" t="s">
         <v>37</v>
       </c>
       <c r="F513" s="1" t="s">
-        <v>1078</v>
+        <v>1077</v>
       </c>
     </row>
     <row r="514" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A514" s="1" t="s">
+        <v>1078</v>
+      </c>
+      <c r="B514" s="1" t="s">
         <v>1079</v>
       </c>
-      <c r="B514" s="1" t="s">
-        <v>1080</v>
-      </c>
       <c r="C514" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D514" s="1" t="s">
-        <v>1055</v>
+        <v>1054</v>
       </c>
       <c r="E514" s="1" t="s">
         <v>66</v>
@@ -15148,16 +15145,16 @@
     </row>
     <row r="515" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A515" s="1" t="s">
+        <v>1080</v>
+      </c>
+      <c r="B515" s="1" t="s">
         <v>1081</v>
       </c>
-      <c r="B515" s="1" t="s">
-        <v>1082</v>
-      </c>
       <c r="C515" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D515" s="1" t="s">
-        <v>1055</v>
+        <v>1054</v>
       </c>
       <c r="E515" s="1" t="s">
         <v>98</v>
@@ -15168,16 +15165,16 @@
     </row>
     <row r="516" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A516" s="1" t="s">
+        <v>1082</v>
+      </c>
+      <c r="B516" s="1" t="s">
         <v>1083</v>
       </c>
-      <c r="B516" s="1" t="s">
-        <v>1084</v>
-      </c>
       <c r="C516" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D516" s="1" t="s">
-        <v>1055</v>
+        <v>1054</v>
       </c>
       <c r="E516" s="1" t="s">
         <v>101</v>
@@ -15188,16 +15185,16 @@
     </row>
     <row r="517" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A517" s="1" t="s">
+        <v>1084</v>
+      </c>
+      <c r="B517" s="1" t="s">
         <v>1085</v>
       </c>
-      <c r="B517" s="1" t="s">
+      <c r="C517" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D517" s="1" t="s">
         <v>1086</v>
-      </c>
-      <c r="C517" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D517" s="1" t="s">
-        <v>1087</v>
       </c>
       <c r="E517" s="1" t="s">
         <v>4</v>
@@ -15208,16 +15205,16 @@
     </row>
     <row r="518" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A518" s="1" t="s">
+        <v>1087</v>
+      </c>
+      <c r="B518" s="1" t="s">
         <v>1088</v>
       </c>
-      <c r="B518" s="1" t="s">
-        <v>1089</v>
-      </c>
       <c r="C518" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D518" s="1" t="s">
-        <v>1087</v>
+        <v>1086</v>
       </c>
       <c r="E518" s="1" t="s">
         <v>4</v>
@@ -15228,16 +15225,16 @@
     </row>
     <row r="519" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A519" s="1" t="s">
+        <v>1089</v>
+      </c>
+      <c r="B519" s="1" t="s">
         <v>1090</v>
       </c>
-      <c r="B519" s="1" t="s">
-        <v>1091</v>
-      </c>
       <c r="C519" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D519" s="1" t="s">
-        <v>1087</v>
+        <v>1086</v>
       </c>
       <c r="E519" s="1" t="s">
         <v>4</v>
@@ -15248,16 +15245,16 @@
     </row>
     <row r="520" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A520" s="1" t="s">
+        <v>1091</v>
+      </c>
+      <c r="B520" s="1" t="s">
         <v>1092</v>
       </c>
-      <c r="B520" s="1" t="s">
-        <v>1093</v>
-      </c>
       <c r="C520" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D520" s="1" t="s">
-        <v>1087</v>
+        <v>1086</v>
       </c>
       <c r="E520" s="1" t="s">
         <v>8</v>
@@ -15268,16 +15265,16 @@
     </row>
     <row r="521" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A521" s="1" t="s">
+        <v>1093</v>
+      </c>
+      <c r="B521" s="1" t="s">
         <v>1094</v>
       </c>
-      <c r="B521" s="1" t="s">
-        <v>1095</v>
-      </c>
       <c r="C521" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D521" s="1" t="s">
-        <v>1087</v>
+        <v>1086</v>
       </c>
       <c r="E521" s="1" t="s">
         <v>8</v>
@@ -15288,16 +15285,16 @@
     </row>
     <row r="522" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A522" s="1" t="s">
+        <v>1095</v>
+      </c>
+      <c r="B522" s="1" t="s">
         <v>1096</v>
       </c>
-      <c r="B522" s="1" t="s">
-        <v>1097</v>
-      </c>
       <c r="C522" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D522" s="1" t="s">
-        <v>1087</v>
+        <v>1086</v>
       </c>
       <c r="E522" s="1" t="s">
         <v>8</v>
@@ -15308,16 +15305,16 @@
     </row>
     <row r="523" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A523" s="1" t="s">
+        <v>1097</v>
+      </c>
+      <c r="B523" s="1" t="s">
         <v>1098</v>
       </c>
-      <c r="B523" s="1" t="s">
-        <v>1099</v>
-      </c>
       <c r="C523" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D523" s="1" t="s">
-        <v>1087</v>
+        <v>1086</v>
       </c>
       <c r="E523" s="1" t="s">
         <v>12</v>
@@ -15328,16 +15325,16 @@
     </row>
     <row r="524" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A524" s="1" t="s">
+        <v>1099</v>
+      </c>
+      <c r="B524" s="1" t="s">
         <v>1100</v>
       </c>
-      <c r="B524" s="1" t="s">
-        <v>1101</v>
-      </c>
       <c r="C524" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D524" s="1" t="s">
-        <v>1087</v>
+        <v>1086</v>
       </c>
       <c r="E524" s="1" t="s">
         <v>12</v>
@@ -15348,16 +15345,16 @@
     </row>
     <row r="525" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A525" s="1" t="s">
+        <v>1101</v>
+      </c>
+      <c r="B525" s="1" t="s">
         <v>1102</v>
       </c>
-      <c r="B525" s="1" t="s">
-        <v>1103</v>
-      </c>
       <c r="C525" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D525" s="1" t="s">
-        <v>1087</v>
+        <v>1086</v>
       </c>
       <c r="E525" s="1" t="s">
         <v>12</v>
@@ -15368,16 +15365,16 @@
     </row>
     <row r="526" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A526" s="1" t="s">
+        <v>1103</v>
+      </c>
+      <c r="B526" s="1" t="s">
         <v>1104</v>
       </c>
-      <c r="B526" s="1" t="s">
-        <v>1105</v>
-      </c>
       <c r="C526" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D526" s="1" t="s">
-        <v>1087</v>
+        <v>1086</v>
       </c>
       <c r="E526" s="1" t="s">
         <v>15</v>
@@ -15388,16 +15385,16 @@
     </row>
     <row r="527" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A527" s="1" t="s">
+        <v>1105</v>
+      </c>
+      <c r="B527" s="1" t="s">
         <v>1106</v>
       </c>
-      <c r="B527" s="1" t="s">
-        <v>1107</v>
-      </c>
       <c r="C527" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D527" s="1" t="s">
-        <v>1087</v>
+        <v>1086</v>
       </c>
       <c r="E527" s="1" t="s">
         <v>15</v>
@@ -15408,16 +15405,16 @@
     </row>
     <row r="528" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A528" s="1" t="s">
+        <v>1107</v>
+      </c>
+      <c r="B528" s="1" t="s">
         <v>1108</v>
       </c>
-      <c r="B528" s="1" t="s">
-        <v>1109</v>
-      </c>
       <c r="C528" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D528" s="1" t="s">
-        <v>1087</v>
+        <v>1086</v>
       </c>
       <c r="E528" s="1" t="s">
         <v>15</v>
@@ -15428,16 +15425,16 @@
     </row>
     <row r="529" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A529" s="1" t="s">
+        <v>1109</v>
+      </c>
+      <c r="B529" s="1" t="s">
         <v>1110</v>
       </c>
-      <c r="B529" s="1" t="s">
-        <v>1111</v>
-      </c>
       <c r="C529" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D529" s="1" t="s">
-        <v>1087</v>
+        <v>1086</v>
       </c>
       <c r="E529" s="1" t="s">
         <v>18</v>
@@ -15448,16 +15445,16 @@
     </row>
     <row r="530" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A530" s="1" t="s">
+        <v>1111</v>
+      </c>
+      <c r="B530" s="1" t="s">
         <v>1112</v>
       </c>
-      <c r="B530" s="1" t="s">
-        <v>1113</v>
-      </c>
       <c r="C530" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D530" s="1" t="s">
-        <v>1087</v>
+        <v>1086</v>
       </c>
       <c r="E530" s="1" t="s">
         <v>18</v>
@@ -15468,16 +15465,16 @@
     </row>
     <row r="531" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A531" s="1" t="s">
+        <v>1113</v>
+      </c>
+      <c r="B531" s="1" t="s">
         <v>1114</v>
       </c>
-      <c r="B531" s="1" t="s">
-        <v>1115</v>
-      </c>
       <c r="C531" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D531" s="1" t="s">
-        <v>1087</v>
+        <v>1086</v>
       </c>
       <c r="E531" s="1" t="s">
         <v>18</v>
@@ -15488,16 +15485,16 @@
     </row>
     <row r="532" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A532" s="1" t="s">
+        <v>1115</v>
+      </c>
+      <c r="B532" s="1" t="s">
         <v>1116</v>
       </c>
-      <c r="B532" s="1" t="s">
-        <v>1117</v>
-      </c>
       <c r="C532" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D532" s="1" t="s">
-        <v>1087</v>
+        <v>1086</v>
       </c>
       <c r="E532" s="1" t="s">
         <v>21</v>
@@ -15508,16 +15505,16 @@
     </row>
     <row r="533" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A533" s="1" t="s">
+        <v>1117</v>
+      </c>
+      <c r="B533" s="1" t="s">
         <v>1118</v>
       </c>
-      <c r="B533" s="1" t="s">
-        <v>1119</v>
-      </c>
       <c r="C533" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D533" s="1" t="s">
-        <v>1087</v>
+        <v>1086</v>
       </c>
       <c r="E533" s="1" t="s">
         <v>21</v>
@@ -15528,16 +15525,16 @@
     </row>
     <row r="534" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A534" s="1" t="s">
+        <v>1119</v>
+      </c>
+      <c r="B534" s="1" t="s">
         <v>1120</v>
       </c>
-      <c r="B534" s="1" t="s">
-        <v>1121</v>
-      </c>
       <c r="C534" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D534" s="1" t="s">
-        <v>1087</v>
+        <v>1086</v>
       </c>
       <c r="E534" s="1" t="s">
         <v>21</v>
@@ -15548,16 +15545,16 @@
     </row>
     <row r="535" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A535" s="1" t="s">
+        <v>1121</v>
+      </c>
+      <c r="B535" s="1" t="s">
         <v>1122</v>
       </c>
-      <c r="B535" s="1" t="s">
-        <v>1123</v>
-      </c>
       <c r="C535" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D535" s="1" t="s">
-        <v>1087</v>
+        <v>1086</v>
       </c>
       <c r="E535" s="1" t="s">
         <v>24</v>
@@ -15568,16 +15565,16 @@
     </row>
     <row r="536" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A536" s="1" t="s">
+        <v>1123</v>
+      </c>
+      <c r="B536" s="1" t="s">
         <v>1124</v>
       </c>
-      <c r="B536" s="1" t="s">
-        <v>1125</v>
-      </c>
       <c r="C536" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D536" s="1" t="s">
-        <v>1087</v>
+        <v>1086</v>
       </c>
       <c r="E536" s="1" t="s">
         <v>24</v>
@@ -15588,16 +15585,16 @@
     </row>
     <row r="537" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A537" s="1" t="s">
+        <v>1125</v>
+      </c>
+      <c r="B537" s="1" t="s">
         <v>1126</v>
       </c>
-      <c r="B537" s="1" t="s">
-        <v>1127</v>
-      </c>
       <c r="C537" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D537" s="1" t="s">
-        <v>1087</v>
+        <v>1086</v>
       </c>
       <c r="E537" s="1" t="s">
         <v>55</v>
@@ -15608,16 +15605,16 @@
     </row>
     <row r="538" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A538" s="1" t="s">
+        <v>1127</v>
+      </c>
+      <c r="B538" s="1" t="s">
         <v>1128</v>
       </c>
-      <c r="B538" s="1" t="s">
-        <v>1129</v>
-      </c>
       <c r="C538" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D538" s="1" t="s">
-        <v>1087</v>
+        <v>1086</v>
       </c>
       <c r="E538" s="1" t="s">
         <v>55</v>
@@ -15628,16 +15625,16 @@
     </row>
     <row r="539" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A539" s="1" t="s">
+        <v>1129</v>
+      </c>
+      <c r="B539" s="1" t="s">
         <v>1130</v>
       </c>
-      <c r="B539" s="1" t="s">
-        <v>1131</v>
-      </c>
       <c r="C539" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D539" s="1" t="s">
-        <v>1087</v>
+        <v>1086</v>
       </c>
       <c r="E539" s="1" t="s">
         <v>55</v>
@@ -15648,16 +15645,16 @@
     </row>
     <row r="540" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A540" s="1" t="s">
+        <v>1131</v>
+      </c>
+      <c r="B540" s="1" t="s">
         <v>1132</v>
       </c>
-      <c r="B540" s="1" t="s">
-        <v>1133</v>
-      </c>
       <c r="C540" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D540" s="1" t="s">
-        <v>1087</v>
+        <v>1086</v>
       </c>
       <c r="E540" s="1" t="s">
         <v>28</v>
@@ -15668,16 +15665,16 @@
     </row>
     <row r="541" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A541" s="1" t="s">
+        <v>1133</v>
+      </c>
+      <c r="B541" s="1" t="s">
         <v>1134</v>
       </c>
-      <c r="B541" s="1" t="s">
-        <v>1135</v>
-      </c>
       <c r="C541" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D541" s="1" t="s">
-        <v>1087</v>
+        <v>1086</v>
       </c>
       <c r="E541" s="1" t="s">
         <v>28</v>
@@ -15688,16 +15685,16 @@
     </row>
     <row r="542" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A542" s="1" t="s">
+        <v>1135</v>
+      </c>
+      <c r="B542" s="1" t="s">
         <v>1136</v>
       </c>
-      <c r="B542" s="1" t="s">
-        <v>1137</v>
-      </c>
       <c r="C542" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D542" s="1" t="s">
-        <v>1087</v>
+        <v>1086</v>
       </c>
       <c r="E542" s="1" t="s">
         <v>28</v>
@@ -15708,16 +15705,16 @@
     </row>
     <row r="543" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A543" s="1" t="s">
+        <v>1137</v>
+      </c>
+      <c r="B543" s="1" t="s">
         <v>1138</v>
       </c>
-      <c r="B543" s="1" t="s">
-        <v>1139</v>
-      </c>
       <c r="C543" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D543" s="1" t="s">
-        <v>1087</v>
+        <v>1086</v>
       </c>
       <c r="E543" s="1" t="s">
         <v>31</v>
@@ -15728,16 +15725,16 @@
     </row>
     <row r="544" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A544" s="1" t="s">
+        <v>1139</v>
+      </c>
+      <c r="B544" s="1" t="s">
         <v>1140</v>
       </c>
-      <c r="B544" s="1" t="s">
-        <v>1141</v>
-      </c>
       <c r="C544" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D544" s="1" t="s">
-        <v>1087</v>
+        <v>1086</v>
       </c>
       <c r="E544" s="1" t="s">
         <v>31</v>
@@ -15748,16 +15745,16 @@
     </row>
     <row r="545" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A545" s="1" t="s">
+        <v>1141</v>
+      </c>
+      <c r="B545" s="1" t="s">
         <v>1142</v>
       </c>
-      <c r="B545" s="1" t="s">
-        <v>1143</v>
-      </c>
       <c r="C545" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D545" s="1" t="s">
-        <v>1087</v>
+        <v>1086</v>
       </c>
       <c r="E545" s="1" t="s">
         <v>31</v>
@@ -15768,16 +15765,16 @@
     </row>
     <row r="546" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A546" s="1" t="s">
+        <v>1143</v>
+      </c>
+      <c r="B546" s="1" t="s">
         <v>1144</v>
       </c>
-      <c r="B546" s="1" t="s">
-        <v>1145</v>
-      </c>
       <c r="C546" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D546" s="1" t="s">
-        <v>1087</v>
+        <v>1086</v>
       </c>
       <c r="E546" s="1" t="s">
         <v>34</v>
@@ -15788,16 +15785,16 @@
     </row>
     <row r="547" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A547" s="1" t="s">
+        <v>1145</v>
+      </c>
+      <c r="B547" s="1" t="s">
         <v>1146</v>
       </c>
-      <c r="B547" s="1" t="s">
-        <v>1147</v>
-      </c>
       <c r="C547" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D547" s="1" t="s">
-        <v>1087</v>
+        <v>1086</v>
       </c>
       <c r="E547" s="1" t="s">
         <v>34</v>
@@ -15808,16 +15805,16 @@
     </row>
     <row r="548" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A548" s="1" t="s">
+        <v>1147</v>
+      </c>
+      <c r="B548" s="1" t="s">
         <v>1148</v>
       </c>
-      <c r="B548" s="1" t="s">
-        <v>1149</v>
-      </c>
       <c r="C548" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D548" s="1" t="s">
-        <v>1087</v>
+        <v>1086</v>
       </c>
       <c r="E548" s="1" t="s">
         <v>37</v>
@@ -15828,16 +15825,16 @@
     </row>
     <row r="549" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A549" s="1" t="s">
+        <v>1149</v>
+      </c>
+      <c r="B549" s="1" t="s">
         <v>1150</v>
       </c>
-      <c r="B549" s="1" t="s">
-        <v>1151</v>
-      </c>
       <c r="C549" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D549" s="1" t="s">
-        <v>1087</v>
+        <v>1086</v>
       </c>
       <c r="E549" s="1" t="s">
         <v>37</v>
@@ -15848,16 +15845,16 @@
     </row>
     <row r="550" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A550" s="1" t="s">
+        <v>1151</v>
+      </c>
+      <c r="B550" s="1" t="s">
         <v>1152</v>
       </c>
-      <c r="B550" s="1" t="s">
-        <v>1153</v>
-      </c>
       <c r="C550" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D550" s="1" t="s">
-        <v>1087</v>
+        <v>1086</v>
       </c>
       <c r="E550" s="1" t="s">
         <v>66</v>
@@ -15868,16 +15865,16 @@
     </row>
     <row r="551" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A551" s="1" t="s">
+        <v>1153</v>
+      </c>
+      <c r="B551" s="1" t="s">
         <v>1154</v>
       </c>
-      <c r="B551" s="1" t="s">
-        <v>1155</v>
-      </c>
       <c r="C551" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D551" s="1" t="s">
-        <v>1087</v>
+        <v>1086</v>
       </c>
       <c r="E551" s="1" t="s">
         <v>98</v>
@@ -15888,16 +15885,16 @@
     </row>
     <row r="552" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A552" s="1" t="s">
+        <v>1155</v>
+      </c>
+      <c r="B552" s="1" t="s">
         <v>1156</v>
       </c>
-      <c r="B552" s="1" t="s">
-        <v>1157</v>
-      </c>
       <c r="C552" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D552" s="1" t="s">
-        <v>1087</v>
+        <v>1086</v>
       </c>
       <c r="E552" s="1" t="s">
         <v>101</v>
@@ -15908,16 +15905,16 @@
     </row>
     <row r="553" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A553" s="1" t="s">
+        <v>1157</v>
+      </c>
+      <c r="B553" s="1" t="s">
         <v>1158</v>
       </c>
-      <c r="B553" s="1" t="s">
-        <v>1159</v>
-      </c>
       <c r="C553" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D553" s="1" t="s">
-        <v>1087</v>
+        <v>1086</v>
       </c>
       <c r="E553" s="1" t="s">
         <v>104</v>
@@ -15928,36 +15925,36 @@
     </row>
     <row r="554" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A554" s="1" t="s">
+        <v>1159</v>
+      </c>
+      <c r="B554" s="1" t="s">
         <v>1160</v>
       </c>
-      <c r="B554" s="1" t="s">
+      <c r="C554" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D554" s="1" t="s">
         <v>1161</v>
-      </c>
-      <c r="C554" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D554" s="1" t="s">
-        <v>1162</v>
       </c>
       <c r="E554" s="1" t="s">
         <v>4</v>
       </c>
       <c r="F554" s="1" t="s">
-        <v>1163</v>
+        <v>1162</v>
       </c>
     </row>
     <row r="555" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A555" s="1" t="s">
+        <v>1163</v>
+      </c>
+      <c r="B555" s="1" t="s">
         <v>1164</v>
       </c>
-      <c r="B555" s="1" t="s">
-        <v>1165</v>
-      </c>
       <c r="C555" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D555" s="1" t="s">
-        <v>1162</v>
+        <v>1161</v>
       </c>
       <c r="E555" s="1" t="s">
         <v>8</v>
@@ -15968,16 +15965,16 @@
     </row>
     <row r="556" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A556" s="1" t="s">
+        <v>1165</v>
+      </c>
+      <c r="B556" s="1" t="s">
         <v>1166</v>
       </c>
-      <c r="B556" s="1" t="s">
-        <v>1167</v>
-      </c>
       <c r="C556" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D556" s="1" t="s">
-        <v>1162</v>
+        <v>1161</v>
       </c>
       <c r="E556" s="1" t="s">
         <v>12</v>
@@ -15988,16 +15985,16 @@
     </row>
     <row r="557" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A557" s="1" t="s">
+        <v>1167</v>
+      </c>
+      <c r="B557" s="1" t="s">
         <v>1168</v>
       </c>
-      <c r="B557" s="1" t="s">
-        <v>1169</v>
-      </c>
       <c r="C557" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D557" s="1" t="s">
-        <v>1162</v>
+        <v>1161</v>
       </c>
       <c r="E557" s="1" t="s">
         <v>15</v>
@@ -16008,16 +16005,16 @@
     </row>
     <row r="558" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A558" s="1" t="s">
+        <v>1169</v>
+      </c>
+      <c r="B558" s="1" t="s">
         <v>1170</v>
       </c>
-      <c r="B558" s="1" t="s">
-        <v>1171</v>
-      </c>
       <c r="C558" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D558" s="1" t="s">
-        <v>1162</v>
+        <v>1161</v>
       </c>
       <c r="E558" s="1" t="s">
         <v>18</v>
@@ -16028,16 +16025,16 @@
     </row>
     <row r="559" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A559" s="1" t="s">
+        <v>1171</v>
+      </c>
+      <c r="B559" s="1" t="s">
         <v>1172</v>
       </c>
-      <c r="B559" s="1" t="s">
-        <v>1173</v>
-      </c>
       <c r="C559" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D559" s="1" t="s">
-        <v>1162</v>
+        <v>1161</v>
       </c>
       <c r="E559" s="1" t="s">
         <v>21</v>
@@ -16048,16 +16045,16 @@
     </row>
     <row r="560" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A560" s="1" t="s">
+        <v>1173</v>
+      </c>
+      <c r="B560" s="1" t="s">
         <v>1174</v>
       </c>
-      <c r="B560" s="1" t="s">
-        <v>1175</v>
-      </c>
       <c r="C560" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D560" s="1" t="s">
-        <v>1162</v>
+        <v>1161</v>
       </c>
       <c r="E560" s="1" t="s">
         <v>24</v>
@@ -16068,16 +16065,16 @@
     </row>
     <row r="561" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A561" s="1" t="s">
+        <v>1175</v>
+      </c>
+      <c r="B561" s="1" t="s">
         <v>1176</v>
       </c>
-      <c r="B561" s="1" t="s">
-        <v>1177</v>
-      </c>
       <c r="C561" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D561" s="1" t="s">
-        <v>1162</v>
+        <v>1161</v>
       </c>
       <c r="E561" s="1" t="s">
         <v>55</v>
@@ -16088,16 +16085,16 @@
     </row>
     <row r="562" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A562" s="1" t="s">
+        <v>1177</v>
+      </c>
+      <c r="B562" s="1" t="s">
         <v>1178</v>
       </c>
-      <c r="B562" s="1" t="s">
-        <v>1179</v>
-      </c>
       <c r="C562" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D562" s="1" t="s">
-        <v>1162</v>
+        <v>1161</v>
       </c>
       <c r="E562" s="1" t="s">
         <v>28</v>
@@ -16108,16 +16105,16 @@
     </row>
     <row r="563" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A563" s="1" t="s">
+        <v>1179</v>
+      </c>
+      <c r="B563" s="1" t="s">
         <v>1180</v>
       </c>
-      <c r="B563" s="1" t="s">
-        <v>1181</v>
-      </c>
       <c r="C563" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D563" s="1" t="s">
-        <v>1162</v>
+        <v>1161</v>
       </c>
       <c r="E563" s="1" t="s">
         <v>31</v>
@@ -16128,16 +16125,16 @@
     </row>
     <row r="564" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A564" s="1" t="s">
+        <v>1181</v>
+      </c>
+      <c r="B564" s="1" t="s">
         <v>1182</v>
       </c>
-      <c r="B564" s="1" t="s">
-        <v>1183</v>
-      </c>
       <c r="C564" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D564" s="1" t="s">
-        <v>1162</v>
+        <v>1161</v>
       </c>
       <c r="E564" s="1" t="s">
         <v>34</v>
@@ -16148,16 +16145,16 @@
     </row>
     <row r="565" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A565" s="1" t="s">
+        <v>1183</v>
+      </c>
+      <c r="B565" s="1" t="s">
         <v>1184</v>
       </c>
-      <c r="B565" s="1" t="s">
-        <v>1185</v>
-      </c>
       <c r="C565" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D565" s="1" t="s">
-        <v>1162</v>
+        <v>1161</v>
       </c>
       <c r="E565" s="1" t="s">
         <v>37</v>
@@ -16168,16 +16165,16 @@
     </row>
     <row r="566" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A566" s="1" t="s">
+        <v>1185</v>
+      </c>
+      <c r="B566" s="1" t="s">
         <v>1186</v>
       </c>
-      <c r="B566" s="1" t="s">
-        <v>1187</v>
-      </c>
       <c r="C566" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D566" s="1" t="s">
-        <v>1162</v>
+        <v>1161</v>
       </c>
       <c r="E566" s="1" t="s">
         <v>66</v>
@@ -16188,16 +16185,16 @@
     </row>
     <row r="567" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A567" s="1" t="s">
+        <v>1187</v>
+      </c>
+      <c r="B567" s="1" t="s">
         <v>1188</v>
       </c>
-      <c r="B567" s="1" t="s">
-        <v>1189</v>
-      </c>
       <c r="C567" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D567" s="1" t="s">
-        <v>1162</v>
+        <v>1161</v>
       </c>
       <c r="E567" s="1" t="s">
         <v>98</v>
@@ -16208,16 +16205,16 @@
     </row>
     <row r="568" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A568" s="1" t="s">
+        <v>1189</v>
+      </c>
+      <c r="B568" s="1" t="s">
         <v>1190</v>
       </c>
-      <c r="B568" s="1" t="s">
+      <c r="C568" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D568" s="1" t="s">
         <v>1191</v>
-      </c>
-      <c r="C568" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D568" s="1" t="s">
-        <v>1192</v>
       </c>
       <c r="E568" s="1" t="s">
         <v>4</v>
@@ -16228,16 +16225,16 @@
     </row>
     <row r="569" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A569" s="1" t="s">
+        <v>1192</v>
+      </c>
+      <c r="B569" s="1" t="s">
         <v>1193</v>
       </c>
-      <c r="B569" s="1" t="s">
-        <v>1194</v>
-      </c>
       <c r="C569" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D569" s="1" t="s">
-        <v>1192</v>
+        <v>1191</v>
       </c>
       <c r="E569" s="1" t="s">
         <v>8</v>
@@ -16248,16 +16245,16 @@
     </row>
     <row r="570" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A570" s="1" t="s">
+        <v>1194</v>
+      </c>
+      <c r="B570" s="1" t="s">
         <v>1195</v>
       </c>
-      <c r="B570" s="1" t="s">
-        <v>1196</v>
-      </c>
       <c r="C570" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D570" s="1" t="s">
-        <v>1192</v>
+        <v>1191</v>
       </c>
       <c r="E570" s="1" t="s">
         <v>12</v>
@@ -16268,16 +16265,16 @@
     </row>
     <row r="571" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A571" s="1" t="s">
+        <v>1196</v>
+      </c>
+      <c r="B571" s="1" t="s">
         <v>1197</v>
       </c>
-      <c r="B571" s="1" t="s">
-        <v>1198</v>
-      </c>
       <c r="C571" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D571" s="1" t="s">
-        <v>1192</v>
+        <v>1191</v>
       </c>
       <c r="E571" s="1" t="s">
         <v>15</v>
@@ -16288,16 +16285,16 @@
     </row>
     <row r="572" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A572" s="1" t="s">
+        <v>1198</v>
+      </c>
+      <c r="B572" s="1" t="s">
         <v>1199</v>
       </c>
-      <c r="B572" s="1" t="s">
-        <v>1200</v>
-      </c>
       <c r="C572" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D572" s="1" t="s">
-        <v>1192</v>
+        <v>1191</v>
       </c>
       <c r="E572" s="1" t="s">
         <v>18</v>
@@ -16308,16 +16305,16 @@
     </row>
     <row r="573" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A573" s="1" t="s">
+        <v>1200</v>
+      </c>
+      <c r="B573" s="1" t="s">
         <v>1201</v>
       </c>
-      <c r="B573" s="1" t="s">
-        <v>1202</v>
-      </c>
       <c r="C573" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D573" s="1" t="s">
-        <v>1192</v>
+        <v>1191</v>
       </c>
       <c r="E573" s="1" t="s">
         <v>21</v>
@@ -16328,16 +16325,16 @@
     </row>
     <row r="574" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A574" s="1" t="s">
+        <v>1202</v>
+      </c>
+      <c r="B574" s="1" t="s">
         <v>1203</v>
       </c>
-      <c r="B574" s="1" t="s">
-        <v>1204</v>
-      </c>
       <c r="C574" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D574" s="1" t="s">
-        <v>1192</v>
+        <v>1191</v>
       </c>
       <c r="E574" s="1" t="s">
         <v>24</v>
@@ -16348,16 +16345,16 @@
     </row>
     <row r="575" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A575" s="1" t="s">
+        <v>1204</v>
+      </c>
+      <c r="B575" s="1" t="s">
         <v>1205</v>
       </c>
-      <c r="B575" s="1" t="s">
-        <v>1206</v>
-      </c>
       <c r="C575" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D575" s="1" t="s">
-        <v>1192</v>
+        <v>1191</v>
       </c>
       <c r="E575" s="1" t="s">
         <v>55</v>
@@ -16368,16 +16365,16 @@
     </row>
     <row r="576" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A576" s="1" t="s">
+        <v>1206</v>
+      </c>
+      <c r="B576" s="1" t="s">
         <v>1207</v>
       </c>
-      <c r="B576" s="1" t="s">
-        <v>1208</v>
-      </c>
       <c r="C576" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D576" s="1" t="s">
-        <v>1192</v>
+        <v>1191</v>
       </c>
       <c r="E576" s="1" t="s">
         <v>28</v>
@@ -16388,16 +16385,16 @@
     </row>
     <row r="577" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A577" s="1" t="s">
+        <v>1208</v>
+      </c>
+      <c r="B577" s="1" t="s">
         <v>1209</v>
       </c>
-      <c r="B577" s="1" t="s">
-        <v>1210</v>
-      </c>
       <c r="C577" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D577" s="1" t="s">
-        <v>1192</v>
+        <v>1191</v>
       </c>
       <c r="E577" s="1" t="s">
         <v>31</v>
@@ -16408,16 +16405,16 @@
     </row>
     <row r="578" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A578" s="1" t="s">
+        <v>1210</v>
+      </c>
+      <c r="B578" s="1" t="s">
         <v>1211</v>
       </c>
-      <c r="B578" s="1" t="s">
-        <v>1212</v>
-      </c>
       <c r="C578" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D578" s="1" t="s">
-        <v>1192</v>
+        <v>1191</v>
       </c>
       <c r="E578" s="1" t="s">
         <v>34</v>
@@ -16428,16 +16425,16 @@
     </row>
     <row r="579" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A579" s="1" t="s">
+        <v>1212</v>
+      </c>
+      <c r="B579" s="1" t="s">
         <v>1213</v>
       </c>
-      <c r="B579" s="1" t="s">
-        <v>1214</v>
-      </c>
       <c r="C579" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D579" s="1" t="s">
-        <v>1192</v>
+        <v>1191</v>
       </c>
       <c r="E579" s="1" t="s">
         <v>37</v>
@@ -16448,16 +16445,16 @@
     </row>
     <row r="580" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A580" s="1" t="s">
+        <v>1214</v>
+      </c>
+      <c r="B580" s="1" t="s">
         <v>1215</v>
       </c>
-      <c r="B580" s="1" t="s">
-        <v>1216</v>
-      </c>
       <c r="C580" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D580" s="1" t="s">
-        <v>1192</v>
+        <v>1191</v>
       </c>
       <c r="E580" s="1" t="s">
         <v>66</v>
@@ -16468,16 +16465,16 @@
     </row>
     <row r="581" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A581" s="1" t="s">
+        <v>1216</v>
+      </c>
+      <c r="B581" s="1" t="s">
         <v>1217</v>
       </c>
-      <c r="B581" s="1" t="s">
-        <v>1218</v>
-      </c>
       <c r="C581" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D581" s="1" t="s">
-        <v>1192</v>
+        <v>1191</v>
       </c>
       <c r="E581" s="1" t="s">
         <v>98</v>
@@ -16488,16 +16485,16 @@
     </row>
     <row r="582" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A582" s="1" t="s">
+        <v>1218</v>
+      </c>
+      <c r="B582" s="1" t="s">
         <v>1219</v>
       </c>
-      <c r="B582" s="1" t="s">
+      <c r="C582" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D582" s="1" t="s">
         <v>1220</v>
-      </c>
-      <c r="C582" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D582" s="1" t="s">
-        <v>1221</v>
       </c>
       <c r="E582" s="1" t="s">
         <v>4</v>
@@ -16508,16 +16505,16 @@
     </row>
     <row r="583" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A583" s="1" t="s">
+        <v>1221</v>
+      </c>
+      <c r="B583" s="1" t="s">
         <v>1222</v>
       </c>
-      <c r="B583" s="1" t="s">
-        <v>1223</v>
-      </c>
       <c r="C583" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D583" s="1" t="s">
-        <v>1221</v>
+        <v>1220</v>
       </c>
       <c r="E583" s="1" t="s">
         <v>8</v>
@@ -16528,56 +16525,56 @@
     </row>
     <row r="584" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A584" s="1" t="s">
+        <v>1223</v>
+      </c>
+      <c r="B584" s="1" t="s">
         <v>1224</v>
       </c>
-      <c r="B584" s="1" t="s">
-        <v>1225</v>
-      </c>
       <c r="C584" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D584" s="1" t="s">
-        <v>1221</v>
+        <v>1220</v>
       </c>
       <c r="E584" s="1" t="s">
         <v>12</v>
       </c>
       <c r="F584" s="1" t="s">
-        <v>1078</v>
+        <v>1077</v>
       </c>
     </row>
     <row r="585" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A585" s="1" t="s">
+        <v>1225</v>
+      </c>
+      <c r="B585" s="1" t="s">
         <v>1226</v>
       </c>
-      <c r="B585" s="1" t="s">
-        <v>1227</v>
-      </c>
       <c r="C585" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D585" s="1" t="s">
-        <v>1221</v>
+        <v>1220</v>
       </c>
       <c r="E585" s="1" t="s">
         <v>15</v>
       </c>
       <c r="F585" s="1" t="s">
-        <v>1078</v>
+        <v>1077</v>
       </c>
     </row>
     <row r="586" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A586" s="1" t="s">
+        <v>1227</v>
+      </c>
+      <c r="B586" s="1" t="s">
         <v>1228</v>
       </c>
-      <c r="B586" s="1" t="s">
-        <v>1229</v>
-      </c>
       <c r="C586" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D586" s="1" t="s">
-        <v>1221</v>
+        <v>1220</v>
       </c>
       <c r="E586" s="1" t="s">
         <v>18</v>
@@ -16588,16 +16585,16 @@
     </row>
     <row r="587" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A587" s="1" t="s">
+        <v>1229</v>
+      </c>
+      <c r="B587" s="1" t="s">
         <v>1230</v>
       </c>
-      <c r="B587" s="1" t="s">
-        <v>1231</v>
-      </c>
       <c r="C587" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D587" s="1" t="s">
-        <v>1221</v>
+        <v>1220</v>
       </c>
       <c r="E587" s="1" t="s">
         <v>21</v>
@@ -16608,16 +16605,16 @@
     </row>
     <row r="588" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A588" s="1" t="s">
+        <v>1231</v>
+      </c>
+      <c r="B588" s="1" t="s">
         <v>1232</v>
       </c>
-      <c r="B588" s="1" t="s">
-        <v>1233</v>
-      </c>
       <c r="C588" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D588" s="1" t="s">
-        <v>1221</v>
+        <v>1220</v>
       </c>
       <c r="E588" s="1" t="s">
         <v>24</v>
@@ -16628,16 +16625,16 @@
     </row>
     <row r="589" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A589" s="1" t="s">
+        <v>1233</v>
+      </c>
+      <c r="B589" s="1" t="s">
         <v>1234</v>
       </c>
-      <c r="B589" s="1" t="s">
-        <v>1235</v>
-      </c>
       <c r="C589" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D589" s="1" t="s">
-        <v>1221</v>
+        <v>1220</v>
       </c>
       <c r="E589" s="1" t="s">
         <v>55</v>
@@ -16648,16 +16645,16 @@
     </row>
     <row r="590" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A590" s="1" t="s">
+        <v>1235</v>
+      </c>
+      <c r="B590" s="1" t="s">
         <v>1236</v>
       </c>
-      <c r="B590" s="1" t="s">
-        <v>1237</v>
-      </c>
       <c r="C590" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D590" s="1" t="s">
-        <v>1221</v>
+        <v>1220</v>
       </c>
       <c r="E590" s="1" t="s">
         <v>28</v>
@@ -16668,16 +16665,16 @@
     </row>
     <row r="591" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A591" s="1" t="s">
+        <v>1237</v>
+      </c>
+      <c r="B591" s="1" t="s">
         <v>1238</v>
       </c>
-      <c r="B591" s="1" t="s">
-        <v>1239</v>
-      </c>
       <c r="C591" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D591" s="1" t="s">
-        <v>1221</v>
+        <v>1220</v>
       </c>
       <c r="E591" s="1" t="s">
         <v>31</v>
@@ -16688,16 +16685,16 @@
     </row>
     <row r="592" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A592" s="1" t="s">
+        <v>1239</v>
+      </c>
+      <c r="B592" s="1" t="s">
         <v>1240</v>
       </c>
-      <c r="B592" s="1" t="s">
-        <v>1241</v>
-      </c>
       <c r="C592" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D592" s="1" t="s">
-        <v>1221</v>
+        <v>1220</v>
       </c>
       <c r="E592" s="1" t="s">
         <v>34</v>
@@ -16708,16 +16705,16 @@
     </row>
     <row r="593" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A593" s="1" t="s">
+        <v>1241</v>
+      </c>
+      <c r="B593" s="1" t="s">
         <v>1242</v>
       </c>
-      <c r="B593" s="1" t="s">
-        <v>1243</v>
-      </c>
       <c r="C593" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D593" s="1" t="s">
-        <v>1221</v>
+        <v>1220</v>
       </c>
       <c r="E593" s="1" t="s">
         <v>37</v>
@@ -16728,16 +16725,16 @@
     </row>
     <row r="594" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A594" s="1" t="s">
+        <v>1243</v>
+      </c>
+      <c r="B594" s="1" t="s">
         <v>1244</v>
       </c>
-      <c r="B594" s="1" t="s">
-        <v>1245</v>
-      </c>
       <c r="C594" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D594" s="1" t="s">
-        <v>1221</v>
+        <v>1220</v>
       </c>
       <c r="E594" s="1" t="s">
         <v>66</v>
@@ -16748,16 +16745,16 @@
     </row>
     <row r="595" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A595" s="1" t="s">
+        <v>1245</v>
+      </c>
+      <c r="B595" s="1" t="s">
         <v>1246</v>
       </c>
-      <c r="B595" s="1" t="s">
+      <c r="C595" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D595" s="1" t="s">
         <v>1247</v>
-      </c>
-      <c r="C595" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D595" s="1" t="s">
-        <v>1248</v>
       </c>
       <c r="E595" s="1" t="s">
         <v>4</v>
@@ -16768,16 +16765,16 @@
     </row>
     <row r="596" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A596" s="1" t="s">
+        <v>1248</v>
+      </c>
+      <c r="B596" s="1" t="s">
         <v>1249</v>
       </c>
-      <c r="B596" s="1" t="s">
-        <v>1250</v>
-      </c>
       <c r="C596" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D596" s="1" t="s">
-        <v>1248</v>
+        <v>1247</v>
       </c>
       <c r="E596" s="1" t="s">
         <v>8</v>
@@ -16788,16 +16785,16 @@
     </row>
     <row r="597" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A597" s="1" t="s">
+        <v>1250</v>
+      </c>
+      <c r="B597" s="1" t="s">
         <v>1251</v>
       </c>
-      <c r="B597" s="1" t="s">
-        <v>1252</v>
-      </c>
       <c r="C597" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D597" s="1" t="s">
-        <v>1248</v>
+        <v>1247</v>
       </c>
       <c r="E597" s="1" t="s">
         <v>12</v>
@@ -16808,16 +16805,16 @@
     </row>
     <row r="598" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A598" s="1" t="s">
+        <v>1252</v>
+      </c>
+      <c r="B598" s="1" t="s">
         <v>1253</v>
       </c>
-      <c r="B598" s="1" t="s">
-        <v>1254</v>
-      </c>
       <c r="C598" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D598" s="1" t="s">
-        <v>1248</v>
+        <v>1247</v>
       </c>
       <c r="E598" s="1" t="s">
         <v>15</v>
@@ -16828,16 +16825,16 @@
     </row>
     <row r="599" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A599" s="1" t="s">
+        <v>1254</v>
+      </c>
+      <c r="B599" s="1" t="s">
         <v>1255</v>
       </c>
-      <c r="B599" s="1" t="s">
-        <v>1256</v>
-      </c>
       <c r="C599" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D599" s="1" t="s">
-        <v>1248</v>
+        <v>1247</v>
       </c>
       <c r="E599" s="1" t="s">
         <v>18</v>
@@ -16848,16 +16845,16 @@
     </row>
     <row r="600" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A600" s="1" t="s">
+        <v>1256</v>
+      </c>
+      <c r="B600" s="1" t="s">
         <v>1257</v>
       </c>
-      <c r="B600" s="1" t="s">
-        <v>1258</v>
-      </c>
       <c r="C600" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D600" s="1" t="s">
-        <v>1248</v>
+        <v>1247</v>
       </c>
       <c r="E600" s="1" t="s">
         <v>21</v>
@@ -16868,16 +16865,16 @@
     </row>
     <row r="601" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A601" s="1" t="s">
+        <v>1258</v>
+      </c>
+      <c r="B601" s="1" t="s">
         <v>1259</v>
       </c>
-      <c r="B601" s="1" t="s">
-        <v>1260</v>
-      </c>
       <c r="C601" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D601" s="1" t="s">
-        <v>1248</v>
+        <v>1247</v>
       </c>
       <c r="E601" s="1" t="s">
         <v>24</v>
@@ -16888,16 +16885,16 @@
     </row>
     <row r="602" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A602" s="1" t="s">
+        <v>1260</v>
+      </c>
+      <c r="B602" s="1" t="s">
         <v>1261</v>
       </c>
-      <c r="B602" s="1" t="s">
-        <v>1262</v>
-      </c>
       <c r="C602" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D602" s="1" t="s">
-        <v>1248</v>
+        <v>1247</v>
       </c>
       <c r="E602" s="1" t="s">
         <v>55</v>
@@ -16908,16 +16905,16 @@
     </row>
     <row r="603" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A603" s="1" t="s">
+        <v>1262</v>
+      </c>
+      <c r="B603" s="1" t="s">
         <v>1263</v>
       </c>
-      <c r="B603" s="1" t="s">
-        <v>1264</v>
-      </c>
       <c r="C603" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D603" s="1" t="s">
-        <v>1248</v>
+        <v>1247</v>
       </c>
       <c r="E603" s="1" t="s">
         <v>28</v>
@@ -16928,16 +16925,16 @@
     </row>
     <row r="604" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A604" s="1" t="s">
+        <v>1264</v>
+      </c>
+      <c r="B604" s="1" t="s">
         <v>1265</v>
       </c>
-      <c r="B604" s="1" t="s">
-        <v>1266</v>
-      </c>
       <c r="C604" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D604" s="1" t="s">
-        <v>1248</v>
+        <v>1247</v>
       </c>
       <c r="E604" s="1" t="s">
         <v>31</v>
@@ -16948,16 +16945,16 @@
     </row>
     <row r="605" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A605" s="1" t="s">
+        <v>1266</v>
+      </c>
+      <c r="B605" s="1" t="s">
         <v>1267</v>
       </c>
-      <c r="B605" s="1" t="s">
-        <v>1268</v>
-      </c>
       <c r="C605" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D605" s="1" t="s">
-        <v>1248</v>
+        <v>1247</v>
       </c>
       <c r="E605" s="1" t="s">
         <v>34</v>
@@ -16968,16 +16965,16 @@
     </row>
     <row r="606" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A606" s="1" t="s">
+        <v>1268</v>
+      </c>
+      <c r="B606" s="1" t="s">
         <v>1269</v>
       </c>
-      <c r="B606" s="1" t="s">
-        <v>1270</v>
-      </c>
       <c r="C606" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D606" s="1" t="s">
-        <v>1248</v>
+        <v>1247</v>
       </c>
       <c r="E606" s="1" t="s">
         <v>37</v>
@@ -16988,16 +16985,16 @@
     </row>
     <row r="607" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A607" s="1" t="s">
+        <v>1270</v>
+      </c>
+      <c r="B607" s="1" t="s">
         <v>1271</v>
       </c>
-      <c r="B607" s="1" t="s">
-        <v>1272</v>
-      </c>
       <c r="C607" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D607" s="1" t="s">
-        <v>1248</v>
+        <v>1247</v>
       </c>
       <c r="E607" s="1" t="s">
         <v>66</v>
@@ -17008,16 +17005,16 @@
     </row>
     <row r="608" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A608" s="1" t="s">
+        <v>1272</v>
+      </c>
+      <c r="B608" s="1" t="s">
         <v>1273</v>
       </c>
-      <c r="B608" s="1" t="s">
-        <v>1274</v>
-      </c>
       <c r="C608" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D608" s="1" t="s">
-        <v>1248</v>
+        <v>1247</v>
       </c>
       <c r="E608" s="1" t="s">
         <v>98</v>
@@ -17028,16 +17025,16 @@
     </row>
     <row r="609" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A609" s="1" t="s">
+        <v>1274</v>
+      </c>
+      <c r="B609" s="1" t="s">
         <v>1275</v>
       </c>
-      <c r="B609" s="1" t="s">
-        <v>1276</v>
-      </c>
       <c r="C609" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D609" s="1" t="s">
-        <v>1248</v>
+        <v>1247</v>
       </c>
       <c r="E609" s="1" t="s">
         <v>101</v>
@@ -17048,16 +17045,16 @@
     </row>
     <row r="610" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A610" s="1" t="s">
+        <v>1276</v>
+      </c>
+      <c r="B610" s="1" t="s">
         <v>1277</v>
       </c>
-      <c r="B610" s="1" t="s">
-        <v>1278</v>
-      </c>
       <c r="C610" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D610" s="1" t="s">
-        <v>1248</v>
+        <v>1247</v>
       </c>
       <c r="E610" s="1" t="s">
         <v>104</v>
@@ -17068,16 +17065,16 @@
     </row>
     <row r="611" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A611" s="1" t="s">
+        <v>1278</v>
+      </c>
+      <c r="B611" s="1" t="s">
         <v>1279</v>
       </c>
-      <c r="B611" s="1" t="s">
-        <v>1280</v>
-      </c>
       <c r="C611" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D611" s="1" t="s">
-        <v>1248</v>
+        <v>1247</v>
       </c>
       <c r="E611" s="1" t="s">
         <v>107</v>
@@ -17088,16 +17085,16 @@
     </row>
     <row r="612" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A612" s="1" t="s">
+        <v>1280</v>
+      </c>
+      <c r="B612" s="1" t="s">
         <v>1281</v>
       </c>
-      <c r="B612" s="1" t="s">
+      <c r="C612" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D612" s="1" t="s">
         <v>1282</v>
-      </c>
-      <c r="C612" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D612" s="1" t="s">
-        <v>1283</v>
       </c>
       <c r="E612" s="1" t="s">
         <v>4</v>
@@ -17108,16 +17105,16 @@
     </row>
     <row r="613" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A613" s="1" t="s">
+        <v>1283</v>
+      </c>
+      <c r="B613" s="1" t="s">
         <v>1284</v>
       </c>
-      <c r="B613" s="1" t="s">
-        <v>1285</v>
-      </c>
       <c r="C613" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D613" s="1" t="s">
-        <v>1283</v>
+        <v>1282</v>
       </c>
       <c r="E613" s="1" t="s">
         <v>8</v>
@@ -17128,16 +17125,16 @@
     </row>
     <row r="614" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A614" s="1" t="s">
+        <v>1285</v>
+      </c>
+      <c r="B614" s="1" t="s">
         <v>1286</v>
       </c>
-      <c r="B614" s="1" t="s">
-        <v>1287</v>
-      </c>
       <c r="C614" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D614" s="1" t="s">
-        <v>1283</v>
+        <v>1282</v>
       </c>
       <c r="E614" s="1" t="s">
         <v>12</v>
@@ -17148,16 +17145,16 @@
     </row>
     <row r="615" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A615" s="1" t="s">
+        <v>1287</v>
+      </c>
+      <c r="B615" s="1" t="s">
         <v>1288</v>
       </c>
-      <c r="B615" s="1" t="s">
-        <v>1289</v>
-      </c>
       <c r="C615" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D615" s="1" t="s">
-        <v>1283</v>
+        <v>1282</v>
       </c>
       <c r="E615" s="1" t="s">
         <v>15</v>
@@ -17168,16 +17165,16 @@
     </row>
     <row r="616" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A616" s="1" t="s">
+        <v>1289</v>
+      </c>
+      <c r="B616" s="1" t="s">
         <v>1290</v>
       </c>
-      <c r="B616" s="1" t="s">
-        <v>1291</v>
-      </c>
       <c r="C616" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D616" s="1" t="s">
-        <v>1283</v>
+        <v>1282</v>
       </c>
       <c r="E616" s="1" t="s">
         <v>18</v>
@@ -17188,16 +17185,16 @@
     </row>
     <row r="617" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A617" s="1" t="s">
+        <v>1291</v>
+      </c>
+      <c r="B617" s="1" t="s">
         <v>1292</v>
       </c>
-      <c r="B617" s="1" t="s">
-        <v>1293</v>
-      </c>
       <c r="C617" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D617" s="1" t="s">
-        <v>1283</v>
+        <v>1282</v>
       </c>
       <c r="E617" s="1" t="s">
         <v>21</v>
@@ -17208,16 +17205,16 @@
     </row>
     <row r="618" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A618" s="1" t="s">
+        <v>1293</v>
+      </c>
+      <c r="B618" s="1" t="s">
         <v>1294</v>
       </c>
-      <c r="B618" s="1" t="s">
-        <v>1295</v>
-      </c>
       <c r="C618" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D618" s="1" t="s">
-        <v>1283</v>
+        <v>1282</v>
       </c>
       <c r="E618" s="1" t="s">
         <v>24</v>
@@ -17228,16 +17225,16 @@
     </row>
     <row r="619" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A619" s="1" t="s">
+        <v>1295</v>
+      </c>
+      <c r="B619" s="1" t="s">
         <v>1296</v>
       </c>
-      <c r="B619" s="1" t="s">
-        <v>1297</v>
-      </c>
       <c r="C619" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D619" s="1" t="s">
-        <v>1283</v>
+        <v>1282</v>
       </c>
       <c r="E619" s="1" t="s">
         <v>55</v>
@@ -17248,16 +17245,16 @@
     </row>
     <row r="620" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A620" s="1" t="s">
+        <v>1297</v>
+      </c>
+      <c r="B620" s="1" t="s">
         <v>1298</v>
       </c>
-      <c r="B620" s="1" t="s">
-        <v>1299</v>
-      </c>
       <c r="C620" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D620" s="1" t="s">
-        <v>1283</v>
+        <v>1282</v>
       </c>
       <c r="E620" s="1" t="s">
         <v>28</v>
@@ -17268,16 +17265,16 @@
     </row>
     <row r="621" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A621" s="1" t="s">
+        <v>1299</v>
+      </c>
+      <c r="B621" s="1" t="s">
         <v>1300</v>
       </c>
-      <c r="B621" s="1" t="s">
-        <v>1301</v>
-      </c>
       <c r="C621" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D621" s="1" t="s">
-        <v>1283</v>
+        <v>1282</v>
       </c>
       <c r="E621" s="1" t="s">
         <v>31</v>
@@ -17288,16 +17285,16 @@
     </row>
     <row r="622" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A622" s="1" t="s">
+        <v>1301</v>
+      </c>
+      <c r="B622" s="1" t="s">
         <v>1302</v>
       </c>
-      <c r="B622" s="1" t="s">
-        <v>1303</v>
-      </c>
       <c r="C622" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D622" s="1" t="s">
-        <v>1283</v>
+        <v>1282</v>
       </c>
       <c r="E622" s="1" t="s">
         <v>34</v>
@@ -17308,16 +17305,16 @@
     </row>
     <row r="623" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A623" s="1" t="s">
+        <v>1303</v>
+      </c>
+      <c r="B623" s="1" t="s">
         <v>1304</v>
       </c>
-      <c r="B623" s="1" t="s">
-        <v>1305</v>
-      </c>
       <c r="C623" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D623" s="1" t="s">
-        <v>1283</v>
+        <v>1282</v>
       </c>
       <c r="E623" s="1" t="s">
         <v>37</v>
@@ -17328,16 +17325,16 @@
     </row>
     <row r="624" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A624" s="1" t="s">
+        <v>1305</v>
+      </c>
+      <c r="B624" s="1" t="s">
         <v>1306</v>
       </c>
-      <c r="B624" s="1" t="s">
-        <v>1307</v>
-      </c>
       <c r="C624" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D624" s="1" t="s">
-        <v>1283</v>
+        <v>1282</v>
       </c>
       <c r="E624" s="1" t="s">
         <v>66</v>
@@ -17348,16 +17345,16 @@
     </row>
     <row r="625" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A625" s="1" t="s">
+        <v>1307</v>
+      </c>
+      <c r="B625" s="1" t="s">
         <v>1308</v>
       </c>
-      <c r="B625" s="1" t="s">
-        <v>1309</v>
-      </c>
       <c r="C625" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D625" s="1" t="s">
-        <v>1283</v>
+        <v>1282</v>
       </c>
       <c r="E625" s="1" t="s">
         <v>98</v>
@@ -17368,16 +17365,16 @@
     </row>
     <row r="626" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A626" s="1" t="s">
+        <v>1309</v>
+      </c>
+      <c r="B626" s="1" t="s">
         <v>1310</v>
       </c>
-      <c r="B626" s="1" t="s">
-        <v>1311</v>
-      </c>
       <c r="C626" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D626" s="1" t="s">
-        <v>1283</v>
+        <v>1282</v>
       </c>
       <c r="E626" s="1" t="s">
         <v>101</v>
@@ -17388,16 +17385,16 @@
     </row>
     <row r="627" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A627" s="1" t="s">
+        <v>1311</v>
+      </c>
+      <c r="B627" s="1" t="s">
         <v>1312</v>
       </c>
-      <c r="B627" s="1" t="s">
-        <v>1313</v>
-      </c>
       <c r="C627" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D627" s="1" t="s">
-        <v>1283</v>
+        <v>1282</v>
       </c>
       <c r="E627" s="1" t="s">
         <v>104</v>
@@ -17408,16 +17405,16 @@
     </row>
     <row r="628" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A628" s="1" t="s">
+        <v>1313</v>
+      </c>
+      <c r="B628" s="1" t="s">
         <v>1314</v>
       </c>
-      <c r="B628" s="1" t="s">
-        <v>1315</v>
-      </c>
       <c r="C628" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D628" s="1" t="s">
-        <v>1283</v>
+        <v>1282</v>
       </c>
       <c r="E628" s="1" t="s">
         <v>107</v>
@@ -17428,16 +17425,16 @@
     </row>
     <row r="629" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A629" s="1" t="s">
+        <v>1315</v>
+      </c>
+      <c r="B629" s="1" t="s">
         <v>1316</v>
       </c>
-      <c r="B629" s="1" t="s">
-        <v>1317</v>
-      </c>
       <c r="C629" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D629" s="1" t="s">
-        <v>1283</v>
+        <v>1282</v>
       </c>
       <c r="E629" s="1" t="s">
         <v>110</v>
@@ -17448,16 +17445,16 @@
     </row>
     <row r="630" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A630" s="1" t="s">
+        <v>1317</v>
+      </c>
+      <c r="B630" s="1" t="s">
         <v>1318</v>
       </c>
-      <c r="B630" s="1" t="s">
+      <c r="C630" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D630" s="1" t="s">
         <v>1319</v>
-      </c>
-      <c r="C630" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D630" s="1" t="s">
-        <v>1320</v>
       </c>
       <c r="E630" s="1" t="s">
         <v>4</v>
@@ -17468,16 +17465,16 @@
     </row>
     <row r="631" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A631" s="1" t="s">
+        <v>1320</v>
+      </c>
+      <c r="B631" s="1" t="s">
         <v>1321</v>
       </c>
-      <c r="B631" s="1" t="s">
-        <v>1322</v>
-      </c>
       <c r="C631" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D631" s="1" t="s">
-        <v>1320</v>
+        <v>1319</v>
       </c>
       <c r="E631" s="1" t="s">
         <v>8</v>
@@ -17488,16 +17485,16 @@
     </row>
     <row r="632" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A632" s="1" t="s">
+        <v>1322</v>
+      </c>
+      <c r="B632" s="1" t="s">
         <v>1323</v>
       </c>
-      <c r="B632" s="1" t="s">
-        <v>1324</v>
-      </c>
       <c r="C632" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D632" s="1" t="s">
-        <v>1320</v>
+        <v>1319</v>
       </c>
       <c r="E632" s="1" t="s">
         <v>12</v>
@@ -17508,16 +17505,16 @@
     </row>
     <row r="633" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A633" s="1" t="s">
+        <v>1324</v>
+      </c>
+      <c r="B633" s="1" t="s">
         <v>1325</v>
       </c>
-      <c r="B633" s="1" t="s">
-        <v>1326</v>
-      </c>
       <c r="C633" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D633" s="1" t="s">
-        <v>1320</v>
+        <v>1319</v>
       </c>
       <c r="E633" s="1" t="s">
         <v>15</v>
@@ -17528,16 +17525,16 @@
     </row>
     <row r="634" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A634" s="1" t="s">
-        <v>1327</v>
+        <v>1326</v>
       </c>
       <c r="B634" s="1" t="s">
-        <v>1326</v>
+        <v>1325</v>
       </c>
       <c r="C634" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D634" s="1" t="s">
-        <v>1320</v>
+        <v>1319</v>
       </c>
       <c r="E634" s="1" t="s">
         <v>18</v>
@@ -17548,16 +17545,16 @@
     </row>
     <row r="635" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A635" s="1" t="s">
+        <v>1327</v>
+      </c>
+      <c r="B635" s="1" t="s">
         <v>1328</v>
       </c>
-      <c r="B635" s="1" t="s">
-        <v>1329</v>
-      </c>
       <c r="C635" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D635" s="1" t="s">
-        <v>1320</v>
+        <v>1319</v>
       </c>
       <c r="E635" s="1" t="s">
         <v>21</v>
@@ -17568,16 +17565,16 @@
     </row>
     <row r="636" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A636" s="1" t="s">
+        <v>1329</v>
+      </c>
+      <c r="B636" s="1" t="s">
         <v>1330</v>
       </c>
-      <c r="B636" s="1" t="s">
-        <v>1331</v>
-      </c>
       <c r="C636" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D636" s="1" t="s">
-        <v>1320</v>
+        <v>1319</v>
       </c>
       <c r="E636" s="1" t="s">
         <v>24</v>
@@ -17588,16 +17585,16 @@
     </row>
     <row r="637" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A637" s="1" t="s">
+        <v>1331</v>
+      </c>
+      <c r="B637" s="1" t="s">
         <v>1332</v>
       </c>
-      <c r="B637" s="1" t="s">
-        <v>1333</v>
-      </c>
       <c r="C637" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D637" s="1" t="s">
-        <v>1320</v>
+        <v>1319</v>
       </c>
       <c r="E637" s="1" t="s">
         <v>55</v>
@@ -17608,16 +17605,16 @@
     </row>
     <row r="638" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A638" s="1" t="s">
+        <v>1333</v>
+      </c>
+      <c r="B638" s="1" t="s">
         <v>1334</v>
       </c>
-      <c r="B638" s="1" t="s">
-        <v>1335</v>
-      </c>
       <c r="C638" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D638" s="1" t="s">
-        <v>1320</v>
+        <v>1319</v>
       </c>
       <c r="E638" s="1" t="s">
         <v>28</v>
@@ -17628,16 +17625,16 @@
     </row>
     <row r="639" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A639" s="1" t="s">
+        <v>1335</v>
+      </c>
+      <c r="B639" s="1" t="s">
         <v>1336</v>
       </c>
-      <c r="B639" s="1" t="s">
-        <v>1337</v>
-      </c>
       <c r="C639" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D639" s="1" t="s">
-        <v>1320</v>
+        <v>1319</v>
       </c>
       <c r="E639" s="1" t="s">
         <v>31</v>
@@ -17648,16 +17645,16 @@
     </row>
     <row r="640" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A640" s="1" t="s">
+        <v>1337</v>
+      </c>
+      <c r="B640" s="1" t="s">
         <v>1338</v>
       </c>
-      <c r="B640" s="1" t="s">
-        <v>1339</v>
-      </c>
       <c r="C640" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D640" s="1" t="s">
-        <v>1320</v>
+        <v>1319</v>
       </c>
       <c r="E640" s="1" t="s">
         <v>34</v>
@@ -17668,16 +17665,16 @@
     </row>
     <row r="641" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A641" s="1" t="s">
+        <v>1339</v>
+      </c>
+      <c r="B641" s="1" t="s">
         <v>1340</v>
       </c>
-      <c r="B641" s="1" t="s">
-        <v>1341</v>
-      </c>
       <c r="C641" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D641" s="1" t="s">
-        <v>1320</v>
+        <v>1319</v>
       </c>
       <c r="E641" s="1" t="s">
         <v>37</v>
@@ -17688,16 +17685,16 @@
     </row>
     <row r="642" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A642" s="1" t="s">
+        <v>1341</v>
+      </c>
+      <c r="B642" s="1" t="s">
         <v>1342</v>
       </c>
-      <c r="B642" s="1" t="s">
-        <v>1343</v>
-      </c>
       <c r="C642" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D642" s="1" t="s">
-        <v>1320</v>
+        <v>1319</v>
       </c>
       <c r="E642" s="1" t="s">
         <v>66</v>
@@ -17708,16 +17705,16 @@
     </row>
     <row r="643" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A643" s="1" t="s">
+        <v>1343</v>
+      </c>
+      <c r="B643" s="1" t="s">
         <v>1344</v>
       </c>
-      <c r="B643" s="1" t="s">
-        <v>1345</v>
-      </c>
       <c r="C643" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D643" s="1" t="s">
-        <v>1320</v>
+        <v>1319</v>
       </c>
       <c r="E643" s="1" t="s">
         <v>98</v>
@@ -17728,16 +17725,16 @@
     </row>
     <row r="644" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A644" s="1" t="s">
+        <v>1345</v>
+      </c>
+      <c r="B644" s="1" t="s">
         <v>1346</v>
       </c>
-      <c r="B644" s="1" t="s">
-        <v>1347</v>
-      </c>
       <c r="C644" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D644" s="1" t="s">
-        <v>1320</v>
+        <v>1319</v>
       </c>
       <c r="E644" s="1" t="s">
         <v>101</v>
@@ -17748,16 +17745,16 @@
     </row>
     <row r="645" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A645" s="1" t="s">
+        <v>1347</v>
+      </c>
+      <c r="B645" s="1" t="s">
         <v>1348</v>
       </c>
-      <c r="B645" s="1" t="s">
-        <v>1349</v>
-      </c>
       <c r="C645" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D645" s="1" t="s">
-        <v>1320</v>
+        <v>1319</v>
       </c>
       <c r="E645" s="1" t="s">
         <v>104</v>
@@ -17768,16 +17765,16 @@
     </row>
     <row r="646" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A646" s="1" t="s">
+        <v>1349</v>
+      </c>
+      <c r="B646" s="1" t="s">
         <v>1350</v>
       </c>
-      <c r="B646" s="1" t="s">
-        <v>1351</v>
-      </c>
       <c r="C646" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D646" s="1" t="s">
-        <v>1320</v>
+        <v>1319</v>
       </c>
       <c r="E646" s="1" t="s">
         <v>107</v>
@@ -17788,16 +17785,16 @@
     </row>
     <row r="647" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A647" s="1" t="s">
+        <v>1351</v>
+      </c>
+      <c r="B647" s="1" t="s">
         <v>1352</v>
       </c>
-      <c r="B647" s="1" t="s">
+      <c r="C647" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D647" s="1" t="s">
         <v>1353</v>
-      </c>
-      <c r="C647" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D647" s="1" t="s">
-        <v>1354</v>
       </c>
       <c r="E647" s="1" t="s">
         <v>4</v>
@@ -17808,16 +17805,16 @@
     </row>
     <row r="648" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A648" s="1" t="s">
+        <v>1354</v>
+      </c>
+      <c r="B648" s="1" t="s">
         <v>1355</v>
       </c>
-      <c r="B648" s="1" t="s">
-        <v>1356</v>
-      </c>
       <c r="C648" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D648" s="1" t="s">
-        <v>1354</v>
+        <v>1353</v>
       </c>
       <c r="E648" s="1" t="s">
         <v>8</v>
@@ -17828,16 +17825,16 @@
     </row>
     <row r="649" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A649" s="1" t="s">
+        <v>1356</v>
+      </c>
+      <c r="B649" s="1" t="s">
         <v>1357</v>
       </c>
-      <c r="B649" s="1" t="s">
-        <v>1358</v>
-      </c>
       <c r="C649" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D649" s="1" t="s">
-        <v>1354</v>
+        <v>1353</v>
       </c>
       <c r="E649" s="1" t="s">
         <v>12</v>
@@ -17848,16 +17845,16 @@
     </row>
     <row r="650" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A650" s="1" t="s">
+        <v>1358</v>
+      </c>
+      <c r="B650" s="1" t="s">
         <v>1359</v>
       </c>
-      <c r="B650" s="1" t="s">
-        <v>1360</v>
-      </c>
       <c r="C650" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D650" s="1" t="s">
-        <v>1354</v>
+        <v>1353</v>
       </c>
       <c r="E650" s="1" t="s">
         <v>15</v>
@@ -17868,16 +17865,16 @@
     </row>
     <row r="651" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A651" s="1" t="s">
+        <v>1360</v>
+      </c>
+      <c r="B651" s="1" t="s">
         <v>1361</v>
       </c>
-      <c r="B651" s="1" t="s">
-        <v>1362</v>
-      </c>
       <c r="C651" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D651" s="1" t="s">
-        <v>1354</v>
+        <v>1353</v>
       </c>
       <c r="E651" s="1" t="s">
         <v>18</v>
@@ -17888,16 +17885,16 @@
     </row>
     <row r="652" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A652" s="1" t="s">
+        <v>1362</v>
+      </c>
+      <c r="B652" s="1" t="s">
         <v>1363</v>
       </c>
-      <c r="B652" s="1" t="s">
-        <v>1364</v>
-      </c>
       <c r="C652" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D652" s="1" t="s">
-        <v>1354</v>
+        <v>1353</v>
       </c>
       <c r="E652" s="1" t="s">
         <v>21</v>
@@ -17908,16 +17905,16 @@
     </row>
     <row r="653" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A653" s="1" t="s">
+        <v>1364</v>
+      </c>
+      <c r="B653" s="1" t="s">
         <v>1365</v>
       </c>
-      <c r="B653" s="1" t="s">
-        <v>1366</v>
-      </c>
       <c r="C653" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D653" s="1" t="s">
-        <v>1354</v>
+        <v>1353</v>
       </c>
       <c r="E653" s="1" t="s">
         <v>24</v>
@@ -17928,16 +17925,16 @@
     </row>
     <row r="654" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A654" s="1" t="s">
+        <v>1366</v>
+      </c>
+      <c r="B654" s="1" t="s">
         <v>1367</v>
       </c>
-      <c r="B654" s="1" t="s">
-        <v>1368</v>
-      </c>
       <c r="C654" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D654" s="1" t="s">
-        <v>1354</v>
+        <v>1353</v>
       </c>
       <c r="E654" s="1" t="s">
         <v>55</v>
@@ -17948,16 +17945,16 @@
     </row>
     <row r="655" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A655" s="1" t="s">
+        <v>1368</v>
+      </c>
+      <c r="B655" s="1" t="s">
         <v>1369</v>
       </c>
-      <c r="B655" s="1" t="s">
-        <v>1370</v>
-      </c>
       <c r="C655" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D655" s="1" t="s">
-        <v>1354</v>
+        <v>1353</v>
       </c>
       <c r="E655" s="1" t="s">
         <v>28</v>
@@ -17968,16 +17965,16 @@
     </row>
     <row r="656" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A656" s="1" t="s">
+        <v>1370</v>
+      </c>
+      <c r="B656" s="1" t="s">
         <v>1371</v>
       </c>
-      <c r="B656" s="1" t="s">
-        <v>1372</v>
-      </c>
       <c r="C656" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D656" s="1" t="s">
-        <v>1354</v>
+        <v>1353</v>
       </c>
       <c r="E656" s="1" t="s">
         <v>31</v>
@@ -17988,16 +17985,16 @@
     </row>
     <row r="657" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A657" s="1" t="s">
+        <v>1372</v>
+      </c>
+      <c r="B657" s="1" t="s">
         <v>1373</v>
       </c>
-      <c r="B657" s="1" t="s">
+      <c r="C657" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D657" s="1" t="s">
         <v>1374</v>
-      </c>
-      <c r="C657" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D657" s="1" t="s">
-        <v>1375</v>
       </c>
       <c r="E657" s="1" t="s">
         <v>4</v>
@@ -18008,16 +18005,16 @@
     </row>
     <row r="658" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A658" s="1" t="s">
+        <v>1375</v>
+      </c>
+      <c r="B658" s="1" t="s">
         <v>1376</v>
       </c>
-      <c r="B658" s="1" t="s">
-        <v>1377</v>
-      </c>
       <c r="C658" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D658" s="1" t="s">
-        <v>1375</v>
+        <v>1374</v>
       </c>
       <c r="E658" s="1" t="s">
         <v>8</v>
@@ -18028,16 +18025,16 @@
     </row>
     <row r="659" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A659" s="1" t="s">
+        <v>1377</v>
+      </c>
+      <c r="B659" s="1" t="s">
         <v>1378</v>
       </c>
-      <c r="B659" s="1" t="s">
-        <v>1379</v>
-      </c>
       <c r="C659" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D659" s="1" t="s">
-        <v>1375</v>
+        <v>1374</v>
       </c>
       <c r="E659" s="1" t="s">
         <v>12</v>
@@ -18048,16 +18045,16 @@
     </row>
     <row r="660" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A660" s="1" t="s">
+        <v>1379</v>
+      </c>
+      <c r="B660" s="1" t="s">
         <v>1380</v>
       </c>
-      <c r="B660" s="1" t="s">
-        <v>1381</v>
-      </c>
       <c r="C660" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D660" s="1" t="s">
-        <v>1375</v>
+        <v>1374</v>
       </c>
       <c r="E660" s="1" t="s">
         <v>15</v>
@@ -18068,16 +18065,16 @@
     </row>
     <row r="661" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A661" s="1" t="s">
+        <v>1381</v>
+      </c>
+      <c r="B661" s="1" t="s">
         <v>1382</v>
       </c>
-      <c r="B661" s="1" t="s">
-        <v>1383</v>
-      </c>
       <c r="C661" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D661" s="1" t="s">
-        <v>1375</v>
+        <v>1374</v>
       </c>
       <c r="E661" s="1" t="s">
         <v>18</v>
@@ -18088,16 +18085,16 @@
     </row>
     <row r="662" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A662" s="1" t="s">
+        <v>1383</v>
+      </c>
+      <c r="B662" s="1" t="s">
         <v>1384</v>
       </c>
-      <c r="B662" s="1" t="s">
-        <v>1385</v>
-      </c>
       <c r="C662" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D662" s="1" t="s">
-        <v>1375</v>
+        <v>1374</v>
       </c>
       <c r="E662" s="1" t="s">
         <v>21</v>
@@ -18108,16 +18105,16 @@
     </row>
     <row r="663" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A663" s="1" t="s">
+        <v>1385</v>
+      </c>
+      <c r="B663" s="1" t="s">
         <v>1386</v>
       </c>
-      <c r="B663" s="1" t="s">
-        <v>1387</v>
-      </c>
       <c r="C663" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D663" s="1" t="s">
-        <v>1375</v>
+        <v>1374</v>
       </c>
       <c r="E663" s="1" t="s">
         <v>24</v>
@@ -18128,16 +18125,16 @@
     </row>
     <row r="664" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A664" s="1" t="s">
+        <v>1387</v>
+      </c>
+      <c r="B664" s="1" t="s">
         <v>1388</v>
       </c>
-      <c r="B664" s="1" t="s">
-        <v>1389</v>
-      </c>
       <c r="C664" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D664" s="1" t="s">
-        <v>1375</v>
+        <v>1374</v>
       </c>
       <c r="E664" s="1" t="s">
         <v>55</v>
@@ -18148,16 +18145,16 @@
     </row>
     <row r="665" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A665" s="1" t="s">
+        <v>1389</v>
+      </c>
+      <c r="B665" s="1" t="s">
         <v>1390</v>
       </c>
-      <c r="B665" s="1" t="s">
-        <v>1391</v>
-      </c>
       <c r="C665" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D665" s="1" t="s">
-        <v>1375</v>
+        <v>1374</v>
       </c>
       <c r="E665" s="1" t="s">
         <v>28</v>
@@ -18168,16 +18165,16 @@
     </row>
     <row r="666" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A666" s="1" t="s">
+        <v>1391</v>
+      </c>
+      <c r="B666" s="1" t="s">
         <v>1392</v>
       </c>
-      <c r="B666" s="1" t="s">
-        <v>1393</v>
-      </c>
       <c r="C666" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D666" s="1" t="s">
-        <v>1375</v>
+        <v>1374</v>
       </c>
       <c r="E666" s="1" t="s">
         <v>31</v>
@@ -18188,16 +18185,16 @@
     </row>
     <row r="667" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A667" s="1" t="s">
+        <v>1393</v>
+      </c>
+      <c r="B667" s="1" t="s">
         <v>1394</v>
       </c>
-      <c r="B667" s="1" t="s">
-        <v>1395</v>
-      </c>
       <c r="C667" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D667" s="1" t="s">
-        <v>1375</v>
+        <v>1374</v>
       </c>
       <c r="E667" s="1" t="s">
         <v>34</v>
@@ -18208,16 +18205,16 @@
     </row>
     <row r="668" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A668" s="1" t="s">
+        <v>1395</v>
+      </c>
+      <c r="B668" s="1" t="s">
         <v>1396</v>
       </c>
-      <c r="B668" s="1" t="s">
-        <v>1397</v>
-      </c>
       <c r="C668" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D668" s="1" t="s">
-        <v>1375</v>
+        <v>1374</v>
       </c>
       <c r="E668" s="1" t="s">
         <v>34</v>
@@ -18228,16 +18225,16 @@
     </row>
     <row r="669" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A669" s="1" t="s">
+        <v>1397</v>
+      </c>
+      <c r="B669" s="1" t="s">
         <v>1398</v>
       </c>
-      <c r="B669" s="1" t="s">
-        <v>1399</v>
-      </c>
       <c r="C669" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D669" s="1" t="s">
-        <v>1375</v>
+        <v>1374</v>
       </c>
       <c r="E669" s="1" t="s">
         <v>37</v>
@@ -18248,16 +18245,16 @@
     </row>
     <row r="670" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A670" s="1" t="s">
+        <v>1399</v>
+      </c>
+      <c r="B670" s="1" t="s">
         <v>1400</v>
       </c>
-      <c r="B670" s="1" t="s">
-        <v>1401</v>
-      </c>
       <c r="C670" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D670" s="1" t="s">
-        <v>1375</v>
+        <v>1374</v>
       </c>
       <c r="E670" s="1" t="s">
         <v>37</v>
@@ -18268,16 +18265,16 @@
     </row>
     <row r="671" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A671" s="1" t="s">
+        <v>1401</v>
+      </c>
+      <c r="B671" s="1" t="s">
         <v>1402</v>
       </c>
-      <c r="B671" s="1" t="s">
-        <v>1403</v>
-      </c>
       <c r="C671" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D671" s="1" t="s">
-        <v>1375</v>
+        <v>1374</v>
       </c>
       <c r="E671" s="1" t="s">
         <v>66</v>
@@ -18288,16 +18285,16 @@
     </row>
     <row r="672" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A672" s="1" t="s">
+        <v>1403</v>
+      </c>
+      <c r="B672" s="1" t="s">
         <v>1404</v>
       </c>
-      <c r="B672" s="1" t="s">
+      <c r="C672" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D672" s="1" t="s">
         <v>1405</v>
-      </c>
-      <c r="C672" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D672" s="1" t="s">
-        <v>1406</v>
       </c>
       <c r="E672" s="1" t="s">
         <v>4</v>
@@ -18308,16 +18305,16 @@
     </row>
     <row r="673" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A673" s="1" t="s">
+        <v>1406</v>
+      </c>
+      <c r="B673" s="1" t="s">
         <v>1407</v>
       </c>
-      <c r="B673" s="1" t="s">
-        <v>1408</v>
-      </c>
       <c r="C673" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D673" s="1" t="s">
-        <v>1406</v>
+        <v>1405</v>
       </c>
       <c r="E673" s="1" t="s">
         <v>4</v>
@@ -18328,16 +18325,16 @@
     </row>
     <row r="674" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A674" s="1" t="s">
+        <v>1408</v>
+      </c>
+      <c r="B674" s="1" t="s">
         <v>1409</v>
       </c>
-      <c r="B674" s="1" t="s">
-        <v>1410</v>
-      </c>
       <c r="C674" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D674" s="1" t="s">
-        <v>1406</v>
+        <v>1405</v>
       </c>
       <c r="E674" s="1" t="s">
         <v>8</v>
@@ -18348,16 +18345,16 @@
     </row>
     <row r="675" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A675" s="1" t="s">
+        <v>1410</v>
+      </c>
+      <c r="B675" s="1" t="s">
         <v>1411</v>
       </c>
-      <c r="B675" s="1" t="s">
-        <v>1412</v>
-      </c>
       <c r="C675" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D675" s="1" t="s">
-        <v>1406</v>
+        <v>1405</v>
       </c>
       <c r="E675" s="1" t="s">
         <v>8</v>
@@ -18368,16 +18365,16 @@
     </row>
     <row r="676" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A676" s="1" t="s">
+        <v>1412</v>
+      </c>
+      <c r="B676" s="1" t="s">
         <v>1413</v>
       </c>
-      <c r="B676" s="1" t="s">
-        <v>1414</v>
-      </c>
       <c r="C676" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D676" s="1" t="s">
-        <v>1406</v>
+        <v>1405</v>
       </c>
       <c r="E676" s="1" t="s">
         <v>12</v>
@@ -18388,16 +18385,16 @@
     </row>
     <row r="677" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A677" s="1" t="s">
+        <v>1414</v>
+      </c>
+      <c r="B677" s="1" t="s">
         <v>1415</v>
       </c>
-      <c r="B677" s="1" t="s">
-        <v>1416</v>
-      </c>
       <c r="C677" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D677" s="1" t="s">
-        <v>1406</v>
+        <v>1405</v>
       </c>
       <c r="E677" s="1" t="s">
         <v>12</v>
@@ -18408,16 +18405,16 @@
     </row>
     <row r="678" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A678" s="1" t="s">
+        <v>1416</v>
+      </c>
+      <c r="B678" s="1" t="s">
         <v>1417</v>
       </c>
-      <c r="B678" s="1" t="s">
-        <v>1418</v>
-      </c>
       <c r="C678" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D678" s="1" t="s">
-        <v>1406</v>
+        <v>1405</v>
       </c>
       <c r="E678" s="1" t="s">
         <v>15</v>
@@ -18428,16 +18425,16 @@
     </row>
     <row r="679" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A679" s="1" t="s">
+        <v>1418</v>
+      </c>
+      <c r="B679" s="1" t="s">
         <v>1419</v>
       </c>
-      <c r="B679" s="1" t="s">
-        <v>1420</v>
-      </c>
       <c r="C679" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D679" s="1" t="s">
-        <v>1406</v>
+        <v>1405</v>
       </c>
       <c r="E679" s="1" t="s">
         <v>15</v>
@@ -18448,16 +18445,16 @@
     </row>
     <row r="680" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A680" s="1" t="s">
+        <v>1420</v>
+      </c>
+      <c r="B680" s="1" t="s">
         <v>1421</v>
       </c>
-      <c r="B680" s="1" t="s">
-        <v>1422</v>
-      </c>
       <c r="C680" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D680" s="1" t="s">
-        <v>1406</v>
+        <v>1405</v>
       </c>
       <c r="E680" s="1" t="s">
         <v>18</v>
@@ -18468,16 +18465,16 @@
     </row>
     <row r="681" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A681" s="1" t="s">
+        <v>1422</v>
+      </c>
+      <c r="B681" s="1" t="s">
         <v>1423</v>
       </c>
-      <c r="B681" s="1" t="s">
-        <v>1424</v>
-      </c>
       <c r="C681" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D681" s="1" t="s">
-        <v>1406</v>
+        <v>1405</v>
       </c>
       <c r="E681" s="1" t="s">
         <v>18</v>
@@ -18488,16 +18485,16 @@
     </row>
     <row r="682" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A682" s="1" t="s">
+        <v>1424</v>
+      </c>
+      <c r="B682" s="1" t="s">
         <v>1425</v>
       </c>
-      <c r="B682" s="1" t="s">
-        <v>1426</v>
-      </c>
       <c r="C682" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D682" s="1" t="s">
-        <v>1406</v>
+        <v>1405</v>
       </c>
       <c r="E682" s="1" t="s">
         <v>21</v>
@@ -18508,16 +18505,16 @@
     </row>
     <row r="683" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A683" s="1" t="s">
+        <v>1426</v>
+      </c>
+      <c r="B683" s="1" t="s">
         <v>1427</v>
       </c>
-      <c r="B683" s="1" t="s">
-        <v>1428</v>
-      </c>
       <c r="C683" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D683" s="1" t="s">
-        <v>1406</v>
+        <v>1405</v>
       </c>
       <c r="E683" s="1" t="s">
         <v>21</v>
@@ -18528,16 +18525,16 @@
     </row>
     <row r="684" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A684" s="1" t="s">
+        <v>1428</v>
+      </c>
+      <c r="B684" s="1" t="s">
         <v>1429</v>
       </c>
-      <c r="B684" s="1" t="s">
-        <v>1430</v>
-      </c>
       <c r="C684" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D684" s="1" t="s">
-        <v>1406</v>
+        <v>1405</v>
       </c>
       <c r="E684" s="1" t="s">
         <v>24</v>
@@ -18548,16 +18545,16 @@
     </row>
     <row r="685" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A685" s="1" t="s">
+        <v>1430</v>
+      </c>
+      <c r="B685" s="1" t="s">
         <v>1431</v>
       </c>
-      <c r="B685" s="1" t="s">
-        <v>1432</v>
-      </c>
       <c r="C685" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D685" s="1" t="s">
-        <v>1406</v>
+        <v>1405</v>
       </c>
       <c r="E685" s="1" t="s">
         <v>24</v>
@@ -18568,16 +18565,16 @@
     </row>
     <row r="686" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A686" s="1" t="s">
+        <v>1432</v>
+      </c>
+      <c r="B686" s="1" t="s">
         <v>1433</v>
       </c>
-      <c r="B686" s="1" t="s">
-        <v>1434</v>
-      </c>
       <c r="C686" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D686" s="1" t="s">
-        <v>1406</v>
+        <v>1405</v>
       </c>
       <c r="E686" s="1" t="s">
         <v>55</v>
@@ -18588,16 +18585,16 @@
     </row>
     <row r="687" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A687" s="1" t="s">
+        <v>1434</v>
+      </c>
+      <c r="B687" s="1" t="s">
         <v>1435</v>
       </c>
-      <c r="B687" s="1" t="s">
-        <v>1436</v>
-      </c>
       <c r="C687" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D687" s="1" t="s">
-        <v>1406</v>
+        <v>1405</v>
       </c>
       <c r="E687" s="1" t="s">
         <v>55</v>
@@ -18608,16 +18605,16 @@
     </row>
     <row r="688" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A688" s="1" t="s">
+        <v>1436</v>
+      </c>
+      <c r="B688" s="1" t="s">
         <v>1437</v>
       </c>
-      <c r="B688" s="1" t="s">
-        <v>1438</v>
-      </c>
       <c r="C688" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D688" s="1" t="s">
-        <v>1406</v>
+        <v>1405</v>
       </c>
       <c r="E688" s="1" t="s">
         <v>28</v>
@@ -18628,16 +18625,16 @@
     </row>
     <row r="689" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A689" s="1" t="s">
+        <v>1438</v>
+      </c>
+      <c r="B689" s="1" t="s">
         <v>1439</v>
       </c>
-      <c r="B689" s="1" t="s">
-        <v>1440</v>
-      </c>
       <c r="C689" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D689" s="1" t="s">
-        <v>1406</v>
+        <v>1405</v>
       </c>
       <c r="E689" s="1" t="s">
         <v>28</v>
@@ -18648,16 +18645,16 @@
     </row>
     <row r="690" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A690" s="1" t="s">
+        <v>1440</v>
+      </c>
+      <c r="B690" s="1" t="s">
         <v>1441</v>
       </c>
-      <c r="B690" s="1" t="s">
-        <v>1442</v>
-      </c>
       <c r="C690" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D690" s="1" t="s">
-        <v>1406</v>
+        <v>1405</v>
       </c>
       <c r="E690" s="1" t="s">
         <v>31</v>
@@ -18668,16 +18665,16 @@
     </row>
     <row r="691" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A691" s="1" t="s">
+        <v>1442</v>
+      </c>
+      <c r="B691" s="1" t="s">
         <v>1443</v>
       </c>
-      <c r="B691" s="1" t="s">
-        <v>1444</v>
-      </c>
       <c r="C691" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D691" s="1" t="s">
-        <v>1406</v>
+        <v>1405</v>
       </c>
       <c r="E691" s="1" t="s">
         <v>31</v>
@@ -18688,16 +18685,16 @@
     </row>
     <row r="692" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A692" s="1" t="s">
+        <v>1444</v>
+      </c>
+      <c r="B692" s="1" t="s">
         <v>1445</v>
       </c>
-      <c r="B692" s="1" t="s">
-        <v>1446</v>
-      </c>
       <c r="C692" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D692" s="1" t="s">
-        <v>1406</v>
+        <v>1405</v>
       </c>
       <c r="E692" s="1" t="s">
         <v>34</v>
@@ -18708,16 +18705,16 @@
     </row>
     <row r="693" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A693" s="1" t="s">
+        <v>1446</v>
+      </c>
+      <c r="B693" s="1" t="s">
         <v>1447</v>
       </c>
-      <c r="B693" s="1" t="s">
-        <v>1448</v>
-      </c>
       <c r="C693" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D693" s="1" t="s">
-        <v>1406</v>
+        <v>1405</v>
       </c>
       <c r="E693" s="1" t="s">
         <v>34</v>
@@ -18728,16 +18725,16 @@
     </row>
     <row r="694" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A694" s="1" t="s">
+        <v>1448</v>
+      </c>
+      <c r="B694" s="1" t="s">
         <v>1449</v>
       </c>
-      <c r="B694" s="1" t="s">
-        <v>1450</v>
-      </c>
       <c r="C694" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D694" s="1" t="s">
-        <v>1406</v>
+        <v>1405</v>
       </c>
       <c r="E694" s="1" t="s">
         <v>37</v>
@@ -18748,16 +18745,16 @@
     </row>
     <row r="695" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A695" s="1" t="s">
+        <v>1450</v>
+      </c>
+      <c r="B695" s="1" t="s">
         <v>1451</v>
       </c>
-      <c r="B695" s="1" t="s">
-        <v>1452</v>
-      </c>
       <c r="C695" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D695" s="1" t="s">
-        <v>1406</v>
+        <v>1405</v>
       </c>
       <c r="E695" s="1" t="s">
         <v>37</v>
@@ -18768,16 +18765,16 @@
     </row>
     <row r="696" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A696" s="1" t="s">
+        <v>1452</v>
+      </c>
+      <c r="B696" s="1" t="s">
         <v>1453</v>
       </c>
-      <c r="B696" s="1" t="s">
-        <v>1454</v>
-      </c>
       <c r="C696" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D696" s="1" t="s">
-        <v>1406</v>
+        <v>1405</v>
       </c>
       <c r="E696" s="1" t="s">
         <v>66</v>
@@ -18788,16 +18785,16 @@
     </row>
     <row r="697" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A697" s="1" t="s">
+        <v>1454</v>
+      </c>
+      <c r="B697" s="1" t="s">
         <v>1455</v>
       </c>
-      <c r="B697" s="1" t="s">
-        <v>1456</v>
-      </c>
       <c r="C697" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D697" s="1" t="s">
-        <v>1406</v>
+        <v>1405</v>
       </c>
       <c r="E697" s="1" t="s">
         <v>66</v>
@@ -18808,16 +18805,16 @@
     </row>
     <row r="698" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A698" s="1" t="s">
+        <v>1456</v>
+      </c>
+      <c r="B698" s="1" t="s">
         <v>1457</v>
       </c>
-      <c r="B698" s="1" t="s">
-        <v>1458</v>
-      </c>
       <c r="C698" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D698" s="1" t="s">
-        <v>1406</v>
+        <v>1405</v>
       </c>
       <c r="E698" s="1" t="s">
         <v>98</v>
@@ -18828,16 +18825,16 @@
     </row>
     <row r="699" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A699" s="1" t="s">
+        <v>1458</v>
+      </c>
+      <c r="B699" s="1" t="s">
         <v>1459</v>
       </c>
-      <c r="B699" s="1" t="s">
-        <v>1460</v>
-      </c>
       <c r="C699" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D699" s="1" t="s">
-        <v>1406</v>
+        <v>1405</v>
       </c>
       <c r="E699" s="1" t="s">
         <v>101</v>
@@ -18848,16 +18845,16 @@
     </row>
     <row r="700" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A700" s="1" t="s">
+        <v>1460</v>
+      </c>
+      <c r="B700" s="1" t="s">
         <v>1461</v>
       </c>
-      <c r="B700" s="1" t="s">
+      <c r="C700" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D700" s="1" t="s">
         <v>1462</v>
-      </c>
-      <c r="C700" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D700" s="1" t="s">
-        <v>1463</v>
       </c>
       <c r="E700" s="1" t="s">
         <v>15</v>
@@ -18868,16 +18865,16 @@
     </row>
     <row r="701" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A701" s="1" t="s">
+        <v>1463</v>
+      </c>
+      <c r="B701" s="1" t="s">
         <v>1464</v>
       </c>
-      <c r="B701" s="1" t="s">
-        <v>1465</v>
-      </c>
       <c r="C701" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D701" s="1" t="s">
-        <v>1463</v>
+        <v>1462</v>
       </c>
       <c r="E701" s="1" t="s">
         <v>18</v>
@@ -18888,16 +18885,16 @@
     </row>
     <row r="702" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A702" s="1" t="s">
+        <v>1465</v>
+      </c>
+      <c r="B702" s="1" t="s">
         <v>1466</v>
       </c>
-      <c r="B702" s="1" t="s">
-        <v>1467</v>
-      </c>
       <c r="C702" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D702" s="1" t="s">
-        <v>1463</v>
+        <v>1462</v>
       </c>
       <c r="E702" s="1" t="s">
         <v>21</v>
@@ -18908,16 +18905,16 @@
     </row>
     <row r="703" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A703" s="1" t="s">
+        <v>1467</v>
+      </c>
+      <c r="B703" s="1" t="s">
         <v>1468</v>
       </c>
-      <c r="B703" s="1" t="s">
-        <v>1469</v>
-      </c>
       <c r="C703" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D703" s="1" t="s">
-        <v>1463</v>
+        <v>1462</v>
       </c>
       <c r="E703" s="1" t="s">
         <v>24</v>
@@ -18928,16 +18925,16 @@
     </row>
     <row r="704" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A704" s="1" t="s">
+        <v>1469</v>
+      </c>
+      <c r="B704" s="1" t="s">
         <v>1470</v>
       </c>
-      <c r="B704" s="1" t="s">
-        <v>1471</v>
-      </c>
       <c r="C704" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D704" s="1" t="s">
-        <v>1463</v>
+        <v>1462</v>
       </c>
       <c r="E704" s="1" t="s">
         <v>55</v>
@@ -18948,16 +18945,16 @@
     </row>
     <row r="705" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A705" s="1" t="s">
+        <v>1471</v>
+      </c>
+      <c r="B705" s="1" t="s">
         <v>1472</v>
       </c>
-      <c r="B705" s="1" t="s">
-        <v>1473</v>
-      </c>
       <c r="C705" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D705" s="1" t="s">
-        <v>1463</v>
+        <v>1462</v>
       </c>
       <c r="E705" s="1" t="s">
         <v>28</v>
@@ -18968,16 +18965,16 @@
     </row>
     <row r="706" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A706" s="1" t="s">
+        <v>1473</v>
+      </c>
+      <c r="B706" s="1" t="s">
         <v>1474</v>
       </c>
-      <c r="B706" s="1" t="s">
-        <v>1475</v>
-      </c>
       <c r="C706" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D706" s="1" t="s">
-        <v>1463</v>
+        <v>1462</v>
       </c>
       <c r="E706" s="1" t="s">
         <v>31</v>
@@ -18988,16 +18985,16 @@
     </row>
     <row r="707" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A707" s="1" t="s">
+        <v>1475</v>
+      </c>
+      <c r="B707" s="1" t="s">
         <v>1476</v>
       </c>
-      <c r="B707" s="1" t="s">
-        <v>1477</v>
-      </c>
       <c r="C707" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D707" s="1" t="s">
-        <v>1463</v>
+        <v>1462</v>
       </c>
       <c r="E707" s="1" t="s">
         <v>34</v>
@@ -19008,16 +19005,16 @@
     </row>
     <row r="708" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A708" s="1" t="s">
+        <v>1477</v>
+      </c>
+      <c r="B708" s="1" t="s">
         <v>1478</v>
       </c>
-      <c r="B708" s="1" t="s">
-        <v>1479</v>
-      </c>
       <c r="C708" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D708" s="1" t="s">
-        <v>1463</v>
+        <v>1462</v>
       </c>
       <c r="E708" s="1" t="s">
         <v>37</v>
@@ -19028,16 +19025,16 @@
     </row>
     <row r="709" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A709" s="1" t="s">
+        <v>1479</v>
+      </c>
+      <c r="B709" s="1" t="s">
         <v>1480</v>
       </c>
-      <c r="B709" s="1" t="s">
-        <v>1481</v>
-      </c>
       <c r="C709" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D709" s="1" t="s">
-        <v>1463</v>
+        <v>1462</v>
       </c>
       <c r="E709" s="1" t="s">
         <v>66</v>
@@ -19048,16 +19045,16 @@
     </row>
     <row r="710" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A710" s="1" t="s">
+        <v>1481</v>
+      </c>
+      <c r="B710" s="1" t="s">
         <v>1482</v>
       </c>
-      <c r="B710" s="1" t="s">
-        <v>1483</v>
-      </c>
       <c r="C710" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D710" s="1" t="s">
-        <v>1463</v>
+        <v>1462</v>
       </c>
       <c r="E710" s="1" t="s">
         <v>98</v>

--- a/PCE06D.xlsx
+++ b/PCE06D.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4260" uniqueCount="1483">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4248" uniqueCount="1479">
   <si>
     <t/>
   </si>
@@ -97,114 +97,114 @@
     <t>LFBUOY SBN T10 4X110</t>
   </si>
   <si>
+    <t>8</t>
+  </si>
+  <si>
+    <t>20059867</t>
+  </si>
+  <si>
+    <t>LFBUOY SBN M/C 4X110</t>
+  </si>
+  <si>
     <t>9</t>
   </si>
   <si>
-    <t>20059867</t>
-  </si>
-  <si>
-    <t>LFBUOY SBN M/C 4X110</t>
+    <t>20074434</t>
+  </si>
+  <si>
+    <t>LFBUOY SBN LMN.FR 4S</t>
   </si>
   <si>
     <t>10</t>
   </si>
   <si>
-    <t>20074434</t>
-  </si>
-  <si>
-    <t>LFBUOY SBN LMN.FR 4S</t>
+    <t>20138026</t>
+  </si>
+  <si>
+    <t>NUVO FRESH.PR 4X100G</t>
   </si>
   <si>
     <t>11</t>
   </si>
   <si>
-    <t>20138026</t>
-  </si>
-  <si>
-    <t>NUVO FRESH.PR 4X100G</t>
+    <t>RT,(E-1B)</t>
+  </si>
+  <si>
+    <t>20021822</t>
+  </si>
+  <si>
+    <t>DREAM PAPAYA SOAP100</t>
+  </si>
+  <si>
+    <t>20070713</t>
+  </si>
+  <si>
+    <t>SHINZUI MATSU 3X100G</t>
+  </si>
+  <si>
+    <t>20068183</t>
+  </si>
+  <si>
+    <t>SHINZUI KIREI 3X100G</t>
+  </si>
+  <si>
+    <t>20034716</t>
+  </si>
+  <si>
+    <t>SHINZU'I SBN KNSH 80</t>
+  </si>
+  <si>
+    <t>10016079</t>
+  </si>
+  <si>
+    <t>SHINZU'I SB.MANDI 80</t>
+  </si>
+  <si>
+    <t>10025484</t>
+  </si>
+  <si>
+    <t>SHINZU'I SBN KREI 80</t>
+  </si>
+  <si>
+    <t>20093185</t>
+  </si>
+  <si>
+    <t>GIV SBN RED.RS 3X100</t>
+  </si>
+  <si>
+    <t>20093183</t>
+  </si>
+  <si>
+    <t>GIV SBN WH.BGK 3X100</t>
+  </si>
+  <si>
+    <t>20085121</t>
+  </si>
+  <si>
+    <t>LUX SOFT TOUCH 3X110</t>
+  </si>
+  <si>
+    <t>20085122</t>
+  </si>
+  <si>
+    <t>LUX VELVET TCH 3X110</t>
+  </si>
+  <si>
+    <t>20140680</t>
+  </si>
+  <si>
+    <t>ZEN BAR JPN RED 4S</t>
+  </si>
+  <si>
+    <t>20113303</t>
+  </si>
+  <si>
+    <t>ZEN BAR SOAP S&amp;S 4'S</t>
   </si>
   <si>
     <t>12</t>
   </si>
   <si>
-    <t>RT,(E-1B)</t>
-  </si>
-  <si>
-    <t>20021822</t>
-  </si>
-  <si>
-    <t>DREAM PAPAYA SOAP100</t>
-  </si>
-  <si>
-    <t>20070713</t>
-  </si>
-  <si>
-    <t>SHINZUI MATSU 3X100G</t>
-  </si>
-  <si>
-    <t>20068183</t>
-  </si>
-  <si>
-    <t>SHINZUI KIREI 3X100G</t>
-  </si>
-  <si>
-    <t>20034716</t>
-  </si>
-  <si>
-    <t>SHINZU'I SBN KNSH 80</t>
-  </si>
-  <si>
-    <t>10016079</t>
-  </si>
-  <si>
-    <t>SHINZU'I SB.MANDI 80</t>
-  </si>
-  <si>
-    <t>10025484</t>
-  </si>
-  <si>
-    <t>SHINZU'I SBN KREI 80</t>
-  </si>
-  <si>
-    <t>20093185</t>
-  </si>
-  <si>
-    <t>GIV SBN RED.RS 3X100</t>
-  </si>
-  <si>
-    <t>20093183</t>
-  </si>
-  <si>
-    <t>GIV SBN WH.BGK 3X100</t>
-  </si>
-  <si>
-    <t>8</t>
-  </si>
-  <si>
-    <t>20085121</t>
-  </si>
-  <si>
-    <t>LUX SOFT TOUCH 3X110</t>
-  </si>
-  <si>
-    <t>20085122</t>
-  </si>
-  <si>
-    <t>LUX VELVET TCH 3X110</t>
-  </si>
-  <si>
-    <t>20140680</t>
-  </si>
-  <si>
-    <t>ZEN BAR JPN RED 4S</t>
-  </si>
-  <si>
-    <t>20113303</t>
-  </si>
-  <si>
-    <t>ZEN BAR SOAP S&amp;S 4'S</t>
-  </si>
-  <si>
     <t>20093639</t>
   </si>
   <si>
@@ -376,7 +376,7 @@
     <t>20041266</t>
   </si>
   <si>
-    <t>PEPSODENT ACT COM190</t>
+    <t>PSODENT A/COM 190 G</t>
   </si>
   <si>
     <t>10004714</t>
@@ -394,13 +394,13 @@
     <t>20092076</t>
   </si>
   <si>
-    <t>PSODENT PG CHARC 160</t>
+    <t>PSODENT CHARC 160 G</t>
   </si>
   <si>
     <t>10025411</t>
   </si>
   <si>
-    <t>PEPSODENT ACT+WHT190</t>
+    <t>PSODENT A/WHT 190 G</t>
   </si>
   <si>
     <t>20136643</t>
@@ -565,13 +565,13 @@
     <t>10003569</t>
   </si>
   <si>
-    <t>CLOSE UP GRN E.FR160</t>
+    <t>CLOSE UP GRN F 160 G</t>
   </si>
   <si>
     <t>10037208</t>
   </si>
   <si>
-    <t>CLOSE UP MT.FRSH 100</t>
+    <t>CLOSE UP MT.FH 100 G</t>
   </si>
   <si>
     <t>20002944</t>
@@ -889,13 +889,13 @@
     <t>20138903</t>
   </si>
   <si>
-    <t>SNSLK SHP G.BLCK 320</t>
+    <t>SNSLK S G.BLC 320 ML</t>
   </si>
   <si>
     <t>20138902</t>
   </si>
   <si>
-    <t>SNSLK SHP S.SMTH 320</t>
+    <t>SNSLK S S.STH 320 ML</t>
   </si>
   <si>
     <t>10003336</t>
@@ -955,19 +955,19 @@
     <t>20030118</t>
   </si>
   <si>
-    <t>REJOICE SHP 3IN1 150</t>
+    <t>RJC 3IN1 A/KTMBE 135</t>
   </si>
   <si>
     <t>20033003</t>
   </si>
   <si>
-    <t>REJOICE CND RICH 150</t>
+    <t>RJC CND RCH SMOTH130</t>
   </si>
   <si>
     <t>10019725</t>
   </si>
   <si>
-    <t>REJOICE SHP RICH 150</t>
+    <t>RJC 3IN1 RCH SMOT135</t>
   </si>
   <si>
     <t>20140224</t>
@@ -1009,31 +1009,31 @@
     <t>20038766</t>
   </si>
   <si>
-    <t>PANTENE SHP HFC 145</t>
+    <t>PNTENE SHP HF 160 ML</t>
   </si>
   <si>
     <t>20038758</t>
   </si>
   <si>
-    <t>PANTENE CND HFC 160</t>
+    <t>PNTENE CON HF 160 ML</t>
   </si>
   <si>
     <t>20038763</t>
   </si>
   <si>
-    <t>PNTENE SHP ANT/D 145</t>
+    <t>PNTENE SHP AD 160 ML</t>
   </si>
   <si>
     <t>20038770</t>
   </si>
   <si>
-    <t>PNTENE SHP SM.CR 145</t>
+    <t>PNTENE SM.CR 160 ML</t>
   </si>
   <si>
     <t>20038986</t>
   </si>
   <si>
-    <t>PNTENE SHP LG BLK145</t>
+    <t>PNTENE SP BLK 160 ML</t>
   </si>
   <si>
     <t>20134589</t>
@@ -1111,13 +1111,13 @@
     <t>10011850</t>
   </si>
   <si>
-    <t>H&amp;S SHP MNT DNGN 145</t>
+    <t>H&amp;S SHP MNT D 160 ML</t>
   </si>
   <si>
     <t>20049799</t>
   </si>
   <si>
-    <t>H&amp;S SHP LMON FRS 145</t>
+    <t>H&amp;S S LMN FRS 160 ML</t>
   </si>
   <si>
     <t>20138023</t>
@@ -1129,13 +1129,13 @@
     <t>20118299</t>
   </si>
   <si>
-    <t>H&amp;S SHP SPRM A.HF135</t>
+    <t>H&amp;S S S A.HF 135 ML</t>
   </si>
   <si>
     <t>10011851</t>
   </si>
   <si>
-    <t>H&amp;S A/D SMTH&amp;SLK 145</t>
+    <t>H&amp;S SMTH&amp;SLK 160 ML</t>
   </si>
   <si>
     <t>20103818</t>
@@ -1555,19 +1555,25 @@
     <t>20046176</t>
   </si>
   <si>
-    <t>BIORE BF ENRG.CL 400</t>
+    <t>BIORE BF E.CL 400 ML</t>
   </si>
   <si>
     <t>20031215</t>
   </si>
   <si>
-    <t>BIORE BF LIVELY 400</t>
+    <t>BIORE BF LVLY 400 ML</t>
   </si>
   <si>
     <t>10013361</t>
   </si>
   <si>
-    <t>BIORE BF A.BACTR 400</t>
+    <t>BIORE BF BACT 400 ML</t>
+  </si>
+  <si>
+    <t>20128894</t>
+  </si>
+  <si>
+    <t>BIORE BF B.LL 400 ML</t>
   </si>
   <si>
     <t>20120877</t>
@@ -1759,7 +1765,7 @@
     <t>20130824</t>
   </si>
   <si>
-    <t>BIORE BF FLOR SPA400</t>
+    <t>BIORE BF F.SP 400 ML</t>
   </si>
   <si>
     <t>20143390</t>
@@ -1801,25 +1807,31 @@
     <t>20009500</t>
   </si>
   <si>
-    <t>BIORE B.FOAM RELX400</t>
+    <t>BIORE BF RELX 400 ML</t>
   </si>
   <si>
     <t>20080927</t>
   </si>
   <si>
-    <t>BIORE BF CHRY SK 400</t>
+    <t>BIORE BF CHRY 400 ML</t>
   </si>
   <si>
     <t>20009499</t>
   </si>
   <si>
-    <t>BIORE BF WHT/S RF380</t>
+    <t>BIORE BF W/S R380 ML</t>
   </si>
   <si>
     <t>10013360</t>
   </si>
   <si>
-    <t>BIORE BF RF P/MLD400</t>
+    <t>BIORE BF P.MD 400 ML</t>
+  </si>
+  <si>
+    <t>20143841</t>
+  </si>
+  <si>
+    <t>IDM HW PUMP J/TEA500</t>
   </si>
   <si>
     <t>20004027</t>
@@ -1864,12 +1876,6 @@
     <t>LERVIA SBN JOJOBA400</t>
   </si>
   <si>
-    <t>20128894</t>
-  </si>
-  <si>
-    <t>BIORE BF BRGHT.LL400</t>
-  </si>
-  <si>
     <t>10037140</t>
   </si>
   <si>
@@ -2065,18 +2071,6 @@
     <t>POND VIT M.WTR BR100</t>
   </si>
   <si>
-    <t>20138989</t>
-  </si>
-  <si>
-    <t>VIVA MC.WTR BR&amp;G 100</t>
-  </si>
-  <si>
-    <t>20138988</t>
-  </si>
-  <si>
-    <t>VIVA MIC WTR SENS100</t>
-  </si>
-  <si>
     <t>20093906</t>
   </si>
   <si>
@@ -3322,12 +3316,6 @@
     <t>HNSUI WH.GOLD SRM 20</t>
   </si>
   <si>
-    <t>20094772</t>
-  </si>
-  <si>
-    <t>EMINA BS MOIS.CRM 20</t>
-  </si>
-  <si>
     <t>20107792</t>
   </si>
   <si>
@@ -3388,6 +3376,12 @@
     <t>VIVA E/BRW D.BRWN1.3</t>
   </si>
   <si>
+    <t>20138591</t>
+  </si>
+  <si>
+    <t>HNSUI RTNL MOIST 30G</t>
+  </si>
+  <si>
     <t>10019513</t>
   </si>
   <si>
@@ -3400,10 +3394,16 @@
     <t>GLW&amp;LOVELY GLW.CRM23</t>
   </si>
   <si>
-    <t>20138591</t>
-  </si>
-  <si>
-    <t>HNSUI RTNL MOIST 30G</t>
+    <t>20138590</t>
+  </si>
+  <si>
+    <t>HNSUI BRGH/E MOIS 30</t>
+  </si>
+  <si>
+    <t>10003931</t>
+  </si>
+  <si>
+    <t>MARCKS BEDAK CRM 40G</t>
   </si>
   <si>
     <t>20086026</t>
@@ -3418,36 +3418,24 @@
     <t>PONDS SS HYDRATE 15G</t>
   </si>
   <si>
-    <t>20138590</t>
-  </si>
-  <si>
-    <t>HNSUI BRGH/E MOIS 30</t>
-  </si>
-  <si>
-    <t>10003931</t>
-  </si>
-  <si>
-    <t>MARCKS BEDAK CRM 40G</t>
-  </si>
-  <si>
     <t>20038957</t>
   </si>
   <si>
     <t>GLW&amp;LOVELY DRM.CRM46</t>
   </si>
   <si>
+    <t>20104076</t>
+  </si>
+  <si>
+    <t>EMINA BS LS.PWDR 55</t>
+  </si>
+  <si>
     <t>20137589</t>
   </si>
   <si>
     <t>PONDS SS BRIGHT 15G</t>
   </si>
   <si>
-    <t>20104076</t>
-  </si>
-  <si>
-    <t>EMINA BS LS.PWDR 55</t>
-  </si>
-  <si>
     <t>20138102</t>
   </si>
   <si>
@@ -3733,7 +3721,7 @@
     <t>20125158</t>
   </si>
   <si>
-    <t>ROMANO EDT GRND100</t>
+    <t>ROMANO EDP GRND100</t>
   </si>
   <si>
     <t>20134769</t>
@@ -4852,7 +4840,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F710"/>
+  <dimension ref="A1:F708"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
@@ -5257,7 +5245,7 @@
         <v>8</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>55</v>
+        <v>28</v>
       </c>
       <c r="F20" s="1" t="s">
         <v>5</v>
@@ -5265,10 +5253,10 @@
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="B21" s="1" t="s">
         <v>56</v>
-      </c>
-      <c r="B21" s="1" t="s">
-        <v>57</v>
       </c>
       <c r="C21" s="1" t="s">
         <v>3</v>
@@ -5277,7 +5265,7 @@
         <v>8</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="F21" s="1" t="s">
         <v>25</v>
@@ -5285,10 +5273,10 @@
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="B22" s="1" t="s">
         <v>58</v>
-      </c>
-      <c r="B22" s="1" t="s">
-        <v>59</v>
       </c>
       <c r="C22" s="1" t="s">
         <v>3</v>
@@ -5297,7 +5285,7 @@
         <v>8</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="F22" s="1" t="s">
         <v>25</v>
@@ -5305,10 +5293,10 @@
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="B23" s="1" t="s">
         <v>60</v>
-      </c>
-      <c r="B23" s="1" t="s">
-        <v>61</v>
       </c>
       <c r="C23" s="1" t="s">
         <v>3</v>
@@ -5317,7 +5305,7 @@
         <v>8</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="F23" s="1" t="s">
         <v>5</v>
@@ -5325,10 +5313,10 @@
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="B24" s="1" t="s">
         <v>62</v>
-      </c>
-      <c r="B24" s="1" t="s">
-        <v>63</v>
       </c>
       <c r="C24" s="1" t="s">
         <v>3</v>
@@ -5337,7 +5325,7 @@
         <v>8</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>37</v>
+        <v>63</v>
       </c>
       <c r="F24" s="1" t="s">
         <v>9</v>
@@ -5517,7 +5505,7 @@
         <v>12</v>
       </c>
       <c r="E33" s="1" t="s">
-        <v>55</v>
+        <v>28</v>
       </c>
       <c r="F33" s="1" t="s">
         <v>25</v>
@@ -5537,7 +5525,7 @@
         <v>12</v>
       </c>
       <c r="E34" s="1" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="F34" s="1" t="s">
         <v>5</v>
@@ -5557,7 +5545,7 @@
         <v>12</v>
       </c>
       <c r="E35" s="1" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="F35" s="1" t="s">
         <v>89</v>
@@ -5577,7 +5565,7 @@
         <v>12</v>
       </c>
       <c r="E36" s="1" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="F36" s="1" t="s">
         <v>9</v>
@@ -5597,7 +5585,7 @@
         <v>12</v>
       </c>
       <c r="E37" s="1" t="s">
-        <v>37</v>
+        <v>63</v>
       </c>
       <c r="F37" s="1" t="s">
         <v>5</v>
@@ -5877,7 +5865,7 @@
         <v>15</v>
       </c>
       <c r="E51" s="1" t="s">
-        <v>55</v>
+        <v>28</v>
       </c>
       <c r="F51" s="1" t="s">
         <v>25</v>
@@ -5897,7 +5885,7 @@
         <v>15</v>
       </c>
       <c r="E52" s="1" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="F52" s="1" t="s">
         <v>71</v>
@@ -5917,7 +5905,7 @@
         <v>15</v>
       </c>
       <c r="E53" s="1" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="F53" s="1" t="s">
         <v>25</v>
@@ -5937,7 +5925,7 @@
         <v>15</v>
       </c>
       <c r="E54" s="1" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="F54" s="1" t="s">
         <v>71</v>
@@ -5957,7 +5945,7 @@
         <v>15</v>
       </c>
       <c r="E55" s="1" t="s">
-        <v>37</v>
+        <v>63</v>
       </c>
       <c r="F55" s="1" t="s">
         <v>25</v>
@@ -6277,7 +6265,7 @@
         <v>18</v>
       </c>
       <c r="E71" s="1" t="s">
-        <v>55</v>
+        <v>28</v>
       </c>
       <c r="F71" s="1" t="s">
         <v>5</v>
@@ -6297,7 +6285,7 @@
         <v>18</v>
       </c>
       <c r="E72" s="1" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="F72" s="1" t="s">
         <v>5</v>
@@ -6317,7 +6305,7 @@
         <v>18</v>
       </c>
       <c r="E73" s="1" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="F73" s="1" t="s">
         <v>5</v>
@@ -6337,7 +6325,7 @@
         <v>18</v>
       </c>
       <c r="E74" s="1" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="F74" s="1" t="s">
         <v>5</v>
@@ -6357,7 +6345,7 @@
         <v>18</v>
       </c>
       <c r="E75" s="1" t="s">
-        <v>37</v>
+        <v>63</v>
       </c>
       <c r="F75" s="1" t="s">
         <v>154</v>
@@ -6697,7 +6685,7 @@
         <v>21</v>
       </c>
       <c r="E92" s="1" t="s">
-        <v>55</v>
+        <v>28</v>
       </c>
       <c r="F92" s="1" t="s">
         <v>25</v>
@@ -6717,7 +6705,7 @@
         <v>21</v>
       </c>
       <c r="E93" s="1" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="F93" s="1" t="s">
         <v>25</v>
@@ -6737,7 +6725,7 @@
         <v>21</v>
       </c>
       <c r="E94" s="1" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="F94" s="1" t="s">
         <v>154</v>
@@ -6757,7 +6745,7 @@
         <v>21</v>
       </c>
       <c r="E95" s="1" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="F95" s="1" t="s">
         <v>154</v>
@@ -6777,7 +6765,7 @@
         <v>21</v>
       </c>
       <c r="E96" s="1" t="s">
-        <v>37</v>
+        <v>63</v>
       </c>
       <c r="F96" s="1" t="s">
         <v>154</v>
@@ -6937,7 +6925,7 @@
         <v>24</v>
       </c>
       <c r="E104" s="1" t="s">
-        <v>55</v>
+        <v>28</v>
       </c>
       <c r="F104" s="1" t="s">
         <v>78</v>
@@ -6957,7 +6945,7 @@
         <v>24</v>
       </c>
       <c r="E105" s="1" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="F105" s="1" t="s">
         <v>5</v>
@@ -6977,7 +6965,7 @@
         <v>24</v>
       </c>
       <c r="E106" s="1" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="F106" s="1" t="s">
         <v>78</v>
@@ -6997,7 +6985,7 @@
         <v>24</v>
       </c>
       <c r="E107" s="1" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="F107" s="1" t="s">
         <v>38</v>
@@ -7017,7 +7005,7 @@
         <v>24</v>
       </c>
       <c r="E108" s="1" t="s">
-        <v>37</v>
+        <v>63</v>
       </c>
       <c r="F108" s="1" t="s">
         <v>5</v>
@@ -7034,7 +7022,7 @@
         <v>3</v>
       </c>
       <c r="D109" s="1" t="s">
-        <v>55</v>
+        <v>28</v>
       </c>
       <c r="E109" s="1" t="s">
         <v>4</v>
@@ -7054,7 +7042,7 @@
         <v>3</v>
       </c>
       <c r="D110" s="1" t="s">
-        <v>55</v>
+        <v>28</v>
       </c>
       <c r="E110" s="1" t="s">
         <v>8</v>
@@ -7074,7 +7062,7 @@
         <v>3</v>
       </c>
       <c r="D111" s="1" t="s">
-        <v>55</v>
+        <v>28</v>
       </c>
       <c r="E111" s="1" t="s">
         <v>12</v>
@@ -7094,7 +7082,7 @@
         <v>3</v>
       </c>
       <c r="D112" s="1" t="s">
-        <v>55</v>
+        <v>28</v>
       </c>
       <c r="E112" s="1" t="s">
         <v>15</v>
@@ -7114,7 +7102,7 @@
         <v>3</v>
       </c>
       <c r="D113" s="1" t="s">
-        <v>55</v>
+        <v>28</v>
       </c>
       <c r="E113" s="1" t="s">
         <v>18</v>
@@ -7134,7 +7122,7 @@
         <v>3</v>
       </c>
       <c r="D114" s="1" t="s">
-        <v>55</v>
+        <v>28</v>
       </c>
       <c r="E114" s="1" t="s">
         <v>21</v>
@@ -7154,7 +7142,7 @@
         <v>3</v>
       </c>
       <c r="D115" s="1" t="s">
-        <v>55</v>
+        <v>28</v>
       </c>
       <c r="E115" s="1" t="s">
         <v>24</v>
@@ -7174,10 +7162,10 @@
         <v>3</v>
       </c>
       <c r="D116" s="1" t="s">
-        <v>55</v>
+        <v>28</v>
       </c>
       <c r="E116" s="1" t="s">
-        <v>55</v>
+        <v>28</v>
       </c>
       <c r="F116" s="1" t="s">
         <v>78</v>
@@ -7194,10 +7182,10 @@
         <v>3</v>
       </c>
       <c r="D117" s="1" t="s">
-        <v>55</v>
+        <v>28</v>
       </c>
       <c r="E117" s="1" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="F117" s="1" t="s">
         <v>78</v>
@@ -7214,10 +7202,10 @@
         <v>3</v>
       </c>
       <c r="D118" s="1" t="s">
-        <v>55</v>
+        <v>28</v>
       </c>
       <c r="E118" s="1" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="F118" s="1" t="s">
         <v>154</v>
@@ -7234,10 +7222,10 @@
         <v>3</v>
       </c>
       <c r="D119" s="1" t="s">
-        <v>55</v>
+        <v>28</v>
       </c>
       <c r="E119" s="1" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="F119" s="1" t="s">
         <v>269</v>
@@ -7254,10 +7242,10 @@
         <v>3</v>
       </c>
       <c r="D120" s="1" t="s">
-        <v>55</v>
+        <v>28</v>
       </c>
       <c r="E120" s="1" t="s">
-        <v>37</v>
+        <v>63</v>
       </c>
       <c r="F120" s="1" t="s">
         <v>154</v>
@@ -7274,7 +7262,7 @@
         <v>3</v>
       </c>
       <c r="D121" s="1" t="s">
-        <v>55</v>
+        <v>28</v>
       </c>
       <c r="E121" s="1" t="s">
         <v>66</v>
@@ -7294,7 +7282,7 @@
         <v>3</v>
       </c>
       <c r="D122" s="1" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="E122" s="1" t="s">
         <v>4</v>
@@ -7314,7 +7302,7 @@
         <v>3</v>
       </c>
       <c r="D123" s="1" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="E123" s="1" t="s">
         <v>8</v>
@@ -7334,7 +7322,7 @@
         <v>3</v>
       </c>
       <c r="D124" s="1" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="E124" s="1" t="s">
         <v>12</v>
@@ -7354,7 +7342,7 @@
         <v>3</v>
       </c>
       <c r="D125" s="1" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="E125" s="1" t="s">
         <v>15</v>
@@ -7374,7 +7362,7 @@
         <v>3</v>
       </c>
       <c r="D126" s="1" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="E126" s="1" t="s">
         <v>18</v>
@@ -7394,7 +7382,7 @@
         <v>3</v>
       </c>
       <c r="D127" s="1" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="E127" s="1" t="s">
         <v>21</v>
@@ -7414,7 +7402,7 @@
         <v>3</v>
       </c>
       <c r="D128" s="1" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="E128" s="1" t="s">
         <v>24</v>
@@ -7434,10 +7422,10 @@
         <v>3</v>
       </c>
       <c r="D129" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="E129" s="1" t="s">
         <v>28</v>
-      </c>
-      <c r="E129" s="1" t="s">
-        <v>55</v>
       </c>
       <c r="F129" s="1" t="s">
         <v>71</v>
@@ -7454,10 +7442,10 @@
         <v>3</v>
       </c>
       <c r="D130" s="1" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="E130" s="1" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="F130" s="1" t="s">
         <v>25</v>
@@ -7474,10 +7462,10 @@
         <v>3</v>
       </c>
       <c r="D131" s="1" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="E131" s="1" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="F131" s="1" t="s">
         <v>25</v>
@@ -7494,10 +7482,10 @@
         <v>3</v>
       </c>
       <c r="D132" s="1" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="E132" s="1" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="F132" s="1" t="s">
         <v>38</v>
@@ -7514,10 +7502,10 @@
         <v>3</v>
       </c>
       <c r="D133" s="1" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="E133" s="1" t="s">
-        <v>37</v>
+        <v>63</v>
       </c>
       <c r="F133" s="1" t="s">
         <v>38</v>
@@ -7534,7 +7522,7 @@
         <v>3</v>
       </c>
       <c r="D134" s="1" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="E134" s="1" t="s">
         <v>66</v>
@@ -7554,7 +7542,7 @@
         <v>3</v>
       </c>
       <c r="D135" s="1" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="E135" s="1" t="s">
         <v>4</v>
@@ -7574,7 +7562,7 @@
         <v>3</v>
       </c>
       <c r="D136" s="1" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="E136" s="1" t="s">
         <v>8</v>
@@ -7594,7 +7582,7 @@
         <v>3</v>
       </c>
       <c r="D137" s="1" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="E137" s="1" t="s">
         <v>12</v>
@@ -7614,7 +7602,7 @@
         <v>3</v>
       </c>
       <c r="D138" s="1" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="E138" s="1" t="s">
         <v>15</v>
@@ -7634,7 +7622,7 @@
         <v>3</v>
       </c>
       <c r="D139" s="1" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="E139" s="1" t="s">
         <v>18</v>
@@ -7654,7 +7642,7 @@
         <v>3</v>
       </c>
       <c r="D140" s="1" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="E140" s="1" t="s">
         <v>21</v>
@@ -7674,7 +7662,7 @@
         <v>3</v>
       </c>
       <c r="D141" s="1" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="E141" s="1" t="s">
         <v>24</v>
@@ -7694,10 +7682,10 @@
         <v>3</v>
       </c>
       <c r="D142" s="1" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="E142" s="1" t="s">
-        <v>55</v>
+        <v>28</v>
       </c>
       <c r="F142" s="1" t="s">
         <v>276</v>
@@ -7714,10 +7702,10 @@
         <v>3</v>
       </c>
       <c r="D143" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="E143" s="1" t="s">
         <v>31</v>
-      </c>
-      <c r="E143" s="1" t="s">
-        <v>28</v>
       </c>
       <c r="F143" s="1" t="s">
         <v>276</v>
@@ -7734,10 +7722,10 @@
         <v>3</v>
       </c>
       <c r="D144" s="1" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="E144" s="1" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="F144" s="1" t="s">
         <v>5</v>
@@ -7754,10 +7742,10 @@
         <v>3</v>
       </c>
       <c r="D145" s="1" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="E145" s="1" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="F145" s="1" t="s">
         <v>5</v>
@@ -7774,10 +7762,10 @@
         <v>3</v>
       </c>
       <c r="D146" s="1" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="E146" s="1" t="s">
-        <v>37</v>
+        <v>63</v>
       </c>
       <c r="F146" s="1" t="s">
         <v>5</v>
@@ -7794,7 +7782,7 @@
         <v>3</v>
       </c>
       <c r="D147" s="1" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="E147" s="1" t="s">
         <v>66</v>
@@ -7814,7 +7802,7 @@
         <v>3</v>
       </c>
       <c r="D148" s="1" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="E148" s="1" t="s">
         <v>98</v>
@@ -7834,7 +7822,7 @@
         <v>3</v>
       </c>
       <c r="D149" s="1" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="E149" s="1" t="s">
         <v>101</v>
@@ -7854,7 +7842,7 @@
         <v>3</v>
       </c>
       <c r="D150" s="1" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="E150" s="1" t="s">
         <v>4</v>
@@ -7874,7 +7862,7 @@
         <v>3</v>
       </c>
       <c r="D151" s="1" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="E151" s="1" t="s">
         <v>8</v>
@@ -7894,7 +7882,7 @@
         <v>3</v>
       </c>
       <c r="D152" s="1" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="E152" s="1" t="s">
         <v>12</v>
@@ -7914,7 +7902,7 @@
         <v>3</v>
       </c>
       <c r="D153" s="1" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="E153" s="1" t="s">
         <v>15</v>
@@ -7934,7 +7922,7 @@
         <v>3</v>
       </c>
       <c r="D154" s="1" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="E154" s="1" t="s">
         <v>18</v>
@@ -7954,7 +7942,7 @@
         <v>3</v>
       </c>
       <c r="D155" s="1" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="E155" s="1" t="s">
         <v>21</v>
@@ -7974,7 +7962,7 @@
         <v>3</v>
       </c>
       <c r="D156" s="1" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="E156" s="1" t="s">
         <v>24</v>
@@ -7994,10 +7982,10 @@
         <v>3</v>
       </c>
       <c r="D157" s="1" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="E157" s="1" t="s">
-        <v>55</v>
+        <v>28</v>
       </c>
       <c r="F157" s="1" t="s">
         <v>5</v>
@@ -8014,10 +8002,10 @@
         <v>3</v>
       </c>
       <c r="D158" s="1" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="E158" s="1" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="F158" s="1" t="s">
         <v>5</v>
@@ -8034,10 +8022,10 @@
         <v>3</v>
       </c>
       <c r="D159" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="E159" s="1" t="s">
         <v>34</v>
-      </c>
-      <c r="E159" s="1" t="s">
-        <v>31</v>
       </c>
       <c r="F159" s="1" t="s">
         <v>5</v>
@@ -8054,10 +8042,10 @@
         <v>3</v>
       </c>
       <c r="D160" s="1" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="E160" s="1" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="F160" s="1" t="s">
         <v>5</v>
@@ -8074,10 +8062,10 @@
         <v>3</v>
       </c>
       <c r="D161" s="1" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="E161" s="1" t="s">
-        <v>37</v>
+        <v>63</v>
       </c>
       <c r="F161" s="1" t="s">
         <v>38</v>
@@ -8094,7 +8082,7 @@
         <v>3</v>
       </c>
       <c r="D162" s="1" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="E162" s="1" t="s">
         <v>66</v>
@@ -8114,7 +8102,7 @@
         <v>3</v>
       </c>
       <c r="D163" s="1" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="E163" s="1" t="s">
         <v>98</v>
@@ -8134,7 +8122,7 @@
         <v>3</v>
       </c>
       <c r="D164" s="1" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="E164" s="1" t="s">
         <v>101</v>
@@ -8154,7 +8142,7 @@
         <v>3</v>
       </c>
       <c r="D165" s="1" t="s">
-        <v>37</v>
+        <v>63</v>
       </c>
       <c r="E165" s="1" t="s">
         <v>4</v>
@@ -8174,7 +8162,7 @@
         <v>3</v>
       </c>
       <c r="D166" s="1" t="s">
-        <v>37</v>
+        <v>63</v>
       </c>
       <c r="E166" s="1" t="s">
         <v>8</v>
@@ -8194,7 +8182,7 @@
         <v>3</v>
       </c>
       <c r="D167" s="1" t="s">
-        <v>37</v>
+        <v>63</v>
       </c>
       <c r="E167" s="1" t="s">
         <v>12</v>
@@ -8214,7 +8202,7 @@
         <v>3</v>
       </c>
       <c r="D168" s="1" t="s">
-        <v>37</v>
+        <v>63</v>
       </c>
       <c r="E168" s="1" t="s">
         <v>15</v>
@@ -8234,7 +8222,7 @@
         <v>3</v>
       </c>
       <c r="D169" s="1" t="s">
-        <v>37</v>
+        <v>63</v>
       </c>
       <c r="E169" s="1" t="s">
         <v>18</v>
@@ -8254,7 +8242,7 @@
         <v>3</v>
       </c>
       <c r="D170" s="1" t="s">
-        <v>37</v>
+        <v>63</v>
       </c>
       <c r="E170" s="1" t="s">
         <v>21</v>
@@ -8274,7 +8262,7 @@
         <v>3</v>
       </c>
       <c r="D171" s="1" t="s">
-        <v>37</v>
+        <v>63</v>
       </c>
       <c r="E171" s="1" t="s">
         <v>24</v>
@@ -8294,10 +8282,10 @@
         <v>3</v>
       </c>
       <c r="D172" s="1" t="s">
-        <v>37</v>
+        <v>63</v>
       </c>
       <c r="E172" s="1" t="s">
-        <v>55</v>
+        <v>28</v>
       </c>
       <c r="F172" s="1" t="s">
         <v>25</v>
@@ -8314,10 +8302,10 @@
         <v>3</v>
       </c>
       <c r="D173" s="1" t="s">
-        <v>37</v>
+        <v>63</v>
       </c>
       <c r="E173" s="1" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="F173" s="1" t="s">
         <v>25</v>
@@ -8334,10 +8322,10 @@
         <v>3</v>
       </c>
       <c r="D174" s="1" t="s">
-        <v>37</v>
+        <v>63</v>
       </c>
       <c r="E174" s="1" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="F174" s="1" t="s">
         <v>25</v>
@@ -8354,10 +8342,10 @@
         <v>3</v>
       </c>
       <c r="D175" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="E175" s="1" t="s">
         <v>37</v>
-      </c>
-      <c r="E175" s="1" t="s">
-        <v>34</v>
       </c>
       <c r="F175" s="1" t="s">
         <v>25</v>
@@ -8374,10 +8362,10 @@
         <v>3</v>
       </c>
       <c r="D176" s="1" t="s">
-        <v>37</v>
+        <v>63</v>
       </c>
       <c r="E176" s="1" t="s">
-        <v>37</v>
+        <v>63</v>
       </c>
       <c r="F176" s="1" t="s">
         <v>38</v>
@@ -8394,7 +8382,7 @@
         <v>3</v>
       </c>
       <c r="D177" s="1" t="s">
-        <v>37</v>
+        <v>63</v>
       </c>
       <c r="E177" s="1" t="s">
         <v>66</v>
@@ -8414,7 +8402,7 @@
         <v>3</v>
       </c>
       <c r="D178" s="1" t="s">
-        <v>37</v>
+        <v>63</v>
       </c>
       <c r="E178" s="1" t="s">
         <v>98</v>
@@ -8434,7 +8422,7 @@
         <v>3</v>
       </c>
       <c r="D179" s="1" t="s">
-        <v>37</v>
+        <v>63</v>
       </c>
       <c r="E179" s="1" t="s">
         <v>101</v>
@@ -8597,7 +8585,7 @@
         <v>66</v>
       </c>
       <c r="E187" s="1" t="s">
-        <v>55</v>
+        <v>28</v>
       </c>
       <c r="F187" s="1" t="s">
         <v>5</v>
@@ -8617,7 +8605,7 @@
         <v>66</v>
       </c>
       <c r="E188" s="1" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="F188" s="1" t="s">
         <v>5</v>
@@ -8637,7 +8625,7 @@
         <v>66</v>
       </c>
       <c r="E189" s="1" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="F189" s="1" t="s">
         <v>154</v>
@@ -8657,7 +8645,7 @@
         <v>66</v>
       </c>
       <c r="E190" s="1" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="F190" s="1" t="s">
         <v>25</v>
@@ -8677,7 +8665,7 @@
         <v>66</v>
       </c>
       <c r="E191" s="1" t="s">
-        <v>37</v>
+        <v>63</v>
       </c>
       <c r="F191" s="1" t="s">
         <v>276</v>
@@ -9237,7 +9225,7 @@
         <v>98</v>
       </c>
       <c r="E219" s="1" t="s">
-        <v>55</v>
+        <v>28</v>
       </c>
       <c r="F219" s="1" t="s">
         <v>5</v>
@@ -9257,7 +9245,7 @@
         <v>98</v>
       </c>
       <c r="E220" s="1" t="s">
-        <v>55</v>
+        <v>28</v>
       </c>
       <c r="F220" s="1" t="s">
         <v>5</v>
@@ -9277,7 +9265,7 @@
         <v>98</v>
       </c>
       <c r="E221" s="1" t="s">
-        <v>55</v>
+        <v>28</v>
       </c>
       <c r="F221" s="1" t="s">
         <v>38</v>
@@ -9297,7 +9285,7 @@
         <v>98</v>
       </c>
       <c r="E222" s="1" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="F222" s="1" t="s">
         <v>5</v>
@@ -9317,7 +9305,7 @@
         <v>98</v>
       </c>
       <c r="E223" s="1" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="F223" s="1" t="s">
         <v>5</v>
@@ -9337,7 +9325,7 @@
         <v>98</v>
       </c>
       <c r="E224" s="1" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="F224" s="1" t="s">
         <v>38</v>
@@ -9357,7 +9345,7 @@
         <v>98</v>
       </c>
       <c r="E225" s="1" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="F225" s="1" t="s">
         <v>25</v>
@@ -9377,7 +9365,7 @@
         <v>98</v>
       </c>
       <c r="E226" s="1" t="s">
-        <v>37</v>
+        <v>63</v>
       </c>
       <c r="F226" s="1" t="s">
         <v>25</v>
@@ -9537,7 +9525,7 @@
         <v>101</v>
       </c>
       <c r="E234" s="1" t="s">
-        <v>55</v>
+        <v>28</v>
       </c>
       <c r="F234" s="1" t="s">
         <v>5</v>
@@ -9557,7 +9545,7 @@
         <v>101</v>
       </c>
       <c r="E235" s="1" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="F235" s="1" t="s">
         <v>5</v>
@@ -9577,7 +9565,7 @@
         <v>101</v>
       </c>
       <c r="E236" s="1" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="F236" s="1" t="s">
         <v>5</v>
@@ -9737,10 +9725,10 @@
         <v>104</v>
       </c>
       <c r="E244" s="1" t="s">
-        <v>55</v>
+        <v>28</v>
       </c>
       <c r="F244" s="1" t="s">
-        <v>38</v>
+        <v>5</v>
       </c>
     </row>
     <row r="245" spans="1:6" x14ac:dyDescent="0.25">
@@ -9757,7 +9745,7 @@
         <v>104</v>
       </c>
       <c r="E245" s="1" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="F245" s="1" t="s">
         <v>38</v>
@@ -9774,13 +9762,13 @@
         <v>3</v>
       </c>
       <c r="D246" s="1" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="E246" s="1" t="s">
-        <v>4</v>
+        <v>34</v>
       </c>
       <c r="F246" s="1" t="s">
-        <v>9</v>
+        <v>38</v>
       </c>
     </row>
     <row r="247" spans="1:6" x14ac:dyDescent="0.25">
@@ -9797,7 +9785,7 @@
         <v>107</v>
       </c>
       <c r="E247" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F247" s="1" t="s">
         <v>9</v>
@@ -9817,10 +9805,10 @@
         <v>107</v>
       </c>
       <c r="E248" s="1" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="F248" s="1" t="s">
-        <v>154</v>
+        <v>9</v>
       </c>
     </row>
     <row r="249" spans="1:6" x14ac:dyDescent="0.25">
@@ -9837,7 +9825,7 @@
         <v>107</v>
       </c>
       <c r="E249" s="1" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="F249" s="1" t="s">
         <v>154</v>
@@ -9857,18 +9845,18 @@
         <v>107</v>
       </c>
       <c r="E250" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="F250" s="1" t="s">
-        <v>533</v>
+        <v>154</v>
       </c>
     </row>
     <row r="251" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A251" s="1" t="s">
+        <v>533</v>
+      </c>
+      <c r="B251" s="1" t="s">
         <v>534</v>
-      </c>
-      <c r="B251" s="1" t="s">
-        <v>535</v>
       </c>
       <c r="C251" s="1" t="s">
         <v>3</v>
@@ -9877,10 +9865,10 @@
         <v>107</v>
       </c>
       <c r="E251" s="1" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="F251" s="1" t="s">
-        <v>533</v>
+        <v>535</v>
       </c>
     </row>
     <row r="252" spans="1:6" x14ac:dyDescent="0.25">
@@ -9897,10 +9885,10 @@
         <v>107</v>
       </c>
       <c r="E252" s="1" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="F252" s="1" t="s">
-        <v>533</v>
+        <v>535</v>
       </c>
     </row>
     <row r="253" spans="1:6" x14ac:dyDescent="0.25">
@@ -9917,10 +9905,10 @@
         <v>107</v>
       </c>
       <c r="E253" s="1" t="s">
-        <v>55</v>
+        <v>24</v>
       </c>
       <c r="F253" s="1" t="s">
-        <v>533</v>
+        <v>535</v>
       </c>
     </row>
     <row r="254" spans="1:6" x14ac:dyDescent="0.25">
@@ -9940,7 +9928,7 @@
         <v>28</v>
       </c>
       <c r="F254" s="1" t="s">
-        <v>533</v>
+        <v>535</v>
       </c>
     </row>
     <row r="255" spans="1:6" x14ac:dyDescent="0.25">
@@ -9960,7 +9948,7 @@
         <v>31</v>
       </c>
       <c r="F255" s="1" t="s">
-        <v>533</v>
+        <v>535</v>
       </c>
     </row>
     <row r="256" spans="1:6" x14ac:dyDescent="0.25">
@@ -9974,13 +9962,13 @@
         <v>3</v>
       </c>
       <c r="D256" s="1" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="E256" s="1" t="s">
-        <v>4</v>
+        <v>34</v>
       </c>
       <c r="F256" s="1" t="s">
-        <v>38</v>
+        <v>535</v>
       </c>
     </row>
     <row r="257" spans="1:6" x14ac:dyDescent="0.25">
@@ -9997,7 +9985,7 @@
         <v>110</v>
       </c>
       <c r="E257" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F257" s="1" t="s">
         <v>38</v>
@@ -10017,7 +10005,7 @@
         <v>110</v>
       </c>
       <c r="E258" s="1" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="F258" s="1" t="s">
         <v>38</v>
@@ -10037,7 +10025,7 @@
         <v>110</v>
       </c>
       <c r="E259" s="1" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="F259" s="1" t="s">
         <v>38</v>
@@ -10057,7 +10045,7 @@
         <v>110</v>
       </c>
       <c r="E260" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="F260" s="1" t="s">
         <v>38</v>
@@ -10077,10 +10065,10 @@
         <v>110</v>
       </c>
       <c r="E261" s="1" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="F261" s="1" t="s">
-        <v>9</v>
+        <v>38</v>
       </c>
     </row>
     <row r="262" spans="1:6" x14ac:dyDescent="0.25">
@@ -10097,7 +10085,7 @@
         <v>110</v>
       </c>
       <c r="E262" s="1" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="F262" s="1" t="s">
         <v>9</v>
@@ -10117,10 +10105,10 @@
         <v>110</v>
       </c>
       <c r="E263" s="1" t="s">
-        <v>55</v>
+        <v>24</v>
       </c>
       <c r="F263" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="264" spans="1:6" x14ac:dyDescent="0.25">
@@ -10140,7 +10128,7 @@
         <v>28</v>
       </c>
       <c r="F264" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="265" spans="1:6" x14ac:dyDescent="0.25">
@@ -10148,7 +10136,7 @@
         <v>562</v>
       </c>
       <c r="B265" s="1" t="s">
-        <v>561</v>
+        <v>563</v>
       </c>
       <c r="C265" s="1" t="s">
         <v>3</v>
@@ -10165,22 +10153,22 @@
     </row>
     <row r="266" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A266" s="1" t="s">
+        <v>564</v>
+      </c>
+      <c r="B266" s="1" t="s">
         <v>563</v>
       </c>
-      <c r="B266" s="1" t="s">
-        <v>564</v>
-      </c>
       <c r="C266" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D266" s="1" t="s">
-        <v>150</v>
+        <v>110</v>
       </c>
       <c r="E266" s="1" t="s">
-        <v>4</v>
+        <v>34</v>
       </c>
       <c r="F266" s="1" t="s">
-        <v>38</v>
+        <v>9</v>
       </c>
     </row>
     <row r="267" spans="1:6" x14ac:dyDescent="0.25">
@@ -10197,7 +10185,7 @@
         <v>150</v>
       </c>
       <c r="E267" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F267" s="1" t="s">
         <v>38</v>
@@ -10217,7 +10205,7 @@
         <v>150</v>
       </c>
       <c r="E268" s="1" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="F268" s="1" t="s">
         <v>38</v>
@@ -10237,7 +10225,7 @@
         <v>150</v>
       </c>
       <c r="E269" s="1" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="F269" s="1" t="s">
         <v>38</v>
@@ -10257,7 +10245,7 @@
         <v>150</v>
       </c>
       <c r="E270" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="F270" s="1" t="s">
         <v>38</v>
@@ -10277,7 +10265,7 @@
         <v>150</v>
       </c>
       <c r="E271" s="1" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="F271" s="1" t="s">
         <v>38</v>
@@ -10297,7 +10285,7 @@
         <v>150</v>
       </c>
       <c r="E272" s="1" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="F272" s="1" t="s">
         <v>38</v>
@@ -10317,7 +10305,7 @@
         <v>150</v>
       </c>
       <c r="E273" s="1" t="s">
-        <v>55</v>
+        <v>24</v>
       </c>
       <c r="F273" s="1" t="s">
         <v>38</v>
@@ -10360,7 +10348,7 @@
         <v>31</v>
       </c>
       <c r="F275" s="1" t="s">
-        <v>5</v>
+        <v>38</v>
       </c>
     </row>
     <row r="276" spans="1:6" x14ac:dyDescent="0.25">
@@ -10374,13 +10362,13 @@
         <v>3</v>
       </c>
       <c r="D276" s="1" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="E276" s="1" t="s">
-        <v>4</v>
+        <v>34</v>
       </c>
       <c r="F276" s="1" t="s">
-        <v>533</v>
+        <v>5</v>
       </c>
     </row>
     <row r="277" spans="1:6" x14ac:dyDescent="0.25">
@@ -10397,10 +10385,10 @@
         <v>153</v>
       </c>
       <c r="E277" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F277" s="1" t="s">
-        <v>533</v>
+        <v>535</v>
       </c>
     </row>
     <row r="278" spans="1:6" x14ac:dyDescent="0.25">
@@ -10417,10 +10405,10 @@
         <v>153</v>
       </c>
       <c r="E278" s="1" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="F278" s="1" t="s">
-        <v>533</v>
+        <v>535</v>
       </c>
     </row>
     <row r="279" spans="1:6" x14ac:dyDescent="0.25">
@@ -10437,10 +10425,10 @@
         <v>153</v>
       </c>
       <c r="E279" s="1" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="F279" s="1" t="s">
-        <v>533</v>
+        <v>535</v>
       </c>
     </row>
     <row r="280" spans="1:6" x14ac:dyDescent="0.25">
@@ -10457,10 +10445,10 @@
         <v>153</v>
       </c>
       <c r="E280" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="F280" s="1" t="s">
-        <v>533</v>
+        <v>535</v>
       </c>
     </row>
     <row r="281" spans="1:6" x14ac:dyDescent="0.25">
@@ -10477,10 +10465,10 @@
         <v>153</v>
       </c>
       <c r="E281" s="1" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="F281" s="1" t="s">
-        <v>533</v>
+        <v>535</v>
       </c>
     </row>
     <row r="282" spans="1:6" x14ac:dyDescent="0.25">
@@ -10497,10 +10485,10 @@
         <v>153</v>
       </c>
       <c r="E282" s="1" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="F282" s="1" t="s">
-        <v>5</v>
+        <v>535</v>
       </c>
     </row>
     <row r="283" spans="1:6" x14ac:dyDescent="0.25">
@@ -10517,7 +10505,7 @@
         <v>153</v>
       </c>
       <c r="E283" s="1" t="s">
-        <v>55</v>
+        <v>24</v>
       </c>
       <c r="F283" s="1" t="s">
         <v>5</v>
@@ -10574,13 +10562,13 @@
         <v>3</v>
       </c>
       <c r="D286" s="1" t="s">
-        <v>197</v>
+        <v>153</v>
       </c>
       <c r="E286" s="1" t="s">
-        <v>4</v>
+        <v>34</v>
       </c>
       <c r="F286" s="1" t="s">
-        <v>71</v>
+        <v>5</v>
       </c>
     </row>
     <row r="287" spans="1:6" x14ac:dyDescent="0.25">
@@ -10597,10 +10585,10 @@
         <v>197</v>
       </c>
       <c r="E287" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F287" s="1" t="s">
-        <v>71</v>
+        <v>5</v>
       </c>
     </row>
     <row r="288" spans="1:6" x14ac:dyDescent="0.25">
@@ -10617,10 +10605,10 @@
         <v>197</v>
       </c>
       <c r="E288" s="1" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="F288" s="1" t="s">
-        <v>38</v>
+        <v>71</v>
       </c>
     </row>
     <row r="289" spans="1:6" x14ac:dyDescent="0.25">
@@ -10637,10 +10625,10 @@
         <v>197</v>
       </c>
       <c r="E289" s="1" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="F289" s="1" t="s">
-        <v>5</v>
+        <v>71</v>
       </c>
     </row>
     <row r="290" spans="1:6" x14ac:dyDescent="0.25">
@@ -10657,10 +10645,10 @@
         <v>197</v>
       </c>
       <c r="E290" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="F290" s="1" t="s">
-        <v>5</v>
+        <v>38</v>
       </c>
     </row>
     <row r="291" spans="1:6" x14ac:dyDescent="0.25">
@@ -10677,7 +10665,7 @@
         <v>197</v>
       </c>
       <c r="E291" s="1" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="F291" s="1" t="s">
         <v>5</v>
@@ -10697,7 +10685,7 @@
         <v>197</v>
       </c>
       <c r="E292" s="1" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="F292" s="1" t="s">
         <v>5</v>
@@ -10717,7 +10705,7 @@
         <v>197</v>
       </c>
       <c r="E293" s="1" t="s">
-        <v>55</v>
+        <v>24</v>
       </c>
       <c r="F293" s="1" t="s">
         <v>5</v>
@@ -10774,33 +10762,33 @@
         <v>3</v>
       </c>
       <c r="D296" s="1" t="s">
-        <v>625</v>
+        <v>197</v>
       </c>
       <c r="E296" s="1" t="s">
-        <v>4</v>
+        <v>34</v>
       </c>
       <c r="F296" s="1" t="s">
-        <v>38</v>
+        <v>5</v>
       </c>
     </row>
     <row r="297" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A297" s="1" t="s">
+        <v>625</v>
+      </c>
+      <c r="B297" s="1" t="s">
         <v>626</v>
       </c>
-      <c r="B297" s="1" t="s">
+      <c r="C297" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D297" s="1" t="s">
         <v>627</v>
       </c>
-      <c r="C297" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D297" s="1" t="s">
-        <v>625</v>
-      </c>
       <c r="E297" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F297" s="1" t="s">
-        <v>5</v>
+        <v>38</v>
       </c>
     </row>
     <row r="298" spans="1:6" x14ac:dyDescent="0.25">
@@ -10814,10 +10802,10 @@
         <v>3</v>
       </c>
       <c r="D298" s="1" t="s">
-        <v>625</v>
+        <v>627</v>
       </c>
       <c r="E298" s="1" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="F298" s="1" t="s">
         <v>5</v>
@@ -10834,10 +10822,10 @@
         <v>3</v>
       </c>
       <c r="D299" s="1" t="s">
-        <v>625</v>
+        <v>627</v>
       </c>
       <c r="E299" s="1" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="F299" s="1" t="s">
         <v>5</v>
@@ -10854,10 +10842,10 @@
         <v>3</v>
       </c>
       <c r="D300" s="1" t="s">
-        <v>625</v>
+        <v>627</v>
       </c>
       <c r="E300" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="F300" s="1" t="s">
         <v>5</v>
@@ -10874,10 +10862,10 @@
         <v>3</v>
       </c>
       <c r="D301" s="1" t="s">
-        <v>625</v>
+        <v>627</v>
       </c>
       <c r="E301" s="1" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="F301" s="1" t="s">
         <v>5</v>
@@ -10894,10 +10882,10 @@
         <v>3</v>
       </c>
       <c r="D302" s="1" t="s">
-        <v>625</v>
+        <v>627</v>
       </c>
       <c r="E302" s="1" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="F302" s="1" t="s">
         <v>5</v>
@@ -10914,10 +10902,10 @@
         <v>3</v>
       </c>
       <c r="D303" s="1" t="s">
-        <v>625</v>
+        <v>627</v>
       </c>
       <c r="E303" s="1" t="s">
-        <v>55</v>
+        <v>24</v>
       </c>
       <c r="F303" s="1" t="s">
         <v>5</v>
@@ -10934,33 +10922,33 @@
         <v>3</v>
       </c>
       <c r="D304" s="1" t="s">
-        <v>625</v>
+        <v>627</v>
       </c>
       <c r="E304" s="1" t="s">
         <v>28</v>
       </c>
       <c r="F304" s="1" t="s">
-        <v>642</v>
+        <v>5</v>
       </c>
     </row>
     <row r="305" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A305" s="1" t="s">
+        <v>642</v>
+      </c>
+      <c r="B305" s="1" t="s">
         <v>643</v>
       </c>
-      <c r="B305" s="1" t="s">
-        <v>644</v>
-      </c>
       <c r="C305" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D305" s="1" t="s">
-        <v>625</v>
+        <v>627</v>
       </c>
       <c r="E305" s="1" t="s">
         <v>31</v>
       </c>
       <c r="F305" s="1" t="s">
-        <v>642</v>
+        <v>644</v>
       </c>
     </row>
     <row r="306" spans="1:6" x14ac:dyDescent="0.25">
@@ -10974,13 +10962,13 @@
         <v>3</v>
       </c>
       <c r="D306" s="1" t="s">
-        <v>625</v>
+        <v>627</v>
       </c>
       <c r="E306" s="1" t="s">
         <v>34</v>
       </c>
       <c r="F306" s="1" t="s">
-        <v>5</v>
+        <v>644</v>
       </c>
     </row>
     <row r="307" spans="1:6" x14ac:dyDescent="0.25">
@@ -10994,7 +10982,7 @@
         <v>3</v>
       </c>
       <c r="D307" s="1" t="s">
-        <v>625</v>
+        <v>627</v>
       </c>
       <c r="E307" s="1" t="s">
         <v>37</v>
@@ -11014,13 +11002,13 @@
         <v>3</v>
       </c>
       <c r="D308" s="1" t="s">
-        <v>625</v>
+        <v>627</v>
       </c>
       <c r="E308" s="1" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="F308" s="1" t="s">
-        <v>38</v>
+        <v>5</v>
       </c>
     </row>
     <row r="309" spans="1:6" x14ac:dyDescent="0.25">
@@ -11034,10 +11022,10 @@
         <v>3</v>
       </c>
       <c r="D309" s="1" t="s">
-        <v>625</v>
+        <v>627</v>
       </c>
       <c r="E309" s="1" t="s">
-        <v>98</v>
+        <v>66</v>
       </c>
       <c r="F309" s="1" t="s">
         <v>38</v>
@@ -11054,13 +11042,13 @@
         <v>3</v>
       </c>
       <c r="D310" s="1" t="s">
-        <v>625</v>
+        <v>627</v>
       </c>
       <c r="E310" s="1" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="F310" s="1" t="s">
-        <v>5</v>
+        <v>38</v>
       </c>
     </row>
     <row r="311" spans="1:6" x14ac:dyDescent="0.25">
@@ -11074,10 +11062,10 @@
         <v>3</v>
       </c>
       <c r="D311" s="1" t="s">
-        <v>657</v>
+        <v>627</v>
       </c>
       <c r="E311" s="1" t="s">
-        <v>4</v>
+        <v>101</v>
       </c>
       <c r="F311" s="1" t="s">
         <v>5</v>
@@ -11085,19 +11073,19 @@
     </row>
     <row r="312" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A312" s="1" t="s">
+        <v>657</v>
+      </c>
+      <c r="B312" s="1" t="s">
         <v>658</v>
       </c>
-      <c r="B312" s="1" t="s">
+      <c r="C312" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D312" s="1" t="s">
         <v>659</v>
       </c>
-      <c r="C312" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D312" s="1" t="s">
-        <v>657</v>
-      </c>
       <c r="E312" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F312" s="1" t="s">
         <v>5</v>
@@ -11114,13 +11102,13 @@
         <v>3</v>
       </c>
       <c r="D313" s="1" t="s">
-        <v>657</v>
+        <v>659</v>
       </c>
       <c r="E313" s="1" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="F313" s="1" t="s">
-        <v>78</v>
+        <v>5</v>
       </c>
     </row>
     <row r="314" spans="1:6" x14ac:dyDescent="0.25">
@@ -11134,13 +11122,13 @@
         <v>3</v>
       </c>
       <c r="D314" s="1" t="s">
-        <v>657</v>
+        <v>659</v>
       </c>
       <c r="E314" s="1" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="F314" s="1" t="s">
-        <v>5</v>
+        <v>78</v>
       </c>
     </row>
     <row r="315" spans="1:6" x14ac:dyDescent="0.25">
@@ -11154,10 +11142,10 @@
         <v>3</v>
       </c>
       <c r="D315" s="1" t="s">
-        <v>657</v>
+        <v>659</v>
       </c>
       <c r="E315" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="F315" s="1" t="s">
         <v>5</v>
@@ -11174,10 +11162,10 @@
         <v>3</v>
       </c>
       <c r="D316" s="1" t="s">
-        <v>657</v>
+        <v>659</v>
       </c>
       <c r="E316" s="1" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="F316" s="1" t="s">
         <v>5</v>
@@ -11194,10 +11182,10 @@
         <v>3</v>
       </c>
       <c r="D317" s="1" t="s">
-        <v>657</v>
+        <v>659</v>
       </c>
       <c r="E317" s="1" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="F317" s="1" t="s">
         <v>5</v>
@@ -11214,10 +11202,10 @@
         <v>3</v>
       </c>
       <c r="D318" s="1" t="s">
-        <v>657</v>
+        <v>659</v>
       </c>
       <c r="E318" s="1" t="s">
-        <v>55</v>
+        <v>24</v>
       </c>
       <c r="F318" s="1" t="s">
         <v>5</v>
@@ -11234,7 +11222,7 @@
         <v>3</v>
       </c>
       <c r="D319" s="1" t="s">
-        <v>657</v>
+        <v>659</v>
       </c>
       <c r="E319" s="1" t="s">
         <v>28</v>
@@ -11254,7 +11242,7 @@
         <v>3</v>
       </c>
       <c r="D320" s="1" t="s">
-        <v>657</v>
+        <v>659</v>
       </c>
       <c r="E320" s="1" t="s">
         <v>31</v>
@@ -11274,7 +11262,7 @@
         <v>3</v>
       </c>
       <c r="D321" s="1" t="s">
-        <v>657</v>
+        <v>659</v>
       </c>
       <c r="E321" s="1" t="s">
         <v>34</v>
@@ -11294,7 +11282,7 @@
         <v>3</v>
       </c>
       <c r="D322" s="1" t="s">
-        <v>657</v>
+        <v>659</v>
       </c>
       <c r="E322" s="1" t="s">
         <v>37</v>
@@ -11314,10 +11302,10 @@
         <v>3</v>
       </c>
       <c r="D323" s="1" t="s">
-        <v>657</v>
+        <v>659</v>
       </c>
       <c r="E323" s="1" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="F323" s="1" t="s">
         <v>5</v>
@@ -11334,13 +11322,13 @@
         <v>3</v>
       </c>
       <c r="D324" s="1" t="s">
-        <v>657</v>
+        <v>659</v>
       </c>
       <c r="E324" s="1" t="s">
-        <v>98</v>
+        <v>66</v>
       </c>
       <c r="F324" s="1" t="s">
-        <v>25</v>
+        <v>5</v>
       </c>
     </row>
     <row r="325" spans="1:6" x14ac:dyDescent="0.25">
@@ -11354,13 +11342,13 @@
         <v>3</v>
       </c>
       <c r="D325" s="1" t="s">
-        <v>657</v>
+        <v>659</v>
       </c>
       <c r="E325" s="1" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="F325" s="1" t="s">
-        <v>38</v>
+        <v>25</v>
       </c>
     </row>
     <row r="326" spans="1:6" x14ac:dyDescent="0.25">
@@ -11374,13 +11362,13 @@
         <v>3</v>
       </c>
       <c r="D326" s="1" t="s">
-        <v>657</v>
+        <v>659</v>
       </c>
       <c r="E326" s="1" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="F326" s="1" t="s">
-        <v>230</v>
+        <v>5</v>
       </c>
     </row>
     <row r="327" spans="1:6" x14ac:dyDescent="0.25">
@@ -11394,10 +11382,10 @@
         <v>3</v>
       </c>
       <c r="D327" s="1" t="s">
-        <v>657</v>
+        <v>659</v>
       </c>
       <c r="E327" s="1" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="F327" s="1" t="s">
         <v>5</v>
@@ -11414,30 +11402,30 @@
         <v>3</v>
       </c>
       <c r="D328" s="1" t="s">
-        <v>657</v>
+        <v>692</v>
       </c>
       <c r="E328" s="1" t="s">
-        <v>110</v>
+        <v>4</v>
       </c>
       <c r="F328" s="1" t="s">
-        <v>5</v>
+        <v>25</v>
       </c>
     </row>
     <row r="329" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A329" s="1" t="s">
+        <v>693</v>
+      </c>
+      <c r="B329" s="1" t="s">
+        <v>694</v>
+      </c>
+      <c r="C329" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D329" s="1" t="s">
         <v>692</v>
       </c>
-      <c r="B329" s="1" t="s">
-        <v>693</v>
-      </c>
-      <c r="C329" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D329" s="1" t="s">
-        <v>694</v>
-      </c>
       <c r="E329" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F329" s="1" t="s">
         <v>25</v>
@@ -11454,13 +11442,13 @@
         <v>3</v>
       </c>
       <c r="D330" s="1" t="s">
-        <v>694</v>
+        <v>692</v>
       </c>
       <c r="E330" s="1" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="F330" s="1" t="s">
-        <v>25</v>
+        <v>535</v>
       </c>
     </row>
     <row r="331" spans="1:6" x14ac:dyDescent="0.25">
@@ -11474,13 +11462,13 @@
         <v>3</v>
       </c>
       <c r="D331" s="1" t="s">
-        <v>694</v>
+        <v>692</v>
       </c>
       <c r="E331" s="1" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="F331" s="1" t="s">
-        <v>533</v>
+        <v>25</v>
       </c>
     </row>
     <row r="332" spans="1:6" x14ac:dyDescent="0.25">
@@ -11494,13 +11482,13 @@
         <v>3</v>
       </c>
       <c r="D332" s="1" t="s">
-        <v>694</v>
+        <v>692</v>
       </c>
       <c r="E332" s="1" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="F332" s="1" t="s">
-        <v>25</v>
+        <v>38</v>
       </c>
     </row>
     <row r="333" spans="1:6" x14ac:dyDescent="0.25">
@@ -11514,10 +11502,10 @@
         <v>3</v>
       </c>
       <c r="D333" s="1" t="s">
-        <v>694</v>
+        <v>692</v>
       </c>
       <c r="E333" s="1" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="F333" s="1" t="s">
         <v>38</v>
@@ -11534,13 +11522,13 @@
         <v>3</v>
       </c>
       <c r="D334" s="1" t="s">
-        <v>694</v>
+        <v>692</v>
       </c>
       <c r="E334" s="1" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="F334" s="1" t="s">
-        <v>38</v>
+        <v>5</v>
       </c>
     </row>
     <row r="335" spans="1:6" x14ac:dyDescent="0.25">
@@ -11554,10 +11542,10 @@
         <v>3</v>
       </c>
       <c r="D335" s="1" t="s">
-        <v>694</v>
+        <v>692</v>
       </c>
       <c r="E335" s="1" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="F335" s="1" t="s">
         <v>5</v>
@@ -11574,10 +11562,10 @@
         <v>3</v>
       </c>
       <c r="D336" s="1" t="s">
-        <v>694</v>
+        <v>692</v>
       </c>
       <c r="E336" s="1" t="s">
-        <v>55</v>
+        <v>31</v>
       </c>
       <c r="F336" s="1" t="s">
         <v>5</v>
@@ -11594,10 +11582,10 @@
         <v>3</v>
       </c>
       <c r="D337" s="1" t="s">
-        <v>694</v>
+        <v>692</v>
       </c>
       <c r="E337" s="1" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="F337" s="1" t="s">
         <v>5</v>
@@ -11614,10 +11602,10 @@
         <v>3</v>
       </c>
       <c r="D338" s="1" t="s">
-        <v>694</v>
+        <v>692</v>
       </c>
       <c r="E338" s="1" t="s">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="F338" s="1" t="s">
         <v>5</v>
@@ -11634,10 +11622,10 @@
         <v>3</v>
       </c>
       <c r="D339" s="1" t="s">
-        <v>694</v>
+        <v>692</v>
       </c>
       <c r="E339" s="1" t="s">
-        <v>34</v>
+        <v>63</v>
       </c>
       <c r="F339" s="1" t="s">
         <v>5</v>
@@ -11654,30 +11642,30 @@
         <v>3</v>
       </c>
       <c r="D340" s="1" t="s">
-        <v>694</v>
+        <v>717</v>
       </c>
       <c r="E340" s="1" t="s">
-        <v>37</v>
+        <v>4</v>
       </c>
       <c r="F340" s="1" t="s">
-        <v>5</v>
+        <v>25</v>
       </c>
     </row>
     <row r="341" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A341" s="1" t="s">
+        <v>718</v>
+      </c>
+      <c r="B341" s="1" t="s">
+        <v>719</v>
+      </c>
+      <c r="C341" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D341" s="1" t="s">
         <v>717</v>
       </c>
-      <c r="B341" s="1" t="s">
-        <v>718</v>
-      </c>
-      <c r="C341" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D341" s="1" t="s">
-        <v>719</v>
-      </c>
       <c r="E341" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F341" s="1" t="s">
         <v>25</v>
@@ -11694,13 +11682,13 @@
         <v>3</v>
       </c>
       <c r="D342" s="1" t="s">
-        <v>719</v>
+        <v>717</v>
       </c>
       <c r="E342" s="1" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="F342" s="1" t="s">
-        <v>25</v>
+        <v>78</v>
       </c>
     </row>
     <row r="343" spans="1:6" x14ac:dyDescent="0.25">
@@ -11714,10 +11702,10 @@
         <v>3</v>
       </c>
       <c r="D343" s="1" t="s">
-        <v>719</v>
+        <v>717</v>
       </c>
       <c r="E343" s="1" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="F343" s="1" t="s">
         <v>78</v>
@@ -11734,13 +11722,13 @@
         <v>3</v>
       </c>
       <c r="D344" s="1" t="s">
-        <v>719</v>
+        <v>717</v>
       </c>
       <c r="E344" s="1" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="F344" s="1" t="s">
-        <v>78</v>
+        <v>5</v>
       </c>
     </row>
     <row r="345" spans="1:6" x14ac:dyDescent="0.25">
@@ -11754,13 +11742,13 @@
         <v>3</v>
       </c>
       <c r="D345" s="1" t="s">
-        <v>719</v>
+        <v>717</v>
       </c>
       <c r="E345" s="1" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="F345" s="1" t="s">
-        <v>5</v>
+        <v>78</v>
       </c>
     </row>
     <row r="346" spans="1:6" x14ac:dyDescent="0.25">
@@ -11774,13 +11762,13 @@
         <v>3</v>
       </c>
       <c r="D346" s="1" t="s">
-        <v>719</v>
+        <v>717</v>
       </c>
       <c r="E346" s="1" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="F346" s="1" t="s">
-        <v>78</v>
+        <v>38</v>
       </c>
     </row>
     <row r="347" spans="1:6" x14ac:dyDescent="0.25">
@@ -11794,10 +11782,10 @@
         <v>3</v>
       </c>
       <c r="D347" s="1" t="s">
-        <v>719</v>
+        <v>717</v>
       </c>
       <c r="E347" s="1" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="F347" s="1" t="s">
         <v>38</v>
@@ -11814,13 +11802,13 @@
         <v>3</v>
       </c>
       <c r="D348" s="1" t="s">
-        <v>719</v>
+        <v>717</v>
       </c>
       <c r="E348" s="1" t="s">
-        <v>55</v>
+        <v>31</v>
       </c>
       <c r="F348" s="1" t="s">
-        <v>38</v>
+        <v>5</v>
       </c>
     </row>
     <row r="349" spans="1:6" x14ac:dyDescent="0.25">
@@ -11834,10 +11822,10 @@
         <v>3</v>
       </c>
       <c r="D349" s="1" t="s">
-        <v>719</v>
+        <v>717</v>
       </c>
       <c r="E349" s="1" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="F349" s="1" t="s">
         <v>5</v>
@@ -11854,10 +11842,10 @@
         <v>3</v>
       </c>
       <c r="D350" s="1" t="s">
-        <v>719</v>
+        <v>717</v>
       </c>
       <c r="E350" s="1" t="s">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="F350" s="1" t="s">
         <v>5</v>
@@ -11874,13 +11862,13 @@
         <v>3</v>
       </c>
       <c r="D351" s="1" t="s">
-        <v>719</v>
+        <v>717</v>
       </c>
       <c r="E351" s="1" t="s">
-        <v>34</v>
+        <v>63</v>
       </c>
       <c r="F351" s="1" t="s">
-        <v>5</v>
+        <v>25</v>
       </c>
     </row>
     <row r="352" spans="1:6" x14ac:dyDescent="0.25">
@@ -11894,10 +11882,10 @@
         <v>3</v>
       </c>
       <c r="D352" s="1" t="s">
-        <v>719</v>
+        <v>717</v>
       </c>
       <c r="E352" s="1" t="s">
-        <v>37</v>
+        <v>66</v>
       </c>
       <c r="F352" s="1" t="s">
         <v>25</v>
@@ -11914,10 +11902,10 @@
         <v>3</v>
       </c>
       <c r="D353" s="1" t="s">
-        <v>719</v>
+        <v>717</v>
       </c>
       <c r="E353" s="1" t="s">
-        <v>66</v>
+        <v>98</v>
       </c>
       <c r="F353" s="1" t="s">
         <v>25</v>
@@ -11934,30 +11922,30 @@
         <v>3</v>
       </c>
       <c r="D354" s="1" t="s">
-        <v>719</v>
+        <v>746</v>
       </c>
       <c r="E354" s="1" t="s">
-        <v>98</v>
+        <v>4</v>
       </c>
       <c r="F354" s="1" t="s">
-        <v>25</v>
+        <v>5</v>
       </c>
     </row>
     <row r="355" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A355" s="1" t="s">
+        <v>747</v>
+      </c>
+      <c r="B355" s="1" t="s">
+        <v>748</v>
+      </c>
+      <c r="C355" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D355" s="1" t="s">
         <v>746</v>
       </c>
-      <c r="B355" s="1" t="s">
-        <v>747</v>
-      </c>
-      <c r="C355" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D355" s="1" t="s">
-        <v>748</v>
-      </c>
       <c r="E355" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F355" s="1" t="s">
         <v>5</v>
@@ -11974,10 +11962,10 @@
         <v>3</v>
       </c>
       <c r="D356" s="1" t="s">
-        <v>748</v>
+        <v>746</v>
       </c>
       <c r="E356" s="1" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="F356" s="1" t="s">
         <v>5</v>
@@ -11994,10 +11982,10 @@
         <v>3</v>
       </c>
       <c r="D357" s="1" t="s">
-        <v>748</v>
+        <v>746</v>
       </c>
       <c r="E357" s="1" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="F357" s="1" t="s">
         <v>5</v>
@@ -12014,10 +12002,10 @@
         <v>3</v>
       </c>
       <c r="D358" s="1" t="s">
-        <v>748</v>
+        <v>746</v>
       </c>
       <c r="E358" s="1" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="F358" s="1" t="s">
         <v>5</v>
@@ -12034,13 +12022,13 @@
         <v>3</v>
       </c>
       <c r="D359" s="1" t="s">
-        <v>748</v>
+        <v>746</v>
       </c>
       <c r="E359" s="1" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="F359" s="1" t="s">
-        <v>5</v>
+        <v>38</v>
       </c>
     </row>
     <row r="360" spans="1:6" x14ac:dyDescent="0.25">
@@ -12054,13 +12042,13 @@
         <v>3</v>
       </c>
       <c r="D360" s="1" t="s">
-        <v>748</v>
+        <v>746</v>
       </c>
       <c r="E360" s="1" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="F360" s="1" t="s">
-        <v>38</v>
+        <v>5</v>
       </c>
     </row>
     <row r="361" spans="1:6" x14ac:dyDescent="0.25">
@@ -12074,13 +12062,13 @@
         <v>3</v>
       </c>
       <c r="D361" s="1" t="s">
-        <v>748</v>
+        <v>746</v>
       </c>
       <c r="E361" s="1" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="F361" s="1" t="s">
-        <v>5</v>
+        <v>38</v>
       </c>
     </row>
     <row r="362" spans="1:6" x14ac:dyDescent="0.25">
@@ -12094,10 +12082,10 @@
         <v>3</v>
       </c>
       <c r="D362" s="1" t="s">
-        <v>748</v>
+        <v>746</v>
       </c>
       <c r="E362" s="1" t="s">
-        <v>55</v>
+        <v>31</v>
       </c>
       <c r="F362" s="1" t="s">
         <v>38</v>
@@ -12114,10 +12102,10 @@
         <v>3</v>
       </c>
       <c r="D363" s="1" t="s">
-        <v>748</v>
+        <v>746</v>
       </c>
       <c r="E363" s="1" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="F363" s="1" t="s">
         <v>38</v>
@@ -12134,10 +12122,10 @@
         <v>3</v>
       </c>
       <c r="D364" s="1" t="s">
-        <v>748</v>
+        <v>746</v>
       </c>
       <c r="E364" s="1" t="s">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="F364" s="1" t="s">
         <v>38</v>
@@ -12154,13 +12142,13 @@
         <v>3</v>
       </c>
       <c r="D365" s="1" t="s">
-        <v>748</v>
+        <v>746</v>
       </c>
       <c r="E365" s="1" t="s">
-        <v>34</v>
+        <v>63</v>
       </c>
       <c r="F365" s="1" t="s">
-        <v>38</v>
+        <v>9</v>
       </c>
     </row>
     <row r="366" spans="1:6" x14ac:dyDescent="0.25">
@@ -12174,13 +12162,13 @@
         <v>3</v>
       </c>
       <c r="D366" s="1" t="s">
-        <v>748</v>
+        <v>746</v>
       </c>
       <c r="E366" s="1" t="s">
-        <v>37</v>
+        <v>66</v>
       </c>
       <c r="F366" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="367" spans="1:6" x14ac:dyDescent="0.25">
@@ -12194,10 +12182,10 @@
         <v>3</v>
       </c>
       <c r="D367" s="1" t="s">
-        <v>748</v>
+        <v>746</v>
       </c>
       <c r="E367" s="1" t="s">
-        <v>66</v>
+        <v>98</v>
       </c>
       <c r="F367" s="1" t="s">
         <v>5</v>
@@ -12214,10 +12202,10 @@
         <v>3</v>
       </c>
       <c r="D368" s="1" t="s">
-        <v>748</v>
+        <v>746</v>
       </c>
       <c r="E368" s="1" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="F368" s="1" t="s">
         <v>5</v>
@@ -12234,10 +12222,10 @@
         <v>3</v>
       </c>
       <c r="D369" s="1" t="s">
-        <v>748</v>
+        <v>746</v>
       </c>
       <c r="E369" s="1" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="F369" s="1" t="s">
         <v>5</v>
@@ -12254,13 +12242,13 @@
         <v>3</v>
       </c>
       <c r="D370" s="1" t="s">
-        <v>748</v>
+        <v>746</v>
       </c>
       <c r="E370" s="1" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="F370" s="1" t="s">
-        <v>5</v>
+        <v>38</v>
       </c>
     </row>
     <row r="371" spans="1:6" x14ac:dyDescent="0.25">
@@ -12274,10 +12262,10 @@
         <v>3</v>
       </c>
       <c r="D371" s="1" t="s">
-        <v>748</v>
+        <v>746</v>
       </c>
       <c r="E371" s="1" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="F371" s="1" t="s">
         <v>38</v>
@@ -12294,10 +12282,10 @@
         <v>3</v>
       </c>
       <c r="D372" s="1" t="s">
-        <v>748</v>
+        <v>746</v>
       </c>
       <c r="E372" s="1" t="s">
-        <v>110</v>
+        <v>150</v>
       </c>
       <c r="F372" s="1" t="s">
         <v>38</v>
@@ -12314,10 +12302,10 @@
         <v>3</v>
       </c>
       <c r="D373" s="1" t="s">
-        <v>748</v>
+        <v>785</v>
       </c>
       <c r="E373" s="1" t="s">
-        <v>150</v>
+        <v>4</v>
       </c>
       <c r="F373" s="1" t="s">
         <v>38</v>
@@ -12325,22 +12313,22 @@
     </row>
     <row r="374" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A374" s="1" t="s">
+        <v>786</v>
+      </c>
+      <c r="B374" s="1" t="s">
+        <v>787</v>
+      </c>
+      <c r="C374" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D374" s="1" t="s">
         <v>785</v>
       </c>
-      <c r="B374" s="1" t="s">
-        <v>786</v>
-      </c>
-      <c r="C374" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D374" s="1" t="s">
-        <v>787</v>
-      </c>
       <c r="E374" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F374" s="1" t="s">
-        <v>38</v>
+        <v>5</v>
       </c>
     </row>
     <row r="375" spans="1:6" x14ac:dyDescent="0.25">
@@ -12354,10 +12342,10 @@
         <v>3</v>
       </c>
       <c r="D375" s="1" t="s">
-        <v>787</v>
+        <v>785</v>
       </c>
       <c r="E375" s="1" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="F375" s="1" t="s">
         <v>5</v>
@@ -12374,10 +12362,10 @@
         <v>3</v>
       </c>
       <c r="D376" s="1" t="s">
-        <v>787</v>
+        <v>785</v>
       </c>
       <c r="E376" s="1" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="F376" s="1" t="s">
         <v>5</v>
@@ -12394,10 +12382,10 @@
         <v>3</v>
       </c>
       <c r="D377" s="1" t="s">
-        <v>787</v>
+        <v>785</v>
       </c>
       <c r="E377" s="1" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="F377" s="1" t="s">
         <v>5</v>
@@ -12414,13 +12402,13 @@
         <v>3</v>
       </c>
       <c r="D378" s="1" t="s">
-        <v>787</v>
+        <v>785</v>
       </c>
       <c r="E378" s="1" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="F378" s="1" t="s">
-        <v>5</v>
+        <v>38</v>
       </c>
     </row>
     <row r="379" spans="1:6" x14ac:dyDescent="0.25">
@@ -12434,13 +12422,13 @@
         <v>3</v>
       </c>
       <c r="D379" s="1" t="s">
-        <v>787</v>
+        <v>785</v>
       </c>
       <c r="E379" s="1" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="F379" s="1" t="s">
-        <v>38</v>
+        <v>5</v>
       </c>
     </row>
     <row r="380" spans="1:6" x14ac:dyDescent="0.25">
@@ -12454,10 +12442,10 @@
         <v>3</v>
       </c>
       <c r="D380" s="1" t="s">
-        <v>787</v>
+        <v>785</v>
       </c>
       <c r="E380" s="1" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="F380" s="1" t="s">
         <v>5</v>
@@ -12474,10 +12462,10 @@
         <v>3</v>
       </c>
       <c r="D381" s="1" t="s">
-        <v>787</v>
+        <v>785</v>
       </c>
       <c r="E381" s="1" t="s">
-        <v>55</v>
+        <v>31</v>
       </c>
       <c r="F381" s="1" t="s">
         <v>5</v>
@@ -12494,10 +12482,10 @@
         <v>3</v>
       </c>
       <c r="D382" s="1" t="s">
-        <v>787</v>
+        <v>785</v>
       </c>
       <c r="E382" s="1" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="F382" s="1" t="s">
         <v>5</v>
@@ -12514,13 +12502,13 @@
         <v>3</v>
       </c>
       <c r="D383" s="1" t="s">
-        <v>787</v>
+        <v>785</v>
       </c>
       <c r="E383" s="1" t="s">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="F383" s="1" t="s">
-        <v>5</v>
+        <v>38</v>
       </c>
     </row>
     <row r="384" spans="1:6" x14ac:dyDescent="0.25">
@@ -12534,10 +12522,10 @@
         <v>3</v>
       </c>
       <c r="D384" s="1" t="s">
-        <v>787</v>
+        <v>785</v>
       </c>
       <c r="E384" s="1" t="s">
-        <v>34</v>
+        <v>63</v>
       </c>
       <c r="F384" s="1" t="s">
         <v>38</v>
@@ -12554,13 +12542,13 @@
         <v>3</v>
       </c>
       <c r="D385" s="1" t="s">
-        <v>787</v>
+        <v>785</v>
       </c>
       <c r="E385" s="1" t="s">
-        <v>37</v>
+        <v>66</v>
       </c>
       <c r="F385" s="1" t="s">
-        <v>38</v>
+        <v>5</v>
       </c>
     </row>
     <row r="386" spans="1:6" x14ac:dyDescent="0.25">
@@ -12574,13 +12562,13 @@
         <v>3</v>
       </c>
       <c r="D386" s="1" t="s">
-        <v>787</v>
+        <v>785</v>
       </c>
       <c r="E386" s="1" t="s">
-        <v>66</v>
+        <v>98</v>
       </c>
       <c r="F386" s="1" t="s">
-        <v>5</v>
+        <v>38</v>
       </c>
     </row>
     <row r="387" spans="1:6" x14ac:dyDescent="0.25">
@@ -12594,10 +12582,10 @@
         <v>3</v>
       </c>
       <c r="D387" s="1" t="s">
-        <v>787</v>
+        <v>785</v>
       </c>
       <c r="E387" s="1" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="F387" s="1" t="s">
         <v>38</v>
@@ -12614,13 +12602,13 @@
         <v>3</v>
       </c>
       <c r="D388" s="1" t="s">
-        <v>787</v>
+        <v>785</v>
       </c>
       <c r="E388" s="1" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="F388" s="1" t="s">
-        <v>38</v>
+        <v>5</v>
       </c>
     </row>
     <row r="389" spans="1:6" x14ac:dyDescent="0.25">
@@ -12634,10 +12622,10 @@
         <v>3</v>
       </c>
       <c r="D389" s="1" t="s">
-        <v>787</v>
+        <v>785</v>
       </c>
       <c r="E389" s="1" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="F389" s="1" t="s">
         <v>5</v>
@@ -12654,13 +12642,13 @@
         <v>3</v>
       </c>
       <c r="D390" s="1" t="s">
-        <v>787</v>
+        <v>785</v>
       </c>
       <c r="E390" s="1" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="F390" s="1" t="s">
-        <v>5</v>
+        <v>38</v>
       </c>
     </row>
     <row r="391" spans="1:6" x14ac:dyDescent="0.25">
@@ -12674,13 +12662,13 @@
         <v>3</v>
       </c>
       <c r="D391" s="1" t="s">
-        <v>787</v>
+        <v>785</v>
       </c>
       <c r="E391" s="1" t="s">
-        <v>110</v>
+        <v>150</v>
       </c>
       <c r="F391" s="1" t="s">
-        <v>38</v>
+        <v>9</v>
       </c>
     </row>
     <row r="392" spans="1:6" x14ac:dyDescent="0.25">
@@ -12694,10 +12682,10 @@
         <v>3</v>
       </c>
       <c r="D392" s="1" t="s">
-        <v>787</v>
+        <v>785</v>
       </c>
       <c r="E392" s="1" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
       <c r="F392" s="1" t="s">
         <v>9</v>
@@ -12714,33 +12702,33 @@
         <v>3</v>
       </c>
       <c r="D393" s="1" t="s">
-        <v>787</v>
+        <v>826</v>
       </c>
       <c r="E393" s="1" t="s">
-        <v>153</v>
+        <v>4</v>
       </c>
       <c r="F393" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="394" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A394" s="1" t="s">
+        <v>827</v>
+      </c>
+      <c r="B394" s="1" t="s">
+        <v>828</v>
+      </c>
+      <c r="C394" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D394" s="1" t="s">
         <v>826</v>
       </c>
-      <c r="B394" s="1" t="s">
-        <v>827</v>
-      </c>
-      <c r="C394" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D394" s="1" t="s">
-        <v>828</v>
-      </c>
       <c r="E394" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F394" s="1" t="s">
-        <v>5</v>
+        <v>78</v>
       </c>
     </row>
     <row r="395" spans="1:6" x14ac:dyDescent="0.25">
@@ -12754,10 +12742,10 @@
         <v>3</v>
       </c>
       <c r="D395" s="1" t="s">
-        <v>828</v>
+        <v>826</v>
       </c>
       <c r="E395" s="1" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="F395" s="1" t="s">
         <v>78</v>
@@ -12774,10 +12762,10 @@
         <v>3</v>
       </c>
       <c r="D396" s="1" t="s">
-        <v>828</v>
+        <v>826</v>
       </c>
       <c r="E396" s="1" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="F396" s="1" t="s">
         <v>78</v>
@@ -12794,10 +12782,10 @@
         <v>3</v>
       </c>
       <c r="D397" s="1" t="s">
-        <v>828</v>
+        <v>826</v>
       </c>
       <c r="E397" s="1" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="F397" s="1" t="s">
         <v>78</v>
@@ -12814,13 +12802,13 @@
         <v>3</v>
       </c>
       <c r="D398" s="1" t="s">
-        <v>828</v>
+        <v>826</v>
       </c>
       <c r="E398" s="1" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="F398" s="1" t="s">
-        <v>78</v>
+        <v>5</v>
       </c>
     </row>
     <row r="399" spans="1:6" x14ac:dyDescent="0.25">
@@ -12834,10 +12822,10 @@
         <v>3</v>
       </c>
       <c r="D399" s="1" t="s">
-        <v>828</v>
+        <v>826</v>
       </c>
       <c r="E399" s="1" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="F399" s="1" t="s">
         <v>5</v>
@@ -12854,13 +12842,13 @@
         <v>3</v>
       </c>
       <c r="D400" s="1" t="s">
-        <v>828</v>
+        <v>826</v>
       </c>
       <c r="E400" s="1" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="F400" s="1" t="s">
-        <v>5</v>
+        <v>25</v>
       </c>
     </row>
     <row r="401" spans="1:6" x14ac:dyDescent="0.25">
@@ -12874,10 +12862,10 @@
         <v>3</v>
       </c>
       <c r="D401" s="1" t="s">
-        <v>828</v>
+        <v>826</v>
       </c>
       <c r="E401" s="1" t="s">
-        <v>55</v>
+        <v>31</v>
       </c>
       <c r="F401" s="1" t="s">
         <v>25</v>
@@ -12894,10 +12882,10 @@
         <v>3</v>
       </c>
       <c r="D402" s="1" t="s">
-        <v>828</v>
+        <v>826</v>
       </c>
       <c r="E402" s="1" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="F402" s="1" t="s">
         <v>25</v>
@@ -12914,10 +12902,10 @@
         <v>3</v>
       </c>
       <c r="D403" s="1" t="s">
-        <v>828</v>
+        <v>826</v>
       </c>
       <c r="E403" s="1" t="s">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="F403" s="1" t="s">
         <v>25</v>
@@ -12934,10 +12922,10 @@
         <v>3</v>
       </c>
       <c r="D404" s="1" t="s">
-        <v>828</v>
+        <v>826</v>
       </c>
       <c r="E404" s="1" t="s">
-        <v>34</v>
+        <v>63</v>
       </c>
       <c r="F404" s="1" t="s">
         <v>25</v>
@@ -12954,10 +12942,10 @@
         <v>3</v>
       </c>
       <c r="D405" s="1" t="s">
-        <v>828</v>
+        <v>826</v>
       </c>
       <c r="E405" s="1" t="s">
-        <v>37</v>
+        <v>66</v>
       </c>
       <c r="F405" s="1" t="s">
         <v>25</v>
@@ -12974,10 +12962,10 @@
         <v>3</v>
       </c>
       <c r="D406" s="1" t="s">
-        <v>828</v>
+        <v>826</v>
       </c>
       <c r="E406" s="1" t="s">
-        <v>66</v>
+        <v>98</v>
       </c>
       <c r="F406" s="1" t="s">
         <v>25</v>
@@ -12994,10 +12982,10 @@
         <v>3</v>
       </c>
       <c r="D407" s="1" t="s">
-        <v>828</v>
+        <v>826</v>
       </c>
       <c r="E407" s="1" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="F407" s="1" t="s">
         <v>25</v>
@@ -13014,10 +13002,10 @@
         <v>3</v>
       </c>
       <c r="D408" s="1" t="s">
-        <v>828</v>
+        <v>826</v>
       </c>
       <c r="E408" s="1" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="F408" s="1" t="s">
         <v>25</v>
@@ -13034,10 +13022,10 @@
         <v>3</v>
       </c>
       <c r="D409" s="1" t="s">
-        <v>828</v>
+        <v>826</v>
       </c>
       <c r="E409" s="1" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="F409" s="1" t="s">
         <v>25</v>
@@ -13054,10 +13042,10 @@
         <v>3</v>
       </c>
       <c r="D410" s="1" t="s">
-        <v>828</v>
+        <v>826</v>
       </c>
       <c r="E410" s="1" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="F410" s="1" t="s">
         <v>25</v>
@@ -13074,13 +13062,13 @@
         <v>3</v>
       </c>
       <c r="D411" s="1" t="s">
-        <v>828</v>
+        <v>826</v>
       </c>
       <c r="E411" s="1" t="s">
-        <v>110</v>
+        <v>150</v>
       </c>
       <c r="F411" s="1" t="s">
-        <v>25</v>
+        <v>5</v>
       </c>
     </row>
     <row r="412" spans="1:6" x14ac:dyDescent="0.25">
@@ -13094,13 +13082,13 @@
         <v>3</v>
       </c>
       <c r="D412" s="1" t="s">
-        <v>828</v>
+        <v>826</v>
       </c>
       <c r="E412" s="1" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
       <c r="F412" s="1" t="s">
-        <v>5</v>
+        <v>38</v>
       </c>
     </row>
     <row r="413" spans="1:6" x14ac:dyDescent="0.25">
@@ -13114,10 +13102,10 @@
         <v>3</v>
       </c>
       <c r="D413" s="1" t="s">
-        <v>828</v>
+        <v>826</v>
       </c>
       <c r="E413" s="1" t="s">
-        <v>153</v>
+        <v>197</v>
       </c>
       <c r="F413" s="1" t="s">
         <v>38</v>
@@ -13134,33 +13122,33 @@
         <v>3</v>
       </c>
       <c r="D414" s="1" t="s">
-        <v>828</v>
+        <v>869</v>
       </c>
       <c r="E414" s="1" t="s">
-        <v>197</v>
+        <v>4</v>
       </c>
       <c r="F414" s="1" t="s">
-        <v>38</v>
+        <v>154</v>
       </c>
     </row>
     <row r="415" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A415" s="1" t="s">
+        <v>870</v>
+      </c>
+      <c r="B415" s="1" t="s">
+        <v>871</v>
+      </c>
+      <c r="C415" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D415" s="1" t="s">
         <v>869</v>
       </c>
-      <c r="B415" s="1" t="s">
-        <v>870</v>
-      </c>
-      <c r="C415" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D415" s="1" t="s">
-        <v>871</v>
-      </c>
       <c r="E415" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F415" s="1" t="s">
-        <v>154</v>
+        <v>78</v>
       </c>
     </row>
     <row r="416" spans="1:6" x14ac:dyDescent="0.25">
@@ -13174,13 +13162,13 @@
         <v>3</v>
       </c>
       <c r="D416" s="1" t="s">
-        <v>871</v>
+        <v>869</v>
       </c>
       <c r="E416" s="1" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="F416" s="1" t="s">
-        <v>78</v>
+        <v>230</v>
       </c>
     </row>
     <row r="417" spans="1:6" x14ac:dyDescent="0.25">
@@ -13194,13 +13182,13 @@
         <v>3</v>
       </c>
       <c r="D417" s="1" t="s">
-        <v>871</v>
+        <v>869</v>
       </c>
       <c r="E417" s="1" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="F417" s="1" t="s">
-        <v>230</v>
+        <v>78</v>
       </c>
     </row>
     <row r="418" spans="1:6" x14ac:dyDescent="0.25">
@@ -13214,13 +13202,13 @@
         <v>3</v>
       </c>
       <c r="D418" s="1" t="s">
-        <v>871</v>
+        <v>869</v>
       </c>
       <c r="E418" s="1" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="F418" s="1" t="s">
-        <v>78</v>
+        <v>117</v>
       </c>
     </row>
     <row r="419" spans="1:6" x14ac:dyDescent="0.25">
@@ -13234,10 +13222,10 @@
         <v>3</v>
       </c>
       <c r="D419" s="1" t="s">
-        <v>871</v>
+        <v>869</v>
       </c>
       <c r="E419" s="1" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="F419" s="1" t="s">
         <v>117</v>
@@ -13254,13 +13242,13 @@
         <v>3</v>
       </c>
       <c r="D420" s="1" t="s">
-        <v>871</v>
+        <v>869</v>
       </c>
       <c r="E420" s="1" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="F420" s="1" t="s">
-        <v>117</v>
+        <v>78</v>
       </c>
     </row>
     <row r="421" spans="1:6" x14ac:dyDescent="0.25">
@@ -13274,30 +13262,30 @@
         <v>3</v>
       </c>
       <c r="D421" s="1" t="s">
-        <v>871</v>
+        <v>884</v>
       </c>
       <c r="E421" s="1" t="s">
-        <v>24</v>
+        <v>4</v>
       </c>
       <c r="F421" s="1" t="s">
-        <v>78</v>
+        <v>5</v>
       </c>
     </row>
     <row r="422" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A422" s="1" t="s">
+        <v>885</v>
+      </c>
+      <c r="B422" s="1" t="s">
+        <v>886</v>
+      </c>
+      <c r="C422" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D422" s="1" t="s">
         <v>884</v>
       </c>
-      <c r="B422" s="1" t="s">
-        <v>885</v>
-      </c>
-      <c r="C422" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D422" s="1" t="s">
-        <v>886</v>
-      </c>
       <c r="E422" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F422" s="1" t="s">
         <v>5</v>
@@ -13314,10 +13302,10 @@
         <v>3</v>
       </c>
       <c r="D423" s="1" t="s">
-        <v>886</v>
+        <v>884</v>
       </c>
       <c r="E423" s="1" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="F423" s="1" t="s">
         <v>5</v>
@@ -13334,33 +13322,33 @@
         <v>3</v>
       </c>
       <c r="D424" s="1" t="s">
-        <v>886</v>
+        <v>884</v>
       </c>
       <c r="E424" s="1" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="F424" s="1" t="s">
-        <v>5</v>
+        <v>891</v>
       </c>
     </row>
     <row r="425" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A425" s="1" t="s">
-        <v>891</v>
+        <v>892</v>
       </c>
       <c r="B425" s="1" t="s">
-        <v>892</v>
+        <v>893</v>
       </c>
       <c r="C425" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D425" s="1" t="s">
-        <v>886</v>
+        <v>884</v>
       </c>
       <c r="E425" s="1" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="F425" s="1" t="s">
-        <v>893</v>
+        <v>9</v>
       </c>
     </row>
     <row r="426" spans="1:6" x14ac:dyDescent="0.25">
@@ -13374,13 +13362,13 @@
         <v>3</v>
       </c>
       <c r="D426" s="1" t="s">
-        <v>886</v>
+        <v>884</v>
       </c>
       <c r="E426" s="1" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="F426" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="427" spans="1:6" x14ac:dyDescent="0.25">
@@ -13394,10 +13382,10 @@
         <v>3</v>
       </c>
       <c r="D427" s="1" t="s">
-        <v>886</v>
+        <v>884</v>
       </c>
       <c r="E427" s="1" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="F427" s="1" t="s">
         <v>5</v>
@@ -13414,13 +13402,13 @@
         <v>3</v>
       </c>
       <c r="D428" s="1" t="s">
-        <v>886</v>
+        <v>884</v>
       </c>
       <c r="E428" s="1" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="F428" s="1" t="s">
-        <v>5</v>
+        <v>78</v>
       </c>
     </row>
     <row r="429" spans="1:6" x14ac:dyDescent="0.25">
@@ -13434,13 +13422,13 @@
         <v>3</v>
       </c>
       <c r="D429" s="1" t="s">
-        <v>886</v>
+        <v>884</v>
       </c>
       <c r="E429" s="1" t="s">
-        <v>55</v>
+        <v>31</v>
       </c>
       <c r="F429" s="1" t="s">
-        <v>78</v>
+        <v>25</v>
       </c>
     </row>
     <row r="430" spans="1:6" x14ac:dyDescent="0.25">
@@ -13454,13 +13442,13 @@
         <v>3</v>
       </c>
       <c r="D430" s="1" t="s">
-        <v>886</v>
+        <v>884</v>
       </c>
       <c r="E430" s="1" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="F430" s="1" t="s">
-        <v>25</v>
+        <v>5</v>
       </c>
     </row>
     <row r="431" spans="1:6" x14ac:dyDescent="0.25">
@@ -13474,10 +13462,10 @@
         <v>3</v>
       </c>
       <c r="D431" s="1" t="s">
-        <v>886</v>
+        <v>884</v>
       </c>
       <c r="E431" s="1" t="s">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="F431" s="1" t="s">
         <v>5</v>
@@ -13494,13 +13482,13 @@
         <v>3</v>
       </c>
       <c r="D432" s="1" t="s">
-        <v>886</v>
+        <v>884</v>
       </c>
       <c r="E432" s="1" t="s">
-        <v>34</v>
+        <v>63</v>
       </c>
       <c r="F432" s="1" t="s">
-        <v>5</v>
+        <v>25</v>
       </c>
     </row>
     <row r="433" spans="1:6" x14ac:dyDescent="0.25">
@@ -13514,13 +13502,13 @@
         <v>3</v>
       </c>
       <c r="D433" s="1" t="s">
-        <v>886</v>
+        <v>884</v>
       </c>
       <c r="E433" s="1" t="s">
-        <v>37</v>
+        <v>66</v>
       </c>
       <c r="F433" s="1" t="s">
-        <v>25</v>
+        <v>5</v>
       </c>
     </row>
     <row r="434" spans="1:6" x14ac:dyDescent="0.25">
@@ -13534,10 +13522,10 @@
         <v>3</v>
       </c>
       <c r="D434" s="1" t="s">
-        <v>886</v>
+        <v>884</v>
       </c>
       <c r="E434" s="1" t="s">
-        <v>66</v>
+        <v>98</v>
       </c>
       <c r="F434" s="1" t="s">
         <v>5</v>
@@ -13554,10 +13542,10 @@
         <v>3</v>
       </c>
       <c r="D435" s="1" t="s">
-        <v>886</v>
+        <v>884</v>
       </c>
       <c r="E435" s="1" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="F435" s="1" t="s">
         <v>5</v>
@@ -13574,10 +13562,10 @@
         <v>3</v>
       </c>
       <c r="D436" s="1" t="s">
-        <v>886</v>
+        <v>884</v>
       </c>
       <c r="E436" s="1" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="F436" s="1" t="s">
         <v>5</v>
@@ -13594,10 +13582,10 @@
         <v>3</v>
       </c>
       <c r="D437" s="1" t="s">
-        <v>886</v>
+        <v>918</v>
       </c>
       <c r="E437" s="1" t="s">
-        <v>104</v>
+        <v>4</v>
       </c>
       <c r="F437" s="1" t="s">
         <v>5</v>
@@ -13605,19 +13593,19 @@
     </row>
     <row r="438" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A438" s="1" t="s">
+        <v>919</v>
+      </c>
+      <c r="B438" s="1" t="s">
+        <v>920</v>
+      </c>
+      <c r="C438" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D438" s="1" t="s">
         <v>918</v>
       </c>
-      <c r="B438" s="1" t="s">
-        <v>919</v>
-      </c>
-      <c r="C438" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D438" s="1" t="s">
-        <v>920</v>
-      </c>
       <c r="E438" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F438" s="1" t="s">
         <v>5</v>
@@ -13634,10 +13622,10 @@
         <v>3</v>
       </c>
       <c r="D439" s="1" t="s">
-        <v>920</v>
+        <v>918</v>
       </c>
       <c r="E439" s="1" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="F439" s="1" t="s">
         <v>5</v>
@@ -13654,10 +13642,10 @@
         <v>3</v>
       </c>
       <c r="D440" s="1" t="s">
-        <v>920</v>
+        <v>918</v>
       </c>
       <c r="E440" s="1" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="F440" s="1" t="s">
         <v>5</v>
@@ -13674,13 +13662,13 @@
         <v>3</v>
       </c>
       <c r="D441" s="1" t="s">
-        <v>920</v>
+        <v>918</v>
       </c>
       <c r="E441" s="1" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="F441" s="1" t="s">
-        <v>5</v>
+        <v>38</v>
       </c>
     </row>
     <row r="442" spans="1:6" x14ac:dyDescent="0.25">
@@ -13694,10 +13682,10 @@
         <v>3</v>
       </c>
       <c r="D442" s="1" t="s">
-        <v>920</v>
+        <v>918</v>
       </c>
       <c r="E442" s="1" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="F442" s="1" t="s">
         <v>38</v>
@@ -13714,13 +13702,13 @@
         <v>3</v>
       </c>
       <c r="D443" s="1" t="s">
-        <v>920</v>
+        <v>918</v>
       </c>
       <c r="E443" s="1" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="F443" s="1" t="s">
-        <v>38</v>
+        <v>78</v>
       </c>
     </row>
     <row r="444" spans="1:6" x14ac:dyDescent="0.25">
@@ -13734,13 +13722,13 @@
         <v>3</v>
       </c>
       <c r="D444" s="1" t="s">
-        <v>920</v>
+        <v>918</v>
       </c>
       <c r="E444" s="1" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="F444" s="1" t="s">
-        <v>78</v>
+        <v>117</v>
       </c>
     </row>
     <row r="445" spans="1:6" x14ac:dyDescent="0.25">
@@ -13754,13 +13742,13 @@
         <v>3</v>
       </c>
       <c r="D445" s="1" t="s">
-        <v>920</v>
+        <v>918</v>
       </c>
       <c r="E445" s="1" t="s">
-        <v>55</v>
+        <v>31</v>
       </c>
       <c r="F445" s="1" t="s">
-        <v>117</v>
+        <v>25</v>
       </c>
     </row>
     <row r="446" spans="1:6" x14ac:dyDescent="0.25">
@@ -13774,13 +13762,13 @@
         <v>3</v>
       </c>
       <c r="D446" s="1" t="s">
-        <v>920</v>
+        <v>918</v>
       </c>
       <c r="E446" s="1" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="F446" s="1" t="s">
-        <v>25</v>
+        <v>5</v>
       </c>
     </row>
     <row r="447" spans="1:6" x14ac:dyDescent="0.25">
@@ -13794,13 +13782,13 @@
         <v>3</v>
       </c>
       <c r="D447" s="1" t="s">
-        <v>920</v>
+        <v>918</v>
       </c>
       <c r="E447" s="1" t="s">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="F447" s="1" t="s">
-        <v>5</v>
+        <v>38</v>
       </c>
     </row>
     <row r="448" spans="1:6" x14ac:dyDescent="0.25">
@@ -13814,10 +13802,10 @@
         <v>3</v>
       </c>
       <c r="D448" s="1" t="s">
-        <v>920</v>
+        <v>918</v>
       </c>
       <c r="E448" s="1" t="s">
-        <v>34</v>
+        <v>63</v>
       </c>
       <c r="F448" s="1" t="s">
         <v>38</v>
@@ -13834,10 +13822,10 @@
         <v>3</v>
       </c>
       <c r="D449" s="1" t="s">
-        <v>920</v>
+        <v>918</v>
       </c>
       <c r="E449" s="1" t="s">
-        <v>37</v>
+        <v>66</v>
       </c>
       <c r="F449" s="1" t="s">
         <v>38</v>
@@ -13854,13 +13842,13 @@
         <v>3</v>
       </c>
       <c r="D450" s="1" t="s">
-        <v>920</v>
+        <v>918</v>
       </c>
       <c r="E450" s="1" t="s">
-        <v>66</v>
+        <v>98</v>
       </c>
       <c r="F450" s="1" t="s">
-        <v>38</v>
+        <v>9</v>
       </c>
     </row>
     <row r="451" spans="1:6" x14ac:dyDescent="0.25">
@@ -13874,13 +13862,13 @@
         <v>3</v>
       </c>
       <c r="D451" s="1" t="s">
-        <v>920</v>
+        <v>918</v>
       </c>
       <c r="E451" s="1" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="F451" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="452" spans="1:6" x14ac:dyDescent="0.25">
@@ -13894,30 +13882,30 @@
         <v>3</v>
       </c>
       <c r="D452" s="1" t="s">
-        <v>920</v>
+        <v>949</v>
       </c>
       <c r="E452" s="1" t="s">
-        <v>101</v>
+        <v>4</v>
       </c>
       <c r="F452" s="1" t="s">
-        <v>5</v>
+        <v>78</v>
       </c>
     </row>
     <row r="453" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A453" s="1" t="s">
+        <v>950</v>
+      </c>
+      <c r="B453" s="1" t="s">
+        <v>951</v>
+      </c>
+      <c r="C453" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D453" s="1" t="s">
         <v>949</v>
       </c>
-      <c r="B453" s="1" t="s">
-        <v>950</v>
-      </c>
-      <c r="C453" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D453" s="1" t="s">
-        <v>951</v>
-      </c>
       <c r="E453" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F453" s="1" t="s">
         <v>78</v>
@@ -13934,10 +13922,10 @@
         <v>3</v>
       </c>
       <c r="D454" s="1" t="s">
-        <v>951</v>
+        <v>949</v>
       </c>
       <c r="E454" s="1" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="F454" s="1" t="s">
         <v>78</v>
@@ -13954,10 +13942,10 @@
         <v>3</v>
       </c>
       <c r="D455" s="1" t="s">
-        <v>951</v>
+        <v>949</v>
       </c>
       <c r="E455" s="1" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="F455" s="1" t="s">
         <v>78</v>
@@ -13974,10 +13962,10 @@
         <v>3</v>
       </c>
       <c r="D456" s="1" t="s">
-        <v>951</v>
+        <v>949</v>
       </c>
       <c r="E456" s="1" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="F456" s="1" t="s">
         <v>78</v>
@@ -13994,10 +13982,10 @@
         <v>3</v>
       </c>
       <c r="D457" s="1" t="s">
-        <v>951</v>
+        <v>949</v>
       </c>
       <c r="E457" s="1" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="F457" s="1" t="s">
         <v>78</v>
@@ -14014,13 +14002,13 @@
         <v>3</v>
       </c>
       <c r="D458" s="1" t="s">
-        <v>951</v>
+        <v>949</v>
       </c>
       <c r="E458" s="1" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="F458" s="1" t="s">
-        <v>78</v>
+        <v>154</v>
       </c>
     </row>
     <row r="459" spans="1:6" x14ac:dyDescent="0.25">
@@ -14034,10 +14022,10 @@
         <v>3</v>
       </c>
       <c r="D459" s="1" t="s">
-        <v>951</v>
+        <v>949</v>
       </c>
       <c r="E459" s="1" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="F459" s="1" t="s">
         <v>154</v>
@@ -14054,13 +14042,13 @@
         <v>3</v>
       </c>
       <c r="D460" s="1" t="s">
-        <v>951</v>
+        <v>949</v>
       </c>
       <c r="E460" s="1" t="s">
-        <v>55</v>
+        <v>31</v>
       </c>
       <c r="F460" s="1" t="s">
-        <v>154</v>
+        <v>25</v>
       </c>
     </row>
     <row r="461" spans="1:6" x14ac:dyDescent="0.25">
@@ -14074,10 +14062,10 @@
         <v>3</v>
       </c>
       <c r="D461" s="1" t="s">
-        <v>951</v>
+        <v>949</v>
       </c>
       <c r="E461" s="1" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="F461" s="1" t="s">
         <v>25</v>
@@ -14094,13 +14082,13 @@
         <v>3</v>
       </c>
       <c r="D462" s="1" t="s">
-        <v>951</v>
+        <v>949</v>
       </c>
       <c r="E462" s="1" t="s">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="F462" s="1" t="s">
-        <v>25</v>
+        <v>78</v>
       </c>
     </row>
     <row r="463" spans="1:6" x14ac:dyDescent="0.25">
@@ -14114,10 +14102,10 @@
         <v>3</v>
       </c>
       <c r="D463" s="1" t="s">
-        <v>951</v>
+        <v>949</v>
       </c>
       <c r="E463" s="1" t="s">
-        <v>34</v>
+        <v>63</v>
       </c>
       <c r="F463" s="1" t="s">
         <v>78</v>
@@ -14134,13 +14122,13 @@
         <v>3</v>
       </c>
       <c r="D464" s="1" t="s">
-        <v>951</v>
+        <v>949</v>
       </c>
       <c r="E464" s="1" t="s">
-        <v>37</v>
+        <v>66</v>
       </c>
       <c r="F464" s="1" t="s">
-        <v>78</v>
+        <v>5</v>
       </c>
     </row>
     <row r="465" spans="1:6" x14ac:dyDescent="0.25">
@@ -14154,10 +14142,10 @@
         <v>3</v>
       </c>
       <c r="D465" s="1" t="s">
-        <v>951</v>
+        <v>949</v>
       </c>
       <c r="E465" s="1" t="s">
-        <v>66</v>
+        <v>98</v>
       </c>
       <c r="F465" s="1" t="s">
         <v>5</v>
@@ -14174,10 +14162,10 @@
         <v>3</v>
       </c>
       <c r="D466" s="1" t="s">
-        <v>951</v>
+        <v>949</v>
       </c>
       <c r="E466" s="1" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="F466" s="1" t="s">
         <v>5</v>
@@ -14194,33 +14182,33 @@
         <v>3</v>
       </c>
       <c r="D467" s="1" t="s">
-        <v>951</v>
+        <v>980</v>
       </c>
       <c r="E467" s="1" t="s">
-        <v>101</v>
+        <v>4</v>
       </c>
       <c r="F467" s="1" t="s">
-        <v>5</v>
+        <v>78</v>
       </c>
     </row>
     <row r="468" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A468" s="1" t="s">
+        <v>981</v>
+      </c>
+      <c r="B468" s="1" t="s">
+        <v>982</v>
+      </c>
+      <c r="C468" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D468" s="1" t="s">
         <v>980</v>
       </c>
-      <c r="B468" s="1" t="s">
-        <v>981</v>
-      </c>
-      <c r="C468" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D468" s="1" t="s">
-        <v>982</v>
-      </c>
       <c r="E468" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F468" s="1" t="s">
-        <v>78</v>
+        <v>5</v>
       </c>
     </row>
     <row r="469" spans="1:6" x14ac:dyDescent="0.25">
@@ -14234,33 +14222,33 @@
         <v>3</v>
       </c>
       <c r="D469" s="1" t="s">
-        <v>982</v>
+        <v>980</v>
       </c>
       <c r="E469" s="1" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="F469" s="1" t="s">
-        <v>5</v>
+        <v>985</v>
       </c>
     </row>
     <row r="470" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A470" s="1" t="s">
+        <v>986</v>
+      </c>
+      <c r="B470" s="1" t="s">
+        <v>987</v>
+      </c>
+      <c r="C470" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D470" s="1" t="s">
+        <v>980</v>
+      </c>
+      <c r="E470" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="F470" s="1" t="s">
         <v>985</v>
-      </c>
-      <c r="B470" s="1" t="s">
-        <v>986</v>
-      </c>
-      <c r="C470" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D470" s="1" t="s">
-        <v>982</v>
-      </c>
-      <c r="E470" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="F470" s="1" t="s">
-        <v>987</v>
       </c>
     </row>
     <row r="471" spans="1:6" x14ac:dyDescent="0.25">
@@ -14274,13 +14262,13 @@
         <v>3</v>
       </c>
       <c r="D471" s="1" t="s">
-        <v>982</v>
+        <v>980</v>
       </c>
       <c r="E471" s="1" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="F471" s="1" t="s">
-        <v>987</v>
+        <v>5</v>
       </c>
     </row>
     <row r="472" spans="1:6" x14ac:dyDescent="0.25">
@@ -14294,10 +14282,10 @@
         <v>3</v>
       </c>
       <c r="D472" s="1" t="s">
-        <v>982</v>
+        <v>980</v>
       </c>
       <c r="E472" s="1" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="F472" s="1" t="s">
         <v>5</v>
@@ -14314,10 +14302,10 @@
         <v>3</v>
       </c>
       <c r="D473" s="1" t="s">
-        <v>982</v>
+        <v>980</v>
       </c>
       <c r="E473" s="1" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="F473" s="1" t="s">
         <v>5</v>
@@ -14334,10 +14322,10 @@
         <v>3</v>
       </c>
       <c r="D474" s="1" t="s">
-        <v>982</v>
+        <v>980</v>
       </c>
       <c r="E474" s="1" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="F474" s="1" t="s">
         <v>5</v>
@@ -14354,10 +14342,10 @@
         <v>3</v>
       </c>
       <c r="D475" s="1" t="s">
-        <v>982</v>
+        <v>980</v>
       </c>
       <c r="E475" s="1" t="s">
-        <v>55</v>
+        <v>31</v>
       </c>
       <c r="F475" s="1" t="s">
         <v>5</v>
@@ -14374,10 +14362,10 @@
         <v>3</v>
       </c>
       <c r="D476" s="1" t="s">
-        <v>982</v>
+        <v>980</v>
       </c>
       <c r="E476" s="1" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="F476" s="1" t="s">
         <v>5</v>
@@ -14394,10 +14382,10 @@
         <v>3</v>
       </c>
       <c r="D477" s="1" t="s">
-        <v>982</v>
+        <v>980</v>
       </c>
       <c r="E477" s="1" t="s">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="F477" s="1" t="s">
         <v>5</v>
@@ -14414,10 +14402,10 @@
         <v>3</v>
       </c>
       <c r="D478" s="1" t="s">
-        <v>982</v>
+        <v>980</v>
       </c>
       <c r="E478" s="1" t="s">
-        <v>34</v>
+        <v>63</v>
       </c>
       <c r="F478" s="1" t="s">
         <v>5</v>
@@ -14434,10 +14422,10 @@
         <v>3</v>
       </c>
       <c r="D479" s="1" t="s">
-        <v>982</v>
+        <v>980</v>
       </c>
       <c r="E479" s="1" t="s">
-        <v>37</v>
+        <v>66</v>
       </c>
       <c r="F479" s="1" t="s">
         <v>5</v>
@@ -14454,10 +14442,10 @@
         <v>3</v>
       </c>
       <c r="D480" s="1" t="s">
-        <v>982</v>
+        <v>980</v>
       </c>
       <c r="E480" s="1" t="s">
-        <v>66</v>
+        <v>98</v>
       </c>
       <c r="F480" s="1" t="s">
         <v>5</v>
@@ -14474,10 +14462,10 @@
         <v>3</v>
       </c>
       <c r="D481" s="1" t="s">
-        <v>982</v>
+        <v>980</v>
       </c>
       <c r="E481" s="1" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="F481" s="1" t="s">
         <v>5</v>
@@ -14494,10 +14482,10 @@
         <v>3</v>
       </c>
       <c r="D482" s="1" t="s">
-        <v>982</v>
+        <v>980</v>
       </c>
       <c r="E482" s="1" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="F482" s="1" t="s">
         <v>5</v>
@@ -14514,33 +14502,33 @@
         <v>3</v>
       </c>
       <c r="D483" s="1" t="s">
-        <v>982</v>
+        <v>1014</v>
       </c>
       <c r="E483" s="1" t="s">
-        <v>104</v>
+        <v>4</v>
       </c>
       <c r="F483" s="1" t="s">
-        <v>5</v>
+        <v>25</v>
       </c>
     </row>
     <row r="484" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A484" s="1" t="s">
+        <v>1015</v>
+      </c>
+      <c r="B484" s="1" t="s">
+        <v>1016</v>
+      </c>
+      <c r="C484" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D484" s="1" t="s">
         <v>1014</v>
       </c>
-      <c r="B484" s="1" t="s">
-        <v>1015</v>
-      </c>
-      <c r="C484" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D484" s="1" t="s">
-        <v>1016</v>
-      </c>
       <c r="E484" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F484" s="1" t="s">
-        <v>25</v>
+        <v>5</v>
       </c>
     </row>
     <row r="485" spans="1:6" x14ac:dyDescent="0.25">
@@ -14554,10 +14542,10 @@
         <v>3</v>
       </c>
       <c r="D485" s="1" t="s">
-        <v>1016</v>
+        <v>1014</v>
       </c>
       <c r="E485" s="1" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="F485" s="1" t="s">
         <v>5</v>
@@ -14574,10 +14562,10 @@
         <v>3</v>
       </c>
       <c r="D486" s="1" t="s">
-        <v>1016</v>
+        <v>1014</v>
       </c>
       <c r="E486" s="1" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="F486" s="1" t="s">
         <v>5</v>
@@ -14594,13 +14582,13 @@
         <v>3</v>
       </c>
       <c r="D487" s="1" t="s">
-        <v>1016</v>
+        <v>1014</v>
       </c>
       <c r="E487" s="1" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="F487" s="1" t="s">
-        <v>5</v>
+        <v>154</v>
       </c>
     </row>
     <row r="488" spans="1:6" x14ac:dyDescent="0.25">
@@ -14614,10 +14602,10 @@
         <v>3</v>
       </c>
       <c r="D488" s="1" t="s">
-        <v>1016</v>
+        <v>1014</v>
       </c>
       <c r="E488" s="1" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="F488" s="1" t="s">
         <v>154</v>
@@ -14634,13 +14622,13 @@
         <v>3</v>
       </c>
       <c r="D489" s="1" t="s">
-        <v>1016</v>
+        <v>1014</v>
       </c>
       <c r="E489" s="1" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="F489" s="1" t="s">
-        <v>154</v>
+        <v>5</v>
       </c>
     </row>
     <row r="490" spans="1:6" x14ac:dyDescent="0.25">
@@ -14654,10 +14642,10 @@
         <v>3</v>
       </c>
       <c r="D490" s="1" t="s">
-        <v>1016</v>
+        <v>1014</v>
       </c>
       <c r="E490" s="1" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="F490" s="1" t="s">
         <v>5</v>
@@ -14674,10 +14662,10 @@
         <v>3</v>
       </c>
       <c r="D491" s="1" t="s">
-        <v>1016</v>
+        <v>1014</v>
       </c>
       <c r="E491" s="1" t="s">
-        <v>55</v>
+        <v>31</v>
       </c>
       <c r="F491" s="1" t="s">
         <v>5</v>
@@ -14694,33 +14682,33 @@
         <v>3</v>
       </c>
       <c r="D492" s="1" t="s">
-        <v>1016</v>
+        <v>1014</v>
       </c>
       <c r="E492" s="1" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="F492" s="1" t="s">
-        <v>5</v>
+        <v>1033</v>
       </c>
     </row>
     <row r="493" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A493" s="1" t="s">
-        <v>1033</v>
+        <v>1034</v>
       </c>
       <c r="B493" s="1" t="s">
-        <v>1034</v>
+        <v>1035</v>
       </c>
       <c r="C493" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D493" s="1" t="s">
-        <v>1016</v>
+        <v>1014</v>
       </c>
       <c r="E493" s="1" t="s">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="F493" s="1" t="s">
-        <v>1035</v>
+        <v>5</v>
       </c>
     </row>
     <row r="494" spans="1:6" x14ac:dyDescent="0.25">
@@ -14734,10 +14722,10 @@
         <v>3</v>
       </c>
       <c r="D494" s="1" t="s">
-        <v>1016</v>
+        <v>1014</v>
       </c>
       <c r="E494" s="1" t="s">
-        <v>34</v>
+        <v>63</v>
       </c>
       <c r="F494" s="1" t="s">
         <v>5</v>
@@ -14754,10 +14742,10 @@
         <v>3</v>
       </c>
       <c r="D495" s="1" t="s">
-        <v>1016</v>
+        <v>1014</v>
       </c>
       <c r="E495" s="1" t="s">
-        <v>37</v>
+        <v>66</v>
       </c>
       <c r="F495" s="1" t="s">
         <v>5</v>
@@ -14774,10 +14762,10 @@
         <v>3</v>
       </c>
       <c r="D496" s="1" t="s">
-        <v>1016</v>
+        <v>1014</v>
       </c>
       <c r="E496" s="1" t="s">
-        <v>66</v>
+        <v>98</v>
       </c>
       <c r="F496" s="1" t="s">
         <v>5</v>
@@ -14794,10 +14782,10 @@
         <v>3</v>
       </c>
       <c r="D497" s="1" t="s">
-        <v>1016</v>
+        <v>1014</v>
       </c>
       <c r="E497" s="1" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="F497" s="1" t="s">
         <v>5</v>
@@ -14814,10 +14802,10 @@
         <v>3</v>
       </c>
       <c r="D498" s="1" t="s">
-        <v>1016</v>
+        <v>1014</v>
       </c>
       <c r="E498" s="1" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="F498" s="1" t="s">
         <v>5</v>
@@ -14834,13 +14822,13 @@
         <v>3</v>
       </c>
       <c r="D499" s="1" t="s">
-        <v>1016</v>
+        <v>1014</v>
       </c>
       <c r="E499" s="1" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="F499" s="1" t="s">
-        <v>5</v>
+        <v>25</v>
       </c>
     </row>
     <row r="500" spans="1:6" x14ac:dyDescent="0.25">
@@ -14854,10 +14842,10 @@
         <v>3</v>
       </c>
       <c r="D500" s="1" t="s">
-        <v>1016</v>
+        <v>1014</v>
       </c>
       <c r="E500" s="1" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="F500" s="1" t="s">
         <v>25</v>
@@ -14874,30 +14862,30 @@
         <v>3</v>
       </c>
       <c r="D501" s="1" t="s">
-        <v>1016</v>
+        <v>1052</v>
       </c>
       <c r="E501" s="1" t="s">
-        <v>110</v>
+        <v>4</v>
       </c>
       <c r="F501" s="1" t="s">
-        <v>25</v>
+        <v>5</v>
       </c>
     </row>
     <row r="502" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A502" s="1" t="s">
+        <v>1053</v>
+      </c>
+      <c r="B502" s="1" t="s">
+        <v>1054</v>
+      </c>
+      <c r="C502" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D502" s="1" t="s">
         <v>1052</v>
       </c>
-      <c r="B502" s="1" t="s">
-        <v>1053</v>
-      </c>
-      <c r="C502" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D502" s="1" t="s">
-        <v>1054</v>
-      </c>
       <c r="E502" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F502" s="1" t="s">
         <v>5</v>
@@ -14914,10 +14902,10 @@
         <v>3</v>
       </c>
       <c r="D503" s="1" t="s">
-        <v>1054</v>
+        <v>1052</v>
       </c>
       <c r="E503" s="1" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="F503" s="1" t="s">
         <v>5</v>
@@ -14934,10 +14922,10 @@
         <v>3</v>
       </c>
       <c r="D504" s="1" t="s">
-        <v>1054</v>
+        <v>1052</v>
       </c>
       <c r="E504" s="1" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="F504" s="1" t="s">
         <v>5</v>
@@ -14954,10 +14942,10 @@
         <v>3</v>
       </c>
       <c r="D505" s="1" t="s">
-        <v>1054</v>
+        <v>1052</v>
       </c>
       <c r="E505" s="1" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="F505" s="1" t="s">
         <v>5</v>
@@ -14974,10 +14962,10 @@
         <v>3</v>
       </c>
       <c r="D506" s="1" t="s">
-        <v>1054</v>
+        <v>1052</v>
       </c>
       <c r="E506" s="1" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="F506" s="1" t="s">
         <v>5</v>
@@ -14994,10 +14982,10 @@
         <v>3</v>
       </c>
       <c r="D507" s="1" t="s">
-        <v>1054</v>
+        <v>1052</v>
       </c>
       <c r="E507" s="1" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="F507" s="1" t="s">
         <v>5</v>
@@ -15014,10 +15002,10 @@
         <v>3</v>
       </c>
       <c r="D508" s="1" t="s">
-        <v>1054</v>
+        <v>1052</v>
       </c>
       <c r="E508" s="1" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="F508" s="1" t="s">
         <v>5</v>
@@ -15034,10 +15022,10 @@
         <v>3</v>
       </c>
       <c r="D509" s="1" t="s">
-        <v>1054</v>
+        <v>1052</v>
       </c>
       <c r="E509" s="1" t="s">
-        <v>55</v>
+        <v>31</v>
       </c>
       <c r="F509" s="1" t="s">
         <v>5</v>
@@ -15054,10 +15042,10 @@
         <v>3</v>
       </c>
       <c r="D510" s="1" t="s">
-        <v>1054</v>
+        <v>1052</v>
       </c>
       <c r="E510" s="1" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="F510" s="1" t="s">
         <v>5</v>
@@ -15074,10 +15062,10 @@
         <v>3</v>
       </c>
       <c r="D511" s="1" t="s">
-        <v>1054</v>
+        <v>1052</v>
       </c>
       <c r="E511" s="1" t="s">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="F511" s="1" t="s">
         <v>5</v>
@@ -15094,33 +15082,33 @@
         <v>3</v>
       </c>
       <c r="D512" s="1" t="s">
-        <v>1054</v>
+        <v>1052</v>
       </c>
       <c r="E512" s="1" t="s">
-        <v>34</v>
+        <v>63</v>
       </c>
       <c r="F512" s="1" t="s">
-        <v>5</v>
+        <v>1075</v>
       </c>
     </row>
     <row r="513" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A513" s="1" t="s">
-        <v>1075</v>
+        <v>1076</v>
       </c>
       <c r="B513" s="1" t="s">
-        <v>1076</v>
+        <v>1077</v>
       </c>
       <c r="C513" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D513" s="1" t="s">
-        <v>1054</v>
+        <v>1052</v>
       </c>
       <c r="E513" s="1" t="s">
-        <v>37</v>
+        <v>66</v>
       </c>
       <c r="F513" s="1" t="s">
-        <v>1077</v>
+        <v>5</v>
       </c>
     </row>
     <row r="514" spans="1:6" x14ac:dyDescent="0.25">
@@ -15134,10 +15122,10 @@
         <v>3</v>
       </c>
       <c r="D514" s="1" t="s">
-        <v>1054</v>
+        <v>1052</v>
       </c>
       <c r="E514" s="1" t="s">
-        <v>66</v>
+        <v>98</v>
       </c>
       <c r="F514" s="1" t="s">
         <v>5</v>
@@ -15154,10 +15142,10 @@
         <v>3</v>
       </c>
       <c r="D515" s="1" t="s">
-        <v>1054</v>
+        <v>1052</v>
       </c>
       <c r="E515" s="1" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="F515" s="1" t="s">
         <v>5</v>
@@ -15174,33 +15162,33 @@
         <v>3</v>
       </c>
       <c r="D516" s="1" t="s">
-        <v>1054</v>
+        <v>1084</v>
       </c>
       <c r="E516" s="1" t="s">
-        <v>101</v>
+        <v>4</v>
       </c>
       <c r="F516" s="1" t="s">
-        <v>5</v>
+        <v>78</v>
       </c>
     </row>
     <row r="517" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A517" s="1" t="s">
+        <v>1085</v>
+      </c>
+      <c r="B517" s="1" t="s">
+        <v>1086</v>
+      </c>
+      <c r="C517" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D517" s="1" t="s">
         <v>1084</v>
-      </c>
-      <c r="B517" s="1" t="s">
-        <v>1085</v>
-      </c>
-      <c r="C517" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D517" s="1" t="s">
-        <v>1086</v>
       </c>
       <c r="E517" s="1" t="s">
         <v>4</v>
       </c>
       <c r="F517" s="1" t="s">
-        <v>78</v>
+        <v>25</v>
       </c>
     </row>
     <row r="518" spans="1:6" x14ac:dyDescent="0.25">
@@ -15214,13 +15202,13 @@
         <v>3</v>
       </c>
       <c r="D518" s="1" t="s">
-        <v>1086</v>
+        <v>1084</v>
       </c>
       <c r="E518" s="1" t="s">
         <v>4</v>
       </c>
       <c r="F518" s="1" t="s">
-        <v>25</v>
+        <v>5</v>
       </c>
     </row>
     <row r="519" spans="1:6" x14ac:dyDescent="0.25">
@@ -15234,13 +15222,13 @@
         <v>3</v>
       </c>
       <c r="D519" s="1" t="s">
-        <v>1086</v>
+        <v>1084</v>
       </c>
       <c r="E519" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F519" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="520" spans="1:6" x14ac:dyDescent="0.25">
@@ -15254,13 +15242,13 @@
         <v>3</v>
       </c>
       <c r="D520" s="1" t="s">
-        <v>1086</v>
+        <v>1084</v>
       </c>
       <c r="E520" s="1" t="s">
         <v>8</v>
       </c>
       <c r="F520" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="521" spans="1:6" x14ac:dyDescent="0.25">
@@ -15274,7 +15262,7 @@
         <v>3</v>
       </c>
       <c r="D521" s="1" t="s">
-        <v>1086</v>
+        <v>1084</v>
       </c>
       <c r="E521" s="1" t="s">
         <v>8</v>
@@ -15294,10 +15282,10 @@
         <v>3</v>
       </c>
       <c r="D522" s="1" t="s">
-        <v>1086</v>
+        <v>1084</v>
       </c>
       <c r="E522" s="1" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="F522" s="1" t="s">
         <v>5</v>
@@ -15314,7 +15302,7 @@
         <v>3</v>
       </c>
       <c r="D523" s="1" t="s">
-        <v>1086</v>
+        <v>1084</v>
       </c>
       <c r="E523" s="1" t="s">
         <v>12</v>
@@ -15334,7 +15322,7 @@
         <v>3</v>
       </c>
       <c r="D524" s="1" t="s">
-        <v>1086</v>
+        <v>1084</v>
       </c>
       <c r="E524" s="1" t="s">
         <v>12</v>
@@ -15354,10 +15342,10 @@
         <v>3</v>
       </c>
       <c r="D525" s="1" t="s">
-        <v>1086</v>
+        <v>1084</v>
       </c>
       <c r="E525" s="1" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="F525" s="1" t="s">
         <v>5</v>
@@ -15374,7 +15362,7 @@
         <v>3</v>
       </c>
       <c r="D526" s="1" t="s">
-        <v>1086</v>
+        <v>1084</v>
       </c>
       <c r="E526" s="1" t="s">
         <v>15</v>
@@ -15394,10 +15382,10 @@
         <v>3</v>
       </c>
       <c r="D527" s="1" t="s">
-        <v>1086</v>
+        <v>1084</v>
       </c>
       <c r="E527" s="1" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="F527" s="1" t="s">
         <v>5</v>
@@ -15414,10 +15402,10 @@
         <v>3</v>
       </c>
       <c r="D528" s="1" t="s">
-        <v>1086</v>
+        <v>1084</v>
       </c>
       <c r="E528" s="1" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="F528" s="1" t="s">
         <v>5</v>
@@ -15434,7 +15422,7 @@
         <v>3</v>
       </c>
       <c r="D529" s="1" t="s">
-        <v>1086</v>
+        <v>1084</v>
       </c>
       <c r="E529" s="1" t="s">
         <v>18</v>
@@ -15454,13 +15442,13 @@
         <v>3</v>
       </c>
       <c r="D530" s="1" t="s">
-        <v>1086</v>
+        <v>1084</v>
       </c>
       <c r="E530" s="1" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="F530" s="1" t="s">
-        <v>5</v>
+        <v>78</v>
       </c>
     </row>
     <row r="531" spans="1:6" x14ac:dyDescent="0.25">
@@ -15474,10 +15462,10 @@
         <v>3</v>
       </c>
       <c r="D531" s="1" t="s">
-        <v>1086</v>
+        <v>1084</v>
       </c>
       <c r="E531" s="1" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="F531" s="1" t="s">
         <v>5</v>
@@ -15494,13 +15482,13 @@
         <v>3</v>
       </c>
       <c r="D532" s="1" t="s">
-        <v>1086</v>
+        <v>1084</v>
       </c>
       <c r="E532" s="1" t="s">
         <v>21</v>
       </c>
       <c r="F532" s="1" t="s">
-        <v>78</v>
+        <v>5</v>
       </c>
     </row>
     <row r="533" spans="1:6" x14ac:dyDescent="0.25">
@@ -15514,13 +15502,13 @@
         <v>3</v>
       </c>
       <c r="D533" s="1" t="s">
-        <v>1086</v>
+        <v>1084</v>
       </c>
       <c r="E533" s="1" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="F533" s="1" t="s">
-        <v>5</v>
+        <v>78</v>
       </c>
     </row>
     <row r="534" spans="1:6" x14ac:dyDescent="0.25">
@@ -15534,13 +15522,13 @@
         <v>3</v>
       </c>
       <c r="D534" s="1" t="s">
-        <v>1086</v>
+        <v>1084</v>
       </c>
       <c r="E534" s="1" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="F534" s="1" t="s">
-        <v>5</v>
+        <v>78</v>
       </c>
     </row>
     <row r="535" spans="1:6" x14ac:dyDescent="0.25">
@@ -15554,13 +15542,13 @@
         <v>3</v>
       </c>
       <c r="D535" s="1" t="s">
-        <v>1086</v>
+        <v>1084</v>
       </c>
       <c r="E535" s="1" t="s">
         <v>24</v>
       </c>
       <c r="F535" s="1" t="s">
-        <v>78</v>
+        <v>5</v>
       </c>
     </row>
     <row r="536" spans="1:6" x14ac:dyDescent="0.25">
@@ -15574,10 +15562,10 @@
         <v>3</v>
       </c>
       <c r="D536" s="1" t="s">
-        <v>1086</v>
+        <v>1084</v>
       </c>
       <c r="E536" s="1" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="F536" s="1" t="s">
         <v>78</v>
@@ -15594,13 +15582,13 @@
         <v>3</v>
       </c>
       <c r="D537" s="1" t="s">
-        <v>1086</v>
+        <v>1084</v>
       </c>
       <c r="E537" s="1" t="s">
-        <v>55</v>
+        <v>28</v>
       </c>
       <c r="F537" s="1" t="s">
-        <v>78</v>
+        <v>25</v>
       </c>
     </row>
     <row r="538" spans="1:6" x14ac:dyDescent="0.25">
@@ -15614,13 +15602,13 @@
         <v>3</v>
       </c>
       <c r="D538" s="1" t="s">
-        <v>1086</v>
+        <v>1084</v>
       </c>
       <c r="E538" s="1" t="s">
-        <v>55</v>
+        <v>28</v>
       </c>
       <c r="F538" s="1" t="s">
-        <v>25</v>
+        <v>5</v>
       </c>
     </row>
     <row r="539" spans="1:6" x14ac:dyDescent="0.25">
@@ -15634,13 +15622,13 @@
         <v>3</v>
       </c>
       <c r="D539" s="1" t="s">
-        <v>1086</v>
+        <v>1084</v>
       </c>
       <c r="E539" s="1" t="s">
-        <v>55</v>
+        <v>31</v>
       </c>
       <c r="F539" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="540" spans="1:6" x14ac:dyDescent="0.25">
@@ -15654,10 +15642,10 @@
         <v>3</v>
       </c>
       <c r="D540" s="1" t="s">
-        <v>1086</v>
+        <v>1084</v>
       </c>
       <c r="E540" s="1" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="F540" s="1" t="s">
         <v>25</v>
@@ -15674,10 +15662,10 @@
         <v>3</v>
       </c>
       <c r="D541" s="1" t="s">
-        <v>1086</v>
+        <v>1084</v>
       </c>
       <c r="E541" s="1" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="F541" s="1" t="s">
         <v>154</v>
@@ -15694,13 +15682,13 @@
         <v>3</v>
       </c>
       <c r="D542" s="1" t="s">
-        <v>1086</v>
+        <v>1084</v>
       </c>
       <c r="E542" s="1" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="F542" s="1" t="s">
-        <v>5</v>
+        <v>25</v>
       </c>
     </row>
     <row r="543" spans="1:6" x14ac:dyDescent="0.25">
@@ -15714,13 +15702,13 @@
         <v>3</v>
       </c>
       <c r="D543" s="1" t="s">
-        <v>1086</v>
+        <v>1084</v>
       </c>
       <c r="E543" s="1" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="F543" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="544" spans="1:6" x14ac:dyDescent="0.25">
@@ -15734,13 +15722,13 @@
         <v>3</v>
       </c>
       <c r="D544" s="1" t="s">
-        <v>1086</v>
+        <v>1084</v>
       </c>
       <c r="E544" s="1" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="F544" s="1" t="s">
-        <v>25</v>
+        <v>154</v>
       </c>
     </row>
     <row r="545" spans="1:6" x14ac:dyDescent="0.25">
@@ -15754,13 +15742,13 @@
         <v>3</v>
       </c>
       <c r="D545" s="1" t="s">
-        <v>1086</v>
+        <v>1084</v>
       </c>
       <c r="E545" s="1" t="s">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="F545" s="1" t="s">
-        <v>154</v>
+        <v>5</v>
       </c>
     </row>
     <row r="546" spans="1:6" x14ac:dyDescent="0.25">
@@ -15774,10 +15762,10 @@
         <v>3</v>
       </c>
       <c r="D546" s="1" t="s">
-        <v>1086</v>
+        <v>1084</v>
       </c>
       <c r="E546" s="1" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="F546" s="1" t="s">
         <v>5</v>
@@ -15794,10 +15782,10 @@
         <v>3</v>
       </c>
       <c r="D547" s="1" t="s">
-        <v>1086</v>
+        <v>1084</v>
       </c>
       <c r="E547" s="1" t="s">
-        <v>34</v>
+        <v>63</v>
       </c>
       <c r="F547" s="1" t="s">
         <v>5</v>
@@ -15814,13 +15802,13 @@
         <v>3</v>
       </c>
       <c r="D548" s="1" t="s">
-        <v>1086</v>
+        <v>1084</v>
       </c>
       <c r="E548" s="1" t="s">
-        <v>37</v>
+        <v>66</v>
       </c>
       <c r="F548" s="1" t="s">
-        <v>5</v>
+        <v>78</v>
       </c>
     </row>
     <row r="549" spans="1:6" x14ac:dyDescent="0.25">
@@ -15834,10 +15822,10 @@
         <v>3</v>
       </c>
       <c r="D549" s="1" t="s">
-        <v>1086</v>
+        <v>1084</v>
       </c>
       <c r="E549" s="1" t="s">
-        <v>37</v>
+        <v>98</v>
       </c>
       <c r="F549" s="1" t="s">
         <v>5</v>
@@ -15854,13 +15842,13 @@
         <v>3</v>
       </c>
       <c r="D550" s="1" t="s">
-        <v>1086</v>
+        <v>1084</v>
       </c>
       <c r="E550" s="1" t="s">
-        <v>66</v>
+        <v>101</v>
       </c>
       <c r="F550" s="1" t="s">
-        <v>78</v>
+        <v>5</v>
       </c>
     </row>
     <row r="551" spans="1:6" x14ac:dyDescent="0.25">
@@ -15874,10 +15862,10 @@
         <v>3</v>
       </c>
       <c r="D551" s="1" t="s">
-        <v>1086</v>
+        <v>1084</v>
       </c>
       <c r="E551" s="1" t="s">
-        <v>98</v>
+        <v>104</v>
       </c>
       <c r="F551" s="1" t="s">
         <v>5</v>
@@ -15894,30 +15882,30 @@
         <v>3</v>
       </c>
       <c r="D552" s="1" t="s">
-        <v>1086</v>
+        <v>1157</v>
       </c>
       <c r="E552" s="1" t="s">
-        <v>101</v>
+        <v>4</v>
       </c>
       <c r="F552" s="1" t="s">
-        <v>5</v>
+        <v>1158</v>
       </c>
     </row>
     <row r="553" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A553" s="1" t="s">
+        <v>1159</v>
+      </c>
+      <c r="B553" s="1" t="s">
+        <v>1160</v>
+      </c>
+      <c r="C553" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D553" s="1" t="s">
         <v>1157</v>
       </c>
-      <c r="B553" s="1" t="s">
-        <v>1158</v>
-      </c>
-      <c r="C553" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D553" s="1" t="s">
-        <v>1086</v>
-      </c>
       <c r="E553" s="1" t="s">
-        <v>104</v>
+        <v>8</v>
       </c>
       <c r="F553" s="1" t="s">
         <v>5</v>
@@ -15925,22 +15913,22 @@
     </row>
     <row r="554" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A554" s="1" t="s">
-        <v>1159</v>
+        <v>1161</v>
       </c>
       <c r="B554" s="1" t="s">
-        <v>1160</v>
+        <v>1162</v>
       </c>
       <c r="C554" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D554" s="1" t="s">
-        <v>1161</v>
+        <v>1157</v>
       </c>
       <c r="E554" s="1" t="s">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="F554" s="1" t="s">
-        <v>1162</v>
+        <v>5</v>
       </c>
     </row>
     <row r="555" spans="1:6" x14ac:dyDescent="0.25">
@@ -15954,10 +15942,10 @@
         <v>3</v>
       </c>
       <c r="D555" s="1" t="s">
-        <v>1161</v>
+        <v>1157</v>
       </c>
       <c r="E555" s="1" t="s">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="F555" s="1" t="s">
         <v>5</v>
@@ -15974,10 +15962,10 @@
         <v>3</v>
       </c>
       <c r="D556" s="1" t="s">
-        <v>1161</v>
+        <v>1157</v>
       </c>
       <c r="E556" s="1" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="F556" s="1" t="s">
         <v>5</v>
@@ -15994,10 +15982,10 @@
         <v>3</v>
       </c>
       <c r="D557" s="1" t="s">
-        <v>1161</v>
+        <v>1157</v>
       </c>
       <c r="E557" s="1" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="F557" s="1" t="s">
         <v>5</v>
@@ -16014,13 +16002,13 @@
         <v>3</v>
       </c>
       <c r="D558" s="1" t="s">
-        <v>1161</v>
+        <v>1157</v>
       </c>
       <c r="E558" s="1" t="s">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="F558" s="1" t="s">
-        <v>5</v>
+        <v>25</v>
       </c>
     </row>
     <row r="559" spans="1:6" x14ac:dyDescent="0.25">
@@ -16034,10 +16022,10 @@
         <v>3</v>
       </c>
       <c r="D559" s="1" t="s">
-        <v>1161</v>
+        <v>1157</v>
       </c>
       <c r="E559" s="1" t="s">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="F559" s="1" t="s">
         <v>5</v>
@@ -16054,13 +16042,13 @@
         <v>3</v>
       </c>
       <c r="D560" s="1" t="s">
-        <v>1161</v>
+        <v>1157</v>
       </c>
       <c r="E560" s="1" t="s">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="F560" s="1" t="s">
-        <v>25</v>
+        <v>78</v>
       </c>
     </row>
     <row r="561" spans="1:6" x14ac:dyDescent="0.25">
@@ -16074,13 +16062,13 @@
         <v>3</v>
       </c>
       <c r="D561" s="1" t="s">
-        <v>1161</v>
+        <v>1157</v>
       </c>
       <c r="E561" s="1" t="s">
-        <v>55</v>
+        <v>34</v>
       </c>
       <c r="F561" s="1" t="s">
-        <v>5</v>
+        <v>78</v>
       </c>
     </row>
     <row r="562" spans="1:6" x14ac:dyDescent="0.25">
@@ -16094,13 +16082,13 @@
         <v>3</v>
       </c>
       <c r="D562" s="1" t="s">
-        <v>1161</v>
+        <v>1157</v>
       </c>
       <c r="E562" s="1" t="s">
-        <v>28</v>
+        <v>37</v>
       </c>
       <c r="F562" s="1" t="s">
-        <v>78</v>
+        <v>5</v>
       </c>
     </row>
     <row r="563" spans="1:6" x14ac:dyDescent="0.25">
@@ -16114,13 +16102,13 @@
         <v>3</v>
       </c>
       <c r="D563" s="1" t="s">
-        <v>1161</v>
+        <v>1157</v>
       </c>
       <c r="E563" s="1" t="s">
-        <v>31</v>
+        <v>63</v>
       </c>
       <c r="F563" s="1" t="s">
-        <v>78</v>
+        <v>5</v>
       </c>
     </row>
     <row r="564" spans="1:6" x14ac:dyDescent="0.25">
@@ -16134,10 +16122,10 @@
         <v>3</v>
       </c>
       <c r="D564" s="1" t="s">
-        <v>1161</v>
+        <v>1157</v>
       </c>
       <c r="E564" s="1" t="s">
-        <v>34</v>
+        <v>66</v>
       </c>
       <c r="F564" s="1" t="s">
         <v>5</v>
@@ -16154,13 +16142,13 @@
         <v>3</v>
       </c>
       <c r="D565" s="1" t="s">
-        <v>1161</v>
+        <v>1157</v>
       </c>
       <c r="E565" s="1" t="s">
-        <v>37</v>
+        <v>98</v>
       </c>
       <c r="F565" s="1" t="s">
-        <v>5</v>
+        <v>78</v>
       </c>
     </row>
     <row r="566" spans="1:6" x14ac:dyDescent="0.25">
@@ -16174,30 +16162,30 @@
         <v>3</v>
       </c>
       <c r="D566" s="1" t="s">
-        <v>1161</v>
+        <v>1187</v>
       </c>
       <c r="E566" s="1" t="s">
-        <v>66</v>
+        <v>4</v>
       </c>
       <c r="F566" s="1" t="s">
-        <v>5</v>
+        <v>78</v>
       </c>
     </row>
     <row r="567" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A567" s="1" t="s">
+        <v>1188</v>
+      </c>
+      <c r="B567" s="1" t="s">
+        <v>1189</v>
+      </c>
+      <c r="C567" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D567" s="1" t="s">
         <v>1187</v>
       </c>
-      <c r="B567" s="1" t="s">
-        <v>1188</v>
-      </c>
-      <c r="C567" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D567" s="1" t="s">
-        <v>1161</v>
-      </c>
       <c r="E567" s="1" t="s">
-        <v>98</v>
+        <v>8</v>
       </c>
       <c r="F567" s="1" t="s">
         <v>78</v>
@@ -16205,22 +16193,22 @@
     </row>
     <row r="568" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A568" s="1" t="s">
-        <v>1189</v>
+        <v>1190</v>
       </c>
       <c r="B568" s="1" t="s">
-        <v>1190</v>
+        <v>1191</v>
       </c>
       <c r="C568" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D568" s="1" t="s">
-        <v>1191</v>
+        <v>1187</v>
       </c>
       <c r="E568" s="1" t="s">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="F568" s="1" t="s">
-        <v>78</v>
+        <v>5</v>
       </c>
     </row>
     <row r="569" spans="1:6" x14ac:dyDescent="0.25">
@@ -16234,10 +16222,10 @@
         <v>3</v>
       </c>
       <c r="D569" s="1" t="s">
-        <v>1191</v>
+        <v>1187</v>
       </c>
       <c r="E569" s="1" t="s">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="F569" s="1" t="s">
         <v>78</v>
@@ -16254,13 +16242,13 @@
         <v>3</v>
       </c>
       <c r="D570" s="1" t="s">
-        <v>1191</v>
+        <v>1187</v>
       </c>
       <c r="E570" s="1" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="F570" s="1" t="s">
-        <v>5</v>
+        <v>78</v>
       </c>
     </row>
     <row r="571" spans="1:6" x14ac:dyDescent="0.25">
@@ -16274,10 +16262,10 @@
         <v>3</v>
       </c>
       <c r="D571" s="1" t="s">
-        <v>1191</v>
+        <v>1187</v>
       </c>
       <c r="E571" s="1" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="F571" s="1" t="s">
         <v>78</v>
@@ -16294,13 +16282,13 @@
         <v>3</v>
       </c>
       <c r="D572" s="1" t="s">
-        <v>1191</v>
+        <v>1187</v>
       </c>
       <c r="E572" s="1" t="s">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="F572" s="1" t="s">
-        <v>78</v>
+        <v>5</v>
       </c>
     </row>
     <row r="573" spans="1:6" x14ac:dyDescent="0.25">
@@ -16314,13 +16302,13 @@
         <v>3</v>
       </c>
       <c r="D573" s="1" t="s">
-        <v>1191</v>
+        <v>1187</v>
       </c>
       <c r="E573" s="1" t="s">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="F573" s="1" t="s">
-        <v>78</v>
+        <v>5</v>
       </c>
     </row>
     <row r="574" spans="1:6" x14ac:dyDescent="0.25">
@@ -16334,10 +16322,10 @@
         <v>3</v>
       </c>
       <c r="D574" s="1" t="s">
-        <v>1191</v>
+        <v>1187</v>
       </c>
       <c r="E574" s="1" t="s">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="F574" s="1" t="s">
         <v>5</v>
@@ -16354,10 +16342,10 @@
         <v>3</v>
       </c>
       <c r="D575" s="1" t="s">
-        <v>1191</v>
+        <v>1187</v>
       </c>
       <c r="E575" s="1" t="s">
-        <v>55</v>
+        <v>34</v>
       </c>
       <c r="F575" s="1" t="s">
         <v>5</v>
@@ -16374,10 +16362,10 @@
         <v>3</v>
       </c>
       <c r="D576" s="1" t="s">
-        <v>1191</v>
+        <v>1187</v>
       </c>
       <c r="E576" s="1" t="s">
-        <v>28</v>
+        <v>37</v>
       </c>
       <c r="F576" s="1" t="s">
         <v>5</v>
@@ -16394,10 +16382,10 @@
         <v>3</v>
       </c>
       <c r="D577" s="1" t="s">
-        <v>1191</v>
+        <v>1187</v>
       </c>
       <c r="E577" s="1" t="s">
-        <v>31</v>
+        <v>63</v>
       </c>
       <c r="F577" s="1" t="s">
         <v>5</v>
@@ -16414,10 +16402,10 @@
         <v>3</v>
       </c>
       <c r="D578" s="1" t="s">
-        <v>1191</v>
+        <v>1187</v>
       </c>
       <c r="E578" s="1" t="s">
-        <v>34</v>
+        <v>66</v>
       </c>
       <c r="F578" s="1" t="s">
         <v>5</v>
@@ -16434,10 +16422,10 @@
         <v>3</v>
       </c>
       <c r="D579" s="1" t="s">
-        <v>1191</v>
+        <v>1187</v>
       </c>
       <c r="E579" s="1" t="s">
-        <v>37</v>
+        <v>98</v>
       </c>
       <c r="F579" s="1" t="s">
         <v>5</v>
@@ -16454,10 +16442,10 @@
         <v>3</v>
       </c>
       <c r="D580" s="1" t="s">
-        <v>1191</v>
+        <v>1216</v>
       </c>
       <c r="E580" s="1" t="s">
-        <v>66</v>
+        <v>4</v>
       </c>
       <c r="F580" s="1" t="s">
         <v>5</v>
@@ -16465,19 +16453,19 @@
     </row>
     <row r="581" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A581" s="1" t="s">
+        <v>1217</v>
+      </c>
+      <c r="B581" s="1" t="s">
+        <v>1218</v>
+      </c>
+      <c r="C581" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D581" s="1" t="s">
         <v>1216</v>
       </c>
-      <c r="B581" s="1" t="s">
-        <v>1217</v>
-      </c>
-      <c r="C581" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D581" s="1" t="s">
-        <v>1191</v>
-      </c>
       <c r="E581" s="1" t="s">
-        <v>98</v>
+        <v>8</v>
       </c>
       <c r="F581" s="1" t="s">
         <v>5</v>
@@ -16485,22 +16473,22 @@
     </row>
     <row r="582" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A582" s="1" t="s">
-        <v>1218</v>
+        <v>1219</v>
       </c>
       <c r="B582" s="1" t="s">
-        <v>1219</v>
+        <v>1220</v>
       </c>
       <c r="C582" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D582" s="1" t="s">
-        <v>1220</v>
+        <v>1216</v>
       </c>
       <c r="E582" s="1" t="s">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="F582" s="1" t="s">
-        <v>5</v>
+        <v>1075</v>
       </c>
     </row>
     <row r="583" spans="1:6" x14ac:dyDescent="0.25">
@@ -16514,13 +16502,13 @@
         <v>3</v>
       </c>
       <c r="D583" s="1" t="s">
-        <v>1220</v>
+        <v>1216</v>
       </c>
       <c r="E583" s="1" t="s">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="F583" s="1" t="s">
-        <v>5</v>
+        <v>1075</v>
       </c>
     </row>
     <row r="584" spans="1:6" x14ac:dyDescent="0.25">
@@ -16534,13 +16522,13 @@
         <v>3</v>
       </c>
       <c r="D584" s="1" t="s">
-        <v>1220</v>
+        <v>1216</v>
       </c>
       <c r="E584" s="1" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="F584" s="1" t="s">
-        <v>1077</v>
+        <v>5</v>
       </c>
     </row>
     <row r="585" spans="1:6" x14ac:dyDescent="0.25">
@@ -16554,13 +16542,13 @@
         <v>3</v>
       </c>
       <c r="D585" s="1" t="s">
-        <v>1220</v>
+        <v>1216</v>
       </c>
       <c r="E585" s="1" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="F585" s="1" t="s">
-        <v>1077</v>
+        <v>5</v>
       </c>
     </row>
     <row r="586" spans="1:6" x14ac:dyDescent="0.25">
@@ -16574,10 +16562,10 @@
         <v>3</v>
       </c>
       <c r="D586" s="1" t="s">
-        <v>1220</v>
+        <v>1216</v>
       </c>
       <c r="E586" s="1" t="s">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="F586" s="1" t="s">
         <v>5</v>
@@ -16594,10 +16582,10 @@
         <v>3</v>
       </c>
       <c r="D587" s="1" t="s">
-        <v>1220</v>
+        <v>1216</v>
       </c>
       <c r="E587" s="1" t="s">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="F587" s="1" t="s">
         <v>5</v>
@@ -16614,13 +16602,13 @@
         <v>3</v>
       </c>
       <c r="D588" s="1" t="s">
-        <v>1220</v>
+        <v>1216</v>
       </c>
       <c r="E588" s="1" t="s">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="F588" s="1" t="s">
-        <v>5</v>
+        <v>38</v>
       </c>
     </row>
     <row r="589" spans="1:6" x14ac:dyDescent="0.25">
@@ -16634,10 +16622,10 @@
         <v>3</v>
       </c>
       <c r="D589" s="1" t="s">
-        <v>1220</v>
+        <v>1216</v>
       </c>
       <c r="E589" s="1" t="s">
-        <v>55</v>
+        <v>34</v>
       </c>
       <c r="F589" s="1" t="s">
         <v>5</v>
@@ -16654,13 +16642,13 @@
         <v>3</v>
       </c>
       <c r="D590" s="1" t="s">
-        <v>1220</v>
+        <v>1216</v>
       </c>
       <c r="E590" s="1" t="s">
-        <v>28</v>
+        <v>37</v>
       </c>
       <c r="F590" s="1" t="s">
-        <v>38</v>
+        <v>5</v>
       </c>
     </row>
     <row r="591" spans="1:6" x14ac:dyDescent="0.25">
@@ -16674,10 +16662,10 @@
         <v>3</v>
       </c>
       <c r="D591" s="1" t="s">
-        <v>1220</v>
+        <v>1216</v>
       </c>
       <c r="E591" s="1" t="s">
-        <v>31</v>
+        <v>63</v>
       </c>
       <c r="F591" s="1" t="s">
         <v>5</v>
@@ -16694,10 +16682,10 @@
         <v>3</v>
       </c>
       <c r="D592" s="1" t="s">
-        <v>1220</v>
+        <v>1216</v>
       </c>
       <c r="E592" s="1" t="s">
-        <v>34</v>
+        <v>66</v>
       </c>
       <c r="F592" s="1" t="s">
         <v>5</v>
@@ -16714,50 +16702,50 @@
         <v>3</v>
       </c>
       <c r="D593" s="1" t="s">
-        <v>1220</v>
+        <v>1243</v>
       </c>
       <c r="E593" s="1" t="s">
-        <v>37</v>
+        <v>4</v>
       </c>
       <c r="F593" s="1" t="s">
-        <v>5</v>
+        <v>38</v>
       </c>
     </row>
     <row r="594" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A594" s="1" t="s">
+        <v>1244</v>
+      </c>
+      <c r="B594" s="1" t="s">
+        <v>1245</v>
+      </c>
+      <c r="C594" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D594" s="1" t="s">
         <v>1243</v>
       </c>
-      <c r="B594" s="1" t="s">
-        <v>1244</v>
-      </c>
-      <c r="C594" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D594" s="1" t="s">
-        <v>1220</v>
-      </c>
       <c r="E594" s="1" t="s">
-        <v>66</v>
+        <v>8</v>
       </c>
       <c r="F594" s="1" t="s">
-        <v>5</v>
+        <v>38</v>
       </c>
     </row>
     <row r="595" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A595" s="1" t="s">
-        <v>1245</v>
+        <v>1246</v>
       </c>
       <c r="B595" s="1" t="s">
-        <v>1246</v>
+        <v>1247</v>
       </c>
       <c r="C595" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D595" s="1" t="s">
-        <v>1247</v>
+        <v>1243</v>
       </c>
       <c r="E595" s="1" t="s">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="F595" s="1" t="s">
         <v>38</v>
@@ -16774,13 +16762,13 @@
         <v>3</v>
       </c>
       <c r="D596" s="1" t="s">
-        <v>1247</v>
+        <v>1243</v>
       </c>
       <c r="E596" s="1" t="s">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="F596" s="1" t="s">
-        <v>38</v>
+        <v>154</v>
       </c>
     </row>
     <row r="597" spans="1:6" x14ac:dyDescent="0.25">
@@ -16794,13 +16782,13 @@
         <v>3</v>
       </c>
       <c r="D597" s="1" t="s">
-        <v>1247</v>
+        <v>1243</v>
       </c>
       <c r="E597" s="1" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="F597" s="1" t="s">
-        <v>38</v>
+        <v>5</v>
       </c>
     </row>
     <row r="598" spans="1:6" x14ac:dyDescent="0.25">
@@ -16814,13 +16802,13 @@
         <v>3</v>
       </c>
       <c r="D598" s="1" t="s">
-        <v>1247</v>
+        <v>1243</v>
       </c>
       <c r="E598" s="1" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="F598" s="1" t="s">
-        <v>154</v>
+        <v>5</v>
       </c>
     </row>
     <row r="599" spans="1:6" x14ac:dyDescent="0.25">
@@ -16834,10 +16822,10 @@
         <v>3</v>
       </c>
       <c r="D599" s="1" t="s">
-        <v>1247</v>
+        <v>1243</v>
       </c>
       <c r="E599" s="1" t="s">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="F599" s="1" t="s">
         <v>5</v>
@@ -16854,10 +16842,10 @@
         <v>3</v>
       </c>
       <c r="D600" s="1" t="s">
-        <v>1247</v>
+        <v>1243</v>
       </c>
       <c r="E600" s="1" t="s">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="F600" s="1" t="s">
         <v>5</v>
@@ -16874,10 +16862,10 @@
         <v>3</v>
       </c>
       <c r="D601" s="1" t="s">
-        <v>1247</v>
+        <v>1243</v>
       </c>
       <c r="E601" s="1" t="s">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="F601" s="1" t="s">
         <v>5</v>
@@ -16894,10 +16882,10 @@
         <v>3</v>
       </c>
       <c r="D602" s="1" t="s">
-        <v>1247</v>
+        <v>1243</v>
       </c>
       <c r="E602" s="1" t="s">
-        <v>55</v>
+        <v>34</v>
       </c>
       <c r="F602" s="1" t="s">
         <v>5</v>
@@ -16914,10 +16902,10 @@
         <v>3</v>
       </c>
       <c r="D603" s="1" t="s">
-        <v>1247</v>
+        <v>1243</v>
       </c>
       <c r="E603" s="1" t="s">
-        <v>28</v>
+        <v>37</v>
       </c>
       <c r="F603" s="1" t="s">
         <v>5</v>
@@ -16934,10 +16922,10 @@
         <v>3</v>
       </c>
       <c r="D604" s="1" t="s">
-        <v>1247</v>
+        <v>1243</v>
       </c>
       <c r="E604" s="1" t="s">
-        <v>31</v>
+        <v>63</v>
       </c>
       <c r="F604" s="1" t="s">
         <v>5</v>
@@ -16954,10 +16942,10 @@
         <v>3</v>
       </c>
       <c r="D605" s="1" t="s">
-        <v>1247</v>
+        <v>1243</v>
       </c>
       <c r="E605" s="1" t="s">
-        <v>34</v>
+        <v>66</v>
       </c>
       <c r="F605" s="1" t="s">
         <v>5</v>
@@ -16974,10 +16962,10 @@
         <v>3</v>
       </c>
       <c r="D606" s="1" t="s">
-        <v>1247</v>
+        <v>1243</v>
       </c>
       <c r="E606" s="1" t="s">
-        <v>37</v>
+        <v>98</v>
       </c>
       <c r="F606" s="1" t="s">
         <v>5</v>
@@ -16994,13 +16982,13 @@
         <v>3</v>
       </c>
       <c r="D607" s="1" t="s">
-        <v>1247</v>
+        <v>1243</v>
       </c>
       <c r="E607" s="1" t="s">
-        <v>66</v>
+        <v>101</v>
       </c>
       <c r="F607" s="1" t="s">
-        <v>5</v>
+        <v>38</v>
       </c>
     </row>
     <row r="608" spans="1:6" x14ac:dyDescent="0.25">
@@ -17014,10 +17002,10 @@
         <v>3</v>
       </c>
       <c r="D608" s="1" t="s">
-        <v>1247</v>
+        <v>1243</v>
       </c>
       <c r="E608" s="1" t="s">
-        <v>98</v>
+        <v>104</v>
       </c>
       <c r="F608" s="1" t="s">
         <v>5</v>
@@ -17034,13 +17022,13 @@
         <v>3</v>
       </c>
       <c r="D609" s="1" t="s">
-        <v>1247</v>
+        <v>1243</v>
       </c>
       <c r="E609" s="1" t="s">
-        <v>101</v>
+        <v>107</v>
       </c>
       <c r="F609" s="1" t="s">
-        <v>38</v>
+        <v>5</v>
       </c>
     </row>
     <row r="610" spans="1:6" x14ac:dyDescent="0.25">
@@ -17054,53 +17042,53 @@
         <v>3</v>
       </c>
       <c r="D610" s="1" t="s">
-        <v>1247</v>
+        <v>1278</v>
       </c>
       <c r="E610" s="1" t="s">
-        <v>104</v>
+        <v>4</v>
       </c>
       <c r="F610" s="1" t="s">
-        <v>5</v>
+        <v>78</v>
       </c>
     </row>
     <row r="611" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A611" s="1" t="s">
+        <v>1279</v>
+      </c>
+      <c r="B611" s="1" t="s">
+        <v>1280</v>
+      </c>
+      <c r="C611" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D611" s="1" t="s">
         <v>1278</v>
       </c>
-      <c r="B611" s="1" t="s">
-        <v>1279</v>
-      </c>
-      <c r="C611" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D611" s="1" t="s">
-        <v>1247</v>
-      </c>
       <c r="E611" s="1" t="s">
-        <v>107</v>
+        <v>8</v>
       </c>
       <c r="F611" s="1" t="s">
-        <v>5</v>
+        <v>38</v>
       </c>
     </row>
     <row r="612" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A612" s="1" t="s">
-        <v>1280</v>
+        <v>1281</v>
       </c>
       <c r="B612" s="1" t="s">
-        <v>1281</v>
+        <v>1282</v>
       </c>
       <c r="C612" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D612" s="1" t="s">
-        <v>1282</v>
+        <v>1278</v>
       </c>
       <c r="E612" s="1" t="s">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="F612" s="1" t="s">
-        <v>78</v>
+        <v>5</v>
       </c>
     </row>
     <row r="613" spans="1:6" x14ac:dyDescent="0.25">
@@ -17114,13 +17102,13 @@
         <v>3</v>
       </c>
       <c r="D613" s="1" t="s">
-        <v>1282</v>
+        <v>1278</v>
       </c>
       <c r="E613" s="1" t="s">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="F613" s="1" t="s">
-        <v>38</v>
+        <v>5</v>
       </c>
     </row>
     <row r="614" spans="1:6" x14ac:dyDescent="0.25">
@@ -17134,10 +17122,10 @@
         <v>3</v>
       </c>
       <c r="D614" s="1" t="s">
-        <v>1282</v>
+        <v>1278</v>
       </c>
       <c r="E614" s="1" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="F614" s="1" t="s">
         <v>5</v>
@@ -17154,13 +17142,13 @@
         <v>3</v>
       </c>
       <c r="D615" s="1" t="s">
-        <v>1282</v>
+        <v>1278</v>
       </c>
       <c r="E615" s="1" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="F615" s="1" t="s">
-        <v>5</v>
+        <v>38</v>
       </c>
     </row>
     <row r="616" spans="1:6" x14ac:dyDescent="0.25">
@@ -17174,13 +17162,13 @@
         <v>3</v>
       </c>
       <c r="D616" s="1" t="s">
-        <v>1282</v>
+        <v>1278</v>
       </c>
       <c r="E616" s="1" t="s">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="F616" s="1" t="s">
-        <v>5</v>
+        <v>38</v>
       </c>
     </row>
     <row r="617" spans="1:6" x14ac:dyDescent="0.25">
@@ -17194,13 +17182,13 @@
         <v>3</v>
       </c>
       <c r="D617" s="1" t="s">
-        <v>1282</v>
+        <v>1278</v>
       </c>
       <c r="E617" s="1" t="s">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="F617" s="1" t="s">
-        <v>38</v>
+        <v>5</v>
       </c>
     </row>
     <row r="618" spans="1:6" x14ac:dyDescent="0.25">
@@ -17214,13 +17202,13 @@
         <v>3</v>
       </c>
       <c r="D618" s="1" t="s">
-        <v>1282</v>
+        <v>1278</v>
       </c>
       <c r="E618" s="1" t="s">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="F618" s="1" t="s">
-        <v>38</v>
+        <v>5</v>
       </c>
     </row>
     <row r="619" spans="1:6" x14ac:dyDescent="0.25">
@@ -17234,13 +17222,13 @@
         <v>3</v>
       </c>
       <c r="D619" s="1" t="s">
-        <v>1282</v>
+        <v>1278</v>
       </c>
       <c r="E619" s="1" t="s">
-        <v>55</v>
+        <v>34</v>
       </c>
       <c r="F619" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="620" spans="1:6" x14ac:dyDescent="0.25">
@@ -17254,13 +17242,13 @@
         <v>3</v>
       </c>
       <c r="D620" s="1" t="s">
-        <v>1282</v>
+        <v>1278</v>
       </c>
       <c r="E620" s="1" t="s">
-        <v>28</v>
+        <v>37</v>
       </c>
       <c r="F620" s="1" t="s">
-        <v>5</v>
+        <v>25</v>
       </c>
     </row>
     <row r="621" spans="1:6" x14ac:dyDescent="0.25">
@@ -17274,13 +17262,13 @@
         <v>3</v>
       </c>
       <c r="D621" s="1" t="s">
-        <v>1282</v>
+        <v>1278</v>
       </c>
       <c r="E621" s="1" t="s">
-        <v>31</v>
+        <v>63</v>
       </c>
       <c r="F621" s="1" t="s">
-        <v>9</v>
+        <v>38</v>
       </c>
     </row>
     <row r="622" spans="1:6" x14ac:dyDescent="0.25">
@@ -17294,13 +17282,13 @@
         <v>3</v>
       </c>
       <c r="D622" s="1" t="s">
-        <v>1282</v>
+        <v>1278</v>
       </c>
       <c r="E622" s="1" t="s">
-        <v>34</v>
+        <v>66</v>
       </c>
       <c r="F622" s="1" t="s">
-        <v>25</v>
+        <v>38</v>
       </c>
     </row>
     <row r="623" spans="1:6" x14ac:dyDescent="0.25">
@@ -17314,13 +17302,13 @@
         <v>3</v>
       </c>
       <c r="D623" s="1" t="s">
-        <v>1282</v>
+        <v>1278</v>
       </c>
       <c r="E623" s="1" t="s">
-        <v>37</v>
+        <v>98</v>
       </c>
       <c r="F623" s="1" t="s">
-        <v>38</v>
+        <v>535</v>
       </c>
     </row>
     <row r="624" spans="1:6" x14ac:dyDescent="0.25">
@@ -17334,13 +17322,13 @@
         <v>3</v>
       </c>
       <c r="D624" s="1" t="s">
-        <v>1282</v>
+        <v>1278</v>
       </c>
       <c r="E624" s="1" t="s">
-        <v>66</v>
+        <v>101</v>
       </c>
       <c r="F624" s="1" t="s">
-        <v>38</v>
+        <v>5</v>
       </c>
     </row>
     <row r="625" spans="1:6" x14ac:dyDescent="0.25">
@@ -17354,13 +17342,13 @@
         <v>3</v>
       </c>
       <c r="D625" s="1" t="s">
-        <v>1282</v>
+        <v>1278</v>
       </c>
       <c r="E625" s="1" t="s">
-        <v>98</v>
+        <v>104</v>
       </c>
       <c r="F625" s="1" t="s">
-        <v>533</v>
+        <v>5</v>
       </c>
     </row>
     <row r="626" spans="1:6" x14ac:dyDescent="0.25">
@@ -17374,10 +17362,10 @@
         <v>3</v>
       </c>
       <c r="D626" s="1" t="s">
-        <v>1282</v>
+        <v>1278</v>
       </c>
       <c r="E626" s="1" t="s">
-        <v>101</v>
+        <v>107</v>
       </c>
       <c r="F626" s="1" t="s">
         <v>5</v>
@@ -17394,13 +17382,13 @@
         <v>3</v>
       </c>
       <c r="D627" s="1" t="s">
-        <v>1282</v>
+        <v>1278</v>
       </c>
       <c r="E627" s="1" t="s">
-        <v>104</v>
+        <v>110</v>
       </c>
       <c r="F627" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="628" spans="1:6" x14ac:dyDescent="0.25">
@@ -17414,10 +17402,10 @@
         <v>3</v>
       </c>
       <c r="D628" s="1" t="s">
-        <v>1282</v>
+        <v>1315</v>
       </c>
       <c r="E628" s="1" t="s">
-        <v>107</v>
+        <v>4</v>
       </c>
       <c r="F628" s="1" t="s">
         <v>5</v>
@@ -17425,39 +17413,39 @@
     </row>
     <row r="629" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A629" s="1" t="s">
+        <v>1316</v>
+      </c>
+      <c r="B629" s="1" t="s">
+        <v>1317</v>
+      </c>
+      <c r="C629" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D629" s="1" t="s">
         <v>1315</v>
       </c>
-      <c r="B629" s="1" t="s">
-        <v>1316</v>
-      </c>
-      <c r="C629" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D629" s="1" t="s">
-        <v>1282</v>
-      </c>
       <c r="E629" s="1" t="s">
-        <v>110</v>
+        <v>8</v>
       </c>
       <c r="F629" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="630" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A630" s="1" t="s">
-        <v>1317</v>
+        <v>1318</v>
       </c>
       <c r="B630" s="1" t="s">
-        <v>1318</v>
+        <v>1319</v>
       </c>
       <c r="C630" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D630" s="1" t="s">
-        <v>1319</v>
+        <v>1315</v>
       </c>
       <c r="E630" s="1" t="s">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="F630" s="1" t="s">
         <v>5</v>
@@ -17474,10 +17462,10 @@
         <v>3</v>
       </c>
       <c r="D631" s="1" t="s">
-        <v>1319</v>
+        <v>1315</v>
       </c>
       <c r="E631" s="1" t="s">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="F631" s="1" t="s">
         <v>5</v>
@@ -17488,16 +17476,16 @@
         <v>1322</v>
       </c>
       <c r="B632" s="1" t="s">
-        <v>1323</v>
+        <v>1321</v>
       </c>
       <c r="C632" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D632" s="1" t="s">
-        <v>1319</v>
+        <v>1315</v>
       </c>
       <c r="E632" s="1" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="F632" s="1" t="s">
         <v>5</v>
@@ -17505,42 +17493,42 @@
     </row>
     <row r="633" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A633" s="1" t="s">
+        <v>1323</v>
+      </c>
+      <c r="B633" s="1" t="s">
         <v>1324</v>
       </c>
-      <c r="B633" s="1" t="s">
-        <v>1325</v>
-      </c>
       <c r="C633" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D633" s="1" t="s">
-        <v>1319</v>
+        <v>1315</v>
       </c>
       <c r="E633" s="1" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="F633" s="1" t="s">
-        <v>5</v>
+        <v>78</v>
       </c>
     </row>
     <row r="634" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A634" s="1" t="s">
+        <v>1325</v>
+      </c>
+      <c r="B634" s="1" t="s">
         <v>1326</v>
       </c>
-      <c r="B634" s="1" t="s">
-        <v>1325</v>
-      </c>
       <c r="C634" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D634" s="1" t="s">
-        <v>1319</v>
+        <v>1315</v>
       </c>
       <c r="E634" s="1" t="s">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="F634" s="1" t="s">
-        <v>5</v>
+        <v>78</v>
       </c>
     </row>
     <row r="635" spans="1:6" x14ac:dyDescent="0.25">
@@ -17554,13 +17542,13 @@
         <v>3</v>
       </c>
       <c r="D635" s="1" t="s">
-        <v>1319</v>
+        <v>1315</v>
       </c>
       <c r="E635" s="1" t="s">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="F635" s="1" t="s">
-        <v>78</v>
+        <v>25</v>
       </c>
     </row>
     <row r="636" spans="1:6" x14ac:dyDescent="0.25">
@@ -17574,13 +17562,13 @@
         <v>3</v>
       </c>
       <c r="D636" s="1" t="s">
-        <v>1319</v>
+        <v>1315</v>
       </c>
       <c r="E636" s="1" t="s">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="F636" s="1" t="s">
-        <v>78</v>
+        <v>25</v>
       </c>
     </row>
     <row r="637" spans="1:6" x14ac:dyDescent="0.25">
@@ -17594,10 +17582,10 @@
         <v>3</v>
       </c>
       <c r="D637" s="1" t="s">
-        <v>1319</v>
+        <v>1315</v>
       </c>
       <c r="E637" s="1" t="s">
-        <v>55</v>
+        <v>34</v>
       </c>
       <c r="F637" s="1" t="s">
         <v>25</v>
@@ -17614,10 +17602,10 @@
         <v>3</v>
       </c>
       <c r="D638" s="1" t="s">
-        <v>1319</v>
+        <v>1315</v>
       </c>
       <c r="E638" s="1" t="s">
-        <v>28</v>
+        <v>37</v>
       </c>
       <c r="F638" s="1" t="s">
         <v>25</v>
@@ -17634,10 +17622,10 @@
         <v>3</v>
       </c>
       <c r="D639" s="1" t="s">
-        <v>1319</v>
+        <v>1315</v>
       </c>
       <c r="E639" s="1" t="s">
-        <v>31</v>
+        <v>63</v>
       </c>
       <c r="F639" s="1" t="s">
         <v>25</v>
@@ -17654,10 +17642,10 @@
         <v>3</v>
       </c>
       <c r="D640" s="1" t="s">
-        <v>1319</v>
+        <v>1315</v>
       </c>
       <c r="E640" s="1" t="s">
-        <v>34</v>
+        <v>66</v>
       </c>
       <c r="F640" s="1" t="s">
         <v>25</v>
@@ -17674,13 +17662,13 @@
         <v>3</v>
       </c>
       <c r="D641" s="1" t="s">
-        <v>1319</v>
+        <v>1315</v>
       </c>
       <c r="E641" s="1" t="s">
-        <v>37</v>
+        <v>98</v>
       </c>
       <c r="F641" s="1" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
     </row>
     <row r="642" spans="1:6" x14ac:dyDescent="0.25">
@@ -17694,13 +17682,13 @@
         <v>3</v>
       </c>
       <c r="D642" s="1" t="s">
-        <v>1319</v>
+        <v>1315</v>
       </c>
       <c r="E642" s="1" t="s">
-        <v>66</v>
+        <v>101</v>
       </c>
       <c r="F642" s="1" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
     </row>
     <row r="643" spans="1:6" x14ac:dyDescent="0.25">
@@ -17714,10 +17702,10 @@
         <v>3</v>
       </c>
       <c r="D643" s="1" t="s">
-        <v>1319</v>
+        <v>1315</v>
       </c>
       <c r="E643" s="1" t="s">
-        <v>98</v>
+        <v>104</v>
       </c>
       <c r="F643" s="1" t="s">
         <v>9</v>
@@ -17734,10 +17722,10 @@
         <v>3</v>
       </c>
       <c r="D644" s="1" t="s">
-        <v>1319</v>
+        <v>1315</v>
       </c>
       <c r="E644" s="1" t="s">
-        <v>101</v>
+        <v>107</v>
       </c>
       <c r="F644" s="1" t="s">
         <v>9</v>
@@ -17754,50 +17742,50 @@
         <v>3</v>
       </c>
       <c r="D645" s="1" t="s">
-        <v>1319</v>
+        <v>1349</v>
       </c>
       <c r="E645" s="1" t="s">
-        <v>104</v>
+        <v>4</v>
       </c>
       <c r="F645" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="646" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A646" s="1" t="s">
+        <v>1350</v>
+      </c>
+      <c r="B646" s="1" t="s">
+        <v>1351</v>
+      </c>
+      <c r="C646" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D646" s="1" t="s">
         <v>1349</v>
       </c>
-      <c r="B646" s="1" t="s">
-        <v>1350</v>
-      </c>
-      <c r="C646" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D646" s="1" t="s">
-        <v>1319</v>
-      </c>
       <c r="E646" s="1" t="s">
-        <v>107</v>
+        <v>8</v>
       </c>
       <c r="F646" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="647" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A647" s="1" t="s">
-        <v>1351</v>
+        <v>1352</v>
       </c>
       <c r="B647" s="1" t="s">
-        <v>1352</v>
+        <v>1353</v>
       </c>
       <c r="C647" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D647" s="1" t="s">
-        <v>1353</v>
+        <v>1349</v>
       </c>
       <c r="E647" s="1" t="s">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="F647" s="1" t="s">
         <v>5</v>
@@ -17814,13 +17802,13 @@
         <v>3</v>
       </c>
       <c r="D648" s="1" t="s">
-        <v>1353</v>
+        <v>1349</v>
       </c>
       <c r="E648" s="1" t="s">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="F648" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="649" spans="1:6" x14ac:dyDescent="0.25">
@@ -17834,13 +17822,13 @@
         <v>3</v>
       </c>
       <c r="D649" s="1" t="s">
-        <v>1353</v>
+        <v>1349</v>
       </c>
       <c r="E649" s="1" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="F649" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="650" spans="1:6" x14ac:dyDescent="0.25">
@@ -17854,10 +17842,10 @@
         <v>3</v>
       </c>
       <c r="D650" s="1" t="s">
-        <v>1353</v>
+        <v>1349</v>
       </c>
       <c r="E650" s="1" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="F650" s="1" t="s">
         <v>9</v>
@@ -17874,13 +17862,13 @@
         <v>3</v>
       </c>
       <c r="D651" s="1" t="s">
-        <v>1353</v>
+        <v>1349</v>
       </c>
       <c r="E651" s="1" t="s">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="F651" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="652" spans="1:6" x14ac:dyDescent="0.25">
@@ -17894,13 +17882,13 @@
         <v>3</v>
       </c>
       <c r="D652" s="1" t="s">
-        <v>1353</v>
+        <v>1349</v>
       </c>
       <c r="E652" s="1" t="s">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="F652" s="1" t="s">
-        <v>9</v>
+        <v>38</v>
       </c>
     </row>
     <row r="653" spans="1:6" x14ac:dyDescent="0.25">
@@ -17914,13 +17902,13 @@
         <v>3</v>
       </c>
       <c r="D653" s="1" t="s">
-        <v>1353</v>
+        <v>1349</v>
       </c>
       <c r="E653" s="1" t="s">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="F653" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="654" spans="1:6" x14ac:dyDescent="0.25">
@@ -17934,13 +17922,13 @@
         <v>3</v>
       </c>
       <c r="D654" s="1" t="s">
-        <v>1353</v>
+        <v>1349</v>
       </c>
       <c r="E654" s="1" t="s">
-        <v>55</v>
+        <v>34</v>
       </c>
       <c r="F654" s="1" t="s">
-        <v>38</v>
+        <v>9</v>
       </c>
     </row>
     <row r="655" spans="1:6" x14ac:dyDescent="0.25">
@@ -17954,50 +17942,50 @@
         <v>3</v>
       </c>
       <c r="D655" s="1" t="s">
-        <v>1353</v>
+        <v>1370</v>
       </c>
       <c r="E655" s="1" t="s">
-        <v>28</v>
+        <v>4</v>
       </c>
       <c r="F655" s="1" t="s">
-        <v>9</v>
+        <v>269</v>
       </c>
     </row>
     <row r="656" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A656" s="1" t="s">
+        <v>1371</v>
+      </c>
+      <c r="B656" s="1" t="s">
+        <v>1372</v>
+      </c>
+      <c r="C656" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D656" s="1" t="s">
         <v>1370</v>
       </c>
-      <c r="B656" s="1" t="s">
-        <v>1371</v>
-      </c>
-      <c r="C656" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D656" s="1" t="s">
-        <v>1353</v>
-      </c>
       <c r="E656" s="1" t="s">
-        <v>31</v>
+        <v>8</v>
       </c>
       <c r="F656" s="1" t="s">
-        <v>9</v>
+        <v>269</v>
       </c>
     </row>
     <row r="657" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A657" s="1" t="s">
-        <v>1372</v>
+        <v>1373</v>
       </c>
       <c r="B657" s="1" t="s">
-        <v>1373</v>
+        <v>1374</v>
       </c>
       <c r="C657" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D657" s="1" t="s">
-        <v>1374</v>
+        <v>1370</v>
       </c>
       <c r="E657" s="1" t="s">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="F657" s="1" t="s">
         <v>269</v>
@@ -18014,10 +18002,10 @@
         <v>3</v>
       </c>
       <c r="D658" s="1" t="s">
-        <v>1374</v>
+        <v>1370</v>
       </c>
       <c r="E658" s="1" t="s">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="F658" s="1" t="s">
         <v>269</v>
@@ -18034,10 +18022,10 @@
         <v>3</v>
       </c>
       <c r="D659" s="1" t="s">
-        <v>1374</v>
+        <v>1370</v>
       </c>
       <c r="E659" s="1" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="F659" s="1" t="s">
         <v>269</v>
@@ -18054,10 +18042,10 @@
         <v>3</v>
       </c>
       <c r="D660" s="1" t="s">
-        <v>1374</v>
+        <v>1370</v>
       </c>
       <c r="E660" s="1" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="F660" s="1" t="s">
         <v>269</v>
@@ -18074,10 +18062,10 @@
         <v>3</v>
       </c>
       <c r="D661" s="1" t="s">
-        <v>1374</v>
+        <v>1370</v>
       </c>
       <c r="E661" s="1" t="s">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="F661" s="1" t="s">
         <v>269</v>
@@ -18094,13 +18082,13 @@
         <v>3</v>
       </c>
       <c r="D662" s="1" t="s">
-        <v>1374</v>
+        <v>1370</v>
       </c>
       <c r="E662" s="1" t="s">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="F662" s="1" t="s">
-        <v>269</v>
+        <v>230</v>
       </c>
     </row>
     <row r="663" spans="1:6" x14ac:dyDescent="0.25">
@@ -18114,13 +18102,13 @@
         <v>3</v>
       </c>
       <c r="D663" s="1" t="s">
-        <v>1374</v>
+        <v>1370</v>
       </c>
       <c r="E663" s="1" t="s">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="F663" s="1" t="s">
-        <v>269</v>
+        <v>5</v>
       </c>
     </row>
     <row r="664" spans="1:6" x14ac:dyDescent="0.25">
@@ -18134,13 +18122,13 @@
         <v>3</v>
       </c>
       <c r="D664" s="1" t="s">
-        <v>1374</v>
+        <v>1370</v>
       </c>
       <c r="E664" s="1" t="s">
-        <v>55</v>
+        <v>34</v>
       </c>
       <c r="F664" s="1" t="s">
-        <v>230</v>
+        <v>269</v>
       </c>
     </row>
     <row r="665" spans="1:6" x14ac:dyDescent="0.25">
@@ -18154,13 +18142,13 @@
         <v>3</v>
       </c>
       <c r="D665" s="1" t="s">
-        <v>1374</v>
+        <v>1370</v>
       </c>
       <c r="E665" s="1" t="s">
-        <v>28</v>
+        <v>37</v>
       </c>
       <c r="F665" s="1" t="s">
-        <v>5</v>
+        <v>269</v>
       </c>
     </row>
     <row r="666" spans="1:6" x14ac:dyDescent="0.25">
@@ -18174,10 +18162,10 @@
         <v>3</v>
       </c>
       <c r="D666" s="1" t="s">
-        <v>1374</v>
+        <v>1370</v>
       </c>
       <c r="E666" s="1" t="s">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="F666" s="1" t="s">
         <v>269</v>
@@ -18194,10 +18182,10 @@
         <v>3</v>
       </c>
       <c r="D667" s="1" t="s">
-        <v>1374</v>
+        <v>1370</v>
       </c>
       <c r="E667" s="1" t="s">
-        <v>34</v>
+        <v>63</v>
       </c>
       <c r="F667" s="1" t="s">
         <v>269</v>
@@ -18214,13 +18202,13 @@
         <v>3</v>
       </c>
       <c r="D668" s="1" t="s">
-        <v>1374</v>
+        <v>1370</v>
       </c>
       <c r="E668" s="1" t="s">
-        <v>34</v>
+        <v>63</v>
       </c>
       <c r="F668" s="1" t="s">
-        <v>269</v>
+        <v>230</v>
       </c>
     </row>
     <row r="669" spans="1:6" x14ac:dyDescent="0.25">
@@ -18234,10 +18222,10 @@
         <v>3</v>
       </c>
       <c r="D669" s="1" t="s">
-        <v>1374</v>
+        <v>1370</v>
       </c>
       <c r="E669" s="1" t="s">
-        <v>37</v>
+        <v>66</v>
       </c>
       <c r="F669" s="1" t="s">
         <v>269</v>
@@ -18254,53 +18242,53 @@
         <v>3</v>
       </c>
       <c r="D670" s="1" t="s">
-        <v>1374</v>
+        <v>1401</v>
       </c>
       <c r="E670" s="1" t="s">
-        <v>37</v>
+        <v>4</v>
       </c>
       <c r="F670" s="1" t="s">
-        <v>230</v>
+        <v>78</v>
       </c>
     </row>
     <row r="671" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A671" s="1" t="s">
+        <v>1402</v>
+      </c>
+      <c r="B671" s="1" t="s">
+        <v>1403</v>
+      </c>
+      <c r="C671" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D671" s="1" t="s">
         <v>1401</v>
       </c>
-      <c r="B671" s="1" t="s">
-        <v>1402</v>
-      </c>
-      <c r="C671" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D671" s="1" t="s">
-        <v>1374</v>
-      </c>
       <c r="E671" s="1" t="s">
-        <v>66</v>
+        <v>4</v>
       </c>
       <c r="F671" s="1" t="s">
-        <v>269</v>
+        <v>9</v>
       </c>
     </row>
     <row r="672" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A672" s="1" t="s">
-        <v>1403</v>
+        <v>1404</v>
       </c>
       <c r="B672" s="1" t="s">
-        <v>1404</v>
+        <v>1405</v>
       </c>
       <c r="C672" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D672" s="1" t="s">
-        <v>1405</v>
+        <v>1401</v>
       </c>
       <c r="E672" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F672" s="1" t="s">
-        <v>78</v>
+        <v>38</v>
       </c>
     </row>
     <row r="673" spans="1:6" x14ac:dyDescent="0.25">
@@ -18314,13 +18302,13 @@
         <v>3</v>
       </c>
       <c r="D673" s="1" t="s">
-        <v>1405</v>
+        <v>1401</v>
       </c>
       <c r="E673" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F673" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="674" spans="1:6" x14ac:dyDescent="0.25">
@@ -18334,13 +18322,13 @@
         <v>3</v>
       </c>
       <c r="D674" s="1" t="s">
-        <v>1405</v>
+        <v>1401</v>
       </c>
       <c r="E674" s="1" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="F674" s="1" t="s">
-        <v>38</v>
+        <v>5</v>
       </c>
     </row>
     <row r="675" spans="1:6" x14ac:dyDescent="0.25">
@@ -18354,10 +18342,10 @@
         <v>3</v>
       </c>
       <c r="D675" s="1" t="s">
-        <v>1405</v>
+        <v>1401</v>
       </c>
       <c r="E675" s="1" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="F675" s="1" t="s">
         <v>5</v>
@@ -18374,13 +18362,13 @@
         <v>3</v>
       </c>
       <c r="D676" s="1" t="s">
-        <v>1405</v>
+        <v>1401</v>
       </c>
       <c r="E676" s="1" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="F676" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="677" spans="1:6" x14ac:dyDescent="0.25">
@@ -18394,10 +18382,10 @@
         <v>3</v>
       </c>
       <c r="D677" s="1" t="s">
-        <v>1405</v>
+        <v>1401</v>
       </c>
       <c r="E677" s="1" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="F677" s="1" t="s">
         <v>5</v>
@@ -18414,10 +18402,10 @@
         <v>3</v>
       </c>
       <c r="D678" s="1" t="s">
-        <v>1405</v>
+        <v>1401</v>
       </c>
       <c r="E678" s="1" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="F678" s="1" t="s">
         <v>9</v>
@@ -18434,13 +18422,13 @@
         <v>3</v>
       </c>
       <c r="D679" s="1" t="s">
-        <v>1405</v>
+        <v>1401</v>
       </c>
       <c r="E679" s="1" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="F679" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="680" spans="1:6" x14ac:dyDescent="0.25">
@@ -18454,13 +18442,13 @@
         <v>3</v>
       </c>
       <c r="D680" s="1" t="s">
-        <v>1405</v>
+        <v>1401</v>
       </c>
       <c r="E680" s="1" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="F680" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="681" spans="1:6" x14ac:dyDescent="0.25">
@@ -18474,10 +18462,10 @@
         <v>3</v>
       </c>
       <c r="D681" s="1" t="s">
-        <v>1405</v>
+        <v>1401</v>
       </c>
       <c r="E681" s="1" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="F681" s="1" t="s">
         <v>9</v>
@@ -18494,13 +18482,13 @@
         <v>3</v>
       </c>
       <c r="D682" s="1" t="s">
-        <v>1405</v>
+        <v>1401</v>
       </c>
       <c r="E682" s="1" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="F682" s="1" t="s">
-        <v>5</v>
+        <v>25</v>
       </c>
     </row>
     <row r="683" spans="1:6" x14ac:dyDescent="0.25">
@@ -18514,13 +18502,13 @@
         <v>3</v>
       </c>
       <c r="D683" s="1" t="s">
-        <v>1405</v>
+        <v>1401</v>
       </c>
       <c r="E683" s="1" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="F683" s="1" t="s">
-        <v>9</v>
+        <v>38</v>
       </c>
     </row>
     <row r="684" spans="1:6" x14ac:dyDescent="0.25">
@@ -18534,10 +18522,10 @@
         <v>3</v>
       </c>
       <c r="D684" s="1" t="s">
-        <v>1405</v>
+        <v>1401</v>
       </c>
       <c r="E684" s="1" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="F684" s="1" t="s">
         <v>25</v>
@@ -18554,13 +18542,13 @@
         <v>3</v>
       </c>
       <c r="D685" s="1" t="s">
-        <v>1405</v>
+        <v>1401</v>
       </c>
       <c r="E685" s="1" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="F685" s="1" t="s">
-        <v>38</v>
+        <v>5</v>
       </c>
     </row>
     <row r="686" spans="1:6" x14ac:dyDescent="0.25">
@@ -18574,10 +18562,10 @@
         <v>3</v>
       </c>
       <c r="D686" s="1" t="s">
-        <v>1405</v>
+        <v>1401</v>
       </c>
       <c r="E686" s="1" t="s">
-        <v>55</v>
+        <v>31</v>
       </c>
       <c r="F686" s="1" t="s">
         <v>25</v>
@@ -18594,10 +18582,10 @@
         <v>3</v>
       </c>
       <c r="D687" s="1" t="s">
-        <v>1405</v>
+        <v>1401</v>
       </c>
       <c r="E687" s="1" t="s">
-        <v>55</v>
+        <v>31</v>
       </c>
       <c r="F687" s="1" t="s">
         <v>5</v>
@@ -18614,10 +18602,10 @@
         <v>3</v>
       </c>
       <c r="D688" s="1" t="s">
-        <v>1405</v>
+        <v>1401</v>
       </c>
       <c r="E688" s="1" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="F688" s="1" t="s">
         <v>25</v>
@@ -18634,13 +18622,13 @@
         <v>3</v>
       </c>
       <c r="D689" s="1" t="s">
-        <v>1405</v>
+        <v>1401</v>
       </c>
       <c r="E689" s="1" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="F689" s="1" t="s">
-        <v>5</v>
+        <v>25</v>
       </c>
     </row>
     <row r="690" spans="1:6" x14ac:dyDescent="0.25">
@@ -18654,10 +18642,10 @@
         <v>3</v>
       </c>
       <c r="D690" s="1" t="s">
-        <v>1405</v>
+        <v>1401</v>
       </c>
       <c r="E690" s="1" t="s">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="F690" s="1" t="s">
         <v>25</v>
@@ -18674,10 +18662,10 @@
         <v>3</v>
       </c>
       <c r="D691" s="1" t="s">
-        <v>1405</v>
+        <v>1401</v>
       </c>
       <c r="E691" s="1" t="s">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="F691" s="1" t="s">
         <v>25</v>
@@ -18694,13 +18682,13 @@
         <v>3</v>
       </c>
       <c r="D692" s="1" t="s">
-        <v>1405</v>
+        <v>1401</v>
       </c>
       <c r="E692" s="1" t="s">
-        <v>34</v>
+        <v>63</v>
       </c>
       <c r="F692" s="1" t="s">
-        <v>25</v>
+        <v>78</v>
       </c>
     </row>
     <row r="693" spans="1:6" x14ac:dyDescent="0.25">
@@ -18714,10 +18702,10 @@
         <v>3</v>
       </c>
       <c r="D693" s="1" t="s">
-        <v>1405</v>
+        <v>1401</v>
       </c>
       <c r="E693" s="1" t="s">
-        <v>34</v>
+        <v>63</v>
       </c>
       <c r="F693" s="1" t="s">
         <v>25</v>
@@ -18734,13 +18722,13 @@
         <v>3</v>
       </c>
       <c r="D694" s="1" t="s">
-        <v>1405</v>
+        <v>1401</v>
       </c>
       <c r="E694" s="1" t="s">
-        <v>37</v>
+        <v>66</v>
       </c>
       <c r="F694" s="1" t="s">
-        <v>78</v>
+        <v>9</v>
       </c>
     </row>
     <row r="695" spans="1:6" x14ac:dyDescent="0.25">
@@ -18754,13 +18742,13 @@
         <v>3</v>
       </c>
       <c r="D695" s="1" t="s">
-        <v>1405</v>
+        <v>1401</v>
       </c>
       <c r="E695" s="1" t="s">
-        <v>37</v>
+        <v>66</v>
       </c>
       <c r="F695" s="1" t="s">
-        <v>25</v>
+        <v>5</v>
       </c>
     </row>
     <row r="696" spans="1:6" x14ac:dyDescent="0.25">
@@ -18774,13 +18762,13 @@
         <v>3</v>
       </c>
       <c r="D696" s="1" t="s">
-        <v>1405</v>
+        <v>1401</v>
       </c>
       <c r="E696" s="1" t="s">
-        <v>66</v>
+        <v>98</v>
       </c>
       <c r="F696" s="1" t="s">
-        <v>9</v>
+        <v>78</v>
       </c>
     </row>
     <row r="697" spans="1:6" x14ac:dyDescent="0.25">
@@ -18794,13 +18782,13 @@
         <v>3</v>
       </c>
       <c r="D697" s="1" t="s">
-        <v>1405</v>
+        <v>1401</v>
       </c>
       <c r="E697" s="1" t="s">
-        <v>66</v>
+        <v>101</v>
       </c>
       <c r="F697" s="1" t="s">
-        <v>5</v>
+        <v>71</v>
       </c>
     </row>
     <row r="698" spans="1:6" x14ac:dyDescent="0.25">
@@ -18814,53 +18802,53 @@
         <v>3</v>
       </c>
       <c r="D698" s="1" t="s">
-        <v>1405</v>
+        <v>1458</v>
       </c>
       <c r="E698" s="1" t="s">
-        <v>98</v>
+        <v>8</v>
       </c>
       <c r="F698" s="1" t="s">
-        <v>78</v>
+        <v>5</v>
       </c>
     </row>
     <row r="699" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A699" s="1" t="s">
+        <v>1459</v>
+      </c>
+      <c r="B699" s="1" t="s">
+        <v>1460</v>
+      </c>
+      <c r="C699" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D699" s="1" t="s">
         <v>1458</v>
       </c>
-      <c r="B699" s="1" t="s">
-        <v>1459</v>
-      </c>
-      <c r="C699" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D699" s="1" t="s">
-        <v>1405</v>
-      </c>
       <c r="E699" s="1" t="s">
-        <v>101</v>
+        <v>12</v>
       </c>
       <c r="F699" s="1" t="s">
-        <v>71</v>
+        <v>25</v>
       </c>
     </row>
     <row r="700" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A700" s="1" t="s">
-        <v>1460</v>
+        <v>1461</v>
       </c>
       <c r="B700" s="1" t="s">
-        <v>1461</v>
+        <v>1462</v>
       </c>
       <c r="C700" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D700" s="1" t="s">
-        <v>1462</v>
+        <v>1458</v>
       </c>
       <c r="E700" s="1" t="s">
         <v>15</v>
       </c>
       <c r="F700" s="1" t="s">
-        <v>5</v>
+        <v>25</v>
       </c>
     </row>
     <row r="701" spans="1:6" x14ac:dyDescent="0.25">
@@ -18874,7 +18862,7 @@
         <v>3</v>
       </c>
       <c r="D701" s="1" t="s">
-        <v>1462</v>
+        <v>1458</v>
       </c>
       <c r="E701" s="1" t="s">
         <v>18</v>
@@ -18894,7 +18882,7 @@
         <v>3</v>
       </c>
       <c r="D702" s="1" t="s">
-        <v>1462</v>
+        <v>1458</v>
       </c>
       <c r="E702" s="1" t="s">
         <v>21</v>
@@ -18914,7 +18902,7 @@
         <v>3</v>
       </c>
       <c r="D703" s="1" t="s">
-        <v>1462</v>
+        <v>1458</v>
       </c>
       <c r="E703" s="1" t="s">
         <v>24</v>
@@ -18934,10 +18922,10 @@
         <v>3</v>
       </c>
       <c r="D704" s="1" t="s">
-        <v>1462</v>
+        <v>1458</v>
       </c>
       <c r="E704" s="1" t="s">
-        <v>55</v>
+        <v>28</v>
       </c>
       <c r="F704" s="1" t="s">
         <v>25</v>
@@ -18954,10 +18942,10 @@
         <v>3</v>
       </c>
       <c r="D705" s="1" t="s">
-        <v>1462</v>
+        <v>1458</v>
       </c>
       <c r="E705" s="1" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="F705" s="1" t="s">
         <v>25</v>
@@ -18974,10 +18962,10 @@
         <v>3</v>
       </c>
       <c r="D706" s="1" t="s">
-        <v>1462</v>
+        <v>1458</v>
       </c>
       <c r="E706" s="1" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="F706" s="1" t="s">
         <v>25</v>
@@ -18994,10 +18982,10 @@
         <v>3</v>
       </c>
       <c r="D707" s="1" t="s">
-        <v>1462</v>
+        <v>1458</v>
       </c>
       <c r="E707" s="1" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="F707" s="1" t="s">
         <v>25</v>
@@ -19014,52 +19002,12 @@
         <v>3</v>
       </c>
       <c r="D708" s="1" t="s">
-        <v>1462</v>
+        <v>1458</v>
       </c>
       <c r="E708" s="1" t="s">
-        <v>37</v>
+        <v>63</v>
       </c>
       <c r="F708" s="1" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="709" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A709" s="1" t="s">
-        <v>1479</v>
-      </c>
-      <c r="B709" s="1" t="s">
-        <v>1480</v>
-      </c>
-      <c r="C709" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D709" s="1" t="s">
-        <v>1462</v>
-      </c>
-      <c r="E709" s="1" t="s">
-        <v>66</v>
-      </c>
-      <c r="F709" s="1" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="710" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A710" s="1" t="s">
-        <v>1481</v>
-      </c>
-      <c r="B710" s="1" t="s">
-        <v>1482</v>
-      </c>
-      <c r="C710" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D710" s="1" t="s">
-        <v>1462</v>
-      </c>
-      <c r="E710" s="1" t="s">
-        <v>98</v>
-      </c>
-      <c r="F710" s="1" t="s">
         <v>25</v>
       </c>
     </row>
